--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4065964826819056</v>
+        <v>0.4032585977661874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>3.713062180061955</v>
+        <v>2.86164737310064</v>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>10.51813182089105</v>
+        <v>11.25064972637323</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>6.061857289511852</v>
+        <v>6.939761134689082</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -763,10 +763,10 @@
         <v>52.17391304347826</v>
       </c>
       <c r="AG2" t="n">
-        <v>36.55360853278271</v>
+        <v>36.70732709956448</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.62030451069555</v>
+        <v>15.46658594391378</v>
       </c>
       <c r="AI2" t="n">
         <v>38.13741307280403</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6521398815877748</v>
+        <v>0.6542260695433766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,37 +816,37 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>2.023684981443985</v>
+        <v>2.350057572361441</v>
       </c>
       <c r="L3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>48.21428571428572</v>
+        <v>49.0566037735849</v>
       </c>
       <c r="N3" t="n">
-        <v>15.17907162020953</v>
+        <v>14.60158168146134</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>5.857772163045261</v>
+        <v>5.520214215457631</v>
       </c>
       <c r="Q3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
-        <v>58.33333333333334</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="S3" t="n">
-        <v>49.04674356596731</v>
+        <v>49.99428392849743</v>
       </c>
       <c r="T3" t="n">
-        <v>9.286589767366024</v>
+        <v>7.148573214359715</v>
       </c>
       <c r="U3" t="n">
-        <v>42.20025157487166</v>
+        <v>40.85741114397492</v>
       </c>
       <c r="V3" t="n">
         <v>72</v>
@@ -866,19 +866,19 @@
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AF3" t="n">
-        <v>60.52631578947368</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="AG3" t="n">
-        <v>36.17984012480561</v>
+        <v>36.72013311457034</v>
       </c>
       <c r="AH3" t="n">
-        <v>24.34647566466808</v>
+        <v>22.73932634488911</v>
       </c>
       <c r="AI3" t="n">
-        <v>44.71786799604255</v>
+        <v>43.48596473022936</v>
       </c>
       <c r="AJ3" t="n">
         <v>67</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447808971432167</v>
+        <v>1.479101671853931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,19 +922,19 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>17.72788870900636</v>
+        <v>15.33976973013975</v>
       </c>
       <c r="K4" t="n">
-        <v>12.09935578847592</v>
+        <v>14.52225247400449</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>53.84615384615385</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N4" t="n">
-        <v>16.66999385576534</v>
+        <v>14.70324685402717</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -964,40 +964,40 @@
         <v>63.01369863013699</v>
       </c>
       <c r="X4" t="n">
-        <v>13.56745302298568</v>
+        <v>15.08759256260652</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.292709482718279</v>
+        <v>0.4912259228070259</v>
       </c>
       <c r="Z4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
-        <v>50.76923076923077</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.45385398054107</v>
+        <v>13.0229670175108</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.82132461710844</v>
+        <v>9.555714222563561</v>
       </c>
       <c r="AE4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>60</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="AG4" t="n">
-        <v>37.7676158108321</v>
+        <v>38.67994283229618</v>
       </c>
       <c r="AH4" t="n">
-        <v>22.2323841891679</v>
+        <v>20.41096625861292</v>
       </c>
       <c r="AI4" t="n">
-        <v>45.45185459035139</v>
+        <v>44.4097537410319</v>
       </c>
       <c r="AJ4" t="n">
         <v>65</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2367814411188314</v>
+        <v>0.2374072894945805</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>15.5457304755158</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3536689523836456</v>
+        <v>0.6189185446555445</v>
       </c>
       <c r="L5" t="n">
         <v>50</v>
@@ -1053,13 +1053,13 @@
         <v>56</v>
       </c>
       <c r="N5" t="n">
-        <v>14.35145358327265</v>
+        <v>14.71420655378216</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.637004780435093</v>
+        <v>2.366435149357837</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1068,10 +1068,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S5" t="n">
-        <v>42.13314487202579</v>
+        <v>41.85307399439394</v>
       </c>
       <c r="T5" t="n">
-        <v>18.84246488407177</v>
+        <v>19.12253576170362</v>
       </c>
       <c r="U5" t="n">
         <v>45.72685693412379</v>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C6" t="n">
-        <v>1.779511627612801</v>
+        <v>1.78785622046829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>8.737734413171761</v>
+        <v>9.24763393145891</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1191,22 +1191,22 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.893043407329188</v>
+        <v>2.437683631294196</v>
       </c>
       <c r="Z6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="n">
         <v>40</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.10020856122188</v>
+        <v>12.87688099612406</v>
       </c>
       <c r="AC6" t="n">
         <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1101430797789904</v>
+        <v>0.5763663570478528</v>
       </c>
       <c r="AE6" t="n">
         <v>50</v>
@@ -1215,19 +1215,19 @@
         <v>48</v>
       </c>
       <c r="AG6" t="n">
-        <v>41.2536494731464</v>
+        <v>41.96399064665</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.746350526853597</v>
+        <v>6.036009353350003</v>
       </c>
       <c r="AI6" t="n">
         <v>34.79713528657805</v>
       </c>
       <c r="AJ6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK6" t="n">
-        <v>43.58974358974359</v>
+        <v>44.30379746835443</v>
       </c>
     </row>
     <row r="7">
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C7" t="n">
-        <v>2.305228931069945</v>
+        <v>2.29688417903892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1264,27 +1264,17 @@
       <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="n">
-        <v>11.64775322580256</v>
-      </c>
-      <c r="K7" t="n">
-        <v>10.80862483648433</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>20</v>
-      </c>
-      <c r="M7" t="n">
-        <v>70</v>
-      </c>
-      <c r="N7" t="n">
-        <v>10.77515611036809</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>8</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
         <v>49</v>
       </c>
@@ -1292,10 +1282,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S7" t="n">
-        <v>53.5492356881112</v>
+        <v>53.2169356428875</v>
       </c>
       <c r="T7" t="n">
-        <v>7.67525410780717</v>
+        <v>8.007554153030867</v>
       </c>
       <c r="U7" t="n">
         <v>47.24599944352045</v>
@@ -1307,25 +1297,25 @@
         <v>69.11764705882354</v>
       </c>
       <c r="X7" t="n">
-        <v>13.79329344082609</v>
+        <v>14.22876300591287</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.098090337374736</v>
+        <v>2.824364072247909</v>
       </c>
       <c r="Z7" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA7" t="n">
-        <v>40.35087719298246</v>
+        <v>34</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.08321249499121</v>
+        <v>10.65854591283888</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.964099140277643</v>
+        <v>2.238869760903472</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1356,19 +1346,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3306595423841233</v>
+        <v>0.377807215817795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1383,27 +1373,17 @@
       <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>15.54295656794631</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.132474061947723</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>8</v>
-      </c>
-      <c r="M8" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>12.06981187684528</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>8</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.727535867140962</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>5</v>
       </c>
@@ -1426,25 +1406,25 @@
         <v>33.33333333333334</v>
       </c>
       <c r="X8" t="n">
-        <v>13.77628913057349</v>
+        <v>21.38322708563636</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.597202488038468</v>
+        <v>1.03824392289974</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
-        <v>40</v>
+        <v>62.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.447062907011711</v>
+        <v>13.84835456004712</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.4359148454454398</v>
+        <v>7.034794402472421</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1475,14 +1455,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5903889321023117</v>
+        <v>0.5991508896807316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1492,7 +1472,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1538,22 +1518,22 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.069715706953925</v>
+        <v>3.660856091443943</v>
       </c>
       <c r="Z9" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>45.71428571428572</v>
+        <v>50</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.71464565042278</v>
+        <v>11.62374908694097</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>0.3520312666240533</v>
       </c>
       <c r="AE9" t="n">
         <v>33</v>
@@ -1584,10 +1564,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C10" t="n">
-        <v>1.934931976079071</v>
+        <v>1.933888822436521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1595,7 @@
         <v>10.51321892894885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3787862166716227</v>
+        <v>0.324670362589341</v>
       </c>
       <c r="L10" t="n">
         <v>43</v>
@@ -1630,7 +1610,7 @@
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.600001748571426</v>
+        <v>5.656963154625005</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1639,10 +1619,10 @@
         <v>48.78048780487805</v>
       </c>
       <c r="S10" t="n">
-        <v>38.05889609023404</v>
+        <v>38.19091809791883</v>
       </c>
       <c r="T10" t="n">
-        <v>10.72159171464401</v>
+        <v>10.58956970695922</v>
       </c>
       <c r="U10" t="n">
         <v>34.25442955443266</v>
@@ -1671,10 +1651,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="AG10" t="n">
-        <v>41.89811398522832</v>
+        <v>42.32591351939572</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.27429980787512</v>
+        <v>12.84650027370773</v>
       </c>
       <c r="AI10" t="n">
         <v>37.54796321097091</v>
@@ -1693,14 +1673,14 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C11" t="n">
-        <v>8.188256610361568</v>
+        <v>8.464675464087149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1710,7 +1690,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1738,10 +1718,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.67895135020238</v>
+        <v>51.71186774256578</v>
       </c>
       <c r="T11" t="n">
-        <v>9.545538445715984</v>
+        <v>9.512622053352587</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1756,22 +1736,22 @@
         <v>21.94683558783998</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.791099962568256</v>
+        <v>0.5432835918778967</v>
       </c>
       <c r="Z11" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
         <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>13.10279264449323</v>
+        <v>12.17036391195194</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.470136253082134</v>
       </c>
       <c r="AE11" t="n">
         <v>46</v>
@@ -1780,10 +1760,10 @@
         <v>56.52173913043478</v>
       </c>
       <c r="AG11" t="n">
-        <v>23.4197438791009</v>
+        <v>23.5034689084781</v>
       </c>
       <c r="AH11" t="n">
-        <v>33.10199525133389</v>
+        <v>33.01827022195668</v>
       </c>
       <c r="AI11" t="n">
         <v>42.24743369429499</v>
@@ -1802,19 +1782,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C12" t="n">
-        <v>6.696637890257486</v>
+        <v>6.967841293912774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1833,22 +1813,22 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>1.98570293884035</v>
+        <v>6.11596505162828</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="M12" t="n">
-        <v>54.83870967741935</v>
+        <v>62.5</v>
       </c>
       <c r="N12" t="n">
-        <v>22.3308485741437</v>
+        <v>19.57997002214874</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>3.936137071651102</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1875,16 +1855,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.399991932332286</v>
+        <v>5.730832727099633</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>20</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.2369542434721</v>
+        <v>8.917895439582416</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1921,19 +1901,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2167541120144304</v>
+        <v>0.2265591439605589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1952,7 +1932,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>2.667988665363508</v>
+        <v>7.312250771180584</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1963,7 +1943,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.271410363591975</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2014,19 +1994,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C14" t="n">
-        <v>8.490752714438619</v>
+        <v>8.683724367039497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2041,27 +2021,17 @@
       <c r="I14" t="n">
         <v>10</v>
       </c>
-      <c r="J14" t="n">
-        <v>10.38986202355683</v>
-      </c>
-      <c r="K14" t="n">
-        <v>9.503072610439567</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>14</v>
-      </c>
-      <c r="M14" t="n">
-        <v>50</v>
-      </c>
-      <c r="N14" t="n">
-        <v>11.00055185791263</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
         <v>2</v>
       </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
         <v>41</v>
       </c>
@@ -2084,25 +2054,25 @@
         <v>58.69565217391305</v>
       </c>
       <c r="X14" t="n">
-        <v>11.79764636037071</v>
+        <v>13.13901871403786</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.874145545340355</v>
+        <v>0.8338296605122197</v>
       </c>
       <c r="Z14" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>37.2093023255814</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.14751110256402</v>
+        <v>12.11589101364306</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.1282582000015076</v>
+        <v>1.175975975975962</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2111,10 +2081,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>27.69927619583165</v>
+        <v>27.82424138658631</v>
       </c>
       <c r="AH14" t="n">
-        <v>24.93230275153677</v>
+        <v>24.80733756078211</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2133,10 +2103,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C15" t="n">
-        <v>13.83137358641967</v>
+        <v>14.2381786919026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,25 +2163,25 @@
         <v>80.64516129032258</v>
       </c>
       <c r="X15" t="n">
-        <v>31.71848563863831</v>
+        <v>35.23869365533523</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.13016216504358</v>
+        <v>0.8714596949891185</v>
       </c>
       <c r="Z15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.05263157894737</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.614455413332683</v>
+        <v>10.07267228124085</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.971227251088298</v>
+        <v>9.208791208791201</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2220,10 +2190,10 @@
         <v>56.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>24.32006656725254</v>
+        <v>24.48545745529968</v>
       </c>
       <c r="AH15" t="n">
-        <v>31.92993343274746</v>
+        <v>31.76454254470032</v>
       </c>
       <c r="AI15" t="n">
         <v>39.32559113685198</v>
@@ -2242,10 +2212,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C16" t="n">
-        <v>35.69454028109208</v>
+        <v>35.86143468334149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,37 +2243,37 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>2.507506556918959</v>
+        <v>2.986793554262834</v>
       </c>
       <c r="L16" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>66.66666666666667</v>
+        <v>72.85714285714286</v>
       </c>
       <c r="N16" t="n">
-        <v>17.85946578771896</v>
+        <v>17.49375999887909</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.309214412430109</v>
+        <v>6.809811436688706</v>
       </c>
       <c r="Q16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R16" t="n">
-        <v>67.85714285714286</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="S16" t="n">
-        <v>53.94310959502992</v>
+        <v>54.08915069114214</v>
       </c>
       <c r="T16" t="n">
-        <v>13.91403326211294</v>
+        <v>16.28121967922823</v>
       </c>
       <c r="U16" t="n">
-        <v>49.33884318085762</v>
+        <v>51.51931703585186</v>
       </c>
       <c r="V16" t="n">
         <v>105</v>
@@ -2315,13 +2285,13 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.79656861964465</v>
+        <v>11.38416216082359</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA16" t="n">
-        <v>55.55555555555556</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="AB16" t="n">
         <v>13.40563990076058</v>
@@ -2361,10 +2331,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6984530638173434</v>
+        <v>0.6972013272198063</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,22 +2362,22 @@
         <v>14.65098631060165</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4199141852733401</v>
+        <v>0.2399460697062761</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M17" t="n">
-        <v>71.875</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N17" t="n">
-        <v>15.55663843377814</v>
+        <v>15.54776227613241</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.548389058311189</v>
+        <v>7.74147855675964</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2416,10 +2386,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="S17" t="n">
-        <v>47.40300921905087</v>
+        <v>47.41500502052035</v>
       </c>
       <c r="T17" t="n">
-        <v>19.2636574476158</v>
+        <v>19.25166164614632</v>
       </c>
       <c r="U17" t="n">
         <v>52.07048830990042</v>
@@ -2470,10 +2440,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09930217413661169</v>
+        <v>0.09951078692397336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,22 +2471,22 @@
         <v>20.56707245057805</v>
       </c>
       <c r="K18" t="n">
-        <v>2.412492439497371</v>
+        <v>2.627639345335187</v>
       </c>
       <c r="L18" t="n">
         <v>37</v>
       </c>
       <c r="M18" t="n">
-        <v>64.86486486486487</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N18" t="n">
-        <v>14.78190186872253</v>
+        <v>16.73453332777512</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.408771508012202</v>
+        <v>7.183601514848559</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2525,10 +2495,10 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>41.81942374818963</v>
+        <v>41.8298132902607</v>
       </c>
       <c r="T18" t="n">
-        <v>35.37355870795073</v>
+        <v>35.36316916587966</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
@@ -2557,10 +2527,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.84306972996058</v>
+        <v>39.89163227852313</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.68073979384894</v>
+        <v>19.6321772452864</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2579,10 +2549,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02545139696888869</v>
+        <v>0.02503416138050118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,22 +2580,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>3.271635229340042</v>
+        <v>1.578659337237709</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="M19" t="n">
-        <v>57.57575757575758</v>
+        <v>59.57446808510638</v>
       </c>
       <c r="N19" t="n">
-        <v>15.69071474462519</v>
+        <v>18.7988403494865</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>6.51521083763027</v>
+        <v>8.290462502368467</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2688,10 +2658,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C20" t="n">
-        <v>1.708581474946866</v>
+        <v>1.717969221236287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2719,7 +2689,7 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>2.564774385009549</v>
+        <v>3.128313258792592</v>
       </c>
       <c r="L20" t="n">
         <v>37</v>
@@ -2728,7 +2698,7 @@
         <v>48.64864864864865</v>
       </c>
       <c r="N20" t="n">
-        <v>12.44028716456575</v>
+        <v>11.99625976033842</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -2797,10 +2767,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9446222912802515</v>
+        <v>0.9542187799088133</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,22 +2798,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>1.681472415808671</v>
+        <v>2.714462112093785</v>
       </c>
       <c r="L21" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>54.09836065573771</v>
+        <v>54.23728813559322</v>
       </c>
       <c r="N21" t="n">
-        <v>18.6173419760409</v>
+        <v>16.94187474368925</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.214040212117333</v>
+        <v>5.145855587636761</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2852,10 +2822,10 @@
         <v>72.5</v>
       </c>
       <c r="S21" t="n">
-        <v>46.4956508342762</v>
+        <v>46.51066584929121</v>
       </c>
       <c r="T21" t="n">
-        <v>26.0043491657238</v>
+        <v>25.98933415070879</v>
       </c>
       <c r="U21" t="n">
         <v>57.16504419378943</v>
@@ -2884,10 +2854,10 @@
         <v>62.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>36.07522177823446</v>
+        <v>36.18401807453076</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.42477822176554</v>
+        <v>26.31598192546924</v>
       </c>
       <c r="AI21" t="n">
         <v>47.0324391373011</v>
@@ -2906,10 +2876,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3365008210114562</v>
+        <v>0.3412990653257371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,25 +2930,25 @@
         <v>9.453120573423075</v>
       </c>
       <c r="V22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W22" t="n">
-        <v>73.68421052631579</v>
+        <v>75</v>
       </c>
       <c r="X22" t="n">
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.291261175033327</v>
+        <v>6.983564708456846</v>
       </c>
       <c r="Z22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>54.54545454545455</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.89827904879843</v>
+        <v>10.46288164843365</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
@@ -3007,10 +2977,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7823175105440988</v>
+        <v>0.7710521191994076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3008,7 @@
         <v>24.33755492423044</v>
       </c>
       <c r="K23" t="n">
-        <v>1.791530530164764</v>
+        <v>0.3257299932448721</v>
       </c>
       <c r="L23" t="n">
         <v>14</v>
@@ -3047,13 +3017,13 @@
         <v>71.42857142857143</v>
       </c>
       <c r="N23" t="n">
-        <v>20.79983647085491</v>
+        <v>19.65944222052416</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.152000420000012</v>
+        <v>4.659093940377868</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3080,7 +3050,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>22.98203912082888</v>
+        <v>24.09109964699624</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3122,10 +3092,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1773253023899957</v>
+        <v>0.17878562194252</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,22 +3123,22 @@
         <v>23.5093122581746</v>
       </c>
       <c r="K24" t="n">
-        <v>4.938266681908465</v>
+        <v>5.802460345069749</v>
       </c>
       <c r="L24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>58.33333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>11.77589766891377</v>
+        <v>12.16385997311514</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.823534329411783</v>
+        <v>3.967336526239729</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3231,10 +3201,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C25" t="n">
-        <v>3.527730554803838</v>
+        <v>3.634125545352363</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,22 +3232,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8949880342516314</v>
+        <v>3.937941891280161</v>
       </c>
       <c r="L25" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="M25" t="n">
-        <v>55.17241379310344</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="N25" t="n">
-        <v>17.92716970565471</v>
+        <v>15.73792626955893</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.041987024505492</v>
+        <v>3.908157151090008</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3286,10 +3256,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="S25" t="n">
-        <v>36.24209861282891</v>
+        <v>36.26937967334133</v>
       </c>
       <c r="T25" t="n">
-        <v>30.42456805383776</v>
+        <v>30.39728699332534</v>
       </c>
       <c r="U25" t="n">
         <v>52.07048830990042</v>
@@ -3318,10 +3288,10 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG25" t="n">
-        <v>54.26633071956535</v>
+        <v>54.42559590069766</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.6077941341994944</v>
+        <v>-0.7670593153318066</v>
       </c>
       <c r="AI25" t="n">
         <v>38.74647126766948</v>
@@ -3340,10 +3310,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C26" t="n">
-        <v>0.438515051506747</v>
+        <v>0.4443563301340799</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,10 +3409,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C27" t="n">
-        <v>42.72496697584838</v>
+        <v>43.74719518962601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3467,10 +3437,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>61.00029220182797</v>
+        <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>29.61414146757517</v>
+        <v>32.71526106323493</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3495,25 +3465,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>30.77516122657997</v>
+        <v>33.34814261336958</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.8877983770887776</v>
+        <v>0.474608448030378</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA27" t="n">
-        <v>15.38461538461539</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>23.16561142243133</v>
+        <v>25.80591578680818</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.149036703429088</v>
+        <v>4.546971864568428</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3534,14 +3504,14 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C28" t="n">
-        <v>1.547945517234766</v>
+        <v>1.58028137129908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3551,7 +3521,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3597,22 +3567,22 @@
         <v>18.63435792130579</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.421796057861329</v>
+        <v>4.466991374761708</v>
       </c>
       <c r="Z28" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>56.52173913043478</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.03249322773166</v>
+        <v>10.57311832441738</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.604689988621688</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3643,14 +3613,14 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3976259023024599</v>
+        <v>0.4264152088039909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3660,14 +3630,10 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3678,17 +3644,13 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>9.996198215136932</v>
+        <v>17.96025248343742</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
-      </c>
-      <c r="M29" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="N29" t="n">
-        <v>20.80812660431195</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>4</v>
       </c>
@@ -3720,10 +3682,10 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.20048884076401</v>
+        <v>6.915944206029712</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3731,7 +3693,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.313194475320724</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3762,10 +3724,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C30" t="n">
-        <v>0.395122508382227</v>
+        <v>0.4053447859304072</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3741,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3793,16 +3755,16 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>7.936755103062842</v>
+        <v>10.72920414078284</v>
       </c>
       <c r="L30" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M30" t="n">
-        <v>52.63157894736842</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N30" t="n">
-        <v>11.62432949210607</v>
+        <v>15.83763170086855</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3831,17 +3793,27 @@
       <c r="W30" t="n">
         <v>64.17910447761194</v>
       </c>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
+      <c r="X30" t="n">
+        <v>11.24210402874228</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.4610663313478036</v>
+      </c>
       <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>45.6140350877193</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>12.67283334448918</v>
+      </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
-      <c r="AD30" t="inlineStr"/>
+      <c r="AD30" t="n">
+        <v>9.58311820016643</v>
+      </c>
       <c r="AE30" t="n">
         <v>47</v>
       </c>
@@ -3871,10 +3843,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1798287161289388</v>
+        <v>0.1833752236370647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,22 +3874,22 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>3.272528412487108</v>
+        <v>5.309226473187412</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>42.85714285714285</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="N31" t="n">
-        <v>5.672894194702997</v>
+        <v>6.439556915855582</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>6.514289609180768</v>
+        <v>4.454285425794957</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3980,10 +3952,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C32" t="n">
-        <v>2.278108527075925</v>
+        <v>2.321918434923376</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4011,16 +3983,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>4.529573858716951</v>
+        <v>6.539763866636217</v>
       </c>
       <c r="L32" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="M32" t="n">
-        <v>55.55555555555556</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="N32" t="n">
-        <v>10.44660475484212</v>
+        <v>12.00261846142334</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4053,22 +4025,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.394499683152223</v>
+        <v>5.613619454300434</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA32" t="n">
-        <v>35.29411764705883</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB32" t="n">
-        <v>14.63702839182677</v>
+        <v>9.992786337953312</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.6538491933805957</v>
+        <v>2.528310262457978</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4099,10 +4071,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C33" t="n">
-        <v>1.723184671306581</v>
+        <v>1.73570171976535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4130,16 +4102,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.154438728343336</v>
+        <v>5.918270502809686</v>
       </c>
       <c r="L33" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M33" t="n">
-        <v>66.66666666666667</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N33" t="n">
-        <v>11.74490182699344</v>
+        <v>11.16684157499097</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4208,10 +4180,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7898277713710203</v>
+        <v>0.7960862956004049</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,16 +4211,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>4.068518225308626</v>
+        <v>4.893147804613807</v>
       </c>
       <c r="L34" t="n">
         <v>22</v>
       </c>
       <c r="M34" t="n">
-        <v>68.18181818181819</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N34" t="n">
-        <v>9.358531883627629</v>
+        <v>9.616943003587124</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4295,10 +4267,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AG34" t="n">
-        <v>30.48141820696055</v>
+        <v>31.08262311990635</v>
       </c>
       <c r="AH34" t="n">
-        <v>23.3647356391933</v>
+        <v>22.76353072624749</v>
       </c>
       <c r="AI34" t="n">
         <v>38.56944827051576</v>
@@ -4317,10 +4289,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C35" t="n">
-        <v>1.943276728110096</v>
+        <v>1.965181522858285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4339,7 +4311,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4352,16 +4324,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.552712789581319</v>
+        <v>10.78760108575154</v>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>80</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N35" t="n">
-        <v>11.21034076274254</v>
+        <v>10.73178574240798</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4394,16 +4366,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.485497659789907</v>
+        <v>5.431393552994201</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
-        <v>41.66666666666666</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB35" t="n">
-        <v>14.75083324357035</v>
+        <v>14.37724655220632</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4440,19 +4412,19 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07906622223118491</v>
+        <v>0.07990069340795994</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4468,25 +4440,25 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>16.73047826371691</v>
+        <v>14.25367779956082</v>
       </c>
       <c r="K36" t="n">
-        <v>1.336897055248931</v>
+        <v>2.406414699448067</v>
       </c>
       <c r="L36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>57.14285714285715</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N36" t="n">
-        <v>16.31362134925253</v>
+        <v>20.67596617644671</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0.6543548934496712</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4549,10 +4521,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06446296099127172</v>
+        <v>0.06571467297188434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4580,22 +4552,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>4.934816764504912</v>
+        <v>6.972392533717642</v>
       </c>
       <c r="L37" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="M37" t="n">
-        <v>59.64912280701754</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N37" t="n">
-        <v>20.24658150753529</v>
+        <v>18.81710672338293</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>2.921035486604984</v>
+        <v>0.9606286649692874</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4622,16 +4594,16 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>6.424585273485894</v>
+        <v>4.60758112253119</v>
       </c>
       <c r="Z37" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA37" t="n">
-        <v>50</v>
+        <v>56.14035087719298</v>
       </c>
       <c r="AB37" t="n">
-        <v>12.99312740151091</v>
+        <v>13.38451986162349</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
@@ -4668,10 +4640,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C38" t="n">
-        <v>1.650168370322465</v>
+        <v>1.664771726066333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4699,22 +4671,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>4.154947659085906</v>
+        <v>5.076678908153798</v>
       </c>
       <c r="L38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>48.88888888888889</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="N38" t="n">
-        <v>11.25045014547</v>
+        <v>10.80256591746088</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>5.611881597834212</v>
+        <v>4.685455557792828</v>
       </c>
       <c r="Q38" t="n">
         <v>44</v>
@@ -4723,10 +4695,10 @@
         <v>52.27272727272727</v>
       </c>
       <c r="S38" t="n">
-        <v>56.00644648192495</v>
+        <v>56.70632663816432</v>
       </c>
       <c r="T38" t="n">
-        <v>-3.733719209197673</v>
+        <v>-4.433599365437047</v>
       </c>
       <c r="U38" t="n">
         <v>37.93546556062164</v>
@@ -4749,19 +4721,19 @@
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF38" t="n">
-        <v>57.57575757575758</v>
+        <v>59.375</v>
       </c>
       <c r="AG38" t="n">
-        <v>19.5580704581568</v>
+        <v>18.45430687339174</v>
       </c>
       <c r="AH38" t="n">
-        <v>38.01768711760079</v>
+        <v>40.92069312660826</v>
       </c>
       <c r="AI38" t="n">
-        <v>40.80726333731245</v>
+        <v>42.26002487538288</v>
       </c>
       <c r="AJ38" t="n">
         <v>67</v>
@@ -4777,10 +4749,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C39" t="n">
-        <v>2.726637233121209</v>
+        <v>2.766274844540915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4797,7 +4769,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>5</v>
       </c>
@@ -4805,19 +4781,19 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>11.93511378024422</v>
+        <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>7.932571531764521</v>
+        <v>9.501606560677555</v>
       </c>
       <c r="L39" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="M39" t="n">
-        <v>61.29032258064516</v>
+        <v>75</v>
       </c>
       <c r="N39" t="n">
-        <v>13.14253392431168</v>
+        <v>14.21313148586994</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4850,22 +4826,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.096418018725832</v>
+        <v>0.6731761983503004</v>
       </c>
       <c r="Z39" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AA39" t="n">
-        <v>37.25490196078432</v>
+        <v>44.89795918367347</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.38546353999404</v>
+        <v>11.73574855497086</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.987169725843942</v>
+        <v>5.362925741275171</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4874,10 +4850,10 @@
         <v>60</v>
       </c>
       <c r="AG39" t="n">
-        <v>37.79622718899726</v>
+        <v>38.15817532762239</v>
       </c>
       <c r="AH39" t="n">
-        <v>22.20377281100274</v>
+        <v>21.84182467237761</v>
       </c>
       <c r="AI39" t="n">
         <v>45.45185459035139</v>
@@ -4896,10 +4872,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2355297243400047</v>
+        <v>0.238658986454697</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4927,16 +4903,16 @@
         <v>11.14545861980583</v>
       </c>
       <c r="K40" t="n">
-        <v>6.993287637341705</v>
+        <v>8.414806906164806</v>
       </c>
       <c r="L40" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>68.75</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N40" t="n">
-        <v>11.60739138857389</v>
+        <v>13.02965706001775</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4969,22 +4945,22 @@
         <v>35.30475215033053</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.931604962248038</v>
+        <v>3.668520535304176</v>
       </c>
       <c r="Z40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="n">
-        <v>10</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB40" t="n">
-        <v>24.60025056300582</v>
+        <v>16.92890853805427</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.07194298139230337</v>
+        <v>1.382185213073361</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -5015,10 +4991,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C41" t="n">
-        <v>1.696064426488097</v>
+        <v>1.756563520046526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5032,14 +5008,10 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>5</v>
       </c>
@@ -5050,17 +5022,13 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>12.08549860086643</v>
+        <v>16.08361975740642</v>
       </c>
       <c r="L41" t="n">
-        <v>11</v>
-      </c>
-      <c r="M41" t="n">
-        <v>81.81818181818181</v>
-      </c>
-      <c r="N41" t="n">
-        <v>12.26057868294358</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>10</v>
       </c>
@@ -5092,22 +5060,22 @@
         <v>19.10146270395254</v>
       </c>
       <c r="Y41" t="n">
-        <v>5.890745540653453</v>
+        <v>2.533842052005275</v>
       </c>
       <c r="Z41" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AA41" t="n">
-        <v>68.18181818181819</v>
+        <v>50</v>
       </c>
       <c r="AB41" t="n">
-        <v>11.49459816602331</v>
+        <v>13.76360946508232</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.4782767247719533</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5138,10 +5106,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C42" t="n">
-        <v>3.623694645211776</v>
+        <v>3.64664275277805</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5199,7 +5167,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>6.301889755239076</v>
+        <v>5.708519031937476</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
@@ -5210,7 +5178,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.946835464558052</v>
+        <v>4.55129235854943</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5239,19 +5207,19 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C43" t="n">
-        <v>7.06693484524836</v>
+        <v>6.853101392366306</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5259,24 +5227,38 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.56: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>5</v>
       </c>
       <c r="I43" t="n">
         <v>10</v>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>11.88137027331979</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.381970970206269</v>
+      </c>
       <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="M43" t="n">
+        <v>80.55555555555556</v>
+      </c>
+      <c r="N43" t="n">
+        <v>14.63490187278898</v>
+      </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>3.604261796042607</v>
+      </c>
       <c r="Q43" t="n">
         <v>10</v>
       </c>
@@ -5302,16 +5284,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.784764492244701</v>
+        <v>11.54478268842032</v>
       </c>
       <c r="Z43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
-        <v>33.33333333333334</v>
+        <v>62.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>12.82467271064334</v>
+        <v>11.9104038953567</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5348,10 +5330,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C44" t="n">
-        <v>4.516579760874597</v>
+        <v>4.527010661015185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,22 +5361,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7445352002869443</v>
+        <v>0.9772015633360942</v>
       </c>
       <c r="L44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M44" t="n">
-        <v>61.53846153846154</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N44" t="n">
-        <v>20.36322934537926</v>
+        <v>19.3802499863943</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>9.187063875288693</v>
+        <v>8.935480778801864</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5449,10 +5431,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02253074513814206</v>
+        <v>0.02273936293233581</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,22 +5494,22 @@
         <v>13.71433374328026</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.88208619177257</v>
+        <v>0.9735879319918372</v>
       </c>
       <c r="Z45" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="n">
-        <v>48.23529411764706</v>
+        <v>46.83544303797468</v>
       </c>
       <c r="AB45" t="n">
-        <v>13.12393849492577</v>
+        <v>13.46906584173004</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.177721261299371</v>
+        <v>4.06599813516717</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5558,10 +5540,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C46" t="n">
-        <v>9.554704528778593</v>
+        <v>9.846769732715057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5570,7 +5552,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5585,68 +5567,58 @@
       <c r="I46" t="n">
         <v>10</v>
       </c>
-      <c r="J46" t="n">
-        <v>15.5773254518138</v>
-      </c>
-      <c r="K46" t="n">
-        <v>15.71319147221368</v>
-      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>40</v>
-      </c>
-      <c r="N46" t="n">
-        <v>42.39223617978435</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
         <v>10</v>
       </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R46" t="n">
-        <v>61.11111111111111</v>
+        <v>61.81818181818182</v>
       </c>
       <c r="S46" t="n">
-        <v>56.67894198923945</v>
+        <v>56.51205213488964</v>
       </c>
       <c r="T46" t="n">
-        <v>4.432169121871667</v>
+        <v>5.306129683292184</v>
       </c>
       <c r="U46" t="n">
-        <v>47.78829853820768</v>
+        <v>48.60922023248993</v>
       </c>
       <c r="V46" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W46" t="n">
-        <v>67.07317073170732</v>
+        <v>67.46987951807229</v>
       </c>
       <c r="X46" t="n">
-        <v>16.09216480672966</v>
+        <v>19.75557370705086</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.3264417845484258</v>
+        <v>0.4219409282700481</v>
       </c>
       <c r="Z46" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AA46" t="n">
-        <v>35.29411764705883</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB46" t="n">
-        <v>10.71776539038433</v>
+        <v>11.21251952225099</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.682314410480346</v>
+        <v>2.58898305084746</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5677,10 +5649,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7134735854711864</v>
+        <v>0.7214010919001596</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5697,11 +5669,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>5</v>
       </c>
@@ -5709,25 +5677,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>27.5639608197357</v>
+        <v>25.52135514083118</v>
       </c>
       <c r="K47" t="n">
-        <v>5.940620010221798</v>
+        <v>7.117741298693603</v>
       </c>
       <c r="L47" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M47" t="n">
-        <v>76.47058823529412</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N47" t="n">
-        <v>11.6991805620498</v>
+        <v>11.41702716750468</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.831750266693312</v>
+        <v>2.690738869548537</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5768,10 +5736,10 @@
         <v>56.81818181818182</v>
       </c>
       <c r="AG47" t="n">
-        <v>30.99787803618449</v>
+        <v>31.33377067451265</v>
       </c>
       <c r="AH47" t="n">
-        <v>25.82030378199733</v>
+        <v>25.48441114366917</v>
       </c>
       <c r="AI47" t="n">
         <v>42.22414699362943</v>
@@ -5790,10 +5758,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05799580415581519</v>
+        <v>0.05945612871517148</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,22 +5789,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7246369591472401</v>
+        <v>3.260866316162558</v>
       </c>
       <c r="L48" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M48" t="n">
-        <v>45.16129032258065</v>
+        <v>56.14035087719298</v>
       </c>
       <c r="N48" t="n">
-        <v>14.62309089727136</v>
+        <v>15.05187700376106</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>9.208633876352156</v>
+        <v>6.526319141274373</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5845,10 +5813,10 @@
         <v>63.82978723404256</v>
       </c>
       <c r="S48" t="n">
-        <v>48.23412847369152</v>
+        <v>48.25943983605992</v>
       </c>
       <c r="T48" t="n">
-        <v>15.59565876035104</v>
+        <v>15.57034739798264</v>
       </c>
       <c r="U48" t="n">
         <v>49.53589653479511</v>
@@ -5877,10 +5845,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>23.90517908715965</v>
+        <v>23.99416728091447</v>
       </c>
       <c r="AH48" t="n">
-        <v>36.47217940340639</v>
+        <v>36.38319120965157</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5899,19 +5867,19 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2607725035146996</v>
+        <v>0.2628586914703013</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5927,25 +5895,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>19.58948492311236</v>
+        <v>18.60609306322062</v>
       </c>
       <c r="K49" t="n">
-        <v>4.931914133811133</v>
+        <v>5.771372636811822</v>
       </c>
       <c r="L49" t="n">
         <v>28</v>
       </c>
       <c r="M49" t="n">
-        <v>64.28571428571429</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N49" t="n">
-        <v>13.06769688809701</v>
+        <v>14.3914678277984</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.06488575639824745</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5986,10 +5954,10 @@
         <v>63.04347826086956</v>
       </c>
       <c r="AG49" t="n">
-        <v>36.33072302172364</v>
+        <v>36.85821306821072</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.71275523914593</v>
+        <v>26.18526519265884</v>
       </c>
       <c r="AI49" t="n">
         <v>48.60009642338971</v>
@@ -6008,10 +5976,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C50" t="n">
-        <v>0.681346394053937</v>
+        <v>0.6909428029904219</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,22 +6007,22 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>1.935077753424741</v>
+        <v>3.37078020907875</v>
       </c>
       <c r="L50" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>56</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="N50" t="n">
-        <v>15.20042476406721</v>
+        <v>16.76810922106695</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.025722932757446</v>
+        <v>0.6087017914042869</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6063,10 +6031,10 @@
         <v>65</v>
       </c>
       <c r="S50" t="n">
-        <v>52.53746034128572</v>
+        <v>52.41246034128572</v>
       </c>
       <c r="T50" t="n">
-        <v>12.46253965871428</v>
+        <v>12.58753965871428</v>
       </c>
       <c r="U50" t="n">
         <v>49.50588083725769</v>
@@ -6104,10 +6072,10 @@
         <v>44.49431275003934</v>
       </c>
       <c r="AJ50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK50" t="n">
-        <v>55</v>
+        <v>54.23728813559322</v>
       </c>
     </row>
     <row r="51">
@@ -6117,10 +6085,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1771166795889699</v>
+        <v>0.1756563600364457</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6148,7 +6116,7 @@
         <v>21.20514974257153</v>
       </c>
       <c r="K51" t="n">
-        <v>2.043270268439157</v>
+        <v>1.201927809206427</v>
       </c>
       <c r="L51" t="n">
         <v>17</v>
@@ -6157,13 +6125,13 @@
         <v>64.70588235294117</v>
       </c>
       <c r="N51" t="n">
-        <v>12.20586534534482</v>
+        <v>13.27232902826984</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.917549022501341</v>
+        <v>2.764840800334079</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6190,7 +6158,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>19.59515799420034</v>
+        <v>20.25809252510493</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6232,10 +6200,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C52" t="n">
-        <v>4.418529363181561</v>
+        <v>4.493631653308322</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6292,25 +6260,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>14.20540211851664</v>
+        <v>16.08466358135892</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.4231283088413029</v>
+        <v>0.3700291680323375</v>
       </c>
       <c r="Z52" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="AA52" t="n">
-        <v>40.81632653061224</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB52" t="n">
-        <v>10.8933591121244</v>
+        <v>12.10932009214383</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.609067811106418</v>
+        <v>7.658308808336489</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6319,10 +6287,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>38.9961270701074</v>
+        <v>39.59177059067351</v>
       </c>
       <c r="AH52" t="n">
-        <v>29.42492556147155</v>
+        <v>28.82928204090543</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6341,10 +6309,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C53" t="n">
-        <v>1.364361770307463</v>
+        <v>1.380008120518345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6361,7 +6329,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6372,22 +6344,22 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>1.160092779969979</v>
+        <v>2.320185559939936</v>
       </c>
       <c r="L53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>71.42857142857143</v>
+        <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>17.90840940822131</v>
+        <v>16.71756518363199</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>6.76146791888308</v>
+        <v>5.551020464806333</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6442,10 +6414,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08052654699915922</v>
+        <v>0.08136102318276631</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6464,7 +6436,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir. SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -6477,22 +6449,22 @@
         <v>42.98617858772242</v>
       </c>
       <c r="K54" t="n">
-        <v>0.658603741275865</v>
+        <v>1.701703323058701</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>100</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N54" t="n">
-        <v>22.84645482583484</v>
+        <v>25.39606819333878</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>9.280276013697208</v>
+        <v>8.159447094589467</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6519,16 +6491,16 @@
         <v>10.17240666043591</v>
       </c>
       <c r="Y54" t="n">
-        <v>8.63537723060065</v>
+        <v>7.688588816512743</v>
       </c>
       <c r="Z54" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA54" t="n">
-        <v>69.56521739130434</v>
+        <v>75</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.6756080381485</v>
+        <v>15.59141213484551</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6565,10 +6537,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9529670433112764</v>
+        <v>0.9667358281589645</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6625,40 +6597,40 @@
         <v>73.41772151898734</v>
       </c>
       <c r="X55" t="n">
-        <v>27.85273536484003</v>
+        <v>26.41142362228692</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.289670043950831</v>
+        <v>0.8779186932569405</v>
       </c>
       <c r="Z55" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="AA55" t="n">
-        <v>53.125</v>
+        <v>51.35135135135135</v>
       </c>
       <c r="AB55" t="n">
-        <v>13.05917445753822</v>
+        <v>12.85141579139036</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.7269752915261662</v>
+        <v>2.140876461397201</v>
       </c>
       <c r="AE55" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF55" t="n">
-        <v>55.31914893617022</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="AG55" t="n">
-        <v>41.20705267682467</v>
+        <v>41.38577329938532</v>
       </c>
       <c r="AH55" t="n">
-        <v>14.11209625934554</v>
+        <v>15.13596583104946</v>
       </c>
       <c r="AI55" t="n">
-        <v>41.24545983821874</v>
+        <v>42.24743369429499</v>
       </c>
       <c r="AJ55" t="n">
         <v>70</v>
@@ -6674,10 +6646,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C56" t="n">
-        <v>1.178691715886442</v>
+        <v>1.208941342149116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6726,25 +6698,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>54.03295778066517</v>
+        <v>54.96406828374303</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.417964582046872</v>
+        <v>0.5150201545064292</v>
       </c>
       <c r="Z56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA56" t="n">
-        <v>25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB56" t="n">
-        <v>11.37684826496634</v>
+        <v>5.950530495629048</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>7.769909067256641</v>
+        <v>9.534082290838619</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6767,10 +6739,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C57" t="n">
-        <v>1.278828341381119</v>
+        <v>1.297603993344113</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6787,11 +6759,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %79.49: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6802,22 +6770,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>1.294456055674531</v>
+        <v>2.781652883536667</v>
       </c>
       <c r="L57" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M57" t="n">
-        <v>79.48717948717949</v>
+        <v>69.76744186046511</v>
       </c>
       <c r="N57" t="n">
-        <v>18.9729472884561</v>
+        <v>18.73607647816584</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>8.594294577721652</v>
+        <v>7.02299186085531</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6835,16 +6803,16 @@
         <v>69.44100627964798</v>
       </c>
       <c r="V57" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="W57" t="n">
-        <v>79.82456140350877</v>
+        <v>79.1304347826087</v>
       </c>
       <c r="X57" t="n">
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>21.15952600749666</v>
+        <v>20.00199668758646</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -6886,10 +6854,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7322491579507222</v>
+        <v>0.743931794897465</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6906,7 +6874,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6917,64 +6889,64 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>10.31783603246221</v>
+        <v>12.0778970897182</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M58" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N58" t="n">
-        <v>13.02241985913761</v>
+        <v>14.19416378953196</v>
       </c>
       <c r="O58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R58" t="n">
-        <v>87.5</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="S58" t="n">
-        <v>44.51276340406775</v>
+        <v>40.04330826349963</v>
       </c>
       <c r="T58" t="n">
-        <v>42.98723659593225</v>
+        <v>42.56538738867427</v>
       </c>
       <c r="U58" t="n">
-        <v>68.99611872949993</v>
+        <v>62.86235235977385</v>
       </c>
       <c r="V58" t="n">
         <v>40</v>
       </c>
       <c r="W58" t="n">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="X58" t="n">
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.61147279005296</v>
+        <v>1.057691821077966</v>
       </c>
       <c r="Z58" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AA58" t="n">
-        <v>37.5</v>
+        <v>28.26086956521739</v>
       </c>
       <c r="AB58" t="n">
-        <v>13.89509757912605</v>
+        <v>12.96779667609787</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.479390547350791</v>
+        <v>4.995141380757595</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -7005,10 +6977,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7860726410618686</v>
+        <v>0.7994241803075052</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7036,22 +7008,22 @@
         <v>11.1236565078948</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4264388273943931</v>
+        <v>2.132194083667138</v>
       </c>
       <c r="L59" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M59" t="n">
-        <v>57.69230769230769</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N59" t="n">
-        <v>13.73624316273638</v>
+        <v>13.53151212263976</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>7.541401707594653</v>
+        <v>5.745304865893641</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7114,10 +7086,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C60" t="n">
-        <v>11.93294976083265</v>
+        <v>11.98510426153559</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7145,22 +7117,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>3.881100218760691</v>
+        <v>4.33512600643009</v>
       </c>
       <c r="L60" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M60" t="n">
-        <v>53.84615384615385</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N60" t="n">
-        <v>13.61912928040403</v>
+        <v>13.35665654615755</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.965013628624869</v>
+        <v>3.512598425715274</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7223,10 +7195,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C61" t="n">
-        <v>0.643377923800737</v>
+        <v>0.6387883421335204</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7243,7 +7215,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7254,22 +7230,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>4.69888157390792</v>
+        <v>3.952004738888459</v>
       </c>
       <c r="L61" t="n">
         <v>20</v>
       </c>
       <c r="M61" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="N61" t="n">
-        <v>20.66685979079341</v>
+        <v>18.652091864523</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>5.063204445359792</v>
+        <v>5.818065054448152</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7288,16 +7264,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>8.470884188414695</v>
+        <v>9.123813573159179</v>
       </c>
       <c r="Z61" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA61" t="n">
-        <v>35.71428571428572</v>
+        <v>36</v>
       </c>
       <c r="AB61" t="n">
-        <v>14.77067929378621</v>
+        <v>13.97515198363194</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7334,7 +7310,7 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C62" t="n">
         <v>9.226131174350073</v>
@@ -7443,10 +7419,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1132795719802795</v>
+        <v>0.1091072158877863</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7463,11 +7439,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>5</v>
       </c>
@@ -7475,19 +7447,19 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>17.92579352879743</v>
+        <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>15.26812438540721</v>
+        <v>11.02252517769273</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M63" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="N63" t="n">
-        <v>12.11578074512405</v>
+        <v>18.53502896780919</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
@@ -7520,22 +7492,22 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.808325066953298</v>
+        <v>5.424958021837023</v>
       </c>
       <c r="Z63" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AA63" t="n">
-        <v>46.15384615384615</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB63" t="n">
-        <v>18.05853779654241</v>
+        <v>17.67862713243624</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>8.342535086230374</v>
+        <v>4.837472849569902</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7566,10 +7538,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1518739104279391</v>
+        <v>0.1481187799101694</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7594,25 +7566,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>23.44387669306003</v>
+        <v>24.31418588816031</v>
       </c>
       <c r="K64" t="n">
-        <v>1.369569641941726</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M64" t="n">
-        <v>65.78947368421052</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N64" t="n">
-        <v>16.30233344950444</v>
+        <v>15.79298447767449</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.581380853131466</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7653,10 +7625,10 @@
         <v>60.78431372549019</v>
       </c>
       <c r="AG64" t="n">
-        <v>37.7448937818306</v>
+        <v>38.36293432934519</v>
       </c>
       <c r="AH64" t="n">
-        <v>23.03941994365959</v>
+        <v>22.42137939614501</v>
       </c>
       <c r="AI64" t="n">
         <v>47.08515898394834</v>
@@ -7675,10 +7647,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C65" t="n">
-        <v>6.790515991522778</v>
+        <v>6.769654191241602</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7703,10 +7675,10 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>27.82512429793246</v>
+        <v>25.04872642808169</v>
       </c>
       <c r="K65" t="n">
-        <v>19.86468300101516</v>
+        <v>19.49643512697212</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7744,7 +7716,7 @@
         <v>21.96943581422117</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.725639541706081</v>
+        <v>2.027557699796068</v>
       </c>
       <c r="Z65" t="n">
         <v>33</v>
@@ -7753,13 +7725,13 @@
         <v>42.42424242424242</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.880988949054537</v>
+        <v>9.23859282732489</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.314296880374134</v>
+        <v>2.013262356122592</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7768,10 +7740,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG65" t="n">
-        <v>20.75332846310948</v>
+        <v>20.75782001898443</v>
       </c>
       <c r="AH65" t="n">
-        <v>33.79212608234506</v>
+        <v>33.78763452647011</v>
       </c>
       <c r="AI65" t="n">
         <v>40.06618319896197</v>
@@ -7790,10 +7762,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4501976483988334</v>
+        <v>0.456456172628218</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,22 +7825,22 @@
         <v>10.67532115313607</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.510008537010244</v>
+        <v>1.154729414909883</v>
       </c>
       <c r="Z66" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AA66" t="n">
-        <v>30</v>
+        <v>30.18867924528302</v>
       </c>
       <c r="AB66" t="n">
-        <v>10.07985030708235</v>
+        <v>11.76787362189428</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>3.579845900709377</v>
+        <v>4.901873965653336</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7899,10 +7871,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0273289571166325</v>
+        <v>0.0279548130026298</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7930,22 +7902,22 @@
         <v>14.0514682678307</v>
       </c>
       <c r="K67" t="n">
-        <v>1.550386094585621</v>
+        <v>3.875974538789895</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>40</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N67" t="n">
-        <v>7.671407444036571</v>
+        <v>7.104188996989391</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>2.412215255521311</v>
+        <v>0.1193976391179907</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7988,14 +7960,14 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C68" t="n">
-        <v>3.717572746477067</v>
+        <v>3.894898048867063</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8005,7 +7977,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -8019,7 +7991,7 @@
         <v>30.89188078077966</v>
       </c>
       <c r="K68" t="n">
-        <v>31.61144929455744</v>
+        <v>37.88921213491048</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8048,16 +8020,16 @@
         <v>11.76207742326478</v>
       </c>
       <c r="V68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W68" t="n">
-        <v>80</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
         <v>128.0325939207301</v>
       </c>
       <c r="Y68" t="n">
-        <v>9.045802715373519</v>
+        <v>4.707358887362423</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8068,7 +8040,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>3.455294211801319</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8099,10 +8071,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3995034674570357</v>
+        <v>0.395122508382227</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8127,25 +8099,25 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>22.58627948191679</v>
+        <v>20.01758548606234</v>
       </c>
       <c r="K69" t="n">
-        <v>2.191568776857644</v>
+        <v>1.283421177786082</v>
       </c>
       <c r="L69" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M69" t="n">
-        <v>62.5</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N69" t="n">
-        <v>24.30827638571526</v>
+        <v>23.467573021129</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>5.683865403637633</v>
+        <v>6.63146914283641</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8192,10 +8164,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C70" t="n">
-        <v>0.417653251225571</v>
+        <v>0.4247462664504409</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8223,16 +8195,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>9.515334946781696</v>
+        <v>11.37523651789316</v>
       </c>
       <c r="L70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M70" t="n">
-        <v>53.33333333333334</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="N70" t="n">
-        <v>9.807543501166204</v>
+        <v>12.00172386214981</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8262,25 +8234,25 @@
         <v>67.79661016949153</v>
       </c>
       <c r="X70" t="n">
-        <v>10.39058153826879</v>
+        <v>11.59404295530768</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.792863466512006</v>
+        <v>0.1960735820837223</v>
       </c>
       <c r="Z70" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AA70" t="n">
-        <v>34.88372093023256</v>
+        <v>44.89795918367347</v>
       </c>
       <c r="AB70" t="n">
-        <v>11.43077003926567</v>
+        <v>9.623333329797317</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>7.264735970940128</v>
+        <v>7.819257917006517</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8289,10 +8261,10 @@
         <v>50</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.52378947020455</v>
+        <v>34.60271054912563</v>
       </c>
       <c r="AH70" t="n">
-        <v>15.47621052979545</v>
+        <v>15.39728945087437</v>
       </c>
       <c r="AI70" t="n">
         <v>35.8317605399894</v>
@@ -8311,10 +8283,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C71" t="n">
-        <v>3.112580538322964</v>
+        <v>3.143873238744728</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8339,25 +8311,25 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>16.08396579947103</v>
+        <v>14.92600999981897</v>
       </c>
       <c r="K71" t="n">
-        <v>0.7427351821020611</v>
+        <v>1.755564309865365</v>
       </c>
       <c r="L71" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="M71" t="n">
-        <v>69.49152542372882</v>
+        <v>59.42028985507246</v>
       </c>
       <c r="N71" t="n">
-        <v>13.80630953371501</v>
+        <v>16.94493886481091</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>1.247995516128597</v>
+        <v>0.2402184998849588</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8420,10 +8392,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07280768318992215</v>
+        <v>0.07239044760153462</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8451,22 +8423,22 @@
         <v>21.72769951373251</v>
       </c>
       <c r="K72" t="n">
-        <v>3.560834537594015</v>
+        <v>2.967363301605341</v>
       </c>
       <c r="L72" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M72" t="n">
-        <v>46.66666666666666</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N72" t="n">
-        <v>14.48088012985361</v>
+        <v>14.07472064720535</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>1.389681213783134</v>
+        <v>1.974059190425992</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8493,7 +8465,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>18.94055240464814</v>
+        <v>19.40507599378076</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8535,10 +8507,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07301630098411589</v>
+        <v>0.07405938995508468</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8566,16 +8538,16 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>10.9840779069958</v>
+        <v>12.56956314875177</v>
       </c>
       <c r="L73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M73" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="N73" t="n">
-        <v>8.996964415772805</v>
+        <v>8.907419983978393</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
@@ -8605,25 +8577,25 @@
         <v>77.27272727272727</v>
       </c>
       <c r="X73" t="n">
-        <v>10.66698085864464</v>
+        <v>13.52085429380536</v>
       </c>
       <c r="Y73" t="n">
-        <v>-0.2865326639354127</v>
+        <v>0.8379880075528034</v>
       </c>
       <c r="Z73" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="AA73" t="n">
-        <v>40</v>
+        <v>42.42424242424242</v>
       </c>
       <c r="AB73" t="n">
-        <v>11.5764397696191</v>
+        <v>12.11058037917597</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>10.25714259999998</v>
+        <v>9.239437369569536</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8654,10 +8626,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C74" t="n">
-        <v>5.580531575214572</v>
+        <v>5.705702376901628</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8646,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -8685,16 +8661,16 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>18.06785928832195</v>
+        <v>20.71611033777965</v>
       </c>
       <c r="L74" t="n">
         <v>3</v>
       </c>
       <c r="M74" t="n">
-        <v>66.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="N74" t="n">
-        <v>20.31187036634743</v>
+        <v>18.31627048481326</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
@@ -8727,22 +8703,22 @@
         <v>35.33255906375725</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.60905474189549</v>
+        <v>1.447014848255757</v>
       </c>
       <c r="Z74" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AA74" t="n">
-        <v>48.14814814814815</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="AB74" t="n">
-        <v>19.84130253243027</v>
+        <v>17.45041565241838</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>6.630234033903881</v>
+        <v>8.678565279960848</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8751,10 +8727,10 @@
         <v>51.28205128205128</v>
       </c>
       <c r="AG74" t="n">
-        <v>30.74338076466355</v>
+        <v>30.76277313699709</v>
       </c>
       <c r="AH74" t="n">
-        <v>20.53867051738774</v>
+        <v>20.51927814505419</v>
       </c>
       <c r="AI74" t="n">
         <v>36.19936288445796</v>
@@ -8773,10 +8749,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1264225084522184</v>
+        <v>0.1262138956648567</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8804,7 +8780,7 @@
         <v>23.39449322057143</v>
       </c>
       <c r="K75" t="n">
-        <v>2.364862468042395</v>
+        <v>2.195947774379103</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
@@ -8819,7 +8795,7 @@
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.551157540110483</v>
+        <v>3.722312193844735</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8882,10 +8858,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C76" t="n">
-        <v>1.864001823204519</v>
+        <v>1.893208375516719</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8910,25 +8886,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>12.16632018667745</v>
+        <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>7.548793934629661</v>
+        <v>9.233947584729506</v>
       </c>
       <c r="L76" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M76" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="N76" t="n">
-        <v>10.52602514346615</v>
+        <v>8.424939522696532</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>2.279157185956215</v>
+        <v>0.7012951854333593</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8955,22 +8931,22 @@
         <v>10.78536860174914</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.921482058478597</v>
+        <v>1.400384397868171</v>
       </c>
       <c r="Z76" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="AA76" t="n">
-        <v>40.90909090909091</v>
+        <v>37.5</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.38606078626817</v>
+        <v>10.15080148371587</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.110974873113624</v>
+        <v>2.636537258544469</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8979,10 +8955,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG76" t="n">
-        <v>29.18890669623226</v>
+        <v>29.58374262512391</v>
       </c>
       <c r="AH76" t="n">
-        <v>25.35654784922229</v>
+        <v>24.96171192033064</v>
       </c>
       <c r="AI76" t="n">
         <v>37.98593853621745</v>
@@ -9001,10 +8977,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5369827344392554</v>
+        <v>0.5378172256433588</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9029,16 +9005,16 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>15.2440585586459</v>
+        <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>10.59483545559095</v>
+        <v>10.76670395617381</v>
       </c>
       <c r="L77" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M77" t="n">
-        <v>68.96551724137932</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N77" t="n">
         <v>16.90273640953321</v>
@@ -9056,10 +9032,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S77" t="n">
-        <v>39.05932081203821</v>
+        <v>38.83204808476547</v>
       </c>
       <c r="T77" t="n">
-        <v>18.08353633081894</v>
+        <v>18.31080905809167</v>
       </c>
       <c r="U77" t="n">
         <v>39.07078562746877</v>
@@ -9074,22 +9050,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.890464340130296</v>
+        <v>4.742660573185342</v>
       </c>
       <c r="Z77" t="n">
         <v>46</v>
       </c>
       <c r="AA77" t="n">
-        <v>43.47826086956522</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="AB77" t="n">
-        <v>12.14668224944233</v>
+        <v>11.33852694491439</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.372264331246868</v>
+        <v>5.519091188615254</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9120,10 +9096,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0475649040152272</v>
+        <v>0.04777352180942095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9151,22 +9127,22 @@
         <v>19.53698884929083</v>
       </c>
       <c r="K78" t="n">
-        <v>1.785712492028058</v>
+        <v>2.232140615035072</v>
       </c>
       <c r="L78" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M78" t="n">
-        <v>66.66666666666667</v>
+        <v>67.34693877551021</v>
       </c>
       <c r="N78" t="n">
-        <v>19.18832399297357</v>
+        <v>19.31228134149281</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>2.175440397045292</v>
+        <v>1.729259873000188</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9229,10 +9205,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8065171957409929</v>
+        <v>0.814444702169966</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9260,22 +9236,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>1.724161797661838</v>
+        <v>2.724039978674409</v>
       </c>
       <c r="L79" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M79" t="n">
-        <v>60.52631578947368</v>
+        <v>56.25</v>
       </c>
       <c r="N79" t="n">
-        <v>13.30192167449316</v>
+        <v>10.39556198725482</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>3.220314765388865</v>
+        <v>2.215606027370121</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9310,19 +9286,19 @@
       </c>
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF79" t="n">
-        <v>54.05405405405406</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>27.56828697900574</v>
+        <v>27.69183331670432</v>
       </c>
       <c r="AH79" t="n">
-        <v>26.48576707504831</v>
+        <v>25.08594446107346</v>
       </c>
       <c r="AI79" t="n">
-        <v>38.38404689217949</v>
+        <v>37.00593802298759</v>
       </c>
       <c r="AJ79" t="n">
         <v>54</v>
@@ -9338,7 +9314,7 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C80" t="n">
         <v>0.1289259221911614</v>
@@ -9431,10 +9407,10 @@
         <v>50</v>
       </c>
       <c r="AG80" t="n">
-        <v>41.23573350117973</v>
+        <v>41.49797126341749</v>
       </c>
       <c r="AH80" t="n">
-        <v>8.76426649882027</v>
+        <v>8.50202873658251</v>
       </c>
       <c r="AI80" t="n">
         <v>32.06059352575905</v>
@@ -9453,10 +9429,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C81" t="n">
-        <v>1.171390117706585</v>
+        <v>1.211027490467297</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9513,25 +9489,25 @@
         <v>64.58333333333333</v>
       </c>
       <c r="X81" t="n">
-        <v>27.80893627966077</v>
+        <v>29.11409862854482</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.006976832902307</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA81" t="n">
-        <v>52.63157894736842</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AB81" t="n">
-        <v>13.86536565245075</v>
+        <v>11.71666497365729</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>8.156726783975209</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9562,14 +9538,14 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C82" t="n">
-        <v>5.288466371278108</v>
+        <v>5.3823444725434</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9579,7 +9555,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9625,22 +9601,22 @@
         <v>21.75875960601758</v>
       </c>
       <c r="Y82" t="n">
-        <v>5.405777568468395</v>
+        <v>3.726590188027012</v>
       </c>
       <c r="Z82" t="n">
         <v>8</v>
       </c>
       <c r="AA82" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AB82" t="n">
-        <v>14.46141572313648</v>
+        <v>10.8165986040599</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>0.2839930698486426</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9671,10 +9647,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C83" t="n">
-        <v>5.856950428940153</v>
+        <v>5.898674029502505</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9710,19 +9686,19 @@
       </c>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R83" t="n">
-        <v>62.7906976744186</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="S83" t="n">
-        <v>58.05656375063227</v>
+        <v>58.54260360742552</v>
       </c>
       <c r="T83" t="n">
-        <v>4.734133923786331</v>
+        <v>3.362158297336386</v>
       </c>
       <c r="U83" t="n">
-        <v>47.85980915968847</v>
+        <v>46.81404026715268</v>
       </c>
       <c r="V83" t="n">
         <v>65</v>
@@ -9734,22 +9710,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.64355637055621</v>
+        <v>1.950010912821976</v>
       </c>
       <c r="Z83" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA83" t="n">
-        <v>49.12280701754386</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.79810217199899</v>
+        <v>11.53491919845318</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.4475824139787</v>
+        <v>4.130534969847998</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9780,10 +9756,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C84" t="n">
-        <v>2.177971981273326</v>
+        <v>2.175885832955144</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9811,7 +9787,7 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>4.265075973028476</v>
+        <v>4.16520673010139</v>
       </c>
       <c r="L84" t="n">
         <v>52</v>
@@ -9820,13 +9796,13 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>11.58160239314899</v>
+        <v>11.61841236501015</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0.704861162870718</v>
+        <v>0.8014127712160368</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9867,10 +9843,10 @@
         <v>41.02564102564103</v>
       </c>
       <c r="AG84" t="n">
-        <v>26.80384782289221</v>
+        <v>26.84396891564488</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.22179320274882</v>
+        <v>14.18167210999615</v>
       </c>
       <c r="AI84" t="n">
         <v>27.07931000072518</v>
@@ -9889,10 +9865,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C85" t="n">
-        <v>6.253324634282497</v>
+        <v>6.310694585055731</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9917,25 +9893,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>16.64733629675238</v>
+        <v>15.93296998857089</v>
       </c>
       <c r="K85" t="n">
-        <v>1.076813999947768</v>
+        <v>2.004124220130787</v>
       </c>
       <c r="L85" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M85" t="n">
-        <v>62.5</v>
+        <v>58</v>
       </c>
       <c r="N85" t="n">
-        <v>14.12167216138053</v>
+        <v>14.21277561927468</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.849430374859078</v>
+        <v>5.878071916905814</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9944,10 +9920,10 @@
         <v>60.60606060606061</v>
       </c>
       <c r="S85" t="n">
-        <v>66.63660413660413</v>
+        <v>66.38783400931739</v>
       </c>
       <c r="T85" t="n">
-        <v>-6.030543530543525</v>
+        <v>-5.781773403256778</v>
       </c>
       <c r="U85" t="n">
         <v>43.68344081994023</v>
@@ -9998,10 +9974,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C86" t="n">
-        <v>4.762749067820964</v>
+        <v>4.787783164529885</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10061,7 +10037,7 @@
         <v>100.8644868744093</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.159441951592182</v>
+        <v>6.671450777671839</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10103,19 +10079,19 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C87" t="n">
-        <v>5.580531575214572</v>
+        <v>5.69527147676104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10134,37 +10110,37 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>3.489115574940915</v>
+        <v>5.616929166201379</v>
       </c>
       <c r="L87" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M87" t="n">
-        <v>46.875</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N87" t="n">
-        <v>11.55282075555252</v>
+        <v>10.20439281236176</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>1.459945248024641</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R87" t="n">
-        <v>56</v>
+        <v>56.25</v>
       </c>
       <c r="S87" t="n">
-        <v>34.34534944884052</v>
+        <v>34.66367189038035</v>
       </c>
       <c r="T87" t="n">
-        <v>21.65465055115948</v>
+        <v>21.58632810961965</v>
       </c>
       <c r="U87" t="n">
-        <v>42.30602802165686</v>
+        <v>42.27501741982778</v>
       </c>
       <c r="V87" t="n">
         <v>66</v>
@@ -10190,10 +10166,10 @@
         <v>44.18604651162791</v>
       </c>
       <c r="AG87" t="n">
-        <v>44.6595215274113</v>
+        <v>45.34425157808585</v>
       </c>
       <c r="AH87" t="n">
-        <v>-0.4734750157833929</v>
+        <v>-1.158205066457946</v>
       </c>
       <c r="AI87" t="n">
         <v>30.43330983917051</v>
@@ -10212,10 +10188,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C88" t="n">
-        <v>1.015969689548238</v>
+        <v>1.069167264410268</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10229,7 +10205,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10243,17 +10219,13 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>13.82070957426915</v>
+        <v>19.78051898661395</v>
       </c>
       <c r="L88" t="n">
-        <v>4</v>
-      </c>
-      <c r="M88" t="n">
-        <v>50</v>
-      </c>
-      <c r="N88" t="n">
-        <v>8.662334745458478</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
         <v>3</v>
       </c>
@@ -10261,19 +10233,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R88" t="n">
-        <v>69.44444444444444</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="S88" t="n">
-        <v>48.16275243264052</v>
+        <v>46.71491829167712</v>
       </c>
       <c r="T88" t="n">
-        <v>21.28169201180393</v>
+        <v>24.71365313689431</v>
       </c>
       <c r="U88" t="n">
-        <v>53.14372714948966</v>
+        <v>54.94506513681738</v>
       </c>
       <c r="V88" t="n">
         <v>78</v>
@@ -10285,22 +10257,22 @@
         <v>27.20319322085054</v>
       </c>
       <c r="Y88" t="n">
-        <v>10.52055636948255</v>
+        <v>5.835289230003315</v>
       </c>
       <c r="Z88" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA88" t="n">
-        <v>46.15384615384615</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB88" t="n">
-        <v>11.81298881821716</v>
+        <v>17.15486565065062</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>0.1749177251752054</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10331,10 +10303,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C89" t="n">
-        <v>1.973526274680692</v>
+        <v>2.07887842993774</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10348,7 +10320,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -10362,16 +10334,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>7.198701239499794</v>
+        <v>12.92125703276628</v>
       </c>
       <c r="L89" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="M89" t="n">
-        <v>74.28571428571429</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N89" t="n">
-        <v>14.86799339732633</v>
+        <v>12.12783772737087</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10404,22 +10376,22 @@
         <v>20.95675253601343</v>
       </c>
       <c r="Y89" t="n">
-        <v>11.37435571645109</v>
+        <v>6.643279796102908</v>
       </c>
       <c r="Z89" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="AA89" t="n">
-        <v>43.75</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.34768627843867</v>
+        <v>13.47962203053799</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>3.595584974028432</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10450,10 +10422,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C90" t="n">
-        <v>2.670310435990524</v>
+        <v>2.705775432840033</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10481,22 +10453,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>5.264302172163626</v>
+        <v>6.662341177136755</v>
       </c>
       <c r="L90" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M90" t="n">
-        <v>65.90909090909091</v>
+        <v>65.78947368421052</v>
       </c>
       <c r="N90" t="n">
-        <v>15.45317636398545</v>
+        <v>15.38832552732793</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>2.598884684916314</v>
+        <v>1.25410600226914</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10523,16 +10495,16 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>12.19558863746717</v>
+        <v>11.02943839127299</v>
       </c>
       <c r="Z90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA90" t="n">
-        <v>64.28571428571429</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB90" t="n">
-        <v>15.26908428627451</v>
+        <v>16.34928743903905</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10569,19 +10541,19 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C91" t="n">
-        <v>0.229062557490884</v>
+        <v>0.2315659910485374</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10600,22 +10572,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>2.317895105460921</v>
+        <v>3.436131341715587</v>
       </c>
       <c r="L91" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="M91" t="n">
-        <v>64.70588235294117</v>
+        <v>64.40677966101696</v>
       </c>
       <c r="N91" t="n">
-        <v>15.29890820780455</v>
+        <v>14.1560316691676</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.6666525868578743</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10678,10 +10650,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C92" t="n">
-        <v>1.128623363293066</v>
+        <v>1.129666517144233</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10713,7 +10685,7 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>7.115265997840181</v>
+        <v>7.214269532481232</v>
       </c>
       <c r="L92" t="n">
         <v>22</v>
@@ -10722,13 +10694,13 @@
         <v>77.27272727272727</v>
       </c>
       <c r="N92" t="n">
-        <v>11.61735801987519</v>
+        <v>11.47873103029748</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.8259644355246953</v>
+        <v>0.7328599737190133</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10755,16 +10727,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>6.584413830866175</v>
+        <v>6.498072513079645</v>
       </c>
       <c r="Z92" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA92" t="n">
-        <v>52.5</v>
+        <v>53.65853658536585</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.49472424221203</v>
+        <v>11.51288427766717</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10779,10 +10751,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.29970314818353</v>
+        <v>40.33109501527519</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.64147332240471</v>
+        <v>12.61008145531304</v>
       </c>
       <c r="AI92" t="n">
         <v>39.52330421009647</v>
@@ -10801,10 +10773,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04151498276815818</v>
+        <v>0.0419322183565457</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10829,25 +10801,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>14.26429335124498</v>
+        <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>2.654511247452485</v>
+        <v>3.686213841192076</v>
       </c>
       <c r="L93" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M93" t="n">
-        <v>55.73770491803279</v>
+        <v>61.40350877192982</v>
       </c>
       <c r="N93" t="n">
-        <v>18.02100894073874</v>
+        <v>19.00391756101635</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.25897879391106</v>
+        <v>2.231527290939339</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10910,10 +10882,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C94" t="n">
-        <v>7.96920770740922</v>
+        <v>8.276919261556566</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10949,46 +10921,46 @@
       </c>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R94" t="n">
-        <v>60</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="S94" t="n">
-        <v>40.13278424462001</v>
+        <v>39.62554850950509</v>
       </c>
       <c r="T94" t="n">
-        <v>19.86721575537999</v>
+        <v>21.35006124659247</v>
       </c>
       <c r="U94" t="n">
-        <v>44.59589366034619</v>
+        <v>45.72685693412379</v>
       </c>
       <c r="V94" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W94" t="n">
-        <v>70.37037037037037</v>
+        <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>46.66010699523364</v>
+        <v>51.31438474680714</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.2610966057441266</v>
+        <v>0.4391468005018773</v>
       </c>
       <c r="Z94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA94" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB94" t="n">
-        <v>10.22374238320803</v>
+        <v>14.2160206715065</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>5.753926701570689</v>
+        <v>5.585381222432273</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10997,10 +10969,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG94" t="n">
-        <v>22.47034315847598</v>
+        <v>22.52046847175919</v>
       </c>
       <c r="AH94" t="n">
-        <v>30.16123578889244</v>
+        <v>30.11111047560923</v>
       </c>
       <c r="AI94" t="n">
         <v>37.25897138449667</v>
@@ -11019,10 +10991,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C95" t="n">
-        <v>0.145823979167206</v>
+        <v>0.1454067435788184</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11054,7 +11026,7 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>9.311209593735059</v>
+        <v>8.998445348014549</v>
       </c>
       <c r="L95" t="n">
         <v>6</v>
@@ -11096,22 +11068,22 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.374302843037079</v>
+        <v>2.653632178497889</v>
       </c>
       <c r="Z95" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA95" t="n">
-        <v>45.71428571428572</v>
+        <v>42.42424242424242</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.88470059760342</v>
+        <v>11.30128484391095</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>3.713875816050272</v>
+        <v>3.437588783628931</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11142,14 +11114,14 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1318465813235382</v>
+        <v>0.1324724296992874</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11159,7 +11131,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -11173,22 +11145,22 @@
         <v>13.52465198145173</v>
       </c>
       <c r="K96" t="n">
-        <v>2.764228735541008</v>
+        <v>3.252029215414165</v>
       </c>
       <c r="L96" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M96" t="n">
-        <v>56.25</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N96" t="n">
-        <v>14.45330189893711</v>
+        <v>15.06215336209593</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.04113810174154</v>
+        <v>6.535436480873025</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11211,27 +11183,17 @@
       <c r="W96" t="n">
         <v>68.57142857142857</v>
       </c>
-      <c r="X96" t="n">
-        <v>15.85386536750038</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>11.13427556236392</v>
-      </c>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>17.45861984610253</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
         <v>8</v>
       </c>
-      <c r="AD96" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD96" t="inlineStr"/>
       <c r="AE96" t="n">
         <v>37</v>
       </c>
@@ -11261,10 +11223,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C97" t="n">
-        <v>2.034025527414657</v>
+        <v>2.007948277063187</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11281,11 +11243,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>5</v>
       </c>
@@ -11293,19 +11251,19 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>15.84006360094385</v>
+        <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>13.80336681555103</v>
+        <v>12.34434929227472</v>
       </c>
       <c r="L97" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M97" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="N97" t="n">
-        <v>14.01259117810928</v>
+        <v>14.95856036459286</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11320,10 +11278,10 @@
         <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>35.44947132877083</v>
+        <v>35.51462284392235</v>
       </c>
       <c r="T97" t="n">
-        <v>20.55052867122917</v>
+        <v>20.48537715607765</v>
       </c>
       <c r="U97" t="n">
         <v>42.30602802165686</v>
@@ -11338,22 +11296,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.662253204144192</v>
+        <v>1.935814060501329</v>
       </c>
       <c r="Z97" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA97" t="n">
-        <v>42.30769230769231</v>
+        <v>39.62264150943396</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.15732492604216</v>
+        <v>11.77031005298663</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>5.373331858256414</v>
+        <v>4.144414090181813</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11362,10 +11320,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG97" t="n">
-        <v>54.79636904025715</v>
+        <v>54.68527829062151</v>
       </c>
       <c r="AH97" t="n">
-        <v>-2.164790092888737</v>
+        <v>-2.053699343253093</v>
       </c>
       <c r="AI97" t="n">
         <v>37.25897138449667</v>
@@ -11384,10 +11342,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6467158087164551</v>
+        <v>0.6475502999205583</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11412,25 +11370,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>13.07885689309274</v>
+        <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>7.989549481999103</v>
+        <v>8.128894041020573</v>
       </c>
       <c r="L98" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M98" t="n">
-        <v>54.83870967741935</v>
+        <v>56</v>
       </c>
       <c r="N98" t="n">
-        <v>12.81696354362054</v>
+        <v>12.32760115428578</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>1.861708403863682</v>
+        <v>1.730440300508018</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11457,7 +11415,7 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.88737716358528</v>
+        <v>1.760777319163676</v>
       </c>
       <c r="Z98" t="n">
         <v>50</v>
@@ -11466,13 +11424,13 @@
         <v>40</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.44983817134005</v>
+        <v>11.12420945547702</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>6.230210404838965</v>
+        <v>6.351050538242308</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11503,10 +11461,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4501976483988334</v>
+        <v>0.4527010819564868</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11534,22 +11492,22 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>2.208308911835744</v>
+        <v>2.776663080967734</v>
       </c>
       <c r="L99" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M99" t="n">
-        <v>54.05405405405406</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N99" t="n">
-        <v>12.77718274545301</v>
+        <v>12.74581620782406</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.752979877310912</v>
+        <v>1.19028666854899</v>
       </c>
       <c r="Q99" t="n">
         <v>33</v>
@@ -11590,10 +11548,10 @@
         <v>52.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>37.03188468537733</v>
+        <v>37.49049274398539</v>
       </c>
       <c r="AH99" t="n">
-        <v>15.46811531462267</v>
+        <v>15.00950725601461</v>
       </c>
       <c r="AI99" t="n">
         <v>37.49736210669248</v>
@@ -11612,10 +11570,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C100" t="n">
-        <v>329.94960168862</v>
+        <v>334.7246721936036</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11640,19 +11598,19 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>19.03946857640767</v>
+        <v>17.72888230032435</v>
       </c>
       <c r="K100" t="n">
-        <v>7.655788758129756</v>
+        <v>9.213796341587365</v>
       </c>
       <c r="L100" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M100" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="N100" t="n">
-        <v>11.19760926904184</v>
+        <v>14.03112317782464</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11721,10 +11679,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C101" t="n">
-        <v>340.3287751585501</v>
+        <v>347.6266566522236</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11738,7 +11696,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -11749,19 +11707,19 @@
         <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>13.42090796247281</v>
+        <v>12.13141269388449</v>
       </c>
       <c r="K101" t="n">
-        <v>7.771587817393844</v>
+        <v>10.08260097198226</v>
       </c>
       <c r="L101" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M101" t="n">
-        <v>38.09523809523809</v>
+        <v>50</v>
       </c>
       <c r="N101" t="n">
-        <v>8.248575669655084</v>
+        <v>7.644950610346948</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11790,17 +11748,27 @@
       <c r="W101" t="n">
         <v>53.84615384615385</v>
       </c>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
+      <c r="X101" t="n">
+        <v>10.33806554889551</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0.2315289611453775</v>
+      </c>
       <c r="Z101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" t="inlineStr"/>
-      <c r="AB101" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>10.67405383856237</v>
+      </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
-      <c r="AD101" t="inlineStr"/>
+      <c r="AD101" t="n">
+        <v>5.781857713954652</v>
+      </c>
       <c r="AE101" t="n">
         <v>28</v>
       </c>
@@ -11830,10 +11798,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C102" t="n">
-        <v>409.8290071354064</v>
+        <v>417.7337551396031</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,10 +11897,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7364215340705434</v>
+        <v>0.7456007770970536</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11951,7 +11919,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -11961,19 +11929,19 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>19.10992799999459</v>
+        <v>16.73842567092216</v>
       </c>
       <c r="K103" t="n">
-        <v>13.26041129473905</v>
+        <v>14.67216365728923</v>
       </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M103" t="n">
-        <v>88.88888888888889</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="N103" t="n">
-        <v>14.82383750962397</v>
+        <v>16.22889652160912</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -12006,43 +11974,43 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.468059176847104</v>
+        <v>1.252356829423396</v>
       </c>
       <c r="Z103" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AA103" t="n">
-        <v>38.46153846153846</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.04732488262861</v>
+        <v>10.93585231302995</v>
       </c>
       <c r="AC103" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.722537621608472</v>
+        <v>6.833219461168028</v>
       </c>
       <c r="AE103" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AF103" t="n">
         <v>60</v>
       </c>
       <c r="AG103" t="n">
-        <v>37.00422769693243</v>
+        <v>37.06551054740267</v>
       </c>
       <c r="AH103" t="n">
-        <v>22.99577230306757</v>
+        <v>22.93448945259733</v>
       </c>
       <c r="AI103" t="n">
-        <v>44.59589366034619</v>
+        <v>43.5727090128925</v>
       </c>
       <c r="AJ103" t="n">
         <v>61</v>
       </c>
       <c r="AK103" t="n">
-        <v>52.45901639344262</v>
+        <v>50.81967213114754</v>
       </c>
     </row>
     <row r="104">
@@ -12052,10 +12020,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04693905063264593</v>
+        <v>0.04735628622103345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12083,22 +12051,22 @@
         <v>21.43553010850433</v>
       </c>
       <c r="K104" t="n">
-        <v>0.8968600816425143</v>
+        <v>1.793720163285029</v>
       </c>
       <c r="L104" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M104" t="n">
-        <v>61.90476190476191</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N104" t="n">
-        <v>12.68455071885503</v>
+        <v>12.32784198497689</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>3.075556479999997</v>
+        <v>2.167402697510146</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12133,19 +12101,19 @@
       </c>
       <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AF104" t="n">
-        <v>60</v>
+        <v>62.7906976744186</v>
       </c>
       <c r="AG104" t="n">
-        <v>38.49482306605341</v>
+        <v>40.12353702583854</v>
       </c>
       <c r="AH104" t="n">
-        <v>21.50517693394659</v>
+        <v>22.66716064858006</v>
       </c>
       <c r="AI104" t="n">
-        <v>45.45185459035139</v>
+        <v>47.85980915968847</v>
       </c>
       <c r="AJ104" t="n">
         <v>78</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -446,14 +446,14 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46254</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4032585977661874</v>
+        <v>0.4028413523727539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>2.86164737310064</v>
+        <v>2.755218027848838</v>
       </c>
       <c r="L2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>50</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="N2" t="n">
-        <v>11.25064972637323</v>
+        <v>12.63834162191096</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>6.939761134689082</v>
+        <v>7.050524646045409</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -788,7 +788,7 @@
         <v>46254</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6542260695433766</v>
+        <v>0.6504709392342248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,22 +816,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>2.350057572361441</v>
+        <v>1.762588161976053</v>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M3" t="n">
-        <v>49.0566037735849</v>
+        <v>52.72727272727273</v>
       </c>
       <c r="N3" t="n">
-        <v>14.60158168146134</v>
+        <v>14.76828998233183</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>5.520214215457631</v>
+        <v>6.129376179088353</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -897,7 +897,7 @@
         <v>46254</v>
       </c>
       <c r="C4" t="n">
-        <v>1.479101671853931</v>
+        <v>1.470756919822906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>15.33976973013975</v>
       </c>
       <c r="K4" t="n">
-        <v>14.52225247400449</v>
+        <v>13.87614421984225</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -934,7 +934,7 @@
         <v>71.42857142857143</v>
       </c>
       <c r="N4" t="n">
-        <v>14.70324685402717</v>
+        <v>15.86493857329252</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -964,25 +964,25 @@
         <v>63.01369863013699</v>
       </c>
       <c r="X4" t="n">
-        <v>15.08759256260652</v>
+        <v>15.89522479111605</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4912259228070259</v>
+        <v>1.742160278745641</v>
       </c>
       <c r="Z4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AA4" t="n">
-        <v>48.33333333333334</v>
+        <v>41.93548387096774</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.0229670175108</v>
+        <v>13.39514955256293</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.555714222563561</v>
+        <v>8.404255319148934</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1016,7 +1016,7 @@
         <v>46254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2374072894945805</v>
+        <v>0.2382417608799736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,22 +1044,22 @@
         <v>15.5457304755158</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6189185446555445</v>
+        <v>0.972587585456508</v>
       </c>
       <c r="L5" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>56</v>
+        <v>57.4074074074074</v>
       </c>
       <c r="N5" t="n">
-        <v>14.71420655378216</v>
+        <v>14.10525323679095</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.366435149357837</v>
+        <v>2.007883984182968</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1125,21 +1125,21 @@
         <v>46254</v>
       </c>
       <c r="C6" t="n">
-        <v>1.78785622046829</v>
+        <v>1.771166875790394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>9.24763393145891</v>
+        <v>8.227825181150617</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1191,22 +1191,22 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.437683631294196</v>
+        <v>3.34841185810022</v>
       </c>
       <c r="Z6" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AA6" t="n">
-        <v>40</v>
+        <v>40.27777777777778</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.87688099612406</v>
+        <v>12.71442674622671</v>
       </c>
       <c r="AC6" t="n">
         <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.5763663570478528</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>50</v>
@@ -1240,7 +1240,7 @@
         <v>46254</v>
       </c>
       <c r="C7" t="n">
-        <v>2.29688417903892</v>
+        <v>2.253074430367004</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,22 +1300,22 @@
         <v>14.22876300591287</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.824364072247909</v>
+        <v>4.677848991461264</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="AA7" t="n">
-        <v>34</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.65854591283888</v>
+        <v>10.49590782904677</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.238869760903472</v>
+        <v>0.3379602800925863</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1349,7 +1349,7 @@
         <v>46254</v>
       </c>
       <c r="C8" t="n">
-        <v>0.377807215817795</v>
+        <v>0.379476158171345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
         <v>33.33333333333334</v>
       </c>
       <c r="X8" t="n">
-        <v>21.38322708563636</v>
+        <v>24.16907222170388</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.03824392289974</v>
+        <v>2.831190168457332</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.84835456004712</v>
+        <v>15.56336848821059</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>7.034794402472421</v>
+        <v>5.319412515707056</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1458,7 +1458,7 @@
         <v>46254</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5991508896807316</v>
+        <v>0.5987336839247186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,22 +1518,22 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.660856091443943</v>
+        <v>3.727939769462729</v>
       </c>
       <c r="Z9" t="n">
         <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>50</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.62374908694097</v>
+        <v>11.80706426686921</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3520312666240533</v>
+        <v>0.2825952097480711</v>
       </c>
       <c r="AE9" t="n">
         <v>33</v>
@@ -1567,7 +1567,7 @@
         <v>46254</v>
       </c>
       <c r="C10" t="n">
-        <v>1.933888822436521</v>
+        <v>1.932845827969508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,22 +1595,22 @@
         <v>10.51321892894885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.324670362589341</v>
+        <v>0.2705627660826826</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>44.18604651162791</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N10" t="n">
-        <v>9.966898464387521</v>
+        <v>10.2480637444662</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.656963154625005</v>
+        <v>5.713977338776188</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1676,7 +1676,7 @@
         <v>46254</v>
       </c>
       <c r="C11" t="n">
-        <v>8.464675464087149</v>
+        <v>8.302996511908036</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,25 +1733,25 @@
         <v>61.76470588235294</v>
       </c>
       <c r="X11" t="n">
-        <v>21.94683558783998</v>
+        <v>22.18106016526054</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5432835918778967</v>
+        <v>2.629969418960254</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA11" t="n">
         <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.17036391195194</v>
+        <v>12.75892080722119</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.470136253082134</v>
+        <v>0.3800251256281362</v>
       </c>
       <c r="AE11" t="n">
         <v>46</v>
@@ -1785,16 +1785,16 @@
         <v>46254</v>
       </c>
       <c r="C12" t="n">
-        <v>6.967841293912774</v>
+        <v>6.847885942296012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1813,22 +1813,22 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>6.11596505162828</v>
+        <v>4.289118347895138</v>
       </c>
       <c r="L12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M12" t="n">
-        <v>62.5</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N12" t="n">
-        <v>19.57997002214874</v>
+        <v>17.98849205808463</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.640517897943661</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1855,16 +1855,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.730832727099633</v>
+        <v>7.353730067875619</v>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>33.33333333333334</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.917895439582416</v>
+        <v>10.81326983452632</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1904,11 +1904,11 @@
         <v>46254</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2265591439605589</v>
+        <v>0.2374072894945805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1932,7 +1932,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>7.312250771180584</v>
+        <v>12.45059519462108</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1964,17 +1964,27 @@
         <v>0</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>12.64821881336995</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1754343040934248</v>
+      </c>
       <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>15.2637032226069</v>
+      </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>9.84183164476261</v>
+      </c>
       <c r="AE13" t="n">
         <v>0</v>
       </c>
@@ -1997,11 +2007,11 @@
         <v>46254</v>
       </c>
       <c r="C14" t="n">
-        <v>8.683724367039497</v>
+        <v>8.527260864930678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2011,7 +2021,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2057,22 +2067,22 @@
         <v>13.13901871403786</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.8338296605122197</v>
+        <v>2.620607504466943</v>
       </c>
       <c r="Z14" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AA14" t="n">
-        <v>46.80851063829788</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.11589101364306</v>
+        <v>12.86836580373686</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.175975975975962</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2106,7 +2116,7 @@
         <v>46254</v>
       </c>
       <c r="C15" t="n">
-        <v>14.2381786919026</v>
+        <v>14.4989511954173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,25 +2173,25 @@
         <v>80.64516129032258</v>
       </c>
       <c r="X15" t="n">
-        <v>35.23869365533523</v>
+        <v>38.77434577704333</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.8714596949891185</v>
+        <v>1.627742392073606</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.07267228124085</v>
+        <v>14.66815013660483</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.208791208791201</v>
+        <v>8.510791366906467</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2215,7 +2225,7 @@
         <v>46254</v>
       </c>
       <c r="C16" t="n">
-        <v>35.86143468334149</v>
+        <v>35.9448818844662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,22 +2253,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>2.986793554262834</v>
+        <v>3.226437052934772</v>
       </c>
       <c r="L16" t="n">
         <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>72.85714285714286</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="N16" t="n">
-        <v>17.49375999887909</v>
+        <v>18.57736065544039</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.809811436688706</v>
+        <v>6.561849018959887</v>
       </c>
       <c r="Q16" t="n">
         <v>27</v>
@@ -2285,7 +2295,7 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.38416216082359</v>
+        <v>11.17795893141304</v>
       </c>
       <c r="Z16" t="n">
         <v>29</v>
@@ -2334,7 +2344,7 @@
         <v>46254</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6972013272198063</v>
+        <v>0.7113873576695462</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,25 +2369,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>14.65098631060165</v>
+        <v>14.70218665633213</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2399460697062761</v>
+        <v>2.34093273486462</v>
       </c>
       <c r="L17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
-        <v>71.42857142857143</v>
+        <v>65.625</v>
       </c>
       <c r="N17" t="n">
-        <v>15.54776227613241</v>
+        <v>15.35419475777581</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.74147855675964</v>
+        <v>5.529622521417088</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2443,7 +2453,7 @@
         <v>46254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09951078692397336</v>
+        <v>0.09971940972499919</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,22 +2481,22 @@
         <v>20.56707245057805</v>
       </c>
       <c r="K18" t="n">
-        <v>2.627639345335187</v>
+        <v>2.842796578482676</v>
       </c>
       <c r="L18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M18" t="n">
-        <v>59.45945945945946</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>16.73453332777512</v>
+        <v>15.97066094670105</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.183601514848559</v>
+        <v>6.959362891357634</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2552,7 +2562,7 @@
         <v>46254</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02503416138050118</v>
+        <v>0.02566001476308245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,22 +2590,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>1.578659337237709</v>
+        <v>4.118123175391197</v>
       </c>
       <c r="L19" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="M19" t="n">
-        <v>59.57446808510638</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N19" t="n">
-        <v>18.7988403494865</v>
+        <v>15.27516299446809</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>8.290462502368467</v>
+        <v>5.649234393805336</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2661,7 +2671,7 @@
         <v>46254</v>
       </c>
       <c r="C20" t="n">
-        <v>1.717969221236287</v>
+        <v>1.708581474946866</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,7 +2699,7 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>3.128313258792592</v>
+        <v>2.564774385009549</v>
       </c>
       <c r="L20" t="n">
         <v>37</v>
@@ -2698,7 +2708,7 @@
         <v>48.64864864864865</v>
       </c>
       <c r="N20" t="n">
-        <v>11.99625976033842</v>
+        <v>12.44028716456575</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -2770,7 +2780,7 @@
         <v>46254</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9542187799088133</v>
+        <v>0.9529670433112764</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,22 +2808,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>2.714462112093785</v>
+        <v>2.579722098556925</v>
       </c>
       <c r="L21" t="n">
         <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>54.23728813559322</v>
+        <v>57.6271186440678</v>
       </c>
       <c r="N21" t="n">
-        <v>16.94187474368925</v>
+        <v>16.37298776094086</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.145855587636761</v>
+        <v>5.283966256250294</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2879,7 +2889,7 @@
         <v>46254</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3412990653257371</v>
+        <v>0.3433852134353002</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2939,16 +2949,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.983564708456846</v>
+        <v>6.41501331070673</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>53.84615384615385</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.46288164843365</v>
+        <v>10.07750348112833</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
@@ -2980,7 +2990,7 @@
         <v>46254</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7710521191994076</v>
+        <v>0.7773106434287922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,22 +3018,22 @@
         <v>24.33755492423044</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3257299932448721</v>
+        <v>1.140060174511159</v>
       </c>
       <c r="L23" t="n">
         <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>71.42857142857143</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N23" t="n">
-        <v>19.65944222052416</v>
+        <v>21.52674789004583</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.659093940377868</v>
+        <v>3.816430224412315</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3050,7 +3060,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>24.09109964699624</v>
+        <v>23.47495752086021</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3095,7 +3105,7 @@
         <v>46254</v>
       </c>
       <c r="C24" t="n">
-        <v>0.17878562194252</v>
+        <v>0.1789942447435458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3123,7 +3133,7 @@
         <v>23.5093122581746</v>
       </c>
       <c r="K24" t="n">
-        <v>5.802460345069749</v>
+        <v>5.925919968907456</v>
       </c>
       <c r="L24" t="n">
         <v>9</v>
@@ -3132,13 +3142,13 @@
         <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>12.16385997311514</v>
+        <v>12.06452679688787</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>3.967336526239729</v>
+        <v>3.846159686211292</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3204,7 +3214,7 @@
         <v>46254</v>
       </c>
       <c r="C25" t="n">
-        <v>3.634125545352363</v>
+        <v>3.6028328449306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,22 +3242,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>3.937941891280161</v>
+        <v>3.042953857028552</v>
       </c>
       <c r="L25" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M25" t="n">
-        <v>51.11111111111111</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N25" t="n">
-        <v>15.73792626955893</v>
+        <v>14.85939201310573</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>3.908157151090008</v>
+        <v>4.810659979574461</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3313,7 +3323,7 @@
         <v>46254</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4443563301340799</v>
+        <v>0.4393495028648118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3412,7 +3422,7 @@
         <v>46254</v>
       </c>
       <c r="C27" t="n">
-        <v>43.74719518962601</v>
+        <v>43.68460978878248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3450,7 @@
         <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>32.71526106323493</v>
+        <v>32.52539659819455</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3465,10 +3475,10 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>33.34814261336958</v>
+        <v>33.98102416350424</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.474608448030378</v>
+        <v>1.086443079829946</v>
       </c>
       <c r="Z27" t="n">
         <v>10</v>
@@ -3483,7 +3493,7 @@
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.546971864568428</v>
+        <v>3.956542502387783</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3507,7 +3517,7 @@
         <v>46254</v>
       </c>
       <c r="C28" t="n">
-        <v>1.58028137129908</v>
+        <v>1.582367519408643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,7 +3577,7 @@
         <v>18.63435792130579</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.466991374761708</v>
+        <v>4.340877121335707</v>
       </c>
       <c r="Z28" t="n">
         <v>34</v>
@@ -3576,13 +3586,13 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.57311832441738</v>
+        <v>10.57564788081844</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.604689988621688</v>
+        <v>1.734411552956383</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3616,7 +3626,7 @@
         <v>46254</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4264152088039909</v>
+        <v>0.4435218787760152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3644,7 +3654,7 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>17.96025248343742</v>
+        <v>22.69251124763734</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3682,7 +3692,7 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.915944206029712</v>
+        <v>3.181653802572504</v>
       </c>
       <c r="Z29" t="n">
         <v>2</v>
@@ -3693,7 +3703,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.313194475320724</v>
+        <v>7.042411345804068</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3794,25 +3804,25 @@
         <v>64.17910447761194</v>
       </c>
       <c r="X30" t="n">
-        <v>11.24210402874228</v>
+        <v>11.81199400890234</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.4610663313478036</v>
+        <v>0.9684022521173286</v>
       </c>
       <c r="Z30" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA30" t="n">
-        <v>45.6140350877193</v>
+        <v>44.06779661016949</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.67283334448918</v>
+        <v>12.6579631094857</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>9.58311820016643</v>
+        <v>9.119915212188701</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3846,7 +3856,7 @@
         <v>46254</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1833752236370647</v>
+        <v>0.1831666008360389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3874,7 +3884,7 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>5.309226473187412</v>
+        <v>5.189417998711154</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -3889,7 +3899,7 @@
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>4.454285425794957</v>
+        <v>4.573256600153264</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3955,7 +3965,7 @@
         <v>46254</v>
       </c>
       <c r="C32" t="n">
-        <v>2.321918434923376</v>
+        <v>2.3010566346422</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3983,16 +3993,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>6.539763866636217</v>
+        <v>5.582533310058646</v>
       </c>
       <c r="L32" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M32" t="n">
-        <v>43.33333333333334</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="N32" t="n">
-        <v>12.00261846142334</v>
+        <v>11.56423396548099</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4025,22 +4035,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.613619454300434</v>
+        <v>6.461655195173666</v>
       </c>
       <c r="Z32" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="n">
-        <v>34.78260869565217</v>
+        <v>40</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.992786337953312</v>
+        <v>11.03406896062765</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.528310262457978</v>
+        <v>1.644614097070229</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4074,7 +4084,7 @@
         <v>46254</v>
       </c>
       <c r="C33" t="n">
-        <v>1.73570171976535</v>
+        <v>1.738831021517463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,7 +4112,7 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.918270502809686</v>
+        <v>6.109230865233051</v>
       </c>
       <c r="L33" t="n">
         <v>28</v>
@@ -4111,7 +4121,7 @@
         <v>64.28571428571429</v>
       </c>
       <c r="N33" t="n">
-        <v>11.16684157499097</v>
+        <v>11.05029636535382</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4183,16 +4193,16 @@
         <v>46254</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7960862956004049</v>
+        <v>0.7881587891714318</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4211,7 +4221,7 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>4.893147804613807</v>
+        <v>3.848611416822889</v>
       </c>
       <c r="L34" t="n">
         <v>22</v>
@@ -4220,13 +4230,13 @@
         <v>72.72727272727273</v>
       </c>
       <c r="N34" t="n">
-        <v>9.616943003587124</v>
+        <v>9.496752559275732</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>0.1457781487028909</v>
       </c>
       <c r="Q34" t="n">
         <v>34</v>
@@ -4292,7 +4302,7 @@
         <v>46254</v>
       </c>
       <c r="C35" t="n">
-        <v>1.965181522858285</v>
+        <v>1.953707628250684</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4324,7 +4334,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>10.78760108575154</v>
+        <v>10.14075740037126</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
@@ -4366,16 +4376,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>5.431393552994201</v>
+        <v>5.983541133733961</v>
       </c>
       <c r="Z35" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>42.85714285714285</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB35" t="n">
-        <v>14.37724655220632</v>
+        <v>15.05640991881998</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4415,7 +4425,7 @@
         <v>46254</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07990069340795994</v>
+        <v>0.08052654699915922</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,16 +4453,16 @@
         <v>14.25367779956082</v>
       </c>
       <c r="K36" t="n">
-        <v>2.406414699448067</v>
+        <v>3.208553199977127</v>
       </c>
       <c r="L36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M36" t="n">
-        <v>55.17241379310344</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N36" t="n">
-        <v>20.67596617644671</v>
+        <v>19.82880345358048</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4524,11 +4534,11 @@
         <v>46254</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06571467297188434</v>
+        <v>0.06634052635446561</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4538,7 +4548,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4552,22 +4562,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>6.972392533717642</v>
+        <v>7.991176173387937</v>
       </c>
       <c r="L37" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M37" t="n">
-        <v>58.33333333333334</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="N37" t="n">
-        <v>18.81710672338293</v>
+        <v>14.75545153938883</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9606286649692874</v>
+        <v>0.008170877403812504</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4594,22 +4604,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.60758112253119</v>
+        <v>3.699082832467171</v>
       </c>
       <c r="Z37" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AA37" t="n">
-        <v>56.14035087719298</v>
+        <v>50</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.38451986162349</v>
+        <v>13.66409114356596</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.3124759102858143</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4643,7 +4653,7 @@
         <v>46254</v>
       </c>
       <c r="C38" t="n">
-        <v>1.664771726066333</v>
+        <v>1.658513122353489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4671,22 +4681,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>5.076678908153798</v>
+        <v>4.681649798486132</v>
       </c>
       <c r="L38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M38" t="n">
-        <v>47.72727272727273</v>
+        <v>54.34782608695652</v>
       </c>
       <c r="N38" t="n">
-        <v>10.80256591746088</v>
+        <v>9.981770234747954</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>4.685455557792828</v>
+        <v>5.080499028962371</v>
       </c>
       <c r="Q38" t="n">
         <v>44</v>
@@ -4752,7 +4762,7 @@
         <v>46254</v>
       </c>
       <c r="C39" t="n">
-        <v>2.766274844540915</v>
+        <v>2.749585340687483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4769,11 +4779,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>5</v>
       </c>
@@ -4784,16 +4790,16 @@
         <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>9.501606560677555</v>
+        <v>8.840960895530481</v>
       </c>
       <c r="L39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M39" t="n">
-        <v>75</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N39" t="n">
-        <v>14.21313148586994</v>
+        <v>14.80960009189019</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4826,22 +4832,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.6731761983503004</v>
+        <v>1.272435310964581</v>
       </c>
       <c r="Z39" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA39" t="n">
-        <v>44.89795918367347</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.73574855497086</v>
+        <v>11.86145501357131</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.362925741275171</v>
+        <v>4.788495192731579</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4875,16 +4881,16 @@
         <v>46254</v>
       </c>
       <c r="C40" t="n">
-        <v>0.238658986454697</v>
+        <v>0.2522191685286875</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4899,27 +4905,17 @@
       <c r="I40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="n">
-        <v>11.14545861980583</v>
-      </c>
-      <c r="K40" t="n">
-        <v>8.414806906164806</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>18</v>
-      </c>
-      <c r="M40" t="n">
-        <v>61.11111111111111</v>
-      </c>
-      <c r="N40" t="n">
-        <v>13.02965706001775</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
         <v>27</v>
       </c>
@@ -4942,25 +4938,25 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>35.30475215033053</v>
+        <v>39.56976926502232</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.668520535304176</v>
+        <v>1.306121224489776</v>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA40" t="n">
-        <v>16.66666666666667</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB40" t="n">
-        <v>16.92890853805427</v>
+        <v>15.93550799562518</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.382185213073361</v>
+        <v>3.742763807988891</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4994,7 +4990,7 @@
         <v>46254</v>
       </c>
       <c r="C41" t="n">
-        <v>1.756563520046526</v>
+        <v>1.759692821798639</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5022,7 +5018,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>16.08361975740642</v>
+        <v>16.29042165813635</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5060,22 +5056,22 @@
         <v>19.10146270395254</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.533842052005275</v>
+        <v>2.360206988224434</v>
       </c>
       <c r="Z41" t="n">
         <v>30</v>
       </c>
       <c r="AA41" t="n">
-        <v>50</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="AB41" t="n">
-        <v>13.76360946508232</v>
+        <v>12.88336797398898</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.4782767247719533</v>
+        <v>0.6552584679265006</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5109,7 +5105,7 @@
         <v>46254</v>
       </c>
       <c r="C42" t="n">
-        <v>3.64664275277805</v>
+        <v>3.598660548502855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5167,7 +5163,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>5.708519031937476</v>
+        <v>6.949198036694271</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
@@ -5178,7 +5174,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.55129235854943</v>
+        <v>3.278641235686286</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5210,7 +5206,7 @@
         <v>46254</v>
       </c>
       <c r="C43" t="n">
-        <v>6.853101392366306</v>
+        <v>6.821808691944542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5229,7 +5225,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.56: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.08: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5239,25 +5235,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>11.88137027331979</v>
+        <v>12.62186296009862</v>
       </c>
       <c r="K43" t="n">
-        <v>0.381970970206269</v>
+        <v>0.7704160246533087</v>
       </c>
       <c r="L43" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M43" t="n">
-        <v>80.55555555555556</v>
+        <v>81.08108108108108</v>
       </c>
       <c r="N43" t="n">
-        <v>14.63490187278898</v>
+        <v>14.71915975186256</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.604261796042607</v>
+        <v>3.204892966360862</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5284,7 +5280,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.54478268842032</v>
+        <v>11.94868779029968</v>
       </c>
       <c r="Z43" t="n">
         <v>8</v>
@@ -5333,7 +5329,7 @@
         <v>46254</v>
       </c>
       <c r="C44" t="n">
-        <v>4.527010661015185</v>
+        <v>4.570820568862636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5361,22 +5357,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9772015633360942</v>
+        <v>1.954403126672211</v>
       </c>
       <c r="L44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>64.28571428571429</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N44" t="n">
-        <v>19.3802499863943</v>
+        <v>16.8319219692671</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>8.935480778801864</v>
+        <v>7.89136773556669</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5434,7 +5430,7 @@
         <v>46254</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02273936293233581</v>
+        <v>0.02336521631491709</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5491,25 +5487,25 @@
         <v>60.82474226804123</v>
       </c>
       <c r="X45" t="n">
-        <v>13.71433374328026</v>
+        <v>15.7065029425477</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.9735879319918372</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="AA45" t="n">
-        <v>46.83544303797468</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="AB45" t="n">
-        <v>13.46906584173004</v>
+        <v>12.23925506743463</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.06599813516717</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5543,7 +5539,7 @@
         <v>46254</v>
       </c>
       <c r="C46" t="n">
-        <v>9.846769732715057</v>
+        <v>9.789399781941823</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5600,25 +5596,25 @@
         <v>67.46987951807229</v>
       </c>
       <c r="X46" t="n">
-        <v>19.75557370705086</v>
+        <v>21.77676482446944</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.4219409282700481</v>
+        <v>2.645228215767648</v>
       </c>
       <c r="Z46" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AA46" t="n">
-        <v>54.54545454545455</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.21251952225099</v>
+        <v>11.47684781562648</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.58898305084746</v>
+        <v>0.3644112946190603</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5652,7 +5648,7 @@
         <v>46254</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7214010919001596</v>
+        <v>0.7101357007640862</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,22 +5676,22 @@
         <v>25.52135514083118</v>
       </c>
       <c r="K47" t="n">
-        <v>7.117741298693603</v>
+        <v>5.444991885237616</v>
       </c>
       <c r="L47" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M47" t="n">
-        <v>54.54545454545455</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N47" t="n">
-        <v>11.41702716750468</v>
+        <v>14.87153524929844</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>2.690738869548537</v>
+        <v>4.319795595147746</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5761,7 +5757,7 @@
         <v>46254</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05945612871517148</v>
+        <v>0.05883027533259021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5789,22 +5785,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>3.260866316162558</v>
+        <v>2.173910877441698</v>
       </c>
       <c r="L48" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M48" t="n">
-        <v>56.14035087719298</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="N48" t="n">
-        <v>15.05187700376106</v>
+        <v>13.99694593261976</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.526319141274373</v>
+        <v>7.659576750415042</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5870,7 +5866,7 @@
         <v>46254</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2628586914703013</v>
+        <v>0.2620242202935263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5898,16 +5894,16 @@
         <v>18.60609306322062</v>
       </c>
       <c r="K49" t="n">
-        <v>5.771372636811822</v>
+        <v>5.435590847365757</v>
       </c>
       <c r="L49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M49" t="n">
-        <v>71.42857142857143</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N49" t="n">
-        <v>14.3914678277984</v>
+        <v>15.58591386271753</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5979,7 +5975,7 @@
         <v>46254</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6909428029904219</v>
+        <v>0.6901083914783956</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6007,22 +6003,22 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>3.37078020907875</v>
+        <v>3.245945318780619</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M50" t="n">
-        <v>51.11111111111111</v>
+        <v>55.31914893617022</v>
       </c>
       <c r="N50" t="n">
-        <v>16.76810922106695</v>
+        <v>17.17727609785498</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>0.6087017914042869</v>
+        <v>0.7303479849898098</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6203,7 +6199,7 @@
         <v>46254</v>
       </c>
       <c r="C52" t="n">
-        <v>4.493631653308322</v>
+        <v>4.431046252464794</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6263,22 +6259,22 @@
         <v>16.08466358135892</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.3700291680323375</v>
+        <v>1.757633257912961</v>
       </c>
       <c r="Z52" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AA52" t="n">
-        <v>38.46153846153846</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.10932009214383</v>
+        <v>11.02536778793847</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.658308808336489</v>
+        <v>6.354047595855405</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6312,7 +6308,7 @@
         <v>46254</v>
       </c>
       <c r="C53" t="n">
-        <v>1.380008120518345</v>
+        <v>1.367491072059576</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6329,11 +6325,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6344,22 +6336,22 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>2.320185559939936</v>
+        <v>1.392113687085339</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N53" t="n">
-        <v>16.71756518363199</v>
+        <v>17.42947082383126</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>5.551020464806333</v>
+        <v>6.517160036043657</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6540,7 +6532,7 @@
         <v>46254</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9667358281589645</v>
+        <v>0.9563049280183765</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6597,25 +6589,25 @@
         <v>73.41772151898734</v>
       </c>
       <c r="X55" t="n">
-        <v>26.41142362228692</v>
+        <v>26.76177647494742</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.8779186932569405</v>
+        <v>2.218431945953014</v>
       </c>
       <c r="Z55" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA55" t="n">
-        <v>51.35135135135135</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.85141579139036</v>
+        <v>12.43173622977016</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.140876461397201</v>
+        <v>0.7992999801506473</v>
       </c>
       <c r="AE55" t="n">
         <v>46</v>
@@ -6649,7 +6641,7 @@
         <v>46254</v>
       </c>
       <c r="C56" t="n">
-        <v>1.208941342149116</v>
+        <v>1.253794164980121</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6698,25 +6690,25 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>54.96406828374303</v>
+        <v>61.88091532996977</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.5150201545064292</v>
+        <v>1.232539061393334</v>
       </c>
       <c r="Z56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA56" t="n">
-        <v>33.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="AB56" t="n">
-        <v>5.950530495629048</v>
+        <v>8.463649353473347</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>9.534082290838619</v>
+        <v>8.876871851607559</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6742,7 +6734,7 @@
         <v>46254</v>
       </c>
       <c r="C57" t="n">
-        <v>1.297603993344113</v>
+        <v>1.290302315472179</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6770,22 +6762,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>2.781652883536667</v>
+        <v>2.203295754281509</v>
       </c>
       <c r="L57" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M57" t="n">
-        <v>69.76744186046511</v>
+        <v>72.5</v>
       </c>
       <c r="N57" t="n">
-        <v>18.73607647816584</v>
+        <v>17.67721820907444</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>7.02299186085531</v>
+        <v>7.628623116482891</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6812,7 +6804,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>20.00199668758646</v>
+        <v>20.45214916367417</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -6857,7 +6849,7 @@
         <v>46254</v>
       </c>
       <c r="C58" t="n">
-        <v>0.743931794897465</v>
+        <v>0.7385077618721837</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6874,11 +6866,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6889,13 +6877,13 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>12.0778970897182</v>
+        <v>11.26073317847216</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M58" t="n">
-        <v>100</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N58" t="n">
         <v>14.19416378953196</v>
@@ -6931,22 +6919,22 @@
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.057691821077966</v>
+        <v>1.779083689043504</v>
       </c>
       <c r="Z58" t="n">
         <v>46</v>
       </c>
       <c r="AA58" t="n">
-        <v>28.26086956521739</v>
+        <v>30.43478260869565</v>
       </c>
       <c r="AB58" t="n">
-        <v>12.96779667609787</v>
+        <v>13.43716932921936</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.995141380757595</v>
+        <v>4.297370121852206</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6980,7 +6968,7 @@
         <v>46254</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7994241803075052</v>
+        <v>0.7960862956004049</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7008,22 +6996,22 @@
         <v>11.1236565078948</v>
       </c>
       <c r="K59" t="n">
-        <v>2.132194083667138</v>
+        <v>1.705755282925159</v>
       </c>
       <c r="L59" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M59" t="n">
-        <v>60.71428571428572</v>
+        <v>62.29508196721311</v>
       </c>
       <c r="N59" t="n">
-        <v>13.53151212263976</v>
+        <v>13.70908536407678</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5.745304865893641</v>
+        <v>6.188680964578164</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7089,7 +7077,7 @@
         <v>46254</v>
       </c>
       <c r="C60" t="n">
-        <v>11.98510426153559</v>
+        <v>11.87036435998913</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7117,22 +7105,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>4.33512600643009</v>
+        <v>3.336269273557391</v>
       </c>
       <c r="L60" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M60" t="n">
-        <v>52.63157894736842</v>
+        <v>51.21951219512195</v>
       </c>
       <c r="N60" t="n">
-        <v>13.35665654615755</v>
+        <v>14.05423700919043</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.512598425715274</v>
+        <v>4.513159570427816</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7198,7 +7186,7 @@
         <v>46254</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6387883421335204</v>
+        <v>0.6446296207608533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7215,11 +7203,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7230,22 +7214,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>3.952004738888459</v>
+        <v>4.902574095745571</v>
       </c>
       <c r="L61" t="n">
         <v>20</v>
       </c>
       <c r="M61" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N61" t="n">
-        <v>18.652091864523</v>
+        <v>20.66685979079341</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>5.818065054448152</v>
+        <v>4.859200022681964</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7264,16 +7248,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>9.123813573159179</v>
+        <v>8.292813552501844</v>
       </c>
       <c r="Z61" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA61" t="n">
-        <v>36</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB61" t="n">
-        <v>13.97515198363194</v>
+        <v>14.59274230445716</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7313,7 +7297,7 @@
         <v>46254</v>
       </c>
       <c r="C62" t="n">
-        <v>9.226131174350073</v>
+        <v>9.257423874771836</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7373,22 +7357,22 @@
         <v>11.63198850618248</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.6737787759685587</v>
+        <v>0.3368893879842738</v>
       </c>
       <c r="Z62" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AA62" t="n">
-        <v>45.45454545454545</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.60101493105652</v>
+        <v>11.60735392349249</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.335217637083097</v>
+        <v>1.668732394366201</v>
       </c>
       <c r="AE62" t="n">
         <v>30</v>
@@ -7422,7 +7406,7 @@
         <v>46254</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1091072158877863</v>
+        <v>0.107646886321598</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7450,16 +7434,16 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>11.02252517769273</v>
+        <v>9.536560434566832</v>
       </c>
       <c r="L63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>20</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="N63" t="n">
-        <v>18.53502896780919</v>
+        <v>19.88912843895996</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
@@ -7492,7 +7476,7 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>5.424958021837023</v>
+        <v>6.690783832718861</v>
       </c>
       <c r="Z63" t="n">
         <v>7</v>
@@ -7501,13 +7485,13 @@
         <v>42.85714285714285</v>
       </c>
       <c r="AB63" t="n">
-        <v>17.67862713243624</v>
+        <v>16.42051519623725</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>4.837472849569902</v>
+        <v>3.546505161235636</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7541,7 +7525,7 @@
         <v>46254</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1481187799101694</v>
+        <v>0.1520825232153008</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7566,25 +7550,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>24.31418588816031</v>
+        <v>24.42078296285393</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2.820871731575347</v>
       </c>
       <c r="L64" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M64" t="n">
-        <v>72.72727272727273</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N64" t="n">
-        <v>15.79298447767449</v>
+        <v>18.48340961826149</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>5.000000000000004</v>
+        <v>2.119344284605473</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7650,7 +7634,7 @@
         <v>46254</v>
       </c>
       <c r="C65" t="n">
-        <v>6.769654191241602</v>
+        <v>6.78008509138219</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7678,7 +7662,7 @@
         <v>25.04872642808169</v>
       </c>
       <c r="K65" t="n">
-        <v>19.49643512697212</v>
+        <v>19.68055906399364</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7716,22 +7700,22 @@
         <v>21.96943581422117</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.027557699796068</v>
+        <v>1.876598620751069</v>
       </c>
       <c r="Z65" t="n">
         <v>33</v>
       </c>
       <c r="AA65" t="n">
-        <v>42.42424242424242</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.23859282732489</v>
+        <v>9.398795371149316</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.013262356122592</v>
+        <v>2.164011183267023</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7765,7 +7749,7 @@
         <v>46254</v>
       </c>
       <c r="C66" t="n">
-        <v>0.456456172628218</v>
+        <v>0.4635491878530878</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7822,25 +7806,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X66" t="n">
-        <v>10.67532115313607</v>
+        <v>11.59726951852917</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.154729414909883</v>
+        <v>0.4480303825667331</v>
       </c>
       <c r="Z66" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AA66" t="n">
-        <v>30.18867924528302</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.76787362189428</v>
+        <v>11.80763088171598</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.901873965653336</v>
+        <v>5.576956075071992</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7963,7 +7947,7 @@
         <v>46254</v>
       </c>
       <c r="C68" t="n">
-        <v>3.894898048867063</v>
+        <v>3.90741525629275</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7991,7 +7975,7 @@
         <v>30.89188078077966</v>
       </c>
       <c r="K68" t="n">
-        <v>37.88921213491048</v>
+        <v>38.33235284062402</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8029,7 +8013,7 @@
         <v>128.0325939207301</v>
       </c>
       <c r="Y68" t="n">
-        <v>4.707358887362423</v>
+        <v>4.401112680149022</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8040,7 +8024,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>3.455294211801319</v>
+        <v>3.764570300708581</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8074,7 +8058,7 @@
         <v>46254</v>
       </c>
       <c r="C69" t="n">
-        <v>0.395122508382227</v>
+        <v>0.3970000737454209</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8102,7 +8086,7 @@
         <v>20.01758548606234</v>
       </c>
       <c r="K69" t="n">
-        <v>1.283421177786082</v>
+        <v>1.76470543630074</v>
       </c>
       <c r="L69" t="n">
         <v>23</v>
@@ -8111,13 +8095,13 @@
         <v>60.8695652173913</v>
       </c>
       <c r="N69" t="n">
-        <v>23.467573021129</v>
+        <v>22.30937951166133</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>6.63146914283641</v>
+        <v>6.127168095231439</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8167,7 +8151,7 @@
         <v>46254</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4247462664504409</v>
+        <v>0.4222428328927876</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8195,16 +8179,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>11.37523651789316</v>
+        <v>10.7187963638206</v>
       </c>
       <c r="L70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M70" t="n">
-        <v>35.71428571428572</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="N70" t="n">
-        <v>12.00172386214981</v>
+        <v>12.42488814076528</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8234,25 +8218,25 @@
         <v>67.79661016949153</v>
       </c>
       <c r="X70" t="n">
-        <v>11.59404295530768</v>
+        <v>12.14107466654</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.1960735820837223</v>
+        <v>1.26829380487804</v>
       </c>
       <c r="Z70" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AA70" t="n">
-        <v>44.89795918367347</v>
+        <v>43.63636363636363</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.623333329797317</v>
+        <v>9.70062685746246</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>7.819257917006517</v>
+        <v>6.81818075929751</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8286,7 +8270,7 @@
         <v>46254</v>
       </c>
       <c r="C71" t="n">
-        <v>3.143873238744728</v>
+        <v>3.13344233860414</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8314,22 +8298,22 @@
         <v>14.92600999981897</v>
       </c>
       <c r="K71" t="n">
-        <v>1.755564309865365</v>
+        <v>1.417954600610938</v>
       </c>
       <c r="L71" t="n">
         <v>69</v>
       </c>
       <c r="M71" t="n">
-        <v>59.42028985507246</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N71" t="n">
-        <v>16.94493886481091</v>
+        <v>16.87349074283409</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.2402184998849588</v>
+        <v>0.5739076494701401</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8395,7 +8379,7 @@
         <v>46254</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07239044760153462</v>
+        <v>0.07218182980734086</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8423,7 +8407,7 @@
         <v>21.72769951373251</v>
       </c>
       <c r="K72" t="n">
-        <v>2.967363301605341</v>
+        <v>2.670627683610993</v>
       </c>
       <c r="L72" t="n">
         <v>17</v>
@@ -8432,13 +8416,13 @@
         <v>52.94117647058823</v>
       </c>
       <c r="N72" t="n">
-        <v>14.07472064720535</v>
+        <v>14.15003240683303</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>1.974059190425992</v>
+        <v>2.268781606719283</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8465,7 +8449,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>19.40507599378076</v>
+        <v>19.63733778834708</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8510,7 +8494,7 @@
         <v>46254</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07405938995508468</v>
+        <v>0.07385077216089092</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8538,16 +8522,16 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>12.56956314875177</v>
+        <v>12.25246610040058</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M73" t="n">
-        <v>37.5</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N73" t="n">
-        <v>8.907419983978393</v>
+        <v>9.761369460484499</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
@@ -8577,25 +8561,25 @@
         <v>77.27272727272727</v>
       </c>
       <c r="X73" t="n">
-        <v>13.52085429380536</v>
+        <v>15.4234441942493</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.8379880075528034</v>
+        <v>2.747256517932517</v>
       </c>
       <c r="Z73" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="AA73" t="n">
-        <v>42.42424242424242</v>
+        <v>32</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.11058037917597</v>
+        <v>16.2781186484243</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>9.239437369569536</v>
+        <v>7.457623530594615</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8629,7 +8613,7 @@
         <v>46254</v>
       </c>
       <c r="C74" t="n">
-        <v>5.705702376901628</v>
+        <v>5.632686075917512</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8648,7 +8632,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -8661,16 +8645,16 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>20.71611033777965</v>
+        <v>19.17129722559601</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N74" t="n">
-        <v>18.31627048481326</v>
+        <v>16.52901193804602</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
@@ -8703,22 +8687,22 @@
         <v>35.33255906375725</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.447014848255757</v>
+        <v>2.708204786212265</v>
       </c>
       <c r="Z74" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA74" t="n">
-        <v>47.22222222222222</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB74" t="n">
-        <v>17.45041565241838</v>
+        <v>17.54270160378733</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>8.678565279960848</v>
+        <v>7.494768903960336</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8752,7 +8736,7 @@
         <v>46254</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1262138956648567</v>
+        <v>0.1264225084522184</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8764,7 @@
         <v>23.39449322057143</v>
       </c>
       <c r="K75" t="n">
-        <v>2.195947774379103</v>
+        <v>2.364862468042395</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
@@ -8795,7 +8779,7 @@
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.722312193844735</v>
+        <v>3.551157540110483</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8861,7 +8845,7 @@
         <v>46254</v>
       </c>
       <c r="C76" t="n">
-        <v>1.893208375516719</v>
+        <v>1.894251529159269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8889,7 +8873,7 @@
         <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>9.233947584729506</v>
+        <v>9.294135249112735</v>
       </c>
       <c r="L76" t="n">
         <v>20</v>
@@ -8904,7 +8888,7 @@
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>0.7012951854333593</v>
+        <v>0.6458395496504954</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8931,22 +8915,22 @@
         <v>10.78536860174914</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.400384397868171</v>
+        <v>1.346056226970815</v>
       </c>
       <c r="Z76" t="n">
         <v>56</v>
       </c>
       <c r="AA76" t="n">
-        <v>37.5</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.15080148371587</v>
+        <v>10.0833294503684</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.636537258544469</v>
+        <v>2.690154768809905</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8980,7 +8964,7 @@
         <v>46254</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5378172256433588</v>
+        <v>0.5319759071699872</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9008,16 +8992,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>10.76670395617381</v>
+        <v>9.563649157622711</v>
       </c>
       <c r="L77" t="n">
         <v>28</v>
       </c>
       <c r="M77" t="n">
-        <v>71.42857142857143</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="N77" t="n">
-        <v>16.90273640953321</v>
+        <v>16.32374360460267</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9050,22 +9034,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.742660573185342</v>
+        <v>5.777265695497025</v>
       </c>
       <c r="Z77" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AA77" t="n">
-        <v>45.65217391304348</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.33852694491439</v>
+        <v>11.36761250699244</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.519091188615254</v>
+        <v>4.481651201987214</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9099,7 +9083,7 @@
         <v>46254</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04777352180942095</v>
+        <v>0.04714766842683969</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9127,22 +9111,22 @@
         <v>19.53698884929083</v>
       </c>
       <c r="K78" t="n">
-        <v>2.232140615035072</v>
+        <v>0.8928562460140288</v>
       </c>
       <c r="L78" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M78" t="n">
-        <v>67.34693877551021</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N78" t="n">
-        <v>19.31228134149281</v>
+        <v>17.89169517458145</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>1.729259873000188</v>
+        <v>3.079646933980751</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9208,7 +9192,7 @@
         <v>46254</v>
       </c>
       <c r="C79" t="n">
-        <v>0.814444702169966</v>
+        <v>0.8177825868770663</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9236,22 +9220,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>2.724039978674409</v>
+        <v>3.145039711600206</v>
       </c>
       <c r="L79" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M79" t="n">
-        <v>56.25</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N79" t="n">
-        <v>10.39556198725482</v>
+        <v>9.830695467993385</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>2.215606027370121</v>
+        <v>1.798399897451564</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9317,7 +9301,7 @@
         <v>46254</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1289259221911614</v>
+        <v>0.1291345449921873</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9345,7 +9329,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.555490654201822</v>
+        <v>5.726296352153559</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9356,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.210590390184743</v>
+        <v>4.042233384976979</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9383,22 +9367,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.997303979247725</v>
+        <v>5.845192554217549</v>
       </c>
       <c r="Z80" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA80" t="n">
-        <v>31.42857142857143</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.86932253340606</v>
+        <v>11.5451345579825</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.130466577586398</v>
+        <v>2.28857931340708</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9432,7 +9416,7 @@
         <v>46254</v>
       </c>
       <c r="C81" t="n">
-        <v>1.211027490467297</v>
+        <v>1.187036467917467</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9489,25 +9473,25 @@
         <v>64.58333333333333</v>
       </c>
       <c r="X81" t="n">
-        <v>29.11409862854482</v>
+        <v>30.67103176118848</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>3.148933565957457</v>
       </c>
       <c r="Z81" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA81" t="n">
-        <v>70.58823529411765</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB81" t="n">
-        <v>11.71666497365729</v>
+        <v>11.67809157816785</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>9.999999999999998</v>
+        <v>7.073816206978211</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9541,11 +9525,11 @@
         <v>46254</v>
       </c>
       <c r="C82" t="n">
-        <v>5.3823444725434</v>
+        <v>5.288466371278108</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9555,7 +9539,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9601,22 +9585,22 @@
         <v>21.75875960601758</v>
       </c>
       <c r="Y82" t="n">
-        <v>3.726590188027012</v>
+        <v>5.405777568468395</v>
       </c>
       <c r="Z82" t="n">
         <v>8</v>
       </c>
       <c r="AA82" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AB82" t="n">
-        <v>10.8165986040599</v>
+        <v>14.46141572313648</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.2839930698486426</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9650,7 +9634,7 @@
         <v>46254</v>
       </c>
       <c r="C83" t="n">
-        <v>5.898674029502505</v>
+        <v>5.851734978869859</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9710,22 +9694,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.950010912821976</v>
+        <v>2.73024955277299</v>
       </c>
       <c r="Z83" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AA83" t="n">
-        <v>57.14285714285715</v>
+        <v>45.6140350877193</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.53491919845318</v>
+        <v>12.11341717953288</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>4.130534969847998</v>
+        <v>3.361528565862826</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9759,7 +9743,7 @@
         <v>46254</v>
       </c>
       <c r="C84" t="n">
-        <v>2.175885832955144</v>
+        <v>2.15711018099215</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9787,22 +9771,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>4.16520673010139</v>
+        <v>3.266368363401972</v>
       </c>
       <c r="L84" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M84" t="n">
-        <v>50</v>
+        <v>47.27272727272727</v>
       </c>
       <c r="N84" t="n">
-        <v>11.61841236501015</v>
+        <v>11.22671898513768</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0.8014127712160368</v>
+        <v>1.678795975953418</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9868,7 +9852,7 @@
         <v>46254</v>
       </c>
       <c r="C85" t="n">
-        <v>6.310694585055731</v>
+        <v>6.326340935266613</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9896,22 +9880,22 @@
         <v>15.93296998857089</v>
       </c>
       <c r="K85" t="n">
-        <v>2.004124220130787</v>
+        <v>2.257027007453427</v>
       </c>
       <c r="L85" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M85" t="n">
-        <v>58</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="N85" t="n">
-        <v>14.21277561927468</v>
+        <v>13.58324536941553</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.878071916905814</v>
+        <v>5.616213536237447</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9977,11 +9961,11 @@
         <v>46254</v>
       </c>
       <c r="C86" t="n">
-        <v>4.787783164529885</v>
+        <v>4.839937665232825</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9991,7 +9975,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -10037,7 +10021,7 @@
         <v>100.8644868744093</v>
       </c>
       <c r="Y86" t="n">
-        <v>6.671450777671839</v>
+        <v>5.654799914683506</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10048,7 +10032,7 @@
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>0.3658904586606782</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10082,7 +10066,7 @@
         <v>46254</v>
       </c>
       <c r="C87" t="n">
-        <v>5.69527147676104</v>
+        <v>5.679625126550158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10110,16 +10094,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>5.616929166201379</v>
+        <v>5.326772767393151</v>
       </c>
       <c r="L87" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M87" t="n">
-        <v>56.52173913043478</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N87" t="n">
-        <v>10.20439281236176</v>
+        <v>11.24467722556862</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10191,7 +10175,7 @@
         <v>46254</v>
       </c>
       <c r="C88" t="n">
-        <v>1.069167264410268</v>
+        <v>1.068124190251178</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10219,7 +10203,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>19.78051898661395</v>
+        <v>19.66366171995766</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10257,22 +10241,22 @@
         <v>27.20319322085054</v>
       </c>
       <c r="Y88" t="n">
-        <v>5.835289230003315</v>
+        <v>5.927155844116849</v>
       </c>
       <c r="Z88" t="n">
         <v>19</v>
       </c>
       <c r="AA88" t="n">
-        <v>36.8421052631579</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB88" t="n">
-        <v>17.15486565065062</v>
+        <v>19.17942262629681</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.1749177251752054</v>
+        <v>0.07743377649180871</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10306,7 +10290,7 @@
         <v>46254</v>
       </c>
       <c r="C89" t="n">
-        <v>2.07887842993774</v>
+        <v>2.090352324545341</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10334,16 +10318,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>12.92125703276628</v>
+        <v>13.54450011590831</v>
       </c>
       <c r="L89" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M89" t="n">
-        <v>72.22222222222223</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N89" t="n">
-        <v>12.12783772737087</v>
+        <v>11.20927338578441</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10376,22 +10360,22 @@
         <v>20.95675253601343</v>
       </c>
       <c r="Y89" t="n">
-        <v>6.643279796102908</v>
+        <v>6.128018704783111</v>
       </c>
       <c r="Z89" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA89" t="n">
-        <v>33.33333333333334</v>
+        <v>31.70731707317073</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.47962203053799</v>
+        <v>13.97360639740168</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>3.595584974028432</v>
+        <v>4.124746534367841</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10425,21 +10409,21 @@
         <v>46254</v>
       </c>
       <c r="C90" t="n">
-        <v>2.705775432840033</v>
+        <v>2.751671329830129</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10453,22 +10437,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>6.662341177136755</v>
+        <v>8.471568862469848</v>
       </c>
       <c r="L90" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M90" t="n">
-        <v>65.78947368421052</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="N90" t="n">
-        <v>15.38832552732793</v>
+        <v>14.19786003508562</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>1.25410600226914</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10495,16 +10479,16 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>11.02943839127299</v>
+        <v>9.520302163193971</v>
       </c>
       <c r="Z90" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA90" t="n">
-        <v>53.33333333333334</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB90" t="n">
-        <v>16.34928743903905</v>
+        <v>15.77585416450943</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10544,7 +10528,7 @@
         <v>46254</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2315659910485374</v>
+        <v>0.2307315198717623</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10572,16 +10556,16 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>3.436131341715587</v>
+        <v>3.063388911573117</v>
       </c>
       <c r="L91" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M91" t="n">
-        <v>64.40677966101696</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N91" t="n">
-        <v>14.1560316691676</v>
+        <v>12.98947866218588</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10653,7 +10637,7 @@
         <v>46254</v>
       </c>
       <c r="C92" t="n">
-        <v>1.129666517144233</v>
+        <v>1.128623363293066</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10685,7 +10669,7 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>7.214269532481232</v>
+        <v>7.115265997840181</v>
       </c>
       <c r="L92" t="n">
         <v>22</v>
@@ -10694,13 +10678,13 @@
         <v>77.27272727272727</v>
       </c>
       <c r="N92" t="n">
-        <v>11.47873103029748</v>
+        <v>11.61735801987519</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.7328599737190133</v>
+        <v>0.8259644355246953</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10727,16 +10711,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>6.498072513079645</v>
+        <v>6.584413830866175</v>
       </c>
       <c r="Z92" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA92" t="n">
-        <v>53.65853658536585</v>
+        <v>52.5</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.51288427766717</v>
+        <v>11.49472424221203</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10776,7 +10760,7 @@
         <v>46254</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0419322183565457</v>
+        <v>0.04214083615073946</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10804,22 +10788,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>3.686213841192076</v>
+        <v>4.202065138061895</v>
       </c>
       <c r="L93" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M93" t="n">
-        <v>61.40350877192982</v>
+        <v>64.15094339622641</v>
       </c>
       <c r="N93" t="n">
-        <v>19.00391756101635</v>
+        <v>19.53194616401082</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.231527290939339</v>
+        <v>1.725431122268017</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10885,7 +10869,7 @@
         <v>46254</v>
       </c>
       <c r="C94" t="n">
-        <v>8.276919261556566</v>
+        <v>8.214333860713039</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10942,10 +10926,10 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>51.31438474680714</v>
+        <v>52.92815171085716</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.4391468005018773</v>
+        <v>2.234636871508366</v>
       </c>
       <c r="Z94" t="n">
         <v>7</v>
@@ -10954,13 +10938,13 @@
         <v>42.85714285714285</v>
       </c>
       <c r="AB94" t="n">
-        <v>14.2160206715065</v>
+        <v>15.19291776523058</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>5.585381222432273</v>
+        <v>3.851428571428595</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10994,7 +10978,7 @@
         <v>46254</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1454067435788184</v>
+        <v>0.1445722724020434</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11026,7 +11010,7 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>8.998445348014549</v>
+        <v>8.372916856573575</v>
       </c>
       <c r="L95" t="n">
         <v>6</v>
@@ -11035,7 +11019,7 @@
         <v>100</v>
       </c>
       <c r="N95" t="n">
-        <v>15.62505504351302</v>
+        <v>18.17529258831296</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
@@ -11068,22 +11052,22 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.653632178497889</v>
+        <v>3.212290849419508</v>
       </c>
       <c r="Z95" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA95" t="n">
-        <v>42.42424242424242</v>
+        <v>40.625</v>
       </c>
       <c r="AB95" t="n">
-        <v>11.30128484391095</v>
+        <v>10.26789382897621</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>3.437588783628931</v>
+        <v>2.880230532415462</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11117,7 +11101,7 @@
         <v>46254</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1324724296992874</v>
+        <v>0.1326810525003132</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11145,22 +11129,22 @@
         <v>13.52465198145173</v>
       </c>
       <c r="K96" t="n">
-        <v>3.252029215414165</v>
+        <v>3.414634578623832</v>
       </c>
       <c r="L96" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M96" t="n">
-        <v>57.14285714285715</v>
+        <v>59.01639344262295</v>
       </c>
       <c r="N96" t="n">
-        <v>15.06215336209593</v>
+        <v>15.03684498165422</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.535436480873025</v>
+        <v>6.367924083674503</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11226,7 +11210,7 @@
         <v>46254</v>
       </c>
       <c r="C97" t="n">
-        <v>2.007948277063187</v>
+        <v>1.965181522858285</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11254,16 +11238,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>12.34434929227472</v>
+        <v>9.951556994098866</v>
       </c>
       <c r="L97" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M97" t="n">
-        <v>62.5</v>
+        <v>52</v>
       </c>
       <c r="N97" t="n">
-        <v>14.95856036459286</v>
+        <v>13.53311566960181</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11296,22 +11280,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.935814060501329</v>
+        <v>4.024456972415502</v>
       </c>
       <c r="Z97" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="AA97" t="n">
-        <v>39.62264150943396</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.77031005298663</v>
+        <v>11.68617653937229</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>4.144414090181813</v>
+        <v>2.058381713992186</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11345,7 +11329,7 @@
         <v>46254</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6475502999205583</v>
+        <v>0.6421262270492386</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11373,22 +11357,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>8.128894041020573</v>
+        <v>7.223174437700708</v>
       </c>
       <c r="L98" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M98" t="n">
-        <v>56</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="N98" t="n">
-        <v>12.32760115428578</v>
+        <v>12.25656894632272</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>1.730440300508018</v>
+        <v>2.589762499442427</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11415,22 +11399,22 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.760777319163676</v>
+        <v>2.583658109594988</v>
       </c>
       <c r="Z98" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="AA98" t="n">
-        <v>40</v>
+        <v>41.46341463414634</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.12420945547702</v>
+        <v>11.60521562902786</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>6.351050538242308</v>
+        <v>5.559993103106331</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11464,16 +11448,16 @@
         <v>46254</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4527010819564868</v>
+        <v>0.4585423605838197</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11492,22 +11476,22 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>2.776663080967734</v>
+        <v>4.102807747662296</v>
       </c>
       <c r="L99" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="M99" t="n">
-        <v>58.06451612903226</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N99" t="n">
-        <v>12.74581620782406</v>
+        <v>13.8514856594738</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.19028666854899</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>33</v>
@@ -11573,7 +11557,7 @@
         <v>46254</v>
       </c>
       <c r="C100" t="n">
-        <v>334.7246721936036</v>
+        <v>332.6361900332805</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11601,16 +11585,16 @@
         <v>17.72888230032435</v>
       </c>
       <c r="K100" t="n">
-        <v>9.213796341587365</v>
+        <v>8.532367441154731</v>
       </c>
       <c r="L100" t="n">
         <v>14</v>
       </c>
       <c r="M100" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N100" t="n">
-        <v>14.03112317782464</v>
+        <v>12.71637279982195</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11682,7 +11666,7 @@
         <v>46254</v>
       </c>
       <c r="C101" t="n">
-        <v>347.6266566522236</v>
+        <v>344.484633204693</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11710,16 +11694,16 @@
         <v>12.13141269388449</v>
       </c>
       <c r="K101" t="n">
-        <v>10.08260097198226</v>
+        <v>9.087619411160341</v>
       </c>
       <c r="L101" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M101" t="n">
-        <v>50</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N101" t="n">
-        <v>7.644950610346948</v>
+        <v>8.162722354966951</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11749,25 +11733,25 @@
         <v>53.84615384615385</v>
       </c>
       <c r="X101" t="n">
-        <v>10.33806554889551</v>
+        <v>10.77566750487711</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.2315289611453775</v>
+        <v>1.523843757152221</v>
       </c>
       <c r="Z101" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA101" t="n">
-        <v>37.5</v>
+        <v>36.58536585365854</v>
       </c>
       <c r="AB101" t="n">
-        <v>10.67405383856237</v>
+        <v>13.56149831951222</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>5.781857713954652</v>
+        <v>4.545421362516755</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11801,21 +11785,21 @@
         <v>46254</v>
       </c>
       <c r="C102" t="n">
-        <v>417.7337551396031</v>
+        <v>416.3420856305074</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>BAND</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>BAND</t>
-        </is>
-      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -11857,17 +11841,27 @@
       <c r="W102" t="n">
         <v>47.22222222222222</v>
       </c>
-      <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
+      <c r="X102" t="n">
+        <v>10.29246150171719</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0.9328813128130276</v>
+      </c>
       <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="inlineStr"/>
-      <c r="AB102" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>32.43243243243244</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>11.3058204132745</v>
+      </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
-      <c r="AD102" t="inlineStr"/>
+      <c r="AD102" t="n">
+        <v>4.105417358537755</v>
+      </c>
       <c r="AE102" t="n">
         <v>24</v>
       </c>
@@ -11900,7 +11894,7 @@
         <v>46254</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7456007770970536</v>
+        <v>0.7397594187776437</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11919,7 +11913,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -11932,16 +11926,16 @@
         <v>16.73842567092216</v>
       </c>
       <c r="K103" t="n">
-        <v>14.67216365728923</v>
+        <v>13.77377243002653</v>
       </c>
       <c r="L103" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M103" t="n">
-        <v>84.61538461538461</v>
+        <v>80</v>
       </c>
       <c r="N103" t="n">
-        <v>16.22889652160912</v>
+        <v>15.78439642498959</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -11974,22 +11968,22 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.252356829423396</v>
+        <v>2.025988489522224</v>
       </c>
       <c r="Z103" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA103" t="n">
-        <v>37.03703703703704</v>
+        <v>35.84905660377358</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.93585231302995</v>
+        <v>11.28279913615487</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.833219461168028</v>
+        <v>6.097547113133039</v>
       </c>
       <c r="AE103" t="n">
         <v>35</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -679,7 +679,7 @@
         <v>46254</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4028413523727539</v>
+        <v>0.3995034674570357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>2.755218027848838</v>
+        <v>1.903803220887501</v>
       </c>
       <c r="L2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M2" t="n">
-        <v>44.82758620689656</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N2" t="n">
-        <v>12.63834162191096</v>
+        <v>10.6972885464287</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>7.050524646045409</v>
+        <v>7.944940741380502</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -788,7 +788,7 @@
         <v>46254</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6504709392342248</v>
+        <v>0.648384751070005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,22 +816,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.762588161976053</v>
+        <v>1.436215538421459</v>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>52.72727272727273</v>
+        <v>53.7037037037037</v>
       </c>
       <c r="N3" t="n">
-        <v>14.76828998233183</v>
+        <v>13.86930271360292</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>6.129376179088353</v>
+        <v>6.470849121034439</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -897,7 +897,7 @@
         <v>46254</v>
       </c>
       <c r="C4" t="n">
-        <v>1.470756919822906</v>
+        <v>1.465541469752612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>15.33976973013975</v>
       </c>
       <c r="K4" t="n">
-        <v>13.87614421984225</v>
+        <v>13.47232810558749</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>71.42857142857143</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N4" t="n">
-        <v>15.86493857329252</v>
+        <v>15.41911658261657</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>15.89522479111605</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.742160278745641</v>
+        <v>2.090592334494767</v>
       </c>
       <c r="Z4" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AA4" t="n">
-        <v>41.93548387096774</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.39514955256293</v>
+        <v>13.06208636967171</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.404255319148934</v>
+        <v>8.078291814946626</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1016,7 +1016,7 @@
         <v>46254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2382417608799736</v>
+        <v>0.2367814411188314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,22 +1044,22 @@
         <v>15.5457304755158</v>
       </c>
       <c r="K5" t="n">
-        <v>0.972587585456508</v>
+        <v>0.3536689523836456</v>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>57.4074074074074</v>
+        <v>56</v>
       </c>
       <c r="N5" t="n">
-        <v>14.10525323679095</v>
+        <v>14.35145358327265</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.007883984182968</v>
+        <v>2.637004780435093</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1125,7 +1125,7 @@
         <v>46254</v>
       </c>
       <c r="C6" t="n">
-        <v>1.771166875790394</v>
+        <v>1.737788027050449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>8.227825181150617</v>
+        <v>6.188197941304718</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1191,16 +1191,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.34841185810022</v>
+        <v>5.16987700921664</v>
       </c>
       <c r="Z6" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="AA6" t="n">
-        <v>40.27777777777778</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.71442674622671</v>
+        <v>11.99236458706045</v>
       </c>
       <c r="AC6" t="n">
         <v>3</v>
@@ -1240,7 +1240,7 @@
         <v>46254</v>
       </c>
       <c r="C7" t="n">
-        <v>2.253074430367004</v>
+        <v>2.269763934220436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,22 +1300,22 @@
         <v>14.22876300591287</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.677848991461264</v>
+        <v>3.971756292022444</v>
       </c>
       <c r="Z7" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
-        <v>54.05405405405406</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.49590782904677</v>
+        <v>10.80683261532237</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3379602800925863</v>
+        <v>1.070772168971934</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1349,7 +1349,7 @@
         <v>46254</v>
       </c>
       <c r="C8" t="n">
-        <v>0.379476158171345</v>
+        <v>0.381770929290552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,22 +1409,22 @@
         <v>24.16907222170388</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.831190168457332</v>
+        <v>2.243590200217793</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
-        <v>70</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.56336848821059</v>
+        <v>15.14402766538854</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.319412515707056</v>
+        <v>5.888524150561658</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1458,11 +1458,11 @@
         <v>46254</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5987336839247186</v>
+        <v>0.5945613080135151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1518,22 +1518,22 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.727939769462729</v>
+        <v>4.398827738208333</v>
       </c>
       <c r="Z9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AA9" t="n">
-        <v>47.72727272727273</v>
+        <v>46.34146341463415</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.80706426686921</v>
+        <v>11.05313074983267</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2825952097480711</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>33</v>
@@ -1676,7 +1676,7 @@
         <v>46254</v>
       </c>
       <c r="C11" t="n">
-        <v>8.302996511908036</v>
+        <v>8.271703811486272</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,22 +1736,22 @@
         <v>22.18106016526054</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.629969418960254</v>
+        <v>2.996941896024463</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>53.125</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.75892080722119</v>
+        <v>12.89529469806293</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.3800251256281362</v>
+        <v>0.003152585119803319</v>
       </c>
       <c r="AE11" t="n">
         <v>46</v>
@@ -1785,7 +1785,7 @@
         <v>46254</v>
       </c>
       <c r="C12" t="n">
-        <v>6.847885942296012</v>
+        <v>6.816593241874248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,22 +1813,22 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>4.289118347895138</v>
+        <v>3.812549642573471</v>
       </c>
       <c r="L12" t="n">
         <v>23</v>
       </c>
       <c r="M12" t="n">
-        <v>65.21739130434783</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N12" t="n">
-        <v>17.98849205808463</v>
+        <v>16.85601468743039</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.640517897943661</v>
+        <v>2.107115531752113</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.353730067875619</v>
+        <v>7.777094591556311</v>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
@@ -1904,7 +1904,7 @@
         <v>46254</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2374072894945805</v>
+        <v>0.2371986669021728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>12.45059519462108</v>
+        <v>12.35177879038494</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1965,25 +1965,25 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>12.64821881336995</v>
+        <v>14.52569442666267</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1754343040934248</v>
+        <v>1.898190311930226</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>55.55555555555556</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB13" t="n">
-        <v>15.2637032226069</v>
+        <v>15.12343652173557</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>9.84183164476261</v>
+        <v>8.258573122994118</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>46254</v>
       </c>
       <c r="C14" t="n">
-        <v>8.527260864930678</v>
+        <v>8.542907215141559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,16 +2067,16 @@
         <v>13.13901871403786</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.620607504466943</v>
+        <v>2.441929720071478</v>
       </c>
       <c r="Z14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AA14" t="n">
-        <v>43.90243902439025</v>
+        <v>41.86046511627907</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.86836580373686</v>
+        <v>13.26142894611053</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2225,7 +2225,7 @@
         <v>46254</v>
       </c>
       <c r="C16" t="n">
-        <v>35.9448818844662</v>
+        <v>35.79884928249796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,22 +2253,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>3.226437052934772</v>
+        <v>2.807060930258887</v>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" t="n">
-        <v>65.71428571428571</v>
+        <v>70.4225352112676</v>
       </c>
       <c r="N16" t="n">
-        <v>18.57736065544039</v>
+        <v>17.88880952447058</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.561849018959887</v>
+        <v>6.996541876263329</v>
       </c>
       <c r="Q16" t="n">
         <v>27</v>
@@ -2295,13 +2295,13 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.17795893141304</v>
+        <v>11.53881458288149</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA16" t="n">
-        <v>51.72413793103448</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="AB16" t="n">
         <v>13.40563990076058</v>
@@ -2453,7 +2453,7 @@
         <v>46254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09971940972499919</v>
+        <v>0.09909355133558585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,22 +2481,22 @@
         <v>20.56707245057805</v>
       </c>
       <c r="K18" t="n">
-        <v>2.842796578482676</v>
+        <v>2.19733520634986</v>
       </c>
       <c r="L18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>58.33333333333334</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N18" t="n">
-        <v>15.97066094670105</v>
+        <v>14.95987164804817</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.959362891357634</v>
+        <v>7.634900438348557</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2562,7 +2562,7 @@
         <v>46254</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02566001476308245</v>
+        <v>0.02545139696888869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,22 +2590,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>4.118123175391197</v>
+        <v>3.271635229340042</v>
       </c>
       <c r="L19" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M19" t="n">
-        <v>58.62068965517241</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N19" t="n">
-        <v>15.27516299446809</v>
+        <v>15.69071474462519</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>5.649234393805336</v>
+        <v>6.51521083763027</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2671,7 +2671,7 @@
         <v>46254</v>
       </c>
       <c r="C20" t="n">
-        <v>1.708581474946866</v>
+        <v>1.704409019343586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,16 +2699,16 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>2.564774385009549</v>
+        <v>2.314305224564506</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>48.64864864864865</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N20" t="n">
-        <v>12.44028716456575</v>
+        <v>12.48292737711242</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -2780,7 +2780,7 @@
         <v>46254</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9529670433112764</v>
+        <v>0.9500464039976099</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,22 +2808,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>2.579722098556925</v>
+        <v>2.265337281947732</v>
       </c>
       <c r="L21" t="n">
         <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>57.6271186440678</v>
+        <v>55.93220338983051</v>
       </c>
       <c r="N21" t="n">
-        <v>16.37298776094086</v>
+        <v>16.53812050199843</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.283966256250294</v>
+        <v>5.607630963208665</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2889,11 +2889,11 @@
         <v>46254</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3433852134353002</v>
+        <v>0.3502696459138008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2949,22 +2949,22 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.41501331070673</v>
+        <v>4.538754530026279</v>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>57.14285714285715</v>
+        <v>37.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.07750348112833</v>
+        <v>12.51117331232154</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>0.4831756255671338</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>46254</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7773106434287922</v>
+        <v>0.7835692471416358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
         <v>24.33755492423044</v>
       </c>
       <c r="K23" t="n">
-        <v>1.140060174511159</v>
+        <v>1.954400697796954</v>
       </c>
       <c r="L23" t="n">
         <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>64.28571428571429</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N23" t="n">
-        <v>21.52674789004583</v>
+        <v>20.79983647085491</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.816430224412315</v>
+        <v>2.987217110157414</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3060,7 +3060,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>23.47495752086021</v>
+        <v>22.85880756969937</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>46254</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1789942447435458</v>
+        <v>0.1794114903455975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>23.5093122581746</v>
       </c>
       <c r="K24" t="n">
-        <v>5.925919968907456</v>
+        <v>6.17283921658287</v>
       </c>
       <c r="L24" t="n">
         <v>9</v>
@@ -3148,7 +3148,7 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>3.846159686211292</v>
+        <v>3.60465144537585</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3214,7 +3214,7 @@
         <v>46254</v>
       </c>
       <c r="C25" t="n">
-        <v>3.6028328449306</v>
+        <v>3.590315955647366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,22 +3242,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>3.042953857028552</v>
+        <v>2.684964102754894</v>
       </c>
       <c r="L25" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>57.14285714285715</v>
+        <v>55.35714285714285</v>
       </c>
       <c r="N25" t="n">
-        <v>14.85939201310573</v>
+        <v>15.14898262115284</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>4.810659979574461</v>
+        <v>5.17606053007571</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3323,7 +3323,7 @@
         <v>46254</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4393495028648118</v>
+        <v>0.4443563301340799</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>46254</v>
       </c>
       <c r="C27" t="n">
-        <v>43.68460978878248</v>
+        <v>43.43426818540837</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>32.52539659819455</v>
+        <v>31.76593873803297</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3478,22 +3478,22 @@
         <v>33.98102416350424</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.086443079829946</v>
+        <v>1.653282947567303</v>
       </c>
       <c r="Z27" t="n">
         <v>10</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB27" t="n">
-        <v>25.80591578680818</v>
+        <v>40.72118972052326</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.956542502387783</v>
+        <v>3.402977905859761</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>46254</v>
       </c>
       <c r="C28" t="n">
-        <v>1.582367519408643</v>
+        <v>1.588626123330104</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,22 +3577,22 @@
         <v>18.63435792130579</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.340877121335707</v>
+        <v>3.962524713169657</v>
       </c>
       <c r="Z28" t="n">
         <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>52.94117647058823</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.57564788081844</v>
+        <v>11.21776450342845</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.734411552956383</v>
+        <v>2.121541909286062</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3626,7 +3626,7 @@
         <v>46254</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4435218787760152</v>
+        <v>0.4180704968276227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>22.69251124763734</v>
+        <v>15.6518349802371</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.181653802572504</v>
+        <v>8.737548171262388</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3703,7 +3703,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>7.042411345804068</v>
+        <v>1.383320087769191</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3737,7 +3737,7 @@
         <v>46254</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4053447859304072</v>
+        <v>0.402632729571728</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,16 +3765,16 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>10.72920414078284</v>
+        <v>9.988343884020946</v>
       </c>
       <c r="L30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M30" t="n">
-        <v>61.53846153846154</v>
+        <v>60</v>
       </c>
       <c r="N30" t="n">
-        <v>15.83763170086855</v>
+        <v>13.51070868134244</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3807,22 +3807,22 @@
         <v>11.81199400890234</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.9684022521173286</v>
+        <v>1.630996872067414</v>
       </c>
       <c r="Z30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA30" t="n">
-        <v>44.06779661016949</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.6579631094857</v>
+        <v>12.91919266329253</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>9.119915212188701</v>
+        <v>8.507764500823878</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3856,7 +3856,7 @@
         <v>46254</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1831666008360389</v>
+        <v>0.1835838464380906</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>5.189417998711154</v>
+        <v>5.429034947663669</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -3899,7 +3899,7 @@
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>4.573256600153264</v>
+        <v>4.335584646682422</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3965,7 +3965,7 @@
         <v>46254</v>
       </c>
       <c r="C32" t="n">
-        <v>2.3010566346422</v>
+        <v>2.292711882819793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3993,16 +3993,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>5.582533310058646</v>
+        <v>5.199639632437192</v>
       </c>
       <c r="L32" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M32" t="n">
-        <v>40.54054054054054</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="N32" t="n">
-        <v>11.56423396548099</v>
+        <v>11.04464267885272</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4035,22 +4035,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.461655195173666</v>
+        <v>6.800870780537283</v>
       </c>
       <c r="Z32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.03406896062765</v>
+        <v>9.612847301691742</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.644614097070229</v>
+        <v>1.286631355362811</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4084,7 +4084,7 @@
         <v>46254</v>
       </c>
       <c r="C33" t="n">
-        <v>1.738831021517463</v>
+        <v>1.727357126909861</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,16 +4112,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>6.109230865233051</v>
+        <v>5.409055795444573</v>
       </c>
       <c r="L33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M33" t="n">
-        <v>64.28571428571429</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N33" t="n">
-        <v>11.05029636535382</v>
+        <v>10.86376214265203</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4193,7 +4193,7 @@
         <v>46254</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7881587891714318</v>
+        <v>0.7777278890308438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,22 +4221,22 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>3.848611416822889</v>
+        <v>2.474225302869404</v>
       </c>
       <c r="L34" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M34" t="n">
-        <v>72.72727272727273</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N34" t="n">
-        <v>9.496752559275732</v>
+        <v>10.26574569507419</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1457781487028909</v>
+        <v>1.488935088429377</v>
       </c>
       <c r="Q34" t="n">
         <v>34</v>
@@ -4302,7 +4302,7 @@
         <v>46254</v>
       </c>
       <c r="C35" t="n">
-        <v>1.953707628250684</v>
+        <v>1.952664474399516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>10.14075740037126</v>
+        <v>10.08194934045925</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
@@ -4376,7 +4376,7 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>5.983541133733961</v>
+        <v>6.033739858313492</v>
       </c>
       <c r="Z35" t="n">
         <v>12</v>
@@ -4653,7 +4653,7 @@
         <v>46254</v>
       </c>
       <c r="C38" t="n">
-        <v>1.658513122353489</v>
+        <v>1.655383820392759</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>4.681649798486132</v>
+        <v>4.484135237068587</v>
       </c>
       <c r="L38" t="n">
         <v>46</v>
@@ -4690,13 +4690,13 @@
         <v>54.34782608695652</v>
       </c>
       <c r="N38" t="n">
-        <v>9.981770234747954</v>
+        <v>10.99199791254927</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>5.080499028962371</v>
+        <v>5.279140943662153</v>
       </c>
       <c r="Q38" t="n">
         <v>44</v>
@@ -4762,7 +4762,7 @@
         <v>46254</v>
       </c>
       <c r="C39" t="n">
-        <v>2.749585340687483</v>
+        <v>2.737068133261797</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4790,16 +4790,16 @@
         <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>8.840960895530481</v>
+        <v>8.345473498292687</v>
       </c>
       <c r="L39" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M39" t="n">
-        <v>73.68421052631579</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N39" t="n">
-        <v>14.80960009189019</v>
+        <v>14.97049295270882</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4832,22 +4832,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.272435310964581</v>
+        <v>1.721882501258576</v>
       </c>
       <c r="Z39" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AA39" t="n">
-        <v>41.1764705882353</v>
+        <v>37.73584905660378</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.86145501357131</v>
+        <v>11.315628006777</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.788495192731579</v>
+        <v>4.353072288748527</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4881,7 +4881,7 @@
         <v>46254</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2522191685286875</v>
+        <v>0.2540967338918814</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4941,22 +4941,22 @@
         <v>39.56976926502232</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.306121224489776</v>
+        <v>0.571426040816303</v>
       </c>
       <c r="Z40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA40" t="n">
-        <v>36.36363636363637</v>
+        <v>30</v>
       </c>
       <c r="AB40" t="n">
-        <v>15.93550799562518</v>
+        <v>14.8106908363406</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.742763807988891</v>
+        <v>4.454025420299867</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4990,7 +4990,7 @@
         <v>46254</v>
       </c>
       <c r="C41" t="n">
-        <v>1.759692821798639</v>
+        <v>1.758649827331625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>16.29042165813635</v>
+        <v>16.22149470403753</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>19.10146270395254</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.360206988224434</v>
+        <v>2.418079454719779</v>
       </c>
       <c r="Z41" t="n">
         <v>30</v>
@@ -5071,7 +5071,7 @@
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.6552584679265006</v>
+        <v>0.5963405331935401</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5105,7 +5105,7 @@
         <v>46254</v>
       </c>
       <c r="C42" t="n">
-        <v>3.598660548502855</v>
+        <v>3.617436041498931</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>6.949198036694271</v>
+        <v>6.463718882160463</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
@@ -5174,7 +5174,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.278641235686286</v>
+        <v>3.780651823632408</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5206,7 +5206,7 @@
         <v>46254</v>
       </c>
       <c r="C43" t="n">
-        <v>6.821808691944542</v>
+        <v>6.827024142014836</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.08: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.38: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5238,22 +5238,22 @@
         <v>12.62186296009862</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7704160246533087</v>
+        <v>0.8474576271186418</v>
       </c>
       <c r="L43" t="n">
         <v>37</v>
       </c>
       <c r="M43" t="n">
-        <v>81.08108108108108</v>
+        <v>78.37837837837837</v>
       </c>
       <c r="N43" t="n">
-        <v>14.71915975186256</v>
+        <v>15.02781735737797</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.204892966360862</v>
+        <v>3.126050420168069</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5280,7 +5280,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.94868779029968</v>
+        <v>11.88137027331979</v>
       </c>
       <c r="Z43" t="n">
         <v>8</v>
@@ -5329,7 +5329,7 @@
         <v>46254</v>
       </c>
       <c r="C44" t="n">
-        <v>4.570820568862636</v>
+        <v>4.572906558005282</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5346,7 +5346,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5357,22 +5361,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>1.954403126672211</v>
+        <v>2.000932141487599</v>
       </c>
       <c r="L44" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M44" t="n">
-        <v>73.33333333333333</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N44" t="n">
-        <v>16.8319219692671</v>
+        <v>17.70517523055278</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>7.89136773556669</v>
+        <v>7.842151724081048</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5539,11 +5543,11 @@
         <v>46254</v>
       </c>
       <c r="C46" t="n">
-        <v>9.789399781941823</v>
+        <v>9.632936279833004</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5553,7 +5557,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5599,22 +5603,22 @@
         <v>21.77676482446944</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.645228215767648</v>
+        <v>4.201244813278016</v>
       </c>
       <c r="Z46" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA46" t="n">
-        <v>44.11764705882353</v>
+        <v>40</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.47684781562648</v>
+        <v>11.19370112057261</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.3644112946190603</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5648,7 +5652,7 @@
         <v>46254</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7101357007640862</v>
+        <v>0.7055460790422132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,22 +5680,22 @@
         <v>25.52135514083118</v>
       </c>
       <c r="K47" t="n">
-        <v>5.444991885237616</v>
+        <v>4.763498721749992</v>
       </c>
       <c r="L47" t="n">
         <v>14</v>
       </c>
       <c r="M47" t="n">
-        <v>64.28571428571429</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N47" t="n">
-        <v>14.87153524929844</v>
+        <v>15.95694146360898</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.319795595147746</v>
+        <v>4.998402441825722</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5757,7 +5761,7 @@
         <v>46254</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05883027533259021</v>
+        <v>0.05903889312678397</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5785,22 +5789,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>2.173910877441698</v>
+        <v>2.53622935701534</v>
       </c>
       <c r="L48" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M48" t="n">
-        <v>51.61290322580645</v>
+        <v>49.18032786885246</v>
       </c>
       <c r="N48" t="n">
-        <v>13.99694593261976</v>
+        <v>14.10204973331093</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>7.659576750415042</v>
+        <v>7.279154587396586</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5866,16 +5870,16 @@
         <v>46254</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2620242202935263</v>
+        <v>0.2599380323379246</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5894,22 +5898,22 @@
         <v>18.60609306322062</v>
       </c>
       <c r="K49" t="n">
-        <v>5.435590847365757</v>
+        <v>4.596132344365089</v>
       </c>
       <c r="L49" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M49" t="n">
-        <v>68.96551724137932</v>
+        <v>65.625</v>
       </c>
       <c r="N49" t="n">
-        <v>15.58591386271753</v>
+        <v>14.90372301236042</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.3861210224344047</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5975,7 +5979,7 @@
         <v>46254</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6901083914783956</v>
+        <v>0.6880221636767554</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6003,22 +6007,22 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>3.245945318780619</v>
+        <v>2.93382831775526</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>55.31914893617022</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N50" t="n">
-        <v>17.17727609785498</v>
+        <v>14.93524715750164</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>0.7303479849898098</v>
+        <v>1.035783570541549</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6199,7 +6203,7 @@
         <v>46254</v>
       </c>
       <c r="C52" t="n">
-        <v>4.431046252464794</v>
+        <v>4.487373367737932</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6259,22 +6263,22 @@
         <v>16.08466358135892</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.757633257912961</v>
+        <v>0.5087839340971012</v>
       </c>
       <c r="Z52" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AA52" t="n">
-        <v>45.45454545454545</v>
+        <v>41.02564102564103</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.02536778793847</v>
+        <v>11.65504806412742</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>6.354047595855405</v>
+        <v>7.529525079822841</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6308,7 +6312,7 @@
         <v>46254</v>
       </c>
       <c r="C53" t="n">
-        <v>1.367491072059576</v>
+        <v>1.37166336848732</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6336,7 +6340,7 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>1.392113687085339</v>
+        <v>1.701467044033356</v>
       </c>
       <c r="L53" t="n">
         <v>7</v>
@@ -6351,7 +6355,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>6.517160036043657</v>
+        <v>6.193158406692012</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6409,7 +6413,7 @@
         <v>46254</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08136102318276631</v>
+        <v>0.08115240517995455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6428,7 +6432,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir. SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -6441,7 +6445,7 @@
         <v>42.98617858772242</v>
       </c>
       <c r="K54" t="n">
-        <v>1.701703323058701</v>
+        <v>1.440929731480955</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
@@ -6456,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>8.159447094589467</v>
+        <v>8.437491938584675</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6483,16 +6487,16 @@
         <v>10.17240666043591</v>
       </c>
       <c r="Y54" t="n">
-        <v>7.688588816512743</v>
+        <v>7.925284736555116</v>
       </c>
       <c r="Z54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA54" t="n">
-        <v>75</v>
+        <v>73.91304347826087</v>
       </c>
       <c r="AB54" t="n">
-        <v>15.59141213484551</v>
+        <v>14.64958628095488</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6532,11 +6536,11 @@
         <v>46254</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9563049280183765</v>
+        <v>0.9450395368823031</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6546,7 +6550,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6592,22 +6596,22 @@
         <v>26.76177647494742</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.218431945953014</v>
+        <v>3.370310993894354</v>
       </c>
       <c r="Z55" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="AA55" t="n">
-        <v>47.22222222222222</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.43173622977016</v>
+        <v>12.18091230502987</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.7992999801506473</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>46</v>
@@ -6641,7 +6645,7 @@
         <v>46254</v>
       </c>
       <c r="C56" t="n">
-        <v>1.253794164980121</v>
+        <v>1.250664942711468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6693,7 +6697,7 @@
         <v>61.88091532996977</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.232539061393334</v>
+        <v>1.479043110319411</v>
       </c>
       <c r="Z56" t="n">
         <v>4</v>
@@ -6702,13 +6706,13 @@
         <v>25</v>
       </c>
       <c r="AB56" t="n">
-        <v>8.463649353473347</v>
+        <v>7.109081084502133</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>8.876871851607559</v>
+        <v>8.648877516711472</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6734,7 +6738,7 @@
         <v>46254</v>
       </c>
       <c r="C57" t="n">
-        <v>1.290302315472179</v>
+        <v>1.308034893484701</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6762,22 +6766,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>2.203295754281509</v>
+        <v>3.607871948067887</v>
       </c>
       <c r="L57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M57" t="n">
-        <v>72.5</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N57" t="n">
-        <v>17.67721820907444</v>
+        <v>17.8456315989677</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>7.628623116482891</v>
+        <v>6.16953898554744</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6804,7 +6808,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>20.45214916367417</v>
+        <v>19.35892592926696</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -6849,7 +6853,7 @@
         <v>46254</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7385077618721837</v>
+        <v>0.7414284011858502</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6866,7 +6870,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6877,13 +6885,13 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>11.26073317847216</v>
+        <v>11.70074544126085</v>
       </c>
       <c r="L58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M58" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="N58" t="n">
         <v>14.19416378953196</v>
@@ -6919,7 +6927,7 @@
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.779083689043504</v>
+        <v>1.390641096544687</v>
       </c>
       <c r="Z58" t="n">
         <v>46</v>
@@ -6934,7 +6942,7 @@
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.297370121852206</v>
+        <v>4.674362509514096</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6968,7 +6976,7 @@
         <v>46254</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7960862956004049</v>
+        <v>0.7919139194805837</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6996,22 +7004,22 @@
         <v>11.1236565078948</v>
       </c>
       <c r="K59" t="n">
-        <v>1.705755282925159</v>
+        <v>1.172704196709939</v>
       </c>
       <c r="L59" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M59" t="n">
-        <v>62.29508196721311</v>
+        <v>64.91228070175438</v>
       </c>
       <c r="N59" t="n">
-        <v>13.70908536407678</v>
+        <v>13.07785096747549</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.188680964578164</v>
+        <v>6.748159849533897</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7077,7 +7085,7 @@
         <v>46254</v>
       </c>
       <c r="C60" t="n">
-        <v>11.87036435998913</v>
+        <v>11.88079526012971</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7113,7 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>3.336269273557391</v>
+        <v>3.42707443109127</v>
       </c>
       <c r="L60" t="n">
         <v>41</v>
@@ -7120,7 +7128,7 @@
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>4.513159570427816</v>
+        <v>4.421400870190384</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7186,7 +7194,7 @@
         <v>46254</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6446296207608533</v>
+        <v>0.6437951694027886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7214,7 +7222,7 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>4.902574095745571</v>
+        <v>4.766781242610207</v>
       </c>
       <c r="L61" t="n">
         <v>20</v>
@@ -7229,7 +7237,7 @@
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>4.859200022681964</v>
+        <v>4.995112663880685</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7248,16 +7256,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>8.292813552501844</v>
+        <v>8.41152542023309</v>
       </c>
       <c r="Z61" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA61" t="n">
-        <v>38.46153846153846</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="AB61" t="n">
-        <v>14.59274230445716</v>
+        <v>14.87198827034417</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7354,25 +7362,25 @@
         <v>73.13432835820896</v>
       </c>
       <c r="X62" t="n">
-        <v>11.63198850618248</v>
+        <v>11.694667893328</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.3368893879842738</v>
+        <v>0.3928170594837188</v>
       </c>
       <c r="Z62" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA62" t="n">
-        <v>46.15384615384615</v>
+        <v>47.16981132075472</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.60735392349249</v>
+        <v>11.85406656056139</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.668732394366201</v>
+        <v>1.613521126760575</v>
       </c>
       <c r="AE62" t="n">
         <v>30</v>
@@ -7406,7 +7414,7 @@
         <v>46254</v>
       </c>
       <c r="C63" t="n">
-        <v>0.107646886321598</v>
+        <v>0.1063951793478174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7434,16 +7442,16 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>9.536560434566832</v>
+        <v>8.262880523656357</v>
       </c>
       <c r="L63" t="n">
         <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>28.57142857142857</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N63" t="n">
-        <v>19.88912843895996</v>
+        <v>15.62495857587261</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
@@ -7476,22 +7484,22 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>6.690783832718861</v>
+        <v>7.775773845766265</v>
       </c>
       <c r="Z63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA63" t="n">
-        <v>42.85714285714285</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB63" t="n">
-        <v>16.42051519623725</v>
+        <v>14.62163007479386</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.546505161235636</v>
+        <v>2.411759086505083</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7525,7 +7533,7 @@
         <v>46254</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1520825232153008</v>
+        <v>0.1508308164501383</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7553,22 +7561,22 @@
         <v>24.42078296285393</v>
       </c>
       <c r="K64" t="n">
-        <v>2.820871731575347</v>
+        <v>1.974610254415876</v>
       </c>
       <c r="L64" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M64" t="n">
-        <v>55.55555555555556</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N64" t="n">
-        <v>18.48340961826149</v>
+        <v>17.07816799144163</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>2.119344284605473</v>
+        <v>2.96680687284423</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7634,7 +7642,7 @@
         <v>46254</v>
       </c>
       <c r="C65" t="n">
-        <v>6.78008509138219</v>
+        <v>6.686206990116898</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7662,7 +7670,7 @@
         <v>25.04872642808169</v>
       </c>
       <c r="K65" t="n">
-        <v>19.68055906399364</v>
+        <v>18.02344363079989</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7700,22 +7708,22 @@
         <v>21.96943581422117</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.876598620751069</v>
+        <v>3.235230332156058</v>
       </c>
       <c r="Z65" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA65" t="n">
-        <v>39.39393939393939</v>
+        <v>34.375</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.398795371149316</v>
+        <v>10.63891475894801</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.164011183267023</v>
+        <v>0.79033895339089</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7749,7 +7757,7 @@
         <v>46254</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4635491878530878</v>
+        <v>0.4660526214107412</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7806,25 +7814,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X66" t="n">
-        <v>11.59726951852917</v>
+        <v>12.19725904675169</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.4480303825667331</v>
+        <v>0.4456344814533719</v>
       </c>
       <c r="Z66" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA66" t="n">
-        <v>36.36363636363637</v>
+        <v>37.5</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.80763088171598</v>
+        <v>11.59642256340731</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>5.576956075071992</v>
+        <v>5.579228484472509</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7858,7 +7866,7 @@
         <v>46254</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0279548130026298</v>
+        <v>0.02753757741424229</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7886,22 +7894,22 @@
         <v>14.0514682678307</v>
       </c>
       <c r="K67" t="n">
-        <v>3.875974538789895</v>
+        <v>2.325588444204296</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M67" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="N67" t="n">
-        <v>7.104188996989391</v>
+        <v>7.077382387711928</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0.1193976391179907</v>
+        <v>1.636356634986491</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7947,7 +7955,7 @@
         <v>46254</v>
       </c>
       <c r="C68" t="n">
-        <v>3.90741525629275</v>
+        <v>3.894898048867063</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7975,7 +7983,7 @@
         <v>30.89188078077966</v>
       </c>
       <c r="K68" t="n">
-        <v>38.33235284062402</v>
+        <v>37.88921213491048</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8013,7 +8021,7 @@
         <v>128.0325939207301</v>
       </c>
       <c r="Y68" t="n">
-        <v>4.401112680149022</v>
+        <v>4.707358887362423</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8024,7 +8032,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>3.764570300708581</v>
+        <v>3.455294211801319</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8058,7 +8066,7 @@
         <v>46254</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3970000737454209</v>
+        <v>0.3967914509443951</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8086,7 +8094,7 @@
         <v>20.01758548606234</v>
       </c>
       <c r="K69" t="n">
-        <v>1.76470543630074</v>
+        <v>1.711228272698739</v>
       </c>
       <c r="L69" t="n">
         <v>23</v>
@@ -8101,7 +8109,7 @@
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>6.127168095231439</v>
+        <v>6.182967047099641</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8151,7 +8159,7 @@
         <v>46254</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4222428328927876</v>
+        <v>0.4247462664504409</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8179,16 +8187,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>10.7187963638206</v>
+        <v>11.37523651789316</v>
       </c>
       <c r="L70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M70" t="n">
-        <v>38.46153846153846</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="N70" t="n">
-        <v>12.42488814076528</v>
+        <v>12.00172386214981</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8221,22 +8229,22 @@
         <v>12.14107466654</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.26829380487804</v>
+        <v>0.6829238536585458</v>
       </c>
       <c r="Z70" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AA70" t="n">
-        <v>43.63636363636363</v>
+        <v>45.28301886792453</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.70062685746246</v>
+        <v>9.427036263969123</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>6.81818075929751</v>
+        <v>7.367389808737324</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8270,7 +8278,7 @@
         <v>46254</v>
       </c>
       <c r="C71" t="n">
-        <v>3.13344233860414</v>
+        <v>3.127183734891296</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8298,22 +8306,22 @@
         <v>14.92600999981897</v>
       </c>
       <c r="K71" t="n">
-        <v>1.417954600610938</v>
+        <v>1.215386715639033</v>
       </c>
       <c r="L71" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M71" t="n">
-        <v>60.8695652173913</v>
+        <v>60.29411764705883</v>
       </c>
       <c r="N71" t="n">
-        <v>16.87349074283409</v>
+        <v>16.85799615847782</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.5739076494701401</v>
+        <v>0.775191707329359</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8494,7 +8502,7 @@
         <v>46254</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07385077216089092</v>
+        <v>0.07426800774927843</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8522,16 +8530,16 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>12.25246610040058</v>
+        <v>12.88666019710296</v>
       </c>
       <c r="L73" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M73" t="n">
-        <v>44.44444444444444</v>
+        <v>50</v>
       </c>
       <c r="N73" t="n">
-        <v>9.761369460484499</v>
+        <v>8.907419983978393</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
@@ -8564,7 +8572,7 @@
         <v>15.4234441942493</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.747256517932517</v>
+        <v>2.197806533027302</v>
       </c>
       <c r="Z73" t="n">
         <v>25</v>
@@ -8573,13 +8581,13 @@
         <v>32</v>
       </c>
       <c r="AB73" t="n">
-        <v>16.2781186484243</v>
+        <v>14.9990389298822</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>7.457623530594615</v>
+        <v>7.97752401085714</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8613,7 +8621,7 @@
         <v>46254</v>
       </c>
       <c r="C74" t="n">
-        <v>5.632686075917512</v>
+        <v>5.653547876198687</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8632,7 +8640,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -8645,13 +8653,13 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>19.17129722559601</v>
+        <v>19.61267240050562</v>
       </c>
       <c r="L74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M74" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N74" t="n">
         <v>16.52901193804602</v>
@@ -8687,7 +8695,7 @@
         <v>35.33255906375725</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.708204786212265</v>
+        <v>2.347864803938982</v>
       </c>
       <c r="Z74" t="n">
         <v>30</v>
@@ -8696,13 +8704,13 @@
         <v>53.33333333333334</v>
       </c>
       <c r="AB74" t="n">
-        <v>17.54270160378733</v>
+        <v>17.54625934594731</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>7.494768903960336</v>
+        <v>7.836116620181876</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8736,7 +8744,7 @@
         <v>46254</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1264225084522184</v>
+        <v>0.1260052728638308</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8764,7 +8772,7 @@
         <v>23.39449322057143</v>
       </c>
       <c r="K75" t="n">
-        <v>2.364862468042395</v>
+        <v>2.02702497260776</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
@@ -8773,13 +8781,13 @@
         <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>13.60056277290218</v>
+        <v>14.84310636894291</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.551157540110483</v>
+        <v>3.894041827112882</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8845,7 +8853,7 @@
         <v>46254</v>
       </c>
       <c r="C76" t="n">
-        <v>1.894251529159269</v>
+        <v>1.899466979229563</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8873,22 +8881,22 @@
         <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>9.294135249112735</v>
+        <v>9.595055214910865</v>
       </c>
       <c r="L76" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M76" t="n">
-        <v>70</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N76" t="n">
-        <v>8.424939522696532</v>
+        <v>8.249073048793266</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>0.6458395496504954</v>
+        <v>0.3694918391117907</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8915,7 +8923,7 @@
         <v>10.78536860174914</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.346056226970815</v>
+        <v>1.074431941565501</v>
       </c>
       <c r="Z76" t="n">
         <v>56</v>
@@ -8924,13 +8932,13 @@
         <v>39.28571428571428</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.0833294503684</v>
+        <v>10.13190010644236</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.690154768809905</v>
+        <v>2.957342692949105</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8964,7 +8972,7 @@
         <v>46254</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5319759071699872</v>
+        <v>0.5298897192143855</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8992,7 +9000,7 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>9.563649157622711</v>
+        <v>9.133986155663942</v>
       </c>
       <c r="L77" t="n">
         <v>28</v>
@@ -9001,7 +9009,7 @@
         <v>67.85714285714286</v>
       </c>
       <c r="N77" t="n">
-        <v>16.32374360460267</v>
+        <v>16.6358709563936</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9034,22 +9042,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>5.777265695497025</v>
+        <v>6.146768018441707</v>
       </c>
       <c r="Z77" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AA77" t="n">
-        <v>46.15384615384615</v>
+        <v>37.83783783783784</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.36761250699244</v>
+        <v>11.95892613000971</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.481651201987214</v>
+        <v>4.105593276015718</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9192,7 +9200,7 @@
         <v>46254</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8177825868770663</v>
+        <v>0.8190342439911441</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9220,7 +9228,7 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>3.145039711600206</v>
+        <v>3.302908349070055</v>
       </c>
       <c r="L79" t="n">
         <v>30</v>
@@ -9229,13 +9237,13 @@
         <v>46.66666666666666</v>
       </c>
       <c r="N79" t="n">
-        <v>9.830695467993385</v>
+        <v>10.0183789596289</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.798399897451564</v>
+        <v>1.64283046629754</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9301,7 +9309,7 @@
         <v>46254</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1291345449921873</v>
+        <v>0.1289259221911614</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9329,7 +9337,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.726296352153559</v>
+        <v>5.555490654201822</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9340,7 +9348,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.042233384976979</v>
+        <v>4.210590390184743</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9367,22 +9375,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.845192554217549</v>
+        <v>5.997303979247725</v>
       </c>
       <c r="Z80" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA80" t="n">
-        <v>33.33333333333334</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.5451345579825</v>
+        <v>11.86932253340606</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.28857931340708</v>
+        <v>2.130466577586398</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9416,7 +9424,7 @@
         <v>46254</v>
       </c>
       <c r="C81" t="n">
-        <v>1.187036467917467</v>
+        <v>1.191208764136593</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9476,22 +9484,22 @@
         <v>30.67103176118848</v>
       </c>
       <c r="Y81" t="n">
-        <v>3.148933565957457</v>
+        <v>2.80851324255319</v>
       </c>
       <c r="Z81" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA81" t="n">
-        <v>57.14285714285715</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB81" t="n">
-        <v>11.67809157816785</v>
+        <v>9.146804146204286</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>7.073816206978211</v>
+        <v>7.399296993361193</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9525,7 +9533,7 @@
         <v>46254</v>
       </c>
       <c r="C82" t="n">
-        <v>5.288466371278108</v>
+        <v>5.236311870575168</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9585,16 +9593,16 @@
         <v>21.75875960601758</v>
       </c>
       <c r="Y82" t="n">
-        <v>5.405777568468395</v>
+        <v>6.33865944649139</v>
       </c>
       <c r="Z82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA82" t="n">
-        <v>25</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB82" t="n">
-        <v>14.46141572313648</v>
+        <v>11.46870465137741</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9634,7 +9642,7 @@
         <v>46254</v>
       </c>
       <c r="C83" t="n">
-        <v>5.851734978869859</v>
+        <v>5.789149578026332</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9694,22 +9702,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.73024955277299</v>
+        <v>3.770567739374342</v>
       </c>
       <c r="Z83" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA83" t="n">
-        <v>45.6140350877193</v>
+        <v>46</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.11341717953288</v>
+        <v>12.49448922988003</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.361528565862826</v>
+        <v>2.316788334142428</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9743,7 +9751,7 @@
         <v>46254</v>
       </c>
       <c r="C84" t="n">
-        <v>2.15711018099215</v>
+        <v>2.152937725388869</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9771,22 +9779,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>3.266368363401972</v>
+        <v>3.066622267395824</v>
       </c>
       <c r="L84" t="n">
         <v>55</v>
       </c>
       <c r="M84" t="n">
-        <v>47.27272727272727</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N84" t="n">
-        <v>11.22671898513768</v>
+        <v>11.54048130099055</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>1.678795975953418</v>
+        <v>1.875852424452429</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9852,7 +9860,7 @@
         <v>46254</v>
       </c>
       <c r="C85" t="n">
-        <v>6.326340935266613</v>
+        <v>6.284617334704261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9880,22 +9888,22 @@
         <v>15.93296998857089</v>
       </c>
       <c r="K85" t="n">
-        <v>2.257027007453427</v>
+        <v>1.582619574593047</v>
       </c>
       <c r="L85" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M85" t="n">
-        <v>52.08333333333334</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="N85" t="n">
-        <v>13.58324536941553</v>
+        <v>15.55268137112559</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.616213536237447</v>
+        <v>6.317400016146091</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9961,7 +9969,7 @@
         <v>46254</v>
       </c>
       <c r="C86" t="n">
-        <v>4.839937665232825</v>
+        <v>4.831593072377336</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10021,7 +10029,7 @@
         <v>100.8644868744093</v>
       </c>
       <c r="Y86" t="n">
-        <v>5.654799914683506</v>
+        <v>5.817461572133542</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10032,7 +10040,7 @@
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.3658904586606782</v>
+        <v>0.1938134508938427</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10066,7 +10074,7 @@
         <v>46254</v>
       </c>
       <c r="C87" t="n">
-        <v>5.679625126550158</v>
+        <v>5.684840576620451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10094,7 +10102,7 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>5.326772767393151</v>
+        <v>5.423491566995886</v>
       </c>
       <c r="L87" t="n">
         <v>24</v>
@@ -10103,7 +10111,7 @@
         <v>54.16666666666666</v>
       </c>
       <c r="N87" t="n">
-        <v>11.24467722556862</v>
+        <v>11.04030646165189</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10175,7 +10183,7 @@
         <v>46254</v>
       </c>
       <c r="C88" t="n">
-        <v>1.068124190251178</v>
+        <v>1.056650216160117</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10189,7 +10197,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10203,10 +10211,10 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>19.66366171995766</v>
+        <v>18.37821404753544</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
@@ -10241,22 +10249,22 @@
         <v>27.20319322085054</v>
       </c>
       <c r="Y88" t="n">
-        <v>5.927155844116849</v>
+        <v>6.937702544929958</v>
       </c>
       <c r="Z88" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA88" t="n">
-        <v>31.57894736842105</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB88" t="n">
-        <v>19.17942262629681</v>
+        <v>14.55636040212929</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.07743377649180871</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10290,7 +10298,7 @@
         <v>46254</v>
       </c>
       <c r="C89" t="n">
-        <v>2.090352324545341</v>
+        <v>2.115386580429798</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10318,16 +10326,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>13.54450011590831</v>
+        <v>14.9043197199038</v>
       </c>
       <c r="L89" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>69.23076923076923</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N89" t="n">
-        <v>11.20927338578441</v>
+        <v>14.19332941038719</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10360,22 +10368,22 @@
         <v>20.95675253601343</v>
       </c>
       <c r="Y89" t="n">
-        <v>6.128018704783111</v>
+        <v>5.003799034954747</v>
       </c>
       <c r="Z89" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AA89" t="n">
-        <v>31.70731707317073</v>
+        <v>29.54545454545455</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.97360639740168</v>
+        <v>12.54478470506723</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>4.124746534367841</v>
+        <v>5.259369231916599</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10409,7 +10417,7 @@
         <v>46254</v>
       </c>
       <c r="C90" t="n">
-        <v>2.751671329830129</v>
+        <v>2.74541304425974</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10437,16 +10445,16 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>8.471568862469848</v>
+        <v>8.224865687257644</v>
       </c>
       <c r="L90" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M90" t="n">
-        <v>64.86486486486487</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N90" t="n">
-        <v>14.19786003508562</v>
+        <v>16.04685375495613</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
@@ -10479,7 +10487,7 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>9.520302163193971</v>
+        <v>9.726085383466931</v>
       </c>
       <c r="Z90" t="n">
         <v>17</v>
@@ -10488,7 +10496,7 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AB90" t="n">
-        <v>15.77585416450943</v>
+        <v>15.5455038079218</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10528,16 +10536,16 @@
         <v>46254</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2307315198717623</v>
+        <v>0.2292711802919098</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10556,22 +10564,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>3.063388911573117</v>
+        <v>2.41108294945338</v>
       </c>
       <c r="L91" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M91" t="n">
-        <v>61.90476190476191</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N91" t="n">
-        <v>12.98947866218588</v>
+        <v>15.26385963516832</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>0.5750520681802485</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10869,7 +10877,7 @@
         <v>46254</v>
       </c>
       <c r="C94" t="n">
-        <v>8.214333860713039</v>
+        <v>8.235195660994213</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10929,7 +10937,7 @@
         <v>52.92815171085716</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.234636871508366</v>
+        <v>1.986343885785236</v>
       </c>
       <c r="Z94" t="n">
         <v>7</v>
@@ -10938,13 +10946,13 @@
         <v>42.85714285714285</v>
       </c>
       <c r="AB94" t="n">
-        <v>15.19291776523058</v>
+        <v>15.72595103883507</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.851428571428595</v>
+        <v>4.09499683343888</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10978,7 +10986,7 @@
         <v>46254</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1445722724020434</v>
+        <v>0.1447808952030692</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11010,16 +11018,16 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>8.372916856573575</v>
+        <v>8.529302732608524</v>
       </c>
       <c r="L95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M95" t="n">
         <v>100</v>
       </c>
       <c r="N95" t="n">
-        <v>18.17529258831296</v>
+        <v>16.62423732037097</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
@@ -11052,22 +11060,22 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>3.212290849419508</v>
+        <v>3.072622829733718</v>
       </c>
       <c r="Z95" t="n">
         <v>32</v>
       </c>
       <c r="AA95" t="n">
-        <v>40.625</v>
+        <v>43.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.26789382897621</v>
+        <v>10.25290628307341</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.880230532415462</v>
+        <v>3.020175780805401</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11101,7 +11109,7 @@
         <v>46254</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1326810525003132</v>
+        <v>0.1322638169119257</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11129,22 +11137,22 @@
         <v>13.52465198145173</v>
       </c>
       <c r="K96" t="n">
-        <v>3.414634578623832</v>
+        <v>3.08943165708242</v>
       </c>
       <c r="L96" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M96" t="n">
-        <v>59.01639344262295</v>
+        <v>56.92307692307692</v>
       </c>
       <c r="N96" t="n">
-        <v>15.03684498165422</v>
+        <v>14.43826969997416</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.367924083674503</v>
+        <v>6.70346924203149</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11210,7 +11218,7 @@
         <v>46254</v>
       </c>
       <c r="C97" t="n">
-        <v>1.965181522858285</v>
+        <v>1.966224676500835</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11238,16 +11246,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>9.951556994098866</v>
+        <v>10.00992125503266</v>
       </c>
       <c r="L97" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M97" t="n">
-        <v>52</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N97" t="n">
-        <v>13.53311566960181</v>
+        <v>13.5133859726113</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11280,22 +11288,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>4.024456972415502</v>
+        <v>3.973511430672727</v>
       </c>
       <c r="Z97" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA97" t="n">
-        <v>35.8974358974359</v>
+        <v>34.14634146341464</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.68617653937229</v>
+        <v>11.70950252888178</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>2.058381713992186</v>
+        <v>2.110343301644557</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11329,7 +11337,7 @@
         <v>46254</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6421262270492386</v>
+        <v>0.6358676629738155</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11357,22 +11365,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>7.223174437700708</v>
+        <v>6.17811027535935</v>
       </c>
       <c r="L98" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M98" t="n">
-        <v>51.61290322580645</v>
+        <v>51.42857142857143</v>
       </c>
       <c r="N98" t="n">
-        <v>12.25656894632272</v>
+        <v>13.19174904222331</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>2.589762499442427</v>
+        <v>3.599508142242391</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11399,22 +11407,22 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.583658109594988</v>
+        <v>3.533138744447917</v>
       </c>
       <c r="Z98" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="AA98" t="n">
-        <v>41.46341463414634</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.60521562902786</v>
+        <v>11.32569027962406</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>5.559993103106331</v>
+        <v>4.630461898950811</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11448,16 +11456,16 @@
         <v>46254</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4585423605838197</v>
+        <v>0.4539527789166031</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11476,22 +11484,22 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>4.102807747662296</v>
+        <v>3.060835666094719</v>
       </c>
       <c r="L99" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M99" t="n">
-        <v>63.63636363636363</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N99" t="n">
-        <v>13.8514856594738</v>
+        <v>12.69849533609901</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>0.9112718015872323</v>
       </c>
       <c r="Q99" t="n">
         <v>33</v>
@@ -11557,7 +11565,7 @@
         <v>46254</v>
       </c>
       <c r="C100" t="n">
-        <v>332.6361900332805</v>
+        <v>330.8049355001482</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11585,16 +11593,16 @@
         <v>17.72888230032435</v>
       </c>
       <c r="K100" t="n">
-        <v>8.532367441154731</v>
+        <v>7.934866640510307</v>
       </c>
       <c r="L100" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M100" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="N100" t="n">
-        <v>12.71637279982195</v>
+        <v>13.19612223309645</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11666,7 +11674,7 @@
         <v>46254</v>
       </c>
       <c r="C101" t="n">
-        <v>344.484633204693</v>
+        <v>343.495368265292</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11694,16 +11702,16 @@
         <v>12.13141269388449</v>
       </c>
       <c r="K101" t="n">
-        <v>9.087619411160341</v>
+        <v>8.774349828705418</v>
       </c>
       <c r="L101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M101" t="n">
-        <v>58.8235294117647</v>
+        <v>50</v>
       </c>
       <c r="N101" t="n">
-        <v>8.162722354966951</v>
+        <v>8.242539018848863</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11736,7 +11744,7 @@
         <v>10.77566750487711</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.523843757152221</v>
+        <v>1.80664014151265</v>
       </c>
       <c r="Z101" t="n">
         <v>41</v>
@@ -11745,13 +11753,13 @@
         <v>36.58536585365854</v>
       </c>
       <c r="AB101" t="n">
-        <v>13.56149831951222</v>
+        <v>14.23201560023499</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.545421362516755</v>
+        <v>4.270512654349201</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11785,7 +11793,7 @@
         <v>46254</v>
       </c>
       <c r="C102" t="n">
-        <v>416.3420856305074</v>
+        <v>415.1921603816235</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11845,22 +11853,22 @@
         <v>10.29246150171719</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.9328813128130276</v>
+        <v>1.206501936440485</v>
       </c>
       <c r="Z102" t="n">
         <v>37</v>
       </c>
       <c r="AA102" t="n">
-        <v>32.43243243243244</v>
+        <v>29.72972972972973</v>
       </c>
       <c r="AB102" t="n">
-        <v>11.3058204132745</v>
+        <v>14.52342882002417</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.105417358537755</v>
+        <v>3.839825634191985</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11894,7 +11902,7 @@
         <v>46254</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7397594187776437</v>
+        <v>0.7343353857523623</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11913,7 +11921,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -11926,16 +11934,16 @@
         <v>16.73842567092216</v>
       </c>
       <c r="K103" t="n">
-        <v>13.77377243002653</v>
+        <v>12.93956514126904</v>
       </c>
       <c r="L103" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M103" t="n">
-        <v>80</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N103" t="n">
-        <v>15.78439642498959</v>
+        <v>12.84408537336701</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -11968,22 +11976,22 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.025988489522224</v>
+        <v>2.744349433043869</v>
       </c>
       <c r="Z103" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AA103" t="n">
-        <v>35.84905660377358</v>
+        <v>34.69387755102041</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.28279913615487</v>
+        <v>11.62555125074009</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.097547113133039</v>
+        <v>5.403953946447404</v>
       </c>
       <c r="AE103" t="n">
         <v>35</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -679,7 +679,7 @@
         <v>46254</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3995034674570357</v>
+        <v>0.3992948446560099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>1.903803220887501</v>
+        <v>1.850588521654872</v>
       </c>
       <c r="L2" t="n">
         <v>33</v>
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>7.944940741380502</v>
+        <v>8.001339606017543</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -788,7 +788,7 @@
         <v>46254</v>
       </c>
       <c r="C3" t="n">
-        <v>0.648384751070005</v>
+        <v>0.6471330543185067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,22 +816,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.436215538421459</v>
+        <v>1.240394490402985</v>
       </c>
       <c r="L3" t="n">
         <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>53.7037037037037</v>
+        <v>57.4074074074074</v>
       </c>
       <c r="N3" t="n">
-        <v>13.86930271360292</v>
+        <v>13.15261140577361</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>6.470849121034439</v>
+        <v>6.676787011372021</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -897,7 +897,7 @@
         <v>46254</v>
       </c>
       <c r="C4" t="n">
-        <v>1.465541469752612</v>
+        <v>1.440507373043691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         <v>15.33976973013975</v>
       </c>
       <c r="K4" t="n">
-        <v>13.47232810558749</v>
+        <v>11.53401568372123</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M4" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>15.41911658261657</v>
+        <v>11.73407357796408</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>15.89522479111605</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.090592334494767</v>
+        <v>3.763061951219515</v>
       </c>
       <c r="Z4" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.82758620689656</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.06208636967171</v>
+        <v>12.95429529791687</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.078291814946626</v>
+        <v>6.480815137342699</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1016,7 +1016,7 @@
         <v>46254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2367814411188314</v>
+        <v>0.2361555727157539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>15.5457304755158</v>
+        <v>15.8444190057863</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3536689523836456</v>
+        <v>0.4436488727525667</v>
       </c>
       <c r="L5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M5" t="n">
-        <v>56</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N5" t="n">
-        <v>14.35145358327265</v>
+        <v>14.71610061633651</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.637004780435093</v>
+        <v>2.545059997258714</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1125,7 +1125,7 @@
         <v>46254</v>
       </c>
       <c r="C6" t="n">
-        <v>1.737788027050449</v>
+        <v>1.70962446941388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>6.188197941304718</v>
+        <v>4.467253046708231</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1191,16 +1191,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.16987700921664</v>
+        <v>6.706746634833161</v>
       </c>
       <c r="Z6" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
         <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.99236458706045</v>
+        <v>11.79569793761581</v>
       </c>
       <c r="AC6" t="n">
         <v>3</v>
@@ -1349,7 +1349,7 @@
         <v>46254</v>
       </c>
       <c r="C8" t="n">
-        <v>0.381770929290552</v>
+        <v>0.3857346824007296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>24.16907222170388</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.243590200217793</v>
+        <v>1.228630066653558</v>
       </c>
       <c r="Z8" t="n">
         <v>9</v>
@@ -1418,13 +1418,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.14402766538854</v>
+        <v>16.17940120368574</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.888524150561658</v>
+        <v>6.855599894904707</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1458,7 +1458,7 @@
         <v>46254</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5945613080135151</v>
+        <v>0.5941440624114636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.398827738208333</v>
+        <v>4.465917823182886</v>
       </c>
       <c r="Z9" t="n">
         <v>41</v>
@@ -1527,7 +1527,7 @@
         <v>46.34146341463415</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.05313074983267</v>
+        <v>11.30822662918063</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1567,7 +1567,7 @@
         <v>46254</v>
       </c>
       <c r="C10" t="n">
-        <v>1.932845827969508</v>
+        <v>1.939104272506815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,22 +1595,22 @@
         <v>10.51321892894885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2705627660826826</v>
+        <v>0.5952331286720014</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>42.85714285714285</v>
+        <v>44.18604651162791</v>
       </c>
       <c r="N10" t="n">
-        <v>10.2480637444662</v>
+        <v>9.405652485945192</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.713977338776188</v>
+        <v>5.372786267530927</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1676,7 +1676,7 @@
         <v>46254</v>
       </c>
       <c r="C11" t="n">
-        <v>8.271703811486272</v>
+        <v>8.323858312189213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,22 +1736,22 @@
         <v>22.18106016526054</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.996941896024463</v>
+        <v>2.385321100917426</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AA11" t="n">
-        <v>53.125</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.89529469806293</v>
+        <v>12.75236640169</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.003152585119803319</v>
+        <v>0.6296992481203079</v>
       </c>
       <c r="AE11" t="n">
         <v>46</v>
@@ -1785,7 +1785,7 @@
         <v>46254</v>
       </c>
       <c r="C12" t="n">
-        <v>6.816593241874248</v>
+        <v>6.868747742577188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,22 +1813,22 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>3.812549642573471</v>
+        <v>4.60683081810962</v>
       </c>
       <c r="L12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M12" t="n">
-        <v>60.8695652173913</v>
+        <v>60</v>
       </c>
       <c r="N12" t="n">
-        <v>16.85601468743039</v>
+        <v>19.40455061121279</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.107115531752113</v>
+        <v>1.331814730447989</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.777094591556311</v>
+        <v>7.071487052088488</v>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
@@ -1904,7 +1904,7 @@
         <v>46254</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2371986669021728</v>
+        <v>0.2434572109502676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>12.35177879038494</v>
+        <v>15.3162075775477</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1965,25 +1965,25 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>14.52569442666267</v>
+        <v>16.20553713266886</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.898190311930226</v>
+        <v>0.7653073829914314</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA13" t="n">
-        <v>46.15384615384615</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB13" t="n">
-        <v>15.12343652173557</v>
+        <v>10.23905013168687</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>8.258573122994118</v>
+        <v>9.305911444346792</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>46254</v>
       </c>
       <c r="C14" t="n">
-        <v>8.542907215141559</v>
+        <v>8.563769015422736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,16 +2067,16 @@
         <v>13.13901871403786</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.441929720071478</v>
+        <v>2.203692674210844</v>
       </c>
       <c r="Z14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>41.86046511627907</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.26142894611053</v>
+        <v>12.75377250494891</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2116,7 +2116,7 @@
         <v>46254</v>
       </c>
       <c r="C15" t="n">
-        <v>14.4989511954173</v>
+        <v>14.60326019682318</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,22 +2176,22 @@
         <v>38.77434577704333</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.627742392073606</v>
+        <v>0.9200283085633476</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
-        <v>16.66666666666667</v>
+        <v>25</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.66815013660483</v>
+        <v>13.24201098214579</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.510791366906467</v>
+        <v>9.164285714285702</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2225,7 +2225,7 @@
         <v>46254</v>
       </c>
       <c r="C16" t="n">
-        <v>35.79884928249796</v>
+        <v>35.67367848081091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,22 +2253,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>2.807060930258887</v>
+        <v>2.447595682250991</v>
       </c>
       <c r="L16" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>70.4225352112676</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N16" t="n">
-        <v>17.88880952447058</v>
+        <v>17.51191872517939</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.996541876263329</v>
+        <v>7.371968338987056</v>
       </c>
       <c r="Q16" t="n">
         <v>27</v>
@@ -2295,13 +2295,13 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.53881458288149</v>
+        <v>11.84811942699728</v>
       </c>
       <c r="Z16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>53.57142857142857</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB16" t="n">
         <v>13.40563990076058</v>
@@ -2344,7 +2344,7 @@
         <v>46254</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7113873576695462</v>
+        <v>0.700122046016932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,25 +2369,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>14.70218665633213</v>
+        <v>14.75338697646304</v>
       </c>
       <c r="K17" t="n">
-        <v>2.34093273486462</v>
+        <v>0.7807871949969458</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M17" t="n">
-        <v>65.625</v>
+        <v>73.13432835820896</v>
       </c>
       <c r="N17" t="n">
-        <v>15.35419475777581</v>
+        <v>16.09095333269455</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>5.529622521417088</v>
+        <v>7.16328281008054</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2453,7 +2453,7 @@
         <v>46254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09909355133558585</v>
+        <v>0.09888492853456003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,22 +2481,22 @@
         <v>20.56707245057805</v>
       </c>
       <c r="K18" t="n">
-        <v>2.19733520634986</v>
+        <v>1.98217797320237</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>63.1578947368421</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="N18" t="n">
-        <v>14.95987164804817</v>
+        <v>15.21052959484214</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.634900438348557</v>
+        <v>7.861983521183924</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2562,7 +2562,7 @@
         <v>46254</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02545139696888869</v>
+        <v>0.02524277917469493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,22 +2590,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>3.271635229340042</v>
+        <v>2.425147283288864</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>57.57575757575758</v>
+        <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>15.69071474462519</v>
+        <v>19.31962096524373</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>6.51521083763027</v>
+        <v>7.395500926896892</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2671,7 +2671,7 @@
         <v>46254</v>
       </c>
       <c r="C20" t="n">
-        <v>1.704409019343586</v>
+        <v>1.699193569273292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,16 +2699,16 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>2.314305224564506</v>
+        <v>2.001225943523699</v>
       </c>
       <c r="L20" t="n">
         <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="N20" t="n">
-        <v>12.48292737711242</v>
+        <v>13.36973631374576</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -2780,7 +2780,7 @@
         <v>46254</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9500464039976099</v>
+        <v>0.9396155038570219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,22 +2808,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>2.265337281947732</v>
+        <v>1.142529473252285</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>55.93220338983051</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N21" t="n">
-        <v>16.53812050199843</v>
+        <v>19.12606231163017</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.607630963208665</v>
+        <v>6.780006949066086</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2889,11 +2889,11 @@
         <v>46254</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3502696459138008</v>
+        <v>0.3460972697939794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2949,22 +2949,22 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.538754530026279</v>
+        <v>5.6758791013782</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>37.5</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.51117331232154</v>
+        <v>10.11838412757147</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.4831756255671338</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>46254</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7835692471416358</v>
+        <v>0.7773106434287922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
         <v>24.33755492423044</v>
       </c>
       <c r="K23" t="n">
-        <v>1.954400697796954</v>
+        <v>1.140060174511159</v>
       </c>
       <c r="L23" t="n">
         <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>71.42857142857143</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N23" t="n">
-        <v>20.79983647085491</v>
+        <v>21.52674789004583</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.987217110157414</v>
+        <v>3.816430224412315</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3060,7 +3060,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>22.85880756969937</v>
+        <v>23.47495752086021</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>46254</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1794114903455975</v>
+        <v>0.1777425479920474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,22 +3133,22 @@
         <v>23.5093122581746</v>
       </c>
       <c r="K24" t="n">
-        <v>6.17283921658287</v>
+        <v>5.185185929583858</v>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>44.44444444444444</v>
+        <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>12.06452679688787</v>
+        <v>12.28855668383958</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>3.60465144537585</v>
+        <v>4.577464048634594</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3214,7 +3214,7 @@
         <v>46254</v>
       </c>
       <c r="C25" t="n">
-        <v>3.590315955647366</v>
+        <v>3.577798748221679</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,22 +3242,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>2.684964102754894</v>
+        <v>2.32696524943623</v>
       </c>
       <c r="L25" t="n">
         <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>55.35714285714285</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N25" t="n">
-        <v>15.14898262115284</v>
+        <v>16.22416845357686</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>5.17606053007571</v>
+        <v>5.544027165014587</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3422,7 +3422,7 @@
         <v>46254</v>
       </c>
       <c r="C27" t="n">
-        <v>43.43426818540837</v>
+        <v>43.45512998568955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>31.76593873803297</v>
+        <v>31.82922689304644</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3478,22 +3478,22 @@
         <v>33.98102416350424</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.653282947567303</v>
+        <v>1.606046291922525</v>
       </c>
       <c r="Z27" t="n">
         <v>10</v>
       </c>
       <c r="AA27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>40.72118972052326</v>
+        <v>25.80591578680818</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.402977905859761</v>
+        <v>3.449351896303421</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>46254</v>
       </c>
       <c r="C28" t="n">
-        <v>1.588626123330104</v>
+        <v>1.58028137129908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,22 +3577,22 @@
         <v>18.63435792130579</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.962524713169657</v>
+        <v>4.466991374761708</v>
       </c>
       <c r="Z28" t="n">
         <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>47.05882352941177</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.21776450342845</v>
+        <v>10.57311832441738</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.121541909286062</v>
+        <v>1.604689988621688</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3626,11 +3626,11 @@
         <v>46254</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4180704968276227</v>
+        <v>0.4047189175273297</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3640,10 +3640,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>VERİ_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3654,13 +3658,17 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>15.6518349802371</v>
+        <v>11.95835587161751</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20.81369456717993</v>
+      </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
@@ -3692,10 +3700,10 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.737548171262388</v>
+        <v>11.65212327755832</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3703,7 +3711,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.383320087769191</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3737,7 +3745,7 @@
         <v>46254</v>
       </c>
       <c r="C30" t="n">
-        <v>0.402632729571728</v>
+        <v>0.4024241466167407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,13 +3773,13 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>9.988343884020946</v>
+        <v>9.931364676677589</v>
       </c>
       <c r="L30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M30" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="N30" t="n">
         <v>13.51070868134244</v>
@@ -3807,7 +3815,7 @@
         <v>11.81199400890234</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.630996872067414</v>
+        <v>1.681956706786758</v>
       </c>
       <c r="Z30" t="n">
         <v>60</v>
@@ -3822,7 +3830,7 @@
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>8.507764500823878</v>
+        <v>8.460342592871173</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3856,7 +3864,7 @@
         <v>46254</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1835838464380906</v>
+        <v>0.184001072012814</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3884,22 +3892,20 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>5.429034947663669</v>
+        <v>5.668640395267155</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="N31" t="n">
-        <v>6.439556915855582</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>4.335584646682422</v>
+        <v>4.099001925766088</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3965,21 +3971,21 @@
         <v>46254</v>
       </c>
       <c r="C32" t="n">
-        <v>2.292711882819793</v>
+        <v>2.26141918239803</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3993,16 +3999,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>5.199639632437192</v>
+        <v>3.763793797570836</v>
       </c>
       <c r="L32" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M32" t="n">
-        <v>43.90243902439025</v>
+        <v>54</v>
       </c>
       <c r="N32" t="n">
-        <v>11.04464267885272</v>
+        <v>10.79288075553727</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4035,22 +4041,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.800870780537283</v>
+        <v>8.072924391847113</v>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA32" t="n">
         <v>50</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.612847301691742</v>
+        <v>12.43651917107008</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.286631355362811</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4193,7 +4199,7 @@
         <v>46254</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7777278890308438</v>
+        <v>0.7852381498577653</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,22 +4227,22 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>2.474225302869404</v>
+        <v>3.463784981666973</v>
       </c>
       <c r="L34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M34" t="n">
-        <v>58.33333333333334</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N34" t="n">
-        <v>10.26574569507419</v>
+        <v>9.994241306368604</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.488935088429377</v>
+        <v>0.5182634855549262</v>
       </c>
       <c r="Q34" t="n">
         <v>34</v>
@@ -4302,7 +4308,7 @@
         <v>46254</v>
       </c>
       <c r="C35" t="n">
-        <v>1.952664474399516</v>
+        <v>1.953707628250684</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4334,7 +4340,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>10.08194934045925</v>
+        <v>10.14075740037126</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
@@ -4376,7 +4382,7 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.033739858313492</v>
+        <v>5.983541133733961</v>
       </c>
       <c r="Z35" t="n">
         <v>12</v>
@@ -4425,7 +4431,7 @@
         <v>46254</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08052654699915922</v>
+        <v>0.08031792899634745</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4453,16 +4459,16 @@
         <v>14.25367779956082</v>
       </c>
       <c r="K36" t="n">
-        <v>3.208553199977127</v>
+        <v>2.941173521547635</v>
       </c>
       <c r="L36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>57.14285714285715</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N36" t="n">
-        <v>19.82880345358048</v>
+        <v>19.23117825848152</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4534,21 +4540,21 @@
         <v>46254</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06634052635446561</v>
+        <v>0.06613190856027185</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4562,22 +4568,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>7.991176173387937</v>
+        <v>7.651581626831172</v>
       </c>
       <c r="L37" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M37" t="n">
-        <v>69.6969696969697</v>
+        <v>62.5</v>
       </c>
       <c r="N37" t="n">
-        <v>14.75545153938883</v>
+        <v>17.11565236973266</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.008170877403812504</v>
+        <v>0.3236537428466413</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4604,22 +4610,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.699082832467171</v>
+        <v>4.001915595821847</v>
       </c>
       <c r="Z37" t="n">
         <v>64</v>
       </c>
       <c r="AA37" t="n">
-        <v>50</v>
+        <v>56.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.66409114356596</v>
+        <v>13.09277213880228</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.3124759102858143</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4653,7 +4659,7 @@
         <v>46254</v>
       </c>
       <c r="C38" t="n">
-        <v>1.655383820392759</v>
+        <v>1.659556275996039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4687,7 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>4.484135237068587</v>
+        <v>4.747491330171116</v>
       </c>
       <c r="L38" t="n">
         <v>46</v>
@@ -4690,13 +4696,13 @@
         <v>54.34782608695652</v>
       </c>
       <c r="N38" t="n">
-        <v>10.99199791254927</v>
+        <v>9.981770234747954</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>5.279140943662153</v>
+        <v>5.014448177353126</v>
       </c>
       <c r="Q38" t="n">
         <v>44</v>
@@ -4762,7 +4768,7 @@
         <v>46254</v>
       </c>
       <c r="C39" t="n">
-        <v>2.737068133261797</v>
+        <v>2.6911722362717</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4790,16 +4796,16 @@
         <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>8.345473498292687</v>
+        <v>6.528707364270669</v>
       </c>
       <c r="L39" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M39" t="n">
-        <v>70.58823529411765</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N39" t="n">
-        <v>14.97049295270882</v>
+        <v>16.07560177070756</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4832,22 +4838,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.721882501258576</v>
+        <v>3.369836493447864</v>
       </c>
       <c r="Z39" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="AA39" t="n">
-        <v>37.73584905660378</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.315628006777</v>
+        <v>14.23899108065609</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.353072288748527</v>
+        <v>2.721886635712667</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4881,7 +4887,7 @@
         <v>46254</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2540967338918814</v>
+        <v>0.2545139594666048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4941,13 +4947,13 @@
         <v>39.56976926502232</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.571426040816303</v>
+        <v>0.4081648163265283</v>
       </c>
       <c r="Z40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="n">
-        <v>30</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB40" t="n">
         <v>14.8106908363406</v>
@@ -4956,7 +4962,7 @@
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.454025420299867</v>
+        <v>4.61065425213315</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4990,7 +4996,7 @@
         <v>46254</v>
       </c>
       <c r="C41" t="n">
-        <v>1.758649827331625</v>
+        <v>1.814976624462309</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5018,10 +5024,10 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>16.22149470403753</v>
+        <v>19.94388699196217</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5053,25 +5059,25 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X41" t="n">
-        <v>19.10146270395254</v>
+        <v>20.97788601775494</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.418079454719779</v>
+        <v>0.8547008547008517</v>
       </c>
       <c r="Z41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA41" t="n">
-        <v>43.33333333333334</v>
+        <v>53.125</v>
       </c>
       <c r="AB41" t="n">
-        <v>12.88336797398898</v>
+        <v>14.65953670141058</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.5963405331935401</v>
+        <v>2.163793103448286</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5105,7 +5111,7 @@
         <v>46254</v>
       </c>
       <c r="C42" t="n">
-        <v>3.617436041498931</v>
+        <v>3.577798748221679</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5163,7 +5169,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>6.463718882160463</v>
+        <v>7.488622975611992</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
@@ -5174,7 +5180,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.780651823632408</v>
+        <v>2.714668298285039</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5206,7 +5212,7 @@
         <v>46254</v>
       </c>
       <c r="C43" t="n">
-        <v>6.827024142014836</v>
+        <v>6.88439409278807</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5225,7 +5231,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.38: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.40: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5238,22 +5244,22 @@
         <v>12.62186296009862</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8474576271186418</v>
+        <v>1.694915254237284</v>
       </c>
       <c r="L43" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M43" t="n">
-        <v>78.37837837837837</v>
+        <v>81.3953488372093</v>
       </c>
       <c r="N43" t="n">
-        <v>15.02781735737797</v>
+        <v>16.51795998000152</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.126050420168069</v>
+        <v>2.266666666666683</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5280,7 +5286,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.88137027331979</v>
+        <v>11.14087758654096</v>
       </c>
       <c r="Z43" t="n">
         <v>8</v>
@@ -5329,7 +5335,7 @@
         <v>46254</v>
       </c>
       <c r="C44" t="n">
-        <v>4.572906558005282</v>
+        <v>4.633405969706165</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5348,7 +5354,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5361,22 +5367,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>2.000932141487599</v>
+        <v>3.350401304967177</v>
       </c>
       <c r="L44" t="n">
         <v>13</v>
       </c>
       <c r="M44" t="n">
-        <v>76.92307692307692</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="N44" t="n">
-        <v>17.70517523055278</v>
+        <v>17.77669066370159</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>7.842151724081048</v>
+        <v>6.434032776913123</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5434,7 +5440,7 @@
         <v>46254</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02336521631491709</v>
+        <v>0.02315659852072333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5494,22 +5500,22 @@
         <v>15.7065029425477</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>0.8928562499999959</v>
       </c>
       <c r="Z45" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="AA45" t="n">
-        <v>56.86274509803921</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.23925506743463</v>
+        <v>12.3520714796086</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.000000000000004</v>
+        <v>4.144145007710409</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5543,7 +5549,7 @@
         <v>46254</v>
       </c>
       <c r="C46" t="n">
-        <v>9.632936279833004</v>
+        <v>9.52341182835683</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5603,16 +5609,16 @@
         <v>21.77676482446944</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.201244813278016</v>
+        <v>5.290456431535273</v>
       </c>
       <c r="Z46" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AA46" t="n">
-        <v>40</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.19370112057261</v>
+        <v>10.84696264243016</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5652,7 +5658,7 @@
         <v>46254</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7055460790422132</v>
+        <v>0.7076322273603943</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,22 +5686,22 @@
         <v>25.52135514083118</v>
       </c>
       <c r="K47" t="n">
-        <v>4.763498721749992</v>
+        <v>5.073261901161086</v>
       </c>
       <c r="L47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M47" t="n">
-        <v>42.85714285714285</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>15.95694146360898</v>
+        <v>15.3849757123887</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.998402441825722</v>
+        <v>4.68885995323276</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5761,7 +5767,7 @@
         <v>46254</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05903889312678397</v>
+        <v>0.05841303974420271</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5789,22 +5795,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>2.53622935701534</v>
+        <v>1.44927391829448</v>
       </c>
       <c r="L48" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M48" t="n">
-        <v>49.18032786885246</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="N48" t="n">
-        <v>14.10204973331093</v>
+        <v>14.53451028628262</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>7.279154587396586</v>
+        <v>8.428572971938797</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5870,7 +5876,7 @@
         <v>46254</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2599380323379246</v>
+        <v>0.2576432414000073</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5898,22 +5904,22 @@
         <v>18.60609306322062</v>
       </c>
       <c r="K49" t="n">
-        <v>4.596132344365089</v>
+        <v>3.672734354135598</v>
       </c>
       <c r="L49" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M49" t="n">
-        <v>65.625</v>
+        <v>60</v>
       </c>
       <c r="N49" t="n">
-        <v>14.90372301236042</v>
+        <v>16.00865088934374</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.3861210224344047</v>
+        <v>1.280245624978504</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5979,7 +5985,7 @@
         <v>46254</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6880221636767554</v>
+        <v>0.6809291484518855</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6007,22 +6013,22 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>2.93382831775526</v>
+        <v>1.872654346977476</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M50" t="n">
-        <v>54.54545454545455</v>
+        <v>56</v>
       </c>
       <c r="N50" t="n">
-        <v>14.93524715750164</v>
+        <v>15.20042476406721</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.035783570541549</v>
+        <v>2.088240133389285</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6088,7 +6094,7 @@
         <v>46254</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1756563600364457</v>
+        <v>0.1775339251910215</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,7 +6122,7 @@
         <v>21.20514974257153</v>
       </c>
       <c r="K51" t="n">
-        <v>1.201927809206427</v>
+        <v>2.283660421626754</v>
       </c>
       <c r="L51" t="n">
         <v>17</v>
@@ -6125,13 +6131,13 @@
         <v>64.70588235294117</v>
       </c>
       <c r="N51" t="n">
-        <v>13.27232902826984</v>
+        <v>12.45585345480625</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>2.764840800334079</v>
+        <v>1.678019315400192</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6158,7 +6164,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>20.25809252510493</v>
+        <v>19.40574293296257</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6203,7 +6209,7 @@
         <v>46254</v>
       </c>
       <c r="C52" t="n">
-        <v>4.487373367737932</v>
+        <v>4.560389668722049</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6260,25 +6266,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>16.08466358135892</v>
+        <v>17.48068965761174</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.5087839340971012</v>
+        <v>0.09140628300368103</v>
       </c>
       <c r="Z52" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA52" t="n">
-        <v>41.02564102564103</v>
+        <v>36.11111111111111</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.65504806412742</v>
+        <v>12.03516021329131</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.529525079822841</v>
+        <v>7.915829282312192</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6312,7 +6318,7 @@
         <v>46254</v>
       </c>
       <c r="C53" t="n">
-        <v>1.37166336848732</v>
+        <v>1.387309718698202</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6329,7 +6335,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6340,22 +6350,22 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>1.701467044033356</v>
+        <v>2.861559824003312</v>
       </c>
       <c r="L53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>71.42857142857143</v>
+        <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>17.42947082383126</v>
+        <v>17.51835792581486</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>6.193158406692012</v>
+        <v>4.995491206616531</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6413,7 +6423,7 @@
         <v>46254</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08115240517995455</v>
+        <v>0.08052654699915922</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6432,7 +6442,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -6445,22 +6455,22 @@
         <v>42.98617858772242</v>
       </c>
       <c r="K54" t="n">
-        <v>1.440929731480955</v>
+        <v>0.658603741275865</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>83.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N54" t="n">
-        <v>25.39606819333878</v>
+        <v>22.84645482583484</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>8.437491938584675</v>
+        <v>9.280276013697208</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6487,16 +6497,16 @@
         <v>10.17240666043591</v>
       </c>
       <c r="Y54" t="n">
-        <v>7.925284736555116</v>
+        <v>8.63537723060065</v>
       </c>
       <c r="Z54" t="n">
         <v>23</v>
       </c>
       <c r="AA54" t="n">
-        <v>73.91304347826087</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.64958628095488</v>
+        <v>14.6756080381485</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6536,7 +6546,7 @@
         <v>46254</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9450395368823031</v>
+        <v>0.9329397340255857</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6596,16 +6606,16 @@
         <v>26.76177647494742</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.370310993894354</v>
+        <v>4.6075081072945</v>
       </c>
       <c r="Z55" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="AA55" t="n">
-        <v>51.51515151515152</v>
+        <v>50</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.18091230502987</v>
+        <v>12.36572635119501</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6645,7 +6655,7 @@
         <v>46254</v>
       </c>
       <c r="C56" t="n">
-        <v>1.250664942711468</v>
+        <v>1.251708016870558</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6697,7 +6707,7 @@
         <v>61.88091532996977</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.479043110319411</v>
+        <v>1.396875088532767</v>
       </c>
       <c r="Z56" t="n">
         <v>4</v>
@@ -6706,13 +6716,13 @@
         <v>25</v>
       </c>
       <c r="AB56" t="n">
-        <v>7.109081084502133</v>
+        <v>8.463649353473347</v>
       </c>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>8.648877516711472</v>
+        <v>8.725002294999996</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6738,7 +6748,7 @@
         <v>46254</v>
       </c>
       <c r="C57" t="n">
-        <v>1.308034893484701</v>
+        <v>1.315336491873177</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6755,7 +6765,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6766,22 +6780,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>3.607871948067887</v>
+        <v>4.186222781533799</v>
       </c>
       <c r="L57" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M57" t="n">
-        <v>69.23076923076923</v>
+        <v>75</v>
       </c>
       <c r="N57" t="n">
-        <v>17.8456315989677</v>
+        <v>17.57291694245328</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>6.16953898554744</v>
+        <v>5.580178514252321</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6808,10 +6822,10 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>19.35892592926696</v>
+        <v>18.90877835337841</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
@@ -6853,7 +6867,7 @@
         <v>46254</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7414284011858502</v>
+        <v>0.7443490404995167</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6872,7 +6886,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6885,13 +6899,13 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>11.70074544126085</v>
+        <v>12.14075770404957</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M58" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N58" t="n">
         <v>14.19416378953196</v>
@@ -6927,22 +6941,22 @@
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.390641096544687</v>
+        <v>1.002198504045881</v>
       </c>
       <c r="Z58" t="n">
         <v>46</v>
       </c>
       <c r="AA58" t="n">
-        <v>30.43478260869565</v>
+        <v>28.26086956521739</v>
       </c>
       <c r="AB58" t="n">
-        <v>13.43716932921936</v>
+        <v>12.96779667609787</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.674362509514096</v>
+        <v>5.048396449650827</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6976,7 +6990,7 @@
         <v>46254</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7919139194805837</v>
+        <v>0.786907132057354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7004,22 +7018,22 @@
         <v>11.1236565078948</v>
       </c>
       <c r="K59" t="n">
-        <v>1.172704196709939</v>
+        <v>0.5330510595628057</v>
       </c>
       <c r="L59" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M59" t="n">
-        <v>64.91228070175438</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N59" t="n">
-        <v>13.07785096747549</v>
+        <v>13.93046650912136</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.748159849533897</v>
+        <v>7.427357333473594</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7085,7 +7099,7 @@
         <v>46254</v>
       </c>
       <c r="C60" t="n">
-        <v>11.88079526012971</v>
+        <v>11.77648625872384</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7113,22 +7127,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>3.42707443109127</v>
+        <v>2.519022855752473</v>
       </c>
       <c r="L60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M60" t="n">
-        <v>51.21951219512195</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N60" t="n">
-        <v>14.05423700919043</v>
+        <v>13.6920950009654</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>4.421400870190384</v>
+        <v>5.346302560803218</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7194,7 +7208,7 @@
         <v>46254</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6437951694027886</v>
+        <v>0.6367021541779186</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7211,7 +7225,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7222,22 +7240,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>4.766781242610207</v>
+        <v>3.612512913595256</v>
       </c>
       <c r="L61" t="n">
         <v>20</v>
       </c>
       <c r="M61" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="N61" t="n">
-        <v>20.66685979079341</v>
+        <v>19.49335756577184</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>4.995112663880685</v>
+        <v>6.164783486847214</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7256,16 +7274,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>8.41152542023309</v>
+        <v>9.420601715756604</v>
       </c>
       <c r="Z61" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA61" t="n">
-        <v>37.03703703703704</v>
+        <v>37.5</v>
       </c>
       <c r="AB61" t="n">
-        <v>14.87198827034417</v>
+        <v>13.95405361141776</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7305,7 +7323,7 @@
         <v>46254</v>
       </c>
       <c r="C62" t="n">
-        <v>9.257423874771836</v>
+        <v>9.241777524560954</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7365,22 +7383,22 @@
         <v>11.694667893328</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.3928170594837188</v>
+        <v>0.561167227833903</v>
       </c>
       <c r="Z62" t="n">
         <v>53</v>
       </c>
       <c r="AA62" t="n">
-        <v>47.16981132075472</v>
+        <v>49.0566037735849</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.85406656056139</v>
+        <v>11.58536197617008</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.613521126760575</v>
+        <v>1.44695259593679</v>
       </c>
       <c r="AE62" t="n">
         <v>30</v>
@@ -7414,7 +7432,7 @@
         <v>46254</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1063951793478174</v>
+        <v>0.1053520953836807</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7442,16 +7460,16 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>8.262880523656357</v>
+        <v>7.201485869521673</v>
       </c>
       <c r="L63" t="n">
         <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>42.85714285714285</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N63" t="n">
-        <v>15.62495857587261</v>
+        <v>18.52195957147963</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
@@ -7484,7 +7502,7 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>7.775773845766265</v>
+        <v>8.67992769931557</v>
       </c>
       <c r="Z63" t="n">
         <v>6</v>
@@ -7493,13 +7511,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="AB63" t="n">
-        <v>14.62163007479386</v>
+        <v>14.52996031924543</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.411759086505083</v>
+        <v>1.445544519870612</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7533,7 +7551,7 @@
         <v>46254</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1508308164501383</v>
+        <v>0.1510394292374999</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7561,22 +7579,22 @@
         <v>24.42078296285393</v>
       </c>
       <c r="K64" t="n">
-        <v>1.974610254415876</v>
+        <v>2.115650448893147</v>
       </c>
       <c r="L64" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M64" t="n">
-        <v>61.11111111111111</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N64" t="n">
-        <v>17.07816799144163</v>
+        <v>15.58895125158012</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>2.96680687284423</v>
+        <v>2.824591077300553</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7642,21 +7660,21 @@
         <v>46254</v>
       </c>
       <c r="C65" t="n">
-        <v>6.686206990116898</v>
+        <v>6.618406139203076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7670,10 +7688,10 @@
         <v>25.04872642808169</v>
       </c>
       <c r="K65" t="n">
-        <v>18.02344363079989</v>
+        <v>16.82663804015993</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -7708,22 +7726,22 @@
         <v>21.96943581422117</v>
       </c>
       <c r="Y65" t="n">
-        <v>3.235230332156058</v>
+        <v>4.216464345948556</v>
       </c>
       <c r="Z65" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA65" t="n">
-        <v>34.375</v>
+        <v>50</v>
       </c>
       <c r="AB65" t="n">
-        <v>10.63891475894801</v>
+        <v>10.29417008407049</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.79033895339089</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7757,7 +7775,7 @@
         <v>46254</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4660526214107412</v>
+        <v>0.4631319820970748</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7814,25 +7832,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X66" t="n">
-        <v>12.19725904675169</v>
+        <v>12.69724877030836</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.4456344814533719</v>
+        <v>1.508430107020586</v>
       </c>
       <c r="Z66" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AA66" t="n">
-        <v>37.5</v>
+        <v>37.70491803278689</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.59642256340731</v>
+        <v>11.17445057007504</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>5.579228484472509</v>
+        <v>4.560359732167885</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7866,7 +7884,7 @@
         <v>46254</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02753757741424229</v>
+        <v>0.0273289571166325</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7894,7 +7912,7 @@
         <v>14.0514682678307</v>
       </c>
       <c r="K67" t="n">
-        <v>2.325588444204296</v>
+        <v>1.550386094585621</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
@@ -7903,13 +7921,13 @@
         <v>40</v>
       </c>
       <c r="N67" t="n">
-        <v>7.077382387711928</v>
+        <v>7.671407444036571</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.636356634986491</v>
+        <v>2.412215255521311</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7955,7 +7973,7 @@
         <v>46254</v>
       </c>
       <c r="C68" t="n">
-        <v>3.894898048867063</v>
+        <v>4.078481954969902</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7964,7 +7982,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7979,12 +7997,8 @@
       <c r="I68" t="n">
         <v>10</v>
       </c>
-      <c r="J68" t="n">
-        <v>30.89188078077966</v>
-      </c>
-      <c r="K68" t="n">
-        <v>37.88921213491048</v>
-      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>0</v>
       </c>
@@ -7993,9 +8007,7 @@
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
         <v>5</v>
       </c>
@@ -8018,13 +8030,13 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>128.0325939207301</v>
+        <v>128.9371825174344</v>
       </c>
       <c r="Y68" t="n">
-        <v>4.707358887362423</v>
+        <v>0.6100645493680612</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
@@ -8032,7 +8044,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>3.455294211801319</v>
+        <v>7.435295552941168</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8066,7 +8078,7 @@
         <v>46254</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3967914509443951</v>
+        <v>0.4149411948668918</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8094,22 +8106,22 @@
         <v>20.01758548606234</v>
       </c>
       <c r="K69" t="n">
-        <v>1.711228272698739</v>
+        <v>6.363628778804387</v>
       </c>
       <c r="L69" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="M69" t="n">
-        <v>60.8695652173913</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N69" t="n">
-        <v>22.30937951166133</v>
+        <v>23.19845319213931</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>6.182967047099641</v>
+        <v>1.538468779208957</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8159,7 +8171,7 @@
         <v>46254</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4247462664504409</v>
+        <v>0.4301703393217607</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8187,16 +8199,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>11.37523651789316</v>
+        <v>12.79751482061256</v>
       </c>
       <c r="L70" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M70" t="n">
-        <v>35.71428571428572</v>
+        <v>37.5</v>
       </c>
       <c r="N70" t="n">
-        <v>12.00172386214981</v>
+        <v>8.534401960408296</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8226,25 +8238,25 @@
         <v>67.79661016949153</v>
       </c>
       <c r="X70" t="n">
-        <v>12.14107466654</v>
+        <v>13.34453608357888</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.6829238536585458</v>
+        <v>0.4826181145273334</v>
       </c>
       <c r="Z70" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AA70" t="n">
-        <v>45.28301886792453</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.427036263969123</v>
+        <v>10.18800156385175</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>7.367389808737324</v>
+        <v>7.553838076371289</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8278,7 +8290,7 @@
         <v>46254</v>
       </c>
       <c r="C71" t="n">
-        <v>3.127183734891296</v>
+        <v>3.123011438463552</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8306,22 +8318,22 @@
         <v>14.92600999981897</v>
       </c>
       <c r="K71" t="n">
-        <v>1.215386715639033</v>
+        <v>1.080344891356511</v>
       </c>
       <c r="L71" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M71" t="n">
-        <v>60.29411764705883</v>
+        <v>61.19402985074627</v>
       </c>
       <c r="N71" t="n">
-        <v>16.85799615847782</v>
+        <v>16.85758192111756</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.775191707329359</v>
+        <v>0.9098258515361834</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8387,7 +8399,7 @@
         <v>46254</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07218182980734086</v>
+        <v>0.0715559764247596</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8415,22 +8427,22 @@
         <v>21.72769951373251</v>
       </c>
       <c r="K72" t="n">
-        <v>2.670627683610993</v>
+        <v>1.780420829627971</v>
       </c>
       <c r="L72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M72" t="n">
-        <v>52.94117647058823</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N72" t="n">
-        <v>14.15003240683303</v>
+        <v>17.3898758509428</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>2.268781606719283</v>
+        <v>3.163259833402865</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8457,7 +8469,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>19.63733778834708</v>
+        <v>20.334123172046</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8502,7 +8514,7 @@
         <v>46254</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07426800774927843</v>
+        <v>0.07468524333766595</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8530,16 +8542,16 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>12.88666019710296</v>
+        <v>13.52085429380536</v>
       </c>
       <c r="L73" t="n">
         <v>6</v>
       </c>
       <c r="M73" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N73" t="n">
-        <v>8.907419983978393</v>
+        <v>11.00909363979409</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
@@ -8572,22 +8584,22 @@
         <v>15.4234441942493</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.197806533027302</v>
+        <v>1.648356548122076</v>
       </c>
       <c r="Z73" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AA73" t="n">
-        <v>32</v>
+        <v>32.25806451612903</v>
       </c>
       <c r="AB73" t="n">
-        <v>14.9990389298822</v>
+        <v>12.97283453243094</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>7.97752401085714</v>
+        <v>8.491615552885257</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8621,7 +8633,7 @@
         <v>46254</v>
       </c>
       <c r="C74" t="n">
-        <v>5.653547876198687</v>
+        <v>5.684840576620451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8653,7 +8665,7 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>19.61267240050562</v>
+        <v>20.27473516287004</v>
       </c>
       <c r="L74" t="n">
         <v>3</v>
@@ -8662,7 +8674,7 @@
         <v>100</v>
       </c>
       <c r="N74" t="n">
-        <v>16.52901193804602</v>
+        <v>18.31627048481326</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
@@ -8695,22 +8707,22 @@
         <v>35.33255906375725</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.347864803938982</v>
+        <v>1.807354830529051</v>
       </c>
       <c r="Z74" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA74" t="n">
-        <v>53.33333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB74" t="n">
-        <v>17.54625934594731</v>
+        <v>17.87470432555786</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>7.836116620181876</v>
+        <v>8.343440748878129</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8744,7 +8756,7 @@
         <v>46254</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1260052728638308</v>
+        <v>0.1253794244880816</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8772,7 +8784,7 @@
         <v>23.39449322057143</v>
       </c>
       <c r="K75" t="n">
-        <v>2.02702497260776</v>
+        <v>1.520272783509835</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
@@ -8781,13 +8793,13 @@
         <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>14.84310636894291</v>
+        <v>15.297617066367</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.894041827112882</v>
+        <v>4.412643005838945</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8853,7 +8865,7 @@
         <v>46254</v>
       </c>
       <c r="C76" t="n">
-        <v>1.899466979229563</v>
+        <v>1.877562025305837</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8881,22 +8893,22 @@
         <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>9.595055214910865</v>
+        <v>8.331187687335051</v>
       </c>
       <c r="L76" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M76" t="n">
-        <v>63.1578947368421</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N76" t="n">
-        <v>8.249073048793266</v>
+        <v>9.728334478495144</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>0.3694918391117907</v>
+        <v>1.540472645311963</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8923,22 +8935,22 @@
         <v>10.78536860174914</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.074431941565501</v>
+        <v>2.215257254084135</v>
       </c>
       <c r="Z76" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AA76" t="n">
-        <v>39.28571428571428</v>
+        <v>32.0754716981132</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.13190010644236</v>
+        <v>10.65356431550411</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.957342692949105</v>
+        <v>1.825175069032348</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8972,7 +8984,7 @@
         <v>46254</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5298897192143855</v>
+        <v>0.5240484405870526</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9000,16 +9012,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>9.133986155663942</v>
+        <v>7.930939563645012</v>
       </c>
       <c r="L77" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M77" t="n">
-        <v>67.85714285714286</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N77" t="n">
-        <v>16.6358709563936</v>
+        <v>13.92336255069648</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9042,22 +9054,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>6.146768018441707</v>
+        <v>7.181366083285823</v>
       </c>
       <c r="Z77" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AA77" t="n">
-        <v>37.83783783783784</v>
+        <v>50</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.95892613000971</v>
+        <v>11.91075471878268</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.105593276015718</v>
+        <v>3.03671126989794</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9091,7 +9103,7 @@
         <v>46254</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04714766842683969</v>
+        <v>0.04693905063264593</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9119,7 +9131,7 @@
         <v>19.53698884929083</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8928562460140288</v>
+        <v>0.4464281230070144</v>
       </c>
       <c r="L78" t="n">
         <v>54</v>
@@ -9128,13 +9140,13 @@
         <v>72.22222222222223</v>
       </c>
       <c r="N78" t="n">
-        <v>17.89169517458145</v>
+        <v>18.03119124624317</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>3.079646933980751</v>
+        <v>3.537778240000011</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9200,7 +9212,7 @@
         <v>46254</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8190342439911441</v>
+        <v>0.8319686175354239</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9228,22 +9240,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>3.302908349070055</v>
+        <v>4.934291181473127</v>
       </c>
       <c r="L79" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M79" t="n">
-        <v>46.66666666666666</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N79" t="n">
-        <v>10.0183789596289</v>
+        <v>11.93733806692384</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.64283046629754</v>
+        <v>0.06261901403921133</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9309,7 +9321,7 @@
         <v>46254</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1289259221911614</v>
+        <v>0.1283000738154122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9337,7 +9349,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.555490654201822</v>
+        <v>5.043089957316416</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9348,7 +9360,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.210590390184743</v>
+        <v>4.71893015018674</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9375,22 +9387,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.997303979247725</v>
+        <v>6.453623651977358</v>
       </c>
       <c r="Z80" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="AA80" t="n">
-        <v>31.42857142857143</v>
+        <v>40.625</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.86932253340606</v>
+        <v>11.40307523818483</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.130466577586398</v>
+        <v>1.653058523902218</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9424,7 +9436,7 @@
         <v>46254</v>
       </c>
       <c r="C81" t="n">
-        <v>1.191208764136593</v>
+        <v>1.211027490467297</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9484,22 +9496,22 @@
         <v>30.67103176118848</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.80851324255319</v>
+        <v>1.19149065531915</v>
       </c>
       <c r="Z81" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA81" t="n">
-        <v>66.66666666666667</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.146804146204286</v>
+        <v>12.52862678478392</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>7.399296993361193</v>
+        <v>8.914727489667406</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9533,7 +9545,7 @@
         <v>46254</v>
       </c>
       <c r="C82" t="n">
-        <v>5.236311870575168</v>
+        <v>5.283250921207815</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9593,16 +9605,16 @@
         <v>21.75875960601758</v>
       </c>
       <c r="Y82" t="n">
-        <v>6.33865944649139</v>
+        <v>5.499065756270682</v>
       </c>
       <c r="Z82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA82" t="n">
-        <v>42.85714285714285</v>
+        <v>25</v>
       </c>
       <c r="AB82" t="n">
-        <v>11.46870465137741</v>
+        <v>13.23504228311709</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9642,7 +9654,7 @@
         <v>46254</v>
       </c>
       <c r="C83" t="n">
-        <v>5.789149578026332</v>
+        <v>5.742210527393685</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9702,22 +9714,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>3.770567739374342</v>
+        <v>4.550806379325367</v>
       </c>
       <c r="Z83" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA83" t="n">
         <v>50</v>
       </c>
-      <c r="AA83" t="n">
-        <v>46</v>
-      </c>
       <c r="AB83" t="n">
-        <v>12.49448922988003</v>
+        <v>12.63382948972703</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.316788334142428</v>
+        <v>1.518287966301624</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9751,7 +9763,7 @@
         <v>46254</v>
       </c>
       <c r="C84" t="n">
-        <v>2.152937725388869</v>
+        <v>2.144593132533381</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9779,22 +9791,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>3.066622267395824</v>
+        <v>2.667145315661656</v>
       </c>
       <c r="L84" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M84" t="n">
-        <v>45.45454545454545</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="N84" t="n">
-        <v>11.54048130099055</v>
+        <v>10.83844897685717</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>1.875852424452429</v>
+        <v>2.272250462565917</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9860,7 +9872,7 @@
         <v>46254</v>
       </c>
       <c r="C85" t="n">
-        <v>6.284617334704261</v>
+        <v>6.289832784774555</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9888,22 +9900,22 @@
         <v>15.93296998857089</v>
       </c>
       <c r="K85" t="n">
-        <v>1.582619574593047</v>
+        <v>1.666920503700609</v>
       </c>
       <c r="L85" t="n">
         <v>51</v>
       </c>
       <c r="M85" t="n">
-        <v>60.78431372549019</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N85" t="n">
-        <v>15.55268137112559</v>
+        <v>15.72056805328279</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.317400016146091</v>
+        <v>6.229242968039816</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9969,11 +9981,11 @@
         <v>46254</v>
       </c>
       <c r="C86" t="n">
-        <v>4.831593072377336</v>
+        <v>4.779438571674397</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9983,7 +9995,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -10029,7 +10041,7 @@
         <v>100.8644868744093</v>
       </c>
       <c r="Y86" t="n">
-        <v>5.817461572133542</v>
+        <v>6.834112435121853</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10040,7 +10052,7 @@
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.1938134508938427</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>51</v>
@@ -10074,7 +10086,7 @@
         <v>46254</v>
       </c>
       <c r="C87" t="n">
-        <v>5.684840576620451</v>
+        <v>5.669194226409569</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10102,16 +10114,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>5.423491566995886</v>
+        <v>5.133335168187636</v>
       </c>
       <c r="L87" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M87" t="n">
-        <v>54.16666666666666</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N87" t="n">
-        <v>11.04030646165189</v>
+        <v>11.72710853195772</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10183,7 +10195,7 @@
         <v>46254</v>
       </c>
       <c r="C88" t="n">
-        <v>1.056650216160117</v>
+        <v>1.061865666230411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10211,10 +10223,10 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>18.37821404753544</v>
+        <v>18.96250926210428</v>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
@@ -10249,16 +10261,16 @@
         <v>27.20319322085054</v>
       </c>
       <c r="Y88" t="n">
-        <v>6.937702544929958</v>
+        <v>6.478362492393397</v>
       </c>
       <c r="Z88" t="n">
         <v>18</v>
       </c>
       <c r="AA88" t="n">
-        <v>38.88888888888889</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB88" t="n">
-        <v>14.55636040212929</v>
+        <v>19.32319524016275</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
@@ -10298,7 +10310,7 @@
         <v>46254</v>
       </c>
       <c r="C89" t="n">
-        <v>2.115386580429798</v>
+        <v>2.1404206769301</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10315,7 +10327,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>5</v>
       </c>
@@ -10326,16 +10342,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>14.9043197199038</v>
+        <v>16.26413066641423</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M89" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="N89" t="n">
-        <v>14.19332941038719</v>
+        <v>16.37411641808841</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10368,22 +10384,22 @@
         <v>20.95675253601343</v>
       </c>
       <c r="Y89" t="n">
-        <v>5.003799034954747</v>
+        <v>3.879586522630918</v>
       </c>
       <c r="Z89" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AA89" t="n">
-        <v>29.54545454545455</v>
+        <v>29.41176470588235</v>
       </c>
       <c r="AB89" t="n">
-        <v>12.54478470506723</v>
+        <v>13.1478587875485</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>5.259369231916599</v>
+        <v>6.367443975685861</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10417,21 +10433,21 @@
         <v>46254</v>
       </c>
       <c r="C90" t="n">
-        <v>2.74541304425974</v>
+        <v>2.739154440546895</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10445,22 +10461,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>8.224865687257644</v>
+        <v>7.978149970790671</v>
       </c>
       <c r="L90" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M90" t="n">
-        <v>61.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="N90" t="n">
-        <v>16.04685375495613</v>
+        <v>15.59263786427928</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>0.02023560249480028</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10487,7 +10503,7 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>9.726085383466931</v>
+        <v>9.931879064812376</v>
       </c>
       <c r="Z90" t="n">
         <v>17</v>
@@ -10496,7 +10512,7 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AB90" t="n">
-        <v>15.5455038079218</v>
+        <v>15.09139627633752</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10536,7 +10552,7 @@
         <v>46254</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2292711802919098</v>
+        <v>0.2273936151373339</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10564,22 +10580,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>2.41108294945338</v>
+        <v>1.572410245176026</v>
       </c>
       <c r="L91" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M91" t="n">
-        <v>64.70588235294117</v>
+        <v>63.38028169014085</v>
       </c>
       <c r="N91" t="n">
-        <v>15.26385963516832</v>
+        <v>13.88224660079332</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.5750520681802485</v>
+        <v>1.405489690928907</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10645,7 +10661,7 @@
         <v>46254</v>
       </c>
       <c r="C92" t="n">
-        <v>1.128623363293066</v>
+        <v>1.120278690954118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10662,11 +10678,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>5</v>
       </c>
@@ -10677,22 +10689,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>7.115265997840181</v>
+        <v>6.323290723960362</v>
       </c>
       <c r="L92" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M92" t="n">
-        <v>77.27272727272727</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N92" t="n">
-        <v>11.61735801987519</v>
+        <v>12.80373380929682</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.8259644355246953</v>
+        <v>1.576991517684267</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10719,16 +10731,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>6.584413830866175</v>
+        <v>7.275098148846004</v>
       </c>
       <c r="Z92" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA92" t="n">
-        <v>52.5</v>
+        <v>50</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.49472424221203</v>
+        <v>11.66875451730866</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10768,7 +10780,7 @@
         <v>46254</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04214083615073946</v>
+        <v>0.0419322183565457</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10796,22 +10808,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>4.202065138061895</v>
+        <v>3.686213841192076</v>
       </c>
       <c r="L93" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M93" t="n">
-        <v>64.15094339622641</v>
+        <v>61.40350877192982</v>
       </c>
       <c r="N93" t="n">
-        <v>19.53194616401082</v>
+        <v>19.00391756101635</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>1.725431122268017</v>
+        <v>2.231527290939339</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10986,7 +10998,7 @@
         <v>46254</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1447808952030692</v>
+        <v>0.1439464240262942</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11005,7 +11017,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -11018,16 +11030,16 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>8.529302732608524</v>
+        <v>7.903774241167505</v>
       </c>
       <c r="L95" t="n">
         <v>7</v>
       </c>
       <c r="M95" t="n">
-        <v>100</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N95" t="n">
-        <v>16.62423732037097</v>
+        <v>18.772825202213</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
@@ -11060,22 +11072,22 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>3.072622829733718</v>
+        <v>3.631281500655348</v>
       </c>
       <c r="Z95" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA95" t="n">
-        <v>43.75</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.25290628307341</v>
+        <v>10.59785310700193</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>3.020175780805401</v>
+        <v>2.457974471623559</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11218,7 +11230,7 @@
         <v>46254</v>
       </c>
       <c r="C97" t="n">
-        <v>1.966224676500835</v>
+        <v>1.935975129721621</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11246,16 +11258,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>10.00992125503266</v>
+        <v>8.31746448803492</v>
       </c>
       <c r="L97" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M97" t="n">
-        <v>53.84615384615385</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N97" t="n">
-        <v>13.5133859726113</v>
+        <v>14.49932491657701</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11288,22 +11300,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>3.973511430672727</v>
+        <v>5.450838916558498</v>
       </c>
       <c r="Z97" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="AA97" t="n">
-        <v>34.14634146341464</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.70950252888178</v>
+        <v>11.4083613888801</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>2.110343301644557</v>
+        <v>0.5808206832812246</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11337,7 +11349,7 @@
         <v>46254</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6358676629738155</v>
+        <v>0.6275229507888291</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11365,22 +11377,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>6.17811027535935</v>
+        <v>4.784698057399006</v>
       </c>
       <c r="L98" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M98" t="n">
-        <v>51.42857142857143</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="N98" t="n">
-        <v>13.19174904222331</v>
+        <v>16.11984600975353</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.599508142242391</v>
+        <v>4.977159870942383</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11407,22 +11419,22 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>3.533138744447917</v>
+        <v>4.799106868698555</v>
       </c>
       <c r="Z98" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AA98" t="n">
-        <v>36.8421052631579</v>
+        <v>32.14285714285715</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.32569027962406</v>
+        <v>12.52421259254083</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>4.630461898950811</v>
+        <v>3.362251157546137</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11456,7 +11468,7 @@
         <v>46254</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4539527789166031</v>
+        <v>0.4497804030053998</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11484,22 +11496,22 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>3.060835666094719</v>
+        <v>2.113581748742432</v>
       </c>
       <c r="L99" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M99" t="n">
-        <v>61.29032258064516</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="N99" t="n">
-        <v>12.69849533609901</v>
+        <v>12.77718274545301</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.9112718015872323</v>
+        <v>1.847372522784707</v>
       </c>
       <c r="Q99" t="n">
         <v>33</v>
@@ -11565,7 +11577,7 @@
         <v>46254</v>
       </c>
       <c r="C100" t="n">
-        <v>330.8049355001482</v>
+        <v>326.3190372542446</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11593,16 +11605,16 @@
         <v>17.72888230032435</v>
       </c>
       <c r="K100" t="n">
-        <v>7.934866640510307</v>
+        <v>6.471210035138131</v>
       </c>
       <c r="L100" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M100" t="n">
-        <v>50</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N100" t="n">
-        <v>13.19612223309645</v>
+        <v>14.73829068705574</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11674,7 +11686,7 @@
         <v>46254</v>
       </c>
       <c r="C101" t="n">
-        <v>343.495368265292</v>
+        <v>343.3804246351229</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11702,7 +11714,7 @@
         <v>12.13141269388449</v>
       </c>
       <c r="K101" t="n">
-        <v>8.774349828705418</v>
+        <v>8.73795073924537</v>
       </c>
       <c r="L101" t="n">
         <v>18</v>
@@ -11711,7 +11723,7 @@
         <v>50</v>
       </c>
       <c r="N101" t="n">
-        <v>8.242539018848863</v>
+        <v>8.322941515058263</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11744,7 +11756,7 @@
         <v>10.77566750487711</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.80664014151265</v>
+        <v>1.839498521227168</v>
       </c>
       <c r="Z101" t="n">
         <v>41</v>
@@ -11759,7 +11771,7 @@
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.270512654349201</v>
+        <v>4.238468035610577</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11793,7 +11805,7 @@
         <v>46254</v>
       </c>
       <c r="C102" t="n">
-        <v>415.1921603816235</v>
+        <v>415.6171380707366</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11853,22 +11865,22 @@
         <v>10.29246150171719</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.206501936440485</v>
+        <v>1.105380006614409</v>
       </c>
       <c r="Z102" t="n">
         <v>37</v>
       </c>
       <c r="AA102" t="n">
-        <v>29.72972972972973</v>
+        <v>32.43243243243244</v>
       </c>
       <c r="AB102" t="n">
-        <v>14.52342882002417</v>
+        <v>11.98803151482821</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>3.839825634191985</v>
+        <v>3.93815153306224</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11902,7 +11914,7 @@
         <v>46254</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7343353857523623</v>
+        <v>0.7239044856117743</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11919,11 +11931,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>5</v>
       </c>
@@ -11934,16 +11942,16 @@
         <v>16.73842567092216</v>
       </c>
       <c r="K103" t="n">
-        <v>12.93956514126904</v>
+        <v>11.33530998924062</v>
       </c>
       <c r="L103" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M103" t="n">
-        <v>78.57142857142857</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N103" t="n">
-        <v>12.84408537336701</v>
+        <v>17.98940078272775</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -11976,22 +11984,22 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.744349433043869</v>
+        <v>4.125821712406341</v>
       </c>
       <c r="Z103" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="AA103" t="n">
-        <v>34.69387755102041</v>
+        <v>42.5</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.62555125074009</v>
+        <v>10.35444912349157</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>5.403953946447404</v>
+        <v>4.040898557661987</v>
       </c>
       <c r="AE103" t="n">
         <v>35</v>
@@ -12025,7 +12033,7 @@
         <v>46254</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04735628622103345</v>
+        <v>0.04714766842683969</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12053,22 +12061,22 @@
         <v>21.43553010850433</v>
       </c>
       <c r="K104" t="n">
-        <v>1.793720163285029</v>
+        <v>1.34529012246376</v>
       </c>
       <c r="L104" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M104" t="n">
-        <v>54.54545454545455</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="N104" t="n">
-        <v>12.32784198497689</v>
+        <v>13.03248067291818</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.167402697510146</v>
+        <v>2.619470400971124</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46254</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3992948446560099</v>
+        <v>0.399086221854984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>1.850588521654872</v>
+        <v>1.797373822422221</v>
       </c>
       <c r="L2" t="n">
         <v>33</v>
@@ -716,13 +716,13 @@
         <v>57.57575757575758</v>
       </c>
       <c r="N2" t="n">
-        <v>10.6972885464287</v>
+        <v>10.7006052392022</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>8.001339606017543</v>
+        <v>8.057797435802861</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -788,7 +788,7 @@
         <v>46254</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6471330543185067</v>
+        <v>0.6475502999205583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.240394490402985</v>
+        <v>1.305670261852465</v>
       </c>
       <c r="L3" t="n">
         <v>54</v>
@@ -831,7 +831,7 @@
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>6.676787011372021</v>
+        <v>6.608050389325881</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -897,7 +897,7 @@
         <v>46254</v>
       </c>
       <c r="C4" t="n">
-        <v>1.440507373043691</v>
+        <v>1.441550367510705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         <v>15.33976973013975</v>
       </c>
       <c r="K4" t="n">
-        <v>11.53401568372123</v>
+        <v>11.61477150866097</v>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N4" t="n">
         <v>11.73407357796408</v>
@@ -967,22 +967,22 @@
         <v>15.89522479111605</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.763061951219515</v>
+        <v>3.693381923344941</v>
       </c>
       <c r="Z4" t="n">
         <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>43.47826086956522</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.95429529791687</v>
+        <v>12.91755796593209</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>6.480815137342699</v>
+        <v>6.548478393909873</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1016,7 +1016,7 @@
         <v>46254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2361555727157539</v>
+        <v>0.2355297243400047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>15.8444190057863</v>
+        <v>15.99376685518751</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4436488727525667</v>
+        <v>0.3555551999999906</v>
       </c>
       <c r="L5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M5" t="n">
-        <v>54.16666666666666</v>
+        <v>55.31914893617022</v>
       </c>
       <c r="N5" t="n">
-        <v>14.71610061633651</v>
+        <v>14.64501183776445</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.545059997258714</v>
+        <v>2.635075651497187</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1125,7 +1125,7 @@
         <v>46254</v>
       </c>
       <c r="C6" t="n">
-        <v>1.70962446941388</v>
+        <v>1.715883073126723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>4.467253046708231</v>
+        <v>4.8496874055314</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1191,16 +1191,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.706746634833161</v>
+        <v>6.365218122378802</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="n">
         <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.79569793761581</v>
+        <v>11.42568615537318</v>
       </c>
       <c r="AC6" t="n">
         <v>3</v>
@@ -1240,7 +1240,7 @@
         <v>46254</v>
       </c>
       <c r="C7" t="n">
-        <v>2.269763934220436</v>
+        <v>2.250988282257441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,22 +1300,22 @@
         <v>14.22876300591287</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.971756292022444</v>
+        <v>4.766108891997956</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AA7" t="n">
-        <v>47.61904761904762</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.80683261532237</v>
+        <v>10.45219184553705</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.070772168971934</v>
+        <v>0.2455965048585473</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1349,7 +1349,7 @@
         <v>46254</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3857346824007296</v>
+        <v>0.3867777964058587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,10 +1406,10 @@
         <v>33.33333333333334</v>
       </c>
       <c r="X8" t="n">
-        <v>24.16907222170388</v>
+        <v>24.89870225327257</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.228630066653558</v>
+        <v>1.540090288008866</v>
       </c>
       <c r="Z8" t="n">
         <v>9</v>
@@ -1418,13 +1418,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="AB8" t="n">
-        <v>16.17940120368574</v>
+        <v>15.78648446130603</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.855599894904707</v>
+        <v>6.560954332466141</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1458,7 +1458,7 @@
         <v>46254</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5941440624114636</v>
+        <v>0.5933096110533987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,16 +1518,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.465917823182886</v>
+        <v>4.600091586176269</v>
       </c>
       <c r="Z9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>46.34146341463415</v>
+        <v>50</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.30822662918063</v>
+        <v>11.18468597526538</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1567,7 +1567,7 @@
         <v>46254</v>
       </c>
       <c r="C10" t="n">
-        <v>1.939104272506815</v>
+        <v>1.929716526008777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,22 +1595,22 @@
         <v>10.51321892894885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5952331286720014</v>
+        <v>0.1082234505889401</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>44.18604651162791</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="N10" t="n">
-        <v>9.405652485945192</v>
+        <v>10.16882093237464</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.372786267530927</v>
+        <v>5.885407158702716</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1676,7 +1676,7 @@
         <v>46254</v>
       </c>
       <c r="C11" t="n">
-        <v>8.323858312189213</v>
+        <v>8.365581912751564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,22 +1736,22 @@
         <v>22.18106016526054</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.385321100917426</v>
+        <v>1.896024464831814</v>
       </c>
       <c r="Z11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AA11" t="n">
-        <v>48.57142857142857</v>
+        <v>45</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.75236640169</v>
+        <v>12.34362310187937</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.6296992481203079</v>
+        <v>1.125311720698252</v>
       </c>
       <c r="AE11" t="n">
         <v>46</v>
@@ -1785,7 +1785,7 @@
         <v>46254</v>
       </c>
       <c r="C12" t="n">
-        <v>6.868747742577188</v>
+        <v>6.842670492225718</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,22 +1813,22 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>4.60683081810962</v>
+        <v>4.209690230341545</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M12" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>19.40455061121279</v>
+        <v>18.08574051873381</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.331814730447989</v>
+        <v>1.717987804878041</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.071487052088488</v>
+        <v>7.4242908218224</v>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
@@ -1904,7 +1904,7 @@
         <v>46254</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2434572109502676</v>
+        <v>0.2445003049280684</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>15.3162075775477</v>
+        <v>15.81028060663348</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>16.20553713266886</v>
+        <v>16.60079365870428</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.7653073829914314</v>
+        <v>0.6779654128124313</v>
       </c>
       <c r="Z13" t="n">
         <v>9</v>
@@ -1983,7 +1983,7 @@
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>9.305911444346792</v>
+        <v>9.385666157497441</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>46254</v>
       </c>
       <c r="C14" t="n">
-        <v>8.563769015422736</v>
+        <v>8.532476315000972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,16 +2067,16 @@
         <v>13.13901871403786</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.203692674210844</v>
+        <v>2.561048243001796</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA14" t="n">
-        <v>47.72727272727273</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.75377250494891</v>
+        <v>12.87233157293113</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2116,7 +2116,7 @@
         <v>46254</v>
       </c>
       <c r="C15" t="n">
-        <v>14.60326019682318</v>
+        <v>14.45722759485495</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,22 +2176,22 @@
         <v>38.77434577704333</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9200283085633476</v>
+        <v>1.910828025477707</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>25</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB15" t="n">
-        <v>13.24201098214579</v>
+        <v>12.42437267126862</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.164285714285702</v>
+        <v>8.246753246753247</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2225,7 +2225,7 @@
         <v>46254</v>
       </c>
       <c r="C16" t="n">
-        <v>35.67367848081091</v>
+        <v>35.5902312796862</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,22 +2253,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>2.447595682250991</v>
+        <v>2.207952183579054</v>
       </c>
       <c r="L16" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="M16" t="n">
-        <v>66.66666666666667</v>
+        <v>67.81609195402299</v>
       </c>
       <c r="N16" t="n">
-        <v>17.51191872517939</v>
+        <v>18.44986819594546</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.371968338987056</v>
+        <v>7.623719730168754</v>
       </c>
       <c r="Q16" t="n">
         <v>27</v>
@@ -2295,16 +2295,16 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.84811942699728</v>
+        <v>12.05432265640782</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA16" t="n">
-        <v>55.55555555555556</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.40563990076058</v>
+        <v>13.1674972814445</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
@@ -2344,7 +2344,7 @@
         <v>46254</v>
       </c>
       <c r="C17" t="n">
-        <v>0.700122046016932</v>
+        <v>0.7176459615910077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,22 +2372,22 @@
         <v>14.75338697646304</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7807871949969458</v>
+        <v>3.303310255571046</v>
       </c>
       <c r="L17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>73.13432835820896</v>
+        <v>65.57377049180327</v>
       </c>
       <c r="N17" t="n">
-        <v>16.09095333269455</v>
+        <v>16.64776798590285</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.16328281008054</v>
+        <v>4.546504591972322</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2453,7 +2453,7 @@
         <v>46254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09888492853456003</v>
+        <v>0.09930217413661169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,22 +2481,22 @@
         <v>20.56707245057805</v>
       </c>
       <c r="K18" t="n">
-        <v>1.98217797320237</v>
+        <v>2.412492439497371</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M18" t="n">
-        <v>69.04761904761905</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="N18" t="n">
-        <v>15.21052959484214</v>
+        <v>14.78190186872253</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.861983521183924</v>
+        <v>7.408771508012202</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2671,16 +2671,16 @@
         <v>46254</v>
       </c>
       <c r="C20" t="n">
-        <v>1.699193569273292</v>
+        <v>1.697107420955111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2699,22 +2699,22 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>2.001225943523699</v>
+        <v>1.87599613462941</v>
       </c>
       <c r="L20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M20" t="n">
-        <v>40</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="N20" t="n">
-        <v>13.36973631374576</v>
+        <v>12.35802226593892</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.1217203954567703</v>
       </c>
       <c r="Q20" t="n">
         <v>48</v>
@@ -2780,7 +2780,7 @@
         <v>46254</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9396155038570219</v>
+        <v>0.942953388564122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,22 +2808,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>1.142529473252285</v>
+        <v>1.501827612736317</v>
       </c>
       <c r="L21" t="n">
         <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>53.33333333333334</v>
+        <v>55</v>
       </c>
       <c r="N21" t="n">
-        <v>19.12606231163017</v>
+        <v>18.21306477199776</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.780006949066086</v>
+        <v>6.402025007920464</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2990,7 +2990,7 @@
         <v>46254</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7773106434287922</v>
+        <v>0.775224495319229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
         <v>24.33755492423044</v>
       </c>
       <c r="K23" t="n">
-        <v>1.140060174511159</v>
+        <v>0.8686202461918313</v>
       </c>
       <c r="L23" t="n">
         <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>64.28571428571429</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N23" t="n">
-        <v>21.52674789004583</v>
+        <v>20.08190631494157</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.816430224412315</v>
+        <v>4.095802781603086</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3060,7 +3060,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>23.47495752086021</v>
+        <v>23.68033560753854</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3214,7 +3214,7 @@
         <v>46254</v>
       </c>
       <c r="C25" t="n">
-        <v>3.577798748221679</v>
+        <v>3.567367848081091</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,22 +3242,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>2.32696524943623</v>
+        <v>2.028635904685672</v>
       </c>
       <c r="L25" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M25" t="n">
-        <v>57.14285714285715</v>
+        <v>56.89655172413793</v>
       </c>
       <c r="N25" t="n">
-        <v>16.22416845357686</v>
+        <v>16.97399430421782</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>5.544027165014587</v>
+        <v>5.852635431578967</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3422,7 +3422,7 @@
         <v>46254</v>
       </c>
       <c r="C27" t="n">
-        <v>43.45512998568955</v>
+        <v>43.35082098428366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>31.82922689304644</v>
+        <v>31.51278611797912</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3478,22 +3478,22 @@
         <v>33.98102416350424</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.606046291922525</v>
+        <v>1.842229570146436</v>
       </c>
       <c r="Z27" t="n">
         <v>10</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB27" t="n">
-        <v>25.80591578680818</v>
+        <v>40.72118972052326</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.449351896303421</v>
+        <v>3.217035611164587</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         <v>46254</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4047189175273297</v>
+        <v>0.4065964826819056</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3658,16 +3658,16 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>11.95835587161751</v>
+        <v>12.47775118190457</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>85.71428571428571</v>
+        <v>80</v>
       </c>
       <c r="N29" t="n">
-        <v>20.81369456717993</v>
+        <v>15.83912322416238</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3700,7 +3700,7 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>11.65212327755832</v>
+        <v>11.24226130266406</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>46254</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4024241466167407</v>
+        <v>0.4015896554126374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>9.931364676677589</v>
+        <v>9.703404307875152</v>
       </c>
       <c r="L30" t="n">
         <v>16</v>
@@ -3782,7 +3782,7 @@
         <v>56.25</v>
       </c>
       <c r="N30" t="n">
-        <v>13.51070868134244</v>
+        <v>13.00992913726943</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3815,22 +3815,22 @@
         <v>11.81199400890234</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.681956706786758</v>
+        <v>1.885834985519796</v>
       </c>
       <c r="Z30" t="n">
         <v>60</v>
       </c>
       <c r="AA30" t="n">
-        <v>41.66666666666666</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.91919266329253</v>
+        <v>12.98827388135968</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>8.460342592871173</v>
+        <v>8.270125942857154</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3864,7 +3864,7 @@
         <v>46254</v>
       </c>
       <c r="C31" t="n">
-        <v>0.184001072012814</v>
+        <v>0.184835543398207</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>5.668640395267155</v>
+        <v>6.147862911628899</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -3905,7 +3905,7 @@
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>4.099001925766088</v>
+        <v>3.629029339552625</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3971,21 +3971,21 @@
         <v>46254</v>
       </c>
       <c r="C32" t="n">
-        <v>2.26141918239803</v>
+        <v>2.278108527075925</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3999,16 +3999,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>3.763793797570836</v>
+        <v>4.529573858716951</v>
       </c>
       <c r="L32" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M32" t="n">
-        <v>54</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N32" t="n">
-        <v>10.79288075553727</v>
+        <v>10.44660475484212</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4041,22 +4041,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>8.072924391847113</v>
+        <v>7.394499683152223</v>
       </c>
       <c r="Z32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>50</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.43651917107008</v>
+        <v>14.63702839182677</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>0.6538491933805957</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4090,7 +4090,7 @@
         <v>46254</v>
       </c>
       <c r="C33" t="n">
-        <v>1.727357126909861</v>
+        <v>1.731529423337606</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4118,16 +4118,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.409055795444573</v>
+        <v>5.663663149127141</v>
       </c>
       <c r="L33" t="n">
         <v>29</v>
       </c>
       <c r="M33" t="n">
-        <v>68.96551724137932</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="N33" t="n">
-        <v>10.86376214265203</v>
+        <v>11.39383009772743</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4199,16 +4199,16 @@
         <v>46254</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7852381498577653</v>
+        <v>0.7960862956004049</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4227,22 +4227,22 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>3.463784981666973</v>
+        <v>4.893147804613807</v>
       </c>
       <c r="L34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M34" t="n">
-        <v>60.8695652173913</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N34" t="n">
-        <v>9.994241306368604</v>
+        <v>9.616943003587124</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0.5182634855549262</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>34</v>
@@ -4308,7 +4308,7 @@
         <v>46254</v>
       </c>
       <c r="C35" t="n">
-        <v>1.953707628250684</v>
+        <v>1.947449024329222</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4340,16 +4340,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>10.14075740037126</v>
+        <v>9.787927035064282</v>
       </c>
       <c r="L35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>81.81818181818181</v>
+        <v>80</v>
       </c>
       <c r="N35" t="n">
-        <v>10.73178574240798</v>
+        <v>10.83557166488997</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4382,7 +4382,7 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>5.983541133733961</v>
+        <v>6.28471812134147</v>
       </c>
       <c r="Z35" t="n">
         <v>12</v>
@@ -4391,7 +4391,7 @@
         <v>41.66666666666666</v>
       </c>
       <c r="AB35" t="n">
-        <v>15.05640991881998</v>
+        <v>14.75083324357035</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4540,11 +4540,11 @@
         <v>46254</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06613190856027185</v>
+        <v>0.06634052635446561</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4568,22 +4568,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>7.651581626831172</v>
+        <v>7.991176173387937</v>
       </c>
       <c r="L37" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M37" t="n">
-        <v>62.5</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="N37" t="n">
-        <v>17.11565236973266</v>
+        <v>14.75545153938883</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.3236537428466413</v>
+        <v>0.008170877403812504</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4610,22 +4610,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.001915595821847</v>
+        <v>3.699082832467171</v>
       </c>
       <c r="Z37" t="n">
         <v>64</v>
       </c>
       <c r="AA37" t="n">
-        <v>56.25</v>
+        <v>50</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.09277213880228</v>
+        <v>13.66409114356596</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.3124759102858143</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4659,7 +4659,7 @@
         <v>46254</v>
       </c>
       <c r="C38" t="n">
-        <v>1.659556275996039</v>
+        <v>1.658513122353489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>4.747491330171116</v>
+        <v>4.681649798486132</v>
       </c>
       <c r="L38" t="n">
         <v>46</v>
@@ -4702,7 +4702,7 @@
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>5.014448177353126</v>
+        <v>5.080499028962371</v>
       </c>
       <c r="Q38" t="n">
         <v>44</v>
@@ -4768,7 +4768,7 @@
         <v>46254</v>
       </c>
       <c r="C39" t="n">
-        <v>2.6911722362717</v>
+        <v>2.695344532699445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4796,16 +4796,16 @@
         <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>6.528707364270669</v>
+        <v>6.693865632179952</v>
       </c>
       <c r="L39" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M39" t="n">
-        <v>60.8695652173913</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N39" t="n">
-        <v>16.07560177070756</v>
+        <v>15.52587907997361</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4838,22 +4838,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.369836493447864</v>
+        <v>3.220024571127611</v>
       </c>
       <c r="Z39" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA39" t="n">
-        <v>35.8974358974359</v>
+        <v>36.58536585365854</v>
       </c>
       <c r="AB39" t="n">
-        <v>14.23899108065609</v>
+        <v>13.81425650134411</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.721886635712667</v>
+        <v>2.872469657646803</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4887,7 +4887,7 @@
         <v>46254</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2545139594666048</v>
+        <v>0.2495071321973366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4947,22 +4947,22 @@
         <v>39.56976926502232</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.4081648163265283</v>
+        <v>2.367346612244892</v>
       </c>
       <c r="Z40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="n">
         <v>33.33333333333334</v>
       </c>
       <c r="AB40" t="n">
-        <v>14.8106908363406</v>
+        <v>16.61113233469046</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.61065425213315</v>
+        <v>2.696488619744197</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4996,7 +4996,7 @@
         <v>46254</v>
       </c>
       <c r="C41" t="n">
-        <v>1.814976624462309</v>
+        <v>1.812890476352746</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>19.94388699196217</v>
+        <v>19.8060225645478</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -5062,13 +5062,13 @@
         <v>20.97788601775494</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.8547008547008517</v>
+        <v>0.9686592250712334</v>
       </c>
       <c r="Z41" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA41" t="n">
-        <v>53.125</v>
+        <v>50</v>
       </c>
       <c r="AB41" t="n">
         <v>14.65953670141058</v>
@@ -5077,7 +5077,7 @@
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.163793103448286</v>
+        <v>2.051210009915394</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5111,7 +5111,7 @@
         <v>46254</v>
       </c>
       <c r="C42" t="n">
-        <v>3.577798748221679</v>
+        <v>3.56945415536619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>7.488622975611992</v>
+        <v>7.70438966068695</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
@@ -5180,7 +5180,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.714668298285039</v>
+        <v>2.487236750343302</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5212,7 +5212,7 @@
         <v>46254</v>
       </c>
       <c r="C43" t="n">
-        <v>6.88439409278807</v>
+        <v>6.842670492225718</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.40: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.50: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5244,22 +5244,22 @@
         <v>12.62186296009862</v>
       </c>
       <c r="K43" t="n">
-        <v>1.694915254237284</v>
+        <v>1.078582434514641</v>
       </c>
       <c r="L43" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M43" t="n">
-        <v>81.3953488372093</v>
+        <v>77.5</v>
       </c>
       <c r="N43" t="n">
-        <v>16.51795998000152</v>
+        <v>15.37350392947494</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.266666666666683</v>
+        <v>2.890243902439016</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5286,7 +5286,7 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.14087758654096</v>
+        <v>11.67941772238011</v>
       </c>
       <c r="Z43" t="n">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>46254</v>
       </c>
       <c r="C44" t="n">
-        <v>4.633405969706165</v>
+        <v>4.652181462702242</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5352,11 +5352,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5367,22 +5363,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>3.350401304967177</v>
+        <v>3.769197919926048</v>
       </c>
       <c r="L44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M44" t="n">
-        <v>84.61538461538461</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N44" t="n">
-        <v>17.77669066370159</v>
+        <v>20.27743358776483</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.434032776913123</v>
+        <v>6.004481295964137</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5440,7 +5436,7 @@
         <v>46254</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02315659852072333</v>
+        <v>0.0237824521119226</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5497,25 +5493,25 @@
         <v>60.82474226804123</v>
       </c>
       <c r="X45" t="n">
-        <v>15.7065029425477</v>
+        <v>17.77268946199939</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.8928562499999959</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="AA45" t="n">
-        <v>51.51515151515152</v>
+        <v>50</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.3520714796086</v>
+        <v>11.62455386702013</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.144145007710409</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5549,7 +5545,7 @@
         <v>46254</v>
       </c>
       <c r="C46" t="n">
-        <v>9.52341182835683</v>
+        <v>9.591212679270653</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,16 +5605,16 @@
         <v>21.77676482446944</v>
       </c>
       <c r="Y46" t="n">
-        <v>5.290456431535273</v>
+        <v>4.616182572614102</v>
       </c>
       <c r="Z46" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA46" t="n">
-        <v>45.16129032258065</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="AB46" t="n">
-        <v>10.84696264243016</v>
+        <v>11.2621540679988</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5658,7 +5654,7 @@
         <v>46254</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7076322273603943</v>
+        <v>0.7067978158483681</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5686,7 +5682,7 @@
         <v>25.52135514083118</v>
       </c>
       <c r="K47" t="n">
-        <v>5.073261901161086</v>
+        <v>4.949363729276635</v>
       </c>
       <c r="L47" t="n">
         <v>15</v>
@@ -5695,13 +5691,13 @@
         <v>53.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>15.3849757123887</v>
+        <v>14.06881185817727</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.68885995323276</v>
+        <v>4.812450586886641</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5767,7 +5763,7 @@
         <v>46254</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05841303974420271</v>
+        <v>0.05883027533259021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5795,22 +5791,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>1.44927391829448</v>
+        <v>2.173910877441698</v>
       </c>
       <c r="L48" t="n">
         <v>62</v>
       </c>
       <c r="M48" t="n">
-        <v>45.16129032258065</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="N48" t="n">
-        <v>14.53451028628262</v>
+        <v>13.99694593261976</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>8.428572971938797</v>
+        <v>7.659576750415042</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5985,7 +5981,7 @@
         <v>46254</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6809291484518855</v>
+        <v>0.6796774913378076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,22 +6009,22 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>1.872654346977476</v>
+        <v>1.68539605023208</v>
       </c>
       <c r="L50" t="n">
         <v>50</v>
       </c>
       <c r="M50" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N50" t="n">
-        <v>15.20042476406721</v>
+        <v>15.29155306294547</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.088240133389285</v>
+        <v>2.276240285895637</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6094,7 +6090,7 @@
         <v>46254</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1775339251910215</v>
+        <v>0.1773253023899957</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6122,7 +6118,7 @@
         <v>21.20514974257153</v>
       </c>
       <c r="K51" t="n">
-        <v>2.283660421626754</v>
+        <v>2.163465345032956</v>
       </c>
       <c r="L51" t="n">
         <v>17</v>
@@ -6131,13 +6127,13 @@
         <v>64.70588235294117</v>
       </c>
       <c r="N51" t="n">
-        <v>12.45585345480625</v>
+        <v>12.69140534648817</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.678019315400192</v>
+        <v>1.797643265882365</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6164,7 +6160,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>19.40574293296257</v>
+        <v>19.50045046358144</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6209,7 +6205,7 @@
         <v>46254</v>
       </c>
       <c r="C52" t="n">
-        <v>4.560389668722049</v>
+        <v>4.539527868440873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6266,25 +6262,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>17.48068965761174</v>
+        <v>17.64177084921177</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.09140628300368103</v>
+        <v>0.6846188764209171</v>
       </c>
       <c r="Z52" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA52" t="n">
-        <v>36.11111111111111</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.03516021329131</v>
+        <v>12.48808235518153</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.915829282312192</v>
+        <v>7.365808841307753</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6318,7 +6314,7 @@
         <v>46254</v>
       </c>
       <c r="C53" t="n">
-        <v>1.387309718698202</v>
+        <v>1.383137422270458</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6350,7 +6346,7 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>2.861559824003312</v>
+        <v>2.552206467055296</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -6365,7 +6361,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4.995491206616531</v>
+        <v>5.31221484219826</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6546,7 +6542,7 @@
         <v>46254</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9329397340255857</v>
+        <v>0.9354431277372005</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6606,16 +6602,16 @@
         <v>26.76177647494742</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.6075081072945</v>
+        <v>4.351537699314301</v>
       </c>
       <c r="Z55" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA55" t="n">
-        <v>50</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.36572635119501</v>
+        <v>12.18141334551018</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6655,7 +6651,7 @@
         <v>46254</v>
       </c>
       <c r="C56" t="n">
-        <v>1.251708016870558</v>
+        <v>1.257966541099943</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6707,7 +6703,7 @@
         <v>61.88091532996977</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.396875088532767</v>
+        <v>0.9038607129483456</v>
       </c>
       <c r="Z56" t="n">
         <v>4</v>
@@ -6722,7 +6718,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>8.725002294999996</v>
+        <v>9.179105616519401</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6748,7 +6744,7 @@
         <v>46254</v>
       </c>
       <c r="C57" t="n">
-        <v>1.315336491873177</v>
+        <v>1.310121041802883</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6765,11 +6761,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6780,22 +6772,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>4.186222781533799</v>
+        <v>3.773113249268167</v>
       </c>
       <c r="L57" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M57" t="n">
-        <v>75</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="N57" t="n">
-        <v>17.57291694245328</v>
+        <v>18.18775420284279</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>5.580178514252321</v>
+        <v>6.000481777755429</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6822,7 +6814,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>18.90877835337841</v>
+        <v>19.23031373253816</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6867,7 +6859,7 @@
         <v>46254</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7443490404995167</v>
+        <v>0.7426800580913101</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6886,7 +6878,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6899,13 +6891,13 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>12.14075770404957</v>
+        <v>11.88931524672414</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N58" t="n">
         <v>14.19416378953196</v>
@@ -6941,7 +6933,7 @@
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.002198504045881</v>
+        <v>1.224171772174221</v>
       </c>
       <c r="Z58" t="n">
         <v>46</v>
@@ -6956,7 +6948,7 @@
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>5.048396449650827</v>
+        <v>4.835017142868569</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6990,7 +6982,7 @@
         <v>46254</v>
       </c>
       <c r="C59" t="n">
-        <v>0.786907132057354</v>
+        <v>0.7860726410618686</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7015,10 +7007,10 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>11.1236565078948</v>
+        <v>11.17103304657197</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5330510595628057</v>
+        <v>0.48000082666666</v>
       </c>
       <c r="L59" t="n">
         <v>52</v>
@@ -7027,13 +7019,13 @@
         <v>57.69230769230769</v>
       </c>
       <c r="N59" t="n">
-        <v>13.93046650912136</v>
+        <v>13.6611314122733</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>7.427357333473594</v>
+        <v>7.484075548830593</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7099,7 +7091,7 @@
         <v>46254</v>
       </c>
       <c r="C60" t="n">
-        <v>11.77648625872384</v>
+        <v>11.75562445844266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7127,22 +7119,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>2.519022855752473</v>
+        <v>2.337412540684691</v>
       </c>
       <c r="L60" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M60" t="n">
-        <v>57.14285714285715</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="N60" t="n">
-        <v>13.6920950009654</v>
+        <v>13.63776857538468</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.346302560803218</v>
+        <v>5.533252520982135</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7208,7 +7200,7 @@
         <v>46254</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6367021541779186</v>
+        <v>0.6371193997799703</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7240,7 +7232,7 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>3.612512913595256</v>
+        <v>3.680412582297565</v>
       </c>
       <c r="L61" t="n">
         <v>20</v>
@@ -7255,7 +7247,7 @@
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>6.164783486847214</v>
+        <v>6.095256818819261</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7274,7 +7266,7 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>9.420601715756604</v>
+        <v>9.361242947574977</v>
       </c>
       <c r="Z61" t="n">
         <v>24</v>
@@ -7323,7 +7315,7 @@
         <v>46254</v>
       </c>
       <c r="C62" t="n">
-        <v>9.241777524560954</v>
+        <v>9.26263932484213</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7383,22 +7375,22 @@
         <v>11.694667893328</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.561167227833903</v>
+        <v>0.3367003367003352</v>
       </c>
       <c r="Z62" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA62" t="n">
-        <v>49.0566037735849</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.58536197617008</v>
+        <v>11.60735392349249</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.44695259593679</v>
+        <v>1.668918918918927</v>
       </c>
       <c r="AE62" t="n">
         <v>30</v>
@@ -7432,7 +7424,7 @@
         <v>46254</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1053520953836807</v>
+        <v>0.1051434725826549</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,7 +7452,7 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>7.201485869521673</v>
+        <v>6.989200825026076</v>
       </c>
       <c r="L63" t="n">
         <v>7</v>
@@ -7502,7 +7494,7 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>8.67992769931557</v>
+        <v>8.860763677981831</v>
       </c>
       <c r="Z63" t="n">
         <v>6</v>
@@ -7517,7 +7509,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.445544519870612</v>
+        <v>1.249995466269826</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7551,7 +7543,7 @@
         <v>46254</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1510394292374999</v>
+        <v>0.1499963452733632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7579,22 +7571,22 @@
         <v>24.42078296285393</v>
       </c>
       <c r="K64" t="n">
-        <v>2.115650448893147</v>
+        <v>1.41043593630954</v>
       </c>
       <c r="L64" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M64" t="n">
-        <v>57.57575757575758</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N64" t="n">
-        <v>15.58895125158012</v>
+        <v>15.9920918134248</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>2.824591077300553</v>
+        <v>3.539639713160159</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7660,21 +7652,21 @@
         <v>46254</v>
       </c>
       <c r="C65" t="n">
-        <v>6.618406139203076</v>
+        <v>6.639267939484252</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7688,7 +7680,7 @@
         <v>25.04872642808169</v>
       </c>
       <c r="K65" t="n">
-        <v>16.82663804015993</v>
+        <v>17.194885914203</v>
       </c>
       <c r="L65" t="n">
         <v>2</v>
@@ -7726,22 +7718,22 @@
         <v>21.96943581422117</v>
       </c>
       <c r="Y65" t="n">
-        <v>4.216464345948556</v>
+        <v>3.914546187858547</v>
       </c>
       <c r="Z65" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA65" t="n">
-        <v>50</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB65" t="n">
-        <v>10.29417008407049</v>
+        <v>10.41068873994096</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>0.08893522250363883</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7884,7 +7876,7 @@
         <v>46254</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0273289571166325</v>
+        <v>0.02753757741424229</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7912,7 +7904,7 @@
         <v>14.0514682678307</v>
       </c>
       <c r="K67" t="n">
-        <v>1.550386094585621</v>
+        <v>2.325588444204296</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
@@ -7921,13 +7913,13 @@
         <v>40</v>
       </c>
       <c r="N67" t="n">
-        <v>7.671407444036571</v>
+        <v>7.077382387711928</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>2.412215255521311</v>
+        <v>1.636356634986491</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7973,7 +7965,7 @@
         <v>46254</v>
       </c>
       <c r="C68" t="n">
-        <v>4.078481954969902</v>
+        <v>4.093085151538235</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,7 +8025,7 @@
         <v>128.9371825174344</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.6100645493680612</v>
+        <v>0.2541942083136406</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8044,7 +8036,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.435295552941168</v>
+        <v>7.765545358230952</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8078,7 +8070,7 @@
         <v>46254</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4149411948668918</v>
+        <v>0.4155670632699693</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8106,7 +8098,7 @@
         <v>20.01758548606234</v>
       </c>
       <c r="K69" t="n">
-        <v>6.363628778804387</v>
+        <v>6.524060269610388</v>
       </c>
       <c r="L69" t="n">
         <v>11</v>
@@ -8121,7 +8113,7 @@
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>1.538468779208957</v>
+        <v>1.385545881985761</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8171,7 +8163,7 @@
         <v>46254</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4301703393217607</v>
+        <v>0.4305875450777739</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8199,7 +8191,7 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>12.79751482061256</v>
+        <v>12.90691281518683</v>
       </c>
       <c r="L70" t="n">
         <v>8</v>
@@ -8241,22 +8233,22 @@
         <v>13.34453608357888</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.4826181145273334</v>
+        <v>0.3861000128575709</v>
       </c>
       <c r="Z70" t="n">
         <v>51</v>
       </c>
       <c r="AA70" t="n">
-        <v>50.98039215686274</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB70" t="n">
-        <v>10.18800156385175</v>
+        <v>9.743295480831128</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>7.553838076371289</v>
+        <v>7.643411198763605</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8399,7 +8391,7 @@
         <v>46254</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0715559764247596</v>
+        <v>0.07176459421895336</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8427,22 +8419,22 @@
         <v>21.72769951373251</v>
       </c>
       <c r="K72" t="n">
-        <v>1.780420829627971</v>
+        <v>2.077156447622319</v>
       </c>
       <c r="L72" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M72" t="n">
-        <v>56.52173913043478</v>
+        <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>17.3898758509428</v>
+        <v>17.02483572560697</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>3.163259833402865</v>
+        <v>2.86336694133662</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8469,7 +8461,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>20.334123172046</v>
+        <v>20.10186137747969</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8514,7 +8506,7 @@
         <v>46254</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07468524333766595</v>
+        <v>0.07405938995508468</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8542,16 +8534,16 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>13.52085429380536</v>
+        <v>12.56956314875177</v>
       </c>
       <c r="L73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M73" t="n">
-        <v>66.66666666666667</v>
+        <v>37.5</v>
       </c>
       <c r="N73" t="n">
-        <v>11.00909363979409</v>
+        <v>8.907419983978393</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
@@ -8584,22 +8576,22 @@
         <v>15.4234441942493</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.648356548122076</v>
+        <v>2.472531525479904</v>
       </c>
       <c r="Z73" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AA73" t="n">
-        <v>32.25806451612903</v>
+        <v>32</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.97283453243094</v>
+        <v>16.09557776918616</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>8.491615552885257</v>
+        <v>7.718306024201493</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8633,7 +8625,7 @@
         <v>46254</v>
       </c>
       <c r="C74" t="n">
-        <v>5.684840576620451</v>
+        <v>5.637901525987806</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8652,7 +8644,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -8665,16 +8657,16 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>20.27473516287004</v>
+        <v>19.28164101932339</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N74" t="n">
-        <v>18.31627048481326</v>
+        <v>16.52901193804602</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
@@ -8707,22 +8699,22 @@
         <v>35.33255906375725</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.807354830529051</v>
+        <v>2.618119790643947</v>
       </c>
       <c r="Z74" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA74" t="n">
-        <v>44.44444444444444</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB74" t="n">
-        <v>17.87470432555786</v>
+        <v>17.54270160378733</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>8.343440748878129</v>
+        <v>7.580342660755923</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8865,7 +8857,7 @@
         <v>46254</v>
       </c>
       <c r="C76" t="n">
-        <v>1.877562025305837</v>
+        <v>1.876518871663288</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8893,7 +8885,7 @@
         <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>8.331187687335051</v>
+        <v>8.271000022951846</v>
       </c>
       <c r="L76" t="n">
         <v>22</v>
@@ -8908,7 +8900,7 @@
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>1.540472645311963</v>
+        <v>1.596918820996973</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8935,22 +8927,22 @@
         <v>10.78536860174914</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.215257254084135</v>
+        <v>2.26958542498148</v>
       </c>
       <c r="Z76" t="n">
         <v>53</v>
       </c>
       <c r="AA76" t="n">
-        <v>32.0754716981132</v>
+        <v>33.9622641509434</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.65356431550411</v>
+        <v>10.35851778511709</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.825175069032348</v>
+        <v>1.770599851175547</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8984,7 +8976,7 @@
         <v>46254</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5240484405870526</v>
+        <v>0.523631194985001</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9012,7 +9004,7 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>7.930939563645012</v>
+        <v>7.845005313353615</v>
       </c>
       <c r="L77" t="n">
         <v>26</v>
@@ -9021,7 +9013,7 @@
         <v>65.38461538461539</v>
       </c>
       <c r="N77" t="n">
-        <v>13.92336255069648</v>
+        <v>13.94235574262528</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9054,22 +9046,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>7.181366083285823</v>
+        <v>7.255267966758283</v>
       </c>
       <c r="Z77" t="n">
         <v>34</v>
       </c>
       <c r="AA77" t="n">
-        <v>50</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.91075471878268</v>
+        <v>11.14518240500392</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>3.03671126989794</v>
+        <v>2.959447909405721</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9103,7 +9095,7 @@
         <v>46254</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04693905063264593</v>
+        <v>0.04735628622103345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9131,22 +9123,22 @@
         <v>19.53698884929083</v>
       </c>
       <c r="K78" t="n">
-        <v>0.4464281230070144</v>
+        <v>1.339284369021043</v>
       </c>
       <c r="L78" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M78" t="n">
-        <v>72.22222222222223</v>
+        <v>69.64285714285714</v>
       </c>
       <c r="N78" t="n">
-        <v>18.03119124624317</v>
+        <v>18.93822661963787</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>3.537778240000011</v>
+        <v>2.625552023132638</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9212,16 +9204,16 @@
         <v>46254</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8319686175354239</v>
+        <v>0.8336375200429356</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9240,7 +9232,7 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>4.934291181473127</v>
+        <v>5.144786022246683</v>
       </c>
       <c r="L79" t="n">
         <v>28</v>
@@ -9249,13 +9241,13 @@
         <v>64.28571428571429</v>
       </c>
       <c r="N79" t="n">
-        <v>11.93733806692384</v>
+        <v>11.69297347871431</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0.06261901403921133</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9321,7 +9313,7 @@
         <v>46254</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1283000738154122</v>
+        <v>0.1280914510143864</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9349,10 +9341,10 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.043089957316416</v>
+        <v>4.872284259364656</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
@@ -9360,7 +9352,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.71893015018674</v>
+        <v>4.889486079995886</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9387,22 +9379,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.453623651977358</v>
+        <v>6.605735077007536</v>
       </c>
       <c r="Z80" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA80" t="n">
-        <v>40.625</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.40307523818483</v>
+        <v>11.58902104315124</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.653058523902218</v>
+        <v>1.492880664719709</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9436,7 +9428,7 @@
         <v>46254</v>
       </c>
       <c r="C81" t="n">
-        <v>1.211027490467297</v>
+        <v>1.201639664277181</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9496,22 +9488,22 @@
         <v>30.67103176118848</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.19149065531915</v>
+        <v>1.957449412765955</v>
       </c>
       <c r="Z81" t="n">
         <v>17</v>
       </c>
       <c r="AA81" t="n">
-        <v>58.8235294117647</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB81" t="n">
-        <v>12.52862678478392</v>
+        <v>13.19770195457422</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>8.914727489667406</v>
+        <v>8.203122561645449</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9545,7 +9537,7 @@
         <v>46254</v>
       </c>
       <c r="C82" t="n">
-        <v>5.283250921207815</v>
+        <v>5.288466371278108</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9605,7 +9597,7 @@
         <v>21.75875960601758</v>
       </c>
       <c r="Y82" t="n">
-        <v>5.499065756270682</v>
+        <v>5.405777568468395</v>
       </c>
       <c r="Z82" t="n">
         <v>8</v>
@@ -9614,7 +9606,7 @@
         <v>25</v>
       </c>
       <c r="AB82" t="n">
-        <v>13.23504228311709</v>
+        <v>14.46141572313648</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9654,7 +9646,7 @@
         <v>46254</v>
       </c>
       <c r="C83" t="n">
-        <v>5.742210527393685</v>
+        <v>5.752641427534273</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9714,22 +9706,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>4.550806379325367</v>
+        <v>4.377420014891809</v>
       </c>
       <c r="Z83" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA83" t="n">
-        <v>50</v>
+        <v>53.06122448979592</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.63382948972703</v>
+        <v>12.57407852015067</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.518287966301624</v>
+        <v>1.696858613688201</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9981,7 +9973,7 @@
         <v>46254</v>
       </c>
       <c r="C86" t="n">
-        <v>4.779438571674397</v>
+        <v>4.76483505696361</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10041,7 +10033,7 @@
         <v>100.8644868744093</v>
       </c>
       <c r="Y86" t="n">
-        <v>6.834112435121853</v>
+        <v>7.118779638014805</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10086,16 +10078,16 @@
         <v>46254</v>
       </c>
       <c r="C87" t="n">
-        <v>5.669194226409569</v>
+        <v>5.658763326268982</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10114,13 +10106,13 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>5.133335168187636</v>
+        <v>4.939897568982166</v>
       </c>
       <c r="L87" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M87" t="n">
-        <v>46.15384615384615</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N87" t="n">
         <v>11.72710853195772</v>
@@ -10129,7 +10121,7 @@
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>0.05727319390447239</v>
       </c>
       <c r="Q87" t="n">
         <v>48</v>
@@ -10195,7 +10187,7 @@
         <v>46254</v>
       </c>
       <c r="C88" t="n">
-        <v>1.061865666230411</v>
+        <v>1.068124190251178</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10209,7 +10201,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10223,7 +10215,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>18.96250926210428</v>
+        <v>19.66366171995766</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10261,22 +10253,22 @@
         <v>27.20319322085054</v>
       </c>
       <c r="Y88" t="n">
-        <v>6.478362492393397</v>
+        <v>5.927155844116849</v>
       </c>
       <c r="Z88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA88" t="n">
-        <v>33.33333333333334</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB88" t="n">
-        <v>19.32319524016275</v>
+        <v>19.17942262629681</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>0.07743377649180871</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10310,7 +10302,7 @@
         <v>46254</v>
       </c>
       <c r="C89" t="n">
-        <v>2.1404206769301</v>
+        <v>2.142506825248281</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10342,7 +10334,7 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>16.26413066641423</v>
+        <v>16.37744681181905</v>
       </c>
       <c r="L89" t="n">
         <v>4</v>
@@ -10384,22 +10376,22 @@
         <v>20.95675253601343</v>
       </c>
       <c r="Y89" t="n">
-        <v>3.879586522630918</v>
+        <v>3.785903331714313</v>
       </c>
       <c r="Z89" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA89" t="n">
-        <v>29.41176470588235</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.1478587875485</v>
+        <v>13.84529800109621</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>6.367443975685861</v>
+        <v>6.458613533222513</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10433,21 +10425,21 @@
         <v>46254</v>
       </c>
       <c r="C90" t="n">
-        <v>2.739154440546895</v>
+        <v>2.74541304425974</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10461,22 +10453,22 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>7.978149970790671</v>
+        <v>8.224865687257644</v>
       </c>
       <c r="L90" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M90" t="n">
-        <v>60</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N90" t="n">
-        <v>15.59263786427928</v>
+        <v>16.04685375495613</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>0.02023560249480028</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>42</v>
@@ -10503,7 +10495,7 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>9.931879064812376</v>
+        <v>9.726085383466931</v>
       </c>
       <c r="Z90" t="n">
         <v>17</v>
@@ -10512,7 +10504,7 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AB90" t="n">
-        <v>15.09139627633752</v>
+        <v>15.5455038079218</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10552,7 +10544,7 @@
         <v>46254</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2273936151373339</v>
+        <v>0.2276022379383598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10580,22 +10572,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>1.572410245176026</v>
+        <v>1.665598089168463</v>
       </c>
       <c r="L91" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M91" t="n">
-        <v>63.38028169014085</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="N91" t="n">
-        <v>13.88224660079332</v>
+        <v>13.84026224612131</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>1.405489690928907</v>
+        <v>1.312540265253914</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10661,7 +10653,7 @@
         <v>46254</v>
       </c>
       <c r="C92" t="n">
-        <v>1.120278690954118</v>
+        <v>1.119235617003645</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10689,7 +10681,7 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>6.323290723960362</v>
+        <v>6.224294772525929</v>
       </c>
       <c r="L92" t="n">
         <v>29</v>
@@ -10698,13 +10690,13 @@
         <v>68.96551724137932</v>
       </c>
       <c r="N92" t="n">
-        <v>12.80373380929682</v>
+        <v>12.9746135125069</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>1.576991517684267</v>
+        <v>1.671656405228816</v>
       </c>
       <c r="Q92" t="n">
         <v>56</v>
@@ -10731,7 +10723,7 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.275098148846004</v>
+        <v>7.36143285329236</v>
       </c>
       <c r="Z92" t="n">
         <v>36</v>
@@ -10740,7 +10732,7 @@
         <v>50</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.66875451730866</v>
+        <v>11.55050149056757</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10780,7 +10772,7 @@
         <v>46254</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0419322183565457</v>
+        <v>0.04214083615073946</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10808,22 +10800,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>3.686213841192076</v>
+        <v>4.202065138061895</v>
       </c>
       <c r="L93" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M93" t="n">
-        <v>61.40350877192982</v>
+        <v>64.15094339622641</v>
       </c>
       <c r="N93" t="n">
-        <v>19.00391756101635</v>
+        <v>19.53194616401082</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.231527290939339</v>
+        <v>1.725431122268017</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10889,7 +10881,7 @@
         <v>46254</v>
       </c>
       <c r="C94" t="n">
-        <v>8.235195660994213</v>
+        <v>8.198687510502156</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10949,22 +10941,22 @@
         <v>52.92815171085716</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.986343885785236</v>
+        <v>2.420856610800748</v>
       </c>
       <c r="Z94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA94" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="AB94" t="n">
-        <v>15.72595103883507</v>
+        <v>14.90686389976875</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.09499683343888</v>
+        <v>3.66793893129771</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10998,7 +10990,7 @@
         <v>46254</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1439464240262942</v>
+        <v>0.1443636596146817</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11017,7 +11009,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -11030,16 +11022,16 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>7.903774241167505</v>
+        <v>8.216538486888014</v>
       </c>
       <c r="L95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M95" t="n">
-        <v>85.71428571428571</v>
+        <v>100</v>
       </c>
       <c r="N95" t="n">
-        <v>18.772825202213</v>
+        <v>18.17529258831296</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
@@ -11072,22 +11064,22 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>3.631281500655348</v>
+        <v>3.351952165194538</v>
       </c>
       <c r="Z95" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA95" t="n">
-        <v>46.66666666666666</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.59785310700193</v>
+        <v>10.28657002552313</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.457974471623559</v>
+        <v>2.739887555030196</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11121,7 +11113,7 @@
         <v>46254</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1322638169119257</v>
+        <v>0.1324724296992874</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11149,22 +11141,22 @@
         <v>13.52465198145173</v>
       </c>
       <c r="K96" t="n">
-        <v>3.08943165708242</v>
+        <v>3.252029215414165</v>
       </c>
       <c r="L96" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M96" t="n">
-        <v>56.92307692307692</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N96" t="n">
-        <v>14.43826969997416</v>
+        <v>15.06215336209593</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.70346924203149</v>
+        <v>6.535436480873025</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11230,7 +11222,7 @@
         <v>46254</v>
       </c>
       <c r="C97" t="n">
-        <v>1.935975129721621</v>
+        <v>1.939104272506815</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11258,13 +11250,13 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>8.31746448803492</v>
+        <v>8.492539470822557</v>
       </c>
       <c r="L97" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M97" t="n">
-        <v>55.17241379310344</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N97" t="n">
         <v>14.49932491657701</v>
@@ -11300,22 +11292,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>5.450838916558498</v>
+        <v>5.298017828772617</v>
       </c>
       <c r="Z97" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA97" t="n">
-        <v>47.05882352941177</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.4083613888801</v>
+        <v>11.54824769362695</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.5808206832812246</v>
+        <v>0.7412539369642368</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11349,7 +11341,7 @@
         <v>46254</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6275229507888291</v>
+        <v>0.6262712540373307</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11377,22 +11369,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>4.784698057399006</v>
+        <v>4.575687907251802</v>
       </c>
       <c r="L98" t="n">
         <v>42</v>
       </c>
       <c r="M98" t="n">
-        <v>40.47619047619047</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="N98" t="n">
-        <v>16.11984600975353</v>
+        <v>14.14358958021403</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>4.977159870942383</v>
+        <v>5.186972422843672</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11419,22 +11411,22 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>4.799106868698555</v>
+        <v>4.98900055867818</v>
       </c>
       <c r="Z98" t="n">
         <v>28</v>
       </c>
       <c r="AA98" t="n">
-        <v>32.14285714285715</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB98" t="n">
-        <v>12.52421259254083</v>
+        <v>11.99119720452292</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>3.362251157546137</v>
+        <v>3.169106165630209</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11468,16 +11460,16 @@
         <v>46254</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4497804030053998</v>
+        <v>0.4593768517879229</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11496,22 +11488,22 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>2.113581748742432</v>
+        <v>4.292262168573968</v>
       </c>
       <c r="L99" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M99" t="n">
-        <v>54.05405405405406</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N99" t="n">
-        <v>12.77718274545301</v>
+        <v>12.91686969642192</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.847372522784707</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>33</v>
@@ -11577,7 +11569,7 @@
         <v>46254</v>
       </c>
       <c r="C100" t="n">
-        <v>326.3190372542446</v>
+        <v>326.6751343313485</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11605,16 +11597,16 @@
         <v>17.72888230032435</v>
       </c>
       <c r="K100" t="n">
-        <v>6.471210035138131</v>
+        <v>6.5873972089183</v>
       </c>
       <c r="L100" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M100" t="n">
-        <v>63.1578947368421</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N100" t="n">
-        <v>14.73829068705574</v>
+        <v>13.89849008366731</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11686,7 +11678,7 @@
         <v>46254</v>
       </c>
       <c r="C101" t="n">
-        <v>343.3804246351229</v>
+        <v>343.5867608785289</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11714,7 +11706,7 @@
         <v>12.13141269388449</v>
       </c>
       <c r="K101" t="n">
-        <v>8.73795073924537</v>
+        <v>8.803291040152295</v>
       </c>
       <c r="L101" t="n">
         <v>18</v>
@@ -11723,7 +11715,7 @@
         <v>50</v>
       </c>
       <c r="N101" t="n">
-        <v>8.322941515058263</v>
+        <v>8.242539018848863</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11756,22 +11748,22 @@
         <v>10.77566750487711</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.839498521227168</v>
+        <v>1.780514177121051</v>
       </c>
       <c r="Z101" t="n">
         <v>41</v>
       </c>
       <c r="AA101" t="n">
-        <v>36.58536585365854</v>
+        <v>39.02439024390244</v>
       </c>
       <c r="AB101" t="n">
-        <v>14.23201560023499</v>
+        <v>13.852550552561</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.238468035610577</v>
+        <v>4.295976289763958</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11805,7 +11797,7 @@
         <v>46254</v>
       </c>
       <c r="C102" t="n">
-        <v>415.6171380707366</v>
+        <v>415.9467300678613</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11865,7 +11857,7 @@
         <v>10.29246150171719</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.105380006614409</v>
+        <v>1.026954762988008</v>
       </c>
       <c r="Z102" t="n">
         <v>37</v>
@@ -11874,13 +11866,13 @@
         <v>32.43243243243244</v>
       </c>
       <c r="AB102" t="n">
-        <v>11.98803151482821</v>
+        <v>11.3058204132745</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>3.93815153306224</v>
+        <v>4.014269973706163</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11914,7 +11906,7 @@
         <v>46254</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7239044856117743</v>
+        <v>0.7255733883279039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11942,16 +11934,16 @@
         <v>16.73842567092216</v>
       </c>
       <c r="K103" t="n">
-        <v>11.33530998924062</v>
+        <v>11.59198446071477</v>
       </c>
       <c r="L103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M103" t="n">
-        <v>70.58823529411765</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N103" t="n">
-        <v>17.98940078272775</v>
+        <v>14.05486902977729</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -11984,22 +11976,22 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>4.125821712406341</v>
+        <v>3.904791618338577</v>
       </c>
       <c r="Z103" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA103" t="n">
-        <v>42.5</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.35444912349157</v>
+        <v>10.14953663953723</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>4.040898557661987</v>
+        <v>4.26161559002659</v>
       </c>
       <c r="AE103" t="n">
         <v>35</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -477,7 +477,7 @@
     <col width="27" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="22" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
     <col width="14" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
   </cols>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C2" t="n">
-        <v>0.399086221854984</v>
+        <v>0.4005465812535469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>1.797373822422221</v>
+        <v>2.169876663837278</v>
       </c>
       <c r="L2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M2" t="n">
-        <v>57.57575757575758</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="N2" t="n">
-        <v>10.7006052392022</v>
+        <v>12.33896209001021</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>8.057797435802861</v>
+        <v>7.663827726763017</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -763,10 +763,10 @@
         <v>52.17391304347826</v>
       </c>
       <c r="AG2" t="n">
-        <v>36.70732709956448</v>
+        <v>36.76608358415216</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.46658594391378</v>
+        <v>15.40782945932609</v>
       </c>
       <c r="AI2" t="n">
         <v>38.13741307280403</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6475502999205583</v>
+        <v>0.6513053903836715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,43 +816,43 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.305670261852465</v>
+        <v>1.893133438545047</v>
       </c>
       <c r="L3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M3" t="n">
-        <v>57.4074074074074</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N3" t="n">
-        <v>13.15261140577361</v>
+        <v>14.67817668540686</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>6.608050389325881</v>
+        <v>7.956244241271149</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R3" t="n">
-        <v>57.14285714285715</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="S3" t="n">
-        <v>49.99428392849743</v>
+        <v>53.43417817185702</v>
       </c>
       <c r="T3" t="n">
-        <v>7.148573214359715</v>
+        <v>6.025281287602439</v>
       </c>
       <c r="U3" t="n">
-        <v>40.85741114397492</v>
+        <v>43.48596473022936</v>
       </c>
       <c r="V3" t="n">
         <v>72</v>
       </c>
       <c r="W3" t="n">
-        <v>56.94444444444444</v>
+        <v>65.27777777777777</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
@@ -872,10 +872,10 @@
         <v>59.45945945945946</v>
       </c>
       <c r="AG3" t="n">
-        <v>36.72013311457034</v>
+        <v>37.28095651308371</v>
       </c>
       <c r="AH3" t="n">
-        <v>22.73932634488911</v>
+        <v>22.17850294637575</v>
       </c>
       <c r="AI3" t="n">
         <v>43.48596473022936</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C4" t="n">
-        <v>1.441550367510705</v>
+        <v>1.446765817580999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,19 +922,19 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>15.33976973013975</v>
+        <v>14.71888288970985</v>
       </c>
       <c r="K4" t="n">
-        <v>11.61477150866097</v>
+        <v>12.01858762291574</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" t="n">
-        <v>53.33333333333334</v>
+        <v>56.25</v>
       </c>
       <c r="N4" t="n">
-        <v>11.73407357796408</v>
+        <v>11.07841973430984</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +967,22 @@
         <v>15.89522479111605</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.693381923344941</v>
+        <v>3.344949867595803</v>
       </c>
       <c r="Z4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA4" t="n">
         <v>46</v>
       </c>
-      <c r="AA4" t="n">
-        <v>45.65217391304348</v>
-      </c>
       <c r="AB4" t="n">
-        <v>12.91755796593209</v>
+        <v>11.6025137220631</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>6.548478393909873</v>
+        <v>6.885362040873899</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -991,10 +991,10 @@
         <v>59.09090909090909</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.67994283229618</v>
+        <v>39.20647024320037</v>
       </c>
       <c r="AH4" t="n">
-        <v>20.41096625861292</v>
+        <v>19.88443884770872</v>
       </c>
       <c r="AI4" t="n">
         <v>44.4097537410319</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2355297243400047</v>
+        <v>0.2359469699420563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,22 +1044,22 @@
         <v>15.99376685518751</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3555551999999906</v>
+        <v>0.5333370666666726</v>
       </c>
       <c r="L5" t="n">
         <v>47</v>
       </c>
       <c r="M5" t="n">
-        <v>55.31914893617022</v>
+        <v>53.19148936170212</v>
       </c>
       <c r="N5" t="n">
-        <v>14.64501183776445</v>
+        <v>15.00246203783031</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.635075651497187</v>
+        <v>2.453577097214632</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1068,10 +1068,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S5" t="n">
-        <v>41.85307399439394</v>
+        <v>42.02425514307264</v>
       </c>
       <c r="T5" t="n">
-        <v>19.12253576170362</v>
+        <v>18.95135461302493</v>
       </c>
       <c r="U5" t="n">
         <v>45.72685693412379</v>
@@ -1122,24 +1122,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C6" t="n">
         <v>1.715883073126723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1203,31 +1203,31 @@
         <v>11.42568615537318</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AF6" t="n">
-        <v>48</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AG6" t="n">
-        <v>41.96399064665</v>
+        <v>39.94930127170949</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.036009353350003</v>
+        <v>6.204544882136659</v>
       </c>
       <c r="AI6" t="n">
-        <v>34.79713528657805</v>
+        <v>33.34047468175682</v>
       </c>
       <c r="AJ6" t="n">
         <v>79</v>
       </c>
       <c r="AK6" t="n">
-        <v>44.30379746835443</v>
+        <v>39.24050632911393</v>
       </c>
     </row>
     <row r="7">
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C7" t="n">
-        <v>2.250988282257441</v>
+        <v>2.26141918239803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,10 +1282,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S7" t="n">
-        <v>53.2169356428875</v>
+        <v>52.82466880932375</v>
       </c>
       <c r="T7" t="n">
-        <v>8.007554153030867</v>
+        <v>8.399820986594612</v>
       </c>
       <c r="U7" t="n">
         <v>47.24599944352045</v>
@@ -1300,22 +1300,22 @@
         <v>14.22876300591287</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.766108891997956</v>
+        <v>4.324802637328784</v>
       </c>
       <c r="Z7" t="n">
         <v>37</v>
       </c>
       <c r="AA7" t="n">
-        <v>54.05405405405406</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.45219184553705</v>
+        <v>11.53950464232632</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2455965048585473</v>
+        <v>0.7057182857034383</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3867777964058587</v>
+        <v>0.3773899702157434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,22 +1409,22 @@
         <v>24.89870225327257</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.540090288008866</v>
+        <v>3.929897892426515</v>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>66.66666666666667</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.78648446130603</v>
+        <v>15.8588210325697</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.560954332466141</v>
+        <v>4.2365960046717</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5933096110533987</v>
+        <v>0.5912234230977971</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,16 +1518,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.600091586176269</v>
+        <v>4.935535570549055</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AA9" t="n">
-        <v>50</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.18468597526538</v>
+        <v>12.10261347953007</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C10" t="n">
-        <v>1.929716526008777</v>
+        <v>1.932845827969508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,22 +1595,22 @@
         <v>10.51321892894885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1082234505889401</v>
+        <v>0.2705627660826826</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>43.90243902439025</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N10" t="n">
-        <v>10.16882093237464</v>
+        <v>10.2480637444662</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.885407158702716</v>
+        <v>5.713977338776188</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1619,10 +1619,10 @@
         <v>48.78048780487805</v>
       </c>
       <c r="S10" t="n">
-        <v>38.19091809791883</v>
+        <v>38.36412638935644</v>
       </c>
       <c r="T10" t="n">
-        <v>10.58956970695922</v>
+        <v>10.41636141552161</v>
       </c>
       <c r="U10" t="n">
         <v>34.25442955443266</v>
@@ -1651,10 +1651,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="AG10" t="n">
-        <v>42.32591351939572</v>
+        <v>41.86902843890139</v>
       </c>
       <c r="AH10" t="n">
-        <v>12.84650027370773</v>
+        <v>13.30338535420206</v>
       </c>
       <c r="AI10" t="n">
         <v>37.54796321097091</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C11" t="n">
-        <v>8.365581912751564</v>
+        <v>8.38644371303274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.71186774256578</v>
+        <v>51.74705423095423</v>
       </c>
       <c r="T11" t="n">
-        <v>9.512622053352587</v>
+        <v>9.477435564964132</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1736,7 +1736,7 @@
         <v>22.18106016526054</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.896024464831814</v>
+        <v>1.651376146788996</v>
       </c>
       <c r="Z11" t="n">
         <v>40</v>
@@ -1745,34 +1745,34 @@
         <v>45</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.34362310187937</v>
+        <v>12.61617163727046</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.125311720698252</v>
+        <v>0.3544776119402959</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
-        <v>56.52173913043478</v>
+        <v>56.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>23.5034689084781</v>
+        <v>25.12593977685399</v>
       </c>
       <c r="AH11" t="n">
-        <v>33.01827022195668</v>
+        <v>31.12406022314601</v>
       </c>
       <c r="AI11" t="n">
-        <v>42.24743369429499</v>
+        <v>42.27501741982778</v>
       </c>
       <c r="AJ11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AK11" t="n">
-        <v>52.23880597014925</v>
+        <v>51.47058823529412</v>
       </c>
     </row>
     <row r="12">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C12" t="n">
-        <v>6.842670492225718</v>
+        <v>6.926117693350422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,22 +1813,22 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>4.209690230341545</v>
+        <v>5.480540111199361</v>
       </c>
       <c r="L12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666667</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N12" t="n">
-        <v>18.08574051873381</v>
+        <v>20.96723808634281</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.717987804878041</v>
+        <v>0.492469879518076</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1855,16 +1855,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.4242908218224</v>
+        <v>6.295318758673885</v>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.22222222222222</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.81326983452632</v>
+        <v>9.25142359009066</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1888,10 +1888,10 @@
         <v>23.07242812760128</v>
       </c>
       <c r="AJ12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>47.36842105263158</v>
       </c>
     </row>
     <row r="13">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2445003049280684</v>
+        <v>0.2376159122956064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>15.81028060663348</v>
+        <v>12.54941169767145</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1968,22 +1968,22 @@
         <v>16.60079365870428</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6779654128124313</v>
+        <v>3.474574944053466</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>33.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.23905013168687</v>
+        <v>11.38665977363141</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>9.385666157497441</v>
+        <v>6.760317348682343</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2004,14 +2004,14 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C14" t="n">
-        <v>8.532476315000972</v>
+        <v>8.589846265774206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2064,25 +2064,25 @@
         <v>58.69565217391305</v>
       </c>
       <c r="X14" t="n">
-        <v>13.13901871403786</v>
+        <v>12.93345142071747</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.561048243001796</v>
+        <v>1.905896366885051</v>
       </c>
       <c r="Z14" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>42.85714285714285</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.87233157293113</v>
+        <v>12.63796621409251</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.0959319975713413</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2091,10 +2091,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>27.82424138658631</v>
+        <v>27.9098721301118</v>
       </c>
       <c r="AH14" t="n">
-        <v>24.80733756078211</v>
+        <v>24.72170681725662</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C15" t="n">
-        <v>14.45722759485495</v>
+        <v>14.61369109696377</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,22 +2176,22 @@
         <v>38.77434577704333</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.910828025477707</v>
+        <v>0.8492569002123251</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.22222222222222</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.42437267126862</v>
+        <v>13.39973570565697</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.246753246753247</v>
+        <v>9.229122055674511</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2200,10 +2200,10 @@
         <v>56.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>24.48545745529968</v>
+        <v>24.52657587635231</v>
       </c>
       <c r="AH15" t="n">
-        <v>31.76454254470032</v>
+        <v>31.72342412364769</v>
       </c>
       <c r="AI15" t="n">
         <v>39.32559113685198</v>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C16" t="n">
-        <v>35.5902312796862</v>
+        <v>35.69454028109208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,22 +2253,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>2.207952183579054</v>
+        <v>2.507506556918959</v>
       </c>
       <c r="L16" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>67.81609195402299</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N16" t="n">
-        <v>18.44986819594546</v>
+        <v>17.85946578771896</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.623719730168754</v>
+        <v>7.309214412430109</v>
       </c>
       <c r="Q16" t="n">
         <v>27</v>
@@ -2295,16 +2295,16 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.05432265640782</v>
+        <v>11.79656861964465</v>
       </c>
       <c r="Z16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>57.69230769230769</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.1674972814445</v>
+        <v>13.40563990076058</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7176459615910077</v>
+        <v>0.7172287159889561</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,22 +2372,22 @@
         <v>14.75338697646304</v>
       </c>
       <c r="K17" t="n">
-        <v>3.303310255571046</v>
+        <v>3.243248812758837</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M17" t="n">
-        <v>65.57377049180327</v>
+        <v>64.51612903225806</v>
       </c>
       <c r="N17" t="n">
-        <v>16.64776798590285</v>
+        <v>16.68556143364886</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.546504591972322</v>
+        <v>4.607324199830232</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2396,10 +2396,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="S17" t="n">
-        <v>47.41500502052035</v>
+        <v>47.42764924369089</v>
       </c>
       <c r="T17" t="n">
-        <v>19.25166164614632</v>
+        <v>19.23901742297578</v>
       </c>
       <c r="U17" t="n">
         <v>52.07048830990042</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09930217413661169</v>
+        <v>0.09971940972499919</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,22 +2481,22 @@
         <v>20.56707245057805</v>
       </c>
       <c r="K18" t="n">
-        <v>2.412492439497371</v>
+        <v>2.842796578482676</v>
       </c>
       <c r="L18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M18" t="n">
-        <v>64.86486486486487</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>14.78190186872253</v>
+        <v>15.97066094670105</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.408771508012202</v>
+        <v>6.959362891357634</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2505,10 +2505,10 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>41.8298132902607</v>
+        <v>41.86541405947298</v>
       </c>
       <c r="T18" t="n">
-        <v>35.36316916587966</v>
+        <v>35.32756839666737</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
@@ -2537,10 +2537,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.89163227852313</v>
+        <v>39.97138293722115</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.6321772452864</v>
+        <v>19.55242658658837</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C19" t="n">
         <v>0.02524277917469493</v>
@@ -2668,19 +2668,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C20" t="n">
-        <v>1.697107420955111</v>
+        <v>1.707538321095699</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2699,22 +2699,22 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>1.87599613462941</v>
+        <v>2.502154696711001</v>
       </c>
       <c r="L20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>47.22222222222222</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="N20" t="n">
-        <v>12.35802226593892</v>
+        <v>12.53782064564077</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1217203954567703</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>48</v>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C21" t="n">
-        <v>0.942953388564122</v>
+        <v>0.9442050456782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,22 +2808,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>1.501827612736317</v>
+        <v>1.636559070477683</v>
       </c>
       <c r="L21" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>55</v>
+        <v>54.09836065573771</v>
       </c>
       <c r="N21" t="n">
-        <v>18.21306477199776</v>
+        <v>18.6173419760409</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.402025007920464</v>
+        <v>6.260976353114955</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2832,10 +2832,10 @@
         <v>72.5</v>
       </c>
       <c r="S21" t="n">
-        <v>46.51066584929121</v>
+        <v>46.53935937798475</v>
       </c>
       <c r="T21" t="n">
-        <v>25.98933415070879</v>
+        <v>25.96064062201525</v>
       </c>
       <c r="U21" t="n">
         <v>57.16504419378943</v>
@@ -2864,10 +2864,10 @@
         <v>62.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>36.18401807453076</v>
+        <v>36.35901807453077</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.31598192546924</v>
+        <v>26.14098192546923</v>
       </c>
       <c r="AI21" t="n">
         <v>47.0324391373011</v>
@@ -2886,14 +2886,14 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3460972697939794</v>
+        <v>0.3483920805506069</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2949,22 +2949,22 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.6758791013782</v>
+        <v>5.050459526770057</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>53.33333333333334</v>
+        <v>43.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.11838412757147</v>
+        <v>11.21366565444535</v>
       </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.00004746573541</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -2977,7 +2977,7 @@
         <v>19</v>
       </c>
       <c r="AK22" t="n">
-        <v>57.89473684210526</v>
+        <v>52.63157894736842</v>
       </c>
     </row>
     <row r="23">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C23" t="n">
-        <v>0.775224495319229</v>
+        <v>0.779814116832484</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
         <v>24.33755492423044</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8686202461918313</v>
+        <v>1.465800536919915</v>
       </c>
       <c r="L23" t="n">
         <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>71.42857142857143</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N23" t="n">
-        <v>20.08190631494157</v>
+        <v>22.62984058851431</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.095802781603086</v>
+        <v>3.483143526566002</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3060,7 +3060,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>23.68033560753854</v>
+        <v>23.22849439806307</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1777425479920474</v>
+        <v>0.1783683963677966</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,22 +3133,22 @@
         <v>23.5093122581746</v>
       </c>
       <c r="K24" t="n">
-        <v>5.185185929583858</v>
+        <v>5.555552949245679</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>50</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>12.28855668383958</v>
+        <v>12.25105140230857</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.577464048634594</v>
+        <v>4.21052888888882</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3183,25 +3183,25 @@
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG24" t="n">
-        <v>24.84848484848485</v>
+        <v>18.63636363636364</v>
       </c>
       <c r="AH24" t="n">
-        <v>-24.84848484848485</v>
+        <v>6.363636363636363</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.551115123125783e-15</v>
+        <v>4.558726080970055</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AK24" t="n">
-        <v>46.66666666666666</v>
+        <v>48.38709677419355</v>
       </c>
     </row>
     <row r="25">
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C25" t="n">
-        <v>3.567367848081091</v>
+        <v>3.577798748221679</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,22 +3242,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>2.028635904685672</v>
+        <v>2.32696524943623</v>
       </c>
       <c r="L25" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>56.89655172413793</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N25" t="n">
-        <v>16.97399430421782</v>
+        <v>16.22416845357686</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>5.852635431578967</v>
+        <v>5.544027165014587</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3266,10 +3266,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="S25" t="n">
-        <v>36.26937967334133</v>
+        <v>36.33689746236128</v>
       </c>
       <c r="T25" t="n">
-        <v>30.39728699332534</v>
+        <v>30.32976920430539</v>
       </c>
       <c r="U25" t="n">
         <v>52.07048830990042</v>
@@ -3298,10 +3298,10 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG25" t="n">
-        <v>54.42559590069766</v>
+        <v>54.59698175248721</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.7670593153318066</v>
+        <v>-0.9384451671213583</v>
       </c>
       <c r="AI25" t="n">
         <v>38.74647126766948</v>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4443563301340799</v>
+        <v>0.4456080667316169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C27" t="n">
-        <v>43.35082098428366</v>
+        <v>43.60116258765778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>31.51278611797912</v>
+        <v>32.27224397814068</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3478,22 +3478,22 @@
         <v>33.98102416350424</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.842229570146436</v>
+        <v>1.275389702409069</v>
       </c>
       <c r="Z27" t="n">
         <v>10</v>
       </c>
       <c r="AA27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>40.72118972052326</v>
+        <v>25.80591578680818</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.217035611164587</v>
+        <v>3.772727272727283</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C28" t="n">
-        <v>1.58028137129908</v>
+        <v>1.593841573400398</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,22 +3577,22 @@
         <v>18.63435792130579</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.466991374761708</v>
+        <v>3.647234255660625</v>
       </c>
       <c r="Z28" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AA28" t="n">
-        <v>52.94117647058823</v>
+        <v>45.94594594594594</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.57311832441738</v>
+        <v>11.88691949635073</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.604689988621688</v>
+        <v>2.441824815472515</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4065964826819056</v>
+        <v>0.4084740478364814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>12.47775118190457</v>
+        <v>12.99714649219166</v>
       </c>
       <c r="L29" t="n">
         <v>5</v>
@@ -3700,10 +3700,10 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>11.24226130266406</v>
+        <v>10.83239932776978</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4015896554126374</v>
+        <v>0.4051361631293814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,16 +3773,16 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>9.703404307875152</v>
+        <v>10.67221404858223</v>
       </c>
       <c r="L30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M30" t="n">
-        <v>56.25</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N30" t="n">
-        <v>13.00992913726943</v>
+        <v>14.83914496442762</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3815,22 +3815,22 @@
         <v>11.81199400890234</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.885834985519796</v>
+        <v>1.019371821800574</v>
       </c>
       <c r="Z30" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AA30" t="n">
-        <v>43.33333333333334</v>
+        <v>44.06779661016949</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.98827388135968</v>
+        <v>12.6579631094857</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>8.270125942857154</v>
+        <v>9.073116976011896</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C31" t="n">
-        <v>0.184835543398207</v>
+        <v>0.1860872601770337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,20 +3892,22 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>6.147862911628899</v>
+        <v>6.866702257137414</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="N31" t="n">
+        <v>10.85546246304441</v>
+      </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>3.629029339552625</v>
+        <v>2.931968215247638</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3968,10 +3970,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C32" t="n">
-        <v>2.278108527075925</v>
+        <v>2.284367130788769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,16 +4001,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>4.529573858716951</v>
+        <v>4.816745945243417</v>
       </c>
       <c r="L32" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M32" t="n">
-        <v>55.55555555555556</v>
+        <v>53.48837209302326</v>
       </c>
       <c r="N32" t="n">
-        <v>10.44660475484212</v>
+        <v>10.55367051125727</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4041,22 +4043,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.394499683152223</v>
+        <v>7.14008637438125</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
-        <v>35.29411764705883</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB32" t="n">
-        <v>14.63702839182677</v>
+        <v>13.33240290501161</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.6538491933805957</v>
+        <v>0.9260331956431056</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4087,10 +4089,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C33" t="n">
-        <v>1.731529423337606</v>
+        <v>1.734658725298336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4118,16 +4120,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.663663149127141</v>
+        <v>5.854623524281033</v>
       </c>
       <c r="L33" t="n">
         <v>29</v>
       </c>
       <c r="M33" t="n">
-        <v>62.06896551724138</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="N33" t="n">
-        <v>11.39383009772743</v>
+        <v>11.31004799319451</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4196,10 +4198,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7960862956004049</v>
+        <v>0.8027620652232232</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4216,7 +4218,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>5</v>
       </c>
@@ -4227,16 +4233,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>4.893147804613807</v>
+        <v>5.772754065424679</v>
       </c>
       <c r="L34" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M34" t="n">
-        <v>72.72727272727273</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="N34" t="n">
-        <v>9.616943003587124</v>
+        <v>10.48324386958539</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4283,10 +4289,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AG34" t="n">
-        <v>31.08262311990635</v>
+        <v>31.7080316729961</v>
       </c>
       <c r="AH34" t="n">
-        <v>22.76353072624749</v>
+        <v>22.13812217315774</v>
       </c>
       <c r="AI34" t="n">
         <v>38.56944827051576</v>
@@ -4305,10 +4311,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C35" t="n">
-        <v>1.947449024329222</v>
+        <v>1.966224676500835</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4340,7 +4346,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.787927035064282</v>
+        <v>10.84640913390267</v>
       </c>
       <c r="L35" t="n">
         <v>10</v>
@@ -4349,7 +4355,7 @@
         <v>80</v>
       </c>
       <c r="N35" t="n">
-        <v>10.83557166488997</v>
+        <v>11.11171484750929</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4382,16 +4388,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.28471812134147</v>
+        <v>5.381194838453796</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>41.66666666666666</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB35" t="n">
-        <v>14.75083324357035</v>
+        <v>12.54392409413347</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4428,10 +4434,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08031792899634745</v>
+        <v>0.08073516479335296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4459,7 +4465,7 @@
         <v>14.25367779956082</v>
       </c>
       <c r="K36" t="n">
-        <v>2.941173521547635</v>
+        <v>3.4759326110269</v>
       </c>
       <c r="L36" t="n">
         <v>29</v>
@@ -4468,7 +4474,7 @@
         <v>58.62068965517241</v>
       </c>
       <c r="N36" t="n">
-        <v>19.23117825848152</v>
+        <v>19.93102979683517</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4537,24 +4543,24 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06634052635446561</v>
+        <v>0.06571467297188434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4568,22 +4574,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>7.991176173387937</v>
+        <v>6.972392533717642</v>
       </c>
       <c r="L37" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M37" t="n">
-        <v>69.6969696969697</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N37" t="n">
-        <v>14.75545153938883</v>
+        <v>18.81710672338293</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.008170877403812504</v>
+        <v>0.9606286649692874</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4610,22 +4616,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.699082832467171</v>
+        <v>4.60758112253119</v>
       </c>
       <c r="Z37" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="AA37" t="n">
-        <v>50</v>
+        <v>56.14035087719298</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.66409114356596</v>
+        <v>13.38451986162349</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.3124759102858143</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4656,10 +4662,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C38" t="n">
-        <v>1.658513122353489</v>
+        <v>1.667900868851528</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,37 +4693,37 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>4.681649798486132</v>
+        <v>5.274183422766465</v>
       </c>
       <c r="L38" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>54.34782608695652</v>
+        <v>53.65853658536585</v>
       </c>
       <c r="N38" t="n">
-        <v>9.981770234747954</v>
+        <v>10.53259634513365</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>5.080499028962371</v>
+        <v>4.48905555339747</v>
       </c>
       <c r="Q38" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R38" t="n">
-        <v>52.27272727272727</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="S38" t="n">
-        <v>56.70632663816432</v>
+        <v>57.62086893326622</v>
       </c>
       <c r="T38" t="n">
-        <v>-4.433599365437047</v>
+        <v>-6.458078235591806</v>
       </c>
       <c r="U38" t="n">
-        <v>37.93546556062164</v>
+        <v>36.75230846944931</v>
       </c>
       <c r="V38" t="n">
         <v>68</v>
@@ -4737,19 +4743,19 @@
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF38" t="n">
-        <v>59.375</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="AG38" t="n">
-        <v>18.45430687339174</v>
+        <v>18.01886325926947</v>
       </c>
       <c r="AH38" t="n">
-        <v>40.92069312660826</v>
+        <v>38.64780340739719</v>
       </c>
       <c r="AI38" t="n">
-        <v>42.26002487538288</v>
+        <v>39.19730700081361</v>
       </c>
       <c r="AJ38" t="n">
         <v>67</v>
@@ -4765,10 +4771,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C39" t="n">
-        <v>2.695344532699445</v>
+        <v>2.701603136412288</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4796,7 +4802,7 @@
         <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>6.693865632179952</v>
+        <v>6.941609330798859</v>
       </c>
       <c r="L39" t="n">
         <v>21</v>
@@ -4805,7 +4811,7 @@
         <v>61.90476190476191</v>
       </c>
       <c r="N39" t="n">
-        <v>15.52587907997361</v>
+        <v>15.46006988334808</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4838,22 +4844,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.220024571127611</v>
+        <v>2.995300975980597</v>
       </c>
       <c r="Z39" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AA39" t="n">
-        <v>36.58536585365854</v>
+        <v>38.63636363636363</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.81425650134411</v>
+        <v>13.78517180818355</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.872469657646803</v>
+        <v>3.097477807003357</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4862,10 +4868,10 @@
         <v>60</v>
       </c>
       <c r="AG39" t="n">
-        <v>38.15817532762239</v>
+        <v>38.69657512107894</v>
       </c>
       <c r="AH39" t="n">
-        <v>21.84182467237761</v>
+        <v>21.30342487892106</v>
       </c>
       <c r="AI39" t="n">
         <v>45.45185459035139</v>
@@ -4884,19 +4890,19 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2495071321973366</v>
+        <v>0.2536794882898297</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4911,17 +4917,27 @@
       <c r="I40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>11.02041126530612</v>
+      </c>
+      <c r="K40" t="n">
+        <v>11.55963554061115</v>
+      </c>
       <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="M40" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="N40" t="n">
+        <v>13.87958643511992</v>
+      </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>27</v>
       </c>
@@ -4947,22 +4963,22 @@
         <v>39.56976926502232</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.367346612244892</v>
+        <v>0.7346951020408166</v>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA40" t="n">
-        <v>33.33333333333334</v>
+        <v>30</v>
       </c>
       <c r="AB40" t="n">
-        <v>16.61113233469046</v>
+        <v>14.591141794334</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.696488619744197</v>
+        <v>4.296873819451575</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4993,10 +5009,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C41" t="n">
-        <v>1.812890476352746</v>
+        <v>1.828536826563628</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5024,7 +5040,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>19.8060225645478</v>
+        <v>20.84002159034057</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -5059,25 +5075,25 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X41" t="n">
-        <v>20.97788601775494</v>
+        <v>21.11575044516931</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.9686592250712334</v>
+        <v>0.2276573061845921</v>
       </c>
       <c r="Z41" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.65953670141058</v>
+        <v>14.59836169912863</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.051210009915394</v>
+        <v>2.778668535751705</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5108,10 +5124,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C42" t="n">
-        <v>3.56945415536619</v>
+        <v>3.563195551653346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5169,7 +5185,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>7.70438966068695</v>
+        <v>7.866218787608337</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
@@ -5180,7 +5196,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.487236750343302</v>
+        <v>2.315959666816192</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5209,10 +5225,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C43" t="n">
-        <v>6.842670492225718</v>
+        <v>6.795731441593072</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5231,7 +5247,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.50: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5244,22 +5260,22 @@
         <v>12.62186296009862</v>
       </c>
       <c r="K43" t="n">
-        <v>1.078582434514641</v>
+        <v>0.3852080123266655</v>
       </c>
       <c r="L43" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M43" t="n">
-        <v>77.5</v>
+        <v>83.78378378378379</v>
       </c>
       <c r="N43" t="n">
-        <v>15.37350392947494</v>
+        <v>14.86607000032023</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.890243902439016</v>
+        <v>3.600920951650033</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5286,16 +5302,16 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.67941772238011</v>
+        <v>12.28527537519915</v>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA43" t="n">
-        <v>62.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB43" t="n">
-        <v>11.9104038953567</v>
+        <v>9.416359483443298</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5332,10 +5348,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C44" t="n">
-        <v>4.652181462702242</v>
+        <v>4.645922858989397</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5352,7 +5368,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5363,22 +5383,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>3.769197919926048</v>
+        <v>3.629596682831715</v>
       </c>
       <c r="L44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M44" t="n">
-        <v>72.72727272727273</v>
+        <v>75</v>
       </c>
       <c r="N44" t="n">
-        <v>20.27743358776483</v>
+        <v>18.72301468868908</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.004481295964137</v>
+        <v>6.147281781541158</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5433,10 +5453,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0237824521119226</v>
+        <v>0.02315659852072333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5496,22 +5516,22 @@
         <v>17.77268946199939</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.631577216066461</v>
       </c>
       <c r="Z45" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA45" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AB45" t="n">
-        <v>11.62455386702013</v>
+        <v>12.29747688746683</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.000000000000004</v>
+        <v>2.432434167275377</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5542,14 +5562,14 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C46" t="n">
-        <v>9.591212679270653</v>
+        <v>9.815477032293293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5559,7 +5579,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5605,22 +5625,22 @@
         <v>21.77676482446944</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.616182572614102</v>
+        <v>2.385892116182586</v>
       </c>
       <c r="Z46" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AA46" t="n">
-        <v>39.39393939393939</v>
+        <v>36.11111111111111</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.2621540679988</v>
+        <v>12.58276405830406</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>0.6291179596174201</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5651,10 +5671,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7067978158483681</v>
+        <v>0.708049472962446</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5679,25 +5699,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>25.52135514083118</v>
+        <v>25.00555187915373</v>
       </c>
       <c r="K47" t="n">
-        <v>4.949363729276635</v>
+        <v>5.135216903669981</v>
       </c>
       <c r="L47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M47" t="n">
-        <v>53.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>14.06881185817727</v>
+        <v>14.74102519690106</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.812450586886641</v>
+        <v>4.627167983861558</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5732,19 +5752,19 @@
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AF47" t="n">
-        <v>56.81818181818182</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="AG47" t="n">
-        <v>31.33377067451265</v>
+        <v>31.15164377116696</v>
       </c>
       <c r="AH47" t="n">
-        <v>25.48441114366917</v>
+        <v>24.66230971720514</v>
       </c>
       <c r="AI47" t="n">
-        <v>42.22414699362943</v>
+        <v>41.1076144528241</v>
       </c>
       <c r="AJ47" t="n">
         <v>76</v>
@@ -5760,10 +5780,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05883027533259021</v>
+        <v>0.05903889312678397</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5791,22 +5811,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>2.173910877441698</v>
+        <v>2.53622935701534</v>
       </c>
       <c r="L48" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M48" t="n">
-        <v>51.61290322580645</v>
+        <v>49.18032786885246</v>
       </c>
       <c r="N48" t="n">
-        <v>13.99694593261976</v>
+        <v>14.10204973331093</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>7.659576750415042</v>
+        <v>7.279154587396586</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5815,10 +5835,10 @@
         <v>63.82978723404256</v>
       </c>
       <c r="S48" t="n">
-        <v>48.25943983605992</v>
+        <v>48.28707294375279</v>
       </c>
       <c r="T48" t="n">
-        <v>15.57034739798264</v>
+        <v>15.54271429028977</v>
       </c>
       <c r="U48" t="n">
         <v>49.53589653479511</v>
@@ -5847,10 +5867,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>23.99416728091447</v>
+        <v>24.09275607382841</v>
       </c>
       <c r="AH48" t="n">
-        <v>36.38319120965157</v>
+        <v>36.28460241673763</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5869,10 +5889,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2576432414000073</v>
+        <v>0.2591035611611496</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5897,25 +5917,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>18.60609306322062</v>
+        <v>17.31218360853012</v>
       </c>
       <c r="K49" t="n">
-        <v>3.672734354135598</v>
+        <v>4.260350554919001</v>
       </c>
       <c r="L49" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M49" t="n">
-        <v>60</v>
+        <v>60.60606060606061</v>
       </c>
       <c r="N49" t="n">
-        <v>16.00865088934374</v>
+        <v>19.09000360666725</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.280245624978504</v>
+        <v>0.7094254346395878</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5956,10 +5976,10 @@
         <v>63.04347826086956</v>
       </c>
       <c r="AG49" t="n">
-        <v>36.85821306821072</v>
+        <v>37.39620847757585</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.18526519265884</v>
+        <v>25.64726978329371</v>
       </c>
       <c r="AI49" t="n">
         <v>48.60009642338971</v>
@@ -5978,10 +5998,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6796774913378076</v>
+        <v>0.6825981306514741</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6009,22 +6029,22 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>1.68539605023208</v>
+        <v>2.122347941555569</v>
       </c>
       <c r="L50" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N50" t="n">
-        <v>15.29155306294547</v>
+        <v>13.73988935945594</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.276240285895637</v>
+        <v>1.838629933889702</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6087,10 +6107,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1773253023899957</v>
+        <v>0.1781597735667708</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,22 +6138,22 @@
         <v>21.20514974257153</v>
       </c>
       <c r="K51" t="n">
-        <v>2.163465345032956</v>
+        <v>2.644234112946209</v>
       </c>
       <c r="L51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M51" t="n">
-        <v>64.70588235294117</v>
+        <v>56.25</v>
       </c>
       <c r="N51" t="n">
-        <v>12.69140534648817</v>
+        <v>13.46594877883989</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.797643265882365</v>
+        <v>1.320839790729944</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6160,7 +6180,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>19.50045046358144</v>
+        <v>19.12162943281972</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6202,10 +6222,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C52" t="n">
-        <v>4.539527868440873</v>
+        <v>4.552044757724106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6262,25 +6282,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>17.64177084921177</v>
+        <v>16.1827388466574</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.6846188764209171</v>
+        <v>0.4107755020276938</v>
       </c>
       <c r="Z52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA52" t="n">
-        <v>39.47368421052632</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.48808235518153</v>
+        <v>12.09096889729116</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.365808841307753</v>
+        <v>7.620527759132035</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6289,10 +6309,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>39.59177059067351</v>
+        <v>40.21614317249325</v>
       </c>
       <c r="AH52" t="n">
-        <v>28.82928204090543</v>
+        <v>28.20490945908569</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6311,10 +6331,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C53" t="n">
-        <v>1.383137422270458</v>
+        <v>1.390439020658933</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6346,7 +6366,7 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>2.552206467055296</v>
+        <v>3.093580746586566</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -6361,7 +6381,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>5.31221484219826</v>
+        <v>4.75918987184456</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6416,10 +6436,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08052654699915922</v>
+        <v>0.0809437873857608</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6451,7 +6471,7 @@
         <v>42.98617858772242</v>
       </c>
       <c r="K54" t="n">
-        <v>0.658603741275865</v>
+        <v>1.180156400676791</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
@@ -6460,13 +6480,13 @@
         <v>100</v>
       </c>
       <c r="N54" t="n">
-        <v>22.84645482583484</v>
+        <v>22.81328516164657</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>9.280276013697208</v>
+        <v>8.716969723189937</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6493,7 +6513,7 @@
         <v>10.17240666043591</v>
       </c>
       <c r="Y54" t="n">
-        <v>8.63537723060065</v>
+        <v>8.161980419901571</v>
       </c>
       <c r="Z54" t="n">
         <v>23</v>
@@ -6502,7 +6522,7 @@
         <v>69.56521739130434</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.6756080381485</v>
+        <v>15.0294452521139</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6539,10 +6559,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9354431277372005</v>
+        <v>0.942953388564122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6599,19 +6619,19 @@
         <v>73.41772151898734</v>
       </c>
       <c r="X55" t="n">
-        <v>26.76177647494742</v>
+        <v>26.27862368424858</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.351537699314301</v>
+        <v>3.583618326909732</v>
       </c>
       <c r="Z55" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA55" t="n">
-        <v>51.85185185185185</v>
+        <v>46.875</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.18141334551018</v>
+        <v>11.98481311669229</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6626,10 +6646,10 @@
         <v>56.52173913043478</v>
       </c>
       <c r="AG55" t="n">
-        <v>41.38577329938532</v>
+        <v>41.90783258398348</v>
       </c>
       <c r="AH55" t="n">
-        <v>15.13596583104946</v>
+        <v>14.6139065464513</v>
       </c>
       <c r="AI55" t="n">
         <v>42.24743369429499</v>
@@ -6648,10 +6668,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C56" t="n">
-        <v>1.257966541099943</v>
+        <v>1.318465793625289</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6700,25 +6720,21 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>61.88091532996977</v>
+        <v>68.26570504629608</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.9038607129483456</v>
+        <v>0.07905018181817436</v>
       </c>
       <c r="Z56" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>8.463649353473347</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>9.179105616519401</v>
+        <v>9.928798551489137</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6741,10 +6757,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C57" t="n">
-        <v>1.310121041802883</v>
+        <v>1.323681243695584</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6772,22 +6788,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>3.773113249268167</v>
+        <v>4.847200544864738</v>
       </c>
       <c r="L57" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M57" t="n">
-        <v>71.7948717948718</v>
+        <v>71.875</v>
       </c>
       <c r="N57" t="n">
-        <v>18.18775420284279</v>
+        <v>20.66881376754441</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>6.000481777755429</v>
+        <v>4.914579910915551</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6814,7 +6830,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>19.23031373253816</v>
+        <v>18.39431979178769</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6856,10 +6872,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7426800580913101</v>
+        <v>0.7481041708086684</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6878,7 +6894,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6891,16 +6907,16 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>11.88931524672414</v>
+        <v>12.70649116407139</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M58" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N58" t="n">
-        <v>14.19416378953196</v>
+        <v>15.40033847307047</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6933,22 +6949,22 @@
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.224171772174221</v>
+        <v>0.5027693052289228</v>
       </c>
       <c r="Z58" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA58" t="n">
-        <v>28.26086956521739</v>
+        <v>31.11111111111111</v>
       </c>
       <c r="AB58" t="n">
-        <v>12.96779667609787</v>
+        <v>12.67099450286217</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.835017142868569</v>
+        <v>5.525008742841298</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6979,10 +6995,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7860726410618686</v>
+        <v>0.790245016973072</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7010,22 +7026,22 @@
         <v>11.17103304657197</v>
       </c>
       <c r="K59" t="n">
-        <v>0.48000082666666</v>
+        <v>1.01333618666668</v>
       </c>
       <c r="L59" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M59" t="n">
-        <v>57.69230769230769</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N59" t="n">
-        <v>13.6611314122733</v>
+        <v>13.24091072374009</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>7.484075548830593</v>
+        <v>6.916575649399781</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7088,10 +7104,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C60" t="n">
-        <v>11.75562445844266</v>
+        <v>11.79734805900501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7119,22 +7135,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>2.337412540684691</v>
+        <v>2.70063317082021</v>
       </c>
       <c r="L60" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M60" t="n">
-        <v>55.81395348837209</v>
+        <v>53.65853658536585</v>
       </c>
       <c r="N60" t="n">
-        <v>13.63776857538468</v>
+        <v>14.33560749626898</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.533252520982135</v>
+        <v>5.160013785275752</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7197,10 +7213,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6371193997799703</v>
+        <v>0.6333642692622006</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7219,7 +7235,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -7232,22 +7248,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>3.680412582297565</v>
+        <v>3.069328566464424</v>
       </c>
       <c r="L61" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M61" t="n">
-        <v>80</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N61" t="n">
-        <v>19.49335756577184</v>
+        <v>20.78004206586317</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>6.095256818819261</v>
+        <v>6.724281151270262</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7266,16 +7282,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>9.361242947574977</v>
+        <v>9.895460494266894</v>
       </c>
       <c r="Z61" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA61" t="n">
-        <v>37.5</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB61" t="n">
-        <v>13.95405361141776</v>
+        <v>12.995828514067</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7312,7 +7328,7 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C62" t="n">
         <v>9.26263932484213</v>
@@ -7351,25 +7367,25 @@
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R62" t="n">
-        <v>72.41379310344827</v>
+        <v>70</v>
       </c>
       <c r="S62" t="n">
-        <v>52.62133980403603</v>
+        <v>52.82807945762698</v>
       </c>
       <c r="T62" t="n">
-        <v>19.79245329941224</v>
+        <v>17.17192054237302</v>
       </c>
       <c r="U62" t="n">
-        <v>54.28286758313406</v>
+        <v>52.12421254128504</v>
       </c>
       <c r="V62" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W62" t="n">
-        <v>73.13432835820896</v>
+        <v>72.05882352941177</v>
       </c>
       <c r="X62" t="n">
         <v>11.694667893328</v>
@@ -7421,10 +7437,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1051434725826549</v>
+        <v>0.1055607081710424</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7452,7 +7468,7 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>6.989200825026076</v>
+        <v>7.413760724569496</v>
       </c>
       <c r="L63" t="n">
         <v>7</v>
@@ -7494,7 +7510,7 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>8.860763677981831</v>
+        <v>8.499100400576653</v>
       </c>
       <c r="Z63" t="n">
         <v>6</v>
@@ -7509,7 +7525,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.249995466269826</v>
+        <v>1.640311304035313</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7540,7 +7556,7 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C64" t="n">
         <v>0.1499963452733632</v>
@@ -7621,19 +7637,19 @@
       </c>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AF64" t="n">
-        <v>60.78431372549019</v>
+        <v>62</v>
       </c>
       <c r="AG64" t="n">
-        <v>38.36293432934519</v>
+        <v>38.6797117586984</v>
       </c>
       <c r="AH64" t="n">
-        <v>22.42137939614501</v>
+        <v>23.3202882413016</v>
       </c>
       <c r="AI64" t="n">
-        <v>47.08515898394834</v>
+        <v>48.15044693099298</v>
       </c>
       <c r="AJ64" t="n">
         <v>100</v>
@@ -7649,7 +7665,7 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C65" t="n">
         <v>6.639267939484252</v>
@@ -7677,16 +7693,20 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>25.04872642808169</v>
+        <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
         <v>17.194885914203</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M65" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N65" t="n">
+        <v>10.40484726341951</v>
+      </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
@@ -7742,10 +7762,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG65" t="n">
-        <v>20.75782001898443</v>
+        <v>20.76273934208557</v>
       </c>
       <c r="AH65" t="n">
-        <v>33.78763452647011</v>
+        <v>33.78271520336897</v>
       </c>
       <c r="AI65" t="n">
         <v>40.06618319896197</v>
@@ -7764,10 +7784,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4631319820970748</v>
+        <v>0.4610457941414731</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7827,22 +7847,22 @@
         <v>12.69724877030836</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.508430107020586</v>
+        <v>1.952087497962707</v>
       </c>
       <c r="Z66" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AA66" t="n">
-        <v>37.70491803278689</v>
+        <v>36.50793650793651</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.17445057007504</v>
+        <v>11.32406401405177</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.560359732167885</v>
+        <v>4.128504522677312</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7873,10 +7893,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02753757741424229</v>
+        <v>0.02774619520843605</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7904,22 +7924,22 @@
         <v>14.0514682678307</v>
       </c>
       <c r="K67" t="n">
-        <v>2.325588444204296</v>
+        <v>3.100781491497107</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>40</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N67" t="n">
-        <v>7.077382387711928</v>
+        <v>6.573256403145478</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.636356634986491</v>
+        <v>0.8721742895586582</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7962,10 +7982,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C68" t="n">
-        <v>4.093085151538235</v>
+        <v>4.29544455063715</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8022,10 +8042,10 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>128.9371825174344</v>
+        <v>142.0891443924669</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.2541942083136406</v>
+        <v>1.009618317307703</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8036,7 +8056,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.765545358230952</v>
+        <v>7.061677673998212</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8054,10 +8074,10 @@
         <v>30.06418425824019</v>
       </c>
       <c r="AJ68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK68" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
@@ -8067,10 +8087,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4155670632699693</v>
+        <v>0.4149411948668918</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8095,25 +8115,25 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>20.01758548606234</v>
+        <v>18.0901893667493</v>
       </c>
       <c r="K69" t="n">
-        <v>6.524060269610388</v>
+        <v>6.363628778804387</v>
       </c>
       <c r="L69" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M69" t="n">
-        <v>63.63636363636363</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N69" t="n">
-        <v>23.19845319213931</v>
+        <v>21.39705057314318</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>1.385545881985761</v>
+        <v>1.538468779208957</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8160,10 +8180,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4305875450777739</v>
+        <v>0.4264152088039909</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8191,16 +8211,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>12.90691281518683</v>
+        <v>11.81285978628521</v>
       </c>
       <c r="L70" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M70" t="n">
-        <v>37.5</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="N70" t="n">
-        <v>8.534401960408296</v>
+        <v>12.00172386214981</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8233,22 +8253,22 @@
         <v>13.34453608357888</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.3861000128575709</v>
+        <v>1.351345508321844</v>
       </c>
       <c r="Z70" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AA70" t="n">
-        <v>52.94117647058823</v>
+        <v>43.63636363636363</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.743295480831128</v>
+        <v>10.44174077450655</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>7.643411198763605</v>
+        <v>6.739731551269179</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8257,10 +8277,10 @@
         <v>50</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.60271054912563</v>
+        <v>34.67448088405386</v>
       </c>
       <c r="AH70" t="n">
-        <v>15.39728945087437</v>
+        <v>15.32551911594614</v>
       </c>
       <c r="AI70" t="n">
         <v>35.8317605399894</v>
@@ -8279,10 +8299,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C71" t="n">
-        <v>3.123011438463552</v>
+        <v>3.139700942316983</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8310,22 +8330,22 @@
         <v>14.92600999981897</v>
       </c>
       <c r="K71" t="n">
-        <v>1.080344891356511</v>
+        <v>1.620522485582798</v>
       </c>
       <c r="L71" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M71" t="n">
-        <v>61.19402985074627</v>
+        <v>59.42028985507246</v>
       </c>
       <c r="N71" t="n">
-        <v>16.85758192111756</v>
+        <v>16.72997395311209</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.9098258515361834</v>
+        <v>0.3734260611295781</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8388,10 +8408,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07176459421895336</v>
+        <v>0.0719732120131471</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8405,7 +8425,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8419,22 +8439,22 @@
         <v>21.72769951373251</v>
       </c>
       <c r="K72" t="n">
-        <v>2.077156447622319</v>
+        <v>2.373892065616645</v>
       </c>
       <c r="L72" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M72" t="n">
-        <v>60</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N72" t="n">
-        <v>17.02483572560697</v>
+        <v>15.92894704940889</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>2.86336694133662</v>
+        <v>2.565212557025909</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8461,7 +8481,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>20.10186137747969</v>
+        <v>19.86959958291339</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8469,31 +8489,31 @@
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF72" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="AG72" t="n">
-        <v>51.56593406593407</v>
+        <v>56.92861952861953</v>
       </c>
       <c r="AH72" t="n">
-        <v>5.57692307692308</v>
+        <v>-6.928619528619528</v>
       </c>
       <c r="AI72" t="n">
-        <v>25.04583645276572</v>
+        <v>23.6593090512564</v>
       </c>
       <c r="AJ72" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AK72" t="n">
-        <v>46.66666666666666</v>
+        <v>45.16129032258065</v>
       </c>
     </row>
     <row r="73">
@@ -8503,10 +8523,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07405938995508468</v>
+        <v>0.07322491877830965</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8534,16 +8554,16 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>12.56956314875177</v>
+        <v>11.30117495534699</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M73" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="N73" t="n">
-        <v>8.907419983978393</v>
+        <v>8.996964415772805</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
@@ -8576,22 +8596,22 @@
         <v>15.4234441942493</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.472531525479904</v>
+        <v>3.571431495290345</v>
       </c>
       <c r="Z73" t="n">
         <v>25</v>
       </c>
       <c r="AA73" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AB73" t="n">
-        <v>16.09557776918616</v>
+        <v>13.46044713942639</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>7.718306024201493</v>
+        <v>6.666663836657161</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8622,10 +8642,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C74" t="n">
-        <v>5.637901525987806</v>
+        <v>5.611824275636335</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8657,7 +8677,7 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>19.28164101932339</v>
+        <v>18.72992205068638</v>
       </c>
       <c r="L74" t="n">
         <v>4</v>
@@ -8696,25 +8716,25 @@
         <v>77.39130434782609</v>
       </c>
       <c r="X74" t="n">
-        <v>35.33255906375725</v>
+        <v>32.26405389680429</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.618119790643947</v>
+        <v>3.068544768485559</v>
       </c>
       <c r="Z74" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA74" t="n">
-        <v>53.33333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB74" t="n">
-        <v>17.54270160378733</v>
+        <v>19.62997595670867</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>7.580342660755923</v>
+        <v>7.150883286502929</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8745,7 +8765,7 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C75" t="n">
         <v>0.1253794244880816</v>
@@ -8854,10 +8874,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C76" t="n">
-        <v>1.876518871663288</v>
+        <v>1.890079073555988</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8885,22 +8905,22 @@
         <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>8.271000022951846</v>
+        <v>9.05339376362042</v>
       </c>
       <c r="L76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M76" t="n">
-        <v>54.54545454545455</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N76" t="n">
-        <v>9.728334478495144</v>
+        <v>9.165714773644876</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>1.596918820996973</v>
+        <v>0.8680208874850992</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8927,22 +8947,22 @@
         <v>10.78536860174914</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.26958542498148</v>
+        <v>1.563360631451982</v>
       </c>
       <c r="Z76" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AA76" t="n">
-        <v>33.9622641509434</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.35851778511709</v>
+        <v>10.10432326031234</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.770599851175547</v>
+        <v>2.475337825609036</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8951,10 +8971,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG76" t="n">
-        <v>29.58374262512391</v>
+        <v>30.23579535077641</v>
       </c>
       <c r="AH76" t="n">
-        <v>24.96171192033064</v>
+        <v>24.30965919467813</v>
       </c>
       <c r="AI76" t="n">
         <v>37.98593853621745</v>
@@ -8973,10 +8993,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C77" t="n">
-        <v>0.523631194985001</v>
+        <v>0.5344793407276406</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9004,16 +9024,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>7.845005313353615</v>
+        <v>10.07924640987292</v>
       </c>
       <c r="L77" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M77" t="n">
-        <v>65.38461538461539</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N77" t="n">
-        <v>13.94235574262528</v>
+        <v>16.90273640953321</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9028,10 +9048,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S77" t="n">
-        <v>38.83204808476547</v>
+        <v>38.66198005755459</v>
       </c>
       <c r="T77" t="n">
-        <v>18.31080905809167</v>
+        <v>18.48087708530255</v>
       </c>
       <c r="U77" t="n">
         <v>39.07078562746877</v>
@@ -9046,22 +9066,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>7.255267966758283</v>
+        <v>5.333861489079883</v>
       </c>
       <c r="Z77" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AA77" t="n">
-        <v>47.05882352941177</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.14518240500392</v>
+        <v>11.13919768245498</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>2.959447909405721</v>
+        <v>4.929047053484559</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9092,10 +9112,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04735628622103345</v>
+        <v>0.0475649040152272</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9123,22 +9143,22 @@
         <v>19.53698884929083</v>
       </c>
       <c r="K78" t="n">
-        <v>1.339284369021043</v>
+        <v>1.785712492028058</v>
       </c>
       <c r="L78" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M78" t="n">
-        <v>69.64285714285714</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N78" t="n">
-        <v>18.93822661963787</v>
+        <v>18.85415131321418</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>2.625552023132638</v>
+        <v>2.175440397045292</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9201,10 +9221,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8336375200429356</v>
+        <v>0.8348892568490904</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9232,7 +9252,7 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>5.144786022246683</v>
+        <v>5.302664711095217</v>
       </c>
       <c r="L79" t="n">
         <v>28</v>
@@ -9241,7 +9261,7 @@
         <v>64.28571428571429</v>
       </c>
       <c r="N79" t="n">
-        <v>11.69297347871431</v>
+        <v>11.65746550447703</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
@@ -9288,10 +9308,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>27.69183331670432</v>
+        <v>27.89670918702137</v>
       </c>
       <c r="AH79" t="n">
-        <v>25.08594446107346</v>
+        <v>24.88106859075641</v>
       </c>
       <c r="AI79" t="n">
         <v>37.00593802298759</v>
@@ -9310,7 +9330,7 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C80" t="n">
         <v>0.1280914510143864</v>
@@ -9382,10 +9402,10 @@
         <v>6.605735077007536</v>
       </c>
       <c r="Z80" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA80" t="n">
-        <v>45.16129032258065</v>
+        <v>43.75</v>
       </c>
       <c r="AB80" t="n">
         <v>11.58902104315124</v>
@@ -9403,10 +9423,10 @@
         <v>50</v>
       </c>
       <c r="AG80" t="n">
-        <v>41.49797126341749</v>
+        <v>41.81265657810281</v>
       </c>
       <c r="AH80" t="n">
-        <v>8.50202873658251</v>
+        <v>8.187343421897189</v>
       </c>
       <c r="AI80" t="n">
         <v>32.06059352575905</v>
@@ -9425,10 +9445,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C81" t="n">
-        <v>1.201639664277181</v>
+        <v>1.211027490467297</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9485,25 +9505,25 @@
         <v>64.58333333333333</v>
       </c>
       <c r="X81" t="n">
-        <v>30.67103176118848</v>
+        <v>29.47918074704852</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.957449412765955</v>
+        <v>1.19149065531915</v>
       </c>
       <c r="Z81" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA81" t="n">
-        <v>52.94117647058823</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AB81" t="n">
-        <v>13.19770195457422</v>
+        <v>14.01965355445153</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>8.203122561645449</v>
+        <v>8.914727489667406</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9534,7 +9554,7 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C82" t="n">
         <v>5.288466371278108</v>
@@ -9594,19 +9614,19 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>21.75875960601758</v>
+        <v>16.65327680511959</v>
       </c>
       <c r="Y82" t="n">
         <v>5.405777568468395</v>
       </c>
       <c r="Z82" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA82" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AB82" t="n">
-        <v>14.46141572313648</v>
+        <v>8.312827786585837</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9643,10 +9663,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C83" t="n">
-        <v>5.752641427534273</v>
+        <v>5.77350322781545</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,10 +9708,10 @@
         <v>61.90476190476191</v>
       </c>
       <c r="S83" t="n">
-        <v>58.54260360742552</v>
+        <v>58.36301266696502</v>
       </c>
       <c r="T83" t="n">
-        <v>3.362158297336386</v>
+        <v>3.541749237796886</v>
       </c>
       <c r="U83" t="n">
         <v>46.81404026715268</v>
@@ -9706,22 +9726,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>4.377420014891809</v>
+        <v>4.03064728602468</v>
       </c>
       <c r="Z83" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA83" t="n">
-        <v>53.06122448979592</v>
+        <v>46</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.57407852015067</v>
+        <v>12.51277349367968</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.696858613688201</v>
+        <v>2.052064183286439</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9752,10 +9772,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C84" t="n">
-        <v>2.144593132533381</v>
+        <v>2.146679280851562</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9783,22 +9803,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>2.667145315661656</v>
+        <v>2.767014558588743</v>
       </c>
       <c r="L84" t="n">
         <v>58</v>
       </c>
       <c r="M84" t="n">
-        <v>46.55172413793103</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="N84" t="n">
-        <v>10.83844897685717</v>
+        <v>10.54561761835785</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>2.272250462565917</v>
+        <v>2.172862032630341</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9807,10 +9827,10 @@
         <v>56.09756097560975</v>
       </c>
       <c r="S84" t="n">
-        <v>27.293360475434</v>
+        <v>27.35433608519009</v>
       </c>
       <c r="T84" t="n">
-        <v>28.80420050017576</v>
+        <v>28.74322489041966</v>
       </c>
       <c r="U84" t="n">
         <v>41.04052722210609</v>
@@ -9839,10 +9859,10 @@
         <v>41.02564102564103</v>
       </c>
       <c r="AG84" t="n">
-        <v>26.84396891564488</v>
+        <v>26.88631895799493</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.18167210999615</v>
+        <v>14.1393220676461</v>
       </c>
       <c r="AI84" t="n">
         <v>27.07931000072518</v>
@@ -9861,10 +9881,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C85" t="n">
-        <v>6.289832784774555</v>
+        <v>6.321125485196319</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9892,22 +9912,22 @@
         <v>15.93296998857089</v>
       </c>
       <c r="K85" t="n">
-        <v>1.666920503700609</v>
+        <v>2.172726078345888</v>
       </c>
       <c r="L85" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M85" t="n">
-        <v>58.8235294117647</v>
+        <v>56</v>
       </c>
       <c r="N85" t="n">
-        <v>15.72056805328279</v>
+        <v>14.44780391972448</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.229242968039816</v>
+        <v>5.703355626613882</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9916,10 +9936,10 @@
         <v>60.60606060606061</v>
       </c>
       <c r="S85" t="n">
-        <v>66.38783400931739</v>
+        <v>66.03551330824058</v>
       </c>
       <c r="T85" t="n">
-        <v>-5.781773403256778</v>
+        <v>-5.429452702179972</v>
       </c>
       <c r="U85" t="n">
         <v>43.68344081994023</v>
@@ -9970,10 +9990,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C86" t="n">
-        <v>4.76483505696361</v>
+        <v>4.75857677139322</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10030,10 +10050,10 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>100.8644868744093</v>
+        <v>88.01181128002702</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.118779638014805</v>
+        <v>7.240772780317196</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10075,19 +10095,19 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C87" t="n">
-        <v>5.658763326268982</v>
+        <v>5.679625126550158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10106,22 +10126,22 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>4.939897568982166</v>
+        <v>5.326772767393151</v>
       </c>
       <c r="L87" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M87" t="n">
-        <v>44.44444444444444</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N87" t="n">
-        <v>11.72710853195772</v>
+        <v>11.24467722556862</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0.05727319390447239</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>48</v>
@@ -10130,10 +10150,10 @@
         <v>56.25</v>
       </c>
       <c r="S87" t="n">
-        <v>34.66367189038035</v>
+        <v>34.92338863896205</v>
       </c>
       <c r="T87" t="n">
-        <v>21.58632810961965</v>
+        <v>21.32661136103795</v>
       </c>
       <c r="U87" t="n">
         <v>42.27501741982778</v>
@@ -10162,10 +10182,10 @@
         <v>44.18604651162791</v>
       </c>
       <c r="AG87" t="n">
-        <v>45.34425157808585</v>
+        <v>45.99400614335055</v>
       </c>
       <c r="AH87" t="n">
-        <v>-1.158205066457946</v>
+        <v>-1.807959631722639</v>
       </c>
       <c r="AI87" t="n">
         <v>30.43330983917051</v>
@@ -10184,10 +10204,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C88" t="n">
-        <v>1.068124190251178</v>
+        <v>1.098373816722469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10215,7 +10235,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>19.66366171995766</v>
+        <v>23.05257576408624</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10229,19 +10249,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R88" t="n">
-        <v>71.42857142857143</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="S88" t="n">
-        <v>46.71491829167712</v>
+        <v>46.57170396883187</v>
       </c>
       <c r="T88" t="n">
-        <v>24.71365313689431</v>
+        <v>24.01653132528578</v>
       </c>
       <c r="U88" t="n">
-        <v>54.94506513681738</v>
+        <v>53.83109020528557</v>
       </c>
       <c r="V88" t="n">
         <v>78</v>
@@ -10253,22 +10273,22 @@
         <v>27.20319322085054</v>
       </c>
       <c r="Y88" t="n">
-        <v>5.927155844116849</v>
+        <v>3.262982124637392</v>
       </c>
       <c r="Z88" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AA88" t="n">
-        <v>31.57894736842105</v>
+        <v>50</v>
       </c>
       <c r="AB88" t="n">
-        <v>19.17942262629681</v>
+        <v>14.43839299220867</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.07743377649180871</v>
+        <v>2.829338691098615</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10299,10 +10319,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C89" t="n">
-        <v>2.142506825248281</v>
+        <v>2.177971981273326</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10321,7 +10341,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -10334,16 +10354,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>16.37744681181905</v>
+        <v>18.30385575499671</v>
       </c>
       <c r="L89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>75</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N89" t="n">
-        <v>16.37411641808841</v>
+        <v>12.23354717638958</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10376,22 +10396,22 @@
         <v>20.95675253601343</v>
       </c>
       <c r="Y89" t="n">
-        <v>3.785903331714313</v>
+        <v>2.193260587272172</v>
       </c>
       <c r="Z89" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AA89" t="n">
-        <v>30.76923076923077</v>
+        <v>41.37931034482759</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.84529800109621</v>
+        <v>13.229850692174</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>6.458613533222513</v>
+        <v>7.981801110641983</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10422,10 +10442,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C90" t="n">
-        <v>2.74541304425974</v>
+        <v>2.822601641671599</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10442,7 +10462,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>5</v>
       </c>
@@ -10453,16 +10477,16 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>8.224865687257644</v>
+        <v>11.26765941367078</v>
       </c>
       <c r="L90" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M90" t="n">
-        <v>61.11111111111111</v>
+        <v>81.25</v>
       </c>
       <c r="N90" t="n">
-        <v>16.04685375495613</v>
+        <v>14.13725471419189</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
@@ -10495,16 +10519,16 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>9.726085383466931</v>
+        <v>7.187991209733235</v>
       </c>
       <c r="Z90" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA90" t="n">
-        <v>52.94117647058823</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB90" t="n">
-        <v>15.5455038079218</v>
+        <v>17.38448689559154</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10541,10 +10565,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2276022379383598</v>
+        <v>0.229062557490884</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10572,22 +10596,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>1.665598089168463</v>
+        <v>2.317895105460921</v>
       </c>
       <c r="L91" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M91" t="n">
-        <v>63.88888888888889</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N91" t="n">
-        <v>13.84026224612131</v>
+        <v>15.29890820780455</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>1.312540265253914</v>
+        <v>0.6666525868578743</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10650,10 +10674,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C92" t="n">
-        <v>1.119235617003645</v>
+        <v>1.122364839272299</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10670,7 +10694,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H92" t="n">
         <v>5</v>
       </c>
@@ -10681,58 +10709,58 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>6.224294772525929</v>
+        <v>6.52128266642813</v>
       </c>
       <c r="L92" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M92" t="n">
-        <v>68.96551724137932</v>
+        <v>75</v>
       </c>
       <c r="N92" t="n">
-        <v>12.9746135125069</v>
+        <v>13.03072625361268</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>1.671656405228816</v>
+        <v>1.388189567903053</v>
       </c>
       <c r="Q92" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R92" t="n">
-        <v>66.07142857142857</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="S92" t="n">
-        <v>25.48654988587356</v>
+        <v>25.52187357208631</v>
       </c>
       <c r="T92" t="n">
-        <v>40.58487868555501</v>
+        <v>41.14479309458036</v>
       </c>
       <c r="U92" t="n">
-        <v>52.99945300706023</v>
+        <v>53.72251158005143</v>
       </c>
       <c r="V92" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W92" t="n">
-        <v>66.66666666666667</v>
+        <v>67.14285714285714</v>
       </c>
       <c r="X92" t="n">
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.36143285329236</v>
+        <v>7.102428705418895</v>
       </c>
       <c r="Z92" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA92" t="n">
-        <v>50</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.55050149056757</v>
+        <v>11.51648162671794</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10747,10 +10775,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.33109501527519</v>
+        <v>40.36481220585512</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.61008145531304</v>
+        <v>12.57636426473311</v>
       </c>
       <c r="AI92" t="n">
         <v>39.52330421009647</v>
@@ -10769,7 +10797,7 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C93" t="n">
         <v>0.04214083615073946</v>
@@ -10878,10 +10906,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C94" t="n">
-        <v>8.198687510502156</v>
+        <v>8.235195660994213</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10923,10 +10951,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S94" t="n">
-        <v>39.62554850950509</v>
+        <v>39.29728034587108</v>
       </c>
       <c r="T94" t="n">
-        <v>21.35006124659247</v>
+        <v>21.67832941022648</v>
       </c>
       <c r="U94" t="n">
         <v>45.72685693412379</v>
@@ -10938,25 +10966,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>52.92815171085716</v>
+        <v>50.4132727790992</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.420856610800748</v>
+        <v>1.986343885785236</v>
       </c>
       <c r="Z94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA94" t="n">
-        <v>50</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB94" t="n">
-        <v>14.90686389976875</v>
+        <v>12.36506894044984</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.66793893129771</v>
+        <v>4.09499683343888</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10987,10 +11015,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1443636596146817</v>
+        <v>0.1441550368136559</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11022,7 +11050,7 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>8.216538486888014</v>
+        <v>8.060152610853066</v>
       </c>
       <c r="L95" t="n">
         <v>6</v>
@@ -11064,7 +11092,7 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>3.351952165194538</v>
+        <v>3.491620184880317</v>
       </c>
       <c r="Z95" t="n">
         <v>29</v>
@@ -11073,13 +11101,13 @@
         <v>44.82758620689656</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.28657002552313</v>
+        <v>10.24624973377114</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.739887555030196</v>
+        <v>2.599131619373329</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11110,7 +11138,7 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C96" t="n">
         <v>0.1324724296992874</v>
@@ -11219,10 +11247,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C97" t="n">
-        <v>1.939104272506815</v>
+        <v>1.946406029862209</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11250,16 +11278,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>8.492539470822557</v>
+        <v>8.901071497345448</v>
       </c>
       <c r="L97" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M97" t="n">
-        <v>57.14285714285715</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N97" t="n">
-        <v>14.49932491657701</v>
+        <v>12.42715529904951</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11274,10 +11302,10 @@
         <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>35.51462284392235</v>
+        <v>35.58075187618041</v>
       </c>
       <c r="T97" t="n">
-        <v>20.48537715607765</v>
+        <v>20.41924812381959</v>
       </c>
       <c r="U97" t="n">
         <v>42.30602802165686</v>
@@ -11292,22 +11320,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>5.298017828772617</v>
+        <v>4.941414574015646</v>
       </c>
       <c r="Z97" t="n">
         <v>36</v>
       </c>
       <c r="AA97" t="n">
-        <v>44.44444444444444</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.54824769362695</v>
+        <v>11.93556647903864</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.7412539369642368</v>
+        <v>1.113613695428495</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11316,10 +11344,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG97" t="n">
-        <v>54.68527829062151</v>
+        <v>54.59500617747585</v>
       </c>
       <c r="AH97" t="n">
-        <v>-2.053699343253093</v>
+        <v>-1.963427230107435</v>
       </c>
       <c r="AI97" t="n">
         <v>37.25897138449667</v>
@@ -11338,10 +11366,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6262712540373307</v>
+        <v>0.6279401963908808</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11369,22 +11397,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>4.575687907251802</v>
+        <v>4.854370336909741</v>
       </c>
       <c r="L98" t="n">
         <v>42</v>
       </c>
       <c r="M98" t="n">
-        <v>45.23809523809524</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="N98" t="n">
-        <v>14.14358958021403</v>
+        <v>16.09032931635308</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>5.186972422843672</v>
+        <v>4.907406001825909</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11411,22 +11439,22 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>4.98900055867818</v>
+        <v>4.735806946487742</v>
       </c>
       <c r="Z98" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA98" t="n">
-        <v>35.71428571428572</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.99119720452292</v>
+        <v>11.93674418801786</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>3.169106165630209</v>
+        <v>3.42646376239043</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11457,10 +11485,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4593768517879229</v>
+        <v>0.4627147367036411</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11488,16 +11516,16 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>4.292262168573968</v>
+        <v>5.050061712377096</v>
       </c>
       <c r="L99" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M99" t="n">
-        <v>68.18181818181819</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N99" t="n">
-        <v>12.91686969642192</v>
+        <v>13.00352492424371</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11544,10 +11572,10 @@
         <v>52.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>37.49049274398539</v>
+        <v>37.81560513159778</v>
       </c>
       <c r="AH99" t="n">
-        <v>15.00950725601461</v>
+        <v>14.68439486840222</v>
       </c>
       <c r="AI99" t="n">
         <v>37.49736210669248</v>
@@ -11566,10 +11594,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C100" t="n">
-        <v>326.6751343313485</v>
+        <v>327.8999298109945</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11594,19 +11622,19 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>17.72888230032435</v>
+        <v>15.65236426997335</v>
       </c>
       <c r="K100" t="n">
-        <v>6.5873972089183</v>
+        <v>6.987022857059277</v>
       </c>
       <c r="L100" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M100" t="n">
-        <v>66.66666666666667</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N100" t="n">
-        <v>13.89849008366731</v>
+        <v>11.8908237696045</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11675,10 +11703,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C101" t="n">
-        <v>343.5867608785289</v>
+        <v>345.3470567686605</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11703,19 +11731,19 @@
         <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>12.13141269388449</v>
+        <v>11.19277381576541</v>
       </c>
       <c r="K101" t="n">
-        <v>8.803291040152295</v>
+        <v>9.360722256538656</v>
       </c>
       <c r="L101" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M101" t="n">
-        <v>50</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N101" t="n">
-        <v>8.242539018848863</v>
+        <v>8.00364326814563</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11745,25 +11773,25 @@
         <v>53.84615384615385</v>
       </c>
       <c r="X101" t="n">
-        <v>10.77566750487711</v>
+        <v>10.7755255729769</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.780514177121051</v>
+        <v>1.277180414284018</v>
       </c>
       <c r="Z101" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA101" t="n">
-        <v>39.02439024390244</v>
+        <v>35</v>
       </c>
       <c r="AB101" t="n">
-        <v>13.852550552561</v>
+        <v>14.15145124560824</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.295976289763958</v>
+        <v>4.78391886043672</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11794,10 +11822,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C102" t="n">
-        <v>415.9467300678613</v>
+        <v>418.5943044012016</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11854,10 +11882,10 @@
         <v>47.22222222222222</v>
       </c>
       <c r="X102" t="n">
-        <v>10.29246150171719</v>
+        <v>10.29256843357016</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.026954762988008</v>
+        <v>0.3970704336589859</v>
       </c>
       <c r="Z102" t="n">
         <v>37</v>
@@ -11866,13 +11894,13 @@
         <v>32.43243243243244</v>
       </c>
       <c r="AB102" t="n">
-        <v>11.3058204132745</v>
+        <v>11.63419257229469</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.014269973706163</v>
+        <v>4.621279300098513</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11903,10 +11931,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7255733883279039</v>
+        <v>0.7280768617315957</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11931,10 +11959,10 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>16.73842567092216</v>
+        <v>16.13876216849247</v>
       </c>
       <c r="K103" t="n">
-        <v>11.59198446071477</v>
+        <v>11.97701452060491</v>
       </c>
       <c r="L103" t="n">
         <v>18</v>
@@ -11943,7 +11971,7 @@
         <v>72.22222222222223</v>
       </c>
       <c r="N103" t="n">
-        <v>14.05486902977729</v>
+        <v>12.59597849727541</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -11976,37 +12004,37 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>3.904791618338577</v>
+        <v>3.57323067319405</v>
       </c>
       <c r="Z103" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA103" t="n">
-        <v>40.47619047619047</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.14953663953723</v>
+        <v>10.15205565550442</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>4.26161559002659</v>
+        <v>4.590809541490404</v>
       </c>
       <c r="AE103" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AF103" t="n">
-        <v>60</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="AG103" t="n">
-        <v>37.06551054740267</v>
+        <v>37.40824031607043</v>
       </c>
       <c r="AH103" t="n">
-        <v>22.93448945259733</v>
+        <v>24.35646556628251</v>
       </c>
       <c r="AI103" t="n">
-        <v>43.5727090128925</v>
+        <v>45.0410173444307</v>
       </c>
       <c r="AJ103" t="n">
         <v>61</v>
@@ -12022,10 +12050,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04714766842683969</v>
+        <v>0.0475649040152272</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12053,22 +12081,22 @@
         <v>21.43553010850433</v>
       </c>
       <c r="K104" t="n">
-        <v>1.34529012246376</v>
+        <v>2.242150204106275</v>
       </c>
       <c r="L104" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M104" t="n">
-        <v>55.81395348837209</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N104" t="n">
-        <v>13.03248067291818</v>
+        <v>10.62247356697882</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.619470400971124</v>
+        <v>1.719300496306597</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12103,19 +12131,19 @@
       </c>
       <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF104" t="n">
-        <v>62.7906976744186</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="AG104" t="n">
-        <v>40.12353702583854</v>
+        <v>40.74419917771555</v>
       </c>
       <c r="AH104" t="n">
-        <v>22.66716064858006</v>
+        <v>23.54151510799874</v>
       </c>
       <c r="AI104" t="n">
-        <v>47.85980915968847</v>
+        <v>49.16636571945582</v>
       </c>
       <c r="AJ104" t="n">
         <v>78</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46255</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4005465812535469</v>
+        <v>0.4036758433682391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>2.169876663837278</v>
+        <v>2.968076771565942</v>
       </c>
       <c r="L2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M2" t="n">
-        <v>43.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>12.33896209001021</v>
+        <v>11.12032742459378</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>7.663827726763017</v>
+        <v>6.829226541770161</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -788,7 +788,7 @@
         <v>46255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6513053903836715</v>
+        <v>0.655477766503493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,22 +816,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.893133438545047</v>
+        <v>2.545878653017053</v>
       </c>
       <c r="L3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>53.57142857142857</v>
+        <v>47.16981132075472</v>
       </c>
       <c r="N3" t="n">
-        <v>14.67817668540686</v>
+        <v>14.9197350734803</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>7.956244241271149</v>
+        <v>7.269059902646458</v>
       </c>
       <c r="Q3" t="n">
         <v>37</v>
@@ -897,7 +897,7 @@
         <v>46255</v>
       </c>
       <c r="C4" t="n">
-        <v>1.446765817580999</v>
+        <v>1.465541469752612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,7 +914,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
@@ -925,16 +929,16 @@
         <v>14.71888288970985</v>
       </c>
       <c r="K4" t="n">
-        <v>12.01858762291574</v>
+        <v>13.47232810558749</v>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>56.25</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N4" t="n">
-        <v>11.07841973430984</v>
+        <v>14.04969835439648</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -967,22 +971,22 @@
         <v>15.89522479111605</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.344949867595803</v>
+        <v>2.090592334494767</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="AA4" t="n">
-        <v>46</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.6025137220631</v>
+        <v>13.06208636967171</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>6.885362040873899</v>
+        <v>8.078291814946626</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1016,7 +1020,7 @@
         <v>46255</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2359469699420563</v>
+        <v>0.2369900441011469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,22 +1048,22 @@
         <v>15.99376685518751</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5333370666666726</v>
+        <v>0.9777747555555605</v>
       </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M5" t="n">
-        <v>53.19148936170212</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="N5" t="n">
-        <v>15.00246203783031</v>
+        <v>14.58080922442367</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.453577097214632</v>
+        <v>2.00264389796645</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1125,7 +1129,7 @@
         <v>46255</v>
       </c>
       <c r="C6" t="n">
-        <v>1.715883073126723</v>
+        <v>1.731529423337606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1157,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8496874055314</v>
+        <v>5.805763582481549</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1191,16 +1195,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.365218122378802</v>
+        <v>5.511405521670998</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
         <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.42568615537318</v>
+        <v>11.90569606962703</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1240,7 +1244,7 @@
         <v>46255</v>
       </c>
       <c r="C7" t="n">
-        <v>2.26141918239803</v>
+        <v>2.271850082538617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,22 +1304,22 @@
         <v>14.22876300591287</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.324802637328784</v>
+        <v>3.883496382659635</v>
       </c>
       <c r="Z7" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AA7" t="n">
-        <v>40.54054054054054</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.53950464232632</v>
+        <v>10.5921569011977</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.7057182857034383</v>
+        <v>1.161614889556739</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1349,7 +1353,7 @@
         <v>46255</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3773899702157434</v>
+        <v>0.4017982782136632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,25 +1410,23 @@
         <v>33.33333333333334</v>
       </c>
       <c r="X8" t="n">
-        <v>24.89870225327257</v>
+        <v>28.48050864786196</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.929897892426515</v>
+        <v>0.567891611924165</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>15.8588210325697</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.2365960046717</v>
+        <v>7.474555763284119</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1458,11 +1460,11 @@
         <v>46255</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5912234230977971</v>
+        <v>0.5987336839247186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1472,7 +1474,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1518,22 +1520,22 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.935535570549055</v>
+        <v>3.727939769462729</v>
       </c>
       <c r="Z9" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>40.54054054054054</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.10261347953007</v>
+        <v>11.80706426686921</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>0.2825952097480711</v>
       </c>
       <c r="AE9" t="n">
         <v>33</v>
@@ -1567,7 +1569,7 @@
         <v>46255</v>
       </c>
       <c r="C10" t="n">
-        <v>1.932845827969508</v>
+        <v>1.946406029862209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,22 +1597,22 @@
         <v>10.51321892894885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2705627660826826</v>
+        <v>0.9740276029192474</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="N10" t="n">
-        <v>10.2480637444662</v>
+        <v>9.700270874208478</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.713977338776188</v>
+        <v>4.977490267938411</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1676,7 +1678,7 @@
         <v>46255</v>
       </c>
       <c r="C11" t="n">
-        <v>8.38644371303274</v>
+        <v>8.422951863524798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1738,7 @@
         <v>22.18106016526054</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.651376146788996</v>
+        <v>1.223241590214075</v>
       </c>
       <c r="Z11" t="n">
         <v>40</v>
@@ -1745,13 +1747,13 @@
         <v>45</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.61617163727046</v>
+        <v>12.94821475243904</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.3544776119402959</v>
+        <v>0.7863777089783253</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1785,7 +1787,7 @@
         <v>46255</v>
       </c>
       <c r="C12" t="n">
-        <v>6.926117693350422</v>
+        <v>6.946979493631598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,22 +1815,22 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>5.480540111199361</v>
+        <v>5.798252581413821</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M12" t="n">
-        <v>61.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="N12" t="n">
-        <v>20.96723808634281</v>
+        <v>20.93539787729433</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0.492469879518076</v>
+        <v>0.1906906906906869</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1855,7 +1857,7 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.295318758673885</v>
+        <v>6.013075742886764</v>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
@@ -1864,7 +1866,7 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.25142359009066</v>
+        <v>8.917895439582416</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1904,7 +1906,7 @@
         <v>46255</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2376159122956064</v>
+        <v>0.2363641955167797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1934,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>12.54941169767145</v>
+        <v>11.95652216553531</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1968,22 +1970,22 @@
         <v>16.60079365870428</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.474574944053466</v>
+        <v>3.983053071459319</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.38665977363141</v>
+        <v>8.977284347248103</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.760317348682343</v>
+        <v>6.266546813885587</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2007,7 +2009,7 @@
         <v>46255</v>
       </c>
       <c r="C14" t="n">
-        <v>8.589846265774206</v>
+        <v>8.657647116688027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,22 +2069,22 @@
         <v>12.93345142071747</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.905896366885051</v>
+        <v>1.131625967838013</v>
       </c>
       <c r="Z14" t="n">
         <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>46.80851063829788</v>
+        <v>48.93617021276596</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.63796621409251</v>
+        <v>12.09559709514738</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0959319975713413</v>
+        <v>0.8783132530120308</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2116,7 +2118,7 @@
         <v>46255</v>
       </c>
       <c r="C15" t="n">
-        <v>14.61369109696377</v>
+        <v>14.13386969049672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,22 +2178,22 @@
         <v>38.77434577704333</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.8492569002123251</v>
+        <v>4.104741684359514</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB15" t="n">
-        <v>13.39973570565697</v>
+        <v>9.389895908407604</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.229122055674511</v>
+        <v>6.147601476014763</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2225,7 +2227,7 @@
         <v>46255</v>
       </c>
       <c r="C16" t="n">
-        <v>35.69454028109208</v>
+        <v>35.5067840785615</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,22 +2255,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>2.507506556918959</v>
+        <v>1.968308684907116</v>
       </c>
       <c r="L16" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="M16" t="n">
-        <v>66.66666666666667</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N16" t="n">
-        <v>17.85946578771896</v>
+        <v>18.18642428626609</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.309214412430109</v>
+        <v>7.876654441638009</v>
       </c>
       <c r="Q16" t="n">
         <v>27</v>
@@ -2295,16 +2297,16 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.79656861964465</v>
+        <v>12.26052588581834</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>55.55555555555556</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.40563990076058</v>
+        <v>12.29477211608372</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
@@ -2344,7 +2346,7 @@
         <v>46255</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7172287159889561</v>
+        <v>0.7159769791828012</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,22 +2374,22 @@
         <v>14.75338697646304</v>
       </c>
       <c r="K17" t="n">
-        <v>3.243248812758837</v>
+        <v>3.063064484322209</v>
       </c>
       <c r="L17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
-        <v>64.51612903225806</v>
+        <v>64.0625</v>
       </c>
       <c r="N17" t="n">
-        <v>16.68556143364886</v>
+        <v>15.94741868230261</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.607324199830232</v>
+        <v>4.790208345132996</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2453,7 +2455,7 @@
         <v>46255</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09971940972499919</v>
+        <v>0.09867631574719835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,22 +2483,22 @@
         <v>20.56707245057805</v>
       </c>
       <c r="K18" t="n">
-        <v>2.842796578482676</v>
+        <v>1.767031067364555</v>
       </c>
       <c r="L18" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M18" t="n">
-        <v>58.33333333333334</v>
+        <v>65.85365853658537</v>
       </c>
       <c r="N18" t="n">
-        <v>15.97066094670105</v>
+        <v>15.22851380311469</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.959362891357634</v>
+        <v>8.090015839398568</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2562,7 +2564,7 @@
         <v>46255</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02524277917469493</v>
+        <v>0.02545139696888869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,22 +2592,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>2.425147283288864</v>
+        <v>3.271635229340042</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N19" t="n">
-        <v>19.31962096524373</v>
+        <v>15.69071474462519</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.395500926896892</v>
+        <v>6.51521083763027</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2671,7 +2673,7 @@
         <v>46255</v>
       </c>
       <c r="C20" t="n">
-        <v>1.707538321095699</v>
+        <v>1.736744873407899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,16 +2701,16 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>2.502154696711001</v>
+        <v>4.255400586584646</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>48.64864864864865</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N20" t="n">
-        <v>12.53782064564077</v>
+        <v>11.32247634963579</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -2780,7 +2782,7 @@
         <v>46255</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9442050456782</v>
+        <v>0.959225567332043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,22 +2810,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>1.636559070477683</v>
+        <v>3.253405054650171</v>
       </c>
       <c r="L21" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M21" t="n">
-        <v>54.09836065573771</v>
+        <v>52.72727272727273</v>
       </c>
       <c r="N21" t="n">
-        <v>18.6173419760409</v>
+        <v>16.30155361855141</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.260976353114955</v>
+        <v>4.597034783344478</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2889,11 +2891,11 @@
         <v>46255</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3483920805506069</v>
+        <v>0.3442197046394035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2903,7 +2905,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2949,22 +2951,22 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.050459526770057</v>
+        <v>6.187584041266003</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>43.75</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.21366565444535</v>
+        <v>10.07750348112833</v>
       </c>
       <c r="AC22" t="n">
         <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.00004746573541</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -2990,7 +2992,7 @@
         <v>46255</v>
       </c>
       <c r="C23" t="n">
-        <v>0.779814116832484</v>
+        <v>0.7760589863147143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,22 +3020,22 @@
         <v>24.33755492423044</v>
       </c>
       <c r="K23" t="n">
-        <v>1.465800536919915</v>
+        <v>0.9772003488984771</v>
       </c>
       <c r="L23" t="n">
         <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>57.14285714285715</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N23" t="n">
-        <v>22.62984058851431</v>
+        <v>20.08190631494157</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.483143526566002</v>
+        <v>3.983869266727402</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3060,7 +3062,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>23.22849439806307</v>
+        <v>23.5981812469649</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3105,7 +3107,7 @@
         <v>46255</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1783683963677966</v>
+        <v>0.1785770191688224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3135,7 @@
         <v>23.5093122581746</v>
       </c>
       <c r="K24" t="n">
-        <v>5.555552949245679</v>
+        <v>5.679012573083342</v>
       </c>
       <c r="L24" t="n">
         <v>9</v>
@@ -3142,13 +3144,13 @@
         <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>12.25105140230857</v>
+        <v>12.17683750688129</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.21052888888882</v>
+        <v>4.088784822746572</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3214,7 +3216,7 @@
         <v>46255</v>
       </c>
       <c r="C25" t="n">
-        <v>3.577798748221679</v>
+        <v>3.559023255225602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,22 +3244,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>2.32696524943623</v>
+        <v>1.789976068503263</v>
       </c>
       <c r="L25" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M25" t="n">
-        <v>57.14285714285715</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N25" t="n">
-        <v>16.22416845357686</v>
+        <v>16.98566670045244</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>5.544027165014587</v>
+        <v>6.100820700967136</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3323,7 +3325,7 @@
         <v>46255</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4456080667316169</v>
+        <v>0.44602527248763</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3422,7 +3424,7 @@
         <v>46255</v>
       </c>
       <c r="C27" t="n">
-        <v>43.60116258765778</v>
+        <v>44.41477279862364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3452,7 @@
         <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>32.27224397814068</v>
+        <v>34.7404820236658</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3475,25 +3477,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>33.98102416350424</v>
+        <v>35.94295696892162</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.275389702409069</v>
+        <v>0.8845437616387453</v>
       </c>
       <c r="Z27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>25.80591578680818</v>
+        <v>20.54491939468352</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.772727272727283</v>
+        <v>4.152184124001868</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3517,7 +3519,7 @@
         <v>46255</v>
       </c>
       <c r="C28" t="n">
-        <v>1.593841573400398</v>
+        <v>1.590712271439668</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,22 +3579,22 @@
         <v>18.63435792130579</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.647234255660625</v>
+        <v>3.836410459743633</v>
       </c>
       <c r="Z28" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>45.94594594594594</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.88691949635073</v>
+        <v>11.57972711841415</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.441824815472515</v>
+        <v>2.249905136237285</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3626,7 +3628,7 @@
         <v>46255</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4084740478364814</v>
+        <v>0.4118119327521996</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3643,11 +3645,7 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3658,16 +3656,16 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>12.99714649219166</v>
+        <v>13.92051352809809</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>80</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N29" t="n">
-        <v>15.83912322416238</v>
+        <v>18.00706743337966</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3700,7 +3698,7 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>10.83239932776978</v>
+        <v>10.10375771435262</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -3745,7 +3743,7 @@
         <v>46255</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4051361631293814</v>
+        <v>0.405553408522815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,16 +3771,16 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>10.67221404858223</v>
+        <v>10.78619417599467</v>
       </c>
       <c r="L30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M30" t="n">
-        <v>64.28571428571429</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N30" t="n">
-        <v>14.83914496442762</v>
+        <v>15.83763170086855</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3815,7 +3813,7 @@
         <v>11.81199400890234</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.019371821800574</v>
+        <v>0.917432733402479</v>
       </c>
       <c r="Z30" t="n">
         <v>59</v>
@@ -3830,7 +3828,7 @@
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>9.073116976011896</v>
+        <v>9.166665254200989</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3864,7 +3862,7 @@
         <v>46255</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1860872601770337</v>
+        <v>0.1854614115926665</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,22 +3890,22 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>6.866702257137414</v>
+        <v>6.50728821525195</v>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
-        <v>10.85546246304441</v>
+        <v>5.988524106612392</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>2.931968215247638</v>
+        <v>3.279317165309159</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3973,7 +3971,7 @@
         <v>46255</v>
       </c>
       <c r="C32" t="n">
-        <v>2.284367130788769</v>
+        <v>2.292711882819793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,16 +3999,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>4.816745945243417</v>
+        <v>5.199639632437192</v>
       </c>
       <c r="L32" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M32" t="n">
-        <v>53.48837209302326</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="N32" t="n">
-        <v>10.55367051125727</v>
+        <v>11.04464267885272</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4043,22 +4041,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.14008637438125</v>
+        <v>6.800870780537283</v>
       </c>
       <c r="Z32" t="n">
         <v>18</v>
       </c>
       <c r="AA32" t="n">
-        <v>44.44444444444444</v>
+        <v>50</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.33240290501161</v>
+        <v>9.612847301691742</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.9260331956431056</v>
+        <v>1.286631355362811</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4092,7 +4090,7 @@
         <v>46255</v>
       </c>
       <c r="C33" t="n">
-        <v>1.734658725298336</v>
+        <v>1.743003477120743</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4120,16 +4118,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.854623524281033</v>
+        <v>6.363847932334288</v>
       </c>
       <c r="L33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M33" t="n">
-        <v>65.51724137931035</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N33" t="n">
-        <v>11.31004799319451</v>
+        <v>10.64617202775737</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4201,7 +4199,7 @@
         <v>46255</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8027620652232232</v>
+        <v>0.7969207865958903</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4218,11 +4216,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>5</v>
       </c>
@@ -4233,16 +4227,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>5.772754065424679</v>
+        <v>5.003101195112825</v>
       </c>
       <c r="L34" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M34" t="n">
-        <v>78.94736842105263</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N34" t="n">
-        <v>10.48324386958539</v>
+        <v>9.716444525284787</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4314,7 +4308,7 @@
         <v>46255</v>
       </c>
       <c r="C35" t="n">
-        <v>1.966224676500835</v>
+        <v>1.951621479932503</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4327,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4346,16 +4340,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>10.84640913390267</v>
+        <v>10.02315026586889</v>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>80</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N35" t="n">
-        <v>11.11171484750929</v>
+        <v>10.73178574240798</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4388,16 +4382,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>5.381194838453796</v>
+        <v>6.083930912997304</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>38.46153846153846</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB35" t="n">
-        <v>12.54392409413347</v>
+        <v>15.05640991881998</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4437,7 +4431,7 @@
         <v>46255</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08073516479335296</v>
+        <v>0.0809437873857608</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,16 +4459,16 @@
         <v>14.25367779956082</v>
       </c>
       <c r="K36" t="n">
-        <v>3.4759326110269</v>
+        <v>3.743318171809307</v>
       </c>
       <c r="L36" t="n">
         <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>58.62068965517241</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N36" t="n">
-        <v>19.93102979683517</v>
+        <v>20.88828552891385</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4546,7 +4540,7 @@
         <v>46255</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06571467297188434</v>
+        <v>0.06613190856027185</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4574,22 +4568,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>6.972392533717642</v>
+        <v>7.651581626831172</v>
       </c>
       <c r="L37" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M37" t="n">
-        <v>58.33333333333334</v>
+        <v>62.5</v>
       </c>
       <c r="N37" t="n">
-        <v>18.81710672338293</v>
+        <v>17.11565236973266</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9606286649692874</v>
+        <v>0.3236537428466413</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4616,16 +4610,16 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.60758112253119</v>
+        <v>4.001915595821847</v>
       </c>
       <c r="Z37" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AA37" t="n">
-        <v>56.14035087719298</v>
+        <v>56.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.38451986162349</v>
+        <v>13.09277213880228</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
@@ -4665,7 +4659,7 @@
         <v>46255</v>
       </c>
       <c r="C38" t="n">
-        <v>1.667900868851528</v>
+        <v>1.682504224595396</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,22 +4687,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>5.274183422766465</v>
+        <v>6.195914671834357</v>
       </c>
       <c r="L38" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>53.65853658536585</v>
+        <v>48.71794871794872</v>
       </c>
       <c r="N38" t="n">
-        <v>10.53259634513365</v>
+        <v>10.54326189753282</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>4.48905555339747</v>
+        <v>3.582139049247801</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4774,7 +4768,7 @@
         <v>46255</v>
       </c>
       <c r="C39" t="n">
-        <v>2.701603136412288</v>
+        <v>2.722464936693464</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4796,7 @@
         <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>6.941609330798859</v>
+        <v>7.767413263855216</v>
       </c>
       <c r="L39" t="n">
         <v>21</v>
@@ -4811,7 +4805,7 @@
         <v>61.90476190476191</v>
       </c>
       <c r="N39" t="n">
-        <v>15.46006988334808</v>
+        <v>14.68366168246508</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4844,22 +4838,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.995300975980597</v>
+        <v>2.246229941046085</v>
       </c>
       <c r="Z39" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA39" t="n">
-        <v>38.63636363636363</v>
+        <v>36</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.78517180818355</v>
+        <v>11.65613829774405</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.097477807003357</v>
+        <v>3.840025869784947</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4893,16 +4887,16 @@
         <v>46255</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2536794882898297</v>
+        <v>0.2595207867358729</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4917,27 +4911,17 @@
       <c r="I40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="n">
-        <v>11.02041126530612</v>
-      </c>
-      <c r="K40" t="n">
-        <v>11.55963554061115</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>15</v>
-      </c>
-      <c r="M40" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="N40" t="n">
-        <v>13.87958643511992</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
         <v>27</v>
       </c>
@@ -4960,25 +4944,25 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>39.56976926502232</v>
+        <v>44.24108228242589</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.7346951020408166</v>
+        <v>1.737758867351025</v>
       </c>
       <c r="Z40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="n">
-        <v>30</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB40" t="n">
-        <v>14.591141794334</v>
+        <v>18.46032019010953</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.296873819451575</v>
+        <v>3.319933572698719</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -5012,7 +4996,7 @@
         <v>46255</v>
       </c>
       <c r="C41" t="n">
-        <v>1.828536826563628</v>
+        <v>1.821235228175153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5040,7 +5024,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>20.84002159034057</v>
+        <v>20.35749080720863</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -5075,25 +5059,25 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X41" t="n">
-        <v>21.11575044516931</v>
+        <v>22.08082251686328</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.2276573061845921</v>
+        <v>1.411631797792479</v>
       </c>
       <c r="Z41" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA41" t="n">
-        <v>48</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.59836169912863</v>
+        <v>15.95457160414137</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.778668535751705</v>
+        <v>1.611111159634715</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5127,7 +5111,7 @@
         <v>46255</v>
       </c>
       <c r="C42" t="n">
-        <v>3.563195551653346</v>
+        <v>3.784330443748339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5185,18 +5169,22 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>7.866218787608337</v>
+        <v>2.148319370818752</v>
       </c>
       <c r="Z42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>9.034478235705823</v>
+      </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.315959666816192</v>
+        <v>8.024063131767733</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5228,7 +5216,7 @@
         <v>46255</v>
       </c>
       <c r="C43" t="n">
-        <v>6.795731441593072</v>
+        <v>6.712284240468368</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5235,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5257,25 +5245,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>12.62186296009862</v>
+        <v>13.8335782657367</v>
       </c>
       <c r="K43" t="n">
-        <v>0.3852080123266655</v>
+        <v>0.5468750000000133</v>
       </c>
       <c r="L43" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M43" t="n">
-        <v>83.78378378378379</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N43" t="n">
-        <v>14.86607000032023</v>
+        <v>15.44808004783934</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.600920951650033</v>
+        <v>3.434343434343434</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5302,17 +5290,13 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>12.28527537519915</v>
+        <v>13.36235564687744</v>
       </c>
       <c r="Z43" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>9.416359483443298</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>2</v>
       </c>
@@ -5351,7 +5335,7 @@
         <v>46255</v>
       </c>
       <c r="C44" t="n">
-        <v>4.645922858989397</v>
+        <v>4.612544169424988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5370,7 +5354,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5383,22 +5367,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>3.629596682831715</v>
+        <v>2.885068578868855</v>
       </c>
       <c r="L44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M44" t="n">
-        <v>75</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N44" t="n">
-        <v>18.72301468868908</v>
+        <v>17.10389424119687</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.147281781541158</v>
+        <v>6.915416901021976</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5456,7 +5440,7 @@
         <v>46255</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02315659852072333</v>
+        <v>0.02336521631491709</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5516,22 +5500,22 @@
         <v>17.77268946199939</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.631577216066461</v>
+        <v>1.754385103108635</v>
       </c>
       <c r="Z45" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AA45" t="n">
-        <v>52</v>
+        <v>44.64285714285715</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.29747688746683</v>
+        <v>12.99257466903162</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.432434167275377</v>
+        <v>3.303572276785727</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5565,7 +5549,7 @@
         <v>46255</v>
       </c>
       <c r="C46" t="n">
-        <v>9.815477032293293</v>
+        <v>9.935432383910056</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5625,22 +5609,22 @@
         <v>21.77676482446944</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.385892116182586</v>
+        <v>1.192946058091282</v>
       </c>
       <c r="Z46" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA46" t="n">
-        <v>36.11111111111111</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.58276405830406</v>
+        <v>11.76900945796669</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.6291179596174201</v>
+        <v>1.828871391076126</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5674,7 +5658,7 @@
         <v>46255</v>
       </c>
       <c r="C47" t="n">
-        <v>0.708049472962446</v>
+        <v>0.7143080766752896</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5702,22 +5686,22 @@
         <v>25.00555187915373</v>
       </c>
       <c r="K47" t="n">
-        <v>5.135216903669981</v>
+        <v>6.064530015239566</v>
       </c>
       <c r="L47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>14.74102519690106</v>
+        <v>14.59222377341274</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.627167983861558</v>
+        <v>3.71044870909718</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5783,7 +5767,7 @@
         <v>46255</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05903889312678397</v>
+        <v>0.05966474671798325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5811,22 +5795,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>2.53622935701534</v>
+        <v>3.62318515805502</v>
       </c>
       <c r="L48" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M48" t="n">
-        <v>49.18032786885246</v>
+        <v>56.36363636363637</v>
       </c>
       <c r="N48" t="n">
-        <v>14.10204973331093</v>
+        <v>15.03939012974418</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>7.279154587396586</v>
+        <v>6.153849480903828</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5892,7 +5876,7 @@
         <v>46255</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2591035611611496</v>
+        <v>0.2595207867358729</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5920,7 +5904,7 @@
         <v>17.31218360853012</v>
       </c>
       <c r="K49" t="n">
-        <v>4.260350554919001</v>
+        <v>4.428237420256531</v>
       </c>
       <c r="L49" t="n">
         <v>33</v>
@@ -5929,13 +5913,13 @@
         <v>60.60606060606061</v>
       </c>
       <c r="N49" t="n">
-        <v>19.09000360666725</v>
+        <v>19.18494824880819</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.7094254346395878</v>
+        <v>0.547517217438509</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -6001,7 +5985,7 @@
         <v>46255</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6825981306514741</v>
+        <v>0.6880221636767554</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6029,22 +6013,22 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>2.122347941555569</v>
+        <v>2.93382831775526</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>60</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N50" t="n">
-        <v>13.73988935945594</v>
+        <v>14.93524715750164</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.838629933889702</v>
+        <v>1.035783570541549</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6110,7 +6094,7 @@
         <v>46255</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1781597735667708</v>
+        <v>0.1779511507657449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6138,7 +6122,7 @@
         <v>21.20514974257153</v>
       </c>
       <c r="K51" t="n">
-        <v>2.644234112946209</v>
+        <v>2.52403903635241</v>
       </c>
       <c r="L51" t="n">
         <v>16</v>
@@ -6147,13 +6131,13 @@
         <v>56.25</v>
       </c>
       <c r="N51" t="n">
-        <v>13.46594877883989</v>
+        <v>13.4505860237715</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.320839790729944</v>
+        <v>1.43962428472435</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6180,7 +6164,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>19.12162943281972</v>
+        <v>19.21633696343861</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6225,7 +6209,7 @@
         <v>46255</v>
       </c>
       <c r="C52" t="n">
-        <v>4.552044757724106</v>
+        <v>4.562475657864694</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6282,25 +6266,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>16.1827388466574</v>
+        <v>16.65998098876651</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.4107755020276938</v>
+        <v>0.5909104772727103</v>
       </c>
       <c r="Z52" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA52" t="n">
-        <v>38.46153846153846</v>
+        <v>36.11111111111111</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.09096889729116</v>
+        <v>11.86472140311879</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.620527759132035</v>
+        <v>7.453130853827394</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6334,7 +6318,7 @@
         <v>46255</v>
       </c>
       <c r="C53" t="n">
-        <v>1.390439020658933</v>
+        <v>1.382094268627908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6366,7 +6350,7 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>3.093580746586566</v>
+        <v>2.474862230679986</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -6381,7 +6365,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4.75918987184456</v>
+        <v>5.391700607396221</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6562,7 +6546,7 @@
         <v>46255</v>
       </c>
       <c r="C55" t="n">
-        <v>0.942953388564122</v>
+        <v>0.9325224884235341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6622,16 +6606,16 @@
         <v>26.27862368424858</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.583618326909732</v>
+        <v>4.650171203590359</v>
       </c>
       <c r="Z55" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA55" t="n">
-        <v>46.875</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="AB55" t="n">
-        <v>11.98481311669229</v>
+        <v>12.36572635119501</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6671,7 +6655,7 @@
         <v>46255</v>
       </c>
       <c r="C56" t="n">
-        <v>1.318465793625289</v>
+        <v>1.313250343554996</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6720,10 +6704,10 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>68.26570504629608</v>
+        <v>73.71938423294128</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.07905018181817436</v>
+        <v>3.598778223946808</v>
       </c>
       <c r="Z56" t="n">
         <v>2</v>
@@ -6734,7 +6718,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>9.928798551489137</v>
+        <v>6.640187394018382</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6760,7 +6744,7 @@
         <v>46255</v>
       </c>
       <c r="C57" t="n">
-        <v>1.323681243695584</v>
+        <v>1.305948665683061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6788,22 +6772,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>4.847200544864738</v>
+        <v>3.442624351078338</v>
       </c>
       <c r="L57" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M57" t="n">
-        <v>71.875</v>
+        <v>70</v>
       </c>
       <c r="N57" t="n">
-        <v>20.66881376754441</v>
+        <v>18.19765533731722</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>4.914579910915551</v>
+        <v>6.339142776063289</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6830,10 +6814,10 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>18.39431979178769</v>
+        <v>19.48754302619493</v>
       </c>
       <c r="Z57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
@@ -6875,7 +6859,7 @@
         <v>46255</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7481041708086684</v>
+        <v>0.7330836491548254</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6892,11 +6876,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6907,16 +6887,16 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>12.70649116407139</v>
+        <v>10.44355726112491</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N58" t="n">
-        <v>15.40033847307047</v>
+        <v>13.02241985913761</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6949,22 +6929,22 @@
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.5027693052289228</v>
+        <v>2.500486155988801</v>
       </c>
       <c r="Z58" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="AA58" t="n">
-        <v>31.11111111111111</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB58" t="n">
-        <v>12.67099450286217</v>
+        <v>14.37975093818692</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>5.525008742841298</v>
+        <v>3.589262865053922</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6998,7 +6978,7 @@
         <v>46255</v>
       </c>
       <c r="C59" t="n">
-        <v>0.790245016973072</v>
+        <v>0.79483455879425</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7026,22 +7006,22 @@
         <v>11.17103304657197</v>
       </c>
       <c r="K59" t="n">
-        <v>1.01333618666668</v>
+        <v>1.599995919999997</v>
       </c>
       <c r="L59" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>64.28571428571429</v>
+        <v>60</v>
       </c>
       <c r="N59" t="n">
-        <v>13.24091072374009</v>
+        <v>14.14811524564401</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.916575649399781</v>
+        <v>6.299216867133905</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7107,7 +7087,7 @@
         <v>46255</v>
       </c>
       <c r="C60" t="n">
-        <v>11.79734805900501</v>
+        <v>11.8912261602703</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7135,22 +7115,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>2.70063317082021</v>
+        <v>3.517879588625172</v>
       </c>
       <c r="L60" t="n">
         <v>41</v>
       </c>
       <c r="M60" t="n">
-        <v>53.65853658536585</v>
+        <v>48.78048780487805</v>
       </c>
       <c r="N60" t="n">
-        <v>14.33560749626898</v>
+        <v>13.76700212351024</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.160013785275752</v>
+        <v>4.329803150128808</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7216,7 +7196,7 @@
         <v>46255</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6333642692622006</v>
+        <v>0.6304435901024956</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7248,7 +7228,7 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>3.069328566464424</v>
+        <v>2.594037403766647</v>
       </c>
       <c r="L61" t="n">
         <v>23</v>
@@ -7257,13 +7237,13 @@
         <v>78.26086956521739</v>
       </c>
       <c r="N61" t="n">
-        <v>20.78004206586317</v>
+        <v>21.0271844363258</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>6.724281151270262</v>
+        <v>7.218706645773798</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7282,16 +7262,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>9.895460494266894</v>
+        <v>10.31096617322754</v>
       </c>
       <c r="Z61" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA61" t="n">
-        <v>45.45454545454545</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="AB61" t="n">
-        <v>12.995828514067</v>
+        <v>12.5541657761293</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7331,7 +7311,7 @@
         <v>46255</v>
       </c>
       <c r="C62" t="n">
-        <v>9.26263932484213</v>
+        <v>9.278285675053013</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7388,25 +7368,25 @@
         <v>72.05882352941177</v>
       </c>
       <c r="X62" t="n">
-        <v>11.694667893328</v>
+        <v>12.1334236033467</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.3367003367003352</v>
+        <v>0.5589714924538858</v>
       </c>
       <c r="Z62" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AA62" t="n">
-        <v>46.15384615384615</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.60735392349249</v>
+        <v>11.76770905719442</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.668918918918927</v>
+        <v>1.449128724002247</v>
       </c>
       <c r="AE62" t="n">
         <v>30</v>
@@ -7440,7 +7420,7 @@
         <v>46255</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1055607081710424</v>
+        <v>0.1072296507332104</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7468,16 +7448,16 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>7.413760724569496</v>
+        <v>9.112000535023368</v>
       </c>
       <c r="L63" t="n">
         <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>71.42857142857143</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="N63" t="n">
-        <v>18.52195957147963</v>
+        <v>20.04183163819911</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
@@ -7510,22 +7490,22 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>8.499100400576653</v>
+        <v>7.052447110124072</v>
       </c>
       <c r="Z63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA63" t="n">
-        <v>66.66666666666667</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB63" t="n">
-        <v>14.52996031924543</v>
+        <v>15.9718454769194</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.640311304035313</v>
+        <v>3.171200099660698</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7559,7 +7539,7 @@
         <v>46255</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1499963452733632</v>
+        <v>0.1491618740965882</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7587,22 +7567,22 @@
         <v>24.42078296285393</v>
       </c>
       <c r="K64" t="n">
-        <v>1.41043593630954</v>
+        <v>0.8462616182032034</v>
       </c>
       <c r="L64" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M64" t="n">
-        <v>66.66666666666667</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N64" t="n">
-        <v>15.9920918134248</v>
+        <v>15.88543773845759</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.539639713160159</v>
+        <v>4.118881865470203</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7787,7 +7767,7 @@
         <v>46255</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4610457941414731</v>
+        <v>0.4639664334551395</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7847,22 +7827,22 @@
         <v>12.69724877030836</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.952087497962707</v>
+        <v>1.330972217191906</v>
       </c>
       <c r="Z66" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AA66" t="n">
-        <v>36.50793650793651</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.32406401405177</v>
+        <v>11.18517533420831</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.128504522677312</v>
+        <v>4.73200951476449</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7985,7 +7965,7 @@
         <v>46255</v>
       </c>
       <c r="C68" t="n">
-        <v>4.29544455063715</v>
+        <v>4.276669057641073</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8042,10 +8022,10 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>142.0891443924669</v>
+        <v>143.1366383982815</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.009618317307703</v>
+        <v>1.866919106693199</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8056,7 +8036,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.061677673998212</v>
+        <v>6.249758835121932</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8090,7 +8070,7 @@
         <v>46255</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4149411948668918</v>
+        <v>0.4201566449371859</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8104,7 +8084,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -8118,22 +8098,22 @@
         <v>18.0901893667493</v>
       </c>
       <c r="K69" t="n">
-        <v>6.363628778804387</v>
+        <v>7.700527120192469</v>
       </c>
       <c r="L69" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M69" t="n">
-        <v>64.28571428571429</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N69" t="n">
-        <v>21.39705057314318</v>
+        <v>17.54135150689928</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>1.538468779208957</v>
+        <v>0.2780607373196409</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8148,17 +8128,27 @@
       <c r="W69" t="n">
         <v>66.66666666666667</v>
       </c>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
+      <c r="X69" t="n">
+        <v>11.44384654025008</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>3.358928766610403</v>
+      </c>
       <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>36.8421052631579</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>14.06027699497266</v>
+      </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
-      <c r="AD69" t="inlineStr"/>
+      <c r="AD69" t="n">
+        <v>2.732866264500911</v>
+      </c>
       <c r="AE69" t="n">
         <v>0</v>
       </c>
@@ -8183,7 +8173,7 @@
         <v>46255</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4264152088039909</v>
+        <v>0.4326737330333755</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8211,16 +8201,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>11.81285978628521</v>
+        <v>13.45394452641913</v>
       </c>
       <c r="L70" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M70" t="n">
-        <v>35.71428571428572</v>
+        <v>20</v>
       </c>
       <c r="N70" t="n">
-        <v>12.00172386214981</v>
+        <v>6.838424675154897</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8250,25 +8240,25 @@
         <v>67.79661016949153</v>
       </c>
       <c r="X70" t="n">
-        <v>13.34453608357888</v>
+        <v>14.32919111790623</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.351345508321844</v>
+        <v>0.7655495354501829</v>
       </c>
       <c r="Z70" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AA70" t="n">
-        <v>43.63636363636363</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB70" t="n">
-        <v>10.44174077450655</v>
+        <v>10.16790083148568</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>6.739731551269179</v>
+        <v>7.290261023951783</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8302,7 +8292,7 @@
         <v>46255</v>
       </c>
       <c r="C71" t="n">
-        <v>3.139700942316983</v>
+        <v>3.127183734891296</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8330,22 +8320,22 @@
         <v>14.92600999981897</v>
       </c>
       <c r="K71" t="n">
-        <v>1.620522485582798</v>
+        <v>1.215386715639033</v>
       </c>
       <c r="L71" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M71" t="n">
-        <v>59.42028985507246</v>
+        <v>60.29411764705883</v>
       </c>
       <c r="N71" t="n">
-        <v>16.72997395311209</v>
+        <v>16.85799615847782</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.3734260611295781</v>
+        <v>0.775191707329359</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8411,7 +8401,7 @@
         <v>46255</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0719732120131471</v>
+        <v>0.07176459421895336</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8439,22 +8429,22 @@
         <v>21.72769951373251</v>
       </c>
       <c r="K72" t="n">
-        <v>2.373892065616645</v>
+        <v>2.077156447622319</v>
       </c>
       <c r="L72" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M72" t="n">
-        <v>61.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>15.92894704940889</v>
+        <v>17.02483572560697</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>2.565212557025909</v>
+        <v>2.86336694133662</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8481,7 +8471,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>19.86959958291339</v>
+        <v>20.10186137747969</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8526,16 +8516,16 @@
         <v>46255</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07322491877830965</v>
+        <v>0.07176459421895336</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8554,22 +8544,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>11.30117495534699</v>
+        <v>9.081495616888645</v>
       </c>
       <c r="L73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N73" t="n">
-        <v>8.996964415772805</v>
+        <v>8.294249049343749</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>0.8420350105367902</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8596,22 +8586,22 @@
         <v>15.4234441942493</v>
       </c>
       <c r="Y73" t="n">
-        <v>3.571431495290345</v>
+        <v>5.494506442458613</v>
       </c>
       <c r="Z73" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AA73" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AB73" t="n">
-        <v>13.46044713942639</v>
+        <v>14.16303952989258</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>6.666663836657161</v>
+        <v>4.767440905219056</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8645,7 +8635,7 @@
         <v>46255</v>
       </c>
       <c r="C74" t="n">
-        <v>5.611824275636335</v>
+        <v>5.533592524581926</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8662,11 +8652,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -8677,16 +8663,16 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>18.72992205068638</v>
+        <v>17.07476514477533</v>
       </c>
       <c r="L74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M74" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N74" t="n">
-        <v>16.52901193804602</v>
+        <v>23.62355792397849</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
@@ -8719,22 +8705,22 @@
         <v>32.26405389680429</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.068544768485559</v>
+        <v>4.419819702010386</v>
       </c>
       <c r="Z74" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA74" t="n">
-        <v>44.44444444444444</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="AB74" t="n">
-        <v>19.62997595670867</v>
+        <v>15.70096465508718</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>7.150883286502929</v>
+        <v>5.838219053984128</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8768,7 +8754,7 @@
         <v>46255</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1253794244880816</v>
+        <v>0.1251708016870558</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8796,7 +8782,7 @@
         <v>23.39449322057143</v>
       </c>
       <c r="K75" t="n">
-        <v>1.520272783509835</v>
+        <v>1.351349981738514</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
@@ -8805,13 +8791,13 @@
         <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>15.297617066367</v>
+        <v>18.41766752278744</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.412643005838945</v>
+        <v>4.586668080000011</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8877,7 +8863,7 @@
         <v>46255</v>
       </c>
       <c r="C76" t="n">
-        <v>1.890079073555988</v>
+        <v>1.90572542376687</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8894,7 +8880,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>5</v>
       </c>
@@ -8905,22 +8895,22 @@
         <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>9.05339376362042</v>
+        <v>9.956153661014877</v>
       </c>
       <c r="L76" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M76" t="n">
-        <v>71.42857142857143</v>
+        <v>75</v>
       </c>
       <c r="N76" t="n">
-        <v>9.165714773644876</v>
+        <v>8.050242483147439</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>0.8680208874850992</v>
+        <v>0.03987620294567673</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8944,25 +8934,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X76" t="n">
-        <v>10.78536860174914</v>
+        <v>10.97927971513522</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.563360631451982</v>
+        <v>0.9219072756162405</v>
       </c>
       <c r="Z76" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA76" t="n">
-        <v>35.71428571428572</v>
+        <v>40.35087719298246</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.10432326031234</v>
+        <v>10.23721050399967</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.475337825609036</v>
+        <v>3.106733930523298</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8996,7 +8986,7 @@
         <v>46255</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5344793407276406</v>
+        <v>0.5286380222542691</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9024,16 +9014,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>10.07924640987292</v>
+        <v>8.876191611321849</v>
       </c>
       <c r="L77" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M77" t="n">
-        <v>68.96551724137932</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N77" t="n">
-        <v>16.90273640953321</v>
+        <v>15.76565179817866</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9066,22 +9056,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>5.333861489079883</v>
+        <v>6.368466611391543</v>
       </c>
       <c r="Z77" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AA77" t="n">
-        <v>47.72727272727273</v>
+        <v>40</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.13919768245498</v>
+        <v>11.70708425880333</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.929047053484559</v>
+        <v>3.878536703586954</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9115,7 +9105,7 @@
         <v>46255</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0475649040152272</v>
+        <v>0.04819075739780847</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9143,22 +9133,22 @@
         <v>19.53698884929083</v>
       </c>
       <c r="K78" t="n">
-        <v>1.785712492028058</v>
+        <v>3.124996861049123</v>
       </c>
       <c r="L78" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="M78" t="n">
-        <v>68.42105263157895</v>
+        <v>63.82978723404256</v>
       </c>
       <c r="N78" t="n">
-        <v>18.85415131321418</v>
+        <v>18.33546205694923</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>2.175440397045292</v>
+        <v>0.8484879181425375</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9224,7 +9214,7 @@
         <v>46255</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8348892568490904</v>
+        <v>0.836558159356602</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9252,16 +9242,16 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>5.302664711095217</v>
+        <v>5.513159551868774</v>
       </c>
       <c r="L79" t="n">
         <v>28</v>
       </c>
       <c r="M79" t="n">
-        <v>64.28571428571429</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="N79" t="n">
-        <v>11.65746550447703</v>
+        <v>11.38934526030933</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
@@ -9333,7 +9323,7 @@
         <v>46255</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1280914510143864</v>
+        <v>0.1285086866027739</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9361,10 +9351,10 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>4.872284259364656</v>
+        <v>5.213887456783239</v>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
@@ -9372,7 +9362,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.889486079995886</v>
+        <v>4.548936132773029</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9399,22 +9389,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.605735077007536</v>
+        <v>6.30151952812763</v>
       </c>
       <c r="Z80" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA80" t="n">
-        <v>43.75</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.58902104315124</v>
+        <v>11.48064104902586</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.492880664719709</v>
+        <v>1.812708662209561</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9448,7 +9438,7 @@
         <v>46255</v>
       </c>
       <c r="C81" t="n">
-        <v>1.211027490467297</v>
+        <v>1.222501464558357</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9505,25 +9495,25 @@
         <v>64.58333333333333</v>
       </c>
       <c r="X81" t="n">
-        <v>29.47918074704852</v>
+        <v>30.69132459397106</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.19149065531915</v>
+        <v>1.180439762177643</v>
       </c>
       <c r="Z81" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA81" t="n">
-        <v>57.89473684210526</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="AB81" t="n">
-        <v>14.01965355445153</v>
+        <v>12.52862678478392</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>8.914727489667406</v>
+        <v>8.924913465104389</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9557,7 +9547,7 @@
         <v>46255</v>
       </c>
       <c r="C82" t="n">
-        <v>5.288466371278108</v>
+        <v>5.345836322051342</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9617,13 +9607,13 @@
         <v>16.65327680511959</v>
       </c>
       <c r="Y82" t="n">
-        <v>5.405777568468395</v>
+        <v>4.379607502643101</v>
       </c>
       <c r="Z82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA82" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="AB82" t="n">
         <v>8.312827786585837</v>
@@ -9666,7 +9656,7 @@
         <v>46255</v>
       </c>
       <c r="C83" t="n">
-        <v>5.77350322781545</v>
+        <v>5.830873178588684</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9726,22 +9716,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>4.03064728602468</v>
+        <v>3.077022281640096</v>
       </c>
       <c r="Z83" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA83" t="n">
-        <v>46</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.51277349367968</v>
+        <v>12.81671318944869</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.052064183286439</v>
+        <v>3.015773748567174</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9775,7 +9765,7 @@
         <v>46255</v>
       </c>
       <c r="C84" t="n">
-        <v>2.146679280851562</v>
+        <v>2.175885832955144</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9803,22 +9793,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>2.767014558588743</v>
+        <v>4.16520673010139</v>
       </c>
       <c r="L84" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="M84" t="n">
-        <v>48.27586206896552</v>
+        <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>10.54561761835785</v>
+        <v>11.61841236501015</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>2.172862032630341</v>
+        <v>0.8014127712160368</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9884,7 +9874,7 @@
         <v>46255</v>
       </c>
       <c r="C85" t="n">
-        <v>6.321125485196319</v>
+        <v>6.315910035126024</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9912,22 +9902,22 @@
         <v>15.93296998857089</v>
       </c>
       <c r="K85" t="n">
-        <v>2.172726078345888</v>
+        <v>2.088425149238327</v>
       </c>
       <c r="L85" t="n">
         <v>50</v>
       </c>
       <c r="M85" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N85" t="n">
-        <v>14.44780391972448</v>
+        <v>14.13006199155937</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.703355626613882</v>
+        <v>5.790641634563198</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9993,7 +9983,7 @@
         <v>46255</v>
       </c>
       <c r="C86" t="n">
-        <v>4.75857677139322</v>
+        <v>4.539527868440873</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10002,7 +9992,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -10017,17 +10007,27 @@
       <c r="I86" t="n">
         <v>10</v>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>12.2426962665338</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.8341070549396479</v>
+      </c>
       <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="M86" t="n">
+        <v>60</v>
+      </c>
+      <c r="N86" t="n">
+        <v>15.14601166450642</v>
+      </c>
       <c r="O86" t="n">
         <v>6</v>
       </c>
-      <c r="P86" t="inlineStr"/>
+      <c r="P86" t="n">
+        <v>5.123160303532726</v>
+      </c>
       <c r="Q86" t="n">
         <v>54</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>88.01181128002702</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.240772780317196</v>
+        <v>11.51070640486815</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10098,7 +10098,7 @@
         <v>46255</v>
       </c>
       <c r="C87" t="n">
-        <v>5.679625126550158</v>
+        <v>5.862165879010448</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10126,16 +10126,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>5.326772767393151</v>
+        <v>8.71193075348935</v>
       </c>
       <c r="L87" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M87" t="n">
-        <v>54.16666666666666</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N87" t="n">
-        <v>11.24467722556862</v>
+        <v>9.954913288470394</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10207,7 +10207,7 @@
         <v>46255</v>
       </c>
       <c r="C88" t="n">
-        <v>1.098373816722469</v>
+        <v>1.10776156301189</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>23.05257576408624</v>
+        <v>24.10429999853672</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10273,22 +10273,22 @@
         <v>27.20319322085054</v>
       </c>
       <c r="Y88" t="n">
-        <v>3.262982124637392</v>
+        <v>2.436175652393824</v>
       </c>
       <c r="Z88" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA88" t="n">
-        <v>50</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="AB88" t="n">
-        <v>14.43839299220867</v>
+        <v>14.98672127802329</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.829338691098615</v>
+        <v>3.652813295744517</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10322,7 +10322,7 @@
         <v>46255</v>
       </c>
       <c r="C89" t="n">
-        <v>2.177971981273326</v>
+        <v>2.215523126232397</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -10354,16 +10354,16 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>18.30385575499671</v>
+        <v>20.34357218609413</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M89" t="n">
-        <v>83.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N89" t="n">
-        <v>12.23354717638958</v>
+        <v>13.47952249834024</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10396,22 +10396,22 @@
         <v>20.95675253601343</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.193260587272172</v>
+        <v>0.5069418094179934</v>
       </c>
       <c r="Z89" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="AA89" t="n">
-        <v>41.37931034482759</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.229850692174</v>
+        <v>12.46435165776869</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>7.981801110641983</v>
+        <v>9.541427676690528</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10445,7 +10445,7 @@
         <v>46255</v>
       </c>
       <c r="C90" t="n">
-        <v>2.822601641671599</v>
+        <v>2.89979023908346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10462,11 +10462,7 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>5</v>
       </c>
@@ -10477,16 +10473,16 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>11.26765941367078</v>
+        <v>14.31045314008395</v>
       </c>
       <c r="L90" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="M90" t="n">
-        <v>81.25</v>
+        <v>70</v>
       </c>
       <c r="N90" t="n">
-        <v>14.13725471419189</v>
+        <v>15.52634973642465</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
@@ -10519,16 +10515,16 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>7.187991209733235</v>
+        <v>4.649897035999495</v>
       </c>
       <c r="Z90" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AA90" t="n">
-        <v>53.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="AB90" t="n">
-        <v>17.38448689559154</v>
+        <v>10.86839151062816</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10568,7 +10564,7 @@
         <v>46255</v>
       </c>
       <c r="C91" t="n">
-        <v>0.229062557490884</v>
+        <v>0.2301056514686849</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10596,22 +10592,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>2.317895105460921</v>
+        <v>2.783825379595828</v>
       </c>
       <c r="L91" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M91" t="n">
-        <v>64.70588235294117</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N91" t="n">
-        <v>15.29890820780455</v>
+        <v>12.55561191083563</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.6666525868578743</v>
+        <v>0.2103196875634872</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10677,7 +10673,7 @@
         <v>46255</v>
       </c>
       <c r="C92" t="n">
-        <v>1.122364839272299</v>
+        <v>1.131752665253796</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10696,7 +10692,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -10709,22 +10705,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>6.52128266642813</v>
+        <v>7.412261455149549</v>
       </c>
       <c r="L92" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="M92" t="n">
-        <v>75</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="N92" t="n">
-        <v>13.03072625361268</v>
+        <v>11.3394348166478</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>1.388189567903053</v>
+        <v>0.5471801234683715</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10751,16 +10747,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.102428705418895</v>
+        <v>6.325403086919723</v>
       </c>
       <c r="Z92" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AA92" t="n">
-        <v>54.05405405405406</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.51648162671794</v>
+        <v>11.63419670347171</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10800,7 +10796,7 @@
         <v>46255</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04214083615073946</v>
+        <v>0.04234945394493321</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10828,22 +10824,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>4.202065138061895</v>
+        <v>4.71791643493169</v>
       </c>
       <c r="L93" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M93" t="n">
-        <v>64.15094339622641</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N93" t="n">
-        <v>19.53194616401082</v>
+        <v>19.60927954851992</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>1.725431122268017</v>
+        <v>1.224321117833704</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10909,7 +10905,7 @@
         <v>46255</v>
       </c>
       <c r="C94" t="n">
-        <v>8.235195660994213</v>
+        <v>8.3342892123298</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10969,22 +10965,22 @@
         <v>50.4132727790992</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.986343885785236</v>
+        <v>0.8069522036002419</v>
       </c>
       <c r="Z94" t="n">
         <v>7</v>
       </c>
       <c r="AA94" t="n">
-        <v>28.57142857142857</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB94" t="n">
-        <v>12.36506894044984</v>
+        <v>9.735429777718856</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.09499683343888</v>
+        <v>5.235294117647071</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11018,16 +11014,16 @@
         <v>46255</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1441550368136559</v>
+        <v>0.1410257746989636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -11035,11 +11031,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>5</v>
       </c>
@@ -11050,22 +11042,22 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>8.060152610853066</v>
+        <v>5.714424364741766</v>
       </c>
       <c r="L95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N95" t="n">
-        <v>18.17529258831296</v>
+        <v>19.08560282706251</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>0.2701387601307115</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11092,22 +11084,22 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>3.491620184880317</v>
+        <v>5.586586988545816</v>
       </c>
       <c r="Z95" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA95" t="n">
-        <v>44.82758620689656</v>
+        <v>50</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.24624973377114</v>
+        <v>10.73253308720716</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.599131619373329</v>
+        <v>0.4378752957527654</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11141,7 +11133,7 @@
         <v>46255</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1324724296992874</v>
+        <v>0.1320551941108999</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11169,22 +11161,22 @@
         <v>13.52465198145173</v>
       </c>
       <c r="K96" t="n">
-        <v>3.252029215414165</v>
+        <v>2.926826293872753</v>
       </c>
       <c r="L96" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M96" t="n">
-        <v>57.14285714285715</v>
+        <v>57.8125</v>
       </c>
       <c r="N96" t="n">
-        <v>15.06215336209593</v>
+        <v>14.18034793826052</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.535436480873025</v>
+        <v>6.872041003122153</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11250,7 +11242,7 @@
         <v>46255</v>
       </c>
       <c r="C97" t="n">
-        <v>1.946406029862209</v>
+        <v>1.932845827969508</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11278,16 +11270,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>8.901071497345448</v>
+        <v>8.142380611076462</v>
       </c>
       <c r="L97" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M97" t="n">
-        <v>55.55555555555556</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N97" t="n">
-        <v>12.42715529904951</v>
+        <v>14.4630255951897</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11320,22 +11312,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>4.941414574015646</v>
+        <v>5.603667767971354</v>
       </c>
       <c r="Z97" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="AA97" t="n">
-        <v>41.66666666666666</v>
+        <v>48.48484848484848</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.93556647903864</v>
+        <v>11.4083613888801</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.113613695428495</v>
+        <v>0.4198597791431724</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11369,7 +11361,7 @@
         <v>46255</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6279401963908808</v>
+        <v>0.6375366055359835</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11397,22 +11389,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>4.854370336909741</v>
+        <v>6.456792739852624</v>
       </c>
       <c r="L98" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M98" t="n">
-        <v>40.47619047619047</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N98" t="n">
-        <v>16.09032931635308</v>
+        <v>13.23775944396483</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>4.907406001825909</v>
+        <v>3.328305473945559</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11439,22 +11431,22 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>4.735806946487742</v>
+        <v>3.279945100608272</v>
       </c>
       <c r="Z98" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AA98" t="n">
-        <v>36.66666666666666</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.93674418801786</v>
+        <v>11.78804775566407</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>3.42646376239043</v>
+        <v>4.880120161533741</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11488,7 +11480,7 @@
         <v>46255</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4627147367036411</v>
+        <v>0.4639664334551395</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11516,16 +11508,16 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>5.050061712377096</v>
+        <v>5.334234250141567</v>
       </c>
       <c r="L99" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M99" t="n">
-        <v>70.58823529411765</v>
+        <v>60</v>
       </c>
       <c r="N99" t="n">
-        <v>13.00352492424371</v>
+        <v>13.58459766824227</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11597,7 +11589,7 @@
         <v>46255</v>
       </c>
       <c r="C100" t="n">
-        <v>327.8999298109945</v>
+        <v>330.6674594959516</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11614,7 +11606,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>5</v>
       </c>
@@ -11625,16 +11621,16 @@
         <v>15.65236426997335</v>
       </c>
       <c r="K100" t="n">
-        <v>6.987022857059277</v>
+        <v>7.890011039559863</v>
       </c>
       <c r="L100" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M100" t="n">
-        <v>68.42105263157895</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N100" t="n">
-        <v>11.8908237696045</v>
+        <v>11.66125686104412</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11706,7 +11702,7 @@
         <v>46255</v>
       </c>
       <c r="C101" t="n">
-        <v>345.3470567686605</v>
+        <v>347.7902099065632</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11734,16 +11730,16 @@
         <v>11.19277381576541</v>
       </c>
       <c r="K101" t="n">
-        <v>9.360722256538656</v>
+        <v>10.13439322464931</v>
       </c>
       <c r="L101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M101" t="n">
-        <v>45.45454545454545</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="N101" t="n">
-        <v>8.00364326814563</v>
+        <v>7.638293933302016</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11776,22 +11772,22 @@
         <v>10.7755255729769</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.277180414284018</v>
+        <v>0.5787671464535071</v>
       </c>
       <c r="Z101" t="n">
         <v>40</v>
       </c>
       <c r="AA101" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="AB101" t="n">
-        <v>14.15145124560824</v>
+        <v>11.1809240817331</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.78391886043672</v>
+        <v>5.452791821171942</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11825,7 +11821,7 @@
         <v>46255</v>
       </c>
       <c r="C102" t="n">
-        <v>418.5943044012016</v>
+        <v>420.4109515994102</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,25 +11878,25 @@
         <v>47.22222222222222</v>
       </c>
       <c r="X102" t="n">
-        <v>10.29256843357016</v>
+        <v>10.50083949700029</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.3970704336589859</v>
+        <v>0.1533516138794599</v>
       </c>
       <c r="Z102" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA102" t="n">
-        <v>32.43243243243244</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB102" t="n">
-        <v>11.63419257229469</v>
+        <v>13.55094174897825</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.621279300098513</v>
+        <v>4.854092214871242</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11934,7 +11930,7 @@
         <v>46255</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7280768617315957</v>
+        <v>0.7339181403589287</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11951,7 +11947,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>5</v>
       </c>
@@ -11962,16 +11962,16 @@
         <v>16.13876216849247</v>
       </c>
       <c r="K103" t="n">
-        <v>11.97701452060491</v>
+        <v>12.87539349135827</v>
       </c>
       <c r="L103" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M103" t="n">
-        <v>72.22222222222223</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N103" t="n">
-        <v>12.59597849727541</v>
+        <v>12.84408537336701</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -12004,22 +12004,22 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>3.57323067319405</v>
+        <v>2.799609567543426</v>
       </c>
       <c r="Z103" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AA103" t="n">
-        <v>43.47826086956522</v>
+        <v>36.73469387755102</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.15205565550442</v>
+        <v>11.3889295216024</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>4.590809541490404</v>
+        <v>5.350174427612265</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -453,7 +453,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -679,7 +679,7 @@
         <v>46255</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4036758433682391</v>
+        <v>0.402632729571728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>2.968076771565942</v>
+        <v>2.702003328616165</v>
       </c>
       <c r="L2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>50</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="N2" t="n">
-        <v>11.12032742459378</v>
+        <v>12.63834162191096</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>6.829226541770161</v>
+        <v>7.105992517042159</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -897,7 +897,7 @@
         <v>46255</v>
       </c>
       <c r="C4" t="n">
-        <v>1.465541469752612</v>
+        <v>1.454067415969474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,11 +914,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>5</v>
       </c>
@@ -929,16 +925,16 @@
         <v>14.71888288970985</v>
       </c>
       <c r="K4" t="n">
-        <v>13.47232810558749</v>
+        <v>12.58392772767043</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
-        <v>77.77777777777777</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N4" t="n">
-        <v>14.04969835439648</v>
+        <v>14.1451842611309</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -971,22 +967,22 @@
         <v>15.89522479111605</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.090592334494767</v>
+        <v>2.857147108013935</v>
       </c>
       <c r="Z4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.82758620689656</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.06208636967171</v>
+        <v>12.93554239735304</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.078291814946626</v>
+        <v>7.352937122330816</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1020,7 +1016,7 @@
         <v>46255</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2369900441011469</v>
+        <v>0.2344866303622039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,25 +1041,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>15.99376685518751</v>
+        <v>16.29245538545801</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9777747555555605</v>
+        <v>0.2676157885187713</v>
       </c>
       <c r="L5" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>56.86274509803921</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N5" t="n">
-        <v>14.58080922442367</v>
+        <v>14.51905653683128</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.00264389796645</v>
+        <v>2.725091436545468</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1129,7 +1125,7 @@
         <v>46255</v>
       </c>
       <c r="C6" t="n">
-        <v>1.731529423337606</v>
+        <v>1.726313973267311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1153,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>5.805763582481549</v>
+        <v>5.487071523498166</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1195,7 +1191,7 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.511405521670998</v>
+        <v>5.796009721906936</v>
       </c>
       <c r="Z6" t="n">
         <v>50</v>
@@ -1204,7 +1200,7 @@
         <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.90569606962703</v>
+        <v>11.82269995469782</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1244,7 +1240,7 @@
         <v>46255</v>
       </c>
       <c r="C7" t="n">
-        <v>2.271850082538617</v>
+        <v>2.257246726794749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,22 +1300,22 @@
         <v>14.22876300591287</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.883496382659635</v>
+        <v>4.501329181561742</v>
       </c>
       <c r="Z7" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="AA7" t="n">
-        <v>48.83720930232558</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5921569011977</v>
+        <v>11.01021328205966</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.161614889556739</v>
+        <v>0.5221756639800068</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1353,7 +1349,7 @@
         <v>46255</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4017982782136632</v>
+        <v>0.3972086965464467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,23 +1406,25 @@
         <v>33.33333333333334</v>
       </c>
       <c r="X8" t="n">
-        <v>28.48050864786196</v>
+        <v>30.27139917619635</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.567891611924165</v>
+        <v>3.054982121361449</v>
       </c>
       <c r="Z8" t="n">
         <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>15.9993759340716</v>
+      </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>7.474555763284119</v>
+        <v>5.100847869076686</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1460,11 +1458,11 @@
         <v>46255</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5987336839247186</v>
+        <v>0.5945613080135151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1474,7 +1472,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1520,22 +1518,22 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.727939769462729</v>
+        <v>4.398827738208333</v>
       </c>
       <c r="Z9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AA9" t="n">
-        <v>47.72727272727273</v>
+        <v>46.34146341463415</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.80706426686921</v>
+        <v>11.05313074983267</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2825952097480711</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>33</v>
@@ -1569,7 +1567,7 @@
         <v>46255</v>
       </c>
       <c r="C10" t="n">
-        <v>1.946406029862209</v>
+        <v>1.938061278039802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,22 +1595,22 @@
         <v>10.51321892894885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9740276029192474</v>
+        <v>0.541125532165343</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>40</v>
+        <v>44.18604651162791</v>
       </c>
       <c r="N10" t="n">
-        <v>9.700270874208478</v>
+        <v>9.686680376807971</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>4.977490267938411</v>
+        <v>5.429494089051401</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1678,7 +1676,7 @@
         <v>46255</v>
       </c>
       <c r="C11" t="n">
-        <v>8.422951863524798</v>
+        <v>8.480321814298032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,22 +1736,22 @@
         <v>22.18106016526054</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.223241590214075</v>
+        <v>0.5504587155963359</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AA11" t="n">
-        <v>45</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.94821475243904</v>
+        <v>12.53596468722206</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.7863777089783253</v>
+        <v>1.457564575645753</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1787,16 +1785,16 @@
         <v>46255</v>
       </c>
       <c r="C12" t="n">
-        <v>6.946979493631598</v>
+        <v>7.035642144826595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1804,7 +1802,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1815,22 +1817,22 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>5.798252581413821</v>
+        <v>7.148530579825252</v>
       </c>
       <c r="L12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N12" t="n">
-        <v>20.93539787729433</v>
+        <v>18.95023129685582</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1906906906906869</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1857,16 +1859,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.013075742886764</v>
+        <v>4.813542925791481</v>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>33.33333333333334</v>
+        <v>30</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.917895439582416</v>
+        <v>10.19016848477012</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1906,7 +1908,7 @@
         <v>46255</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2363641955167797</v>
+        <v>0.238658986454697</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1936,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>11.95652216553531</v>
+        <v>13.04347533940535</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1970,22 +1972,22 @@
         <v>16.60079365870428</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.983053071459319</v>
+        <v>3.050852577994756</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>55.55555555555556</v>
+        <v>62.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.977284347248103</v>
+        <v>11.96446601497775</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.266546813885587</v>
+        <v>7.167827264902737</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2009,7 +2011,7 @@
         <v>46255</v>
       </c>
       <c r="C14" t="n">
-        <v>8.657647116688027</v>
+        <v>8.709801617390967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,22 +2071,22 @@
         <v>12.93345142071747</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.131625967838013</v>
+        <v>0.536033353186427</v>
       </c>
       <c r="Z14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
-        <v>48.93617021276596</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.09559709514738</v>
+        <v>12.39046602360439</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.8783132530120308</v>
+        <v>1.471856287425144</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2118,7 +2120,7 @@
         <v>46255</v>
       </c>
       <c r="C15" t="n">
-        <v>14.13386969049672</v>
+        <v>14.3216258930273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2180,7 @@
         <v>38.77434577704333</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.104741684359514</v>
+        <v>2.830856334041054</v>
       </c>
       <c r="Z15" t="n">
         <v>17</v>
@@ -2187,13 +2189,13 @@
         <v>35.29411764705883</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.389895908407604</v>
+        <v>11.03006502530144</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.147601476014763</v>
+        <v>7.378004369992707</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2227,7 +2229,7 @@
         <v>46255</v>
       </c>
       <c r="C16" t="n">
-        <v>35.5067840785615</v>
+        <v>35.48592227828033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,7 +2257,7 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>1.968308684907116</v>
+        <v>1.908397810239149</v>
       </c>
       <c r="L16" t="n">
         <v>95</v>
@@ -2264,13 +2266,13 @@
         <v>68.42105263157895</v>
       </c>
       <c r="N16" t="n">
-        <v>18.18642428626609</v>
+        <v>18.16138921050452</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.876654441638009</v>
+        <v>7.940073991574281</v>
       </c>
       <c r="Q16" t="n">
         <v>27</v>
@@ -2297,7 +2299,7 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.26052588581834</v>
+        <v>12.31207669317097</v>
       </c>
       <c r="Z16" t="n">
         <v>23</v>
@@ -2346,7 +2348,7 @@
         <v>46255</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7159769791828012</v>
+        <v>0.6980358182152917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,22 +2376,22 @@
         <v>14.75338697646304</v>
       </c>
       <c r="K17" t="n">
-        <v>3.063064484322209</v>
+        <v>0.4804800109659224</v>
       </c>
       <c r="L17" t="n">
         <v>64</v>
       </c>
       <c r="M17" t="n">
-        <v>64.0625</v>
+        <v>71.875</v>
       </c>
       <c r="N17" t="n">
-        <v>15.94741868230261</v>
+        <v>15.7891862097217</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.790208345132996</v>
+        <v>7.483562964879797</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2455,7 +2457,7 @@
         <v>46255</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09867631574719835</v>
+        <v>0.09721598618100998</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,25 +2482,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>20.56707245057805</v>
+        <v>20.7015863320355</v>
       </c>
       <c r="K18" t="n">
-        <v>1.767031067364555</v>
+        <v>0.4310340638005394</v>
       </c>
       <c r="L18" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M18" t="n">
-        <v>65.85365853658537</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N18" t="n">
-        <v>15.22851380311469</v>
+        <v>15.88557305699444</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>8.090015839398568</v>
+        <v>9.52789745261471</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2673,7 +2675,7 @@
         <v>46255</v>
       </c>
       <c r="C20" t="n">
-        <v>1.736744873407899</v>
+        <v>1.745089625438924</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,16 +2703,16 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>4.255400586584646</v>
+        <v>4.75632935229513</v>
       </c>
       <c r="L20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M20" t="n">
-        <v>52.94117647058823</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N20" t="n">
-        <v>11.32247634963579</v>
+        <v>11.54120742415455</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -2782,7 +2784,7 @@
         <v>46255</v>
       </c>
       <c r="C21" t="n">
-        <v>0.959225567332043</v>
+        <v>0.9563049280183765</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,22 +2812,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>3.253405054650171</v>
+        <v>2.939020238040979</v>
       </c>
       <c r="L21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M21" t="n">
-        <v>52.72727272727273</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N21" t="n">
-        <v>16.30155361855141</v>
+        <v>16.97221783368339</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.597034783344478</v>
+        <v>4.916483322121956</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2891,7 +2893,7 @@
         <v>46255</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3442197046394035</v>
+        <v>0.3433852134353002</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,7 +2953,7 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.187584041266003</v>
+        <v>6.41501331070673</v>
       </c>
       <c r="Z22" t="n">
         <v>14</v>
@@ -2992,7 +2994,7 @@
         <v>46255</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7760589863147143</v>
+        <v>0.7610384646608712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,25 +3019,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>24.33755492423044</v>
+        <v>26.4735215749153</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9772003488984771</v>
+        <v>1.899442219094305</v>
       </c>
       <c r="L23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>71.42857142857143</v>
+        <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>20.08190631494157</v>
+        <v>19.52872039775613</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.983869266727402</v>
+        <v>3.042762269727817</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3062,7 +3064,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>23.5981812469649</v>
+        <v>25.07692860149599</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3121,7 +3123,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -3173,17 +3175,27 @@
       <c r="W24" t="n">
         <v>75</v>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>12.34567843316572</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>5.934065246709386</v>
+      </c>
       <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>15.2747307352476</v>
+      </c>
       <c r="AC24" t="n">
         <v>2</v>
       </c>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
       <c r="AE24" t="n">
         <v>4</v>
       </c>
@@ -3216,7 +3228,7 @@
         <v>46255</v>
       </c>
       <c r="C25" t="n">
-        <v>3.559023255225602</v>
+        <v>3.554850640655403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3244,22 +3256,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>1.789976068503263</v>
+        <v>1.67063705136703</v>
       </c>
       <c r="L25" t="n">
         <v>60</v>
       </c>
       <c r="M25" t="n">
-        <v>56.66666666666666</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N25" t="n">
-        <v>16.98566670045244</v>
+        <v>16.76352102277555</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>6.100820700967136</v>
+        <v>6.225359781541639</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3325,7 +3337,7 @@
         <v>46255</v>
       </c>
       <c r="C26" t="n">
-        <v>0.44602527248763</v>
+        <v>0.4518665909610014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3424,7 +3436,7 @@
         <v>46255</v>
       </c>
       <c r="C27" t="n">
-        <v>44.41477279862364</v>
+        <v>44.66511440199775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3464,7 @@
         <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>34.7404820236658</v>
+        <v>35.49993988382736</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3477,25 +3489,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>35.94295696892162</v>
+        <v>36.63912667406974</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.8845437616387453</v>
+        <v>0.8337193144974608</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="AB27" t="n">
-        <v>20.54491939468352</v>
+        <v>10.45678423176366</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.152184124001868</v>
+        <v>4.201307800093412</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3628,11 +3640,11 @@
         <v>46255</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4118119327521996</v>
+        <v>0.417653251225571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3642,7 +3654,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3656,17 +3668,13 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>13.92051352809809</v>
+        <v>15.53641133785888</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N29" t="n">
-        <v>18.00706743337966</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>4</v>
       </c>
@@ -3698,7 +3706,7 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>10.10375771435262</v>
+        <v>8.828630553173921</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -3709,7 +3717,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.284799662364677</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3743,7 +3751,7 @@
         <v>46255</v>
       </c>
       <c r="C30" t="n">
-        <v>0.405553408522815</v>
+        <v>0.4074309738860089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,7 +3779,7 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>10.78619417599467</v>
+        <v>11.2990941209429</v>
       </c>
       <c r="L30" t="n">
         <v>13</v>
@@ -3780,7 +3788,7 @@
         <v>61.53846153846154</v>
       </c>
       <c r="N30" t="n">
-        <v>15.83763170086855</v>
+        <v>14.77749324550151</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3810,25 +3818,25 @@
         <v>64.17910447761194</v>
       </c>
       <c r="X30" t="n">
-        <v>11.81199400890234</v>
+        <v>12.26790380466121</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.917432733402479</v>
+        <v>0.8629444844752476</v>
       </c>
       <c r="Z30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA30" t="n">
-        <v>44.06779661016949</v>
+        <v>45</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.6579631094857</v>
+        <v>12.72600051764911</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>9.166665254200989</v>
+        <v>9.216589566848587</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3862,7 +3870,7 @@
         <v>46255</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1854614115926665</v>
+        <v>0.184001072012814</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,22 +3898,20 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>6.50728821525195</v>
+        <v>5.668640395267155</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>25</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5.988524106612392</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>3.279317165309159</v>
+        <v>4.099001925766088</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3971,7 +3977,7 @@
         <v>46255</v>
       </c>
       <c r="C32" t="n">
-        <v>2.292711882819793</v>
+        <v>2.317745979320096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,16 +4005,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>5.199639632437192</v>
+        <v>6.348313371204761</v>
       </c>
       <c r="L32" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M32" t="n">
-        <v>43.90243902439025</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N32" t="n">
-        <v>11.04464267885272</v>
+        <v>11.82690449155654</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4041,22 +4047,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.800870780537283</v>
+        <v>5.783230486478774</v>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA32" t="n">
-        <v>50</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.612847301691742</v>
+        <v>9.590042009487464</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.286631355362811</v>
+        <v>2.352839653670236</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4090,7 +4096,7 @@
         <v>46255</v>
       </c>
       <c r="C33" t="n">
-        <v>1.743003477120743</v>
+        <v>1.745089625438924</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4118,7 +4124,7 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>6.363847932334288</v>
+        <v>6.491151615540836</v>
       </c>
       <c r="L33" t="n">
         <v>28</v>
@@ -4127,7 +4133,7 @@
         <v>64.28571428571429</v>
       </c>
       <c r="N33" t="n">
-        <v>10.64617202775737</v>
+        <v>10.63635283345433</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4199,7 +4205,7 @@
         <v>46255</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7969207865958903</v>
+        <v>0.7956690499983533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4227,16 +4233,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>5.003101195112825</v>
+        <v>4.838171095620458</v>
       </c>
       <c r="L34" t="n">
         <v>22</v>
       </c>
       <c r="M34" t="n">
-        <v>68.18181818181819</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N34" t="n">
-        <v>9.716444525284787</v>
+        <v>9.616943003587124</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4308,7 +4314,7 @@
         <v>46255</v>
       </c>
       <c r="C35" t="n">
-        <v>1.951621479932503</v>
+        <v>1.941190579791915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4327,7 +4333,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4340,16 +4346,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>10.02315026586889</v>
+        <v>9.435105655078967</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>81.81818181818181</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="N35" t="n">
-        <v>10.73178574240798</v>
+        <v>11.13327172976649</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4382,16 +4388,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.083930912997304</v>
+        <v>6.58588743905325</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA35" t="n">
-        <v>41.66666666666666</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB35" t="n">
-        <v>15.05640991881998</v>
+        <v>14.75083324357035</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4431,7 +4437,7 @@
         <v>46255</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0809437873857608</v>
+        <v>0.08073516479335296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4459,16 +4465,16 @@
         <v>14.25367779956082</v>
       </c>
       <c r="K36" t="n">
-        <v>3.743318171809307</v>
+        <v>3.4759326110269</v>
       </c>
       <c r="L36" t="n">
         <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>55.17241379310344</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N36" t="n">
-        <v>20.88828552891385</v>
+        <v>19.93102979683517</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4540,7 +4546,7 @@
         <v>46255</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06613190856027185</v>
+        <v>0.06592329076607809</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4568,22 +4574,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>7.651581626831172</v>
+        <v>7.311987080274385</v>
       </c>
       <c r="L37" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M37" t="n">
-        <v>62.5</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="N37" t="n">
-        <v>17.11565236973266</v>
+        <v>19.27046095990698</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.3236537428466413</v>
+        <v>0.6411333332323466</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4610,16 +4616,16 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.001915595821847</v>
+        <v>4.304748359176525</v>
       </c>
       <c r="Z37" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AA37" t="n">
-        <v>56.25</v>
+        <v>54.09836065573771</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.09277213880228</v>
+        <v>13.89254843608937</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
@@ -4659,7 +4665,7 @@
         <v>46255</v>
       </c>
       <c r="C38" t="n">
-        <v>1.682504224595396</v>
+        <v>1.677288774525102</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,22 +4693,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>6.195914671834357</v>
+        <v>5.866727093851698</v>
       </c>
       <c r="L38" t="n">
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>48.71794871794872</v>
+        <v>56.41025641025641</v>
       </c>
       <c r="N38" t="n">
-        <v>10.54326189753282</v>
+        <v>9.949257097497322</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>3.582139049247801</v>
+        <v>3.904222808818991</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4768,7 +4774,7 @@
         <v>46255</v>
       </c>
       <c r="C39" t="n">
-        <v>2.722464936693464</v>
+        <v>2.718292640265719</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4796,16 +4802,16 @@
         <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>7.767413263855216</v>
+        <v>7.602254995945934</v>
       </c>
       <c r="L39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M39" t="n">
-        <v>61.90476190476191</v>
+        <v>60</v>
       </c>
       <c r="N39" t="n">
-        <v>14.68366168246508</v>
+        <v>13.82079674590696</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4838,13 +4844,13 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.246229941046085</v>
+        <v>2.396041863366338</v>
       </c>
       <c r="Z39" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AA39" t="n">
-        <v>36</v>
+        <v>38.29787234042553</v>
       </c>
       <c r="AB39" t="n">
         <v>11.65613829774405</v>
@@ -4853,7 +4859,7 @@
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.840025869784947</v>
+        <v>3.692430312701622</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4887,7 +4893,7 @@
         <v>46255</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2595207867358729</v>
+        <v>0.255139807842354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4947,22 +4953,22 @@
         <v>44.24108228242589</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.737758867351025</v>
+        <v>3.39652697547228</v>
       </c>
       <c r="Z40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="AB40" t="n">
-        <v>18.46032019010953</v>
+        <v>16.33457280603697</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.319933572698719</v>
+        <v>1.659850287287912</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4996,7 +5002,7 @@
         <v>46255</v>
       </c>
       <c r="C41" t="n">
-        <v>1.821235228175153</v>
+        <v>1.800373427893977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5024,7 +5030,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>20.35749080720863</v>
+        <v>18.97882543948495</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -5062,22 +5068,22 @@
         <v>22.08082251686328</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.411631797792479</v>
+        <v>2.540937236026442</v>
       </c>
       <c r="Z41" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA41" t="n">
-        <v>43.33333333333334</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="AB41" t="n">
-        <v>15.95457160414137</v>
+        <v>16.51101596372883</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.611111159634715</v>
+        <v>0.4710313755892814</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5111,7 +5117,7 @@
         <v>46255</v>
       </c>
       <c r="C42" t="n">
-        <v>3.784330443748339</v>
+        <v>3.761382654324518</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5169,7 +5175,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.148319370818752</v>
+        <v>2.741681867890056</v>
       </c>
       <c r="Z42" t="n">
         <v>3</v>
@@ -5178,13 +5184,13 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.034478235705823</v>
+        <v>8.674423338154757</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>8.024063131767733</v>
+        <v>7.462927872401282</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5216,7 +5222,7 @@
         <v>46255</v>
       </c>
       <c r="C43" t="n">
-        <v>6.712284240468368</v>
+        <v>6.686206990116898</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5248,7 +5254,7 @@
         <v>13.8335782657367</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5468750000000133</v>
+        <v>0.1562500000000133</v>
       </c>
       <c r="L43" t="n">
         <v>35</v>
@@ -5257,13 +5263,13 @@
         <v>85.71428571428571</v>
       </c>
       <c r="N43" t="n">
-        <v>15.44808004783934</v>
+        <v>15.62295410946941</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.434343434343434</v>
+        <v>3.837753510140396</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5290,10 +5296,10 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.36235564687744</v>
+        <v>13.69894323177691</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
@@ -5335,7 +5341,7 @@
         <v>46255</v>
       </c>
       <c r="C44" t="n">
-        <v>4.612544169424988</v>
+        <v>4.545786154011262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5352,11 +5358,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5367,22 +5369,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>2.885068578868855</v>
+        <v>1.395998178294966</v>
       </c>
       <c r="L44" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>76.92307692307692</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N44" t="n">
-        <v>17.10389424119687</v>
+        <v>17.27078993253876</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.915416901021976</v>
+        <v>8.485543785047355</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5440,7 +5442,7 @@
         <v>46255</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02336521631491709</v>
+        <v>0.02294798072652957</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5500,22 +5502,22 @@
         <v>17.77268946199939</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.754385103108635</v>
+        <v>3.508769329024286</v>
       </c>
       <c r="Z45" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AA45" t="n">
-        <v>44.64285714285715</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.99257466903162</v>
+        <v>12.5345853482408</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.303572276785727</v>
+        <v>1.545457199173517</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5549,7 +5551,7 @@
         <v>46255</v>
       </c>
       <c r="C46" t="n">
-        <v>9.935432383910056</v>
+        <v>9.893708783347703</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5606,25 +5608,25 @@
         <v>67.46987951807229</v>
       </c>
       <c r="X46" t="n">
-        <v>21.77676482446944</v>
+        <v>21.83992704688877</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.192946058091282</v>
+        <v>1.658890616899955</v>
       </c>
       <c r="Z46" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA46" t="n">
-        <v>33.33333333333334</v>
+        <v>34.14634146341464</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.76900945796669</v>
+        <v>12.67033385078146</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.828871391076126</v>
+        <v>1.363732208750656</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5658,7 +5660,7 @@
         <v>46255</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7143080766752896</v>
+        <v>0.713890831073238</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5686,22 +5688,22 @@
         <v>25.00555187915373</v>
       </c>
       <c r="K47" t="n">
-        <v>6.064530015239566</v>
+        <v>6.002575012730693</v>
       </c>
       <c r="L47" t="n">
         <v>12</v>
       </c>
       <c r="M47" t="n">
-        <v>58.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N47" t="n">
-        <v>14.59222377341274</v>
+        <v>13.90859617018367</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.71044870909718</v>
+        <v>3.771064039519079</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5767,7 +5769,7 @@
         <v>46255</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05966474671798325</v>
+        <v>0.05924751092097773</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5795,22 +5797,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>3.62318515805502</v>
+        <v>2.898547836588938</v>
       </c>
       <c r="L48" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M48" t="n">
-        <v>56.36363636363637</v>
+        <v>54.23728813559322</v>
       </c>
       <c r="N48" t="n">
-        <v>15.03939012974418</v>
+        <v>14.30510744762529</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.153849480903828</v>
+        <v>6.90141145110108</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5876,7 +5878,7 @@
         <v>46255</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2595207867358729</v>
+        <v>0.2588949383601237</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5904,22 +5906,22 @@
         <v>17.31218360853012</v>
       </c>
       <c r="K49" t="n">
-        <v>4.428237420256531</v>
+        <v>4.176403092864733</v>
       </c>
       <c r="L49" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M49" t="n">
-        <v>60.60606060606061</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N49" t="n">
-        <v>19.18494824880819</v>
+        <v>19.46717584041633</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.547517217438509</v>
+        <v>0.7905791356619396</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5985,7 +5987,7 @@
         <v>46255</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6880221636767554</v>
+        <v>0.6876049180747038</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6015,7 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>2.93382831775526</v>
+        <v>2.871404911307995</v>
       </c>
       <c r="L50" t="n">
         <v>44</v>
@@ -6028,7 +6030,7 @@
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.035783570541549</v>
+        <v>1.097093103438262</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6094,7 +6096,7 @@
         <v>46255</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1779511507657449</v>
+        <v>0.1764908312132207</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6122,22 +6124,22 @@
         <v>21.20514974257153</v>
       </c>
       <c r="K51" t="n">
-        <v>2.52403903635241</v>
+        <v>1.682696577119724</v>
       </c>
       <c r="L51" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M51" t="n">
-        <v>56.25</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N51" t="n">
-        <v>13.4505860237715</v>
+        <v>13.79407064977819</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.43962428472435</v>
+        <v>2.278955516411552</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6164,7 +6166,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>19.21633696343861</v>
+        <v>19.87927149434318</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6209,7 +6211,7 @@
         <v>46255</v>
       </c>
       <c r="C52" t="n">
-        <v>4.562475657864694</v>
+        <v>4.66052605555773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6266,25 +6268,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>16.65998098876651</v>
+        <v>18.51593523176962</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.5909104772727103</v>
+        <v>0.04474545861297141</v>
       </c>
       <c r="Z52" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="AA52" t="n">
-        <v>36.11111111111111</v>
+        <v>35.48387096774194</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.86472140311879</v>
+        <v>13.37116462006711</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.453130853827394</v>
+        <v>7.958815749994519</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6318,7 +6320,7 @@
         <v>46255</v>
       </c>
       <c r="C53" t="n">
-        <v>1.382094268627908</v>
+        <v>1.365404764774476</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,11 +6337,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6350,22 +6348,22 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>2.474862230679986</v>
+        <v>1.23742521433472</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N53" t="n">
-        <v>17.51835792581486</v>
+        <v>17.90840940822131</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>5.391700607396221</v>
+        <v>6.679915822975446</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6546,7 +6544,7 @@
         <v>46255</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9325224884235341</v>
+        <v>0.938363767050867</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6606,16 +6604,16 @@
         <v>26.27862368424858</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.650171203590359</v>
+        <v>4.052904195038232</v>
       </c>
       <c r="Z55" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA55" t="n">
-        <v>48.14814814814815</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.36572635119501</v>
+        <v>12.30548381211707</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6655,7 +6653,7 @@
         <v>46255</v>
       </c>
       <c r="C56" t="n">
-        <v>1.313250343554996</v>
+        <v>1.316379565823649</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6707,7 +6705,7 @@
         <v>73.71938423294128</v>
       </c>
       <c r="Y56" t="n">
-        <v>3.598778223946808</v>
+        <v>3.369072706345</v>
       </c>
       <c r="Z56" t="n">
         <v>2</v>
@@ -6718,7 +6716,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>6.640187394018382</v>
+        <v>6.862117004739121</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6744,7 +6742,7 @@
         <v>46255</v>
       </c>
       <c r="C57" t="n">
-        <v>1.305948665683061</v>
+        <v>1.278828341381119</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6761,7 +6759,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %79.49: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6772,22 +6774,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>3.442624351078338</v>
+        <v>1.294456055674531</v>
       </c>
       <c r="L57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M57" t="n">
-        <v>70</v>
+        <v>79.48717948717949</v>
       </c>
       <c r="N57" t="n">
-        <v>18.19765533731722</v>
+        <v>18.9729472884561</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>6.339142776063289</v>
+        <v>8.594294577721652</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6814,7 +6816,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>19.48754302619493</v>
+        <v>21.15952600749666</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -6859,7 +6861,7 @@
         <v>46255</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7330836491548254</v>
+        <v>0.7351698769564656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6887,16 +6889,16 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>10.44355726112491</v>
+        <v>10.75786030135211</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M58" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>13.02241985913761</v>
+        <v>14.19416378953196</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6929,22 +6931,22 @@
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.500486155988801</v>
+        <v>2.223019598574383</v>
       </c>
       <c r="Z58" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA58" t="n">
-        <v>36.36363636363637</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB58" t="n">
-        <v>14.37975093818692</v>
+        <v>14.22943621407547</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.589262865053922</v>
+        <v>3.862852366599112</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6978,7 +6980,7 @@
         <v>46255</v>
       </c>
       <c r="C59" t="n">
-        <v>0.79483455879425</v>
+        <v>0.7927484106846868</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7006,22 +7008,22 @@
         <v>11.17103304657197</v>
       </c>
       <c r="K59" t="n">
-        <v>1.599995919999997</v>
+        <v>1.333333333333342</v>
       </c>
       <c r="L59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M59" t="n">
-        <v>60</v>
+        <v>59.32203389830509</v>
       </c>
       <c r="N59" t="n">
-        <v>14.14811524564401</v>
+        <v>14.16144631113641</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.299216867133905</v>
+        <v>6.57894736842104</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7087,7 +7089,7 @@
         <v>46255</v>
       </c>
       <c r="C60" t="n">
-        <v>11.8912261602703</v>
+        <v>11.96424246125442</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7115,22 +7117,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>3.517879588625172</v>
+        <v>4.153515691362331</v>
       </c>
       <c r="L60" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M60" t="n">
-        <v>48.78048780487805</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N60" t="n">
-        <v>13.76700212351024</v>
+        <v>13.51098476889908</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>4.329803150128808</v>
+        <v>3.693091186701691</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7196,7 +7198,7 @@
         <v>46255</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6304435901024956</v>
+        <v>0.6300263843464825</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7215,7 +7217,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -7228,22 +7230,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>2.594037403766647</v>
+        <v>2.52614421933357</v>
       </c>
       <c r="L61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M61" t="n">
-        <v>78.26086956521739</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N61" t="n">
-        <v>21.0271844363258</v>
+        <v>20.52585329832347</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>7.218706645773798</v>
+        <v>7.289707262059575</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7262,7 +7264,7 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>10.31096617322754</v>
+        <v>10.37031927277718</v>
       </c>
       <c r="Z61" t="n">
         <v>21</v>
@@ -7311,7 +7313,7 @@
         <v>46255</v>
       </c>
       <c r="C62" t="n">
-        <v>9.278285675053013</v>
+        <v>9.283501125123307</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7368,25 +7370,25 @@
         <v>72.05882352941177</v>
       </c>
       <c r="X62" t="n">
-        <v>12.1334236033467</v>
+        <v>12.50949992621986</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.5589714924538858</v>
+        <v>0.8356545961002881</v>
       </c>
       <c r="Z62" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AA62" t="n">
-        <v>48.14814814814815</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.76770905719442</v>
+        <v>11.78152481132399</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.449128724002247</v>
+        <v>1.174157303370782</v>
       </c>
       <c r="AE62" t="n">
         <v>30</v>
@@ -7420,7 +7422,7 @@
         <v>46255</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1072296507332104</v>
+        <v>0.1070210377372308</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7448,7 +7450,7 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>9.112000535023368</v>
+        <v>8.899725467695397</v>
       </c>
       <c r="L63" t="n">
         <v>7</v>
@@ -7490,7 +7492,7 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>7.052447110124072</v>
+        <v>7.233274589694805</v>
       </c>
       <c r="Z63" t="n">
         <v>7</v>
@@ -7505,7 +7507,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.171200099660698</v>
+        <v>2.982454536438606</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7539,7 +7541,7 @@
         <v>46255</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1491618740965882</v>
+        <v>0.1483274027111952</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7567,22 +7569,22 @@
         <v>24.42078296285393</v>
       </c>
       <c r="K64" t="n">
-        <v>0.8462616182032034</v>
+        <v>0.2820871590531571</v>
       </c>
       <c r="L64" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M64" t="n">
-        <v>70.58823529411765</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="N64" t="n">
-        <v>15.88543773845759</v>
+        <v>16.28133986699973</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.118881865470203</v>
+        <v>4.704641650969998</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7648,21 +7650,21 @@
         <v>46255</v>
       </c>
       <c r="C65" t="n">
-        <v>6.639267939484252</v>
+        <v>6.613190689132782</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7676,7 +7678,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>17.194885914203</v>
+        <v>16.73457607164919</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -7718,22 +7720,22 @@
         <v>21.96943581422117</v>
       </c>
       <c r="Y65" t="n">
-        <v>3.914546187858547</v>
+        <v>4.29194388547105</v>
       </c>
       <c r="Z65" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA65" t="n">
-        <v>48.27586206896552</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="AB65" t="n">
-        <v>10.41068873994096</v>
+        <v>10.27316155150781</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.08893522250363883</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7767,7 +7769,7 @@
         <v>46255</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4639664334551395</v>
+        <v>0.4635491878530878</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7827,22 +7829,22 @@
         <v>12.69724877030836</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.330972217191906</v>
+        <v>1.419705399018245</v>
       </c>
       <c r="Z66" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA66" t="n">
-        <v>38.33333333333334</v>
+        <v>37.70491803278689</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.18517533420831</v>
+        <v>11.17445057007504</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.73200951476449</v>
+        <v>4.64625777344364</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7876,7 +7878,7 @@
         <v>46255</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02774619520843605</v>
+        <v>0.02753757741424229</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7904,22 +7906,22 @@
         <v>14.0514682678307</v>
       </c>
       <c r="K67" t="n">
-        <v>3.100781491497107</v>
+        <v>2.325588444204296</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M67" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="N67" t="n">
-        <v>6.573256403145478</v>
+        <v>7.077382387711928</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0.8721742895586582</v>
+        <v>1.636356634986491</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7965,7 +7967,7 @@
         <v>46255</v>
       </c>
       <c r="C68" t="n">
-        <v>4.276669057641073</v>
+        <v>4.182790956375782</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8025,10 +8027,10 @@
         <v>143.1366383982815</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.866919106693199</v>
+        <v>4.021059906790169</v>
       </c>
       <c r="Z68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
@@ -8036,7 +8038,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>6.249758835121932</v>
+        <v>4.145638709226929</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8070,7 +8072,7 @@
         <v>46255</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4201566449371859</v>
+        <v>0.4189049479770694</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8098,22 +8100,22 @@
         <v>18.0901893667493</v>
       </c>
       <c r="K69" t="n">
-        <v>7.700527120192469</v>
+        <v>7.379674352483812</v>
       </c>
       <c r="L69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M69" t="n">
-        <v>69.23076923076923</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N69" t="n">
-        <v>17.54135150689928</v>
+        <v>20.57486714421613</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>0.2780607373196409</v>
+        <v>0.5776937313852537</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8132,7 +8134,7 @@
         <v>11.44384654025008</v>
       </c>
       <c r="Y69" t="n">
-        <v>3.358928766610403</v>
+        <v>3.646834090833739</v>
       </c>
       <c r="Z69" t="n">
         <v>19</v>
@@ -8141,13 +8143,13 @@
         <v>36.8421052631579</v>
       </c>
       <c r="AB69" t="n">
-        <v>14.06027699497266</v>
+        <v>14.05521575818754</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.732866264500911</v>
+        <v>2.442229984829591</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8173,7 +8175,7 @@
         <v>46255</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4326737330333755</v>
+        <v>0.4339254299934919</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8201,13 +8203,13 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>13.45394452641913</v>
+        <v>13.78215940667391</v>
       </c>
       <c r="L70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M70" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N70" t="n">
         <v>6.838424675154897</v>
@@ -8243,22 +8245,22 @@
         <v>14.32919111790623</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.7655495354501829</v>
+        <v>0.4784707264028243</v>
       </c>
       <c r="Z70" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA70" t="n">
-        <v>47.05882352941177</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="AB70" t="n">
-        <v>10.16790083148568</v>
+        <v>10.21589682510675</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>7.290261023951783</v>
+        <v>7.557690610761759</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8292,7 +8294,7 @@
         <v>46255</v>
       </c>
       <c r="C71" t="n">
-        <v>3.127183734891296</v>
+        <v>3.125097745748651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8320,22 +8322,22 @@
         <v>14.92600999981897</v>
       </c>
       <c r="K71" t="n">
-        <v>1.215386715639033</v>
+        <v>1.147870952045826</v>
       </c>
       <c r="L71" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M71" t="n">
-        <v>60.29411764705883</v>
+        <v>61.19402985074627</v>
       </c>
       <c r="N71" t="n">
-        <v>16.85799615847782</v>
+        <v>16.85758192111756</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.775191707329359</v>
+        <v>0.8424587091488744</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8516,7 +8518,7 @@
         <v>46255</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07176459421895336</v>
+        <v>0.07093012304217833</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8533,7 +8535,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8544,22 +8550,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>9.081495616888645</v>
+        <v>7.813107423483867</v>
       </c>
       <c r="L73" t="n">
         <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>57.14285714285715</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N73" t="n">
-        <v>8.294249049343749</v>
+        <v>10.73778244840042</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>0.8420350105367902</v>
+        <v>2.028410671743419</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8586,22 +8592,22 @@
         <v>15.4234441942493</v>
       </c>
       <c r="Y73" t="n">
-        <v>5.494506442458613</v>
+        <v>6.593406412269054</v>
       </c>
       <c r="Z73" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA73" t="n">
-        <v>55</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB73" t="n">
-        <v>14.16303952989258</v>
+        <v>13.36571475343514</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>4.767440905219056</v>
+        <v>3.647059010380616</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8635,7 +8641,7 @@
         <v>46255</v>
       </c>
       <c r="C74" t="n">
-        <v>5.533592524581926</v>
+        <v>5.549238874792808</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8663,7 +8669,7 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>17.07476514477533</v>
+        <v>17.40579652595755</v>
       </c>
       <c r="L74" t="n">
         <v>3</v>
@@ -8705,7 +8711,7 @@
         <v>32.26405389680429</v>
       </c>
       <c r="Y74" t="n">
-        <v>4.419819702010386</v>
+        <v>4.14956471530542</v>
       </c>
       <c r="Z74" t="n">
         <v>23</v>
@@ -8720,7 +8726,7 @@
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>5.838219053984128</v>
+        <v>6.103712797252969</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8863,16 +8869,16 @@
         <v>46255</v>
       </c>
       <c r="C76" t="n">
-        <v>1.90572542376687</v>
+        <v>1.934931976079071</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8880,11 +8886,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>5</v>
       </c>
@@ -8895,22 +8897,22 @@
         <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>9.956153661014877</v>
+        <v>11.64130731111472</v>
       </c>
       <c r="L76" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M76" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N76" t="n">
-        <v>8.050242483147439</v>
+        <v>8.171123468305536</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>0.03987620294567673</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>40</v>
@@ -8934,25 +8936,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X76" t="n">
-        <v>10.97927971513522</v>
+        <v>11.76167345580381</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.9219072756162405</v>
+        <v>0.1076989463088873</v>
       </c>
       <c r="Z76" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="AA76" t="n">
-        <v>40.35087719298246</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.23721050399967</v>
+        <v>9.609892728943459</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.106733930523298</v>
+        <v>3.896497540485166</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8986,7 +8988,7 @@
         <v>46255</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5286380222542691</v>
+        <v>0.5257173829406027</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9014,16 +9016,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>8.876191611321849</v>
+        <v>8.274668315312383</v>
       </c>
       <c r="L77" t="n">
         <v>27</v>
       </c>
       <c r="M77" t="n">
-        <v>62.96296296296296</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N77" t="n">
-        <v>15.76565179817866</v>
+        <v>15.00075501371142</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9056,22 +9058,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>6.368466611391543</v>
+        <v>6.885765643813602</v>
       </c>
       <c r="Z77" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA77" t="n">
-        <v>40</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.70708425880333</v>
+        <v>11.09045251573717</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>3.878536703586954</v>
+        <v>3.344530917017086</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9105,7 +9107,7 @@
         <v>46255</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04819075739780847</v>
+        <v>0.04798213960361472</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9133,7 +9135,7 @@
         <v>19.53698884929083</v>
       </c>
       <c r="K78" t="n">
-        <v>3.124996861049123</v>
+        <v>2.678568738042109</v>
       </c>
       <c r="L78" t="n">
         <v>47</v>
@@ -9142,13 +9144,13 @@
         <v>63.82978723404256</v>
       </c>
       <c r="N78" t="n">
-        <v>18.33546205694923</v>
+        <v>18.11052823619765</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.8484879181425375</v>
+        <v>1.286959175803459</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9323,7 +9325,7 @@
         <v>46255</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1285086866027739</v>
+        <v>0.1283000738154122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9351,7 +9353,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.213887456783239</v>
+        <v>5.043089957316416</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9362,7 +9364,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.548936132773029</v>
+        <v>4.71893015018674</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9389,22 +9391,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.30151952812763</v>
+        <v>6.453623651977358</v>
       </c>
       <c r="Z80" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA80" t="n">
-        <v>35.29411764705883</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.48064104902586</v>
+        <v>11.40307523818483</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.812708662209561</v>
+        <v>1.653058523902218</v>
       </c>
       <c r="AE80" t="n">
         <v>26</v>
@@ -9438,7 +9440,7 @@
         <v>46255</v>
       </c>
       <c r="C81" t="n">
-        <v>1.222501464558357</v>
+        <v>1.233975518550113</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9495,25 +9497,25 @@
         <v>64.58333333333333</v>
       </c>
       <c r="X81" t="n">
-        <v>30.69132459397106</v>
+        <v>30.91171973579283</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.180439762177643</v>
+        <v>0.4208754100347045</v>
       </c>
       <c r="Z81" t="n">
         <v>17</v>
       </c>
       <c r="AA81" t="n">
-        <v>58.8235294117647</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AB81" t="n">
-        <v>12.52862678478392</v>
+        <v>12.10152155368538</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>8.924913465104389</v>
+        <v>9.619611167911991</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9547,11 +9549,11 @@
         <v>46255</v>
       </c>
       <c r="C82" t="n">
-        <v>5.345836322051342</v>
+        <v>5.3823444725434</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9561,7 +9563,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9607,22 +9609,22 @@
         <v>16.65327680511959</v>
       </c>
       <c r="Y82" t="n">
-        <v>4.379607502643101</v>
+        <v>3.726590188027012</v>
       </c>
       <c r="Z82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA82" t="n">
-        <v>37.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB82" t="n">
-        <v>8.312827786585837</v>
+        <v>12.95948113262313</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>0.2839930698486426</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9656,7 +9658,7 @@
         <v>46255</v>
       </c>
       <c r="C83" t="n">
-        <v>5.830873178588684</v>
+        <v>5.846519528799566</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9716,22 +9718,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>3.077022281640096</v>
+        <v>2.816942734989758</v>
       </c>
       <c r="Z83" t="n">
         <v>57</v>
       </c>
       <c r="AA83" t="n">
-        <v>36.8421052631579</v>
+        <v>45.6140350877193</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.81671318944869</v>
+        <v>12.28672320010427</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.015773748567174</v>
+        <v>3.275321187241842</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9765,7 +9767,7 @@
         <v>46255</v>
       </c>
       <c r="C84" t="n">
-        <v>2.175885832955144</v>
+        <v>2.182144277492452</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9793,22 +9795,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>4.16520673010139</v>
+        <v>4.464814438908493</v>
       </c>
       <c r="L84" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M84" t="n">
-        <v>50</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="N84" t="n">
-        <v>11.61841236501015</v>
+        <v>10.80372727629718</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0.8014127712160368</v>
+        <v>0.5123117903057084</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9874,7 +9876,7 @@
         <v>46255</v>
       </c>
       <c r="C85" t="n">
-        <v>6.315910035126024</v>
+        <v>6.289832784774555</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9902,22 +9904,22 @@
         <v>15.93296998857089</v>
       </c>
       <c r="K85" t="n">
-        <v>2.088425149238327</v>
+        <v>1.666920503700609</v>
       </c>
       <c r="L85" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M85" t="n">
-        <v>58</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N85" t="n">
-        <v>14.13006199155937</v>
+        <v>15.72056805328279</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.790641634563198</v>
+        <v>6.229242968039816</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9983,7 +9985,7 @@
         <v>46255</v>
       </c>
       <c r="C86" t="n">
-        <v>4.539527868440873</v>
+        <v>4.489459356880578</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10008,25 +10010,25 @@
         <v>10</v>
       </c>
       <c r="J86" t="n">
-        <v>12.2426962665338</v>
+        <v>12.64935661172912</v>
       </c>
       <c r="K86" t="n">
-        <v>0.8341070549396479</v>
+        <v>0.1862168967971867</v>
       </c>
       <c r="L86" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M86" t="n">
-        <v>60</v>
+        <v>64.78873239436619</v>
       </c>
       <c r="N86" t="n">
-        <v>15.14601166450642</v>
+        <v>14.81634309904413</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
       </c>
       <c r="P86" t="n">
-        <v>5.123160303532726</v>
+        <v>5.802976979549657</v>
       </c>
       <c r="Q86" t="n">
         <v>54</v>
@@ -10053,7 +10055,7 @@
         <v>88.01181128002702</v>
       </c>
       <c r="Y86" t="n">
-        <v>11.51070640486815</v>
+        <v>12.48669495427911</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10098,7 +10100,7 @@
         <v>46255</v>
       </c>
       <c r="C87" t="n">
-        <v>5.862165879010448</v>
+        <v>5.883027679291623</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10112,7 +10114,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -10126,16 +10128,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>8.71193075348935</v>
+        <v>9.098805951900335</v>
       </c>
       <c r="L87" t="n">
         <v>18</v>
       </c>
       <c r="M87" t="n">
-        <v>61.11111111111111</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N87" t="n">
-        <v>9.954913288470394</v>
+        <v>10.97653318407152</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10164,17 +10166,27 @@
       <c r="W87" t="n">
         <v>63.63636363636363</v>
       </c>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
+      <c r="X87" t="n">
+        <v>10.54958794594156</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>1.312335958005262</v>
+      </c>
       <c r="Z87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>44.64285714285715</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>11.34288488421424</v>
+      </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
-      <c r="AD87" t="inlineStr"/>
+      <c r="AD87" t="n">
+        <v>2.72340425531914</v>
+      </c>
       <c r="AE87" t="n">
         <v>43</v>
       </c>
@@ -10207,7 +10219,7 @@
         <v>46255</v>
       </c>
       <c r="C88" t="n">
-        <v>1.10776156301189</v>
+        <v>1.145312867355115</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10235,7 +10247,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>24.10429999853672</v>
+        <v>28.31123269520586</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10270,25 +10282,25 @@
         <v>61.53846153846154</v>
       </c>
       <c r="X88" t="n">
-        <v>27.20319322085054</v>
+        <v>28.54494720514669</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.436175652393824</v>
+        <v>0.1818153999999961</v>
       </c>
       <c r="Z88" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA88" t="n">
-        <v>37.03703703703704</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB88" t="n">
-        <v>14.98672127802329</v>
+        <v>13.61845768572016</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>3.652813295744517</v>
+        <v>5.82878222371519</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10322,7 +10334,7 @@
         <v>46255</v>
       </c>
       <c r="C89" t="n">
-        <v>2.215523126232397</v>
+        <v>2.269763934220436</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10339,11 +10351,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>5</v>
       </c>
@@ -10354,17 +10362,13 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>20.34357218609413</v>
+        <v>23.28984366223126</v>
       </c>
       <c r="L89" t="n">
-        <v>4</v>
-      </c>
-      <c r="M89" t="n">
-        <v>100</v>
-      </c>
-      <c r="N89" t="n">
-        <v>13.47952249834024</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
         <v>4</v>
       </c>
@@ -10393,25 +10397,25 @@
         <v>76.08695652173913</v>
       </c>
       <c r="X89" t="n">
-        <v>20.95675253601343</v>
+        <v>24.19638141496434</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.5069418094179934</v>
+        <v>0.7299228386567713</v>
       </c>
       <c r="Z89" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="AA89" t="n">
-        <v>51.02040816326531</v>
+        <v>39.02439024390244</v>
       </c>
       <c r="AB89" t="n">
-        <v>12.46435165776869</v>
+        <v>12.87161838633467</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>9.541427676690528</v>
+        <v>9.338239101271784</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10445,21 +10449,21 @@
         <v>46255</v>
       </c>
       <c r="C90" t="n">
-        <v>2.89979023908346</v>
+        <v>3.00201293320424</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10473,17 +10477,13 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>14.31045314008395</v>
+        <v>18.34009719111018</v>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
-      </c>
-      <c r="M90" t="n">
-        <v>70</v>
-      </c>
-      <c r="N90" t="n">
-        <v>15.52634973642465</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
         <v>8</v>
       </c>
@@ -10515,22 +10515,22 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>4.649897035999495</v>
+        <v>1.288638597956515</v>
       </c>
       <c r="Z90" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AA90" t="n">
-        <v>50</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="AB90" t="n">
-        <v>10.86839151062816</v>
+        <v>12.76646402340407</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>1.733702562436812</v>
       </c>
       <c r="AE90" t="n">
         <v>23</v>
@@ -10564,7 +10564,7 @@
         <v>46255</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2301056514686849</v>
+        <v>0.2298970486949873</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10592,22 +10592,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>2.783825379595828</v>
+        <v>2.69064648143067</v>
       </c>
       <c r="L91" t="n">
         <v>65</v>
       </c>
       <c r="M91" t="n">
-        <v>61.53846153846154</v>
+        <v>60</v>
       </c>
       <c r="N91" t="n">
-        <v>12.55561191083563</v>
+        <v>12.9767005168435</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.2103196875634872</v>
+        <v>0.3012479998607098</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10673,26 +10673,26 @@
         <v>46255</v>
       </c>
       <c r="C92" t="n">
-        <v>1.131752665253796</v>
+        <v>1.146355941305588</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -10705,22 +10705,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>7.412261455149549</v>
+        <v>8.798227623848586</v>
       </c>
       <c r="L92" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M92" t="n">
-        <v>80.95238095238095</v>
+        <v>75</v>
       </c>
       <c r="N92" t="n">
-        <v>11.3394348166478</v>
+        <v>8.746314114254508</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.5471801234683715</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10747,16 +10747,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>6.325403086919723</v>
+        <v>5.116697298314199</v>
       </c>
       <c r="Z92" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AA92" t="n">
-        <v>52.38095238095238</v>
+        <v>53.19148936170212</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.63419670347171</v>
+        <v>11.12706433169667</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10796,7 +10796,7 @@
         <v>46255</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04234945394493321</v>
+        <v>0.0419322183565457</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10824,22 +10824,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>4.71791643493169</v>
+        <v>3.686213841192076</v>
       </c>
       <c r="L93" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M93" t="n">
-        <v>61.22448979591837</v>
+        <v>61.40350877192982</v>
       </c>
       <c r="N93" t="n">
-        <v>19.60927954851992</v>
+        <v>19.00391756101635</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>1.224321117833704</v>
+        <v>2.231527290939339</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10905,7 +10905,7 @@
         <v>46255</v>
       </c>
       <c r="C94" t="n">
-        <v>8.3342892123298</v>
+        <v>8.428167313595091</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10962,10 +10962,10 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>50.4132727790992</v>
+        <v>50.97347118795989</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.8069522036002419</v>
+        <v>0.06184291898577721</v>
       </c>
       <c r="Z94" t="n">
         <v>7</v>
@@ -10974,13 +10974,13 @@
         <v>42.85714285714285</v>
       </c>
       <c r="AB94" t="n">
-        <v>9.735429777718856</v>
+        <v>14.2160206715065</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>5.235294117647071</v>
+        <v>5.941831683168319</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11014,7 +11014,7 @@
         <v>46255</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1410257746989636</v>
+        <v>0.1408171518979378</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>5.714424364741766</v>
+        <v>5.558038488706796</v>
       </c>
       <c r="L95" t="n">
         <v>10</v>
@@ -11051,13 +11051,13 @@
         <v>60</v>
       </c>
       <c r="N95" t="n">
-        <v>19.08560282706251</v>
+        <v>19.32811751426809</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>0.2701387601307115</v>
+        <v>0.418690530461574</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11084,22 +11084,22 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>5.586586988545816</v>
+        <v>5.726255008231618</v>
       </c>
       <c r="Z95" t="n">
         <v>28</v>
       </c>
       <c r="AA95" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.73253308720716</v>
+        <v>11.91893305379972</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>0.4378752957527654</v>
+        <v>0.2903724592592472</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11133,7 +11133,7 @@
         <v>46255</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1320551941108999</v>
+        <v>0.1318465813235382</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11161,22 +11161,22 @@
         <v>13.52465198145173</v>
       </c>
       <c r="K96" t="n">
-        <v>2.926826293872753</v>
+        <v>2.764228735541008</v>
       </c>
       <c r="L96" t="n">
         <v>64</v>
       </c>
       <c r="M96" t="n">
-        <v>57.8125</v>
+        <v>56.25</v>
       </c>
       <c r="N96" t="n">
-        <v>14.18034793826052</v>
+        <v>14.45330189893711</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.872041003122153</v>
+        <v>7.04113810174154</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11242,7 +11242,7 @@
         <v>46255</v>
       </c>
       <c r="C97" t="n">
-        <v>1.932845827969508</v>
+        <v>1.943276728110096</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11270,16 +11270,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>8.142380611076462</v>
+        <v>8.725987620386988</v>
       </c>
       <c r="L97" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M97" t="n">
-        <v>53.57142857142857</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N97" t="n">
-        <v>14.4630255951897</v>
+        <v>12.28821615530306</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11312,22 +11312,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>5.603667767971354</v>
+        <v>5.094243425428502</v>
       </c>
       <c r="Z97" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AA97" t="n">
-        <v>48.48484848484848</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.4083613888801</v>
+        <v>11.78962056378606</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.4198597791431724</v>
+        <v>0.954374747394604</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11361,7 +11361,7 @@
         <v>46255</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6375366055359835</v>
+        <v>0.6371193997799703</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>6.456792739852624</v>
+        <v>6.387127113891555</v>
       </c>
       <c r="L98" t="n">
         <v>34</v>
@@ -11398,13 +11398,13 @@
         <v>52.94117647058823</v>
       </c>
       <c r="N98" t="n">
-        <v>13.23775944396483</v>
+        <v>13.24455457470219</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.328305473945559</v>
+        <v>3.395968087605872</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11431,7 +11431,7 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>3.279945100608272</v>
+        <v>3.343238977815532</v>
       </c>
       <c r="Z98" t="n">
         <v>39</v>
@@ -11440,13 +11440,13 @@
         <v>38.46153846153846</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.78804775566407</v>
+        <v>11.61064391364317</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>4.880120161533741</v>
+        <v>4.817832682305223</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11480,7 +11480,7 @@
         <v>46255</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4639664334551395</v>
+        <v>0.4706422032865757</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11508,16 +11508,16 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>5.334234250141567</v>
+        <v>6.849833337747802</v>
       </c>
       <c r="L99" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M99" t="n">
-        <v>60</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N99" t="n">
-        <v>13.58459766824227</v>
+        <v>11.06927854023787</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11589,7 +11589,7 @@
         <v>46255</v>
       </c>
       <c r="C100" t="n">
-        <v>330.6674594959516</v>
+        <v>329.4001051288702</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -11621,16 +11621,16 @@
         <v>15.65236426997335</v>
       </c>
       <c r="K100" t="n">
-        <v>7.890011039559863</v>
+        <v>7.47649929920331</v>
       </c>
       <c r="L100" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M100" t="n">
-        <v>76.47058823529412</v>
+        <v>75</v>
       </c>
       <c r="N100" t="n">
-        <v>11.66125686104412</v>
+        <v>11.92641646772385</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11702,7 +11702,7 @@
         <v>46255</v>
       </c>
       <c r="C101" t="n">
-        <v>347.7902099065632</v>
+        <v>349.4660399530825</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11730,16 +11730,16 @@
         <v>11.19277381576541</v>
       </c>
       <c r="K101" t="n">
-        <v>10.13439322464931</v>
+        <v>10.66507672310264</v>
       </c>
       <c r="L101" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M101" t="n">
-        <v>41.66666666666666</v>
+        <v>30</v>
       </c>
       <c r="N101" t="n">
-        <v>7.638293933302016</v>
+        <v>5.693386098790065</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11769,25 +11769,25 @@
         <v>53.84615384615385</v>
       </c>
       <c r="X101" t="n">
-        <v>10.7755255729769</v>
+        <v>11.24226228404977</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.5787671464535071</v>
+        <v>0.5188545693841862</v>
       </c>
       <c r="Z101" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA101" t="n">
-        <v>37.5</v>
+        <v>36.58536585365854</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.1809240817331</v>
+        <v>11.30094056760116</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>5.452791821171942</v>
+        <v>5.509732931692768</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>46255</v>
       </c>
       <c r="C102" t="n">
-        <v>420.4109515994102</v>
+        <v>422.4796109751565</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11878,25 +11878,25 @@
         <v>47.22222222222222</v>
       </c>
       <c r="X102" t="n">
-        <v>10.50083949700029</v>
+        <v>11.14205602519744</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.1533516138794599</v>
+        <v>0.2409336471784318</v>
       </c>
       <c r="Z102" t="n">
         <v>36</v>
       </c>
       <c r="AA102" t="n">
-        <v>33.33333333333334</v>
+        <v>36.11111111111111</v>
       </c>
       <c r="AB102" t="n">
-        <v>13.55094174897825</v>
+        <v>13.18660135094703</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.854092214871242</v>
+        <v>4.770560237592846</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11930,7 +11930,7 @@
         <v>46255</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7339181403589287</v>
+        <v>0.7330836491548254</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11947,11 +11947,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>5</v>
       </c>
@@ -11962,13 +11958,13 @@
         <v>16.13876216849247</v>
       </c>
       <c r="K103" t="n">
-        <v>12.87539349135827</v>
+        <v>12.74705012736652</v>
       </c>
       <c r="L103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M103" t="n">
-        <v>78.57142857142857</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N103" t="n">
         <v>12.84408537336701</v>
@@ -12004,22 +12000,22 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.799609567543426</v>
+        <v>2.910129891801416</v>
       </c>
       <c r="Z103" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA103" t="n">
-        <v>36.73469387755102</v>
+        <v>35.41666666666666</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.3889295216024</v>
+        <v>11.32844267601609</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>5.350174427612265</v>
+        <v>5.242431679562809</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -12053,7 +12049,7 @@
         <v>46255</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0475649040152272</v>
+        <v>0.04777352180942095</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12081,22 +12077,22 @@
         <v>21.43553010850433</v>
       </c>
       <c r="K104" t="n">
-        <v>2.242150204106275</v>
+        <v>2.690580244927521</v>
       </c>
       <c r="L104" t="n">
         <v>42</v>
       </c>
       <c r="M104" t="n">
-        <v>52.38095238095238</v>
+        <v>50</v>
       </c>
       <c r="N104" t="n">
-        <v>10.62247356697882</v>
+        <v>10.86271338555909</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>1.719300496306597</v>
+        <v>1.27511184760023</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -679,7 +679,7 @@
         <v>46255</v>
       </c>
       <c r="C2" t="n">
-        <v>0.402632729571728</v>
+        <v>0.4013810326116116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>2.702003328616165</v>
+        <v>2.382725296994082</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -716,13 +716,13 @@
         <v>44.82758620689656</v>
       </c>
       <c r="N2" t="n">
-        <v>12.63834162191096</v>
+        <v>12.51278923498183</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>7.105992517042159</v>
+        <v>7.43999994228477</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -1016,7 +1016,7 @@
         <v>46255</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2344866303622039</v>
+        <v>0.2326090652076279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>16.29245538545801</v>
+        <v>17.18852105094173</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2676157885187713</v>
+        <v>0.5410231667129395</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>59.09090909090909</v>
+        <v>67.5</v>
       </c>
       <c r="N5" t="n">
-        <v>14.51905653683128</v>
+        <v>13.73332433230867</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.725091436545468</v>
+        <v>2.445744787388615</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1125,7 +1125,7 @@
         <v>46255</v>
       </c>
       <c r="C6" t="n">
-        <v>1.726313973267311</v>
+        <v>1.723184671306581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>5.487071523498166</v>
+        <v>5.295854337712735</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1191,16 +1191,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.796009721906936</v>
+        <v>5.966773983826201</v>
       </c>
       <c r="Z6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA6" t="n">
         <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.82269995469782</v>
+        <v>11.59356805429494</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1240,11 +1240,11 @@
         <v>46255</v>
       </c>
       <c r="C7" t="n">
-        <v>2.257246726794749</v>
+        <v>2.217609433517497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1300,22 +1300,22 @@
         <v>14.22876300591287</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.501329181561742</v>
+        <v>6.178287565368246</v>
       </c>
       <c r="Z7" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>48.64864864864865</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.01021328205966</v>
+        <v>9.2049799707391</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.5221756639800068</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
@@ -1349,7 +1349,7 @@
         <v>46255</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3972086965464467</v>
+        <v>0.4007551642085341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>30.27139917619635</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.054982121361449</v>
+        <v>2.189411015047904</v>
       </c>
       <c r="Z8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>33.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="AB8" t="n">
         <v>15.9993759340716</v>
@@ -1424,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.100847869076686</v>
+        <v>5.940654325112016</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1567,7 +1567,7 @@
         <v>46255</v>
       </c>
       <c r="C10" t="n">
-        <v>1.938061278039802</v>
+        <v>1.929716526008777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,22 +1595,22 @@
         <v>10.51321892894885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.541125532165343</v>
+        <v>0.1082234505889401</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>44.18604651162791</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="N10" t="n">
-        <v>9.686680376807971</v>
+        <v>10.16882093237464</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.429494089051401</v>
+        <v>5.885407158702716</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1676,7 +1676,7 @@
         <v>46255</v>
       </c>
       <c r="C11" t="n">
-        <v>8.480321814298032</v>
+        <v>8.41252096338421</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,22 +1736,22 @@
         <v>22.18106016526054</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5504587155963359</v>
+        <v>1.345565749235478</v>
       </c>
       <c r="Z11" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA11" t="n">
-        <v>48.64864864864865</v>
+        <v>45</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.53596468722206</v>
+        <v>12.84589812680843</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.457564575645753</v>
+        <v>0.6633601983880966</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1785,7 +1785,7 @@
         <v>46255</v>
       </c>
       <c r="C12" t="n">
-        <v>7.035642144826595</v>
+        <v>7.004349444404832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,11 +1802,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1817,16 +1813,16 @@
         <v>11.16401078100182</v>
       </c>
       <c r="K12" t="n">
-        <v>7.148530579825252</v>
+        <v>6.671961874503562</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N12" t="n">
-        <v>18.95023129685582</v>
+        <v>17.80846345924088</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1859,13 +1855,13 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.813542925791481</v>
+        <v>5.236907449472161</v>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>30</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB12" t="n">
         <v>10.19016848477012</v>
@@ -1908,7 +1904,7 @@
         <v>46255</v>
       </c>
       <c r="C13" t="n">
-        <v>0.238658986454697</v>
+        <v>0.2378245152779219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,7 +1932,7 @@
         <v>45.34593765398164</v>
       </c>
       <c r="K13" t="n">
-        <v>13.04347533940535</v>
+        <v>12.64821881336995</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1972,22 +1968,22 @@
         <v>16.60079365870428</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.050852577994756</v>
+        <v>3.389835284400977</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.96446601497775</v>
+        <v>11.39090220800516</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>7.167827264902737</v>
+        <v>6.842100657894557</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2011,7 +2007,7 @@
         <v>46255</v>
       </c>
       <c r="C14" t="n">
-        <v>8.709801617390967</v>
+        <v>8.688939817109791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,22 +2067,22 @@
         <v>12.93345142071747</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.536033353186427</v>
+        <v>0.7742703990470612</v>
       </c>
       <c r="Z14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>45.65217391304348</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.39046602360439</v>
+        <v>12.11589101364306</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.471856287425144</v>
+        <v>1.235294117647057</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2120,7 +2116,7 @@
         <v>46255</v>
       </c>
       <c r="C15" t="n">
-        <v>14.3216258930273</v>
+        <v>14.40507309415201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,22 +2176,22 @@
         <v>38.77434577704333</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.830856334041054</v>
+        <v>2.264685067232841</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>35.29411764705883</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.03006502530144</v>
+        <v>10.100436433351</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>7.378004369992707</v>
+        <v>7.914554670528595</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2348,7 +2344,7 @@
         <v>46255</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6980358182152917</v>
+        <v>0.698870309419395</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,25 +2369,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>14.75338697646304</v>
+        <v>15.57257289886932</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4804800109659224</v>
+        <v>1.576714576267091</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M17" t="n">
-        <v>71.875</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N17" t="n">
-        <v>15.7891862097217</v>
+        <v>17.64065595520045</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.483562964879797</v>
+        <v>6.32358060656717</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2457,7 +2453,7 @@
         <v>46255</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09721598618100998</v>
+        <v>0.09742460898203581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,22 +2481,22 @@
         <v>20.7015863320355</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4310340638005394</v>
+        <v>0.6465562681147397</v>
       </c>
       <c r="L18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>72.22222222222223</v>
+        <v>71.05263157894737</v>
       </c>
       <c r="N18" t="n">
-        <v>15.88557305699444</v>
+        <v>15.51418388438247</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>9.52789745261471</v>
+        <v>9.293356950006725</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2566,7 +2562,7 @@
         <v>46255</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02545139696888869</v>
+        <v>0.02524277917469493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,22 +2590,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>3.271635229340042</v>
+        <v>2.425147283288864</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>57.57575757575758</v>
+        <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>15.69071474462519</v>
+        <v>19.31962096524373</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>6.51521083763027</v>
+        <v>7.395500926896892</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2675,7 +2671,7 @@
         <v>46255</v>
       </c>
       <c r="C20" t="n">
-        <v>1.745089625438924</v>
+        <v>1.73570171976535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,16 +2699,16 @@
         <v>15.90954673249845</v>
       </c>
       <c r="K20" t="n">
-        <v>4.75632935229513</v>
+        <v>4.192780910809257</v>
       </c>
       <c r="L20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>57.57575757575758</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N20" t="n">
-        <v>11.54120742415455</v>
+        <v>11.01224316795551</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -2784,7 +2780,7 @@
         <v>46255</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9563049280183765</v>
+        <v>0.9521325521071731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,22 +2808,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>2.939020238040979</v>
+        <v>2.489895407894926</v>
       </c>
       <c r="L21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>52.63157894736842</v>
+        <v>56.89655172413793</v>
       </c>
       <c r="N21" t="n">
-        <v>16.97221783368339</v>
+        <v>16.84555044496366</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.916483322121956</v>
+        <v>5.376241794545367</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2893,7 +2889,7 @@
         <v>46255</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3433852134353002</v>
+        <v>0.338378386166032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,16 +2949,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.41501331070673</v>
+        <v>7.779556235145558</v>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA22" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.07750348112833</v>
+        <v>10.89827904879843</v>
       </c>
       <c r="AC22" t="n">
         <v>6</v>
@@ -2994,7 +2990,7 @@
         <v>46255</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7610384646608712</v>
+        <v>0.7593695621533597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,22 +3018,22 @@
         <v>26.4735215749153</v>
       </c>
       <c r="K23" t="n">
-        <v>1.899442219094305</v>
+        <v>1.675984085858895</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N23" t="n">
-        <v>19.52872039775613</v>
+        <v>20.58908139023668</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.042762269727817</v>
+        <v>3.269224236211166</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3064,7 +3060,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>25.07692860149599</v>
+        <v>25.24122949761842</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3109,7 +3105,7 @@
         <v>46255</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1785770191688224</v>
+        <v>0.1850441661992328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,22 +3133,22 @@
         <v>23.5093122581746</v>
       </c>
       <c r="K24" t="n">
-        <v>5.679012573083342</v>
+        <v>9.506166344155154</v>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
-        <v>44.44444444444444</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N24" t="n">
-        <v>12.17683750688129</v>
+        <v>10.64091777321344</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.088784822746572</v>
+        <v>0.4509642446004714</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3179,16 +3175,16 @@
         <v>12.34567843316572</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.934065246709386</v>
+        <v>2.527477806544887</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>53.84615384615385</v>
+        <v>56.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>15.2747307352476</v>
+        <v>13.49437352217959</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3228,7 +3224,7 @@
         <v>46255</v>
       </c>
       <c r="C25" t="n">
-        <v>3.554850640655403</v>
+        <v>3.54233375137217</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,22 +3252,22 @@
         <v>15.86762151234635</v>
       </c>
       <c r="K25" t="n">
-        <v>1.67063705136703</v>
+        <v>1.312647297093372</v>
       </c>
       <c r="L25" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M25" t="n">
-        <v>58.33333333333334</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N25" t="n">
-        <v>16.76352102277555</v>
+        <v>17.66168357682097</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>6.225359781541639</v>
+        <v>6.600708678844769</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3337,7 +3333,7 @@
         <v>46255</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4518665909610014</v>
+        <v>0.4506148940008851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3432,7 @@
         <v>46255</v>
       </c>
       <c r="C27" t="n">
-        <v>44.66511440199775</v>
+        <v>44.85287060452833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3464,7 +3460,7 @@
         <v>60.44609892941529</v>
       </c>
       <c r="K27" t="n">
-        <v>35.49993988382736</v>
+        <v>36.06953327894855</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3492,7 +3488,7 @@
         <v>36.63912667406974</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.8337193144974608</v>
+        <v>0.416859657248736</v>
       </c>
       <c r="Z27" t="n">
         <v>5</v>
@@ -3507,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.201307800093412</v>
+        <v>4.602325581395339</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3531,7 +3527,7 @@
         <v>46255</v>
       </c>
       <c r="C28" t="n">
-        <v>1.590712271439668</v>
+        <v>1.586539975011923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3591,22 +3587,22 @@
         <v>18.63435792130579</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.836410459743633</v>
+        <v>4.088638979207293</v>
       </c>
       <c r="Z28" t="n">
         <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>44.11764705882353</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.57972711841415</v>
+        <v>10.61912843879964</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.249905136237285</v>
+        <v>1.992841098749865</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3640,7 +3636,7 @@
         <v>46255</v>
       </c>
       <c r="C29" t="n">
-        <v>0.417653251225571</v>
+        <v>0.4151498176679176</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3668,10 +3664,10 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>15.53641133785888</v>
+        <v>14.84388056400452</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3706,7 +3702,7 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.828630553173921</v>
+        <v>9.375116100935465</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -3717,7 +3713,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.284799662364677</v>
+        <v>0.6895279444004698</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3751,7 +3747,7 @@
         <v>46255</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4074309738860089</v>
+        <v>0.4057620313238409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3775,7 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>11.2990941209429</v>
+        <v>10.84318426819528</v>
       </c>
       <c r="L30" t="n">
         <v>13</v>
@@ -3788,7 +3784,7 @@
         <v>61.53846153846154</v>
       </c>
       <c r="N30" t="n">
-        <v>14.77749324550151</v>
+        <v>15.83763170086855</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3821,22 +3817,22 @@
         <v>12.26790380466121</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.8629444844752476</v>
+        <v>1.269035484037218</v>
       </c>
       <c r="Z30" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA30" t="n">
-        <v>45</v>
+        <v>44.26229508196721</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.72600051764911</v>
+        <v>13.18964501957661</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>9.216589566848587</v>
+        <v>8.843187705870292</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3870,7 +3866,7 @@
         <v>46255</v>
       </c>
       <c r="C31" t="n">
-        <v>0.184001072012814</v>
+        <v>0.1842096948138398</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3898,7 +3894,7 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>5.668640395267155</v>
+        <v>5.788448869743434</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -3911,7 +3907,7 @@
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>4.099001925766088</v>
+        <v>3.981106798760448</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3977,7 +3973,7 @@
         <v>46255</v>
       </c>
       <c r="C32" t="n">
-        <v>2.317745979320096</v>
+        <v>2.303142782960381</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,16 +4001,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>6.348313371204761</v>
+        <v>5.678254910725955</v>
       </c>
       <c r="L32" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M32" t="n">
-        <v>46.66666666666666</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="N32" t="n">
-        <v>11.82690449155654</v>
+        <v>12.13319448867921</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4047,22 +4043,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.783230486478774</v>
+        <v>6.376852910100672</v>
       </c>
       <c r="Z32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA32" t="n">
-        <v>34.78260869565217</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.590042009487464</v>
+        <v>11.03406896062765</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.352839653670236</v>
+        <v>1.733702765130007</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4096,7 +4092,7 @@
         <v>46255</v>
       </c>
       <c r="C33" t="n">
-        <v>1.745089625438924</v>
+        <v>1.736744873407899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,7 +4120,7 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>6.491151615540836</v>
+        <v>5.981927194757031</v>
       </c>
       <c r="L33" t="n">
         <v>28</v>
@@ -4133,7 +4129,7 @@
         <v>64.28571428571429</v>
       </c>
       <c r="N33" t="n">
-        <v>10.63635283345433</v>
+        <v>11.05029636535382</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4314,7 +4310,7 @@
         <v>46255</v>
       </c>
       <c r="C35" t="n">
-        <v>1.941190579791915</v>
+        <v>1.940147426149365</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4346,7 +4342,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.435105655078967</v>
+        <v>9.376297606927842</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
@@ -4388,13 +4384,13 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.58588743905325</v>
+        <v>6.636086153593657</v>
       </c>
       <c r="Z35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA35" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="AB35" t="n">
         <v>14.75083324357035</v>
@@ -4437,7 +4433,7 @@
         <v>46255</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08073516479335296</v>
+        <v>0.0809437873857608</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,16 +4461,16 @@
         <v>14.25367779956082</v>
       </c>
       <c r="K36" t="n">
-        <v>3.4759326110269</v>
+        <v>3.743318171809307</v>
       </c>
       <c r="L36" t="n">
         <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>58.62068965517241</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N36" t="n">
-        <v>19.93102979683517</v>
+        <v>20.88828552891385</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4546,21 +4542,21 @@
         <v>46255</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06592329076607809</v>
+        <v>0.06654914414865935</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4574,22 +4570,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>7.311987080274385</v>
+        <v>8.330770719944681</v>
       </c>
       <c r="L37" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M37" t="n">
-        <v>65.71428571428571</v>
+        <v>62.5</v>
       </c>
       <c r="N37" t="n">
-        <v>19.27046095990698</v>
+        <v>14.55815754988779</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.6411333332323466</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4616,22 +4612,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.304748359176525</v>
+        <v>3.396250069112505</v>
       </c>
       <c r="Z37" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AA37" t="n">
-        <v>54.09836065573771</v>
+        <v>48.48484848484848</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.89254843608937</v>
+        <v>13.19858307042675</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.6249756674243323</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4665,7 +4661,7 @@
         <v>46255</v>
       </c>
       <c r="C38" t="n">
-        <v>1.677288774525102</v>
+        <v>1.673116318921822</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,22 +4689,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>5.866727093851698</v>
+        <v>5.603371000749147</v>
       </c>
       <c r="L38" t="n">
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>56.41025641025641</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N38" t="n">
-        <v>9.949257097497322</v>
+        <v>10.24068983236122</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>3.904222808818991</v>
+        <v>4.163341527440134</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4774,7 +4770,7 @@
         <v>46255</v>
       </c>
       <c r="C39" t="n">
-        <v>2.718292640265719</v>
+        <v>2.709947729267776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4798,7 @@
         <v>10.28651724741822</v>
       </c>
       <c r="K39" t="n">
-        <v>7.602254995945934</v>
+        <v>7.271925866617401</v>
       </c>
       <c r="L39" t="n">
         <v>20</v>
@@ -4811,7 +4807,7 @@
         <v>60</v>
       </c>
       <c r="N39" t="n">
-        <v>13.82079674590696</v>
+        <v>14.00932717052249</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4844,22 +4840,22 @@
         <v>10.2437411865161</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.396041863366338</v>
+        <v>2.695677131340113</v>
       </c>
       <c r="Z39" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA39" t="n">
-        <v>38.29787234042553</v>
+        <v>40</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.65613829774405</v>
+        <v>13.44893944893184</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.692430312701622</v>
+        <v>3.395864408943094</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4893,7 +4889,7 @@
         <v>46255</v>
       </c>
       <c r="C40" t="n">
-        <v>0.255139807842354</v>
+        <v>0.2534708654888039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4953,7 +4949,7 @@
         <v>44.24108228242589</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.39652697547228</v>
+        <v>4.028437883433322</v>
       </c>
       <c r="Z40" t="n">
         <v>6</v>
@@ -4962,13 +4958,13 @@
         <v>50</v>
       </c>
       <c r="AB40" t="n">
-        <v>16.33457280603697</v>
+        <v>15.74098979535976</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.659850287287912</v>
+        <v>1.012343755941603</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -5002,7 +4998,7 @@
         <v>46255</v>
       </c>
       <c r="C41" t="n">
-        <v>1.800373427893977</v>
+        <v>1.795157977823683</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5030,7 +5026,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>18.97882543948495</v>
+        <v>18.63415909755402</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -5068,22 +5064,22 @@
         <v>22.08082251686328</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.540937236026442</v>
+        <v>2.823263595584946</v>
       </c>
       <c r="Z41" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="n">
-        <v>52.17391304347826</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AB41" t="n">
-        <v>16.51101596372883</v>
+        <v>14.05755699448648</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.4710313755892814</v>
+        <v>0.1818711051167043</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5117,7 +5113,7 @@
         <v>46255</v>
       </c>
       <c r="C42" t="n">
-        <v>3.761382654324518</v>
+        <v>3.77598585089285</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5175,7 +5171,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.741681867890056</v>
+        <v>2.36408605589371</v>
       </c>
       <c r="Z42" t="n">
         <v>3</v>
@@ -5190,7 +5186,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>7.462927872401282</v>
+        <v>7.820804492573941</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5222,7 +5218,7 @@
         <v>46255</v>
       </c>
       <c r="C43" t="n">
-        <v>6.686206990116898</v>
+        <v>6.644483389554546</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5241,7 +5237,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5251,25 +5247,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>13.8335782657367</v>
+        <v>14.23748336761605</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1562500000000133</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M43" t="n">
-        <v>85.71428571428571</v>
+        <v>87.5</v>
       </c>
       <c r="N43" t="n">
-        <v>15.62295410946941</v>
+        <v>15.08065821191502</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.837753510140396</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5296,10 +5292,10 @@
         <v>22.98532002896849</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.69894323177691</v>
+        <v>14.23748336761605</v>
       </c>
       <c r="Z43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
@@ -5341,7 +5337,7 @@
         <v>46255</v>
       </c>
       <c r="C44" t="n">
-        <v>4.545786154011262</v>
+        <v>4.589596061858713</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5358,7 +5354,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5369,22 +5369,22 @@
         <v>20.19885997293468</v>
       </c>
       <c r="K44" t="n">
-        <v>1.395998178294966</v>
+        <v>2.37319974163106</v>
       </c>
       <c r="L44" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M44" t="n">
-        <v>73.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N44" t="n">
-        <v>17.27078993253876</v>
+        <v>17.79362702945675</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>8.485543785047355</v>
+        <v>7.449996950000015</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5442,7 +5442,7 @@
         <v>46255</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02294798072652957</v>
+        <v>0.02336521631491709</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5502,22 +5502,22 @@
         <v>17.77268946199939</v>
       </c>
       <c r="Y45" t="n">
-        <v>3.508769329024286</v>
+        <v>1.754385103108635</v>
       </c>
       <c r="Z45" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AA45" t="n">
-        <v>46.15384615384615</v>
+        <v>44.64285714285715</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.5345853482408</v>
+        <v>12.99257466903162</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.545457199173517</v>
+        <v>3.303572276785727</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5551,7 +5551,7 @@
         <v>46255</v>
       </c>
       <c r="C46" t="n">
-        <v>9.893708783347703</v>
+        <v>9.925001483769467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5611,22 +5611,22 @@
         <v>21.83992704688877</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.658890616899955</v>
+        <v>1.347848626231218</v>
       </c>
       <c r="Z46" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA46" t="n">
-        <v>34.14634146341464</v>
+        <v>35</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.67033385078146</v>
+        <v>11.96142056988751</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.363732208750656</v>
+        <v>1.674724119810822</v>
       </c>
       <c r="AE46" t="n">
         <v>37</v>
@@ -5660,7 +5660,7 @@
         <v>46255</v>
       </c>
       <c r="C47" t="n">
-        <v>0.713890831073238</v>
+        <v>0.7134735854711864</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>25.00555187915373</v>
       </c>
       <c r="K47" t="n">
-        <v>6.002575012730693</v>
+        <v>5.940620010221798</v>
       </c>
       <c r="L47" t="n">
         <v>12</v>
@@ -5703,7 +5703,7 @@
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.771064039519079</v>
+        <v>3.831750266693312</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5769,7 +5769,7 @@
         <v>46255</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05924751092097773</v>
+        <v>0.05945612871517148</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5797,22 +5797,22 @@
         <v>15.10031522654484</v>
       </c>
       <c r="K48" t="n">
-        <v>2.898547836588938</v>
+        <v>3.260866316162558</v>
       </c>
       <c r="L48" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M48" t="n">
-        <v>54.23728813559322</v>
+        <v>56.14035087719298</v>
       </c>
       <c r="N48" t="n">
-        <v>14.30510744762529</v>
+        <v>15.05187700376106</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.90141145110108</v>
+        <v>6.526319141274373</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5878,7 +5878,7 @@
         <v>46255</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2588949383601237</v>
+        <v>0.2584777125767824</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5906,22 +5906,22 @@
         <v>17.31218360853012</v>
       </c>
       <c r="K49" t="n">
-        <v>4.176403092864733</v>
+        <v>4.008516143581664</v>
       </c>
       <c r="L49" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>64.70588235294117</v>
+        <v>55.26315789473684</v>
       </c>
       <c r="N49" t="n">
-        <v>19.46717584041633</v>
+        <v>20.16929977836655</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.7905791356619396</v>
+        <v>0.953271802329736</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5987,7 +5987,7 @@
         <v>46255</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6876049180747038</v>
+        <v>0.6859360155671922</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6015,22 +6015,22 @@
         <v>15.86420264054068</v>
       </c>
       <c r="K50" t="n">
-        <v>2.871404911307995</v>
+        <v>2.621723239326301</v>
       </c>
       <c r="L50" t="n">
         <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>54.54545454545455</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N50" t="n">
-        <v>14.93524715750164</v>
+        <v>14.3136552748645</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.097093103438262</v>
+        <v>1.343065305441615</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6096,7 +6096,7 @@
         <v>46255</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1764908312132207</v>
+        <v>0.1756563600364457</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,22 +6124,22 @@
         <v>21.20514974257153</v>
       </c>
       <c r="K51" t="n">
-        <v>1.682696577119724</v>
+        <v>1.201927809206427</v>
       </c>
       <c r="L51" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M51" t="n">
-        <v>68.42105263157895</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N51" t="n">
-        <v>13.79407064977819</v>
+        <v>13.27232902826984</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>2.278955516411552</v>
+        <v>2.764840800334079</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6166,7 +6166,7 @@
         <v>27.67519948889778</v>
       </c>
       <c r="Y51" t="n">
-        <v>19.87927149434318</v>
+        <v>20.25809252510493</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6211,7 +6211,7 @@
         <v>46255</v>
       </c>
       <c r="C52" t="n">
-        <v>4.66052605555773</v>
+        <v>4.639664255276553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6268,25 +6268,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>18.51593523176962</v>
+        <v>18.67501864135859</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.04474545861297141</v>
+        <v>0.6255626143522597</v>
       </c>
       <c r="Z52" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA52" t="n">
-        <v>35.48387096774194</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.37116462006711</v>
+        <v>13.88094524686134</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.958815749994519</v>
+        <v>7.420859508395861</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6320,7 +6320,7 @@
         <v>46255</v>
       </c>
       <c r="C53" t="n">
-        <v>1.365404764774476</v>
+        <v>1.366447918417026</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>32.2233051798102</v>
       </c>
       <c r="K53" t="n">
-        <v>1.23742521433472</v>
+        <v>1.314769450710029</v>
       </c>
       <c r="L53" t="n">
         <v>7</v>
@@ -6357,13 +6357,13 @@
         <v>71.42857142857143</v>
       </c>
       <c r="N53" t="n">
-        <v>17.90840940822131</v>
+        <v>17.42947082383126</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>6.679915822975446</v>
+        <v>6.59847580519084</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6421,7 +6421,7 @@
         <v>46255</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0809437873857608</v>
+        <v>0.08136102318276631</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir. SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -6453,22 +6453,22 @@
         <v>42.98617858772242</v>
       </c>
       <c r="K54" t="n">
-        <v>1.180156400676791</v>
+        <v>1.701703323058701</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>100</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N54" t="n">
-        <v>22.81328516164657</v>
+        <v>25.39606819333878</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>8.716969723189937</v>
+        <v>8.159447094589467</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6495,16 +6495,16 @@
         <v>10.17240666043591</v>
       </c>
       <c r="Y54" t="n">
-        <v>8.161980419901571</v>
+        <v>7.688588816512743</v>
       </c>
       <c r="Z54" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA54" t="n">
-        <v>69.56521739130434</v>
+        <v>75</v>
       </c>
       <c r="AB54" t="n">
-        <v>15.0294452521139</v>
+        <v>15.59141213484551</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6653,7 +6653,7 @@
         <v>46255</v>
       </c>
       <c r="C56" t="n">
-        <v>1.316379565823649</v>
+        <v>1.324724317854674</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>73.71938423294128</v>
       </c>
       <c r="Y56" t="n">
-        <v>3.369072706345</v>
+        <v>2.75651296466517</v>
       </c>
       <c r="Z56" t="n">
         <v>2</v>
@@ -6716,7 +6716,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>6.862117004739121</v>
+        <v>7.448814574803142</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6742,7 +6742,7 @@
         <v>46255</v>
       </c>
       <c r="C57" t="n">
-        <v>1.278828341381119</v>
+        <v>1.314293417714086</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6759,11 +6759,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %79.49: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6774,22 +6770,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>1.294456055674531</v>
+        <v>4.103602130933659</v>
       </c>
       <c r="L57" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M57" t="n">
-        <v>79.48717948717949</v>
+        <v>72.97297297297297</v>
       </c>
       <c r="N57" t="n">
-        <v>18.9729472884561</v>
+        <v>17.55747606584726</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>8.594294577721652</v>
+        <v>5.663971033058313</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6816,10 +6812,10 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>21.15952600749666</v>
+        <v>18.97308445174279</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
@@ -6861,7 +6857,7 @@
         <v>46255</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7351698769564656</v>
+        <v>0.7247389768158776</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6889,16 +6885,16 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>10.75786030135211</v>
+        <v>9.186381087090156</v>
       </c>
       <c r="L58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M58" t="n">
-        <v>66.66666666666667</v>
+        <v>40</v>
       </c>
       <c r="N58" t="n">
-        <v>14.19416378953196</v>
+        <v>16.53858197175638</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6931,22 +6927,22 @@
         <v>13.2760081633051</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.223019598574383</v>
+        <v>3.610320616453133</v>
       </c>
       <c r="Z58" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA58" t="n">
-        <v>35.29411764705883</v>
+        <v>43.75</v>
       </c>
       <c r="AB58" t="n">
-        <v>14.22943621407547</v>
+        <v>15.45903670279456</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.862852366599112</v>
+        <v>2.479185944833395</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6980,7 +6976,7 @@
         <v>46255</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7927484106846868</v>
+        <v>0.79483455879425</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7008,22 +7004,22 @@
         <v>11.17103304657197</v>
       </c>
       <c r="K59" t="n">
-        <v>1.333333333333342</v>
+        <v>1.599995919999997</v>
       </c>
       <c r="L59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>59.32203389830509</v>
+        <v>60</v>
       </c>
       <c r="N59" t="n">
-        <v>14.16144631113641</v>
+        <v>14.14811524564401</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.57894736842104</v>
+        <v>6.299216867133905</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7089,7 +7085,7 @@
         <v>46255</v>
       </c>
       <c r="C60" t="n">
-        <v>11.96424246125442</v>
+        <v>11.95381156111383</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7117,7 +7113,7 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>4.153515691362331</v>
+        <v>4.062710533828451</v>
       </c>
       <c r="L60" t="n">
         <v>38</v>
@@ -7126,13 +7122,13 @@
         <v>52.63157894736842</v>
       </c>
       <c r="N60" t="n">
-        <v>13.51098476889908</v>
+        <v>13.55102180851627</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.693091186701691</v>
+        <v>3.783573814264263</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7198,7 +7194,7 @@
         <v>46255</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6300263843464825</v>
+        <v>0.6308608357045473</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7217,7 +7213,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -7230,22 +7226,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>2.52614421933357</v>
+        <v>2.661937072468956</v>
       </c>
       <c r="L61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M61" t="n">
-        <v>83.33333333333333</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N61" t="n">
-        <v>20.52585329832347</v>
+        <v>21.0271844363258</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>7.289707262059575</v>
+        <v>7.147793171242345</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7264,7 +7260,7 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>10.37031927277718</v>
+        <v>10.25160740504591</v>
       </c>
       <c r="Z61" t="n">
         <v>21</v>
@@ -7273,7 +7269,7 @@
         <v>47.61904761904762</v>
       </c>
       <c r="AB61" t="n">
-        <v>12.5541657761293</v>
+        <v>12.61964957502634</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7422,7 +7418,7 @@
         <v>46255</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1070210377372308</v>
+        <v>0.1074382735342363</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7450,7 +7446,7 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>8.899725467695397</v>
+        <v>9.324285579518987</v>
       </c>
       <c r="L63" t="n">
         <v>7</v>
@@ -7492,7 +7488,7 @@
         <v>17.39093407257215</v>
       </c>
       <c r="Y63" t="n">
-        <v>7.233274589694805</v>
+        <v>6.8716111314578</v>
       </c>
       <c r="Z63" t="n">
         <v>7</v>
@@ -7507,7 +7503,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.982454536438606</v>
+        <v>3.359221507587939</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7541,7 +7537,7 @@
         <v>46255</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1483274027111952</v>
+        <v>0.1485360157071749</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7569,22 +7565,22 @@
         <v>24.42078296285393</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2820871590531571</v>
+        <v>0.4231274945741603</v>
       </c>
       <c r="L64" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M64" t="n">
-        <v>69.6969696969697</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N64" t="n">
-        <v>16.28133986699973</v>
+        <v>16.04486965664466</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.704641650969998</v>
+        <v>4.557588097097587</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7650,7 +7646,7 @@
         <v>46255</v>
       </c>
       <c r="C65" t="n">
-        <v>6.613190689132782</v>
+        <v>6.602759788992194</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7678,7 +7674,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>16.73457607164919</v>
+        <v>16.55045213462765</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -7720,7 +7716,7 @@
         <v>21.96943581422117</v>
       </c>
       <c r="Y65" t="n">
-        <v>4.29194388547105</v>
+        <v>4.442902964516049</v>
       </c>
       <c r="Z65" t="n">
         <v>27</v>
@@ -7769,7 +7765,7 @@
         <v>46255</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4635491878530878</v>
+        <v>0.4606285485394214</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7829,22 +7825,22 @@
         <v>12.69724877030836</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.419705399018245</v>
+        <v>2.040820679789046</v>
       </c>
       <c r="Z66" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA66" t="n">
-        <v>37.70491803278689</v>
+        <v>33.87096774193548</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.17445057007504</v>
+        <v>12.09095509275395</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.64625777344364</v>
+        <v>4.041662402324864</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7967,7 +7963,7 @@
         <v>46255</v>
       </c>
       <c r="C68" t="n">
-        <v>4.182790956375782</v>
+        <v>4.220342260510389</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8027,7 +8023,7 @@
         <v>143.1366383982815</v>
       </c>
       <c r="Y68" t="n">
-        <v>4.021059906790169</v>
+        <v>3.159402126722621</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8038,7 +8034,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>4.145638709226929</v>
+        <v>4.99852126027932</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8072,7 +8068,7 @@
         <v>46255</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4189049479770694</v>
+        <v>0.4180704968276227</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8100,7 +8096,7 @@
         <v>18.0901893667493</v>
       </c>
       <c r="K69" t="n">
-        <v>7.379674352483812</v>
+        <v>7.16577596545509</v>
       </c>
       <c r="L69" t="n">
         <v>14</v>
@@ -8115,7 +8111,7 @@
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>0.5776937313852537</v>
+        <v>0.7784425830255959</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8134,22 +8130,22 @@
         <v>11.44384654025008</v>
       </c>
       <c r="Y69" t="n">
-        <v>3.646834090833739</v>
+        <v>3.838767870642268</v>
       </c>
       <c r="Z69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA69" t="n">
-        <v>36.8421052631579</v>
+        <v>40</v>
       </c>
       <c r="AB69" t="n">
-        <v>14.05521575818754</v>
+        <v>15.89332679715676</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.442229984829591</v>
+        <v>2.247508774066465</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8175,7 +8171,7 @@
         <v>46255</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4339254299934919</v>
+        <v>0.4293358481176574</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8203,16 +8199,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>13.78215940667391</v>
+        <v>12.57869793493205</v>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M70" t="n">
-        <v>25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N70" t="n">
-        <v>6.838424675154897</v>
+        <v>8.534401960408296</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8245,22 +8241,22 @@
         <v>14.32919111790623</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.4784707264028243</v>
+        <v>1.531099070900377</v>
       </c>
       <c r="Z70" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AA70" t="n">
-        <v>52.08333333333334</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB70" t="n">
-        <v>10.21589682510675</v>
+        <v>10.2189247408603</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>7.557690610761759</v>
+        <v>6.569486272378944</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8294,7 +8290,7 @@
         <v>46255</v>
       </c>
       <c r="C71" t="n">
-        <v>3.125097745748651</v>
+        <v>3.118839142035807</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8322,22 +8318,22 @@
         <v>14.92600999981897</v>
       </c>
       <c r="K71" t="n">
-        <v>1.147870952045826</v>
+        <v>0.9453030670739437</v>
       </c>
       <c r="L71" t="n">
         <v>67</v>
       </c>
       <c r="M71" t="n">
-        <v>61.19402985074627</v>
+        <v>59.70149253731343</v>
       </c>
       <c r="N71" t="n">
-        <v>16.85758192111756</v>
+        <v>17.21374694450511</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.8424587091488744</v>
+        <v>1.044820215384612</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8403,7 +8399,7 @@
         <v>46255</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07176459421895336</v>
+        <v>0.0715559764247596</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8431,22 +8427,22 @@
         <v>21.72769951373251</v>
       </c>
       <c r="K72" t="n">
-        <v>2.077156447622319</v>
+        <v>1.780420829627971</v>
       </c>
       <c r="L72" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M72" t="n">
-        <v>60</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N72" t="n">
-        <v>17.02483572560697</v>
+        <v>17.3898758509428</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>2.86336694133662</v>
+        <v>3.163259833402865</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8473,7 +8469,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>20.10186137747969</v>
+        <v>20.334123172046</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8518,7 +8514,7 @@
         <v>46255</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07093012304217833</v>
+        <v>0.07134735863056584</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8535,11 +8531,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8550,22 +8542,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>7.813107423483867</v>
+        <v>8.447301520186246</v>
       </c>
       <c r="L73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M73" t="n">
-        <v>85.71428571428571</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N73" t="n">
-        <v>10.73778244840042</v>
+        <v>10.41015246766233</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>2.028410671743419</v>
+        <v>1.431753910008315</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8592,22 +8584,22 @@
         <v>15.4234441942493</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.593406412269054</v>
+        <v>6.043956427363839</v>
       </c>
       <c r="Z73" t="n">
         <v>19</v>
       </c>
       <c r="AA73" t="n">
-        <v>47.36842105263158</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AB73" t="n">
-        <v>13.36571475343514</v>
+        <v>13.22595385437325</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>3.647059010380616</v>
+        <v>4.210525924899966</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8641,7 +8633,7 @@
         <v>46255</v>
       </c>
       <c r="C74" t="n">
-        <v>5.549238874792808</v>
+        <v>5.648332426128394</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8658,7 +8650,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -8669,16 +8665,16 @@
         <v>18.35970785011217</v>
       </c>
       <c r="K74" t="n">
-        <v>17.40579652595755</v>
+        <v>19.50232860677821</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="N74" t="n">
-        <v>23.62355792397849</v>
+        <v>16.52901193804602</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
@@ -8711,22 +8707,22 @@
         <v>32.26405389680429</v>
       </c>
       <c r="Y74" t="n">
-        <v>4.14956471530542</v>
+        <v>2.4379497995073</v>
       </c>
       <c r="Z74" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA74" t="n">
-        <v>60.8695652173913</v>
+        <v>50</v>
       </c>
       <c r="AB74" t="n">
-        <v>15.70096465508718</v>
+        <v>17.95958840191798</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>6.103712797252969</v>
+        <v>7.751016081511686</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8760,7 +8756,7 @@
         <v>46255</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1251708016870558</v>
+        <v>0.12496217888603</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8788,22 +8784,22 @@
         <v>23.39449322057143</v>
       </c>
       <c r="K75" t="n">
-        <v>1.351349981738514</v>
+        <v>1.182427179967194</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>72.72727272727273</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N75" t="n">
-        <v>18.41766752278744</v>
+        <v>19.66198819310451</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.586668080000011</v>
+        <v>4.761274219548106</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8869,7 +8865,7 @@
         <v>46255</v>
       </c>
       <c r="C76" t="n">
-        <v>1.934931976079071</v>
+        <v>1.927630377899214</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8897,7 +8893,7 @@
         <v>11.17000304157492</v>
       </c>
       <c r="K76" t="n">
-        <v>11.64130731111472</v>
+        <v>11.22002120062751</v>
       </c>
       <c r="L76" t="n">
         <v>15</v>
@@ -8939,22 +8935,22 @@
         <v>11.76167345580381</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.1076989463088873</v>
+        <v>0.4846493779376848</v>
       </c>
       <c r="Z76" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AA76" t="n">
-        <v>46.15384615384615</v>
+        <v>44.64285714285715</v>
       </c>
       <c r="AB76" t="n">
-        <v>9.609892728943459</v>
+        <v>9.905833547760849</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.896497540485166</v>
+        <v>3.53247071942987</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8988,7 +8984,7 @@
         <v>46255</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5257173829406027</v>
+        <v>0.5240484405870526</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9016,16 +9012,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>8.274668315312383</v>
+        <v>7.930939563645012</v>
       </c>
       <c r="L77" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M77" t="n">
-        <v>66.66666666666667</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N77" t="n">
-        <v>15.00075501371142</v>
+        <v>13.92336255069648</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -9058,22 +9054,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>6.885765643813602</v>
+        <v>7.181366083285823</v>
       </c>
       <c r="Z77" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA77" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.09045251573717</v>
+        <v>11.91075471878268</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>3.344530917017086</v>
+        <v>3.03671126989794</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9107,7 +9103,7 @@
         <v>46255</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04798213960361472</v>
+        <v>0.04839937519200223</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9135,22 +9131,22 @@
         <v>19.53698884929083</v>
       </c>
       <c r="K78" t="n">
-        <v>2.678568738042109</v>
+        <v>3.571424984056137</v>
       </c>
       <c r="L78" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M78" t="n">
-        <v>63.82978723404256</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N78" t="n">
-        <v>18.11052823619765</v>
+        <v>18.4831683459156</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>1.286959175803459</v>
+        <v>0.4137965814507538</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9216,16 +9212,16 @@
         <v>46255</v>
       </c>
       <c r="C79" t="n">
-        <v>0.836558159356602</v>
+        <v>0.8323858631374755</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9244,22 +9240,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>5.513159551868774</v>
+        <v>4.986917411089298</v>
       </c>
       <c r="L79" t="n">
         <v>28</v>
       </c>
       <c r="M79" t="n">
-        <v>67.85714285714286</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N79" t="n">
-        <v>11.38934526030933</v>
+        <v>12.07238133735722</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>0.01246116109827611</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9440,7 +9436,7 @@
         <v>46255</v>
       </c>
       <c r="C81" t="n">
-        <v>1.233975518550113</v>
+        <v>1.230846216589382</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9500,7 +9496,7 @@
         <v>30.91171973579283</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.4208754100347045</v>
+        <v>0.673403231813019</v>
       </c>
       <c r="Z81" t="n">
         <v>17</v>
@@ -9515,7 +9511,7 @@
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>9.619611167911991</v>
+        <v>9.389828174576264</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9549,7 +9545,7 @@
         <v>46255</v>
       </c>
       <c r="C82" t="n">
-        <v>5.3823444725434</v>
+        <v>5.377129022473106</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9609,13 +9605,13 @@
         <v>16.65327680511959</v>
       </c>
       <c r="Y82" t="n">
-        <v>3.726590188027012</v>
+        <v>3.8198783758293</v>
       </c>
       <c r="Z82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA82" t="n">
-        <v>33.33333333333334</v>
+        <v>37.5</v>
       </c>
       <c r="AB82" t="n">
         <v>12.95948113262313</v>
@@ -9624,7 +9620,7 @@
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.2839930698486426</v>
+        <v>0.1872753133693617</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9658,7 +9654,7 @@
         <v>46255</v>
       </c>
       <c r="C83" t="n">
-        <v>5.846519528799566</v>
+        <v>5.836088628658977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,22 +9714,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.816942734989758</v>
+        <v>2.990329099423328</v>
       </c>
       <c r="Z83" t="n">
         <v>57</v>
       </c>
       <c r="AA83" t="n">
-        <v>45.6140350877193</v>
+        <v>38.59649122807018</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.28672320010427</v>
+        <v>12.67589451319982</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.275321187241842</v>
+        <v>3.102444192044762</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9767,7 +9763,7 @@
         <v>46255</v>
       </c>
       <c r="C84" t="n">
-        <v>2.182144277492452</v>
+        <v>2.175885832955144</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9795,22 +9791,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>4.464814438908493</v>
+        <v>4.16520673010139</v>
       </c>
       <c r="L84" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M84" t="n">
-        <v>50.98039215686274</v>
+        <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>10.80372727629718</v>
+        <v>11.61841236501015</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0.5123117903057084</v>
+        <v>0.8014127712160368</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9876,7 +9872,7 @@
         <v>46255</v>
       </c>
       <c r="C85" t="n">
-        <v>6.289832784774555</v>
+        <v>6.279401884633967</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9904,22 +9900,22 @@
         <v>15.93296998857089</v>
       </c>
       <c r="K85" t="n">
-        <v>1.666920503700609</v>
+        <v>1.498318645485508</v>
       </c>
       <c r="L85" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M85" t="n">
-        <v>58.8235294117647</v>
+        <v>60</v>
       </c>
       <c r="N85" t="n">
-        <v>15.72056805328279</v>
+        <v>15.37314992968119</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.229242968039816</v>
+        <v>6.405703504531579</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9985,7 +9981,7 @@
         <v>46255</v>
       </c>
       <c r="C86" t="n">
-        <v>4.489459356880578</v>
+        <v>4.29544455063715</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10010,25 +10006,25 @@
         <v>10</v>
       </c>
       <c r="J86" t="n">
-        <v>12.64935661172912</v>
+        <v>16.26863740490974</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1862168967971867</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M86" t="n">
-        <v>64.78873239436619</v>
+        <v>58.49056603773585</v>
       </c>
       <c r="N86" t="n">
-        <v>14.81634309904413</v>
+        <v>15.77569664569882</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
       </c>
       <c r="P86" t="n">
-        <v>5.802976979549657</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q86" t="n">
         <v>54</v>
@@ -10055,7 +10051,7 @@
         <v>88.01181128002702</v>
       </c>
       <c r="Y86" t="n">
-        <v>12.48669495427911</v>
+        <v>16.26863740490974</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10100,7 +10096,7 @@
         <v>46255</v>
       </c>
       <c r="C87" t="n">
-        <v>5.883027679291623</v>
+        <v>5.867381329080741</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10128,7 +10124,7 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>9.098805951900335</v>
+        <v>8.808649553092085</v>
       </c>
       <c r="L87" t="n">
         <v>18</v>
@@ -10137,7 +10133,7 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N87" t="n">
-        <v>10.97653318407152</v>
+        <v>10.8676286810291</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10170,22 +10166,22 @@
         <v>10.54958794594156</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.312335958005262</v>
+        <v>1.574803149606308</v>
       </c>
       <c r="Z87" t="n">
         <v>56</v>
       </c>
       <c r="AA87" t="n">
-        <v>44.64285714285715</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.34288488421424</v>
+        <v>11.27959213501269</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>2.72340425531914</v>
+        <v>2.464</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10219,7 +10215,7 @@
         <v>46255</v>
       </c>
       <c r="C88" t="n">
-        <v>1.145312867355115</v>
+        <v>1.138011189483181</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10247,7 +10243,7 @@
         <v>24.22103615752376</v>
       </c>
       <c r="K88" t="n">
-        <v>28.31123269520586</v>
+        <v>27.49321404266529</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -10285,22 +10281,22 @@
         <v>28.54494720514669</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.1818153999999961</v>
+        <v>0.8181832</v>
       </c>
       <c r="Z88" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA88" t="n">
-        <v>33.33333333333334</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.61845768572016</v>
+        <v>12.99798546139592</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.82878222371519</v>
+        <v>5.224563299187324</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10334,7 +10330,7 @@
         <v>46255</v>
       </c>
       <c r="C89" t="n">
-        <v>2.269763934220436</v>
+        <v>2.24890213393926</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10362,10 +10358,10 @@
         <v>19.71415010641037</v>
       </c>
       <c r="K89" t="n">
-        <v>23.28984366223126</v>
+        <v>22.15666498386695</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -10400,22 +10396,22 @@
         <v>24.19638141496434</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.7299228386567713</v>
+        <v>1.642331610517955</v>
       </c>
       <c r="Z89" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AA89" t="n">
-        <v>39.02439024390244</v>
+        <v>37.77777777777778</v>
       </c>
       <c r="AB89" t="n">
-        <v>12.87161838633467</v>
+        <v>13.84011558011209</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>9.338239101271784</v>
+        <v>8.497220934911642</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10449,7 +10445,7 @@
         <v>46255</v>
       </c>
       <c r="C90" t="n">
-        <v>3.00201293320424</v>
+        <v>2.989496043921007</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10477,7 +10473,7 @@
         <v>16.58671596100499</v>
       </c>
       <c r="K90" t="n">
-        <v>18.34009719111018</v>
+        <v>17.84667829943103</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
@@ -10515,22 +10511,22 @@
         <v>24.88307914387619</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.288638597956515</v>
+        <v>1.70021549957492</v>
       </c>
       <c r="Z90" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA90" t="n">
-        <v>40.47619047619047</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB90" t="n">
-        <v>12.76646402340407</v>
+        <v>13.02002130004772</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
       </c>
       <c r="AD90" t="n">
-        <v>1.733702562436812</v>
+        <v>1.322265869687089</v>
       </c>
       <c r="AE90" t="n">
         <v>23</v>
@@ -10564,7 +10560,7 @@
         <v>46255</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2298970486949873</v>
+        <v>0.2296884258939615</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10592,22 +10588,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>2.69064648143067</v>
+        <v>2.59745863743821</v>
       </c>
       <c r="L91" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M91" t="n">
-        <v>60</v>
+        <v>63.23529411764706</v>
       </c>
       <c r="N91" t="n">
-        <v>12.9767005168435</v>
+        <v>13.40930703367147</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.3012479998607098</v>
+        <v>0.392350227683802</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10673,7 +10669,7 @@
         <v>46255</v>
       </c>
       <c r="C92" t="n">
-        <v>1.146355941305588</v>
+        <v>1.144269713503947</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10705,7 +10701,7 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>8.798227623848586</v>
+        <v>8.600228137773126</v>
       </c>
       <c r="L92" t="n">
         <v>20</v>
@@ -10714,7 +10710,7 @@
         <v>75</v>
       </c>
       <c r="N92" t="n">
-        <v>8.746314114254508</v>
+        <v>9.652661034213956</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
@@ -10747,7 +10743,7 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>5.116697298314199</v>
+        <v>5.289373320547108</v>
       </c>
       <c r="Z92" t="n">
         <v>47</v>
@@ -10756,7 +10752,7 @@
         <v>53.19148936170212</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.12706433169667</v>
+        <v>10.95182935235971</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10905,7 +10901,7 @@
         <v>46255</v>
       </c>
       <c r="C94" t="n">
-        <v>8.428167313595091</v>
+        <v>8.485537264368325</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10962,10 +10958,10 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>50.97347118795989</v>
+        <v>51.90713520272774</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.06184291898577721</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
         <v>7</v>
@@ -10980,7 +10976,7 @@
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>5.941831683168319</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11014,16 +11010,16 @@
         <v>46255</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1408171518979378</v>
+        <v>0.1414430102873511</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -11042,7 +11038,7 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>5.558038488706796</v>
+        <v>6.027188610462231</v>
       </c>
       <c r="L95" t="n">
         <v>10</v>
@@ -11051,13 +11047,13 @@
         <v>60</v>
       </c>
       <c r="N95" t="n">
-        <v>19.32811751426809</v>
+        <v>19.08560282706251</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>0.418690530461574</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11084,22 +11080,22 @@
         <v>11.96970959191628</v>
       </c>
       <c r="Y95" t="n">
-        <v>5.726255008231618</v>
+        <v>5.307257653085018</v>
       </c>
       <c r="Z95" t="n">
         <v>28</v>
       </c>
       <c r="AA95" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="AB95" t="n">
-        <v>11.91893305379972</v>
+        <v>10.75512027761017</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>0.2903724592592472</v>
+        <v>0.7315685761608459</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11133,7 +11129,7 @@
         <v>46255</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1318465813235382</v>
+        <v>0.1320551941108999</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11161,22 +11157,22 @@
         <v>13.52465198145173</v>
       </c>
       <c r="K96" t="n">
-        <v>2.764228735541008</v>
+        <v>2.926826293872753</v>
       </c>
       <c r="L96" t="n">
         <v>64</v>
       </c>
       <c r="M96" t="n">
-        <v>56.25</v>
+        <v>57.8125</v>
       </c>
       <c r="N96" t="n">
-        <v>14.45330189893711</v>
+        <v>14.18034793826052</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.04113810174154</v>
+        <v>6.872041003122153</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11242,7 +11238,7 @@
         <v>46255</v>
       </c>
       <c r="C97" t="n">
-        <v>1.943276728110096</v>
+        <v>1.949535172647404</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11270,16 +11266,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>8.725987620386988</v>
+        <v>9.076146480133085</v>
       </c>
       <c r="L97" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M97" t="n">
-        <v>55.55555555555556</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N97" t="n">
-        <v>12.28821615530306</v>
+        <v>11.94044546982779</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11312,22 +11308,22 @@
         <v>14.56205771349215</v>
       </c>
       <c r="Y97" t="n">
-        <v>5.094243425428502</v>
+        <v>4.788593486229775</v>
       </c>
       <c r="Z97" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA97" t="n">
-        <v>44.44444444444444</v>
+        <v>43.24324324324324</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.78962056378606</v>
+        <v>11.78585369827368</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.954374747394604</v>
+        <v>1.272333387486535</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11361,7 +11357,7 @@
         <v>46255</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6371193997799703</v>
+        <v>0.6383710965314688</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11389,22 +11385,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>6.387127113891555</v>
+        <v>6.596137264038759</v>
       </c>
       <c r="L98" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M98" t="n">
-        <v>52.94117647058823</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N98" t="n">
-        <v>13.24455457470219</v>
+        <v>13.06644539420603</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.395968087605872</v>
+        <v>3.193232722429595</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11431,22 +11427,22 @@
         <v>10.06692753699225</v>
       </c>
       <c r="Y98" t="n">
-        <v>3.343238977815532</v>
+        <v>3.153345287835885</v>
       </c>
       <c r="Z98" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA98" t="n">
-        <v>38.46153846153846</v>
+        <v>40</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.61064391364317</v>
+        <v>11.60719818483285</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>4.817832682305223</v>
+        <v>5.004462700925238</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11480,7 +11476,7 @@
         <v>46255</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4706422032865757</v>
+        <v>0.4589596061858713</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11508,16 +11504,16 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>6.849833337747802</v>
+        <v>4.197534958118143</v>
       </c>
       <c r="L99" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M99" t="n">
-        <v>58.8235294117647</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N99" t="n">
-        <v>11.06927854023787</v>
+        <v>13.29618674290244</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11589,7 +11585,7 @@
         <v>46255</v>
       </c>
       <c r="C100" t="n">
-        <v>329.4001051288702</v>
+        <v>329.124114104981</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11621,7 +11617,7 @@
         <v>15.65236426997335</v>
       </c>
       <c r="K100" t="n">
-        <v>7.47649929920331</v>
+        <v>7.386449087853175</v>
       </c>
       <c r="L100" t="n">
         <v>16</v>
@@ -11702,7 +11698,7 @@
         <v>46255</v>
       </c>
       <c r="C101" t="n">
-        <v>349.4660399530825</v>
+        <v>348.9156877336598</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11730,16 +11726,16 @@
         <v>11.19277381576541</v>
       </c>
       <c r="K101" t="n">
-        <v>10.66507672310264</v>
+        <v>10.49079721200816</v>
       </c>
       <c r="L101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M101" t="n">
-        <v>30</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="N101" t="n">
-        <v>5.693386098790065</v>
+        <v>7.894792849727322</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11769,25 +11765,25 @@
         <v>53.84615384615385</v>
       </c>
       <c r="X101" t="n">
-        <v>11.24226228404977</v>
+        <v>11.24259775946232</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.5188545693841862</v>
+        <v>0.6758207400727634</v>
       </c>
       <c r="Z101" t="n">
         <v>41</v>
       </c>
       <c r="AA101" t="n">
-        <v>36.58536585365854</v>
+        <v>39.02439024390244</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.30094056760116</v>
+        <v>11.08541206052342</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>5.509732931692768</v>
+        <v>5.360405995396233</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11821,7 +11817,7 @@
         <v>46255</v>
       </c>
       <c r="C102" t="n">
-        <v>422.4796109751565</v>
+        <v>422.9584137389274</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11878,10 +11874,10 @@
         <v>47.22222222222222</v>
       </c>
       <c r="X102" t="n">
-        <v>11.14205602519744</v>
+        <v>11.14228058200113</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.2409336471784318</v>
+        <v>0.1280769200425524</v>
       </c>
       <c r="Z102" t="n">
         <v>36</v>
@@ -11896,7 +11892,7 @@
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.770560237592846</v>
+        <v>4.878170890989042</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11930,7 +11926,7 @@
         <v>46255</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7330836491548254</v>
+        <v>0.7322491579507222</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11958,7 +11954,7 @@
         <v>16.13876216849247</v>
       </c>
       <c r="K103" t="n">
-        <v>12.74705012736652</v>
+        <v>12.61870676337478</v>
       </c>
       <c r="L103" t="n">
         <v>15</v>
@@ -12000,13 +11996,13 @@
         <v>16.12648158012706</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.910129891801416</v>
+        <v>3.020650216059384</v>
       </c>
       <c r="Z103" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA103" t="n">
-        <v>35.41666666666666</v>
+        <v>36.17021276595744</v>
       </c>
       <c r="AB103" t="n">
         <v>11.32844267601609</v>
@@ -12015,7 +12011,7 @@
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>5.242431679562809</v>
+        <v>5.134443358337681</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -12049,7 +12045,7 @@
         <v>46255</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04777352180942095</v>
+        <v>0.04735628622103345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12077,22 +12073,22 @@
         <v>21.43553010850433</v>
       </c>
       <c r="K104" t="n">
-        <v>2.690580244927521</v>
+        <v>1.793720163285029</v>
       </c>
       <c r="L104" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M104" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N104" t="n">
-        <v>10.86271338555909</v>
+        <v>12.32784198497689</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>1.27511184760023</v>
+        <v>2.167402697510146</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -22,16 +22,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -51,7 +48,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -59,19 +56,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -676,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4013810326116116</v>
+        <v>0.3942917363105504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,22 +698,22 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>2.382725296994082</v>
+        <v>0.5744149465573889</v>
       </c>
       <c r="L2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" t="n">
-        <v>44.82758620689656</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N2" t="n">
-        <v>12.51278923498183</v>
+        <v>11.49230194429774</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>7.43999994228477</v>
+        <v>9.371752307434388</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -753,29 +744,29 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>52.17391304347826</v>
+        <v>55</v>
       </c>
       <c r="AG2" t="n">
-        <v>36.76608358415216</v>
+        <v>38.88610988889963</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.40782945932609</v>
+        <v>16.11389011110037</v>
       </c>
       <c r="AI2" t="n">
-        <v>38.13741307280403</v>
+        <v>39.82909179893205</v>
       </c>
       <c r="AJ2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AK2" t="n">
-        <v>50.9433962264151</v>
+        <v>46.2962962962963</v>
       </c>
     </row>
     <row r="3">
@@ -785,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" t="n">
-        <v>0.655477766503493</v>
+        <v>0.6482705430099892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,22 +807,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>2.545878653017053</v>
+        <v>1.418348317804585</v>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>47.16981132075472</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N3" t="n">
-        <v>14.9197350734803</v>
+        <v>13.47976363276248</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>7.269059902646458</v>
+        <v>8.461636207389178</v>
       </c>
       <c r="Q3" t="n">
         <v>37</v>
@@ -840,10 +831,10 @@
         <v>59.45945945945946</v>
       </c>
       <c r="S3" t="n">
-        <v>53.43417817185702</v>
+        <v>54.10842708140005</v>
       </c>
       <c r="T3" t="n">
-        <v>6.025281287602439</v>
+        <v>5.351032378059408</v>
       </c>
       <c r="U3" t="n">
         <v>43.48596473022936</v>
@@ -866,19 +857,19 @@
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>59.45945945945946</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="AG3" t="n">
-        <v>37.28095651308371</v>
+        <v>37.93578782904118</v>
       </c>
       <c r="AH3" t="n">
-        <v>22.17850294637575</v>
+        <v>23.17532328206993</v>
       </c>
       <c r="AI3" t="n">
-        <v>43.48596473022936</v>
+        <v>44.86445909660515</v>
       </c>
       <c r="AJ3" t="n">
         <v>67</v>
@@ -894,19 +885,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454067415969474</v>
+        <v>1.500973220127166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -921,27 +912,17 @@
       <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="n">
-        <v>14.71888288970985</v>
-      </c>
-      <c r="K4" t="n">
-        <v>12.58392772767043</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M4" t="n">
-        <v>63.63636363636363</v>
-      </c>
-      <c r="N4" t="n">
-        <v>14.1451842611309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>54</v>
       </c>
@@ -964,25 +945,25 @@
         <v>63.01369863013699</v>
       </c>
       <c r="X4" t="n">
-        <v>15.89522479111605</v>
+        <v>18.2305339009923</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.857147108013935</v>
+        <v>1.704158181422788</v>
       </c>
       <c r="Z4" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>42.10526315789474</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.93554239735304</v>
+        <v>14.31240375911076</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.352937122330816</v>
+        <v>8.439667095876436</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -991,10 +972,10 @@
         <v>59.09090909090909</v>
       </c>
       <c r="AG4" t="n">
-        <v>39.20647024320037</v>
+        <v>39.61983283006133</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.88443884770872</v>
+        <v>19.47107626084776</v>
       </c>
       <c r="AI4" t="n">
         <v>44.4097537410319</v>
@@ -1013,10 +994,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2326090652076279</v>
+        <v>0.2346181586719366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,7 +1014,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1041,25 +1026,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>17.18852105094173</v>
+        <v>17.37484898646685</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5410231667129395</v>
+        <v>1.638105473796014</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="N5" t="n">
-        <v>13.73332433230867</v>
+        <v>13.41667696322739</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.445744787388615</v>
+        <v>1.339944816813921</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1068,10 +1053,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S5" t="n">
-        <v>42.02425514307264</v>
+        <v>42.26754690342509</v>
       </c>
       <c r="T5" t="n">
-        <v>18.95135461302493</v>
+        <v>18.70806285267248</v>
       </c>
       <c r="U5" t="n">
         <v>45.72685693412379</v>
@@ -1122,10 +1107,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C6" t="n">
-        <v>1.723184671306581</v>
+        <v>1.694580097192065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1138,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>5.295854337712735</v>
+        <v>3.54796096359713</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1191,16 +1176,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.966773983826201</v>
+        <v>7.527709632567293</v>
       </c>
       <c r="Z6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.59356805429494</v>
+        <v>11.40216735484644</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1215,10 +1200,10 @@
         <v>46.15384615384615</v>
       </c>
       <c r="AG6" t="n">
-        <v>39.94930127170949</v>
+        <v>40.78998004793637</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.204544882136659</v>
+        <v>5.363866105909786</v>
       </c>
       <c r="AI6" t="n">
         <v>33.34047468175682</v>
@@ -1237,10 +1222,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C7" t="n">
-        <v>2.217609433517497</v>
+        <v>2.165065439747232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,7 +1234,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1264,17 +1249,27 @@
       <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>10.98106443010587</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.192675283355892</v>
+      </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="M7" t="n">
+        <v>61.29032258064516</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13.57600105369179</v>
+      </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>7.792310859615381</v>
+      </c>
       <c r="Q7" t="n">
         <v>49</v>
       </c>
@@ -1282,10 +1277,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S7" t="n">
-        <v>52.82466880932375</v>
+        <v>52.34661923893561</v>
       </c>
       <c r="T7" t="n">
-        <v>8.399820986594612</v>
+        <v>8.877870556982757</v>
       </c>
       <c r="U7" t="n">
         <v>47.24599944352045</v>
@@ -1297,19 +1292,19 @@
         <v>69.11764705882354</v>
       </c>
       <c r="X7" t="n">
-        <v>14.22876300591287</v>
+        <v>17.31307710509156</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.178287565368246</v>
+        <v>10.80954694375619</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>48.27586206896552</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.2049799707391</v>
+        <v>12.16677010797909</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1346,10 +1341,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4007551642085341</v>
+        <v>0.3913771982865213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,25 +1401,21 @@
         <v>33.33333333333334</v>
       </c>
       <c r="X8" t="n">
-        <v>30.27139917619635</v>
+        <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.189411015047904</v>
+        <v>4.713635690231777</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>15.9993759340716</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.940654325112016</v>
+        <v>3.448934518148383</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1455,10 +1446,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5945613080135151</v>
+        <v>0.5895639671391472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,16 +1509,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.398827738208333</v>
+        <v>5.202364126032755</v>
       </c>
       <c r="Z9" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AA9" t="n">
-        <v>46.34146341463415</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.05313074983267</v>
+        <v>12.08997104184201</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1564,10 +1555,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C10" t="n">
-        <v>1.929716526008777</v>
+        <v>1.93294541123058</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,25 +1583,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10.51321892894885</v>
+        <v>10.66625626204533</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1082234505889401</v>
+        <v>0.4475108740565004</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>43.90243902439025</v>
+        <v>44.18604651162791</v>
       </c>
       <c r="N10" t="n">
-        <v>10.16882093237464</v>
+        <v>9.966898464387521</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.885407158702716</v>
+        <v>5.527751835389272</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1619,10 +1610,10 @@
         <v>48.78048780487805</v>
       </c>
       <c r="S10" t="n">
-        <v>38.36412638935644</v>
+        <v>38.50181325009601</v>
       </c>
       <c r="T10" t="n">
-        <v>10.41636141552161</v>
+        <v>10.27867455478204</v>
       </c>
       <c r="U10" t="n">
         <v>34.25442955443266</v>
@@ -1651,10 +1642,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="AG10" t="n">
-        <v>41.86902843890139</v>
+        <v>41.47063826283426</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.30338535420206</v>
+        <v>13.70177553026918</v>
       </c>
       <c r="AI10" t="n">
         <v>37.54796321097091</v>
@@ -1673,14 +1664,14 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C11" t="n">
-        <v>8.41252096338421</v>
+        <v>8.321970284028421</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1690,7 +1681,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1718,10 +1709,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.74705423095423</v>
+        <v>51.78475403994187</v>
       </c>
       <c r="T11" t="n">
-        <v>9.477435564964132</v>
+        <v>9.4397357559765</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1733,25 +1724,25 @@
         <v>61.76470588235294</v>
       </c>
       <c r="X11" t="n">
-        <v>22.18106016526054</v>
+        <v>22.29702291509528</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.345565749235478</v>
+        <v>2.500000000000002</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AA11" t="n">
-        <v>45</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.84589812680843</v>
+        <v>12.75892080722119</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.6633601983880966</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1782,10 +1773,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C12" t="n">
-        <v>7.004349444404832</v>
+        <v>7.104120974170604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,19 +1801,19 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>11.16401078100182</v>
+        <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>6.671961874503562</v>
+        <v>8.136342936811335</v>
       </c>
       <c r="L12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
-        <v>71.42857142857143</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N12" t="n">
-        <v>17.80846345924088</v>
+        <v>11.82093754578351</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1855,16 +1846,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.236907449472161</v>
+        <v>3.887080633413731</v>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>33.33333333333334</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.19016848477012</v>
+        <v>9.759433103302454</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1901,10 +1892,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2378245152779219</v>
+        <v>0.2246255385410578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,10 +1920,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>45.34593765398164</v>
+        <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>12.64821881336995</v>
+        <v>6.342212580490059</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1965,25 +1956,25 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>16.60079365870428</v>
+        <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.389835284400977</v>
+        <v>8.809071004620794</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>50</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.39090220800516</v>
+        <v>17.02852793358301</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.842100657894557</v>
+        <v>1.30597309238899</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2004,10 +1995,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C14" t="n">
-        <v>8.688939817109791</v>
+        <v>8.582194495536502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,25 +2055,25 @@
         <v>58.69565217391305</v>
       </c>
       <c r="X14" t="n">
-        <v>12.93345142071747</v>
+        <v>12.90895707120068</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.7742703990470612</v>
+        <v>1.97201637975768</v>
       </c>
       <c r="Z14" t="n">
         <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>46.80851063829788</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.11589101364306</v>
+        <v>12.83340848040575</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.235294117647057</v>
+        <v>0.02854656314337234</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2091,10 +2082,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>27.9098721301118</v>
+        <v>27.72785600382322</v>
       </c>
       <c r="AH14" t="n">
-        <v>24.72170681725662</v>
+        <v>24.9037229435452</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2113,10 +2104,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C15" t="n">
-        <v>14.40507309415201</v>
+        <v>15.67590650124678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,25 +2164,25 @@
         <v>80.64516129032258</v>
       </c>
       <c r="X15" t="n">
-        <v>38.77434577704333</v>
+        <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.264685067232841</v>
+        <v>0.8558262014483176</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>33.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.100436433351</v>
+        <v>10.36329355586816</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>7.914554670528595</v>
+        <v>9.223107569721112</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2200,10 +2191,10 @@
         <v>56.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>24.52657587635231</v>
+        <v>24.83073325918522</v>
       </c>
       <c r="AH15" t="n">
-        <v>31.72342412364769</v>
+        <v>31.41926674081478</v>
       </c>
       <c r="AI15" t="n">
         <v>39.32559113685198</v>
@@ -2222,10 +2213,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C16" t="n">
-        <v>35.48592227828033</v>
+        <v>37.30574296179845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,58 +2244,58 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>1.908397810239149</v>
+        <v>7.134555065077541</v>
       </c>
       <c r="L16" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="M16" t="n">
-        <v>68.42105263157895</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="N16" t="n">
-        <v>18.16138921050452</v>
+        <v>21.48344922057068</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.940073991574281</v>
+        <v>2.674622518553327</v>
       </c>
       <c r="Q16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R16" t="n">
-        <v>70.37037037037037</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="S16" t="n">
-        <v>54.08915069114214</v>
+        <v>53.28180661229836</v>
       </c>
       <c r="T16" t="n">
-        <v>16.28121967922823</v>
+        <v>14.5753362448445</v>
       </c>
       <c r="U16" t="n">
-        <v>51.51931703585186</v>
+        <v>49.33884318085762</v>
       </c>
       <c r="V16" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="W16" t="n">
-        <v>77.14285714285714</v>
+        <v>76.41509433962264</v>
       </c>
       <c r="X16" t="n">
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.31207669317097</v>
+        <v>7.815186481973346</v>
       </c>
       <c r="Z16" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
-        <v>56.52173913043478</v>
+        <v>45</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.29477211608372</v>
+        <v>13.02601819878429</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
@@ -2313,19 +2304,19 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF16" t="n">
-        <v>50</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="AG16" t="n">
-        <v>34.76864739885718</v>
+        <v>36.75049596077679</v>
       </c>
       <c r="AH16" t="n">
-        <v>15.23135260114282</v>
+        <v>11.63660081341676</v>
       </c>
       <c r="AI16" t="n">
-        <v>33.15412564053376</v>
+        <v>31.97025156241731</v>
       </c>
       <c r="AJ16" t="n">
         <v>115</v>
@@ -2341,10 +2332,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C17" t="n">
-        <v>0.698870309419395</v>
+        <v>0.69573541379118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,25 +2360,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>15.57257289886932</v>
+        <v>16.09305130534204</v>
       </c>
       <c r="K17" t="n">
-        <v>1.576714576267091</v>
+        <v>1.748334196536838</v>
       </c>
       <c r="L17" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M17" t="n">
-        <v>66.66666666666667</v>
+        <v>65</v>
       </c>
       <c r="N17" t="n">
-        <v>17.64065595520045</v>
+        <v>18.17539053542477</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.32358060656717</v>
+        <v>6.144243886477252</v>
       </c>
       <c r="Q17" t="n">
         <v>45</v>
@@ -2396,10 +2387,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="S17" t="n">
-        <v>47.42764924369089</v>
+        <v>47.44099592370424</v>
       </c>
       <c r="T17" t="n">
-        <v>19.23901742297578</v>
+        <v>19.22567074296244</v>
       </c>
       <c r="U17" t="n">
         <v>52.07048830990042</v>
@@ -2428,10 +2419,10 @@
         <v>56.09756097560975</v>
       </c>
       <c r="AG17" t="n">
-        <v>39.29148310899126</v>
+        <v>39.33376648054293</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.80607786661849</v>
+        <v>16.76379449506683</v>
       </c>
       <c r="AI17" t="n">
         <v>41.04052722210609</v>
@@ -2450,10 +2441,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09742460898203581</v>
+        <v>0.09784429957163032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,25 +2469,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>20.7015863320355</v>
+        <v>20.88000978125635</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6465562681147397</v>
+        <v>1.308072264219784</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>71.05263157894737</v>
+        <v>65</v>
       </c>
       <c r="N18" t="n">
-        <v>15.51418388438247</v>
+        <v>16.06293984455046</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>9.293356950006725</v>
+        <v>8.579699071867598</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2505,10 +2496,10 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>41.86541405947298</v>
+        <v>41.6906452912378</v>
       </c>
       <c r="T18" t="n">
-        <v>35.32756839666737</v>
+        <v>35.50233716490256</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
@@ -2537,10 +2528,10 @@
         <v>59.52380952380953</v>
       </c>
       <c r="AG18" t="n">
-        <v>39.97138293722115</v>
+        <v>40.02689641378726</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.55242658658837</v>
+        <v>19.49691311002226</v>
       </c>
       <c r="AI18" t="n">
         <v>44.49431275003934</v>
@@ -2559,10 +2550,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02524277917469493</v>
+        <v>0.02560606282875388</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,22 +2581,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>2.425147283288864</v>
+        <v>3.899207707265506</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N19" t="n">
-        <v>19.31962096524373</v>
+        <v>15.85846737675938</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.395500926896892</v>
+        <v>5.871837165422278</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2668,19 +2659,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C20" t="n">
-        <v>1.73570171976535</v>
+        <v>1.662312231262176</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2696,25 +2687,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>15.90954673249845</v>
+        <v>17.71726923698957</v>
       </c>
       <c r="K20" t="n">
-        <v>4.192780910809257</v>
+        <v>1.979559846262346</v>
       </c>
       <c r="L20" t="n">
         <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>55.88235294117647</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>11.01224316795551</v>
+        <v>15.85353760891969</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.02004338297643127</v>
       </c>
       <c r="Q20" t="n">
         <v>48</v>
@@ -2755,10 +2746,10 @@
         <v>50</v>
       </c>
       <c r="AG20" t="n">
-        <v>40.66099521324126</v>
+        <v>40.82021099745704</v>
       </c>
       <c r="AH20" t="n">
-        <v>9.339004786758743</v>
+        <v>9.179789002542961</v>
       </c>
       <c r="AI20" t="n">
         <v>35.19952693346539</v>
@@ -2777,10 +2768,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9521325521071731</v>
+        <v>0.9572087300350731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,22 +2799,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>2.489895407894926</v>
+        <v>3.036307715457509</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M21" t="n">
-        <v>56.89655172413793</v>
+        <v>50.87719298245614</v>
       </c>
       <c r="N21" t="n">
-        <v>16.84555044496366</v>
+        <v>17.39378741457684</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.376241794545367</v>
+        <v>4.817420572027986</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2832,10 +2823,10 @@
         <v>72.5</v>
       </c>
       <c r="S21" t="n">
-        <v>46.53935937798475</v>
+        <v>46.65139214655776</v>
       </c>
       <c r="T21" t="n">
-        <v>25.96064062201525</v>
+        <v>25.84860785344224</v>
       </c>
       <c r="U21" t="n">
         <v>57.16504419378943</v>
@@ -2886,10 +2877,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C22" t="n">
-        <v>0.338378386166032</v>
+        <v>0.3362096733576243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2949,16 +2940,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.779556235145558</v>
+        <v>8.370609522726857</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA22" t="n">
         <v>50</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.89827904879843</v>
+        <v>10.32220118604125</v>
       </c>
       <c r="AC22" t="n">
         <v>6</v>
@@ -2987,10 +2978,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7593695621533597</v>
+        <v>0.739869497312277</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,25 +3006,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>26.4735215749153</v>
+        <v>27.1609810190017</v>
       </c>
       <c r="K23" t="n">
-        <v>1.675984085858895</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N23" t="n">
-        <v>20.58908139023668</v>
+        <v>19.39401750526293</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.269224236211166</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3060,7 +3051,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>25.24122949761842</v>
+        <v>27.1609810190017</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3102,10 +3093,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1850441661992328</v>
+        <v>0.1790342654283756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,25 +3121,25 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>23.5093122581746</v>
+        <v>23.47035234733546</v>
       </c>
       <c r="K24" t="n">
-        <v>9.506166344155154</v>
+        <v>5.895666469546246</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>42.85714285714285</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>10.64091777321344</v>
+        <v>12.06452679688787</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4509642446004714</v>
+        <v>3.875827658758912</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3172,19 +3163,19 @@
         <v>75</v>
       </c>
       <c r="X24" t="n">
-        <v>12.34567843316572</v>
+        <v>12.66805408629466</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.527477806544887</v>
+        <v>6.010920905371552</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA24" t="n">
-        <v>56.25</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="AB24" t="n">
-        <v>13.49437352217959</v>
+        <v>15.12175849663499</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3221,10 +3212,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C25" t="n">
-        <v>3.54233375137217</v>
+        <v>3.497413402668605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3249,25 +3240,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>15.86762151234635</v>
+        <v>15.84414756511959</v>
       </c>
       <c r="K25" t="n">
-        <v>1.312647297093372</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>55.17241379310344</v>
+        <v>58.92857142857143</v>
       </c>
       <c r="N25" t="n">
-        <v>17.66168357682097</v>
+        <v>17.44339762958513</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>6.600708678844769</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3276,10 +3267,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="S25" t="n">
-        <v>36.33689746236128</v>
+        <v>36.36804514163651</v>
       </c>
       <c r="T25" t="n">
-        <v>30.32976920430539</v>
+        <v>30.29862152503016</v>
       </c>
       <c r="U25" t="n">
         <v>52.07048830990042</v>
@@ -3308,10 +3299,10 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG25" t="n">
-        <v>54.59698175248721</v>
+        <v>54.71095697250696</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.9384451671213583</v>
+        <v>-1.052420387141112</v>
       </c>
       <c r="AI25" t="n">
         <v>38.74647126766948</v>
@@ -3330,10 +3321,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4506148940008851</v>
+        <v>0.4509165105785117</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,10 +3398,10 @@
         <v>51.35135135135135</v>
       </c>
       <c r="AG26" t="n">
-        <v>41.1933407176374</v>
+        <v>41.57071733862015</v>
       </c>
       <c r="AH26" t="n">
-        <v>10.15801063371396</v>
+        <v>9.780634012731205</v>
       </c>
       <c r="AI26" t="n">
         <v>35.89489666561879</v>
@@ -3429,10 +3420,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C27" t="n">
-        <v>44.85287060452833</v>
+        <v>45.79946122542221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,10 +3448,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>60.44609892941529</v>
+        <v>59.63969482143187</v>
       </c>
       <c r="K27" t="n">
-        <v>36.06953327894855</v>
+        <v>38.94119215507532</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3485,25 +3476,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>36.63912667406974</v>
+        <v>38.94119215507532</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.416859657248736</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA27" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB27" t="n">
-        <v>10.45678423176366</v>
+        <v>12.27246413141115</v>
       </c>
       <c r="AC27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.602325581395339</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3524,10 +3515,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C28" t="n">
-        <v>1.586539975011923</v>
+        <v>1.630044524381325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3584,25 +3575,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X28" t="n">
-        <v>18.63435792130579</v>
+        <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.088638979207293</v>
+        <v>1.571338720394932</v>
       </c>
       <c r="Z28" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AA28" t="n">
-        <v>52.94117647058823</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.61912843879964</v>
+        <v>11.49430578992027</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.992841098749865</v>
+        <v>4.499361488849907</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3633,14 +3624,14 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4151498176679176</v>
+        <v>0.4121951352071678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3650,7 +3641,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3664,13 +3655,17 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>14.84388056400452</v>
+        <v>14.02651973380333</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N29" t="n">
+        <v>18.00706743337966</v>
+      </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
@@ -3702,7 +3697,7 @@
         <v>54.29671088217374</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.375116100935465</v>
+        <v>10.02010676109818</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -3713,7 +3708,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.6895279444004698</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3744,10 +3739,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4057620313238409</v>
+        <v>0.4313476386314181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3775,17 +3770,13 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>10.84318426819528</v>
+        <v>17.83247840238216</v>
       </c>
       <c r="L30" t="n">
-        <v>13</v>
-      </c>
-      <c r="M30" t="n">
-        <v>61.53846153846154</v>
-      </c>
-      <c r="N30" t="n">
-        <v>15.83763170086855</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>5</v>
       </c>
@@ -3814,25 +3805,25 @@
         <v>64.17910447761194</v>
       </c>
       <c r="X30" t="n">
-        <v>12.26790380466121</v>
+        <v>18.28742967351311</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.269035484037218</v>
+        <v>0.3846150621301558</v>
       </c>
       <c r="Z30" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="AA30" t="n">
-        <v>44.26229508196721</v>
+        <v>37.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>13.18964501957661</v>
+        <v>13.71773330520145</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>8.843187705870292</v>
+        <v>9.652509944991895</v>
       </c>
       <c r="AE30" t="n">
         <v>47</v>
@@ -3863,10 +3854,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1842096948138398</v>
+        <v>0.1848632821453136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3885,7 @@
         <v>20.56525919639532</v>
       </c>
       <c r="K31" t="n">
-        <v>5.788448869743434</v>
+        <v>6.163792795411416</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -3907,7 +3898,7 @@
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>3.981106798760448</v>
+        <v>3.613479797186003</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3970,10 +3961,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C32" t="n">
-        <v>2.303142782960381</v>
+        <v>2.302463791572055</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +3992,7 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>5.678254910725955</v>
+        <v>5.647099818845147</v>
       </c>
       <c r="L32" t="n">
         <v>37</v>
@@ -4043,7 +4034,7 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.376852910100672</v>
+        <v>6.404454025885742</v>
       </c>
       <c r="Z32" t="n">
         <v>22</v>
@@ -4058,7 +4049,7 @@
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.733702765130007</v>
+        <v>1.704724255313961</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4089,10 +4080,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C33" t="n">
-        <v>1.736744873407899</v>
+        <v>1.726847804072916</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4120,16 +4111,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.981927194757031</v>
+        <v>5.377975228200493</v>
       </c>
       <c r="L33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M33" t="n">
-        <v>64.28571428571429</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N33" t="n">
-        <v>11.05029636535382</v>
+        <v>11.14242984879175</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4198,10 +4189,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7956690499983533</v>
+        <v>0.7948288380838421</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,7 +4220,7 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>4.838171095620458</v>
+        <v>4.72746391095582</v>
       </c>
       <c r="L34" t="n">
         <v>22</v>
@@ -4279,19 +4270,19 @@
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AF34" t="n">
-        <v>53.84615384615385</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="AG34" t="n">
-        <v>31.7080316729961</v>
+        <v>30.89327423650132</v>
       </c>
       <c r="AH34" t="n">
-        <v>22.13812217315774</v>
+        <v>23.16077981755273</v>
       </c>
       <c r="AI34" t="n">
-        <v>38.56944827051576</v>
+        <v>38.38404689217949</v>
       </c>
       <c r="AJ34" t="n">
         <v>50</v>
@@ -4307,10 +4298,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C35" t="n">
-        <v>1.940147426149365</v>
+        <v>1.940231657509542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4342,7 +4333,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.376297606927842</v>
+        <v>9.381046170977347</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
@@ -4384,7 +4375,7 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.636086153593657</v>
+        <v>6.632032766026952</v>
       </c>
       <c r="Z35" t="n">
         <v>10</v>
@@ -4430,10 +4421,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0809437873857608</v>
+        <v>0.08139813523334197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4458,19 +4449,19 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>14.25367779956082</v>
+        <v>14.21000360644873</v>
       </c>
       <c r="K36" t="n">
-        <v>3.743318171809307</v>
+        <v>4.272532338489099</v>
       </c>
       <c r="L36" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M36" t="n">
-        <v>55.17241379310344</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N36" t="n">
-        <v>20.88828552891385</v>
+        <v>20.5096675101567</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4539,24 +4530,24 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06654914414865935</v>
+        <v>0.06516014485159648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4570,22 +4561,22 @@
         <v>14.09373072523551</v>
       </c>
       <c r="K37" t="n">
-        <v>8.330770719944681</v>
+        <v>6.069714378721769</v>
       </c>
       <c r="L37" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M37" t="n">
-        <v>62.5</v>
+        <v>58.13953488372093</v>
       </c>
       <c r="N37" t="n">
-        <v>14.55815754988779</v>
+        <v>22.10605372631138</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.819827301868804</v>
       </c>
       <c r="Q37" t="n">
         <v>36</v>
@@ -4612,22 +4603,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.396250069112505</v>
+        <v>5.412542576915458</v>
       </c>
       <c r="Z37" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="AA37" t="n">
-        <v>48.48484848484848</v>
+        <v>56.60377358490566</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.19858307042675</v>
+        <v>12.70203986642455</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.6249756674243323</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4658,10 +4649,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C38" t="n">
-        <v>1.673116318921822</v>
+        <v>1.667516715492338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4689,22 +4680,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>5.603371000749147</v>
+        <v>5.249936519396448</v>
       </c>
       <c r="L38" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>53.84615384615385</v>
+        <v>53.65853658536585</v>
       </c>
       <c r="N38" t="n">
-        <v>10.24068983236122</v>
+        <v>10.53259634513365</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>4.163341527440134</v>
+        <v>4.513127169181885</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4713,10 +4704,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S38" t="n">
-        <v>57.62086893326622</v>
+        <v>57.98301689992832</v>
       </c>
       <c r="T38" t="n">
-        <v>-6.458078235591806</v>
+        <v>-6.820226202253906</v>
       </c>
       <c r="U38" t="n">
         <v>36.75230846944931</v>
@@ -4745,10 +4736,10 @@
         <v>56.66666666666666</v>
       </c>
       <c r="AG38" t="n">
-        <v>18.01886325926947</v>
+        <v>18.29908604822881</v>
       </c>
       <c r="AH38" t="n">
-        <v>38.64780340739719</v>
+        <v>38.36758061843786</v>
       </c>
       <c r="AI38" t="n">
         <v>39.19730700081361</v>
@@ -4767,19 +4758,19 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C39" t="n">
-        <v>2.709947729267776</v>
+        <v>2.739640625746489</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4794,27 +4785,17 @@
       <c r="I39" t="n">
         <v>10</v>
       </c>
-      <c r="J39" t="n">
-        <v>10.28651724741822</v>
-      </c>
-      <c r="K39" t="n">
-        <v>7.271925866617401</v>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>20</v>
-      </c>
-      <c r="M39" t="n">
-        <v>60</v>
-      </c>
-      <c r="N39" t="n">
-        <v>14.00932717052249</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
         <v>5</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
         <v>43</v>
       </c>
@@ -4837,25 +4818,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X39" t="n">
-        <v>10.2437411865161</v>
+        <v>11.08431820998319</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.695677131340113</v>
+        <v>2.37388492403301</v>
       </c>
       <c r="Z39" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AA39" t="n">
         <v>40</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.44893944893184</v>
+        <v>11.86565257041252</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.395864408943094</v>
+        <v>3.71428799880581</v>
       </c>
       <c r="AE39" t="n">
         <v>45</v>
@@ -4864,10 +4845,10 @@
         <v>60</v>
       </c>
       <c r="AG39" t="n">
-        <v>38.69657512107894</v>
+        <v>39.15097959687783</v>
       </c>
       <c r="AH39" t="n">
-        <v>21.30342487892106</v>
+        <v>20.84902040312217</v>
       </c>
       <c r="AI39" t="n">
         <v>45.45185459035139</v>
@@ -4886,14 +4867,14 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2534708654888039</v>
+        <v>0.2477334414448768</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4903,7 +4884,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4946,25 +4927,25 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>44.24108228242589</v>
+        <v>43.91653617576685</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.028437883433322</v>
+        <v>5.989269685016363</v>
       </c>
       <c r="Z40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB40" t="n">
-        <v>15.74098979535976</v>
+        <v>11.63467188629951</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.012343755941603</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4995,10 +4976,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C41" t="n">
-        <v>1.795157977823683</v>
+        <v>1.845510139866752</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5026,7 +5007,7 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>18.63415909755402</v>
+        <v>21.96171381781607</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -5061,25 +5042,25 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X41" t="n">
-        <v>22.08082251686328</v>
+        <v>22.99353879000634</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.823263595584946</v>
+        <v>0.8389261601391751</v>
       </c>
       <c r="Z41" t="n">
         <v>21</v>
       </c>
       <c r="AA41" t="n">
-        <v>52.38095238095238</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.05755699448648</v>
+        <v>15.75920552664896</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.1818711051167043</v>
+        <v>2.179357036160012</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5097,10 +5078,10 @@
         <v>43.43546988238708</v>
       </c>
       <c r="AJ41" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AK41" t="n">
-        <v>53.125</v>
+        <v>51.51515151515152</v>
       </c>
     </row>
     <row r="42">
@@ -5110,10 +5091,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C42" t="n">
-        <v>3.77598585089285</v>
+        <v>3.684774834954423</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5171,22 +5152,18 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.36408605589371</v>
+        <v>4.72253528070028</v>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>8.674423338154757</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>7.820804492573941</v>
+        <v>5.539048225986953</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5215,10 +5192,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C43" t="n">
-        <v>6.644483389554546</v>
+        <v>6.677353267297351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,11 +5212,7 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5247,25 +5220,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>14.23748336761605</v>
+        <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1.825396825396819</v>
       </c>
       <c r="L43" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M43" t="n">
-        <v>87.5</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="N43" t="n">
-        <v>15.08065821191502</v>
+        <v>19.09694860740999</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>4.000000000000004</v>
+        <v>2.135619641465336</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5289,13 +5262,13 @@
         <v>65.21739130434783</v>
       </c>
       <c r="X43" t="n">
-        <v>22.98532002896849</v>
+        <v>21.54591253356677</v>
       </c>
       <c r="Y43" t="n">
-        <v>14.23748336761605</v>
+        <v>13.81322112308199</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
@@ -5334,10 +5307,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C44" t="n">
-        <v>4.589596061858713</v>
+        <v>4.617418472494092</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5356,7 +5329,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5366,25 +5339,25 @@
         <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>20.19885997293468</v>
+        <v>20.15821391009879</v>
       </c>
       <c r="K44" t="n">
-        <v>2.37319974163106</v>
+        <v>2.941359962571521</v>
       </c>
       <c r="L44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M44" t="n">
-        <v>75</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N44" t="n">
-        <v>17.79362702945675</v>
+        <v>17.71688663511587</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>7.449996950000015</v>
+        <v>6.856952385314252</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5439,10 +5412,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02336521631491709</v>
+        <v>0.02331608935112403</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5499,25 +5472,25 @@
         <v>60.82474226804123</v>
       </c>
       <c r="X45" t="n">
-        <v>17.77268946199939</v>
+        <v>19.58690552546656</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.754385103108635</v>
+        <v>3.448273365041554</v>
       </c>
       <c r="Z45" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="AA45" t="n">
-        <v>44.64285714285715</v>
+        <v>41.46341463414634</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.99257466903162</v>
+        <v>12.12027427869573</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.303572276785727</v>
+        <v>1.607145401785715</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5548,10 +5521,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C46" t="n">
-        <v>9.925001483769467</v>
+        <v>10.24762944918822</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5608,46 +5581,46 @@
         <v>67.46987951807229</v>
       </c>
       <c r="X46" t="n">
-        <v>21.83992704688877</v>
+        <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.347848626231218</v>
+        <v>2.524752475247527</v>
       </c>
       <c r="Z46" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AA46" t="n">
-        <v>35</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.96142056988751</v>
+        <v>13.92874497046169</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.674724119810822</v>
+        <v>0.4875571356018238</v>
       </c>
       <c r="AE46" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF46" t="n">
-        <v>56.75675675675676</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AG46" t="n">
-        <v>17.51782422577153</v>
+        <v>18.47930395809475</v>
       </c>
       <c r="AH46" t="n">
-        <v>39.23893253098522</v>
+        <v>39.41543288401051</v>
       </c>
       <c r="AI46" t="n">
-        <v>40.91418109016808</v>
+        <v>42.19234534367055</v>
       </c>
       <c r="AJ46" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="n">
-        <v>55</v>
+        <v>55.55555555555556</v>
       </c>
     </row>
     <row r="47">
@@ -5657,10 +5630,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7134735854711864</v>
+        <v>0.7190515603916305</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5685,25 +5658,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>25.00555187915373</v>
+        <v>21.47935966243942</v>
       </c>
       <c r="K47" t="n">
-        <v>5.940620010221798</v>
+        <v>6.768869483652629</v>
       </c>
       <c r="L47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>13.90859617018367</v>
+        <v>11.93630097509912</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.831750266693312</v>
+        <v>3.026285219627711</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5744,10 +5717,10 @@
         <v>55.81395348837209</v>
       </c>
       <c r="AG47" t="n">
-        <v>31.15164377116696</v>
+        <v>31.53536093163715</v>
       </c>
       <c r="AH47" t="n">
-        <v>24.66230971720514</v>
+        <v>24.27859255673494</v>
       </c>
       <c r="AI47" t="n">
         <v>41.1076144528241</v>
@@ -5766,10 +5739,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05945612871517148</v>
+        <v>0.06037201915166842</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5794,25 +5767,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>15.10031522654484</v>
+        <v>15.05707226133306</v>
       </c>
       <c r="K48" t="n">
-        <v>3.260866316162558</v>
+        <v>4.798167633235773</v>
       </c>
       <c r="L48" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="M48" t="n">
-        <v>56.14035087719298</v>
+        <v>53.19148936170212</v>
       </c>
       <c r="N48" t="n">
-        <v>15.05187700376106</v>
+        <v>16.33831490238179</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.526319141274373</v>
+        <v>4.963667289459872</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5821,10 +5794,10 @@
         <v>63.82978723404256</v>
       </c>
       <c r="S48" t="n">
-        <v>48.28707294375279</v>
+        <v>48.30174645805947</v>
       </c>
       <c r="T48" t="n">
-        <v>15.54271429028977</v>
+        <v>15.52804077598309</v>
       </c>
       <c r="U48" t="n">
         <v>49.53589653479511</v>
@@ -5853,10 +5826,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>24.09275607382841</v>
+        <v>24.16906018037669</v>
       </c>
       <c r="AH48" t="n">
-        <v>36.28460241673763</v>
+        <v>36.20829831018935</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5875,19 +5848,19 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2584777125767824</v>
+        <v>0.2620978289536294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5903,25 +5876,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>17.31218360853012</v>
+        <v>16.44500858212767</v>
       </c>
       <c r="K49" t="n">
-        <v>4.008516143581664</v>
+        <v>5.465210141951427</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M49" t="n">
-        <v>55.26315789473684</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N49" t="n">
-        <v>20.16929977836655</v>
+        <v>19.62381254669566</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.953271802329736</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5962,10 +5935,10 @@
         <v>63.04347826086956</v>
       </c>
       <c r="AG49" t="n">
-        <v>37.39620847757585</v>
+        <v>37.56267591119892</v>
       </c>
       <c r="AH49" t="n">
-        <v>25.64726978329371</v>
+        <v>25.48080234967065</v>
       </c>
       <c r="AI49" t="n">
         <v>48.60009642338971</v>
@@ -5984,10 +5957,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6859360155671922</v>
+        <v>0.6765829499210099</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6012,25 +5985,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>15.86420264054068</v>
+        <v>15.82134875518189</v>
       </c>
       <c r="K50" t="n">
-        <v>2.621723239326301</v>
+        <v>1.17089638562069</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M50" t="n">
-        <v>59.09090909090909</v>
+        <v>56.25</v>
       </c>
       <c r="N50" t="n">
-        <v>14.3136552748645</v>
+        <v>13.93148522800849</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.343065305441615</v>
+        <v>2.796361123060498</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6093,10 +6066,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1756563600364457</v>
+        <v>0.1746624978423223</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6121,25 +6094,25 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>21.20514974257153</v>
+        <v>21.1650162252606</v>
       </c>
       <c r="K51" t="n">
-        <v>1.201927809206427</v>
+        <v>0.5780995221746688</v>
       </c>
       <c r="L51" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>64.70588235294117</v>
+        <v>60</v>
       </c>
       <c r="N51" t="n">
-        <v>13.27232902826984</v>
+        <v>12.53420429163367</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>2.764840800334079</v>
+        <v>3.402232189792875</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6163,10 +6136,10 @@
         <v>84.61538461538461</v>
       </c>
       <c r="X51" t="n">
-        <v>27.67519948889778</v>
+        <v>27.46610563666652</v>
       </c>
       <c r="Y51" t="n">
-        <v>20.25809252510493</v>
+        <v>20.70927156075235</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6208,10 +6181,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C52" t="n">
-        <v>4.639664255276553</v>
+        <v>4.554964661732152</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6268,25 +6241,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>18.67501864135859</v>
+        <v>17.40749557792611</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.6255626143522597</v>
+        <v>3.527336813234672</v>
       </c>
       <c r="Z52" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA52" t="n">
-        <v>36.36363636363637</v>
+        <v>46.875</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.88094524686134</v>
+        <v>11.52777534943247</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>7.420859508395861</v>
+        <v>4.636197487475302</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6295,10 +6268,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>40.21614317249325</v>
+        <v>40.66320175807991</v>
       </c>
       <c r="AH52" t="n">
-        <v>28.20490945908569</v>
+        <v>27.75785087349903</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6317,10 +6290,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C53" t="n">
-        <v>1.366447918417026</v>
+        <v>1.433314925135065</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,7 +6310,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6345,25 +6322,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>32.2233051798102</v>
+        <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>1.314769450710029</v>
+        <v>6.218497106349585</v>
       </c>
       <c r="L53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>71.42857142857143</v>
+        <v>80</v>
       </c>
       <c r="N53" t="n">
-        <v>17.42947082383126</v>
+        <v>12.01629352258359</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>6.59847580519084</v>
+        <v>1.677205893684142</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6418,10 +6395,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08136102318276631</v>
+        <v>0.08056541359292872</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6417,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir. SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -6453,22 +6430,22 @@
         <v>42.98617858772242</v>
       </c>
       <c r="K54" t="n">
-        <v>1.701703323058701</v>
+        <v>0.7071871861994206</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>83.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N54" t="n">
-        <v>25.39606819333878</v>
+        <v>22.84645482583484</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>8.159447094589467</v>
+        <v>9.227556715112041</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6495,16 +6472,16 @@
         <v>10.17240666043591</v>
       </c>
       <c r="Y54" t="n">
-        <v>7.688588816512743</v>
+        <v>8.591279578206358</v>
       </c>
       <c r="Z54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA54" t="n">
-        <v>75</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="AB54" t="n">
-        <v>15.59141213484551</v>
+        <v>14.6756080381485</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6541,10 +6518,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C55" t="n">
-        <v>0.938363767050867</v>
+        <v>0.940970764634852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6601,19 +6578,19 @@
         <v>73.41772151898734</v>
       </c>
       <c r="X55" t="n">
-        <v>26.27862368424858</v>
+        <v>23.83539141846003</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.052904195038232</v>
+        <v>3.765467867902927</v>
       </c>
       <c r="Z55" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA55" t="n">
-        <v>46.66666666666666</v>
+        <v>40.625</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.30548381211707</v>
+        <v>12.1129640054664</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6628,10 +6605,10 @@
         <v>56.52173913043478</v>
       </c>
       <c r="AG55" t="n">
-        <v>41.90783258398348</v>
+        <v>42.1045199545839</v>
       </c>
       <c r="AH55" t="n">
-        <v>14.6139065464513</v>
+        <v>14.41721917585088</v>
       </c>
       <c r="AI55" t="n">
         <v>42.24743369429499</v>
@@ -6650,14 +6627,14 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C56" t="n">
-        <v>1.324724317854674</v>
+        <v>1.219931071698439</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6667,7 +6644,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6702,13 +6679,13 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>73.71938423294128</v>
+        <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.75651296466517</v>
+        <v>12.40658127082107</v>
       </c>
       <c r="Z56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="inlineStr"/>
@@ -6716,7 +6693,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>7.448814574803142</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6739,10 +6716,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C57" t="n">
-        <v>1.314293417714086</v>
+        <v>1.35316589984202</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6759,7 +6736,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6770,22 +6751,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>4.103602130933659</v>
+        <v>7.182644724273768</v>
       </c>
       <c r="L57" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M57" t="n">
-        <v>72.97297297297297</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="N57" t="n">
-        <v>17.55747606584726</v>
+        <v>14.44298545863656</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>5.663971033058313</v>
+        <v>2.628555474604921</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6812,7 +6793,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>18.97308445174279</v>
+        <v>16.57657444562146</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6854,10 +6835,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7247389768158776</v>
+        <v>0.7252969254380132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6885,7 +6866,7 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>9.186381087090156</v>
+        <v>9.270439476154802</v>
       </c>
       <c r="L58" t="n">
         <v>5</v>
@@ -6924,25 +6905,25 @@
         <v>82.5</v>
       </c>
       <c r="X58" t="n">
-        <v>13.2760081633051</v>
+        <v>13.39281154402059</v>
       </c>
       <c r="Y58" t="n">
-        <v>3.610320616453133</v>
+        <v>3.635479191082081</v>
       </c>
       <c r="Z58" t="n">
         <v>32</v>
       </c>
       <c r="AA58" t="n">
-        <v>43.75</v>
+        <v>46.875</v>
       </c>
       <c r="AB58" t="n">
-        <v>15.45903670279456</v>
+        <v>15.72239388744154</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.479185944833395</v>
+        <v>2.453725488457059</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6973,10 +6954,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C59" t="n">
-        <v>0.79483455879425</v>
+        <v>0.7952452061903268</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7001,25 +6982,25 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>11.17103304657197</v>
+        <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>1.599995919999997</v>
+        <v>1.67453944493241</v>
       </c>
       <c r="L59" t="n">
         <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>60</v>
+        <v>61.66666666666666</v>
       </c>
       <c r="N59" t="n">
-        <v>14.14811524564401</v>
+        <v>13.80404332835052</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.299216867133905</v>
+        <v>6.221282721908472</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7082,10 +7063,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C60" t="n">
-        <v>11.95381156111383</v>
+        <v>11.76213436016525</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7113,22 +7094,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>4.062710533828451</v>
+        <v>2.39408383879729</v>
       </c>
       <c r="L60" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M60" t="n">
-        <v>52.63157894736842</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="N60" t="n">
-        <v>13.55102180851627</v>
+        <v>13.86551306065141</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.783573814264263</v>
+        <v>5.47484381033998</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7169,10 +7150,10 @@
         <v>60.60606060606061</v>
       </c>
       <c r="AG60" t="n">
-        <v>25.49712065599171</v>
+        <v>24.59235950815647</v>
       </c>
       <c r="AH60" t="n">
-        <v>35.1089399500689</v>
+        <v>36.01370109790414</v>
       </c>
       <c r="AI60" t="n">
         <v>43.68344081994023</v>
@@ -7191,10 +7172,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6308608357045473</v>
+        <v>0.6195418075465641</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7213,7 +7194,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -7226,22 +7207,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>2.661937072468956</v>
+        <v>0.8199565742206927</v>
       </c>
       <c r="L61" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M61" t="n">
-        <v>78.26086956521739</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N61" t="n">
-        <v>21.0271844363258</v>
+        <v>19.19745484542576</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>7.147793171242345</v>
+        <v>9.105383237316955</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7260,16 +7241,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>10.25160740504591</v>
+        <v>11.86189056960708</v>
       </c>
       <c r="Z61" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA61" t="n">
-        <v>47.61904761904762</v>
+        <v>56.25</v>
       </c>
       <c r="AB61" t="n">
-        <v>12.61964957502634</v>
+        <v>11.77948701260922</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7306,10 +7287,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C62" t="n">
-        <v>9.283501125123307</v>
+        <v>9.269186413917835</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7366,46 +7347,46 @@
         <v>72.05882352941177</v>
       </c>
       <c r="X62" t="n">
-        <v>12.50949992621986</v>
+        <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.8356545961002881</v>
+        <v>0.8351893095768448</v>
       </c>
       <c r="Z62" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA62" t="n">
-        <v>48.27586206896552</v>
+        <v>47.45762711864407</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.78152481132399</v>
+        <v>11.73099212142922</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.174157303370782</v>
+        <v>1.174620999438514</v>
       </c>
       <c r="AE62" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF62" t="n">
-        <v>43.33333333333334</v>
+        <v>41.93548387096774</v>
       </c>
       <c r="AG62" t="n">
-        <v>44.33940860366076</v>
+        <v>44.36592091717431</v>
       </c>
       <c r="AH62" t="n">
-        <v>-1.006075270327429</v>
+        <v>-2.430437046206563</v>
       </c>
       <c r="AI62" t="n">
-        <v>27.37748557646652</v>
+        <v>26.41554306731223</v>
       </c>
       <c r="AJ62" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AK62" t="n">
-        <v>35.48387096774194</v>
+        <v>34.92063492063492</v>
       </c>
     </row>
     <row r="63">
@@ -7415,10 +7396,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1074382735342363</v>
+        <v>0.1124168614532846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7446,17 +7427,13 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>9.324285579518987</v>
+        <v>14.39026951187747</v>
       </c>
       <c r="L63" t="n">
-        <v>7</v>
-      </c>
-      <c r="M63" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="N63" t="n">
-        <v>20.04183163819911</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>5</v>
       </c>
@@ -7485,25 +7462,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X63" t="n">
-        <v>17.39093407257215</v>
+        <v>18.41511331267116</v>
       </c>
       <c r="Y63" t="n">
-        <v>6.8716111314578</v>
+        <v>3.398927457989431</v>
       </c>
       <c r="Z63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA63" t="n">
-        <v>42.85714285714285</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB63" t="n">
-        <v>15.9718454769194</v>
+        <v>14.16240728590613</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.359221507587939</v>
+        <v>6.83333255864198</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7534,10 +7511,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1485360157071749</v>
+        <v>0.1480155342121281</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7562,25 +7539,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>24.42078296285393</v>
+        <v>24.59083812498669</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4231274945741603</v>
+        <v>0.2969078143066461</v>
       </c>
       <c r="L64" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M64" t="n">
-        <v>70.58823529411765</v>
+        <v>70</v>
       </c>
       <c r="N64" t="n">
-        <v>16.04486965664466</v>
+        <v>15.93250966279426</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.557588097097587</v>
+        <v>4.689169674503657</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7621,10 +7598,10 @@
         <v>62</v>
       </c>
       <c r="AG64" t="n">
-        <v>38.6797117586984</v>
+        <v>39.37911668908677</v>
       </c>
       <c r="AH64" t="n">
-        <v>23.3202882413016</v>
+        <v>22.62088331091323</v>
       </c>
       <c r="AI64" t="n">
         <v>48.15044693099298</v>
@@ -7643,24 +7620,24 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C65" t="n">
-        <v>6.602759788992194</v>
+        <v>6.880328152273654</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7674,17 +7651,13 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>16.55045213462765</v>
+        <v>21.45002735356205</v>
       </c>
       <c r="L65" t="n">
-        <v>3</v>
-      </c>
-      <c r="M65" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N65" t="n">
-        <v>10.40484726341951</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
         <v>10</v>
       </c>
@@ -7713,25 +7686,25 @@
         <v>63.63636363636363</v>
       </c>
       <c r="X65" t="n">
-        <v>21.96943581422117</v>
+        <v>23.0117901863991</v>
       </c>
       <c r="Y65" t="n">
-        <v>4.442902964516049</v>
+        <v>1.269604182225548</v>
       </c>
       <c r="Z65" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA65" t="n">
-        <v>51.85185185185185</v>
+        <v>40</v>
       </c>
       <c r="AB65" t="n">
-        <v>10.27316155150781</v>
+        <v>9.344780687814966</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2.765506807866869</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7740,10 +7713,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG65" t="n">
-        <v>20.76273934208557</v>
+        <v>20.77548197579595</v>
       </c>
       <c r="AH65" t="n">
-        <v>33.78271520336897</v>
+        <v>33.76997256965859</v>
       </c>
       <c r="AI65" t="n">
         <v>40.06618319896197</v>
@@ -7762,10 +7735,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4606285485394214</v>
+        <v>0.4642399775087839</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7822,25 +7795,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X66" t="n">
-        <v>12.69724877030836</v>
+        <v>13.05901358398374</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.040820679789046</v>
+        <v>1.588705262061163</v>
       </c>
       <c r="Z66" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA66" t="n">
-        <v>33.87096774193548</v>
+        <v>39.34426229508197</v>
       </c>
       <c r="AB66" t="n">
-        <v>12.09095509275395</v>
+        <v>10.87162127762553</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.041662402324864</v>
+        <v>4.482508587744682</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7871,10 +7844,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02753757741424229</v>
+        <v>0.02747967777615017</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7888,7 +7861,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -7899,10 +7872,10 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>14.0514682678307</v>
+        <v>13.52521428537139</v>
       </c>
       <c r="K67" t="n">
-        <v>2.325588444204296</v>
+        <v>2.061245107645004</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
@@ -7911,13 +7884,13 @@
         <v>40</v>
       </c>
       <c r="N67" t="n">
-        <v>7.077382387711928</v>
+        <v>7.671407444036571</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.636356634986491</v>
+        <v>1.899599490786308</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7930,17 +7903,25 @@
         <v>0</v>
       </c>
       <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
+      <c r="X67" t="n">
+        <v>10.87173616493582</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>7.94656182183715</v>
+      </c>
       <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>3</v>
       </c>
-      <c r="AD67" t="inlineStr"/>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
       <c r="AE67" t="n">
         <v>0</v>
       </c>
@@ -7960,10 +7941,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C68" t="n">
-        <v>4.220342260510389</v>
+        <v>4.57994612254222</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8020,10 +8001,10 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>143.1366383982815</v>
+        <v>138.7086256764711</v>
       </c>
       <c r="Y68" t="n">
-        <v>3.159402126722621</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8034,7 +8015,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>4.99852126027932</v>
+        <v>7.999999999999996</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8065,19 +8046,19 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4180704968276227</v>
+        <v>0.4588273488835499</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8085,7 +8066,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8093,25 +8078,25 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>18.0901893667493</v>
+        <v>17.65828511877414</v>
       </c>
       <c r="K69" t="n">
-        <v>7.16577596545509</v>
+        <v>17.63866684189834</v>
       </c>
       <c r="L69" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M69" t="n">
-        <v>64.28571428571429</v>
+        <v>100</v>
       </c>
       <c r="N69" t="n">
-        <v>20.57486714421613</v>
+        <v>31.87870734966179</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>0.7784425830255959</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8127,25 +8112,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X69" t="n">
-        <v>11.44384654025008</v>
+        <v>17.63866684189834</v>
       </c>
       <c r="Y69" t="n">
-        <v>3.838767870642268</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA69" t="n">
-        <v>40</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB69" t="n">
-        <v>15.89332679715676</v>
+        <v>17.4308752423508</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.247508774066465</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8168,10 +8153,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4293358481176574</v>
+        <v>0.4330130721278142</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8199,16 +8184,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>12.57869793493205</v>
+        <v>13.5429246420508</v>
       </c>
       <c r="L70" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M70" t="n">
-        <v>33.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="N70" t="n">
-        <v>8.534401960408296</v>
+        <v>6.838424675154897</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8238,25 +8223,25 @@
         <v>67.79661016949153</v>
       </c>
       <c r="X70" t="n">
-        <v>14.32919111790623</v>
+        <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.531099070900377</v>
+        <v>1.328276475629142</v>
       </c>
       <c r="Z70" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA70" t="n">
-        <v>41.1764705882353</v>
+        <v>43.75</v>
       </c>
       <c r="AB70" t="n">
-        <v>10.2189247408603</v>
+        <v>9.881238882796172</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>6.569486272378944</v>
+        <v>6.761535408594554</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8265,10 +8250,10 @@
         <v>50</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.67448088405386</v>
+        <v>34.43478125619634</v>
       </c>
       <c r="AH70" t="n">
-        <v>15.32551911594614</v>
+        <v>15.56521874380366</v>
       </c>
       <c r="AI70" t="n">
         <v>35.8317605399894</v>
@@ -8287,10 +8272,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C71" t="n">
-        <v>3.118839142035807</v>
+        <v>3.114363490318125</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8315,25 +8300,25 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>14.92600999981897</v>
+        <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>0.9453030670739437</v>
+        <v>0.7491270026070751</v>
       </c>
       <c r="L71" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M71" t="n">
-        <v>59.70149253731343</v>
+        <v>61.42857142857143</v>
       </c>
       <c r="N71" t="n">
-        <v>17.21374694450511</v>
+        <v>16.76404623989205</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>1.044820215384612</v>
+        <v>1.241572045939976</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8396,10 +8381,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0715559764247596</v>
+        <v>0.0728627792222626</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8424,25 +8409,25 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>21.72769951373251</v>
+        <v>21.68783215290538</v>
       </c>
       <c r="K72" t="n">
-        <v>1.780420829627971</v>
+        <v>3.586441604887636</v>
       </c>
       <c r="L72" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M72" t="n">
-        <v>56.52173913043478</v>
+        <v>40</v>
       </c>
       <c r="N72" t="n">
-        <v>17.3898758509428</v>
+        <v>15.320771416384</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>3.163259833402865</v>
+        <v>1.364617196238993</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8469,7 +8454,7 @@
         <v>37.9194877971514</v>
       </c>
       <c r="Y72" t="n">
-        <v>20.334123172046</v>
+        <v>18.87921198354775</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8511,10 +8496,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07134735863056584</v>
+        <v>0.07057280824278518</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8531,7 +8516,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8542,22 +8531,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>8.447301520186246</v>
+        <v>7.269992351935683</v>
       </c>
       <c r="L73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M73" t="n">
-        <v>66.66666666666667</v>
+        <v>87.5</v>
       </c>
       <c r="N73" t="n">
-        <v>10.41015246766233</v>
+        <v>11.41329860865269</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>1.431753910008315</v>
+        <v>2.544987268301102</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8581,25 +8570,25 @@
         <v>77.27272727272727</v>
       </c>
       <c r="X73" t="n">
-        <v>15.4234441942493</v>
+        <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.043956427363839</v>
+        <v>7.0437863473783</v>
       </c>
       <c r="Z73" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA73" t="n">
-        <v>57.89473684210526</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AB73" t="n">
-        <v>13.22595385437325</v>
+        <v>12.3210114297409</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>4.210525924899966</v>
+        <v>3.180221672613626</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8630,19 +8619,19 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C74" t="n">
-        <v>5.648332426128394</v>
+        <v>5.54798018935228</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8650,38 +8639,24 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>5</v>
       </c>
       <c r="I74" t="n">
         <v>10</v>
       </c>
-      <c r="J74" t="n">
-        <v>18.35970785011217</v>
-      </c>
-      <c r="K74" t="n">
-        <v>19.50232860677821</v>
-      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
-        <v>4</v>
-      </c>
-      <c r="M74" t="n">
-        <v>75</v>
-      </c>
-      <c r="N74" t="n">
-        <v>16.52901193804602</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
         <v>8</v>
       </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="n">
         <v>35</v>
       </c>
@@ -8704,25 +8679,25 @@
         <v>77.39130434782609</v>
       </c>
       <c r="X74" t="n">
-        <v>32.26405389680429</v>
+        <v>33.81594625096176</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.4379497995073</v>
+        <v>5.407729434752351</v>
       </c>
       <c r="Z74" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AA74" t="n">
-        <v>50</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AB74" t="n">
-        <v>17.95958840191798</v>
+        <v>18.08889136107177</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>7.751016081511686</v>
+        <v>4.854805300481713</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8731,10 +8706,10 @@
         <v>51.28205128205128</v>
       </c>
       <c r="AG74" t="n">
-        <v>30.76277313699709</v>
+        <v>30.78334080462358</v>
       </c>
       <c r="AH74" t="n">
-        <v>20.51927814505419</v>
+        <v>20.49871047742771</v>
       </c>
       <c r="AI74" t="n">
         <v>36.19936288445796</v>
@@ -8753,10 +8728,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C75" t="n">
-        <v>0.12496217888603</v>
+        <v>0.1246994373665468</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8781,25 +8756,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>23.39449322057143</v>
+        <v>23.35547482758762</v>
       </c>
       <c r="K75" t="n">
-        <v>1.182427179967194</v>
+        <v>0.9182823054377121</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>63.63636363636363</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>19.66198819310451</v>
+        <v>18.24441559719496</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.761274219548106</v>
+        <v>5.03547779299498</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8862,19 +8837,19 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C76" t="n">
-        <v>1.927630377899214</v>
+        <v>1.962090554770929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8889,27 +8864,17 @@
       <c r="I76" t="n">
         <v>10</v>
       </c>
-      <c r="J76" t="n">
-        <v>11.17000304157492</v>
-      </c>
-      <c r="K76" t="n">
-        <v>11.22002120062751</v>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
-        <v>15</v>
-      </c>
-      <c r="M76" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N76" t="n">
-        <v>8.171123468305536</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
         <v>10</v>
       </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="n">
         <v>40</v>
       </c>
@@ -8932,25 +8897,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X76" t="n">
-        <v>11.76167345580381</v>
+        <v>14.64967258969352</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.4846493779376848</v>
+        <v>1.257199568721401</v>
       </c>
       <c r="Z76" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="AA76" t="n">
-        <v>44.64285714285715</v>
+        <v>36.73469387755102</v>
       </c>
       <c r="AB76" t="n">
-        <v>9.905833547760849</v>
+        <v>11.17042929607493</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.53247071942987</v>
+        <v>2.777721939522559</v>
       </c>
       <c r="AE76" t="n">
         <v>33</v>
@@ -8959,10 +8924,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG76" t="n">
-        <v>30.23579535077641</v>
+        <v>30.74315192765171</v>
       </c>
       <c r="AH76" t="n">
-        <v>24.30965919467813</v>
+        <v>23.80230261780284</v>
       </c>
       <c r="AI76" t="n">
         <v>37.98593853621745</v>
@@ -8981,10 +8946,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5240484405870526</v>
+        <v>0.5391845583339272</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9012,64 +8977,64 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>7.930939563645012</v>
+        <v>11.04831437719485</v>
       </c>
       <c r="L77" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M77" t="n">
-        <v>65.38461538461539</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N77" t="n">
-        <v>13.92336255069648</v>
+        <v>17.60712689589592</v>
       </c>
       <c r="O77" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R77" t="n">
-        <v>57.14285714285715</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="S77" t="n">
-        <v>38.66198005755459</v>
+        <v>41.43697369229825</v>
       </c>
       <c r="T77" t="n">
-        <v>18.48087708530255</v>
+        <v>17.18371596287417</v>
       </c>
       <c r="U77" t="n">
-        <v>39.07078562746877</v>
+        <v>40.73783598787858</v>
       </c>
       <c r="V77" t="n">
         <v>75</v>
       </c>
       <c r="W77" t="n">
-        <v>61.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="X77" t="n">
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>7.181366083285823</v>
+        <v>4.500480761895275</v>
       </c>
       <c r="Z77" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="AA77" t="n">
-        <v>50</v>
+        <v>42.22222222222222</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.91075471878268</v>
+        <v>10.98534356164255</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>3.03671126989794</v>
+        <v>5.758687878200741</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9100,10 +9065,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04839937519200223</v>
+        <v>0.04850579135967129</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9128,25 +9093,25 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>19.53698884929083</v>
+        <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>3.571424984056137</v>
+        <v>3.821666540896906</v>
       </c>
       <c r="L78" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M78" t="n">
-        <v>59.09090909090909</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N78" t="n">
-        <v>18.4831683459156</v>
+        <v>19.00474876988608</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.4137965814507538</v>
+        <v>0.1717690199404043</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9209,10 +9174,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8323858631374755</v>
+        <v>0.8273048482006242</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9240,22 +9205,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>4.986917411089298</v>
+        <v>4.346060665241835</v>
       </c>
       <c r="L79" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M79" t="n">
-        <v>64.28571428571429</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N79" t="n">
-        <v>12.07238133735722</v>
+        <v>11.5741910175252</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0.01246116109827611</v>
+        <v>0.6267024654204256</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9296,10 +9261,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>27.89670918702137</v>
+        <v>28.05013312467481</v>
       </c>
       <c r="AH79" t="n">
-        <v>24.88106859075641</v>
+        <v>24.72764465310297</v>
       </c>
       <c r="AI79" t="n">
         <v>37.00593802298759</v>
@@ -9318,10 +9283,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1283000738154122</v>
+        <v>0.1301121057540404</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9349,7 +9314,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.043089957316416</v>
+        <v>6.52665445010614</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9360,7 +9325,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.71893015018674</v>
+        <v>3.260541286895169</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9387,43 +9352,43 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.453623651977358</v>
+        <v>5.132431725545405</v>
       </c>
       <c r="Z80" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="AA80" t="n">
-        <v>39.39393939393939</v>
+        <v>34.88372093023256</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.40307523818483</v>
+        <v>12.29734885658497</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.653058523902218</v>
+        <v>3.022706628421878</v>
       </c>
       <c r="AE80" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF80" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AG80" t="n">
-        <v>41.81265657810281</v>
+        <v>40.28516284122691</v>
       </c>
       <c r="AH80" t="n">
-        <v>8.187343421897189</v>
+        <v>11.71483715877309</v>
       </c>
       <c r="AI80" t="n">
-        <v>32.06059352575905</v>
+        <v>33.49851695035678</v>
       </c>
       <c r="AJ80" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK80" t="n">
-        <v>52.77777777777778</v>
+        <v>52.05479452054794</v>
       </c>
     </row>
     <row r="81">
@@ -9433,10 +9398,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C81" t="n">
-        <v>1.230846216589382</v>
+        <v>1.225135555928601</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9493,25 +9458,25 @@
         <v>64.58333333333333</v>
       </c>
       <c r="X81" t="n">
-        <v>30.91171973579283</v>
+        <v>30.54991476816724</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.673403231813019</v>
+        <v>3.682487817253788</v>
       </c>
       <c r="Z81" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA81" t="n">
-        <v>64.70588235294117</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB81" t="n">
-        <v>12.10152155368538</v>
+        <v>12.75904350803913</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>9.389828174576264</v>
+        <v>6.559048338748408</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9542,14 +9507,14 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C82" t="n">
-        <v>5.377129022473106</v>
+        <v>5.308573914764847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9559,7 +9524,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9602,25 +9567,25 @@
         <v>57.14285714285715</v>
       </c>
       <c r="X82" t="n">
-        <v>16.65327680511959</v>
+        <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>3.8198783758293</v>
+        <v>5.046116126454425</v>
       </c>
       <c r="Z82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA82" t="n">
-        <v>37.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB82" t="n">
-        <v>12.95948113262313</v>
+        <v>7.560260277872317</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.1872753133693617</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9651,10 +9616,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C83" t="n">
-        <v>5.836088628658977</v>
+        <v>5.745750590098422</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9696,10 +9661,10 @@
         <v>61.90476190476191</v>
       </c>
       <c r="S83" t="n">
-        <v>58.36301266696502</v>
+        <v>58.76678340717467</v>
       </c>
       <c r="T83" t="n">
-        <v>3.541749237796886</v>
+        <v>3.137978497587234</v>
       </c>
       <c r="U83" t="n">
         <v>46.81404026715268</v>
@@ -9714,22 +9679,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.990329099423328</v>
+        <v>4.491962119101577</v>
       </c>
       <c r="Z83" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="AA83" t="n">
-        <v>38.59649122807018</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.67589451319982</v>
+        <v>12.49305910300401</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.102444192044762</v>
+        <v>1.578964361909518</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9760,10 +9725,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C84" t="n">
-        <v>2.175885832955144</v>
+        <v>2.146329264667207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9791,22 +9756,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>4.16520673010139</v>
+        <v>2.750258390755822</v>
       </c>
       <c r="L84" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M84" t="n">
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>11.61841236501015</v>
+        <v>10.44668109268372</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0.8014127712160368</v>
+        <v>2.189524040599955</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9869,10 +9834,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C85" t="n">
-        <v>6.279401884633967</v>
+        <v>6.25579004465426</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9897,25 +9862,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>15.93296998857089</v>
+        <v>14.50238586538229</v>
       </c>
       <c r="K85" t="n">
-        <v>1.498318645485508</v>
+        <v>1.116664134101075</v>
       </c>
       <c r="L85" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M85" t="n">
-        <v>60</v>
+        <v>62.71186440677966</v>
       </c>
       <c r="N85" t="n">
-        <v>15.37314992968119</v>
+        <v>13.80805675789563</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.405703504531579</v>
+        <v>6.807320954309026</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9924,10 +9889,10 @@
         <v>60.60606060606061</v>
       </c>
       <c r="S85" t="n">
-        <v>66.03551330824058</v>
+        <v>65.70160479251388</v>
       </c>
       <c r="T85" t="n">
-        <v>-5.429452702179972</v>
+        <v>-5.095544186453267</v>
       </c>
       <c r="U85" t="n">
         <v>43.68344081994023</v>
@@ -9978,24 +9943,24 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C86" t="n">
-        <v>4.29544455063715</v>
+        <v>4.521655835669703</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -10006,25 +9971,25 @@
         <v>10</v>
       </c>
       <c r="J86" t="n">
-        <v>16.26863740490974</v>
+        <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>6.002929924928613</v>
       </c>
       <c r="L86" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="M86" t="n">
-        <v>58.49056603773585</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N86" t="n">
-        <v>15.77569664569882</v>
+        <v>14.84796328255281</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
       </c>
       <c r="P86" t="n">
-        <v>6.000000000000005</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>54</v>
@@ -10048,10 +10013,10 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>88.01181128002702</v>
+        <v>80.42094873883605</v>
       </c>
       <c r="Y86" t="n">
-        <v>16.26863740490974</v>
+        <v>11.85908702965172</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -10093,10 +10058,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C87" t="n">
-        <v>5.867381329080741</v>
+        <v>5.77177301124923</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10124,16 +10089,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>8.808649553092085</v>
+        <v>7.035624865276313</v>
       </c>
       <c r="L87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M87" t="n">
-        <v>66.66666666666667</v>
+        <v>65</v>
       </c>
       <c r="N87" t="n">
-        <v>10.8676286810291</v>
+        <v>9.196302056878018</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10142,19 +10107,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R87" t="n">
-        <v>56.25</v>
+        <v>55.31914893617022</v>
       </c>
       <c r="S87" t="n">
-        <v>34.92338863896205</v>
+        <v>35.43920972095994</v>
       </c>
       <c r="T87" t="n">
-        <v>21.32661136103795</v>
+        <v>19.87993921521028</v>
       </c>
       <c r="U87" t="n">
-        <v>42.27501741982778</v>
+        <v>41.24545983821874</v>
       </c>
       <c r="V87" t="n">
         <v>66</v>
@@ -10163,25 +10128,25 @@
         <v>63.63636363636363</v>
       </c>
       <c r="X87" t="n">
-        <v>10.54958794594156</v>
+        <v>10.60669620884278</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.574803149606308</v>
+        <v>3.228621291448519</v>
       </c>
       <c r="Z87" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="AA87" t="n">
-        <v>46.42857142857143</v>
+        <v>47.5</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.27959213501269</v>
+        <v>11.30063569394995</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>2.464</v>
+        <v>0.7971145175834082</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10190,10 +10155,10 @@
         <v>44.18604651162791</v>
       </c>
       <c r="AG87" t="n">
-        <v>45.99400614335055</v>
+        <v>46.51018272212174</v>
       </c>
       <c r="AH87" t="n">
-        <v>-1.807959631722639</v>
+        <v>-2.324136210493833</v>
       </c>
       <c r="AI87" t="n">
         <v>30.43330983917051</v>
@@ -10212,19 +10177,19 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C88" t="n">
-        <v>1.138011189483181</v>
+        <v>1.174131674175904</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10239,12 +10204,8 @@
       <c r="I88" t="n">
         <v>10</v>
       </c>
-      <c r="J88" t="n">
-        <v>24.22103615752376</v>
-      </c>
-      <c r="K88" t="n">
-        <v>27.49321404266529</v>
-      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>0</v>
       </c>
@@ -10253,9 +10214,7 @@
       <c r="O88" t="n">
         <v>3</v>
       </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="n">
         <v>34</v>
       </c>
@@ -10263,10 +10222,10 @@
         <v>70.58823529411765</v>
       </c>
       <c r="S88" t="n">
-        <v>46.57170396883187</v>
+        <v>46.24430828482993</v>
       </c>
       <c r="T88" t="n">
-        <v>24.01653132528578</v>
+        <v>24.34392700928773</v>
       </c>
       <c r="U88" t="n">
         <v>53.83109020528557</v>
@@ -10278,25 +10237,25 @@
         <v>61.53846153846154</v>
       </c>
       <c r="X88" t="n">
-        <v>28.54494720514669</v>
+        <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.8181832</v>
+        <v>1.827674875734864</v>
       </c>
       <c r="Z88" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AA88" t="n">
-        <v>37.03703703703704</v>
+        <v>56.25</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.99798546139592</v>
+        <v>15.72146942893418</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>5.224563299187324</v>
+        <v>4.250001330806697</v>
       </c>
       <c r="AE88" t="n">
         <v>31</v>
@@ -10327,19 +10286,19 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C89" t="n">
-        <v>2.24890213393926</v>
+        <v>2.279564092810787</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10354,12 +10313,8 @@
       <c r="I89" t="n">
         <v>10</v>
       </c>
-      <c r="J89" t="n">
-        <v>19.71415010641037</v>
-      </c>
-      <c r="K89" t="n">
-        <v>22.15666498386695</v>
-      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
         <v>0</v>
       </c>
@@ -10368,9 +10323,7 @@
       <c r="O89" t="n">
         <v>4</v>
       </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
+      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="n">
         <v>44</v>
       </c>
@@ -10393,25 +10346,25 @@
         <v>76.08695652173913</v>
       </c>
       <c r="X89" t="n">
-        <v>24.19638141496434</v>
+        <v>27.21456043612742</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.642331610517955</v>
+        <v>2.666666666666673</v>
       </c>
       <c r="Z89" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AA89" t="n">
-        <v>37.77777777777778</v>
+        <v>41.37931034482759</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.84011558011209</v>
+        <v>13.33137870103895</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>8.497220934911642</v>
+        <v>7.534246575342463</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10442,19 +10395,19 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C90" t="n">
-        <v>2.989496043921007</v>
+        <v>3.060236727335029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10469,23 +10422,17 @@
       <c r="I90" t="n">
         <v>10</v>
       </c>
-      <c r="J90" t="n">
-        <v>16.58671596100499</v>
-      </c>
-      <c r="K90" t="n">
-        <v>17.84667829943103</v>
-      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
         <v>8</v>
       </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
+      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
         <v>42</v>
       </c>
@@ -10508,25 +10455,25 @@
         <v>71.59090909090909</v>
       </c>
       <c r="X90" t="n">
-        <v>24.88307914387619</v>
+        <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.70021549957492</v>
+        <v>2.065293786820177</v>
       </c>
       <c r="Z90" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="AA90" t="n">
-        <v>36.36363636363637</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="AB90" t="n">
-        <v>13.02002130004772</v>
+        <v>12.07408683126673</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
       </c>
       <c r="AD90" t="n">
-        <v>1.322265869687089</v>
+        <v>0.9544177435374168</v>
       </c>
       <c r="AE90" t="n">
         <v>23</v>
@@ -10557,19 +10504,19 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2296884258939615</v>
+        <v>0.2321199887543919</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10588,22 +10535,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>2.59745863743821</v>
+        <v>3.68359159788838</v>
       </c>
       <c r="L91" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="M91" t="n">
-        <v>63.23529411764706</v>
+        <v>64.40677966101696</v>
       </c>
       <c r="N91" t="n">
-        <v>13.40930703367147</v>
+        <v>12.86145680465763</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.392350227683802</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10666,31 +10613,27 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C92" t="n">
-        <v>1.144269713503947</v>
+        <v>1.111677863413964</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>5</v>
       </c>
@@ -10701,22 +10644,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>8.600228137773126</v>
+        <v>5.507004299517559</v>
       </c>
       <c r="L92" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="M92" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N92" t="n">
-        <v>9.652661034213956</v>
+        <v>13.49671023601048</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.362872225435608</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10743,16 +10686,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>5.289373320547108</v>
+        <v>7.986984303549349</v>
       </c>
       <c r="Z92" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="AA92" t="n">
-        <v>53.19148936170212</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="AB92" t="n">
-        <v>10.95182935235971</v>
+        <v>11.39327922069919</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10767,10 +10710,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.36481220585512</v>
+        <v>40.40112302647967</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.57636426473311</v>
+        <v>12.54005344410856</v>
       </c>
       <c r="AI92" t="n">
         <v>39.52330421009647</v>
@@ -10789,10 +10732,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0419322183565457</v>
+        <v>0.0422604113243742</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10820,22 +10763,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>3.686213841192076</v>
+        <v>4.497739860495331</v>
       </c>
       <c r="L93" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M93" t="n">
-        <v>61.40350877192982</v>
+        <v>63.46153846153846</v>
       </c>
       <c r="N93" t="n">
-        <v>19.00391756101635</v>
+        <v>19.11345824251768</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.231527290939339</v>
+        <v>1.437600604099365</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10898,10 +10841,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C94" t="n">
-        <v>8.485537264368325</v>
+        <v>8.337583736718907</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10943,10 +10886,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S94" t="n">
-        <v>39.29728034587108</v>
+        <v>38.93356815930909</v>
       </c>
       <c r="T94" t="n">
-        <v>21.67832941022648</v>
+        <v>22.04204159678847</v>
       </c>
       <c r="U94" t="n">
         <v>45.72685693412379</v>
@@ -10958,25 +10901,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>51.90713520272774</v>
+        <v>49.568993011392</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.717791411042946</v>
       </c>
       <c r="Z94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA94" t="n">
-        <v>42.85714285714285</v>
+        <v>37.5</v>
       </c>
       <c r="AB94" t="n">
-        <v>14.2160206715065</v>
+        <v>11.204957938577</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>6.000000000000005</v>
+        <v>4.357053682896384</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11007,10 +10950,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1414430102873511</v>
+        <v>0.1440601251563084</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11027,7 +10970,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>5</v>
       </c>
@@ -11038,16 +10985,16 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>6.027188610462231</v>
+        <v>7.989005820534723</v>
       </c>
       <c r="L95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M95" t="n">
-        <v>60</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N95" t="n">
-        <v>19.08560282706251</v>
+        <v>18.17529258831296</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
@@ -11077,25 +11024,25 @@
         <v>84.78260869565217</v>
       </c>
       <c r="X95" t="n">
-        <v>11.96970959191628</v>
+        <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>5.307257653085018</v>
+        <v>3.604259677282939</v>
       </c>
       <c r="Z95" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA95" t="n">
-        <v>50</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.75512027761017</v>
+        <v>10.2632587778579</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>0.7315685761608459</v>
+        <v>2.485317623679761</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11126,10 +11073,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1320551941108999</v>
+        <v>0.1286548466305458</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11154,25 +11101,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>13.52465198145173</v>
+        <v>13.70647230932033</v>
       </c>
       <c r="K96" t="n">
-        <v>2.926826293872753</v>
+        <v>0.4878004798731794</v>
       </c>
       <c r="L96" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M96" t="n">
-        <v>57.8125</v>
+        <v>55.22388059701493</v>
       </c>
       <c r="N96" t="n">
-        <v>14.18034793826052</v>
+        <v>13.62785923657208</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.872041003122153</v>
+        <v>9.466024208612311</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11235,10 +11182,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C97" t="n">
-        <v>1.949535172647404</v>
+        <v>1.910045712469312</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11252,7 +11199,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -11266,16 +11213,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>9.076146480133085</v>
+        <v>6.866718200387001</v>
       </c>
       <c r="L97" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="M97" t="n">
-        <v>57.69230769230769</v>
+        <v>48.48484848484848</v>
       </c>
       <c r="N97" t="n">
-        <v>11.94044546982779</v>
+        <v>14.90139410824436</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11290,10 +11237,10 @@
         <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>35.58075187618041</v>
+        <v>35.69795617725568</v>
       </c>
       <c r="T97" t="n">
-        <v>20.41924812381959</v>
+        <v>20.30204382274432</v>
       </c>
       <c r="U97" t="n">
         <v>42.30602802165686</v>
@@ -11305,25 +11252,25 @@
         <v>61.29032258064516</v>
       </c>
       <c r="X97" t="n">
-        <v>14.56205771349215</v>
+        <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>4.788593486229775</v>
+        <v>9.035307526847468</v>
       </c>
       <c r="Z97" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="AA97" t="n">
-        <v>43.24324324324324</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.78585369827368</v>
+        <v>10.41431718008398</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.272333387486535</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
         <v>38</v>
@@ -11332,10 +11279,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG97" t="n">
-        <v>54.59500617747585</v>
+        <v>54.14294147759284</v>
       </c>
       <c r="AH97" t="n">
-        <v>-1.963427230107435</v>
+        <v>-1.511362530224424</v>
       </c>
       <c r="AI97" t="n">
         <v>37.25897138449667</v>
@@ -11354,10 +11301,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6383710965314688</v>
+        <v>0.6532668430828188</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11385,22 +11332,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>6.596137264038759</v>
+        <v>9.083450760319156</v>
       </c>
       <c r="L98" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="M98" t="n">
-        <v>54.54545454545455</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N98" t="n">
-        <v>13.06644539420603</v>
+        <v>12.41406750555115</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.193232722429595</v>
+        <v>0.8402275810789339</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11424,25 +11371,25 @@
         <v>72.05882352941177</v>
       </c>
       <c r="X98" t="n">
-        <v>10.06692753699225</v>
+        <v>10.54345902266514</v>
       </c>
       <c r="Y98" t="n">
-        <v>3.153345287835885</v>
+        <v>1.320755000118667</v>
       </c>
       <c r="Z98" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AA98" t="n">
-        <v>40</v>
+        <v>41.50943396226415</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.60719818483285</v>
+        <v>11.24652735569172</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>5.004462700925238</v>
+        <v>6.768642179912665</v>
       </c>
       <c r="AE98" t="n">
         <v>50</v>
@@ -11473,10 +11420,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4589596061858713</v>
+        <v>0.4596600455424388</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11504,16 +11451,16 @@
         <v>22.659960715244</v>
       </c>
       <c r="K99" t="n">
-        <v>4.197534958118143</v>
+        <v>4.356555606903556</v>
       </c>
       <c r="L99" t="n">
         <v>22</v>
       </c>
       <c r="M99" t="n">
-        <v>63.63636363636363</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N99" t="n">
-        <v>13.29618674290244</v>
+        <v>12.91686969642192</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11560,10 +11507,10 @@
         <v>52.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>37.81560513159778</v>
+        <v>38.44711166735622</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.68439486840222</v>
+        <v>14.05288833264378</v>
       </c>
       <c r="AI99" t="n">
         <v>37.49736210669248</v>
@@ -11582,10 +11529,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C100" t="n">
-        <v>329.124114104981</v>
+        <v>337.4406434389041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11599,14 +11546,10 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>5</v>
       </c>
@@ -11614,19 +11557,19 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>15.65236426997335</v>
+        <v>14.94373428959337</v>
       </c>
       <c r="K100" t="n">
-        <v>7.386449087853175</v>
+        <v>10.09996206253634</v>
       </c>
       <c r="L100" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M100" t="n">
-        <v>75</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N100" t="n">
-        <v>11.92641646772385</v>
+        <v>14.65805885884244</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11655,17 +11598,27 @@
       <c r="W100" t="n">
         <v>64.91228070175438</v>
       </c>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
+      <c r="X100" t="n">
+        <v>11.67316747858962</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1.408758658479792</v>
+      </c>
       <c r="Z100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>13.39108595075927</v>
+      </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
-      <c r="AD100" t="inlineStr"/>
+      <c r="AD100" t="n">
+        <v>6.685422814272246</v>
+      </c>
       <c r="AE100" t="n">
         <v>39</v>
       </c>
@@ -11695,10 +11648,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C101" t="n">
-        <v>348.9156877336598</v>
+        <v>349.0480867033897</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11726,7 +11679,7 @@
         <v>11.19277381576541</v>
       </c>
       <c r="K101" t="n">
-        <v>10.49079721200816</v>
+        <v>10.53272386715667</v>
       </c>
       <c r="L101" t="n">
         <v>11</v>
@@ -11765,25 +11718,25 @@
         <v>53.84615384615385</v>
       </c>
       <c r="X101" t="n">
-        <v>11.24259775946232</v>
+        <v>11.75542022182081</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.6758207400727634</v>
+        <v>1.094082374024663</v>
       </c>
       <c r="Z101" t="n">
         <v>41</v>
       </c>
       <c r="AA101" t="n">
-        <v>39.02439024390244</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.08541206052342</v>
+        <v>11.81175403647738</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>5.360405995396233</v>
+        <v>4.960186148343182</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11814,10 +11767,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C102" t="n">
-        <v>422.9584137389274</v>
+        <v>422.3847179507953</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11874,25 +11827,25 @@
         <v>47.22222222222222</v>
       </c>
       <c r="X102" t="n">
-        <v>11.14228058200113</v>
+        <v>11.51578143108469</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.1280769200425524</v>
+        <v>0.9335598427556158</v>
       </c>
       <c r="Z102" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA102" t="n">
-        <v>36.11111111111111</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB102" t="n">
-        <v>13.18660135094703</v>
+        <v>11.2667372239588</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.878170890989042</v>
+        <v>4.104760553412323</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11923,19 +11876,19 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7322491579507222</v>
+        <v>0.7602710659182595</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11950,27 +11903,17 @@
       <c r="I103" t="n">
         <v>10</v>
       </c>
-      <c r="J103" t="n">
-        <v>16.13876216849247</v>
-      </c>
-      <c r="K103" t="n">
-        <v>12.61870676337478</v>
-      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
-        <v>15</v>
-      </c>
-      <c r="M103" t="n">
-        <v>73.33333333333333</v>
-      </c>
-      <c r="N103" t="n">
-        <v>12.84408537336701</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
         <v>10</v>
       </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
+      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="n">
         <v>44</v>
       </c>
@@ -11993,10 +11936,10 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>16.12648158012706</v>
+        <v>17.69684631574038</v>
       </c>
       <c r="Y103" t="n">
-        <v>3.020650216059384</v>
+        <v>0.6528777773894157</v>
       </c>
       <c r="Z103" t="n">
         <v>47</v>
@@ -12005,13 +11948,13 @@
         <v>36.17021276595744</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.32844267601609</v>
+        <v>11.69385969484624</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>5.134443358337681</v>
+        <v>7.395405179575942</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -12020,10 +11963,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="AG103" t="n">
-        <v>37.40824031607043</v>
+        <v>37.81883034290784</v>
       </c>
       <c r="AH103" t="n">
-        <v>24.35646556628251</v>
+        <v>23.9458755394451</v>
       </c>
       <c r="AI103" t="n">
         <v>45.0410173444307</v>
@@ -12042,10 +11985,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04735628622103345</v>
+        <v>0.04725671639350872</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12070,25 +12013,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>21.43553010850433</v>
+        <v>19.88964985877965</v>
       </c>
       <c r="K104" t="n">
-        <v>1.793720163285029</v>
+        <v>1.527979459194229</v>
       </c>
       <c r="L104" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M104" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="N104" t="n">
-        <v>12.32784198497689</v>
+        <v>13.17943248787203</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.167402697510146</v>
+        <v>2.434817036617298</v>
       </c>
       <c r="Q104" t="n">
         <v>40</v>
@@ -12129,10 +12072,10 @@
         <v>64.28571428571429</v>
       </c>
       <c r="AG104" t="n">
-        <v>40.74419917771555</v>
+        <v>41.2461647343334</v>
       </c>
       <c r="AH104" t="n">
-        <v>23.54151510799874</v>
+        <v>23.03954955138089</v>
       </c>
       <c r="AI104" t="n">
         <v>49.16636571945582</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3942917363105504</v>
+        <v>0.3972062347804994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>17.68960189117161</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5744149465573889</v>
+        <v>1.317833972328941</v>
       </c>
       <c r="L2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M2" t="n">
-        <v>56.66666666666666</v>
+        <v>53.125</v>
       </c>
       <c r="N2" t="n">
-        <v>11.49230194429774</v>
+        <v>11.31574803100355</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>9.371752307434388</v>
+        <v>8.56923770206366</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -754,10 +754,10 @@
         <v>55</v>
       </c>
       <c r="AG2" t="n">
-        <v>38.88610988889963</v>
+        <v>39.07109157388132</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.11389011110037</v>
+        <v>15.92890842611868</v>
       </c>
       <c r="AI2" t="n">
         <v>39.82909179893205</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6482705430099892</v>
+        <v>0.6461887811693681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.418348317804585</v>
+        <v>1.092668168145861</v>
       </c>
       <c r="L3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>55.55555555555556</v>
+        <v>58.49056603773585</v>
       </c>
       <c r="N3" t="n">
-        <v>13.47976363276248</v>
+        <v>12.80061761725111</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>8.461636207389178</v>
+        <v>8.811056225203906</v>
       </c>
       <c r="Q3" t="n">
         <v>37</v>
@@ -831,10 +831,10 @@
         <v>59.45945945945946</v>
       </c>
       <c r="S3" t="n">
-        <v>54.10842708140005</v>
+        <v>55.15049442537836</v>
       </c>
       <c r="T3" t="n">
-        <v>5.351032378059408</v>
+        <v>4.308965034081098</v>
       </c>
       <c r="U3" t="n">
         <v>43.48596473022936</v>
@@ -863,10 +863,10 @@
         <v>61.11111111111111</v>
       </c>
       <c r="AG3" t="n">
-        <v>37.93578782904118</v>
+        <v>38.43474324065539</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.17532328206993</v>
+        <v>22.67636787045572</v>
       </c>
       <c r="AI3" t="n">
         <v>44.86445909660515</v>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C4" t="n">
-        <v>1.500973220127166</v>
+        <v>1.503054982175967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>18.2305339009923</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.704158181422788</v>
+        <v>1.567827599165317</v>
       </c>
       <c r="Z4" t="n">
         <v>50</v>
@@ -957,13 +957,13 @@
         <v>44</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.31240375911076</v>
+        <v>13.5986836850724</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.439667095876436</v>
+        <v>8.566480039165715</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -972,10 +972,10 @@
         <v>59.09090909090909</v>
       </c>
       <c r="AG4" t="n">
-        <v>39.61983283006133</v>
+        <v>40.1861461049917</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.47107626084776</v>
+        <v>18.90476298591739</v>
       </c>
       <c r="AI4" t="n">
         <v>44.4097537410319</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2346181586719366</v>
+        <v>0.2337854220426087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,11 +1014,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1029,22 +1025,22 @@
         <v>17.37484898646685</v>
       </c>
       <c r="K5" t="n">
-        <v>1.638105473796014</v>
+        <v>1.277358574056398</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N5" t="n">
-        <v>13.41667696322739</v>
+        <v>13.21227524363912</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.339944816813921</v>
+        <v>1.700914646864504</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1053,10 +1049,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S5" t="n">
-        <v>42.26754690342509</v>
+        <v>42.35647588418864</v>
       </c>
       <c r="T5" t="n">
-        <v>18.70806285267248</v>
+        <v>18.61913387190892</v>
       </c>
       <c r="U5" t="n">
         <v>45.72685693412379</v>
@@ -1107,10 +1103,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C6" t="n">
-        <v>1.694580097192065</v>
+        <v>1.700825382922108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,7 +1134,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>3.54796096359713</v>
+        <v>3.929581522018988</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1176,16 +1172,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.527709632567293</v>
+        <v>7.186907875003246</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA6" t="n">
-        <v>52.77777777777778</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.40216735484644</v>
+        <v>12.01867986203533</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1200,10 +1196,10 @@
         <v>46.15384615384615</v>
       </c>
       <c r="AG6" t="n">
-        <v>40.78998004793637</v>
+        <v>41.27416342503602</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.363866105909786</v>
+        <v>4.879682728810131</v>
       </c>
       <c r="AI6" t="n">
         <v>33.34047468175682</v>
@@ -1222,10 +1218,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C7" t="n">
-        <v>2.165065439747232</v>
+        <v>2.169228963636653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,25 +1246,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>10.98106443010587</v>
+        <v>11.0668297124846</v>
       </c>
       <c r="K7" t="n">
-        <v>0.192675283355892</v>
+        <v>0.4821600913267776</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M7" t="n">
-        <v>61.29032258064516</v>
+        <v>60.60606060606061</v>
       </c>
       <c r="N7" t="n">
-        <v>13.57600105369179</v>
+        <v>13.24631496318597</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>7.792310859615381</v>
+        <v>7.481765819763808</v>
       </c>
       <c r="Q7" t="n">
         <v>49</v>
@@ -1277,10 +1273,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S7" t="n">
-        <v>52.34661923893561</v>
+        <v>51.82831483228989</v>
       </c>
       <c r="T7" t="n">
-        <v>8.877870556982757</v>
+        <v>9.396174963628475</v>
       </c>
       <c r="U7" t="n">
         <v>47.24599944352045</v>
@@ -1295,16 +1291,16 @@
         <v>17.31307710509156</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.80954694375619</v>
+        <v>10.63802945740652</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>52.94117647058823</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.16677010797909</v>
+        <v>12.97318896738145</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1341,10 +1337,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3913771982865213</v>
+        <v>0.393667184046734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,10 +1400,10 @@
         <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.713635690231777</v>
+        <v>4.156105976270097</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
@@ -1415,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.448934518148383</v>
+        <v>4.010577891146816</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1446,10 +1442,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5895639671391472</v>
+        <v>0.5908130323208794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,16 +1505,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.202364126032755</v>
+        <v>5.001523449057055</v>
       </c>
       <c r="Z9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>42.85714285714285</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.08997104184201</v>
+        <v>11.69782377250188</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1527,25 +1523,25 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AF9" t="n">
-        <v>45.45454545454545</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AG9" t="n">
-        <v>29.35148216111522</v>
+        <v>29.66467386225889</v>
       </c>
       <c r="AH9" t="n">
-        <v>16.10306329343024</v>
+        <v>14.45297319656464</v>
       </c>
       <c r="AI9" t="n">
-        <v>29.84293851387612</v>
+        <v>28.88348224624216</v>
       </c>
       <c r="AJ9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AK9" t="n">
-        <v>47.27272727272727</v>
+        <v>46.42857142857143</v>
       </c>
     </row>
     <row r="10">
@@ -1555,10 +1551,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C10" t="n">
-        <v>1.93294541123058</v>
+        <v>1.940231657509542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,22 +1582,22 @@
         <v>10.66625626204533</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4475108740565004</v>
+        <v>0.8261482106748819</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>44.18604651162791</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="N10" t="n">
-        <v>9.966898464387521</v>
+        <v>9.624545134931306</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.527751835389272</v>
+        <v>5.131458338083528</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1642,10 +1638,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="AG10" t="n">
-        <v>41.47063826283426</v>
+        <v>41.21864473497867</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.70177553026918</v>
+        <v>13.95376905812477</v>
       </c>
       <c r="AI10" t="n">
         <v>37.54796321097091</v>
@@ -1664,10 +1660,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C11" t="n">
-        <v>8.321970284028421</v>
+        <v>8.290743378647452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,10 +1705,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.78475403994187</v>
+        <v>51.82524642737302</v>
       </c>
       <c r="T11" t="n">
-        <v>9.4397357559765</v>
+        <v>9.399243368545342</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1727,16 +1723,16 @@
         <v>22.29702291509528</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.500000000000002</v>
+        <v>2.865853658536577</v>
       </c>
       <c r="Z11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA11" t="n">
-        <v>48.57142857142857</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.75892080722119</v>
+        <v>12.63968901524</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1751,10 +1747,10 @@
         <v>56.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>25.12593977685399</v>
+        <v>25.15264917856339</v>
       </c>
       <c r="AH11" t="n">
-        <v>31.12406022314601</v>
+        <v>31.09735082143661</v>
       </c>
       <c r="AI11" t="n">
         <v>42.27501741982778</v>
@@ -1773,10 +1769,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C12" t="n">
-        <v>7.104120974170604</v>
+        <v>7.005235773797533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,16 +1800,16 @@
         <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>8.136342936811335</v>
+        <v>6.631148419742172</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>72.72727272727273</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N12" t="n">
-        <v>11.82093754578351</v>
+        <v>17.80846345924088</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1846,16 +1842,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.887080633413731</v>
+        <v>5.224916141080516</v>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>27.27272727272727</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.759433103302454</v>
+        <v>10.19016848477012</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1892,10 +1888,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2246255385410578</v>
+        <v>0.2244173543837258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1919,7 @@
         <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>6.342212580490059</v>
+        <v>6.243654045878744</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1959,7 +1955,7 @@
         <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.809071004620794</v>
+        <v>8.893587248109958</v>
       </c>
       <c r="Z13" t="n">
         <v>6</v>
@@ -1974,7 +1970,7 @@
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.30597309238899</v>
+        <v>1.214418083722746</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1995,14 +1991,14 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C14" t="n">
-        <v>8.582194495536502</v>
+        <v>8.556172074385694</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2012,7 +2008,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2058,22 +2054,22 @@
         <v>12.90895707120068</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.97201637975768</v>
+        <v>2.269251017781448</v>
       </c>
       <c r="Z14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>44.68085106382978</v>
+        <v>43.18181818181818</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.83340848040575</v>
+        <v>12.96436820482929</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.02854656314337234</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2082,10 +2078,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>27.72785600382322</v>
+        <v>27.59290323729151</v>
       </c>
       <c r="AH14" t="n">
-        <v>24.9037229435452</v>
+        <v>25.03867571007691</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2104,10 +2100,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C15" t="n">
-        <v>15.67590650124678</v>
+        <v>15.51977197434193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,22 +2163,22 @@
         <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.8558262014483176</v>
+        <v>1.843317972350222</v>
       </c>
       <c r="Z15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>66.66666666666667</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.36329355586816</v>
+        <v>11.99294426310307</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.223107569721112</v>
+        <v>8.309859154929578</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2191,10 +2187,10 @@
         <v>56.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>24.83073325918522</v>
+        <v>24.45117694948185</v>
       </c>
       <c r="AH15" t="n">
-        <v>31.41926674081478</v>
+        <v>31.79882305051815</v>
       </c>
       <c r="AI15" t="n">
         <v>39.32559113685198</v>
@@ -2213,10 +2209,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C16" t="n">
-        <v>37.30574296179845</v>
+        <v>36.55629723265518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,22 +2240,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>7.134555065077541</v>
+        <v>4.982298378502326</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>60.97560975609756</v>
+        <v>65.45454545454545</v>
       </c>
       <c r="N16" t="n">
-        <v>21.48344922057068</v>
+        <v>16.71603705115386</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>2.674622518553327</v>
+        <v>4.779569221667157</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2286,16 +2282,16 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.815186481973346</v>
+        <v>9.667113539255146</v>
       </c>
       <c r="Z16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="n">
-        <v>45</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.02601819878429</v>
+        <v>13.06432062655764</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
@@ -2304,25 +2300,25 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>48.38709677419355</v>
+        <v>50</v>
       </c>
       <c r="AG16" t="n">
-        <v>36.75049596077679</v>
+        <v>37.23247774461121</v>
       </c>
       <c r="AH16" t="n">
-        <v>11.63660081341676</v>
+        <v>12.76752225538879</v>
       </c>
       <c r="AI16" t="n">
-        <v>31.97025156241731</v>
+        <v>33.63088286932749</v>
       </c>
       <c r="AJ16" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK16" t="n">
-        <v>53.04347826086956</v>
+        <v>53.44827586206897</v>
       </c>
     </row>
     <row r="17">
@@ -2332,10 +2328,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C17" t="n">
-        <v>0.69573541379118</v>
+        <v>0.6949027566863712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,43 +2359,43 @@
         <v>16.09305130534204</v>
       </c>
       <c r="K17" t="n">
-        <v>1.748334196536838</v>
+        <v>1.626561649542957</v>
       </c>
       <c r="L17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>65</v>
+        <v>64.40677966101696</v>
       </c>
       <c r="N17" t="n">
-        <v>18.17539053542477</v>
+        <v>18.36278129194078</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.144243886477252</v>
+        <v>6.271429680397644</v>
       </c>
       <c r="Q17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R17" t="n">
-        <v>66.66666666666667</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="S17" t="n">
-        <v>47.44099592370424</v>
+        <v>47.33511350157781</v>
       </c>
       <c r="T17" t="n">
-        <v>19.22567074296244</v>
+        <v>17.88227780277002</v>
       </c>
       <c r="U17" t="n">
-        <v>52.07048830990042</v>
+        <v>50.77005884206276</v>
       </c>
       <c r="V17" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="W17" t="n">
-        <v>73.86363636363636</v>
+        <v>73.03370786516854</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
@@ -2441,7 +2437,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C18" t="n">
         <v>0.09784429957163032</v>
@@ -2496,10 +2492,10 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>41.6906452912378</v>
+        <v>41.50182979771316</v>
       </c>
       <c r="T18" t="n">
-        <v>35.50233716490256</v>
+        <v>35.6911526584272</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
@@ -2522,19 +2518,19 @@
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AF18" t="n">
-        <v>59.52380952380953</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="AG18" t="n">
-        <v>40.02689641378726</v>
+        <v>40.84872725724959</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.49691311002226</v>
+        <v>17.68785810860407</v>
       </c>
       <c r="AI18" t="n">
-        <v>44.49431275003934</v>
+        <v>43.36710313403013</v>
       </c>
       <c r="AJ18" t="n">
         <v>87</v>
@@ -2550,10 +2546,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02560606282875388</v>
+        <v>0.02581424198978097</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,22 +2577,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>3.899207707265506</v>
+        <v>4.743915854571501</v>
       </c>
       <c r="L19" t="n">
         <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>60.71428571428572</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N19" t="n">
-        <v>15.85846737675938</v>
+        <v>16.66899705560132</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>5.871837165422278</v>
+        <v>5.018032887682145</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2659,10 +2655,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C20" t="n">
-        <v>1.662312231262176</v>
+        <v>1.64149429434153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,43 +2686,43 @@
         <v>17.71726923698957</v>
       </c>
       <c r="K20" t="n">
-        <v>1.979559846262346</v>
+        <v>0.7024206878367467</v>
       </c>
       <c r="L20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M20" t="n">
-        <v>50</v>
+        <v>56.25</v>
       </c>
       <c r="N20" t="n">
-        <v>15.85353760891969</v>
+        <v>14.63837999942642</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>0.02004338297643127</v>
+        <v>1.288528421958768</v>
       </c>
       <c r="Q20" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R20" t="n">
-        <v>68.75</v>
+        <v>67.34693877551021</v>
       </c>
       <c r="S20" t="n">
-        <v>40.45064634790101</v>
+        <v>40.44144948365813</v>
       </c>
       <c r="T20" t="n">
-        <v>28.29935365209899</v>
+        <v>26.90548929185208</v>
       </c>
       <c r="U20" t="n">
-        <v>54.66692858410841</v>
+        <v>53.37920531457014</v>
       </c>
       <c r="V20" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W20" t="n">
-        <v>70</v>
+        <v>68.85245901639344</v>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
@@ -2746,10 +2742,10 @@
         <v>50</v>
       </c>
       <c r="AG20" t="n">
-        <v>40.82021099745704</v>
+        <v>40.74517029741634</v>
       </c>
       <c r="AH20" t="n">
-        <v>9.179789002542961</v>
+        <v>9.254829702583663</v>
       </c>
       <c r="AI20" t="n">
         <v>35.19952693346539</v>
@@ -2768,10 +2764,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9572087300350731</v>
+        <v>0.954710599879788</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,22 +2795,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>3.036307715457509</v>
+        <v>2.767402826360033</v>
       </c>
       <c r="L21" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>50.87719298245614</v>
+        <v>54.23728813559322</v>
       </c>
       <c r="N21" t="n">
-        <v>17.39378741457684</v>
+        <v>16.59487055692764</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.817420572027986</v>
+        <v>5.091689611423944</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2823,10 +2819,10 @@
         <v>72.5</v>
       </c>
       <c r="S21" t="n">
-        <v>46.65139214655776</v>
+        <v>46.68344220956758</v>
       </c>
       <c r="T21" t="n">
-        <v>25.84860785344224</v>
+        <v>25.81655779043242</v>
       </c>
       <c r="U21" t="n">
         <v>57.16504419378943</v>
@@ -2855,10 +2851,10 @@
         <v>62.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>36.35901807453077</v>
+        <v>36.47568474119743</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.14098192546923</v>
+        <v>26.02431525880257</v>
       </c>
       <c r="AI21" t="n">
         <v>47.0324391373011</v>
@@ -2877,10 +2873,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3362096733576243</v>
+        <v>0.3366260416722882</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2940,19 +2936,19 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.370609522726857</v>
+        <v>8.257133980795839</v>
       </c>
       <c r="Z22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.32220118604125</v>
+        <v>10.89827904879843</v>
       </c>
       <c r="AC22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -2965,10 +2961,10 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
-        <v>52.63157894736842</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -2978,7 +2974,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C23" t="n">
         <v>0.739869497312277</v>
@@ -3006,40 +3002,40 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>27.1609810190017</v>
+        <v>27.73484467032905</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.794108375896263</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>66.66666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="N23" t="n">
-        <v>19.39401750526293</v>
+        <v>21.84187412476708</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>5.000000000000004</v>
+        <v>9.13336282491013</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>83.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="S23" t="n">
-        <v>3.812636165577342</v>
+        <v>6.25</v>
       </c>
       <c r="T23" t="n">
-        <v>79.52069716775598</v>
+        <v>93.75</v>
       </c>
       <c r="U23" t="n">
-        <v>43.64971778135299</v>
+        <v>34.2380227506653</v>
       </c>
       <c r="V23" t="n">
         <v>16</v>
@@ -3093,10 +3089,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1790342654283756</v>
+        <v>0.1792424298086674</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3120,7 @@
         <v>23.47035234733546</v>
       </c>
       <c r="K24" t="n">
-        <v>5.895666469546246</v>
+        <v>6.018792094316905</v>
       </c>
       <c r="L24" t="n">
         <v>9</v>
@@ -3139,7 +3135,7 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>3.875827658758912</v>
+        <v>3.755190779896189</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3166,16 +3162,16 @@
         <v>12.66805408629466</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.010920905371552</v>
+        <v>5.9016391521992</v>
       </c>
       <c r="Z24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
-        <v>53.57142857142857</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="AB24" t="n">
-        <v>15.12175849663499</v>
+        <v>15.2747307352476</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3212,7 +3208,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C25" t="n">
         <v>3.497413402668605</v>
@@ -3240,10 +3236,10 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>15.84414756511959</v>
+        <v>15.89424339008501</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.05956289674409199</v>
       </c>
       <c r="L25" t="n">
         <v>56</v>
@@ -3252,13 +3248,13 @@
         <v>58.92857142857143</v>
       </c>
       <c r="N25" t="n">
-        <v>17.44339762958513</v>
+        <v>17.64570129619283</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>8.000000000000007</v>
+        <v>7.935710364285731</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3267,10 +3263,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="S25" t="n">
-        <v>36.36804514163651</v>
+        <v>36.41827758267355</v>
       </c>
       <c r="T25" t="n">
-        <v>30.29862152503016</v>
+        <v>30.24838908399312</v>
       </c>
       <c r="U25" t="n">
         <v>52.07048830990042</v>
@@ -3299,10 +3295,10 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG25" t="n">
-        <v>54.71095697250696</v>
+        <v>54.90570193925618</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.052420387141112</v>
+        <v>-1.247165353890324</v>
       </c>
       <c r="AI25" t="n">
         <v>38.74647126766948</v>
@@ -3321,10 +3317,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4509165105785117</v>
+        <v>0.4517492469996602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,10 +3394,10 @@
         <v>51.35135135135135</v>
       </c>
       <c r="AG26" t="n">
-        <v>41.57071733862015</v>
+        <v>41.99260026050308</v>
       </c>
       <c r="AH26" t="n">
-        <v>9.780634012731205</v>
+        <v>9.358751090848273</v>
       </c>
       <c r="AI26" t="n">
         <v>35.89489666561879</v>
@@ -3420,10 +3416,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C27" t="n">
-        <v>45.79946122542221</v>
+        <v>45.50801010853316</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,10 +3444,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>59.63969482143187</v>
+        <v>50.20031327035493</v>
       </c>
       <c r="K27" t="n">
-        <v>38.94119215507532</v>
+        <v>38.05702093227031</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3476,25 +3472,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>38.94119215507532</v>
+        <v>40.26744898928287</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.575866726699682</v>
       </c>
       <c r="Z27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB27" t="n">
-        <v>12.27246413141115</v>
+        <v>12.92066461084936</v>
       </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>6.000000000000005</v>
+        <v>4.494967978042097</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3515,10 +3511,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C28" t="n">
-        <v>1.630044524381325</v>
+        <v>1.625880841651045</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,22 +3574,22 @@
         <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.571338720394932</v>
+        <v>1.82275867304319</v>
       </c>
       <c r="Z28" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA28" t="n">
-        <v>42.85714285714285</v>
+        <v>41.86046511627907</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.49430578992027</v>
+        <v>11.4704057594197</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.499361488849907</v>
+        <v>4.254795989882698</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3624,10 +3620,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4121951352071678</v>
+        <v>0.405533401637942</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3644,7 +3640,11 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3655,16 +3655,16 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>14.02651973380333</v>
+        <v>12.18366854655952</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>66.66666666666667</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N29" t="n">
-        <v>18.00706743337966</v>
+        <v>20.81369456717993</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3694,13 +3694,13 @@
         <v>100</v>
       </c>
       <c r="X29" t="n">
-        <v>54.29671088217374</v>
+        <v>48.55798797437896</v>
       </c>
       <c r="Y29" t="n">
-        <v>10.02010676109818</v>
+        <v>11.4743259503753</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4313476386314181</v>
+        <v>0.4255186416915201</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,10 +3770,10 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>17.83247840238216</v>
+        <v>16.24015449814726</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3808,37 +3808,37 @@
         <v>18.28742967351311</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.3846150621301558</v>
+        <v>1.730763092085563</v>
       </c>
       <c r="Z30" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA30" t="n">
-        <v>37.5</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB30" t="n">
-        <v>13.71773330520145</v>
+        <v>14.78543534679678</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>9.652509944991895</v>
+        <v>8.414878519575076</v>
       </c>
       <c r="AE30" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AF30" t="n">
-        <v>57.4468085106383</v>
+        <v>58</v>
       </c>
       <c r="AG30" t="n">
-        <v>42.68797981510033</v>
+        <v>41.47694845391194</v>
       </c>
       <c r="AH30" t="n">
-        <v>14.75882869553797</v>
+        <v>16.52305154608806</v>
       </c>
       <c r="AI30" t="n">
-        <v>43.2819193454928</v>
+        <v>44.23344176857823</v>
       </c>
       <c r="AJ30" t="n">
         <v>64</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1848632821453136</v>
+        <v>0.1859041831549333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3882,23 +3882,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>20.56525919639532</v>
+        <v>18.68860738081651</v>
       </c>
       <c r="K31" t="n">
-        <v>6.163792795411416</v>
+        <v>6.76156428266077</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
+        <v>63.63636363636363</v>
+      </c>
+      <c r="N31" t="n">
+        <v>17.7792118719494</v>
+      </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>3.613479797186003</v>
+        <v>3.03333483271675</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3961,10 +3963,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C32" t="n">
-        <v>2.302463791572055</v>
+        <v>2.308709236351135</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3992,16 +3994,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>5.647099818845147</v>
+        <v>5.933668115990054</v>
       </c>
       <c r="L32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M32" t="n">
-        <v>40.54054054054054</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N32" t="n">
-        <v>12.13319448867921</v>
+        <v>12.04808016565562</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4034,22 +4036,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.404454025885742</v>
+        <v>6.150575630017419</v>
       </c>
       <c r="Z32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA32" t="n">
-        <v>36.36363636363637</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.03406896062765</v>
+        <v>10.49284904697489</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.704724255313961</v>
+        <v>1.970629423033632</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4080,10 +4082,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C33" t="n">
-        <v>1.726847804072916</v>
+        <v>1.732052288303078</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4111,16 +4113,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.377975228200493</v>
+        <v>5.695570101928227</v>
       </c>
       <c r="L33" t="n">
         <v>29</v>
       </c>
       <c r="M33" t="n">
-        <v>68.96551724137932</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="N33" t="n">
-        <v>11.14242984879175</v>
+        <v>11.39383009772743</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4189,10 +4191,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7948288380838421</v>
+        <v>0.7985760729749396</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4220,16 +4222,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>4.72746391095582</v>
+        <v>5.221203428220167</v>
       </c>
       <c r="L34" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M34" t="n">
-        <v>72.72727272727273</v>
+        <v>70</v>
       </c>
       <c r="N34" t="n">
-        <v>9.616943003587124</v>
+        <v>9.756922704522095</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4276,10 +4278,10 @@
         <v>54.05405405405406</v>
       </c>
       <c r="AG34" t="n">
-        <v>30.89327423650132</v>
+        <v>30.47347742351565</v>
       </c>
       <c r="AH34" t="n">
-        <v>23.16077981755273</v>
+        <v>23.58057663053841</v>
       </c>
       <c r="AI34" t="n">
         <v>38.38404689217949</v>
@@ -4298,10 +4300,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C35" t="n">
-        <v>1.940231657509542</v>
+        <v>1.948558863921065</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,7 +4322,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4333,16 +4335,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.381046170977347</v>
+        <v>9.850494520327114</v>
       </c>
       <c r="L35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>90.90909090909091</v>
+        <v>80</v>
       </c>
       <c r="N35" t="n">
-        <v>11.13327172976649</v>
+        <v>10.83557166488997</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4375,13 +4377,13 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.632032766026952</v>
+        <v>6.231310340757612</v>
       </c>
       <c r="Z35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>50</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB35" t="n">
         <v>14.75083324357035</v>
@@ -4421,10 +4423,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08139813523334197</v>
+        <v>0.08202267271642326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4441,7 +4443,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>5</v>
       </c>
@@ -4452,16 +4458,16 @@
         <v>14.21000360644873</v>
       </c>
       <c r="K36" t="n">
-        <v>4.272532338489099</v>
+        <v>5.072576525183403</v>
       </c>
       <c r="L36" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M36" t="n">
-        <v>61.53846153846154</v>
+        <v>75</v>
       </c>
       <c r="N36" t="n">
-        <v>20.5096675101567</v>
+        <v>18.04659990485045</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4530,10 +4536,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06516014485159648</v>
+        <v>0.06557650338183003</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4558,61 +4564,61 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>14.09373072523551</v>
+        <v>14.02780799500539</v>
       </c>
       <c r="K37" t="n">
-        <v>6.069714378721769</v>
+        <v>6.747475769240485</v>
       </c>
       <c r="L37" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>58.13953488372093</v>
+        <v>55.26315789473684</v>
       </c>
       <c r="N37" t="n">
-        <v>22.10605372631138</v>
+        <v>18.8141351286606</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>1.819827301868804</v>
+        <v>1.173352551649232</v>
       </c>
       <c r="Q37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R37" t="n">
-        <v>55.55555555555556</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="S37" t="n">
-        <v>35.14247721492947</v>
+        <v>34.54520697292785</v>
       </c>
       <c r="T37" t="n">
-        <v>20.41307834062609</v>
+        <v>19.50884708112621</v>
       </c>
       <c r="U37" t="n">
-        <v>39.5810617556973</v>
+        <v>38.38404689217949</v>
       </c>
       <c r="V37" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="W37" t="n">
-        <v>70.29702970297029</v>
+        <v>69.6078431372549</v>
       </c>
       <c r="X37" t="n">
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.412542576915458</v>
+        <v>4.808150201163408</v>
       </c>
       <c r="Z37" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AA37" t="n">
-        <v>56.60377358490566</v>
+        <v>54.3859649122807</v>
       </c>
       <c r="AB37" t="n">
-        <v>12.70203986642455</v>
+        <v>12.86768914035915</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
@@ -4649,10 +4655,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C38" t="n">
-        <v>1.667516715492338</v>
+        <v>1.658148707580934</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4680,22 +4686,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>5.249936519396448</v>
+        <v>4.6586487506874</v>
       </c>
       <c r="L38" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M38" t="n">
-        <v>53.65853658536585</v>
+        <v>54.34782608695652</v>
       </c>
       <c r="N38" t="n">
-        <v>10.53259634513365</v>
+        <v>10.45233449384154</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>4.513127169181885</v>
+        <v>5.103592787669675</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4704,10 +4710,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S38" t="n">
-        <v>57.98301689992832</v>
+        <v>58.37035432382478</v>
       </c>
       <c r="T38" t="n">
-        <v>-6.820226202253906</v>
+        <v>-7.207563626150367</v>
       </c>
       <c r="U38" t="n">
         <v>36.75230846944931</v>
@@ -4736,10 +4742,10 @@
         <v>56.66666666666666</v>
       </c>
       <c r="AG38" t="n">
-        <v>18.29908604822881</v>
+        <v>18.53072784867085</v>
       </c>
       <c r="AH38" t="n">
-        <v>38.36758061843786</v>
+        <v>38.13593881799581</v>
       </c>
       <c r="AI38" t="n">
         <v>39.19730700081361</v>
@@ -4758,10 +4764,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C39" t="n">
-        <v>2.739640625746489</v>
+        <v>2.758376641985655</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4821,37 +4827,37 @@
         <v>11.08431820998319</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.37388492403301</v>
+        <v>1.70623367801177</v>
       </c>
       <c r="Z39" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AA39" t="n">
-        <v>40</v>
+        <v>38.70967741935484</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.86565257041252</v>
+        <v>12.08059302588321</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.71428799880581</v>
+        <v>4.368299723018875</v>
       </c>
       <c r="AE39" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AF39" t="n">
-        <v>60</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="AG39" t="n">
-        <v>39.15097959687783</v>
+        <v>39.5316764229192</v>
       </c>
       <c r="AH39" t="n">
-        <v>20.84902040312217</v>
+        <v>19.55923266798989</v>
       </c>
       <c r="AI39" t="n">
-        <v>45.45185459035139</v>
+        <v>44.4097537410319</v>
       </c>
       <c r="AJ39" t="n">
         <v>66</v>
@@ -4867,10 +4873,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2477334414448768</v>
+        <v>0.2487743422463171</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,7 +4936,7 @@
         <v>43.91653617576685</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.989269685016363</v>
+        <v>5.594265102840756</v>
       </c>
       <c r="Z40" t="n">
         <v>5</v>
@@ -4939,7 +4945,7 @@
         <v>60</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.63467188629951</v>
+        <v>13.95377872703095</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -4976,10 +4982,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C41" t="n">
-        <v>1.845510139866752</v>
+        <v>1.863205354397858</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5007,10 +5013,10 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>21.96171381781607</v>
+        <v>23.13111334804212</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5042,25 +5048,25 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X41" t="n">
-        <v>22.99353879000634</v>
+        <v>23.19990587560969</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.8389261601391751</v>
+        <v>0.05583813321824449</v>
       </c>
       <c r="Z41" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>47.61904761904762</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB41" t="n">
-        <v>15.75920552664896</v>
+        <v>14.93319642729028</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.179357036160012</v>
+        <v>2.945806750279334</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5091,10 +5097,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C42" t="n">
-        <v>3.684774834954423</v>
+        <v>3.703510851193589</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5152,18 +5158,22 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.72253528070028</v>
+        <v>4.238076879260532</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>7.174717563702993</v>
+      </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.539048225986953</v>
+        <v>6.0169250292464</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5192,10 +5202,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C43" t="n">
-        <v>6.677353267297351</v>
+        <v>6.682557751527513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5223,7 +5233,7 @@
         <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>1.825396825396819</v>
+        <v>1.904761904761898</v>
       </c>
       <c r="L43" t="n">
         <v>33</v>
@@ -5232,13 +5242,13 @@
         <v>69.6969696969697</v>
       </c>
       <c r="N43" t="n">
-        <v>19.09694860740999</v>
+        <v>19.07969709630667</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.135619641465336</v>
+        <v>2.056074766355143</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5262,10 +5272,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="X43" t="n">
-        <v>21.54591253356677</v>
+        <v>20.83229097494805</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.81322112308199</v>
+        <v>13.74604514578119</v>
       </c>
       <c r="Z43" t="n">
         <v>2</v>
@@ -5307,7 +5317,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C44" t="n">
         <v>4.617418472494092</v>
@@ -5412,10 +5422,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02331608935112403</v>
+        <v>0.02394062704238469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5475,22 +5485,22 @@
         <v>19.58690552546656</v>
       </c>
       <c r="Y45" t="n">
-        <v>3.448273365041554</v>
+        <v>0.8620681257431539</v>
       </c>
       <c r="Z45" t="n">
         <v>41</v>
       </c>
       <c r="AA45" t="n">
-        <v>41.46341463414634</v>
+        <v>51.21951219512195</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.12027427869573</v>
+        <v>12.3323041522808</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.607145401785715</v>
+        <v>4.173913855198497</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5521,14 +5531,14 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C46" t="n">
-        <v>10.24762944918822</v>
+        <v>10.17476666996596</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5538,7 +5548,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5584,22 +5594,22 @@
         <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.524752475247527</v>
+        <v>3.21782178217821</v>
       </c>
       <c r="Z46" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA46" t="n">
-        <v>23.07692307692308</v>
+        <v>25</v>
       </c>
       <c r="AB46" t="n">
-        <v>13.92874497046169</v>
+        <v>15.61331922051397</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.4875571356018238</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>38</v>
@@ -5630,10 +5640,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7190515603916305</v>
+        <v>0.7232151635973919</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5658,25 +5668,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>21.47935966243942</v>
+        <v>20.24791594168004</v>
       </c>
       <c r="K47" t="n">
-        <v>6.768869483652629</v>
+        <v>7.387104992404647</v>
       </c>
       <c r="L47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>11.93630097509912</v>
+        <v>17.21933616649681</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3.026285219627711</v>
+        <v>2.433155272954024</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5711,19 +5721,19 @@
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF47" t="n">
-        <v>55.81395348837209</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="AG47" t="n">
-        <v>31.53536093163715</v>
+        <v>32.64690266031537</v>
       </c>
       <c r="AH47" t="n">
-        <v>24.27859255673494</v>
+        <v>22.11500210158939</v>
       </c>
       <c r="AI47" t="n">
-        <v>41.1076144528241</v>
+        <v>39.94911903473349</v>
       </c>
       <c r="AJ47" t="n">
         <v>76</v>
@@ -5739,10 +5749,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06037201915166842</v>
+        <v>0.05995566062143486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5770,22 +5780,22 @@
         <v>15.05707226133306</v>
       </c>
       <c r="K48" t="n">
-        <v>4.798167633235773</v>
+        <v>4.075422035853538</v>
       </c>
       <c r="L48" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M48" t="n">
-        <v>53.19148936170212</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N48" t="n">
-        <v>16.33831490238179</v>
+        <v>15.71039766258824</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>4.963667289459872</v>
+        <v>5.692581253339024</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5826,10 +5836,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>24.16906018037669</v>
+        <v>24.25553816779807</v>
       </c>
       <c r="AH48" t="n">
-        <v>36.20829831018935</v>
+        <v>36.12182032276797</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5848,7 +5858,7 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C49" t="n">
         <v>0.2620978289536294</v>
@@ -5935,10 +5945,10 @@
         <v>63.04347826086956</v>
       </c>
       <c r="AG49" t="n">
-        <v>37.56267591119892</v>
+        <v>38.13302762758735</v>
       </c>
       <c r="AH49" t="n">
-        <v>25.48080234967065</v>
+        <v>24.91045063328222</v>
       </c>
       <c r="AI49" t="n">
         <v>48.60009642338971</v>
@@ -5957,10 +5967,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6765829499210099</v>
+        <v>0.6803301850202866</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5988,22 +5998,22 @@
         <v>15.82134875518189</v>
       </c>
       <c r="K50" t="n">
-        <v>1.17089638562069</v>
+        <v>1.731228469078827</v>
       </c>
       <c r="L50" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M50" t="n">
-        <v>56.25</v>
+        <v>58</v>
       </c>
       <c r="N50" t="n">
-        <v>13.93148522800849</v>
+        <v>15.01785959482368</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.796361123060498</v>
+        <v>2.230162325829732</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6066,10 +6076,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1746624978423223</v>
+        <v>0.1744543136849904</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6097,7 +6107,7 @@
         <v>21.1650162252606</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5780995221746688</v>
+        <v>0.4582182245078004</v>
       </c>
       <c r="L51" t="n">
         <v>15</v>
@@ -6106,13 +6116,13 @@
         <v>60</v>
       </c>
       <c r="N51" t="n">
-        <v>12.53420429163367</v>
+        <v>11.45443472377427</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>3.402232189792875</v>
+        <v>3.525626711372576</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6136,10 +6146,10 @@
         <v>84.61538461538461</v>
       </c>
       <c r="X51" t="n">
-        <v>27.46610563666652</v>
+        <v>27.09436430358245</v>
       </c>
       <c r="Y51" t="n">
-        <v>20.70927156075235</v>
+        <v>20.80377996231697</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -6181,10 +6191,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C52" t="n">
-        <v>4.554964661732152</v>
+        <v>4.542473772590349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6244,22 +6254,22 @@
         <v>17.40749557792611</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.527336813234672</v>
+        <v>3.791889763821576</v>
       </c>
       <c r="Z52" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA52" t="n">
-        <v>46.875</v>
+        <v>50</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.52777534943247</v>
+        <v>11.56773445517566</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.636197487475302</v>
+        <v>4.373966213293301</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6268,10 +6278,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>40.66320175807991</v>
+        <v>41.22689725018098</v>
       </c>
       <c r="AH52" t="n">
-        <v>27.75785087349903</v>
+        <v>27.19415538139796</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6290,10 +6300,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C53" t="n">
-        <v>1.433314925135065</v>
+        <v>1.413537948763338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6325,7 +6335,7 @@
         <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>6.218497106349585</v>
+        <v>4.7528870923363</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
@@ -6334,13 +6344,13 @@
         <v>80</v>
       </c>
       <c r="N53" t="n">
-        <v>12.01629352258359</v>
+        <v>16.25373172741129</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>1.677205893684142</v>
+        <v>3.099783688827107</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6395,10 +6405,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08056541359292872</v>
+        <v>0.07973269674064098</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6412,7 +6422,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6427,10 +6437,10 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>42.98617858772242</v>
+        <v>43.17644124828992</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7071871861994206</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
@@ -6445,7 +6455,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>9.227556715112041</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6468,27 +6478,17 @@
       <c r="W54" t="n">
         <v>69.09090909090909</v>
       </c>
-      <c r="X54" t="n">
-        <v>10.17240666043591</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>8.591279578206358</v>
-      </c>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>69.56521739130434</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>14.6756080381485</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
         <v>2</v>
       </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="n">
         <v>7</v>
       </c>
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C55" t="n">
-        <v>0.940970764634852</v>
+        <v>0.9472161298894138</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6578,19 +6578,19 @@
         <v>73.41772151898734</v>
       </c>
       <c r="X55" t="n">
-        <v>23.83539141846003</v>
+        <v>21.18657262526651</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.765467867902927</v>
+        <v>3.12674472595702</v>
       </c>
       <c r="Z55" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AA55" t="n">
-        <v>40.625</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.1129640054664</v>
+        <v>13.45364936717568</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6605,10 +6605,10 @@
         <v>56.52173913043478</v>
       </c>
       <c r="AG55" t="n">
-        <v>42.1045199545839</v>
+        <v>42.59801633826019</v>
       </c>
       <c r="AH55" t="n">
-        <v>14.41721917585088</v>
+        <v>13.92372279217459</v>
       </c>
       <c r="AI55" t="n">
         <v>42.24743369429499</v>
@@ -6627,19 +6627,19 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C56" t="n">
-        <v>1.219931071698439</v>
+        <v>1.132495800334611</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6647,24 +6647,38 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>5</v>
       </c>
       <c r="I56" t="n">
         <v>10</v>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>19.65620512594927</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1.209305172093011</v>
+      </c>
       <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="M56" t="n">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="N56" t="n">
+        <v>19.62124520003125</v>
+      </c>
       <c r="O56" t="n">
         <v>4</v>
       </c>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>2.757350051126006</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
@@ -6682,7 +6696,7 @@
         <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>12.40658127082107</v>
+        <v>18.68460345908157</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6716,10 +6730,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C57" t="n">
-        <v>1.35316589984202</v>
+        <v>1.35212493950128</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6751,7 +6765,7 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>7.182644724273768</v>
+        <v>7.100191506684839</v>
       </c>
       <c r="L57" t="n">
         <v>22</v>
@@ -6766,7 +6780,7 @@
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>2.628555474604921</v>
+        <v>2.707566114047677</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6793,7 +6807,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>16.57657444562146</v>
+        <v>16.64075022591635</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6822,10 +6836,10 @@
         <v>36.48450865154381</v>
       </c>
       <c r="AJ57" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK57" t="n">
-        <v>48.18181818181818</v>
+        <v>47.74774774774774</v>
       </c>
     </row>
     <row r="58">
@@ -6835,10 +6849,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7252969254380132</v>
+        <v>0.725713293752677</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6866,7 +6880,7 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>9.270439476154802</v>
+        <v>9.333167921749407</v>
       </c>
       <c r="L58" t="n">
         <v>5</v>
@@ -6908,7 +6922,7 @@
         <v>13.39281154402059</v>
       </c>
       <c r="Y58" t="n">
-        <v>3.635479191082081</v>
+        <v>3.580159594768662</v>
       </c>
       <c r="Z58" t="n">
         <v>32</v>
@@ -6923,7 +6937,7 @@
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.453725488457059</v>
+        <v>2.50969136130208</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6954,10 +6968,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7952452061903268</v>
+        <v>0.7956615745049906</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6985,22 +6999,22 @@
         <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>1.67453944493241</v>
+        <v>1.727773411391276</v>
       </c>
       <c r="L59" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M59" t="n">
-        <v>61.66666666666666</v>
+        <v>62.29508196721311</v>
       </c>
       <c r="N59" t="n">
-        <v>13.80404332835052</v>
+        <v>13.70908536407678</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.221282721908472</v>
+        <v>6.165697309862073</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7063,10 +7077,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C60" t="n">
-        <v>11.76213436016525</v>
+        <v>11.75172539170492</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7094,22 +7108,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>2.39408383879729</v>
+        <v>2.303469605311625</v>
       </c>
       <c r="L60" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M60" t="n">
-        <v>54.76190476190476</v>
+        <v>58.13953488372093</v>
       </c>
       <c r="N60" t="n">
-        <v>13.86551306065141</v>
+        <v>13.58799988709937</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.47484381033998</v>
+        <v>5.568267055521847</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7144,25 +7158,25 @@
       </c>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AF60" t="n">
-        <v>60.60606060606061</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="AG60" t="n">
-        <v>24.59235950815647</v>
+        <v>25.77078802032711</v>
       </c>
       <c r="AH60" t="n">
-        <v>36.01370109790414</v>
+        <v>35.99391786202583</v>
       </c>
       <c r="AI60" t="n">
-        <v>43.68344081994023</v>
+        <v>45.0410173444307</v>
       </c>
       <c r="AJ60" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AK60" t="n">
-        <v>47.27272727272727</v>
+        <v>48.21428571428572</v>
       </c>
     </row>
     <row r="61">
@@ -7172,10 +7186,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6195418075465641</v>
+        <v>0.622872674331177</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7192,11 +7206,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7207,22 +7217,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>0.8199565742206927</v>
+        <v>1.361998839147183</v>
       </c>
       <c r="L61" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M61" t="n">
-        <v>78.57142857142857</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N61" t="n">
-        <v>19.19745484542576</v>
+        <v>19.57989531500803</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>9.105383237316955</v>
+        <v>8.521932538604137</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7241,16 +7251,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.86189056960708</v>
+        <v>11.3880302141246</v>
       </c>
       <c r="Z61" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="n">
-        <v>56.25</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB61" t="n">
-        <v>11.77948701260922</v>
+        <v>11.83234893488008</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7287,10 +7297,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C62" t="n">
-        <v>9.269186413917835</v>
+        <v>9.206732603155896</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7350,22 +7360,22 @@
         <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.8351893095768448</v>
+        <v>1.503340757238314</v>
       </c>
       <c r="Z62" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AA62" t="n">
-        <v>47.45762711864407</v>
+        <v>45.90163934426229</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.73099212142922</v>
+        <v>14.73910895473776</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.174620999438514</v>
+        <v>0.5042396834369689</v>
       </c>
       <c r="AE62" t="n">
         <v>31</v>
@@ -7396,10 +7406,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1124168614532846</v>
+        <v>0.1140822947415013</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7427,10 +7437,10 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>14.39026951187747</v>
+        <v>16.08493844525931</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7465,22 +7475,22 @@
         <v>18.41511331267116</v>
       </c>
       <c r="Y63" t="n">
-        <v>3.398927457989431</v>
+        <v>1.967801914996359</v>
       </c>
       <c r="Z63" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AA63" t="n">
-        <v>22.22222222222222</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB63" t="n">
-        <v>14.16240728590613</v>
+        <v>14.19162034110392</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>6.83333255864198</v>
+        <v>8.193428528491143</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7511,10 +7521,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1480155342121281</v>
+        <v>0.1482237085850297</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7542,22 +7552,22 @@
         <v>24.59083812498669</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2969078143066461</v>
+        <v>0.4379689941304221</v>
       </c>
       <c r="L64" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M64" t="n">
-        <v>70</v>
+        <v>70.96774193548387</v>
       </c>
       <c r="N64" t="n">
-        <v>15.93250966279426</v>
+        <v>15.69039807896171</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.689169674503657</v>
+        <v>4.542137850414107</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7598,10 +7608,10 @@
         <v>62</v>
       </c>
       <c r="AG64" t="n">
-        <v>39.37911668908677</v>
+        <v>40.09797484696545</v>
       </c>
       <c r="AH64" t="n">
-        <v>22.62088331091323</v>
+        <v>21.90202515303455</v>
       </c>
       <c r="AI64" t="n">
         <v>48.15044693099298</v>
@@ -7620,10 +7630,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C65" t="n">
-        <v>6.880328152273654</v>
+        <v>6.895941604964139</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7651,7 +7661,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>21.45002735356205</v>
+        <v>21.72563255935682</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7689,13 +7699,13 @@
         <v>23.0117901863991</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.269604182225548</v>
+        <v>1.045556385362212</v>
       </c>
       <c r="Z65" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA65" t="n">
-        <v>40</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB65" t="n">
         <v>9.344780687814966</v>
@@ -7704,7 +7714,7 @@
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.765506807866869</v>
+        <v>2.98566037735849</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7713,10 +7723,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG65" t="n">
-        <v>20.77548197579595</v>
+        <v>20.78146283703997</v>
       </c>
       <c r="AH65" t="n">
-        <v>33.76997256965859</v>
+        <v>33.76399170841458</v>
       </c>
       <c r="AI65" t="n">
         <v>40.06618319896197</v>
@@ -7735,10 +7745,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4642399775087839</v>
+        <v>0.4667381474263286</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7798,22 +7808,22 @@
         <v>13.05901358398374</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.588705262061163</v>
+        <v>1.059134031724174</v>
       </c>
       <c r="Z66" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AA66" t="n">
-        <v>39.34426229508197</v>
+        <v>40.67796610169491</v>
       </c>
       <c r="AB66" t="n">
-        <v>10.87162127762553</v>
+        <v>11.21664880997691</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.482508587744682</v>
+        <v>4.993756543287242</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7844,10 +7854,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02747967777615017</v>
+        <v>0.02768785693717727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7875,22 +7885,22 @@
         <v>13.52521428537139</v>
       </c>
       <c r="K67" t="n">
-        <v>2.061245107645004</v>
+        <v>2.834435555981729</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N67" t="n">
-        <v>7.671407444036571</v>
+        <v>6.573256403145478</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.899599490786308</v>
+        <v>1.133437877804799</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7907,7 +7917,7 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>7.94656182183715</v>
+        <v>7.249188013974606</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
@@ -7941,10 +7951,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C68" t="n">
-        <v>4.57994612254222</v>
+        <v>4.617418472494092</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8001,13 +8011,13 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>138.7086256764711</v>
+        <v>139.3015969106096</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>0.6717420418772324</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
@@ -8015,7 +8025,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.999999999999996</v>
+        <v>7.377817862478153</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8033,10 +8043,10 @@
         <v>30.06418425824019</v>
       </c>
       <c r="AJ68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK68" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
     </row>
     <row r="69">
@@ -8046,10 +8056,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4588273488835499</v>
+        <v>0.4563291789660053</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8081,16 +8091,16 @@
         <v>17.65828511877414</v>
       </c>
       <c r="K69" t="n">
-        <v>17.63866684189834</v>
+        <v>16.99816147673303</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M69" t="n">
         <v>100</v>
       </c>
       <c r="N69" t="n">
-        <v>31.87870734966179</v>
+        <v>28.02442612048434</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
@@ -8112,25 +8122,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X69" t="n">
-        <v>17.63866684189834</v>
+        <v>18.91966737758988</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.615801610641687</v>
       </c>
       <c r="Z69" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA69" t="n">
-        <v>36.8421052631579</v>
+        <v>40</v>
       </c>
       <c r="AB69" t="n">
-        <v>17.4308752423508</v>
+        <v>17.62762228324134</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>6.000000000000005</v>
+        <v>4.456201769320445</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8153,10 +8163,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4330130721278142</v>
+        <v>0.4313476386314181</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8184,16 +8194,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>13.5429246420508</v>
+        <v>13.10622145189437</v>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M70" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="N70" t="n">
-        <v>6.838424675154897</v>
+        <v>8.534401960408296</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8226,22 +8236,22 @@
         <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.328276475629142</v>
+        <v>1.707782786367296</v>
       </c>
       <c r="Z70" t="n">
         <v>48</v>
       </c>
       <c r="AA70" t="n">
-        <v>43.75</v>
+        <v>39.58333333333334</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.881238882796172</v>
+        <v>9.824234195123243</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>6.761535408594554</v>
+        <v>6.401541639819675</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8250,10 +8260,10 @@
         <v>50</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.43478125619634</v>
+        <v>34.51648060260157</v>
       </c>
       <c r="AH70" t="n">
-        <v>15.56521874380366</v>
+        <v>15.48351939739843</v>
       </c>
       <c r="AI70" t="n">
         <v>35.8317605399894</v>
@@ -8272,10 +8282,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C71" t="n">
-        <v>3.114363490318125</v>
+        <v>3.118527014207547</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8303,22 +8313,22 @@
         <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>0.7491270026070751</v>
+        <v>0.8838162893321844</v>
       </c>
       <c r="L71" t="n">
         <v>70</v>
       </c>
       <c r="M71" t="n">
-        <v>61.42857142857143</v>
+        <v>60</v>
       </c>
       <c r="N71" t="n">
-        <v>16.76404623989205</v>
+        <v>17.04168941424902</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>1.241572045939976</v>
+        <v>1.106405121973797</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8381,10 +8391,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0728627792222626</v>
+        <v>0.07244642090020841</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8412,22 +8422,22 @@
         <v>21.68783215290538</v>
       </c>
       <c r="K72" t="n">
-        <v>3.586441604887636</v>
+        <v>2.994519673353646</v>
       </c>
       <c r="L72" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M72" t="n">
-        <v>40</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N72" t="n">
-        <v>15.320771416384</v>
+        <v>14.012342122491</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>1.364617196238993</v>
+        <v>1.947171881578491</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8451,10 +8461,10 @@
         <v>74.07407407407408</v>
       </c>
       <c r="X72" t="n">
-        <v>37.9194877971514</v>
+        <v>36.68527402492516</v>
       </c>
       <c r="Y72" t="n">
-        <v>18.87921198354775</v>
+        <v>19.34275888009441</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8496,10 +8506,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07057280824278518</v>
+        <v>0.07078098761199166</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,7 +8528,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -8531,22 +8541,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>7.269992351935683</v>
+        <v>7.586422998506892</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>87.5</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N73" t="n">
-        <v>11.41329860865269</v>
+        <v>10.78728381292863</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>2.544987268301102</v>
+        <v>2.243384373441448</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8573,22 +8583,22 @@
         <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>7.0437863473783</v>
+        <v>6.769579235547751</v>
       </c>
       <c r="Z73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA73" t="n">
-        <v>70.58823529411765</v>
+        <v>50</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.3210114297409</v>
+        <v>13.29567252782323</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>3.180221672613626</v>
+        <v>3.464985718142299</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8619,10 +8629,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C74" t="n">
-        <v>5.54798018935228</v>
+        <v>5.594820547423735</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8682,22 +8692,22 @@
         <v>33.81594625096176</v>
       </c>
       <c r="Y74" t="n">
-        <v>5.407729434752351</v>
+        <v>4.609108013469765</v>
       </c>
       <c r="Z74" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AA74" t="n">
-        <v>27.77777777777778</v>
+        <v>48</v>
       </c>
       <c r="AB74" t="n">
-        <v>18.08889136107177</v>
+        <v>19.63294624302093</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>4.854805300481713</v>
+        <v>5.651369721221878</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8706,10 +8716,10 @@
         <v>51.28205128205128</v>
       </c>
       <c r="AG74" t="n">
-        <v>30.78334080462358</v>
+        <v>30.72506574634853</v>
       </c>
       <c r="AH74" t="n">
-        <v>20.49871047742771</v>
+        <v>20.55698553570276</v>
       </c>
       <c r="AI74" t="n">
         <v>36.19936288445796</v>
@@ -8728,10 +8738,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1246994373665468</v>
+        <v>0.1253239798459329</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8759,7 +8769,7 @@
         <v>23.35547482758762</v>
       </c>
       <c r="K75" t="n">
-        <v>0.9182823054377121</v>
+        <v>1.423719664077616</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
@@ -8768,13 +8778,13 @@
         <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>18.24441559719496</v>
+        <v>14.10454760014903</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>5.03547779299498</v>
+        <v>4.512041513641329</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8837,10 +8847,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C76" t="n">
-        <v>1.962090554770929</v>
+        <v>1.955845110200027</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8900,7 +8910,7 @@
         <v>14.64967258969352</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.257199568721401</v>
+        <v>1.571503455139711</v>
       </c>
       <c r="Z76" t="n">
         <v>49</v>
@@ -8909,28 +8919,28 @@
         <v>36.73469387755102</v>
       </c>
       <c r="AB76" t="n">
-        <v>11.17042929607493</v>
+        <v>10.7293359413496</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.777721939522559</v>
+        <v>2.467269774615999</v>
       </c>
       <c r="AE76" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF76" t="n">
-        <v>54.54545454545455</v>
+        <v>56.25</v>
       </c>
       <c r="AG76" t="n">
-        <v>30.74315192765171</v>
+        <v>29.36012542539082</v>
       </c>
       <c r="AH76" t="n">
-        <v>23.80230261780284</v>
+        <v>26.88987457460918</v>
       </c>
       <c r="AI76" t="n">
-        <v>37.98593853621745</v>
+        <v>39.32559113685198</v>
       </c>
       <c r="AJ76" t="n">
         <v>53</v>
@@ -8946,10 +8956,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5391845583339272</v>
+        <v>0.5425154251185401</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8977,16 +8987,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>11.04831437719485</v>
+        <v>11.73432649703223</v>
       </c>
       <c r="L77" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M77" t="n">
-        <v>66.66666666666667</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N77" t="n">
-        <v>17.60712689589592</v>
+        <v>17.05136670624185</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
@@ -9001,10 +9011,10 @@
         <v>58.62068965517241</v>
       </c>
       <c r="S77" t="n">
-        <v>41.43697369229825</v>
+        <v>41.28967845879612</v>
       </c>
       <c r="T77" t="n">
-        <v>17.18371596287417</v>
+        <v>17.33101119637629</v>
       </c>
       <c r="U77" t="n">
         <v>40.73783598787858</v>
@@ -9019,22 +9029,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.500480761895275</v>
+        <v>3.91052288632181</v>
       </c>
       <c r="Z77" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AA77" t="n">
-        <v>42.22222222222222</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="AB77" t="n">
-        <v>10.98534356164255</v>
+        <v>11.53545727026889</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.758687878200741</v>
+        <v>6.337298626855947</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9065,10 +9075,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04850579135967129</v>
+        <v>0.0482976121986442</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9096,22 +9106,22 @@
         <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>3.821666540896906</v>
+        <v>3.3760804195067</v>
       </c>
       <c r="L78" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M78" t="n">
-        <v>57.14285714285715</v>
+        <v>63.04347826086956</v>
       </c>
       <c r="N78" t="n">
-        <v>19.00474876988608</v>
+        <v>17.99693567127776</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.1717690199404043</v>
+        <v>0.6035434676584739</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9174,10 +9184,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8273048482006242</v>
+        <v>0.8289702417265815</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9205,22 +9215,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>4.346060665241835</v>
+        <v>4.556112926230038</v>
       </c>
       <c r="L79" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M79" t="n">
-        <v>58.06451612903226</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N79" t="n">
-        <v>11.5741910175252</v>
+        <v>11.87481780639837</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0.6267024654204256</v>
+        <v>0.4245443535981108</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9261,10 +9271,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>28.05013312467481</v>
+        <v>28.28921100399428</v>
       </c>
       <c r="AH79" t="n">
-        <v>24.72764465310297</v>
+        <v>24.4885667737835</v>
       </c>
       <c r="AI79" t="n">
         <v>37.00593802298759</v>
@@ -9283,10 +9293,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1301121057540404</v>
+        <v>0.1290712049526</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9314,7 +9324,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>6.52665445010614</v>
+        <v>5.674437976094993</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9325,7 +9335,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>3.260541286895169</v>
+        <v>4.093290777551628</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9352,37 +9362,37 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.132431725545405</v>
+        <v>5.891375155715128</v>
       </c>
       <c r="Z80" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="AA80" t="n">
-        <v>34.88372093023256</v>
+        <v>32.43243243243244</v>
       </c>
       <c r="AB80" t="n">
-        <v>12.29734885658497</v>
+        <v>11.5451345579825</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>3.022706628421878</v>
+        <v>2.240628686025181</v>
       </c>
       <c r="AE80" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF80" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AG80" t="n">
-        <v>40.28516284122691</v>
+        <v>38.2137112929447</v>
       </c>
       <c r="AH80" t="n">
-        <v>11.71483715877309</v>
+        <v>11.7862887070553</v>
       </c>
       <c r="AI80" t="n">
-        <v>33.49851695035678</v>
+        <v>31.42742581957335</v>
       </c>
       <c r="AJ80" t="n">
         <v>73</v>
@@ -9398,10 +9408,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C81" t="n">
-        <v>1.225135555928601</v>
+        <v>1.210563063787035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9458,25 +9468,25 @@
         <v>64.58333333333333</v>
       </c>
       <c r="X81" t="n">
-        <v>30.54991476816724</v>
+        <v>26.61221483076936</v>
       </c>
       <c r="Y81" t="n">
-        <v>3.682487817253788</v>
+        <v>4.828145685549323</v>
       </c>
       <c r="Z81" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA81" t="n">
-        <v>53.33333333333334</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB81" t="n">
-        <v>12.75904350803913</v>
+        <v>12.94561142715581</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>6.559048338748408</v>
+        <v>5.434226696227551</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9507,14 +9517,14 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C82" t="n">
-        <v>5.308573914764847</v>
+        <v>5.428277052058564</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9524,7 +9534,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9570,22 +9580,22 @@
         <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>5.046116126454425</v>
+        <v>2.904999137148989</v>
       </c>
       <c r="Z82" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA82" t="n">
-        <v>33.33333333333334</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB82" t="n">
-        <v>7.560260277872317</v>
+        <v>8.544375716600737</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.127762349369288</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9616,10 +9626,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C83" t="n">
-        <v>5.745750590098422</v>
+        <v>5.782181979709554</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9655,19 +9665,19 @@
       </c>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R83" t="n">
-        <v>61.90476190476191</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="S83" t="n">
-        <v>58.76678340717467</v>
+        <v>58.92640685071011</v>
       </c>
       <c r="T83" t="n">
-        <v>3.137978497587234</v>
+        <v>2.049202905387453</v>
       </c>
       <c r="U83" t="n">
-        <v>46.81404026715268</v>
+        <v>45.72685693412379</v>
       </c>
       <c r="V83" t="n">
         <v>65</v>
@@ -9679,22 +9689,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>4.491962119101577</v>
+        <v>3.886385791958191</v>
       </c>
       <c r="Z83" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA83" t="n">
-        <v>52.08333333333334</v>
+        <v>46</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.49305910300401</v>
+        <v>12.49448922988003</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.578964361909518</v>
+        <v>2.199078897883089</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9725,10 +9735,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C84" t="n">
-        <v>2.146329264667207</v>
+        <v>2.138002058255684</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9756,22 +9766,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>2.750258390755822</v>
+        <v>2.351613772456873</v>
       </c>
       <c r="L84" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M84" t="n">
-        <v>50</v>
+        <v>49.18032786885246</v>
       </c>
       <c r="N84" t="n">
-        <v>10.44668109268372</v>
+        <v>10.92194658681683</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>2.189524040599955</v>
+        <v>2.587537343017265</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9780,10 +9790,10 @@
         <v>56.09756097560975</v>
       </c>
       <c r="S84" t="n">
-        <v>27.35433608519009</v>
+        <v>27.43720037537145</v>
       </c>
       <c r="T84" t="n">
-        <v>28.74322489041966</v>
+        <v>28.66036060023831</v>
       </c>
       <c r="U84" t="n">
         <v>41.04052722210609</v>
@@ -9812,10 +9822,10 @@
         <v>41.02564102564103</v>
       </c>
       <c r="AG84" t="n">
-        <v>26.88631895799493</v>
+        <v>26.93108900276497</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.1393220676461</v>
+        <v>14.09455202287606</v>
       </c>
       <c r="AI84" t="n">
         <v>27.07931000072518</v>
@@ -9834,7 +9844,7 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C85" t="n">
         <v>6.25579004465426</v>
@@ -9862,19 +9872,19 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>14.50238586538229</v>
+        <v>12.61214035274981</v>
       </c>
       <c r="K85" t="n">
         <v>1.116664134101075</v>
       </c>
       <c r="L85" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M85" t="n">
-        <v>62.71186440677966</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N85" t="n">
-        <v>13.80805675789563</v>
+        <v>14.0527399580849</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
@@ -9889,10 +9899,10 @@
         <v>60.60606060606061</v>
       </c>
       <c r="S85" t="n">
-        <v>65.70160479251388</v>
+        <v>66.09293694520967</v>
       </c>
       <c r="T85" t="n">
-        <v>-5.095544186453267</v>
+        <v>-5.486876339149063</v>
       </c>
       <c r="U85" t="n">
         <v>43.68344081994023</v>
@@ -9943,10 +9953,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C86" t="n">
-        <v>4.521655835669703</v>
+        <v>4.592437011684024</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9974,16 +9984,16 @@
         <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>6.002929924928613</v>
+        <v>7.662280462371474</v>
       </c>
       <c r="L86" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="M86" t="n">
-        <v>55.88235294117647</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N86" t="n">
-        <v>14.84796328255281</v>
+        <v>13.18969080957488</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
@@ -10013,13 +10023,13 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>80.42094873883605</v>
+        <v>71.56995669069586</v>
       </c>
       <c r="Y86" t="n">
-        <v>11.85908702965172</v>
+        <v>10.47934524881954</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
@@ -10058,10 +10068,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C87" t="n">
-        <v>5.77177301124923</v>
+        <v>5.756159558558745</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10089,16 +10099,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>7.035624865276313</v>
+        <v>6.746078540122258</v>
       </c>
       <c r="L87" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M87" t="n">
-        <v>65</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N87" t="n">
-        <v>9.196302056878018</v>
+        <v>9.337848288486441</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10113,10 +10123,10 @@
         <v>55.31914893617022</v>
       </c>
       <c r="S87" t="n">
-        <v>35.43920972095994</v>
+        <v>35.62106096664097</v>
       </c>
       <c r="T87" t="n">
-        <v>19.87993921521028</v>
+        <v>19.69808796952925</v>
       </c>
       <c r="U87" t="n">
         <v>41.24545983821874</v>
@@ -10131,22 +10141,22 @@
         <v>10.60669620884278</v>
       </c>
       <c r="Y87" t="n">
-        <v>3.228621291448519</v>
+        <v>3.490401396160558</v>
       </c>
       <c r="Z87" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA87" t="n">
-        <v>47.5</v>
+        <v>43.58974358974359</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.30063569394995</v>
+        <v>11.95288012215483</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.7971145175834082</v>
+        <v>0.5280289330922283</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10155,10 +10165,10 @@
         <v>44.18604651162791</v>
       </c>
       <c r="AG87" t="n">
-        <v>46.51018272212174</v>
+        <v>47.19173853599511</v>
       </c>
       <c r="AH87" t="n">
-        <v>-2.324136210493833</v>
+        <v>-3.005692024367207</v>
       </c>
       <c r="AI87" t="n">
         <v>30.43330983917051</v>
@@ -10177,10 +10187,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C88" t="n">
-        <v>1.174131674175904</v>
+        <v>1.16164086435044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10222,10 +10232,10 @@
         <v>70.58823529411765</v>
       </c>
       <c r="S88" t="n">
-        <v>46.24430828482993</v>
+        <v>45.45875949106314</v>
       </c>
       <c r="T88" t="n">
-        <v>24.34392700928773</v>
+        <v>25.12947580305451</v>
       </c>
       <c r="U88" t="n">
         <v>53.83109020528557</v>
@@ -10240,43 +10250,43 @@
         <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.827674875734864</v>
+        <v>2.872065270970081</v>
       </c>
       <c r="Z88" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA88" t="n">
-        <v>56.25</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="AB88" t="n">
-        <v>15.72146942893418</v>
+        <v>15.83781769132357</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>4.250001330806697</v>
+        <v>3.220427509095425</v>
       </c>
       <c r="AE88" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF88" t="n">
-        <v>54.83870967741935</v>
+        <v>53.125</v>
       </c>
       <c r="AG88" t="n">
-        <v>49.73289718371112</v>
+        <v>50.26207748005349</v>
       </c>
       <c r="AH88" t="n">
-        <v>5.105812493708228</v>
+        <v>2.862922519946508</v>
       </c>
       <c r="AI88" t="n">
-        <v>37.77216763735451</v>
+        <v>36.44951711897464</v>
       </c>
       <c r="AJ88" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK88" t="n">
-        <v>43.42105263157895</v>
+        <v>42.85714285714285</v>
       </c>
     </row>
     <row r="89">
@@ -10286,10 +10296,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C89" t="n">
-        <v>2.279564092810787</v>
+        <v>2.273318648239885</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10349,22 +10359,22 @@
         <v>27.21456043612742</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.666666666666673</v>
+        <v>2.933336044444457</v>
       </c>
       <c r="Z89" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA89" t="n">
-        <v>41.37931034482759</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.33137870103895</v>
+        <v>13.73854354552278</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>7.534246575342463</v>
+        <v>7.280217190518867</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10395,10 +10405,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C90" t="n">
-        <v>3.060236727335029</v>
+        <v>3.066482171905931</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10458,22 +10468,22 @@
         <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.065293786820177</v>
+        <v>1.865425007467747</v>
       </c>
       <c r="Z90" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AA90" t="n">
-        <v>45.16129032258065</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB90" t="n">
-        <v>12.07408683126673</v>
+        <v>12.43479427582735</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.9544177435374168</v>
+        <v>1.156141953657608</v>
       </c>
       <c r="AE90" t="n">
         <v>23</v>
@@ -10491,10 +10501,10 @@
         <v>40.78552239138171</v>
       </c>
       <c r="AJ90" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK90" t="n">
-        <v>42.68292682926829</v>
+        <v>42.16867469879518</v>
       </c>
     </row>
     <row r="91">
@@ -10504,10 +10514,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2321199887543919</v>
+        <v>0.2319118243741001</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10535,7 +10545,7 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>3.68359159788838</v>
+        <v>3.590608521733563</v>
       </c>
       <c r="L91" t="n">
         <v>59</v>
@@ -10544,7 +10554,7 @@
         <v>64.40677966101696</v>
       </c>
       <c r="N91" t="n">
-        <v>12.86145680465763</v>
+        <v>12.91518156554474</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10585,19 +10595,19 @@
       </c>
       <c r="AD91" t="inlineStr"/>
       <c r="AE91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF91" t="n">
-        <v>41.02564102564103</v>
+        <v>40</v>
       </c>
       <c r="AG91" t="n">
-        <v>33.55355159658959</v>
+        <v>34.01938528685042</v>
       </c>
       <c r="AH91" t="n">
-        <v>7.472089429051444</v>
+        <v>5.980614713149578</v>
       </c>
       <c r="AI91" t="n">
-        <v>27.07931000072518</v>
+        <v>26.34832568429192</v>
       </c>
       <c r="AJ91" t="n">
         <v>72</v>
@@ -10613,10 +10623,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C92" t="n">
-        <v>1.111677863413964</v>
+        <v>1.110636902865045</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10644,7 +10654,7 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>5.507004299517559</v>
+        <v>5.408208926572788</v>
       </c>
       <c r="L92" t="n">
         <v>34</v>
@@ -10653,13 +10663,13 @@
         <v>50</v>
       </c>
       <c r="N92" t="n">
-        <v>13.49671023601048</v>
+        <v>13.49423494098676</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.362872225435608</v>
+        <v>2.45881331237936</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10686,7 +10696,7 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.986984303549349</v>
+        <v>8.073144082815753</v>
       </c>
       <c r="Z92" t="n">
         <v>31</v>
@@ -10710,10 +10720,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.40112302647967</v>
+        <v>40.44033871275418</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.54005344410856</v>
+        <v>12.50083775783405</v>
       </c>
       <c r="AI92" t="n">
         <v>39.52330421009647</v>
@@ -10732,7 +10742,7 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C93" t="n">
         <v>0.0422604113243742</v>
@@ -10841,10 +10851,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C94" t="n">
-        <v>8.337583736718907</v>
+        <v>8.353197189409391</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10886,10 +10896,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S94" t="n">
-        <v>38.93356815930909</v>
+        <v>38.59318609941483</v>
       </c>
       <c r="T94" t="n">
-        <v>22.04204159678847</v>
+        <v>22.38242365668273</v>
       </c>
       <c r="U94" t="n">
         <v>45.72685693412379</v>
@@ -10901,25 +10911,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>49.568993011392</v>
+        <v>48.9849654478532</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.717791411042946</v>
+        <v>1.533742331288346</v>
       </c>
       <c r="Z94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA94" t="n">
-        <v>37.5</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB94" t="n">
-        <v>11.204957938577</v>
+        <v>9.960569015483692</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.357053682896384</v>
+        <v>4.535825545171345</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10950,10 +10960,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1440601251563084</v>
+        <v>0.1442682993210307</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10972,7 +10982,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -10985,13 +10995,13 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>7.989005820534723</v>
+        <v>8.145055394013001</v>
       </c>
       <c r="L95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M95" t="n">
-        <v>85.71428571428571</v>
+        <v>100</v>
       </c>
       <c r="N95" t="n">
         <v>18.17529258831296</v>
@@ -11027,22 +11037,22 @@
         <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>3.604259677282939</v>
+        <v>3.464962958619899</v>
       </c>
       <c r="Z95" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA95" t="n">
-        <v>46.66666666666666</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.2632587778579</v>
+        <v>10.24624973377114</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.485317623679761</v>
+        <v>2.626027936668685</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11073,10 +11083,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1286548466305458</v>
+        <v>0.1276139556135358</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11101,25 +11111,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>13.70647230932033</v>
+        <v>13.98710152278624</v>
       </c>
       <c r="K96" t="n">
-        <v>0.4878004798731794</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M96" t="n">
-        <v>55.22388059701493</v>
+        <v>53.44827586206897</v>
       </c>
       <c r="N96" t="n">
-        <v>13.62785923657208</v>
+        <v>13.13871883252217</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>9.466024208612311</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11182,10 +11192,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C97" t="n">
-        <v>1.910045712469312</v>
+        <v>1.906922990079772</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11213,16 +11223,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>6.866718200387001</v>
+        <v>6.692002437595312</v>
       </c>
       <c r="L97" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M97" t="n">
-        <v>48.48484848484848</v>
+        <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>14.90139410824436</v>
+        <v>14.76284884323322</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11237,10 +11247,10 @@
         <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>35.69795617725568</v>
+        <v>35.7305919960984</v>
       </c>
       <c r="T97" t="n">
-        <v>20.30204382274432</v>
+        <v>20.2694080039016</v>
       </c>
       <c r="U97" t="n">
         <v>42.30602802165686</v>
@@ -11255,7 +11265,7 @@
         <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>9.035307526847468</v>
+        <v>9.184025162236598</v>
       </c>
       <c r="Z97" t="n">
         <v>13</v>
@@ -11279,10 +11289,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG97" t="n">
-        <v>54.14294147759284</v>
+        <v>54.04129508084883</v>
       </c>
       <c r="AH97" t="n">
-        <v>-1.511362530224424</v>
+        <v>-1.409716133480408</v>
       </c>
       <c r="AI97" t="n">
         <v>37.25897138449667</v>
@@ -11301,10 +11311,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6532668430828188</v>
+        <v>0.6545159478186312</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11332,7 +11342,7 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>9.083450760319156</v>
+        <v>9.292028091904614</v>
       </c>
       <c r="L98" t="n">
         <v>23</v>
@@ -11341,13 +11351,13 @@
         <v>65.21739130434783</v>
       </c>
       <c r="N98" t="n">
-        <v>12.41406750555115</v>
+        <v>12.22938373902756</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>0.8402275810789339</v>
+        <v>0.6477800077971496</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11374,43 +11384,43 @@
         <v>10.54345902266514</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.320755000118667</v>
+        <v>1.132071442150129</v>
       </c>
       <c r="Z98" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AA98" t="n">
-        <v>41.50943396226415</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.24652735569172</v>
+        <v>11.17770303992751</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>6.768642179912665</v>
+        <v>6.946568678063569</v>
       </c>
       <c r="AE98" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AF98" t="n">
-        <v>58</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="AG98" t="n">
-        <v>37.63964522834021</v>
+        <v>38.07808355719629</v>
       </c>
       <c r="AH98" t="n">
-        <v>20.36035477165979</v>
+        <v>18.78466154084293</v>
       </c>
       <c r="AI98" t="n">
-        <v>44.23344176857823</v>
+        <v>43.26530210930225</v>
       </c>
       <c r="AJ98" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AK98" t="n">
-        <v>52.23880597014925</v>
+        <v>51.47058823529412</v>
       </c>
     </row>
     <row r="99">
@@ -11420,10 +11430,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4596600455424388</v>
+        <v>0.4617418473534989</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11448,19 +11458,19 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>22.659960715244</v>
+        <v>21.64053449738032</v>
       </c>
       <c r="K99" t="n">
-        <v>4.356555606903556</v>
+        <v>4.829186779800199</v>
       </c>
       <c r="L99" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M99" t="n">
-        <v>68.18181818181819</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N99" t="n">
-        <v>12.91686969642192</v>
+        <v>12.14580322778225</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11501,19 +11511,19 @@
       </c>
       <c r="AD99" t="inlineStr"/>
       <c r="AE99" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF99" t="n">
-        <v>52.5</v>
+        <v>51.28205128205128</v>
       </c>
       <c r="AG99" t="n">
-        <v>38.44711166735622</v>
+        <v>37.9132228715562</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.05288833264378</v>
+        <v>13.36882841049508</v>
       </c>
       <c r="AI99" t="n">
-        <v>37.49736210669248</v>
+        <v>36.19936288445796</v>
       </c>
       <c r="AJ99" t="n">
         <v>79</v>
@@ -11529,10 +11539,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C100" t="n">
-        <v>337.4406434389041</v>
+        <v>337.9721310609448</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11557,19 +11567,19 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>14.94373428959337</v>
+        <v>12.69669682287478</v>
       </c>
       <c r="K100" t="n">
-        <v>10.09996206253634</v>
+        <v>10.2733755743974</v>
       </c>
       <c r="L100" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M100" t="n">
-        <v>52.63157894736842</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N100" t="n">
-        <v>14.65805885884244</v>
+        <v>8.779532552360974</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11599,25 +11609,25 @@
         <v>64.91228070175438</v>
       </c>
       <c r="X100" t="n">
-        <v>11.67316747858962</v>
+        <v>11.67288888132132</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.408758658479792</v>
+        <v>1.253225667342794</v>
       </c>
       <c r="Z100" t="n">
         <v>57</v>
       </c>
       <c r="AA100" t="n">
-        <v>33.33333333333334</v>
+        <v>35.08771929824562</v>
       </c>
       <c r="AB100" t="n">
-        <v>13.39108595075927</v>
+        <v>11.45203400959957</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>6.685422814272246</v>
+        <v>6.832399719639182</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11648,19 +11658,19 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C101" t="n">
-        <v>349.0480867033897</v>
+        <v>348.4491644165907</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11675,27 +11685,17 @@
       <c r="I101" t="n">
         <v>10</v>
       </c>
-      <c r="J101" t="n">
-        <v>11.19277381576541</v>
-      </c>
-      <c r="K101" t="n">
-        <v>10.53272386715667</v>
-      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="n">
-        <v>11</v>
-      </c>
-      <c r="M101" t="n">
-        <v>36.36363636363637</v>
-      </c>
-      <c r="N101" t="n">
-        <v>7.894792849727322</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
+      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="n">
         <v>30</v>
       </c>
@@ -11718,10 +11718,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="X101" t="n">
-        <v>11.75542022182081</v>
+        <v>11.75561335839466</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.094082374024663</v>
+        <v>1.263963032082616</v>
       </c>
       <c r="Z101" t="n">
         <v>41</v>
@@ -11730,13 +11730,13 @@
         <v>43.90243902439025</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.81175403647738</v>
+        <v>12.38952217998343</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.960186148343182</v>
+        <v>4.796665040806003</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11767,10 +11767,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C102" t="n">
-        <v>422.3847179507953</v>
+        <v>421.6889434652756</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11827,25 +11827,25 @@
         <v>47.22222222222222</v>
       </c>
       <c r="X102" t="n">
-        <v>11.51578143108469</v>
+        <v>11.13903673030769</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.9335598427556158</v>
+        <v>1.096935968105639</v>
       </c>
       <c r="Z102" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA102" t="n">
-        <v>36.8421052631579</v>
+        <v>37.83783783783784</v>
       </c>
       <c r="AB102" t="n">
-        <v>11.2667372239588</v>
+        <v>11.7842686229323</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.104760553412323</v>
+        <v>3.946352997350722</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7602710659182595</v>
+        <v>0.7606874342329235</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11939,22 +11939,22 @@
         <v>17.69684631574038</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.6528777773894157</v>
+        <v>0.5984695594512757</v>
       </c>
       <c r="Z103" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA103" t="n">
-        <v>36.17021276595744</v>
+        <v>36.95652173913044</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.69385969484624</v>
+        <v>11.97992118648431</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.395405179575942</v>
+        <v>7.446093040766122</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11963,10 +11963,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="AG103" t="n">
-        <v>37.81883034290784</v>
+        <v>38.26204122409825</v>
       </c>
       <c r="AH103" t="n">
-        <v>23.9458755394451</v>
+        <v>23.50266465825469</v>
       </c>
       <c r="AI103" t="n">
         <v>45.0410173444307</v>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04725671639350872</v>
+        <v>0.04746489555453581</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12013,40 +12013,40 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>19.88964985877965</v>
+        <v>18.611805593619</v>
       </c>
       <c r="K104" t="n">
-        <v>1.527979459194229</v>
+        <v>1.975238837281168</v>
       </c>
       <c r="L104" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M104" t="n">
-        <v>50</v>
+        <v>45.28301886792453</v>
       </c>
       <c r="N104" t="n">
-        <v>13.17943248787203</v>
+        <v>15.97840695207225</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.434817036617298</v>
+        <v>1.985541966662785</v>
       </c>
       <c r="Q104" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="R104" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="S104" t="n">
-        <v>45.89404516916189</v>
+        <v>50.23156808333601</v>
       </c>
       <c r="T104" t="n">
-        <v>16.60595483083811</v>
+        <v>9.768431916663992</v>
       </c>
       <c r="U104" t="n">
-        <v>47.0324391373011</v>
+        <v>43.5727090128925</v>
       </c>
       <c r="V104" t="n">
         <v>69</v>
@@ -12072,10 +12072,10 @@
         <v>64.28571428571429</v>
       </c>
       <c r="AG104" t="n">
-        <v>41.2461647343334</v>
+        <v>42.12299183139859</v>
       </c>
       <c r="AH104" t="n">
-        <v>23.03954955138089</v>
+        <v>22.1627224543157</v>
       </c>
       <c r="AI104" t="n">
         <v>49.16636571945582</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -437,7 +437,7 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -670,7 +670,7 @@
         <v>46259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3972062347804994</v>
+        <v>0.393667184046734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>17.68960189117161</v>
+        <v>17.69759076271513</v>
       </c>
       <c r="K2" t="n">
-        <v>1.317833972328941</v>
+        <v>0.4248535865102765</v>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M2" t="n">
-        <v>53.125</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N2" t="n">
-        <v>11.31574803100355</v>
+        <v>11.49230194429774</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>8.56923770206366</v>
+        <v>9.534638161300668</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -779,7 +779,7 @@
         <v>46259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6461887811693681</v>
+        <v>0.6436906112518235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.092668168145861</v>
+        <v>0.7018432732212476</v>
       </c>
       <c r="L3" t="n">
         <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>58.49056603773585</v>
+        <v>60.37735849056604</v>
       </c>
       <c r="N3" t="n">
-        <v>12.80061761725111</v>
+        <v>12.41245197393265</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>8.811056225203906</v>
+        <v>9.233353059438333</v>
       </c>
       <c r="Q3" t="n">
         <v>37</v>
@@ -888,7 +888,7 @@
         <v>46259</v>
       </c>
       <c r="C4" t="n">
-        <v>1.503054982175967</v>
+        <v>1.494727934397123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         <v>18.2305339009923</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.567827599165317</v>
+        <v>2.11314990092869</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>44</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5986836850724</v>
+        <v>14.05792332230468</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.566480039165715</v>
+        <v>8.057108887546205</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -997,7 +997,7 @@
         <v>46259</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2337854220426087</v>
+        <v>0.2314954562676156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>17.37484898646685</v>
+        <v>17.43715476141968</v>
       </c>
       <c r="K5" t="n">
-        <v>1.277358574056398</v>
+        <v>0.3610105621733695</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>72.72727272727273</v>
+        <v>74.35897435897436</v>
       </c>
       <c r="N5" t="n">
-        <v>13.21227524363912</v>
+        <v>12.93324869837158</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.700914646864504</v>
+        <v>2.629496677090337</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1106,7 +1106,7 @@
         <v>46259</v>
       </c>
       <c r="C6" t="n">
-        <v>1.700825382922108</v>
+        <v>1.694580097192065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>3.929581522018988</v>
+        <v>3.54796096359713</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1172,16 +1172,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.186907875003246</v>
+        <v>7.527709632567293</v>
       </c>
       <c r="Z6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>48.57142857142857</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.01867986203533</v>
+        <v>11.40216735484644</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1221,7 +1221,7 @@
         <v>46259</v>
       </c>
       <c r="C7" t="n">
-        <v>2.169228963636653</v>
+        <v>2.183801614827257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,25 +1246,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>11.0668297124846</v>
+        <v>12.3532304777189</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4821600913267776</v>
+        <v>2.641883229527853</v>
       </c>
       <c r="L7" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M7" t="n">
-        <v>60.60606060606061</v>
+        <v>57.97101449275362</v>
       </c>
       <c r="N7" t="n">
-        <v>13.24631496318597</v>
+        <v>12.83211617703734</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>7.481765819763808</v>
+        <v>5.220205048742455</v>
       </c>
       <c r="Q7" t="n">
         <v>49</v>
@@ -1291,16 +1291,16 @@
         <v>17.31307710509156</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.63802945740652</v>
+        <v>10.03770517248683</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.97318896738145</v>
+        <v>12.36271703915551</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1340,7 +1340,7 @@
         <v>46259</v>
       </c>
       <c r="C8" t="n">
-        <v>0.393667184046734</v>
+        <v>0.3892954362377208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.156105976270097</v>
+        <v>5.220470370066721</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
@@ -1411,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.010577891146816</v>
+        <v>2.932626528941373</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1445,7 +1445,7 @@
         <v>46259</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5908130323208794</v>
+        <v>0.5878985338509305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,16 +1505,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.001523449057055</v>
+        <v>5.470153793021493</v>
       </c>
       <c r="Z9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>42.10526315789474</v>
+        <v>50</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.69782377250188</v>
+        <v>10.86767921021994</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1554,7 +1554,7 @@
         <v>46259</v>
       </c>
       <c r="C10" t="n">
-        <v>1.940231657509542</v>
+        <v>1.926700125500537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,22 +1582,22 @@
         <v>10.66625626204533</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8261482106748819</v>
+        <v>0.1229681308236641</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>40.90909090909091</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="N10" t="n">
-        <v>9.624545134931306</v>
+        <v>10.16882093237464</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.131458338083528</v>
+        <v>5.869813868779072</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1663,11 +1663,11 @@
         <v>46259</v>
       </c>
       <c r="C11" t="n">
-        <v>8.290743378647452</v>
+        <v>8.441673421322138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1720,25 +1720,25 @@
         <v>61.76470588235294</v>
       </c>
       <c r="X11" t="n">
-        <v>22.29702291509528</v>
+        <v>23.11730782489165</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.865853658536577</v>
+        <v>1.756511205330114</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>52.94117647058823</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.63968901524</v>
+        <v>12.28509325710722</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.247842170160284</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1772,7 +1772,7 @@
         <v>46259</v>
       </c>
       <c r="C12" t="n">
-        <v>7.005235773797533</v>
+        <v>7.088507521480119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1800,16 +1804,16 @@
         <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>6.631148419742172</v>
+        <v>7.89868064464252</v>
       </c>
       <c r="L12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>71.42857142857143</v>
+        <v>75</v>
       </c>
       <c r="N12" t="n">
-        <v>17.80846345924088</v>
+        <v>18.03133326988203</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1842,16 +1846,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.224916141080516</v>
+        <v>4.098317818834807</v>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>33.33333333333334</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.19016848477012</v>
+        <v>9.759433103302454</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1891,7 +1895,7 @@
         <v>46259</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2244173543837258</v>
+        <v>0.223168289410173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1923,7 @@
         <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>6.243654045878744</v>
+        <v>5.652321761014245</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1955,22 +1959,22 @@
         <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.893587248109958</v>
+        <v>9.400668482299423</v>
       </c>
       <c r="Z13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.02852793358301</v>
+        <v>17.12278197065909</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.214418083722746</v>
+        <v>0.661518697390695</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1994,11 +1998,11 @@
         <v>46259</v>
       </c>
       <c r="C14" t="n">
-        <v>8.556172074385694</v>
+        <v>8.597807948226986</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2008,7 +2012,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2054,22 +2058,22 @@
         <v>12.90895707120068</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.269251017781448</v>
+        <v>1.793675596943411</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>43.18181818181818</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.96436820482929</v>
+        <v>12.64386317536204</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.2100927860916535</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2103,7 +2107,7 @@
         <v>46259</v>
       </c>
       <c r="C15" t="n">
-        <v>15.51977197434193</v>
+        <v>15.0097325197861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,22 +2167,22 @@
         <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.843317972350222</v>
+        <v>5.069124423963123</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
-        <v>42.85714285714285</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.99294426310307</v>
+        <v>10.18153610059048</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.309859154929578</v>
+        <v>5.194174757281567</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2212,7 +2216,7 @@
         <v>46259</v>
       </c>
       <c r="C16" t="n">
-        <v>36.55629723265518</v>
+        <v>35.97339499887708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,22 +2244,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>4.982298378502326</v>
+        <v>3.308320955610489</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>65.45454545454545</v>
+        <v>63.76811594202898</v>
       </c>
       <c r="N16" t="n">
-        <v>16.71603705115386</v>
+        <v>18.14434792096311</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>4.779569221667157</v>
+        <v>6.477386315536782</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2282,16 +2286,16 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.667113539255146</v>
+        <v>11.10750125047431</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA16" t="n">
-        <v>47.36842105263158</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.06432062655764</v>
+        <v>13.40563990076058</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
@@ -2331,7 +2335,7 @@
         <v>46259</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6949027566863712</v>
+        <v>0.6849101565407119</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,25 +2360,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>16.09305130534204</v>
+        <v>16.15881909709504</v>
       </c>
       <c r="K17" t="n">
-        <v>1.626561649542957</v>
+        <v>0.2437594172932656</v>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>64.40677966101696</v>
+        <v>68.51851851851852</v>
       </c>
       <c r="N17" t="n">
-        <v>18.36278129194078</v>
+        <v>15.68280410259236</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.271429680397644</v>
+        <v>7.737379990328552</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2440,7 +2444,7 @@
         <v>46259</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09784429957163032</v>
+        <v>0.09701158292752196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,22 +2472,22 @@
         <v>20.88000978125635</v>
       </c>
       <c r="K18" t="n">
-        <v>1.308072264219784</v>
+        <v>0.4458767318659573</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M18" t="n">
-        <v>65</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N18" t="n">
-        <v>16.06293984455046</v>
+        <v>15.88557305699444</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>8.579699071867598</v>
+        <v>9.511712754161316</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2549,7 +2553,7 @@
         <v>46259</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02581424198978097</v>
+        <v>0.02560606282875388</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,22 +2581,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>4.743915854571501</v>
+        <v>3.899207707265506</v>
       </c>
       <c r="L19" t="n">
         <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>53.57142857142857</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N19" t="n">
-        <v>16.66899705560132</v>
+        <v>15.85846737675938</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>5.018032887682145</v>
+        <v>5.871837165422278</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2658,7 +2662,7 @@
         <v>46259</v>
       </c>
       <c r="C20" t="n">
-        <v>1.64149429434153</v>
+        <v>1.622758119469684</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2683,25 +2687,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>17.71726923698957</v>
+        <v>18.29524817848574</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7024206878367467</v>
+        <v>0.2572308038585103</v>
       </c>
       <c r="L20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M20" t="n">
-        <v>56.25</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>14.63837999942642</v>
+        <v>12.76603255396804</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.288528421958768</v>
+        <v>1.738297758842955</v>
       </c>
       <c r="Q20" t="n">
         <v>49</v>
@@ -2767,7 +2771,7 @@
         <v>46259</v>
       </c>
       <c r="C21" t="n">
-        <v>0.954710599879788</v>
+        <v>0.9630377269749711</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,22 +2799,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>2.767402826360033</v>
+        <v>3.663755317559714</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M21" t="n">
-        <v>54.23728813559322</v>
+        <v>52.83018867924528</v>
       </c>
       <c r="N21" t="n">
-        <v>16.59487055692764</v>
+        <v>14.88081334089142</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.091689611423944</v>
+        <v>4.182990158090272</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2876,7 +2880,7 @@
         <v>46259</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3366260416722882</v>
+        <v>0.3389160274325008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,16 +2940,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.257133980795839</v>
+        <v>7.633029393576773</v>
       </c>
       <c r="Z22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA22" t="n">
-        <v>54.54545454545455</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.89827904879843</v>
+        <v>10.21192621751102</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
@@ -2977,7 +2981,7 @@
         <v>46259</v>
       </c>
       <c r="C23" t="n">
-        <v>0.739869497312277</v>
+        <v>0.7519438592985576</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3005,22 +3009,22 @@
         <v>27.73484467032905</v>
       </c>
       <c r="K23" t="n">
-        <v>0.794108375896263</v>
+        <v>2.439026236459574</v>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>62.5</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N23" t="n">
-        <v>21.84187412476708</v>
+        <v>25.2492217942063</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>9.13336282491013</v>
+        <v>7.380950445670442</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -3047,7 +3051,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>27.1609810190017</v>
+        <v>25.97227857202011</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3211,7 +3215,7 @@
         <v>46259</v>
       </c>
       <c r="C25" t="n">
-        <v>3.497413402668605</v>
+        <v>3.491167958097704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,25 +3240,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>15.89424339008501</v>
+        <v>16.09461141165198</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05956289674409199</v>
+        <v>0.1194011641791226</v>
       </c>
       <c r="L25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M25" t="n">
-        <v>58.92857142857143</v>
+        <v>58.18181818181818</v>
       </c>
       <c r="N25" t="n">
-        <v>17.64570129619283</v>
+        <v>17.76371357663987</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.935710364285731</v>
+        <v>7.871200530752298</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3320,7 +3324,7 @@
         <v>46259</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4517492469996602</v>
+        <v>0.4405075421181885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3419,7 +3423,7 @@
         <v>46259</v>
       </c>
       <c r="C27" t="n">
-        <v>45.50801010853316</v>
+        <v>47.81880110672491</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,7 +3451,7 @@
         <v>50.20031327035493</v>
       </c>
       <c r="K27" t="n">
-        <v>38.05702093227031</v>
+        <v>45.06723562736727</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3472,25 +3476,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>40.26744898928287</v>
+        <v>47.34081877172307</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.575866726699682</v>
+        <v>1.543077582511798</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>42.85714285714285</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB27" t="n">
-        <v>12.92066461084936</v>
+        <v>19.54791007974723</v>
       </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.494967978042097</v>
+        <v>4.526774053112748</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3514,7 +3518,7 @@
         <v>46259</v>
       </c>
       <c r="C28" t="n">
-        <v>1.625880841651045</v>
+        <v>1.61443107169084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,22 +3578,22 @@
         <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.82275867304319</v>
+        <v>2.514141952631899</v>
       </c>
       <c r="Z28" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AA28" t="n">
-        <v>41.86046511627907</v>
+        <v>50</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.4704057594197</v>
+        <v>11.35666482995179</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.254795989882698</v>
+        <v>3.575757671101731</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3623,7 +3627,7 @@
         <v>46259</v>
       </c>
       <c r="C29" t="n">
-        <v>0.405533401637942</v>
+        <v>0.3805519012737937</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,7 +3646,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3655,16 +3659,16 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>12.18366854655952</v>
+        <v>5.272976738367996</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
-        <v>85.71428571428571</v>
+        <v>87.5</v>
       </c>
       <c r="N29" t="n">
-        <v>20.81369456717993</v>
+        <v>13.37665263975417</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3697,7 +3701,7 @@
         <v>48.55798797437896</v>
       </c>
       <c r="Y29" t="n">
-        <v>11.4743259503753</v>
+        <v>16.92764779655356</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3742,7 +3746,7 @@
         <v>46259</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4255186416915201</v>
+        <v>0.4184405400158098</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,7 +3763,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>5</v>
       </c>
@@ -3770,13 +3778,17 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>16.24015449814726</v>
+        <v>14.3066090509548</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>100</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9.068551388840314</v>
+      </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
@@ -3808,22 +3820,22 @@
         <v>18.28742967351311</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.730763092085563</v>
+        <v>3.365379257581158</v>
       </c>
       <c r="Z30" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA30" t="n">
-        <v>36.36363636363637</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.78543534679678</v>
+        <v>14.64473726428202</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>8.414878519575076</v>
+        <v>6.865676805524523</v>
       </c>
       <c r="AE30" t="n">
         <v>50</v>
@@ -3857,7 +3869,7 @@
         <v>46259</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1859041831549333</v>
+        <v>0.1875696164431501</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3874,7 +3886,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>5</v>
       </c>
@@ -3885,22 +3901,22 @@
         <v>18.68860738081651</v>
       </c>
       <c r="K31" t="n">
-        <v>6.76156428266077</v>
+        <v>7.717993880106966</v>
       </c>
       <c r="L31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>63.63636363636363</v>
+        <v>75</v>
       </c>
       <c r="N31" t="n">
-        <v>17.7792118719494</v>
+        <v>15.80297145497943</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>3.03333483271675</v>
+        <v>2.118500389482714</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3966,7 +3982,7 @@
         <v>46259</v>
       </c>
       <c r="C32" t="n">
-        <v>2.308709236351135</v>
+        <v>2.279564092810787</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,16 +4010,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>5.933668115990054</v>
+        <v>4.596361575008845</v>
       </c>
       <c r="L32" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="M32" t="n">
-        <v>44.44444444444444</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N32" t="n">
-        <v>12.04808016565562</v>
+        <v>10.76786269654213</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4036,22 +4052,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.150575630017419</v>
+        <v>7.335330687681241</v>
       </c>
       <c r="Z32" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>43.47826086956522</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.49284904697489</v>
+        <v>14.63702839182677</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.970629423033632</v>
+        <v>0.7172845025524732</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4085,7 +4101,7 @@
         <v>46259</v>
       </c>
       <c r="C33" t="n">
-        <v>1.732052288303078</v>
+        <v>1.733093248643818</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4113,7 +4129,7 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.695570101928227</v>
+        <v>5.759092951331213</v>
       </c>
       <c r="L33" t="n">
         <v>29</v>
@@ -4194,7 +4210,7 @@
         <v>46259</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7985760729749396</v>
+        <v>0.7914979712992293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4222,16 +4238,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>5.221203428220167</v>
+        <v>4.288585482967844</v>
       </c>
       <c r="L34" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M34" t="n">
-        <v>70</v>
+        <v>73.91304347826087</v>
       </c>
       <c r="N34" t="n">
-        <v>9.756922704522095</v>
+        <v>10.23547984669301</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4303,7 +4319,7 @@
         <v>46259</v>
       </c>
       <c r="C35" t="n">
-        <v>1.948558863921065</v>
+        <v>1.983949452032315</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4338,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4335,16 +4351,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>9.850494520327114</v>
+        <v>11.84564779866479</v>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>80</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N35" t="n">
-        <v>10.83557166488997</v>
+        <v>10.30232128559899</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4377,16 +4393,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.231310340757612</v>
+        <v>4.528241916751141</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AA35" t="n">
-        <v>41.66666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>14.75083324357035</v>
+        <v>14.89562390716056</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4426,7 +4442,7 @@
         <v>46259</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08202267271642326</v>
+        <v>0.08223085187745036</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4445,7 +4461,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -4458,16 +4474,16 @@
         <v>14.21000360644873</v>
       </c>
       <c r="K36" t="n">
-        <v>5.072576525183403</v>
+        <v>5.339257920748164</v>
       </c>
       <c r="L36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M36" t="n">
-        <v>75</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N36" t="n">
-        <v>18.04659990485045</v>
+        <v>17.97175001920986</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4539,7 +4555,7 @@
         <v>46259</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06557650338183003</v>
+        <v>0.06516014485159648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4567,22 +4583,22 @@
         <v>14.02780799500539</v>
       </c>
       <c r="K37" t="n">
-        <v>6.747475769240485</v>
+        <v>6.069714378721769</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M37" t="n">
-        <v>55.26315789473684</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="N37" t="n">
-        <v>18.8141351286606</v>
+        <v>21.97037154756377</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>1.173352551649232</v>
+        <v>1.819827301868804</v>
       </c>
       <c r="Q37" t="n">
         <v>37</v>
@@ -4609,16 +4625,16 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.808150201163408</v>
+        <v>5.412542576915458</v>
       </c>
       <c r="Z37" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AA37" t="n">
-        <v>54.3859649122807</v>
+        <v>56.60377358490566</v>
       </c>
       <c r="AB37" t="n">
-        <v>12.86768914035915</v>
+        <v>12.70203986642455</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
@@ -4658,7 +4674,7 @@
         <v>46259</v>
       </c>
       <c r="C38" t="n">
-        <v>1.658148707580934</v>
+        <v>1.64357605639033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4686,22 +4702,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>4.6586487506874</v>
+        <v>3.738855504550442</v>
       </c>
       <c r="L38" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M38" t="n">
-        <v>54.34782608695652</v>
+        <v>50.9433962264151</v>
       </c>
       <c r="N38" t="n">
-        <v>10.45233449384154</v>
+        <v>11.09903794367203</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>5.103592787669675</v>
+        <v>6.035486380679145</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4767,7 +4783,7 @@
         <v>46259</v>
       </c>
       <c r="C39" t="n">
-        <v>2.758376641985655</v>
+        <v>2.764622086556557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4827,22 +4843,22 @@
         <v>11.08431820998319</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.70623367801177</v>
+        <v>1.483679491652656</v>
       </c>
       <c r="Z39" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA39" t="n">
-        <v>38.70967741935484</v>
+        <v>39.34426229508197</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.08059302588321</v>
+        <v>12.15607792814228</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.368299723018875</v>
+        <v>4.58433738191093</v>
       </c>
       <c r="AE39" t="n">
         <v>44</v>
@@ -4876,11 +4892,11 @@
         <v>46259</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2487743422463171</v>
+        <v>0.2558524439220275</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4890,7 +4906,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4936,22 +4952,22 @@
         <v>43.91653617576685</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.594265102840756</v>
+        <v>2.908242965917018</v>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA40" t="n">
-        <v>60</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB40" t="n">
-        <v>13.95377872703095</v>
+        <v>18.41651882502994</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.154412586589305</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4985,7 +5001,7 @@
         <v>46259</v>
       </c>
       <c r="C41" t="n">
-        <v>1.863205354397858</v>
+        <v>1.884023291318504</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,10 +5029,10 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>23.13111334804212</v>
+        <v>24.50687997762919</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5048,25 +5064,25 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X41" t="n">
-        <v>23.19990587560969</v>
+        <v>26.020221165252</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.05583813321824449</v>
+        <v>1.20087171219796</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AA41" t="n">
-        <v>47.05882352941177</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.93319642729028</v>
+        <v>19.44397771139826</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.945806750279334</v>
+        <v>1.820996115027629</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5100,7 +5116,7 @@
         <v>46259</v>
       </c>
       <c r="C42" t="n">
-        <v>3.703510851193589</v>
+        <v>3.730574232685138</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5158,22 +5174,22 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.238076879260532</v>
+        <v>3.538297248009925</v>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>33.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="AB42" t="n">
-        <v>7.174717563702993</v>
+        <v>7.843680062354141</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.0169250292464</v>
+        <v>6.69872350128794</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5205,7 +5221,7 @@
         <v>46259</v>
       </c>
       <c r="C43" t="n">
-        <v>6.682557751527513</v>
+        <v>6.64092187768622</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,22 +5249,22 @@
         <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>1.904761904761898</v>
+        <v>1.269841269841265</v>
       </c>
       <c r="L43" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M43" t="n">
-        <v>69.6969696969697</v>
+        <v>70.96774193548387</v>
       </c>
       <c r="N43" t="n">
-        <v>19.07969709630667</v>
+        <v>17.89917316071853</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.056074766355143</v>
+        <v>2.69592476489029</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5275,7 +5291,7 @@
         <v>20.83229097494805</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.74604514578119</v>
+        <v>14.28345296418754</v>
       </c>
       <c r="Z43" t="n">
         <v>2</v>
@@ -5320,7 +5336,7 @@
         <v>46259</v>
       </c>
       <c r="C44" t="n">
-        <v>4.617418472494092</v>
+        <v>4.634072885525317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5352,7 +5368,7 @@
         <v>20.15821391009879</v>
       </c>
       <c r="K44" t="n">
-        <v>2.941359962571521</v>
+        <v>3.312655728165548</v>
       </c>
       <c r="L44" t="n">
         <v>14</v>
@@ -5361,13 +5377,13 @@
         <v>78.57142857142857</v>
       </c>
       <c r="N44" t="n">
-        <v>17.71688663511587</v>
+        <v>17.88671937823317</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.856952385314252</v>
+        <v>6.472918757823898</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5425,7 +5441,7 @@
         <v>46259</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02394062704238469</v>
+        <v>0.02373244788135759</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5485,22 +5501,22 @@
         <v>19.58690552546656</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.8620681257431539</v>
+        <v>1.724136251486297</v>
       </c>
       <c r="Z45" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="AA45" t="n">
-        <v>51.21951219512195</v>
+        <v>53.19148936170212</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.3323041522808</v>
+        <v>13.18215995678039</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.173913855198497</v>
+        <v>3.333334985380121</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5534,7 +5550,7 @@
         <v>46259</v>
       </c>
       <c r="C46" t="n">
-        <v>10.17476666996596</v>
+        <v>9.987405237680138</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5594,16 +5610,16 @@
         <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>3.21782178217821</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Z46" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="n">
-        <v>25</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB46" t="n">
-        <v>15.61331922051397</v>
+        <v>15.95100982119853</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5643,7 +5659,7 @@
         <v>46259</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7232151635973919</v>
+        <v>0.725713293752677</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5671,7 +5687,7 @@
         <v>20.24791594168004</v>
       </c>
       <c r="K47" t="n">
-        <v>7.387104992404647</v>
+        <v>7.758041580536856</v>
       </c>
       <c r="L47" t="n">
         <v>15</v>
@@ -5680,13 +5696,13 @@
         <v>53.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>17.21933616649681</v>
+        <v>14.90888708292778</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>2.433155272954024</v>
+        <v>2.080548594405873</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5752,7 +5768,7 @@
         <v>46259</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05995566062143486</v>
+        <v>0.05933111814204871</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5780,22 +5796,22 @@
         <v>15.05707226133306</v>
       </c>
       <c r="K48" t="n">
-        <v>4.075422035853538</v>
+        <v>2.991295508888148</v>
       </c>
       <c r="L48" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M48" t="n">
-        <v>55.55555555555556</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N48" t="n">
-        <v>15.71039766258824</v>
+        <v>14.08651342994457</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>5.692581253339024</v>
+        <v>6.80514256712792</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5861,7 +5877,7 @@
         <v>46259</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2620978289536294</v>
+        <v>0.2625141774912533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5889,16 +5905,16 @@
         <v>16.44500858212767</v>
       </c>
       <c r="K49" t="n">
-        <v>5.465210141951427</v>
+        <v>5.632744097452314</v>
       </c>
       <c r="L49" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M49" t="n">
-        <v>61.29032258064516</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="N49" t="n">
-        <v>19.62381254669566</v>
+        <v>19.51519067238355</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5970,7 +5986,7 @@
         <v>46259</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6803301850202866</v>
+        <v>0.6765829499210099</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5998,22 +6014,22 @@
         <v>15.82134875518189</v>
       </c>
       <c r="K50" t="n">
-        <v>1.731228469078827</v>
+        <v>1.17089638562069</v>
       </c>
       <c r="L50" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M50" t="n">
-        <v>58</v>
+        <v>56.25</v>
       </c>
       <c r="N50" t="n">
-        <v>15.01785959482368</v>
+        <v>13.93148522800849</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.230162325829732</v>
+        <v>2.796361123060498</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6079,7 +6095,7 @@
         <v>46259</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1744543136849904</v>
+        <v>0.1750788463799462</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6093,7 +6109,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -6104,25 +6120,25 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>21.1650162252606</v>
+        <v>21.55982902963817</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4582182245078004</v>
+        <v>1.325297078095611</v>
       </c>
       <c r="L51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M51" t="n">
-        <v>60</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N51" t="n">
-        <v>11.45443472377427</v>
+        <v>13.65413182000791</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>3.525626711372576</v>
+        <v>2.639718805702485</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6145,12 +6161,8 @@
       <c r="W51" t="n">
         <v>84.61538461538461</v>
       </c>
-      <c r="X51" t="n">
-        <v>27.09436430358245</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>20.80377996231697</v>
-      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
         <v>0</v>
       </c>
@@ -6159,9 +6171,7 @@
       <c r="AC51" t="n">
         <v>10</v>
       </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
         <v>11</v>
       </c>
@@ -6194,7 +6204,7 @@
         <v>46259</v>
       </c>
       <c r="C52" t="n">
-        <v>4.542473772590349</v>
+        <v>4.496674374859635</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6254,22 +6264,22 @@
         <v>17.40749557792611</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.791889763821576</v>
+        <v>4.761906042663955</v>
       </c>
       <c r="Z52" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA52" t="n">
-        <v>50</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.56773445517566</v>
+        <v>11.01739931790417</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.373966213293301</v>
+        <v>3.399998700925932</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6303,7 +6313,7 @@
         <v>46259</v>
       </c>
       <c r="C53" t="n">
-        <v>1.413537948763338</v>
+        <v>1.438519409365227</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6345,7 @@
         <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>4.7528870923363</v>
+        <v>6.604185194464174</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
@@ -6344,13 +6354,13 @@
         <v>80</v>
       </c>
       <c r="N53" t="n">
-        <v>16.25373172741129</v>
+        <v>12.01629352258359</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>3.099783688827107</v>
+        <v>1.309343346126268</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6408,7 +6418,7 @@
         <v>46259</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07973269674064098</v>
+        <v>0.07931633841858679</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6437,7 +6447,7 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>43.17644124828992</v>
+        <v>43.47316972408662</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -6521,7 +6531,7 @@
         <v>46259</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9472161298894138</v>
+        <v>0.9326435582233292</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6581,16 +6591,16 @@
         <v>21.18657262526651</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.12674472595702</v>
+        <v>4.617104117506566</v>
       </c>
       <c r="Z55" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AA55" t="n">
-        <v>42.85714285714285</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AB55" t="n">
-        <v>13.45364936717568</v>
+        <v>14.0495159489861</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6630,16 +6640,16 @@
         <v>46259</v>
       </c>
       <c r="C56" t="n">
-        <v>1.132495800334611</v>
+        <v>1.198072253961572</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6649,7 +6659,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %91.67: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -6662,22 +6672,22 @@
         <v>19.65620512594927</v>
       </c>
       <c r="K56" t="n">
-        <v>1.209305172093011</v>
+        <v>7.069766027906965</v>
       </c>
       <c r="L56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M56" t="n">
-        <v>90.90909090909091</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="N56" t="n">
-        <v>19.62124520003125</v>
+        <v>24.6329919682953</v>
       </c>
       <c r="O56" t="n">
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>2.757350051126006</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6696,7 +6706,7 @@
         <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>18.68460345908157</v>
+        <v>13.97608681041236</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6733,7 +6743,7 @@
         <v>46259</v>
       </c>
       <c r="C57" t="n">
-        <v>1.35212493950128</v>
+        <v>1.35316589984202</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6765,7 +6775,7 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>7.100191506684839</v>
+        <v>7.182644724273768</v>
       </c>
       <c r="L57" t="n">
         <v>22</v>
@@ -6780,7 +6790,7 @@
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>2.707566114047677</v>
+        <v>2.628555474604921</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6807,7 +6817,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>16.64075022591635</v>
+        <v>16.57657444562146</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6852,21 +6862,21 @@
         <v>46259</v>
       </c>
       <c r="C58" t="n">
-        <v>0.725713293752677</v>
+        <v>0.6961517821058439</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6880,22 +6890,22 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>9.333167921749407</v>
+        <v>4.879544507754963</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M58" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>16.53858197175638</v>
+        <v>17.87195045712985</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.975275595341964</v>
       </c>
       <c r="Q58" t="n">
         <v>23</v>
@@ -6922,22 +6932,22 @@
         <v>13.39281154402059</v>
       </c>
       <c r="Y58" t="n">
-        <v>3.580159594768662</v>
+        <v>7.507766074713373</v>
       </c>
       <c r="Z58" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AA58" t="n">
-        <v>46.875</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB58" t="n">
-        <v>15.72239388744154</v>
+        <v>16.39955447694265</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.50969136130208</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>3</v>
@@ -6971,7 +6981,7 @@
         <v>46259</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7956615745049906</v>
+        <v>0.8035723332855098</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6999,22 +7009,22 @@
         <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>1.727773411391276</v>
+        <v>2.739188191899533</v>
       </c>
       <c r="L59" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M59" t="n">
-        <v>62.29508196721311</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N59" t="n">
-        <v>13.70908536407678</v>
+        <v>13.3915163865691</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.165697309862073</v>
+        <v>5.120550298951332</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7080,7 +7090,7 @@
         <v>46259</v>
       </c>
       <c r="C60" t="n">
-        <v>11.75172539170492</v>
+        <v>11.61640880172072</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7108,22 +7118,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>2.303469605311625</v>
+        <v>1.125484569998014</v>
       </c>
       <c r="L60" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M60" t="n">
-        <v>58.13953488372093</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="N60" t="n">
-        <v>13.58799988709937</v>
+        <v>14.30264373061478</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.568267055521847</v>
+        <v>6.798004933408763</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7189,7 +7199,7 @@
         <v>46259</v>
       </c>
       <c r="C61" t="n">
-        <v>0.622872674331177</v>
+        <v>0.6207908725201169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7206,7 +7216,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7217,22 +7231,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>1.361998839147183</v>
+        <v>1.023220784735668</v>
       </c>
       <c r="L61" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M61" t="n">
-        <v>73.33333333333333</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N61" t="n">
-        <v>19.57989531500803</v>
+        <v>19.13859326488512</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.521932538604137</v>
+        <v>8.885857276707121</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7251,16 +7265,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.3880302141246</v>
+        <v>11.68419436898967</v>
       </c>
       <c r="Z61" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA61" t="n">
-        <v>52.63157894736842</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB61" t="n">
-        <v>11.83234893488008</v>
+        <v>11.77948701260922</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7300,7 +7314,7 @@
         <v>46259</v>
       </c>
       <c r="C62" t="n">
-        <v>9.206732603155896</v>
+        <v>9.191119150465411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7360,7 +7374,7 @@
         <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.503340757238314</v>
+        <v>1.670378619153678</v>
       </c>
       <c r="Z62" t="n">
         <v>61</v>
@@ -7369,13 +7383,13 @@
         <v>45.90163934426229</v>
       </c>
       <c r="AB62" t="n">
-        <v>14.73910895473776</v>
+        <v>14.66823620462634</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.5042396834369689</v>
+        <v>0.3352208380520971</v>
       </c>
       <c r="AE62" t="n">
         <v>31</v>
@@ -7409,7 +7423,7 @@
         <v>46259</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1140822947415013</v>
+        <v>0.1111677862789426</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7426,7 +7440,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>5</v>
       </c>
@@ -7437,13 +7455,17 @@
         <v>16.12393160164715</v>
       </c>
       <c r="K63" t="n">
-        <v>16.08493844525931</v>
+        <v>13.1192676000073</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M63" t="n">
+        <v>100</v>
+      </c>
+      <c r="N63" t="n">
+        <v>16.02109596766168</v>
+      </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
@@ -7475,22 +7497,22 @@
         <v>18.41511331267116</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.967801914996359</v>
+        <v>4.472271794125094</v>
       </c>
       <c r="Z63" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AA63" t="n">
-        <v>28.57142857142857</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB63" t="n">
-        <v>14.19162034110392</v>
+        <v>10.64322758039532</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>8.193428528491143</v>
+        <v>5.786516972288835</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7524,7 +7546,7 @@
         <v>46259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1482237085850297</v>
+        <v>0.1469746334106878</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7549,25 +7571,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>24.59083812498669</v>
+        <v>25.00519543112713</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4379689941304221</v>
+        <v>0.1418404217092606</v>
       </c>
       <c r="L64" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M64" t="n">
-        <v>70.96774193548387</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N64" t="n">
-        <v>15.69039807896171</v>
+        <v>17.601835030586</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.542137850414107</v>
+        <v>4.851278504401813</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7633,7 +7655,7 @@
         <v>46259</v>
       </c>
       <c r="C65" t="n">
-        <v>6.895941604964139</v>
+        <v>6.93237299457527</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7683,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>21.72563255935682</v>
+        <v>22.36871137287795</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7696,10 +7718,10 @@
         <v>63.63636363636363</v>
       </c>
       <c r="X65" t="n">
-        <v>23.0117901863991</v>
+        <v>23.7467374018518</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.045556385362212</v>
+        <v>1.113585746102452</v>
       </c>
       <c r="Z65" t="n">
         <v>28</v>
@@ -7708,13 +7730,13 @@
         <v>42.85714285714285</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.344780687814966</v>
+        <v>9.129985776808761</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.98566037735849</v>
+        <v>2.918918918918922</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7748,7 +7770,7 @@
         <v>46259</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4667381474263286</v>
+        <v>0.4750653140755917</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7805,25 +7827,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X66" t="n">
-        <v>13.05901358398374</v>
+        <v>15.2543368949956</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.059134031724174</v>
+        <v>1.212124179194496</v>
       </c>
       <c r="Z66" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="AA66" t="n">
-        <v>40.67796610169491</v>
+        <v>39.58333333333334</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.21664880997691</v>
+        <v>9.886460238219779</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.993756543287242</v>
+        <v>4.846622908959386</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7954,7 +7976,7 @@
         <v>46259</v>
       </c>
       <c r="C68" t="n">
-        <v>4.617418472494092</v>
+        <v>4.696526696287256</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8011,10 +8033,10 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>139.3015969106096</v>
+        <v>145.7315546439382</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.6717420418772324</v>
+        <v>1.613605277272145</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8025,7 +8047,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.377817862478153</v>
+        <v>6.491136036365564</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8059,7 +8081,7 @@
         <v>46259</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4563291789660053</v>
+        <v>0.470069014002762</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8068,7 +8090,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8076,38 +8098,24 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>5</v>
       </c>
       <c r="I69" t="n">
         <v>10</v>
       </c>
-      <c r="J69" t="n">
-        <v>17.65828511877414</v>
-      </c>
-      <c r="K69" t="n">
-        <v>16.99816147673303</v>
-      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
-        <v>4</v>
-      </c>
-      <c r="M69" t="n">
-        <v>100</v>
-      </c>
-      <c r="N69" t="n">
-        <v>28.02442612048434</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
         <v>8</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -8122,25 +8130,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X69" t="n">
-        <v>18.91966737758988</v>
+        <v>25.43142265824418</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.615801610641687</v>
+        <v>3.914893957446808</v>
       </c>
       <c r="Z69" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AA69" t="n">
-        <v>40</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AB69" t="n">
-        <v>17.62762228324134</v>
+        <v>15.8102876255904</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>4.456201769320445</v>
+        <v>2.170061655164091</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8166,7 +8174,7 @@
         <v>46259</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4313476386314181</v>
+        <v>0.4188569083304737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8194,16 +8202,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>13.10622145189437</v>
+        <v>9.830953011809761</v>
       </c>
       <c r="L70" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>37.5</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N70" t="n">
-        <v>8.534401960408296</v>
+        <v>9.807543501166204</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8236,22 +8244,22 @@
         <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.707782786367296</v>
+        <v>4.554075349351328</v>
       </c>
       <c r="Z70" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA70" t="n">
-        <v>39.58333333333334</v>
+        <v>30.55555555555556</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.824234195123243</v>
+        <v>11.142082824893</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>6.401541639819675</v>
+        <v>3.610342362192465</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8285,7 +8293,7 @@
         <v>46259</v>
       </c>
       <c r="C71" t="n">
-        <v>3.118527014207547</v>
+        <v>3.12685406198639</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8313,22 +8321,22 @@
         <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8838162893321844</v>
+        <v>1.15319486278247</v>
       </c>
       <c r="L71" t="n">
         <v>70</v>
       </c>
       <c r="M71" t="n">
-        <v>60</v>
+        <v>58.57142857142857</v>
       </c>
       <c r="N71" t="n">
-        <v>17.04168941424902</v>
+        <v>17.18235027996364</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>1.106405121973797</v>
+        <v>0.8371511531259701</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8394,7 +8402,7 @@
         <v>46259</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07244642090020841</v>
+        <v>0.07119734593404584</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8422,22 +8430,22 @@
         <v>21.68783215290538</v>
       </c>
       <c r="K72" t="n">
-        <v>2.994519673353646</v>
+        <v>1.218753878751722</v>
       </c>
       <c r="L72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M72" t="n">
-        <v>52.94117647058823</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N72" t="n">
-        <v>14.012342122491</v>
+        <v>15.629536440011</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>1.947171881578491</v>
+        <v>3.735716926309696</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8464,7 +8472,7 @@
         <v>36.68527402492516</v>
       </c>
       <c r="Y72" t="n">
-        <v>19.34275888009441</v>
+        <v>20.73339956973437</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8509,7 +8517,7 @@
         <v>46259</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07078098761199166</v>
+        <v>0.07140552509507293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8526,11 +8534,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8541,22 +8545,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>7.586422998506892</v>
+        <v>8.535713988928473</v>
       </c>
       <c r="L73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M73" t="n">
-        <v>85.71428571428571</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N73" t="n">
-        <v>10.78728381292863</v>
+        <v>10.41015246766233</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>2.243384373441448</v>
+        <v>1.349128279766876</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8583,22 +8587,22 @@
         <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.769579235547751</v>
+        <v>5.946958722677509</v>
       </c>
       <c r="Z73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA73" t="n">
-        <v>50</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AB73" t="n">
-        <v>13.29567252782323</v>
+        <v>13.22595385437325</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>3.464985718142299</v>
+        <v>4.309314427559863</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8632,7 +8636,7 @@
         <v>46259</v>
       </c>
       <c r="C74" t="n">
-        <v>5.594820547423735</v>
+        <v>5.54277570512212</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8692,22 +8696,22 @@
         <v>33.81594625096176</v>
       </c>
       <c r="Y74" t="n">
-        <v>4.609108013469765</v>
+        <v>5.496465148228181</v>
       </c>
       <c r="Z74" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AA74" t="n">
-        <v>48</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB74" t="n">
-        <v>19.63294624302093</v>
+        <v>18.0541574746302</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>5.651369721221878</v>
+        <v>4.765467089496267</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8741,7 +8745,7 @@
         <v>46259</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1253239798459329</v>
+        <v>0.1246994373665468</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8769,7 +8773,7 @@
         <v>23.35547482758762</v>
       </c>
       <c r="K75" t="n">
-        <v>1.423719664077616</v>
+        <v>0.9182823054377121</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
@@ -8778,13 +8782,13 @@
         <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>14.10454760014903</v>
+        <v>18.24441559719496</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.512041513641329</v>
+        <v>5.03547779299498</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8850,7 +8854,7 @@
         <v>46259</v>
       </c>
       <c r="C76" t="n">
-        <v>1.955845110200027</v>
+        <v>1.942313578191022</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8910,22 +8914,22 @@
         <v>14.64967258969352</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.571503455139711</v>
+        <v>2.252481894919534</v>
       </c>
       <c r="Z76" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA76" t="n">
-        <v>36.73469387755102</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.7293359413496</v>
+        <v>11.293656019294</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.467269774615999</v>
+        <v>1.787787699327414</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -8959,7 +8963,7 @@
         <v>46259</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5425154251185401</v>
+        <v>0.537935493152195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8987,16 +8991,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>11.73432649703223</v>
+        <v>10.79106186349674</v>
       </c>
       <c r="L77" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M77" t="n">
-        <v>61.53846153846154</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N77" t="n">
-        <v>17.05136670624185</v>
+        <v>16.90273640953321</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
@@ -9029,22 +9033,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>3.91052288632181</v>
+        <v>4.721713218405288</v>
       </c>
       <c r="Z77" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AA77" t="n">
-        <v>44.23076923076923</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.53545727026889</v>
+        <v>11.15240524749853</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>6.337298626855947</v>
+        <v>5.539863236304898</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9078,7 +9082,7 @@
         <v>46259</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0482976121986442</v>
+        <v>0.0480894330376171</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9106,22 +9110,22 @@
         <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>3.3760804195067</v>
+        <v>2.930494298116493</v>
       </c>
       <c r="L78" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M78" t="n">
-        <v>63.04347826086956</v>
+        <v>62.5</v>
       </c>
       <c r="N78" t="n">
-        <v>17.99693567127776</v>
+        <v>18.54425621787096</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.6035434676584739</v>
+        <v>1.039056218641976</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9187,7 +9191,7 @@
         <v>46259</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8289702417265815</v>
+        <v>0.8293866100412455</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9215,22 +9219,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>4.556112926230038</v>
+        <v>4.608628505602619</v>
       </c>
       <c r="L79" t="n">
         <v>30</v>
       </c>
       <c r="M79" t="n">
-        <v>56.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="N79" t="n">
-        <v>11.87481780639837</v>
+        <v>12.11724597546695</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0.4245443535981108</v>
+        <v>0.3741292663792306</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9296,7 +9300,7 @@
         <v>46259</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1290712049526</v>
+        <v>0.1294875632746542</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9324,7 +9328,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.674437976094993</v>
+        <v>6.01532292945004</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9335,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.093290777551628</v>
+        <v>3.758585985916074</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9362,22 +9366,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.891375155715128</v>
+        <v>5.587799240813085</v>
       </c>
       <c r="Z80" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA80" t="n">
-        <v>32.43243243243244</v>
+        <v>35</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.5451345579825</v>
+        <v>11.51348611190969</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.240628686025181</v>
+        <v>2.554967196813474</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9520,11 +9524,11 @@
         <v>46259</v>
       </c>
       <c r="C82" t="n">
-        <v>5.428277052058564</v>
+        <v>5.339800820145816</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9534,7 +9538,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9580,22 +9584,22 @@
         <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.904999137148989</v>
+        <v>4.487563868374744</v>
       </c>
       <c r="Z82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA82" t="n">
-        <v>45.45454545454545</v>
+        <v>30</v>
       </c>
       <c r="AB82" t="n">
-        <v>8.544375716600737</v>
+        <v>7.560260277872317</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.127762349369288</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>8</v>
@@ -9629,7 +9633,7 @@
         <v>46259</v>
       </c>
       <c r="C83" t="n">
-        <v>5.782181979709554</v>
+        <v>5.855044758931816</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9689,22 +9693,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>3.886385791958191</v>
+        <v>2.67523313767144</v>
       </c>
       <c r="Z83" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA83" t="n">
-        <v>46</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.49448922988003</v>
+        <v>11.98905293309322</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.199078897883089</v>
+        <v>3.416157027153877</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9738,7 +9742,7 @@
         <v>46259</v>
       </c>
       <c r="C84" t="n">
-        <v>2.138002058255684</v>
+        <v>2.146329264667207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9766,22 +9770,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>2.351613772456873</v>
+        <v>2.750258390755822</v>
       </c>
       <c r="L84" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="M84" t="n">
-        <v>49.18032786885246</v>
+        <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>10.92194658681683</v>
+        <v>10.44668109268372</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>2.587537343017265</v>
+        <v>2.189524040599955</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9847,7 +9851,7 @@
         <v>46259</v>
       </c>
       <c r="C85" t="n">
-        <v>6.25579004465426</v>
+        <v>6.313039371186038</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9875,22 +9879,22 @@
         <v>12.61214035274981</v>
       </c>
       <c r="K85" t="n">
-        <v>1.116664134101075</v>
+        <v>2.04202462118519</v>
       </c>
       <c r="L85" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M85" t="n">
-        <v>58.8235294117647</v>
+        <v>56.92307692307692</v>
       </c>
       <c r="N85" t="n">
-        <v>14.0527399580849</v>
+        <v>12.98174554119793</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.807320954309026</v>
+        <v>5.838746732959144</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9956,21 +9960,21 @@
         <v>46259</v>
       </c>
       <c r="C86" t="n">
-        <v>4.592437011684024</v>
+        <v>4.463365548797185</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -9984,22 +9988,22 @@
         <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>7.662280462371474</v>
+        <v>4.63640814193309</v>
       </c>
       <c r="L86" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M86" t="n">
-        <v>69.23076923076923</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N86" t="n">
-        <v>13.18969080957488</v>
+        <v>16.62126646767561</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.303171508159262</v>
       </c>
       <c r="Q86" t="n">
         <v>54</v>
@@ -10026,10 +10030,10 @@
         <v>71.56995669069586</v>
       </c>
       <c r="Y86" t="n">
-        <v>10.47934524881954</v>
+        <v>12.99534314665145</v>
       </c>
       <c r="Z86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
@@ -10071,7 +10075,7 @@
         <v>46259</v>
       </c>
       <c r="C87" t="n">
-        <v>5.756159558558745</v>
+        <v>5.678092295106321</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10085,7 +10089,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -10099,16 +10103,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>6.746078540122258</v>
+        <v>5.29834691435207</v>
       </c>
       <c r="L87" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M87" t="n">
-        <v>66.66666666666667</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N87" t="n">
-        <v>9.337848288486441</v>
+        <v>11.24467722556862</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10141,22 +10145,22 @@
         <v>10.60669620884278</v>
       </c>
       <c r="Y87" t="n">
-        <v>3.490401396160558</v>
+        <v>4.799301919720778</v>
       </c>
       <c r="Z87" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="AA87" t="n">
-        <v>43.58974358974359</v>
+        <v>40.625</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.95288012215483</v>
+        <v>11.6941012351613</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.5280289330922283</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10190,7 +10194,7 @@
         <v>46259</v>
       </c>
       <c r="C88" t="n">
-        <v>1.16164086435044</v>
+        <v>1.12937307794507</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10250,22 +10254,22 @@
         <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.872065270970081</v>
+        <v>5.570062171745038</v>
       </c>
       <c r="Z88" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA88" t="n">
-        <v>69.23076923076923</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB88" t="n">
-        <v>15.83781769132357</v>
+        <v>14.62604774501775</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>3.220427509095425</v>
+        <v>0.4552982223041568</v>
       </c>
       <c r="AE88" t="n">
         <v>32</v>
@@ -10299,7 +10303,7 @@
         <v>46259</v>
       </c>
       <c r="C89" t="n">
-        <v>2.273318648239885</v>
+        <v>2.204619551747903</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10359,22 +10363,22 @@
         <v>27.21456043612742</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.933336044444457</v>
+        <v>5.866665306666663</v>
       </c>
       <c r="Z89" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AA89" t="n">
-        <v>43.33333333333334</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.73854354552278</v>
+        <v>13.38450532899653</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>7.280217190518867</v>
+        <v>4.390936225513387</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10408,11 +10412,11 @@
         <v>46259</v>
       </c>
       <c r="C90" t="n">
-        <v>3.066482171905931</v>
+        <v>2.929083661240249</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10422,7 +10426,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10468,22 +10472,22 @@
         <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.865425007467747</v>
+        <v>6.262497513649334</v>
       </c>
       <c r="Z90" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="AA90" t="n">
-        <v>42.85714285714285</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AB90" t="n">
-        <v>12.43479427582735</v>
+        <v>12.953476211778</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
       </c>
       <c r="AD90" t="n">
-        <v>1.156141953657608</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="n">
         <v>23</v>
@@ -10517,7 +10521,7 @@
         <v>46259</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2319118243741001</v>
+        <v>0.2308709235726598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10545,16 +10549,16 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>3.590608521733563</v>
+        <v>3.125657897835965</v>
       </c>
       <c r="L91" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M91" t="n">
-        <v>64.40677966101696</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N91" t="n">
-        <v>12.91518156554474</v>
+        <v>13.28140913362387</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10626,7 +10630,7 @@
         <v>46259</v>
       </c>
       <c r="C92" t="n">
-        <v>1.110636902865045</v>
+        <v>1.112718744230185</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10654,22 +10658,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>5.408208926572788</v>
+        <v>5.605792105199892</v>
       </c>
       <c r="L92" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M92" t="n">
-        <v>50</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="N92" t="n">
-        <v>13.49423494098676</v>
+        <v>13.43574145268475</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.45881331237936</v>
+        <v>2.267117974376931</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10696,16 +10700,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>8.073144082815753</v>
+        <v>7.900831123718167</v>
       </c>
       <c r="Z92" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA92" t="n">
-        <v>48.38709677419355</v>
+        <v>50</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.39327922069919</v>
+        <v>11.25604859314078</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10745,7 +10749,7 @@
         <v>46259</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0422604113243742</v>
+        <v>0.04205223216334711</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10773,22 +10777,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>4.497739860495331</v>
+        <v>3.982973176224136</v>
       </c>
       <c r="L93" t="n">
         <v>52</v>
       </c>
       <c r="M93" t="n">
-        <v>63.46153846153846</v>
+        <v>59.61538461538461</v>
       </c>
       <c r="N93" t="n">
-        <v>19.11345824251768</v>
+        <v>18.233323415934</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>1.437600604099365</v>
+        <v>1.939766446529223</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10854,7 +10858,7 @@
         <v>46259</v>
       </c>
       <c r="C94" t="n">
-        <v>8.353197189409391</v>
+        <v>7.999292261758401</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10914,22 +10918,22 @@
         <v>48.9849654478532</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.533742331288346</v>
+        <v>5.705521472392638</v>
       </c>
       <c r="Z94" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA94" t="n">
-        <v>57.14285714285715</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB94" t="n">
-        <v>9.960569015483692</v>
+        <v>7.911842375757001</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.535825545171345</v>
+        <v>0.3122966818477568</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10963,28 +10967,24 @@
         <v>46259</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1442682993210307</v>
+        <v>0.1398965317349774</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>5</v>
       </c>
@@ -10995,22 +10995,22 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>8.145055394013001</v>
+        <v>4.867931798680258</v>
       </c>
       <c r="L95" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M95" t="n">
-        <v>100</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N95" t="n">
-        <v>18.17529258831296</v>
+        <v>19.44007145253257</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.079518001263757</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11037,22 +11037,22 @@
         <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>3.464962958619899</v>
+        <v>6.390267740350508</v>
       </c>
       <c r="Z95" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA95" t="n">
-        <v>44.82758620689656</v>
+        <v>44</v>
       </c>
       <c r="AB95" t="n">
-        <v>10.24624973377114</v>
+        <v>11.55158951422049</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.626027936668685</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -11086,7 +11086,7 @@
         <v>46259</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1276139556135358</v>
+        <v>0.1274057716643832</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11111,25 +11111,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>13.98710152278624</v>
+        <v>14.68867757321659</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>0.6578942520775621</v>
       </c>
       <c r="L96" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M96" t="n">
-        <v>53.44827586206897</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N96" t="n">
-        <v>13.13871883252217</v>
+        <v>12.75896352486635</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>10.00000000000001</v>
+        <v>9.281046277927295</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11195,7 +11195,7 @@
         <v>46259</v>
       </c>
       <c r="C97" t="n">
-        <v>1.906922990079772</v>
+        <v>1.893391299438088</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11223,16 +11223,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>6.692002437595312</v>
+        <v>5.934906750754299</v>
       </c>
       <c r="L97" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M97" t="n">
         <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>14.76284884323322</v>
+        <v>14.76656774783397</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11265,16 +11265,16 @@
         <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>9.184025162236598</v>
+        <v>9.828463182660375</v>
       </c>
       <c r="Z97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA97" t="n">
-        <v>30.76923076923077</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB97" t="n">
-        <v>10.41431718008398</v>
+        <v>10.42692936952895</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11314,7 +11314,7 @@
         <v>46259</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6545159478186312</v>
+        <v>0.6586795114703123</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11342,22 +11342,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>9.292028091904614</v>
+        <v>9.987266026287323</v>
       </c>
       <c r="L98" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M98" t="n">
-        <v>65.21739130434783</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N98" t="n">
-        <v>12.22938373902756</v>
+        <v>13.17398737151013</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>0.6477800077971496</v>
+        <v>0.01157768001038839</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11381,25 +11381,25 @@
         <v>72.05882352941177</v>
       </c>
       <c r="X98" t="n">
-        <v>10.54345902266514</v>
+        <v>10.6825105654681</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.132071442150129</v>
+        <v>0.6281430874930605</v>
       </c>
       <c r="Z98" t="n">
         <v>51</v>
       </c>
       <c r="AA98" t="n">
-        <v>43.13725490196079</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.17770303992751</v>
+        <v>10.98217636308735</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>6.946568678063569</v>
+        <v>7.418455427473358</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11433,7 +11433,7 @@
         <v>46259</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4617418473534989</v>
+        <v>0.4600764138571027</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11461,16 +11461,16 @@
         <v>21.64053449738032</v>
       </c>
       <c r="K99" t="n">
-        <v>4.829186779800199</v>
+        <v>4.451083646926945</v>
       </c>
       <c r="L99" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M99" t="n">
-        <v>57.14285714285715</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N99" t="n">
-        <v>12.14580322778225</v>
+        <v>12.84057962852784</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11542,7 +11542,7 @@
         <v>46259</v>
       </c>
       <c r="C100" t="n">
-        <v>337.9721310609448</v>
+        <v>337.6046863421847</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11570,16 +11570,16 @@
         <v>12.69669682287478</v>
       </c>
       <c r="K100" t="n">
-        <v>10.2733755743974</v>
+        <v>10.15348589785079</v>
       </c>
       <c r="L100" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M100" t="n">
-        <v>58.8235294117647</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N100" t="n">
-        <v>8.779532552360974</v>
+        <v>10.18641432150756</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11612,7 +11612,7 @@
         <v>11.67288888132132</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.253225667342794</v>
+        <v>1.360583574662644</v>
       </c>
       <c r="Z100" t="n">
         <v>57</v>
@@ -11621,13 +11621,13 @@
         <v>35.08771929824562</v>
       </c>
       <c r="AB100" t="n">
-        <v>11.45203400959957</v>
+        <v>11.42378967284656</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>6.832399719639182</v>
+        <v>6.730997268584704</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11661,7 +11661,7 @@
         <v>46259</v>
       </c>
       <c r="C101" t="n">
-        <v>348.4491644165907</v>
+        <v>348.2615996842437</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>11.75561335839466</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.263963032082616</v>
+        <v>1.317111095668599</v>
       </c>
       <c r="Z101" t="n">
         <v>41</v>
@@ -11736,7 +11736,7 @@
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.796665040806003</v>
+        <v>4.745390975401276</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>46259</v>
       </c>
       <c r="C102" t="n">
-        <v>421.6889434652756</v>
+        <v>416.1351488910934</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11830,22 +11830,22 @@
         <v>11.13903673030769</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.096935968105639</v>
+        <v>2.399524781263762</v>
       </c>
       <c r="Z102" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AA102" t="n">
-        <v>37.83783783783784</v>
+        <v>32.35294117647059</v>
       </c>
       <c r="AB102" t="n">
-        <v>11.7842686229323</v>
+        <v>14.53902862438785</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>3.946352997350722</v>
+        <v>2.664408357549708</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11879,7 +11879,7 @@
         <v>46259</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7606874342329235</v>
+        <v>0.7598546976035957</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11936,25 +11936,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>17.69684631574038</v>
+        <v>18.08106682362138</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.5984695594512757</v>
+        <v>1.030371634964811</v>
       </c>
       <c r="Z103" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA103" t="n">
-        <v>36.95652173913044</v>
+        <v>38.29787234042553</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.97992118648431</v>
+        <v>12.65910342047405</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.446093040766122</v>
+        <v>7.042189083835614</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11988,7 +11988,7 @@
         <v>46259</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04746489555453581</v>
+        <v>0.04725671639350872</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12016,22 +12016,22 @@
         <v>18.611805593619</v>
       </c>
       <c r="K104" t="n">
-        <v>1.975238837281168</v>
+        <v>1.527979459194229</v>
       </c>
       <c r="L104" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M104" t="n">
-        <v>45.28301886792453</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N104" t="n">
-        <v>15.97840695207225</v>
+        <v>15.49298906260249</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>1.985541966662785</v>
+        <v>2.434817036617298</v>
       </c>
       <c r="Q104" t="n">
         <v>35</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -670,7 +670,7 @@
         <v>46259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.393667184046734</v>
+        <v>0.3920017505503378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>17.69759076271513</v>
+        <v>18.04725545643595</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4248535865102765</v>
+        <v>0.4266662399999843</v>
       </c>
       <c r="L2" t="n">
         <v>30</v>
       </c>
       <c r="M2" t="n">
-        <v>56.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>11.49230194429774</v>
+        <v>11.16500173156578</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>9.534638161300668</v>
+        <v>9.532661113256147</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -779,7 +779,7 @@
         <v>46259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6436906112518235</v>
+        <v>0.6424415460700912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7018432732212476</v>
+        <v>0.5064339197677015</v>
       </c>
       <c r="L3" t="n">
         <v>53</v>
@@ -816,13 +816,13 @@
         <v>60.37735849056604</v>
       </c>
       <c r="N3" t="n">
-        <v>12.41245197393265</v>
+        <v>12.66709532431191</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>9.233353059438333</v>
+        <v>9.445729701056592</v>
       </c>
       <c r="Q3" t="n">
         <v>37</v>
@@ -997,7 +997,7 @@
         <v>46259</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2314954562676156</v>
+        <v>0.2302463910858833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>17.43715476141968</v>
+        <v>17.80973219631822</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3610105621733695</v>
+        <v>0.2719917564313334</v>
       </c>
       <c r="L5" t="n">
         <v>39</v>
@@ -1034,13 +1034,13 @@
         <v>74.35897435897436</v>
       </c>
       <c r="N5" t="n">
-        <v>12.93324869837158</v>
+        <v>13.33766417053529</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.629496677090337</v>
+        <v>2.720608412960646</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1106,7 +1106,7 @@
         <v>46259</v>
       </c>
       <c r="C6" t="n">
-        <v>1.694580097192065</v>
+        <v>1.697702819373426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>3.54796096359713</v>
+        <v>3.738776089463158</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1172,16 +1172,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.527709632567293</v>
+        <v>7.357304425536859</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA6" t="n">
-        <v>52.77777777777778</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.40216735484644</v>
+        <v>12.15406463341447</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1221,7 +1221,7 @@
         <v>46259</v>
       </c>
       <c r="C7" t="n">
-        <v>2.183801614827257</v>
+        <v>2.187965138508499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,22 +1249,22 @@
         <v>12.3532304777189</v>
       </c>
       <c r="K7" t="n">
-        <v>2.641883229527853</v>
+        <v>2.837574957481448</v>
       </c>
       <c r="L7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M7" t="n">
-        <v>57.97101449275362</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N7" t="n">
-        <v>12.83211617703734</v>
+        <v>13.04964433203072</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>5.220205048742455</v>
+        <v>5.019979365181437</v>
       </c>
       <c r="Q7" t="n">
         <v>49</v>
@@ -1291,13 +1291,13 @@
         <v>17.31307710509156</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.03770517248683</v>
+        <v>9.866187694713169</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>52.94117647058823</v>
+        <v>56.25</v>
       </c>
       <c r="AB7" t="n">
         <v>12.36271703915551</v>
@@ -1340,7 +1340,7 @@
         <v>46259</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3892954362377208</v>
+        <v>0.3870054504775082</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.220470370066721</v>
+        <v>5.77800008402839</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
@@ -1411,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.932626528941373</v>
+        <v>2.358260191837591</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1445,7 +1445,7 @@
         <v>46259</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5878985338509305</v>
+        <v>0.5787386305723394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,16 +1505,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.470153793021493</v>
+        <v>6.943000208412564</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>50</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.86767921021994</v>
+        <v>10.11294478239028</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1554,7 +1554,7 @@
         <v>46259</v>
       </c>
       <c r="C10" t="n">
-        <v>1.926700125500537</v>
+        <v>1.922536442770257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10.66625626204533</v>
+        <v>10.84633778363752</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1229681308236641</v>
+        <v>0.1083994254742704</v>
       </c>
       <c r="L10" t="n">
         <v>41</v>
@@ -1591,13 +1591,13 @@
         <v>43.90243902439025</v>
       </c>
       <c r="N10" t="n">
-        <v>10.16882093237464</v>
+        <v>10.11695680133792</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.869813868779072</v>
+        <v>5.885221028742693</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1663,7 +1663,7 @@
         <v>46259</v>
       </c>
       <c r="C11" t="n">
-        <v>8.441673421322138</v>
+        <v>8.478104810933269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>23.11730782489165</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.756511205330114</v>
+        <v>1.332525741974566</v>
       </c>
       <c r="Z11" t="n">
         <v>38</v>
@@ -1732,13 +1732,13 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.28509325710722</v>
+        <v>12.53590431090026</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.247842170160284</v>
+        <v>0.6764886433394679</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1772,7 +1772,7 @@
         <v>46259</v>
       </c>
       <c r="C12" t="n">
-        <v>7.088507521480119</v>
+        <v>7.078098553019795</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>7.89868064464252</v>
+        <v>7.740239116529968</v>
       </c>
       <c r="L12" t="n">
         <v>12</v>
@@ -1813,7 +1813,7 @@
         <v>75</v>
       </c>
       <c r="N12" t="n">
-        <v>18.03133326988203</v>
+        <v>18.35196818008896</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1846,7 +1846,7 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.098317818834807</v>
+        <v>4.23914260911552</v>
       </c>
       <c r="Z12" t="n">
         <v>11</v>
@@ -1855,7 +1855,7 @@
         <v>27.27272727272727</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.759433103302454</v>
+        <v>10.40124120252835</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1895,7 +1895,7 @@
         <v>46259</v>
       </c>
       <c r="C13" t="n">
-        <v>0.223168289410173</v>
+        <v>0.2223355727660646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>5.652321761014245</v>
+        <v>5.25809708397067</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1959,22 +1959,22 @@
         <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.400668482299423</v>
+        <v>9.738725342883326</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.12278197065909</v>
+        <v>13.48475647319801</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.661518697390695</v>
+        <v>0.2894648431558289</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>46259</v>
       </c>
       <c r="C14" t="n">
-        <v>8.597807948226986</v>
+        <v>8.665466243219088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,22 +2058,22 @@
         <v>12.90895707120068</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.793675596943411</v>
+        <v>1.020865538081583</v>
       </c>
       <c r="Z14" t="n">
         <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>46.80851063829788</v>
+        <v>48.93617021276596</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.64386317536204</v>
+        <v>12.08317190342756</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.2100927860916535</v>
+        <v>0.9892332027768291</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2107,7 +2107,7 @@
         <v>46259</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0097325197861</v>
+        <v>14.90564283518286</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,22 +2167,22 @@
         <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.069124423963123</v>
+        <v>5.727452271231071</v>
       </c>
       <c r="Z15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.18153610059048</v>
+        <v>9.567483531887934</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.194174757281567</v>
+        <v>4.532122905027935</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2216,7 +2216,7 @@
         <v>46259</v>
       </c>
       <c r="C16" t="n">
-        <v>35.97339499887708</v>
+        <v>35.93175912503578</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>3.308320955610489</v>
+        <v>3.188751139689638</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>63.76811594202898</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="N16" t="n">
-        <v>18.14434792096311</v>
+        <v>18.36942990324292</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.477386315536782</v>
+        <v>6.600766832704252</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2286,7 +2286,7 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.10750125047431</v>
+        <v>11.21038608698997</v>
       </c>
       <c r="Z16" t="n">
         <v>29</v>
@@ -2335,7 +2335,7 @@
         <v>46259</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6849101565407119</v>
+        <v>0.6878246550106608</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,25 +2360,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>16.15881909709504</v>
+        <v>16.87409721257028</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2437594172932656</v>
+        <v>1.53657033147987</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>68.51851851851852</v>
+        <v>67.24137931034483</v>
       </c>
       <c r="N17" t="n">
-        <v>15.68280410259236</v>
+        <v>16.30300633150743</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.737379990328552</v>
+        <v>6.365617478923502</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2444,7 +2444,7 @@
         <v>46259</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09701158292752196</v>
+        <v>0.09659522460546775</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,25 +2469,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>20.88000978125635</v>
+        <v>21.20940117548115</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4458767318659573</v>
+        <v>0.4329000103071357</v>
       </c>
       <c r="L18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M18" t="n">
-        <v>72.22222222222223</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N18" t="n">
-        <v>15.88557305699444</v>
+        <v>15.8391443743535</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>9.511712754161316</v>
+        <v>9.52586252981944</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2553,7 +2553,7 @@
         <v>46259</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02560606282875388</v>
+        <v>0.02518970450669969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,22 +2581,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>3.899207707265506</v>
+        <v>2.209791412653428</v>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>60.71428571428572</v>
+        <v>55</v>
       </c>
       <c r="N19" t="n">
-        <v>15.85846737675938</v>
+        <v>18.14575358321196</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>5.871837165422278</v>
+        <v>7.62178307936765</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2662,7 +2662,7 @@
         <v>46259</v>
       </c>
       <c r="C20" t="n">
-        <v>1.622758119469684</v>
+        <v>1.611308349509479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,25 +2687,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>18.29524817848574</v>
+        <v>18.71559577638767</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2572308038585103</v>
+        <v>0.06464519843447647</v>
       </c>
       <c r="L20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M20" t="n">
-        <v>63.33333333333334</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="N20" t="n">
-        <v>12.76603255396804</v>
+        <v>11.80397784294498</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.738297758842955</v>
+        <v>1.934104495876232</v>
       </c>
       <c r="Q20" t="n">
         <v>49</v>
@@ -2771,7 +2771,7 @@
         <v>46259</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9630377269749711</v>
+        <v>0.9622050698701623</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,22 +2799,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>3.663755317559714</v>
+        <v>3.574126053867777</v>
       </c>
       <c r="L21" t="n">
         <v>53</v>
       </c>
       <c r="M21" t="n">
-        <v>52.83018867924528</v>
+        <v>54.71698113207547</v>
       </c>
       <c r="N21" t="n">
-        <v>14.88081334089142</v>
+        <v>16.30703483238944</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.182990158090272</v>
+        <v>4.273146310527776</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2880,7 +2880,7 @@
         <v>46259</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3389160274325008</v>
+        <v>0.337666922488509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2940,16 +2940,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.633029393576773</v>
+        <v>7.973456019369807</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>58.33333333333334</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.21192621751102</v>
+        <v>10.89827904879843</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
@@ -2981,7 +2981,7 @@
         <v>46259</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7519438592985576</v>
+        <v>0.7486129925139446</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,22 +3009,22 @@
         <v>27.73484467032905</v>
       </c>
       <c r="K23" t="n">
-        <v>2.439026236459574</v>
+        <v>1.985254660670099</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>25.2492217942063</v>
+        <v>25.26583029055753</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>7.380950445670442</v>
+        <v>7.858729544772847</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -3051,7 +3051,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>25.97227857202011</v>
+        <v>26.30019730610627</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>46259</v>
       </c>
       <c r="C25" t="n">
-        <v>3.491167958097704</v>
+        <v>3.464104576606155</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,25 +3240,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>16.09461141165198</v>
+        <v>16.74581894046563</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1194011641791226</v>
+        <v>0.1203351105115491</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>58.18181818181818</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N25" t="n">
-        <v>17.76371357663987</v>
+        <v>17.5338212425245</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.871200530752298</v>
+        <v>7.870194282501131</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3324,7 +3324,7 @@
         <v>46259</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4405075421181885</v>
+        <v>0.4396748452511202</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46259</v>
       </c>
       <c r="C27" t="n">
-        <v>47.81880110672491</v>
+        <v>47.54816792675651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>50.20031327035493</v>
       </c>
       <c r="K27" t="n">
-        <v>45.06723562736727</v>
+        <v>44.24621949190546</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>47.34081877172307</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.543077582511798</v>
+        <v>2.100300042863279</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="AB27" t="n">
-        <v>19.54791007974723</v>
+        <v>12.91986477688082</v>
       </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.526774053112748</v>
+        <v>3.983362521891409</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>46259</v>
       </c>
       <c r="C28" t="n">
-        <v>1.61443107169084</v>
+        <v>1.615471873190722</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,22 +3578,22 @@
         <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.514141952631899</v>
+        <v>2.451294161201167</v>
       </c>
       <c r="Z28" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA28" t="n">
-        <v>50</v>
+        <v>51.28205128205128</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.35666482995179</v>
+        <v>11.1655074559226</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.575757671101731</v>
+        <v>3.637881003427301</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3627,7 +3627,7 @@
         <v>46259</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3805519012737937</v>
+        <v>0.4015780223517721</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3644,11 +3644,7 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3659,16 +3655,16 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>5.272976738367996</v>
+        <v>11.08948257562987</v>
       </c>
       <c r="L29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>87.5</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N29" t="n">
-        <v>13.37665263975417</v>
+        <v>21.19010258095587</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3701,7 +3697,7 @@
         <v>48.55798797437896</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.92764779655356</v>
+        <v>12.3377631321607</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3746,7 +3742,7 @@
         <v>46259</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4184405400158098</v>
+        <v>0.4180241717011459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,7 +3774,7 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>14.3066090509548</v>
+        <v>14.19286851767927</v>
       </c>
       <c r="L30" t="n">
         <v>3</v>
@@ -3820,22 +3816,22 @@
         <v>18.28742967351311</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.365379257581158</v>
+        <v>3.461535318786868</v>
       </c>
       <c r="Z30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA30" t="n">
-        <v>45.45454545454545</v>
+        <v>43.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.64473726428202</v>
+        <v>14.82654903909837</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.865676805524523</v>
+        <v>6.772911401485704</v>
       </c>
       <c r="AE30" t="n">
         <v>50</v>
@@ -3869,7 +3865,7 @@
         <v>46259</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1875696164431501</v>
+        <v>0.190900483227763</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3883,12 +3879,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3901,22 +3897,22 @@
         <v>18.68860738081651</v>
       </c>
       <c r="K31" t="n">
-        <v>7.717993880106966</v>
+        <v>9.630853194553168</v>
       </c>
       <c r="L31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M31" t="n">
-        <v>75</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N31" t="n">
-        <v>15.80297145497943</v>
+        <v>14.72026057876797</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>2.118500389482714</v>
+        <v>0.3367179901370809</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3939,17 +3935,27 @@
       <c r="W31" t="n">
         <v>87.5</v>
       </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
+      <c r="X31" t="n">
+        <v>10.34816965405449</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.6500483530901602</v>
+      </c>
       <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.15303860280935</v>
+      </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
-      <c r="AD31" t="inlineStr"/>
+      <c r="AD31" t="n">
+        <v>9.411128532945446</v>
+      </c>
       <c r="AE31" t="n">
         <v>10</v>
       </c>
@@ -3982,7 +3988,7 @@
         <v>46259</v>
       </c>
       <c r="C32" t="n">
-        <v>2.279564092810787</v>
+        <v>2.273318648239885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4010,16 +4016,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>4.596361575008845</v>
+        <v>4.309793287416075</v>
       </c>
       <c r="L32" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>53.33333333333334</v>
+        <v>53.19148936170212</v>
       </c>
       <c r="N32" t="n">
-        <v>10.76786269654213</v>
+        <v>10.04046136466732</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4052,22 +4058,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.335330687681241</v>
+        <v>7.589209075087067</v>
       </c>
       <c r="Z32" t="n">
         <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>35.29411764705883</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB32" t="n">
-        <v>14.63702839182677</v>
+        <v>13.40978584043263</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.7172845025524732</v>
+        <v>0.4445270090229103</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4101,7 +4107,7 @@
         <v>46259</v>
       </c>
       <c r="C33" t="n">
-        <v>1.733093248643818</v>
+        <v>1.743502217104141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4129,16 +4135,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>5.759092951331213</v>
+        <v>6.394282698786657</v>
       </c>
       <c r="L33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M33" t="n">
-        <v>62.06896551724138</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N33" t="n">
-        <v>11.39383009772743</v>
+        <v>10.64617202775737</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4210,7 +4216,7 @@
         <v>46259</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7914979712992293</v>
+        <v>0.7935797331398504</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,16 +4244,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>4.288585482967844</v>
+        <v>4.562880560837002</v>
       </c>
       <c r="L34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M34" t="n">
-        <v>73.91304347826087</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N34" t="n">
-        <v>10.23547984669301</v>
+        <v>10.11946514086019</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4319,7 +4325,7 @@
         <v>46259</v>
       </c>
       <c r="C35" t="n">
-        <v>1.983949452032315</v>
+        <v>1.980826729850954</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4351,7 +4357,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>11.84564779866479</v>
+        <v>11.66960355272302</v>
       </c>
       <c r="L35" t="n">
         <v>9</v>
@@ -4393,16 +4399,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>4.528241916751141</v>
+        <v>4.678513777939298</v>
       </c>
       <c r="Z35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>37.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB35" t="n">
-        <v>14.89562390716056</v>
+        <v>12.40592897629132</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4442,7 +4448,7 @@
         <v>46259</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08223085187745036</v>
+        <v>0.08160631439436906</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4459,11 +4465,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>5</v>
       </c>
@@ -4474,16 +4476,16 @@
         <v>14.21000360644873</v>
       </c>
       <c r="K36" t="n">
-        <v>5.339257920748164</v>
+        <v>4.53921373405386</v>
       </c>
       <c r="L36" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M36" t="n">
-        <v>78.26086956521739</v>
+        <v>64</v>
       </c>
       <c r="N36" t="n">
-        <v>17.97175001920986</v>
+        <v>20.37787463574827</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4555,7 +4557,7 @@
         <v>46259</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06516014485159648</v>
+        <v>0.06557650338183003</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4583,22 +4585,22 @@
         <v>14.02780799500539</v>
       </c>
       <c r="K37" t="n">
-        <v>6.069714378721769</v>
+        <v>6.747475769240485</v>
       </c>
       <c r="L37" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>59.52380952380953</v>
+        <v>55.26315789473684</v>
       </c>
       <c r="N37" t="n">
-        <v>21.97037154756377</v>
+        <v>18.8141351286606</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>1.819827301868804</v>
+        <v>1.173352551649232</v>
       </c>
       <c r="Q37" t="n">
         <v>37</v>
@@ -4625,16 +4627,16 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.412542576915458</v>
+        <v>4.808150201163408</v>
       </c>
       <c r="Z37" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AA37" t="n">
-        <v>56.60377358490566</v>
+        <v>54.3859649122807</v>
       </c>
       <c r="AB37" t="n">
-        <v>12.70203986642455</v>
+        <v>12.86768914035915</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
@@ -4674,7 +4676,7 @@
         <v>46259</v>
       </c>
       <c r="C38" t="n">
-        <v>1.64357605639033</v>
+        <v>1.633167087930007</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4702,22 +4704,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>3.738855504550442</v>
+        <v>3.081864627335795</v>
       </c>
       <c r="L38" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M38" t="n">
-        <v>50.9433962264151</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="N38" t="n">
-        <v>11.09903794367203</v>
+        <v>11.73894987460513</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>6.035486380679145</v>
+        <v>6.711302126397145</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4783,7 +4785,7 @@
         <v>46259</v>
       </c>
       <c r="C39" t="n">
-        <v>2.764622086556557</v>
+        <v>2.756294721304176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4843,22 +4845,22 @@
         <v>11.08431820998319</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.483679491652656</v>
+        <v>1.780422177816854</v>
       </c>
       <c r="Z39" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA39" t="n">
-        <v>39.34426229508197</v>
+        <v>38.70967741935484</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.15607792814228</v>
+        <v>12.08059302588321</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.58433738191093</v>
+        <v>4.296065932824799</v>
       </c>
       <c r="AE39" t="n">
         <v>44</v>
@@ -4892,11 +4894,11 @@
         <v>46259</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2558524439220275</v>
+        <v>0.247317092907253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4906,7 +4908,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4952,22 +4954,22 @@
         <v>43.91653617576685</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.908242965917018</v>
+        <v>6.147267046451721</v>
       </c>
       <c r="Z40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="n">
-        <v>57.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="AB40" t="n">
-        <v>18.41651882502994</v>
+        <v>11.63467188629951</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.154412586589305</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -5001,7 +5003,7 @@
         <v>46259</v>
       </c>
       <c r="C41" t="n">
-        <v>1.884023291318504</v>
+        <v>1.854878147778156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5029,10 +5031,10 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>24.50687997762919</v>
+        <v>22.58080459128436</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5067,22 +5069,22 @@
         <v>26.020221165252</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.20087171219796</v>
+        <v>2.729257687508335</v>
       </c>
       <c r="Z41" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="n">
-        <v>36.36363636363637</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="AB41" t="n">
-        <v>19.44397771139826</v>
+        <v>16.89080470537415</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.820996115027629</v>
+        <v>0.2783388982700252</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5116,7 +5118,7 @@
         <v>46259</v>
       </c>
       <c r="C42" t="n">
-        <v>3.730574232685138</v>
+        <v>3.676447787175579</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5174,22 +5176,18 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.538297248009925</v>
+        <v>4.937848301577031</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>7.843680062354141</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.69872350128794</v>
+        <v>5.325096905530014</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5221,7 +5219,7 @@
         <v>46259</v>
       </c>
       <c r="C43" t="n">
-        <v>6.64092187768622</v>
+        <v>6.656535330376705</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5249,22 +5247,22 @@
         <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>1.269841269841265</v>
+        <v>1.507936507936503</v>
       </c>
       <c r="L43" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M43" t="n">
-        <v>70.96774193548387</v>
+        <v>71.875</v>
       </c>
       <c r="N43" t="n">
-        <v>17.89917316071853</v>
+        <v>18.368861113349</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.69592476489029</v>
+        <v>2.45504300234558</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5291,7 +5289,7 @@
         <v>20.83229097494805</v>
       </c>
       <c r="Y43" t="n">
-        <v>14.28345296418754</v>
+        <v>14.08192503228517</v>
       </c>
       <c r="Z43" t="n">
         <v>2</v>
@@ -5336,7 +5334,7 @@
         <v>46259</v>
       </c>
       <c r="C44" t="n">
-        <v>4.634072885525317</v>
+        <v>4.625745520272935</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5368,7 +5366,7 @@
         <v>20.15821391009879</v>
       </c>
       <c r="K44" t="n">
-        <v>3.312655728165548</v>
+        <v>3.127004306469261</v>
       </c>
       <c r="L44" t="n">
         <v>14</v>
@@ -5383,7 +5381,7 @@
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.472918757823898</v>
+        <v>6.664593565721955</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5550,7 +5548,7 @@
         <v>46259</v>
       </c>
       <c r="C46" t="n">
-        <v>9.987405237680138</v>
+        <v>9.86770210038642</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5610,16 +5608,16 @@
         <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>5.000000000000004</v>
+        <v>6.138613861386144</v>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA46" t="n">
-        <v>47.05882352941177</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="AB46" t="n">
-        <v>15.95100982119853</v>
+        <v>14.23125963062444</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5659,7 +5657,7 @@
         <v>46259</v>
       </c>
       <c r="C47" t="n">
-        <v>0.725713293752677</v>
+        <v>0.7194679284981151</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5687,7 +5685,7 @@
         <v>20.24791594168004</v>
       </c>
       <c r="K47" t="n">
-        <v>7.758041580536856</v>
+        <v>6.830694190623854</v>
       </c>
       <c r="L47" t="n">
         <v>15</v>
@@ -5696,13 +5694,13 @@
         <v>53.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>14.90888708292778</v>
+        <v>12.92127445020113</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>2.080548594405873</v>
+        <v>2.966662187667701</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5768,7 +5766,7 @@
         <v>46259</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05933111814204871</v>
+        <v>0.05912293898102162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,22 +5794,22 @@
         <v>15.05707226133306</v>
       </c>
       <c r="K48" t="n">
-        <v>2.991295508888148</v>
+        <v>2.629922890883529</v>
       </c>
       <c r="L48" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M48" t="n">
-        <v>57.89473684210526</v>
+        <v>50.81967213114754</v>
       </c>
       <c r="N48" t="n">
-        <v>14.08651342994457</v>
+        <v>13.8759031246287</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.80514256712792</v>
+        <v>7.181216648630206</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5877,16 +5875,16 @@
         <v>46259</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2625141774912533</v>
+        <v>0.2600160273507488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5905,22 +5903,22 @@
         <v>16.44500858212767</v>
       </c>
       <c r="K49" t="n">
-        <v>5.632744097452314</v>
+        <v>4.627516657811581</v>
       </c>
       <c r="L49" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M49" t="n">
-        <v>65.51724137931035</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N49" t="n">
-        <v>19.51519067238355</v>
+        <v>17.90458776653778</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.3560089678957379</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5986,7 +5984,7 @@
         <v>46259</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6765829499210099</v>
+        <v>0.6699212165599634</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6011,25 +6009,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>15.82134875518189</v>
+        <v>15.88388393069994</v>
       </c>
       <c r="K50" t="n">
-        <v>1.17089638562069</v>
+        <v>0.2492269277668768</v>
       </c>
       <c r="L50" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>56.25</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N50" t="n">
-        <v>13.93148522800849</v>
+        <v>14.51295312933297</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.796361123060498</v>
+        <v>3.741448375393142</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6095,7 +6093,7 @@
         <v>46259</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1750788463799462</v>
+        <v>0.1740379455785058</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6123,22 +6121,22 @@
         <v>21.55982902963817</v>
       </c>
       <c r="K51" t="n">
-        <v>1.325297078095611</v>
+        <v>0.7228851641749134</v>
       </c>
       <c r="L51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M51" t="n">
-        <v>64.70588235294117</v>
+        <v>56.25</v>
       </c>
       <c r="N51" t="n">
-        <v>13.65413182000791</v>
+        <v>13.98141433611268</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>2.639718805702485</v>
+        <v>3.253595079691673</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6204,7 +6202,7 @@
         <v>46259</v>
       </c>
       <c r="C52" t="n">
-        <v>4.496674374859635</v>
+        <v>4.527901280240605</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6264,22 +6262,22 @@
         <v>17.40749557792611</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.761906042663955</v>
+        <v>4.100530390182444</v>
       </c>
       <c r="Z52" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AA52" t="n">
-        <v>56.52173913043478</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.01739931790417</v>
+        <v>12.14437304511339</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.399998700925932</v>
+        <v>4.066205606436791</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6313,7 +6311,7 @@
         <v>46259</v>
       </c>
       <c r="C53" t="n">
-        <v>1.438519409365227</v>
+        <v>1.415619710603959</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6345,7 +6343,7 @@
         <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>6.604185194464174</v>
+        <v>4.907159967171038</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
@@ -6354,13 +6352,13 @@
         <v>80</v>
       </c>
       <c r="N53" t="n">
-        <v>12.01629352258359</v>
+        <v>16.25373172741129</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>1.309343346126268</v>
+        <v>2.948168679618068</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6418,7 +6416,7 @@
         <v>46259</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07931633841858679</v>
+        <v>0.07910815925755969</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6447,7 +6445,7 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>43.47316972408662</v>
+        <v>43.62153396198496</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -6531,7 +6529,7 @@
         <v>46259</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9326435582233292</v>
+        <v>0.9309781644891926</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6591,16 +6589,16 @@
         <v>21.18657262526651</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.617104117506566</v>
+        <v>4.787426504602788</v>
       </c>
       <c r="Z55" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA55" t="n">
-        <v>40.54054054054054</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB55" t="n">
-        <v>14.0495159489861</v>
+        <v>14.03605547884542</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6640,7 +6638,7 @@
         <v>46259</v>
       </c>
       <c r="C56" t="n">
-        <v>1.198072253961572</v>
+        <v>1.240749008619085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6659,7 +6657,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %91.67: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -6672,16 +6670,16 @@
         <v>19.65620512594927</v>
       </c>
       <c r="K56" t="n">
-        <v>7.069766027906965</v>
+        <v>10.88371808372093</v>
       </c>
       <c r="L56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M56" t="n">
-        <v>91.66666666666667</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N56" t="n">
-        <v>24.6329919682953</v>
+        <v>25.91408746801734</v>
       </c>
       <c r="O56" t="n">
         <v>4</v>
@@ -6706,7 +6704,7 @@
         <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>13.97608681041236</v>
+        <v>10.91181299409456</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6743,7 +6741,7 @@
         <v>46259</v>
       </c>
       <c r="C57" t="n">
-        <v>1.35316589984202</v>
+        <v>1.327143478691212</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,11 +6758,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>5</v>
       </c>
@@ -6775,22 +6769,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>7.182644724273768</v>
+        <v>5.121440018037737</v>
       </c>
       <c r="L57" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M57" t="n">
-        <v>90.90909090909091</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N57" t="n">
-        <v>14.44298545863656</v>
+        <v>19.34929690151939</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>2.628555474604921</v>
+        <v>4.640880091754029</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6817,7 +6811,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>16.57657444562146</v>
+        <v>18.18087109089797</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6862,7 +6856,7 @@
         <v>46259</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6961517821058439</v>
+        <v>0.6936536517423796</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6890,22 +6884,22 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>4.879544507754963</v>
+        <v>4.503185815044897</v>
       </c>
       <c r="L58" t="n">
         <v>6</v>
       </c>
       <c r="M58" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>17.87195045712985</v>
+        <v>15.3426468546036</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>2.975275595341964</v>
+        <v>3.346131658745755</v>
       </c>
       <c r="Q58" t="n">
         <v>23</v>
@@ -6932,16 +6926,16 @@
         <v>13.39281154402059</v>
       </c>
       <c r="Y58" t="n">
-        <v>7.507766074713373</v>
+        <v>7.839673086794074</v>
       </c>
       <c r="Z58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="n">
-        <v>52.94117647058823</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB58" t="n">
-        <v>16.39955447694265</v>
+        <v>16.53962485713378</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -6981,7 +6975,7 @@
         <v>46259</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8035723332855098</v>
+        <v>0.8019069397595525</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7009,22 +7003,22 @@
         <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>2.739188191899533</v>
+        <v>2.526262520134148</v>
       </c>
       <c r="L59" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M59" t="n">
-        <v>61.11111111111111</v>
+        <v>61.81818181818182</v>
       </c>
       <c r="N59" t="n">
-        <v>13.3915163865691</v>
+        <v>13.59018791299919</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5.120550298951332</v>
+        <v>5.338863765555613</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7090,7 +7084,7 @@
         <v>46259</v>
       </c>
       <c r="C60" t="n">
-        <v>11.61640880172072</v>
+        <v>11.6059998332604</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7118,22 +7112,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>1.125484569998014</v>
+        <v>1.03487033651235</v>
       </c>
       <c r="L60" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M60" t="n">
-        <v>58.53658536585366</v>
+        <v>58.97435897435897</v>
       </c>
       <c r="N60" t="n">
-        <v>14.30264373061478</v>
+        <v>13.55750584364111</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.798004933408763</v>
+        <v>6.893787897474613</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7314,11 +7308,11 @@
         <v>46259</v>
       </c>
       <c r="C62" t="n">
-        <v>9.191119150465411</v>
+        <v>9.139074308163794</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7328,7 +7322,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7374,22 +7368,22 @@
         <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.670378619153678</v>
+        <v>2.227171492204916</v>
       </c>
       <c r="Z62" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AA62" t="n">
-        <v>45.90163934426229</v>
+        <v>47.45762711864407</v>
       </c>
       <c r="AB62" t="n">
-        <v>14.66823620462634</v>
+        <v>15.1354421363008</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.3352208380520971</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>31</v>
@@ -7423,7 +7417,7 @@
         <v>46259</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1111677862789426</v>
+        <v>0.1163722705091042</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7432,7 +7426,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7440,38 +7434,24 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>5</v>
       </c>
       <c r="I63" t="n">
         <v>10</v>
       </c>
-      <c r="J63" t="n">
-        <v>16.12393160164715</v>
-      </c>
-      <c r="K63" t="n">
-        <v>13.1192676000073</v>
-      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>3</v>
-      </c>
-      <c r="M63" t="n">
-        <v>100</v>
-      </c>
-      <c r="N63" t="n">
-        <v>16.02109596766168</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>5</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
         <v>4</v>
       </c>
@@ -7494,10 +7474,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X63" t="n">
-        <v>18.41511331267116</v>
+        <v>21.38078415792315</v>
       </c>
       <c r="Y63" t="n">
-        <v>4.472271794125094</v>
+        <v>2.443278700023466</v>
       </c>
       <c r="Z63" t="n">
         <v>7</v>
@@ -7506,13 +7486,13 @@
         <v>14.28571428571429</v>
       </c>
       <c r="AB63" t="n">
-        <v>10.64322758039532</v>
+        <v>7.899991244479065</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>5.786516972288835</v>
+        <v>7.745977108784152</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7546,7 +7526,7 @@
         <v>46259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1469746334106878</v>
+        <v>0.1461419167665794</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7571,25 +7551,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>25.00519543112713</v>
+        <v>25.32432448436694</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1418404217092606</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M64" t="n">
-        <v>60.71428571428572</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N64" t="n">
-        <v>17.601835030586</v>
+        <v>17.70355895708433</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.851278504401813</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7655,7 +7635,7 @@
         <v>46259</v>
       </c>
       <c r="C65" t="n">
-        <v>6.93237299457527</v>
+        <v>6.937577478805432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7683,7 +7663,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>22.36871137287795</v>
+        <v>22.46057977480955</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7718,25 +7698,25 @@
         <v>63.63636363636363</v>
       </c>
       <c r="X65" t="n">
-        <v>23.7467374018518</v>
+        <v>23.83860580378341</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.113585746102452</v>
+        <v>1.112759643916916</v>
       </c>
       <c r="Z65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA65" t="n">
-        <v>42.85714285714285</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.129985776808761</v>
+        <v>9.083640390388112</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.918918918918922</v>
+        <v>2.919729932483117</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7770,7 +7750,7 @@
         <v>46259</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4750653140755917</v>
+        <v>0.4775634839931363</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7830,22 +7810,22 @@
         <v>15.2543368949956</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.212124179194496</v>
+        <v>0.6926400318959858</v>
       </c>
       <c r="Z66" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA66" t="n">
-        <v>39.58333333333334</v>
+        <v>42.5531914893617</v>
       </c>
       <c r="AB66" t="n">
-        <v>9.886460238219779</v>
+        <v>9.98915149477493</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.846622908959386</v>
+        <v>5.344377264493449</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7879,7 +7859,7 @@
         <v>46259</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02768785693717727</v>
+        <v>0.02747967777615017</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7907,22 +7887,22 @@
         <v>13.52521428537139</v>
       </c>
       <c r="K67" t="n">
-        <v>2.834435555981729</v>
+        <v>2.061245107645004</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="N67" t="n">
-        <v>6.573256403145478</v>
+        <v>7.671407444036571</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.133437877804799</v>
+        <v>1.899599490786308</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7939,7 +7919,7 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>7.249188013974606</v>
+        <v>7.94656182183715</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
@@ -7976,7 +7956,7 @@
         <v>46259</v>
       </c>
       <c r="C68" t="n">
-        <v>4.696526696287256</v>
+        <v>4.667381394114228</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8036,7 +8016,7 @@
         <v>145.7315546439382</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.613605277272145</v>
+        <v>2.224163119129097</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8047,7 +8027,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>6.491136036365564</v>
+        <v>5.907223159754816</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8081,7 +8061,7 @@
         <v>46259</v>
       </c>
       <c r="C69" t="n">
-        <v>0.470069014002762</v>
+        <v>0.4671545155328131</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8133,22 +8113,22 @@
         <v>25.43142265824418</v>
       </c>
       <c r="Y69" t="n">
-        <v>3.914893957446808</v>
+        <v>4.510636042553184</v>
       </c>
       <c r="Z69" t="n">
         <v>7</v>
       </c>
       <c r="AA69" t="n">
-        <v>71.42857142857143</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB69" t="n">
-        <v>15.8102876255904</v>
+        <v>18.25732355523538</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.170061655164091</v>
+        <v>1.559717120024517</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8174,16 +8154,16 @@
         <v>46259</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4188569083304737</v>
+        <v>0.4101133731583673</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8202,22 +8182,22 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>9.830953011809761</v>
+        <v>7.538258820677912</v>
       </c>
       <c r="L70" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M70" t="n">
-        <v>53.33333333333334</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N70" t="n">
-        <v>9.807543501166204</v>
+        <v>9.232269942075462</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>0.4293738659950419</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8244,22 +8224,22 @@
         <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>4.554075349351328</v>
+        <v>6.546485603591956</v>
       </c>
       <c r="Z70" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA70" t="n">
-        <v>30.55555555555556</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB70" t="n">
-        <v>11.142082824893</v>
+        <v>11.55268773488956</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>3.610342362192465</v>
+        <v>1.555334120707941</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8293,7 +8273,7 @@
         <v>46259</v>
       </c>
       <c r="C71" t="n">
-        <v>3.12685406198639</v>
+        <v>3.12893598266787</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8321,22 +8301,22 @@
         <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>1.15319486278247</v>
+        <v>1.220544641252386</v>
       </c>
       <c r="L71" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M71" t="n">
-        <v>58.57142857142857</v>
+        <v>57.74647887323944</v>
       </c>
       <c r="N71" t="n">
-        <v>17.18235027996364</v>
+        <v>17.18276451732391</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.8371511531259701</v>
+        <v>0.7700564756988548</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8402,7 +8382,7 @@
         <v>46259</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07119734593404584</v>
+        <v>0.07078098761199166</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8430,22 +8410,22 @@
         <v>21.68783215290538</v>
       </c>
       <c r="K72" t="n">
-        <v>1.218753878751722</v>
+        <v>0.6268319472177541</v>
       </c>
       <c r="L72" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M72" t="n">
-        <v>65.21739130434783</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N72" t="n">
-        <v>15.629536440011</v>
+        <v>16.46682554870169</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>3.735716926309696</v>
+        <v>4.34592639771878</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8472,7 +8452,7 @@
         <v>36.68527402492516</v>
       </c>
       <c r="Y72" t="n">
-        <v>20.73339956973437</v>
+        <v>21.19694646628101</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8517,7 +8497,7 @@
         <v>46259</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07140552509507293</v>
+        <v>0.07119734593404584</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8545,22 +8525,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>8.535713988928473</v>
+        <v>8.219283658787923</v>
       </c>
       <c r="L73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M73" t="n">
-        <v>66.66666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="N73" t="n">
-        <v>10.41015246766233</v>
+        <v>10.17048915836387</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>1.349128279766876</v>
+        <v>1.645470456842646</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8587,22 +8567,22 @@
         <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>5.946958722677509</v>
+        <v>6.221165560300923</v>
       </c>
       <c r="Z73" t="n">
         <v>19</v>
       </c>
       <c r="AA73" t="n">
-        <v>57.89473684210526</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB73" t="n">
-        <v>13.22595385437325</v>
+        <v>12.4822167630246</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>4.309314427559863</v>
+        <v>4.029517387666948</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8636,7 +8616,7 @@
         <v>46259</v>
       </c>
       <c r="C74" t="n">
-        <v>5.54277570512212</v>
+        <v>5.594820547423735</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8696,22 +8676,22 @@
         <v>33.81594625096176</v>
       </c>
       <c r="Y74" t="n">
-        <v>5.496465148228181</v>
+        <v>4.609108013469765</v>
       </c>
       <c r="Z74" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA74" t="n">
-        <v>31.57894736842105</v>
+        <v>48</v>
       </c>
       <c r="AB74" t="n">
-        <v>18.0541574746302</v>
+        <v>19.63294624302093</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>4.765467089496267</v>
+        <v>5.651369721221878</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8745,7 +8725,7 @@
         <v>46259</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1246994373665468</v>
+        <v>0.1240749048797704</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8762,7 +8742,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8773,22 +8757,22 @@
         <v>23.35547482758762</v>
       </c>
       <c r="K75" t="n">
-        <v>0.9182823054377121</v>
+        <v>0.4128530337389247</v>
       </c>
       <c r="L75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M75" t="n">
-        <v>72.72727272727273</v>
+        <v>80</v>
       </c>
       <c r="N75" t="n">
-        <v>18.24441559719496</v>
+        <v>21.88013391565777</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>5.03547779299498</v>
+        <v>5.56417510055589</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8963,7 +8947,7 @@
         <v>46259</v>
       </c>
       <c r="C77" t="n">
-        <v>0.537935493152195</v>
+        <v>0.5329391930793653</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8991,16 +8975,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>10.79106186349674</v>
+        <v>9.762043705178524</v>
       </c>
       <c r="L77" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M77" t="n">
-        <v>68.96551724137932</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N77" t="n">
-        <v>16.90273640953321</v>
+        <v>16.36595029257426</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
@@ -9033,22 +9017,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>4.721713218405288</v>
+        <v>5.606650013329295</v>
       </c>
       <c r="Z77" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AA77" t="n">
-        <v>44.68085106382978</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.15240524749853</v>
+        <v>11.63900580344974</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.539863236304898</v>
+        <v>4.654300315955617</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9082,7 +9066,7 @@
         <v>46259</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0480894330376171</v>
+        <v>0.0482976121986442</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9110,22 +9094,22 @@
         <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>2.930494298116493</v>
+        <v>3.3760804195067</v>
       </c>
       <c r="L78" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M78" t="n">
-        <v>62.5</v>
+        <v>63.04347826086956</v>
       </c>
       <c r="N78" t="n">
-        <v>18.54425621787096</v>
+        <v>17.99693567127776</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>1.039056218641976</v>
+        <v>0.6035434676584739</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9191,7 +9175,7 @@
         <v>46259</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8293866100412455</v>
+        <v>0.8218921400508712</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9219,22 +9203,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>4.608628505602619</v>
+        <v>3.663368216157559</v>
       </c>
       <c r="L79" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M79" t="n">
-        <v>60</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="N79" t="n">
-        <v>12.11724597546695</v>
+        <v>11.1415732128032</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0.3741292663792306</v>
+        <v>1.289396444320934</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9300,7 +9284,7 @@
         <v>46259</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1294875632746542</v>
+        <v>0.1288630307878778</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9328,7 +9312,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>6.01532292945004</v>
+        <v>5.503999590040975</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9339,7 +9323,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>3.758585985916074</v>
+        <v>4.261450207981898</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9366,22 +9350,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.587799240813085</v>
+        <v>6.043159470251524</v>
       </c>
       <c r="Z80" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA80" t="n">
-        <v>35</v>
+        <v>32.35294117647059</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.51348611190969</v>
+        <v>11.76250695783027</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.554967196813474</v>
+        <v>2.082701502855344</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9415,7 +9399,7 @@
         <v>46259</v>
       </c>
       <c r="C81" t="n">
-        <v>1.210563063787035</v>
+        <v>1.202235857167333</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9475,22 +9459,22 @@
         <v>26.61221483076936</v>
       </c>
       <c r="Y81" t="n">
-        <v>4.828145685549323</v>
+        <v>5.482812690486149</v>
       </c>
       <c r="Z81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA81" t="n">
-        <v>57.14285714285715</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB81" t="n">
-        <v>12.94561142715581</v>
+        <v>13.83922218726296</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>5.434226696227551</v>
+        <v>4.77922316363636</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9524,7 +9508,7 @@
         <v>46259</v>
       </c>
       <c r="C82" t="n">
-        <v>5.339800820145816</v>
+        <v>5.251324588233069</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9584,16 +9568,16 @@
         <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>4.487563868374744</v>
+        <v>6.07012859960051</v>
       </c>
       <c r="Z82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA82" t="n">
-        <v>30</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB82" t="n">
-        <v>7.560260277872317</v>
+        <v>8.470858704440229</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9633,7 +9617,7 @@
         <v>46259</v>
       </c>
       <c r="C83" t="n">
-        <v>5.855044758931816</v>
+        <v>5.907089601233432</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9693,22 +9677,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.67523313767144</v>
+        <v>1.810124098895194</v>
       </c>
       <c r="Z83" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA83" t="n">
-        <v>47.36842105263158</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.98905293309322</v>
+        <v>11.44930613497256</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.416157027153877</v>
+        <v>4.267115996077619</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9742,7 +9726,7 @@
         <v>46259</v>
       </c>
       <c r="C84" t="n">
-        <v>2.146329264667207</v>
+        <v>2.138002058255684</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9770,22 +9754,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>2.750258390755822</v>
+        <v>2.351613772456873</v>
       </c>
       <c r="L84" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M84" t="n">
-        <v>50</v>
+        <v>49.18032786885246</v>
       </c>
       <c r="N84" t="n">
-        <v>10.44668109268372</v>
+        <v>10.92194658681683</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>2.189524040599955</v>
+        <v>2.587537343017265</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9851,7 +9835,7 @@
         <v>46259</v>
       </c>
       <c r="C85" t="n">
-        <v>6.313039371186038</v>
+        <v>6.292221434265391</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9879,22 +9863,22 @@
         <v>12.61214035274981</v>
       </c>
       <c r="K85" t="n">
-        <v>2.04202462118519</v>
+        <v>1.705529898609148</v>
       </c>
       <c r="L85" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M85" t="n">
-        <v>56.92307692307692</v>
+        <v>58.57142857142857</v>
       </c>
       <c r="N85" t="n">
-        <v>12.98174554119793</v>
+        <v>14.54219798356717</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.838746732959144</v>
+        <v>6.188916283771251</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9960,7 +9944,7 @@
         <v>46259</v>
       </c>
       <c r="C86" t="n">
-        <v>4.463365548797185</v>
+        <v>4.509165264001438</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9988,22 +9972,22 @@
         <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>4.63640814193309</v>
+        <v>5.710108613136478</v>
       </c>
       <c r="L86" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M86" t="n">
-        <v>44.44444444444444</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="N86" t="n">
-        <v>16.62126646767561</v>
+        <v>15.52741283158099</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
       </c>
       <c r="P86" t="n">
-        <v>1.303171508159262</v>
+        <v>0.2742324179463518</v>
       </c>
       <c r="Q86" t="n">
         <v>54</v>
@@ -10030,10 +10014,10 @@
         <v>71.56995669069586</v>
       </c>
       <c r="Y86" t="n">
-        <v>12.99534314665145</v>
+        <v>12.10256650495314</v>
       </c>
       <c r="Z86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
@@ -10194,11 +10178,11 @@
         <v>46259</v>
       </c>
       <c r="C88" t="n">
-        <v>1.12937307794507</v>
+        <v>1.103350656794262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10208,7 +10192,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10254,22 +10238,22 @@
         <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>5.570062171745038</v>
+        <v>7.745867190829269</v>
       </c>
       <c r="Z88" t="n">
         <v>12</v>
       </c>
       <c r="AA88" t="n">
-        <v>66.66666666666667</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB88" t="n">
-        <v>14.62604774501775</v>
+        <v>13.54845664667655</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.4552982223041568</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
         <v>32</v>
@@ -10303,7 +10287,7 @@
         <v>46259</v>
       </c>
       <c r="C89" t="n">
-        <v>2.204619551747903</v>
+        <v>2.175474408207555</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10363,22 +10347,22 @@
         <v>27.21456043612742</v>
       </c>
       <c r="Y89" t="n">
-        <v>5.866665306666663</v>
+        <v>7.111111111111123</v>
       </c>
       <c r="Z89" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA89" t="n">
-        <v>55.55555555555556</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.38450532899653</v>
+        <v>13.56081322869333</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>4.390936225513387</v>
+        <v>3.110047846889941</v>
       </c>
       <c r="AE89" t="n">
         <v>21</v>
@@ -10412,7 +10396,7 @@
         <v>46259</v>
       </c>
       <c r="C90" t="n">
-        <v>2.929083661240249</v>
+        <v>2.881202342828054</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10472,16 +10456,16 @@
         <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>6.262497513649334</v>
+        <v>7.794811275494018</v>
       </c>
       <c r="Z90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA90" t="n">
-        <v>71.42857142857143</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB90" t="n">
-        <v>12.953476211778</v>
+        <v>15.81985550752225</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10521,16 +10505,16 @@
         <v>46259</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2308709235726598</v>
+        <v>0.2285809378124471</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10549,22 +10533,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>3.125657897835965</v>
+        <v>2.102764739857665</v>
       </c>
       <c r="L91" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M91" t="n">
-        <v>61.90476190476191</v>
+        <v>64.17910447761194</v>
       </c>
       <c r="N91" t="n">
-        <v>13.28140913362387</v>
+        <v>15.1274368629663</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>0.8787570664010591</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10630,7 +10614,7 @@
         <v>46259</v>
       </c>
       <c r="C92" t="n">
-        <v>1.112718744230185</v>
+        <v>1.107514260000024</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10658,7 +10642,7 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>5.605792105199892</v>
+        <v>5.111845470010001</v>
       </c>
       <c r="L92" t="n">
         <v>33</v>
@@ -10667,13 +10651,13 @@
         <v>51.51515151515152</v>
       </c>
       <c r="N92" t="n">
-        <v>13.43574145268475</v>
+        <v>12.53228292565582</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.267117974376931</v>
+        <v>2.747696529421173</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10700,16 +10684,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.900831123718167</v>
+        <v>8.331603656771158</v>
       </c>
       <c r="Z92" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA92" t="n">
-        <v>50</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.25604859314078</v>
+        <v>11.50569588085053</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10749,7 +10733,7 @@
         <v>46259</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04205223216334711</v>
+        <v>0.04184405300232</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10777,22 +10761,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>3.982973176224136</v>
+        <v>3.468206491952897</v>
       </c>
       <c r="L93" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M93" t="n">
-        <v>59.61538461538461</v>
+        <v>56.89655172413793</v>
       </c>
       <c r="N93" t="n">
-        <v>18.233323415934</v>
+        <v>20.27323651027488</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>1.939766446529223</v>
+        <v>2.446928959036332</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10858,11 +10842,11 @@
         <v>46259</v>
       </c>
       <c r="C94" t="n">
-        <v>7.999292261758401</v>
+        <v>7.858771187544038</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10872,7 +10856,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -10918,22 +10902,18 @@
         <v>48.9849654478532</v>
       </c>
       <c r="Y94" t="n">
-        <v>5.705521472392638</v>
+        <v>7.361963190184051</v>
       </c>
       <c r="Z94" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>7.911842375757001</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.3122966818477568</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10967,7 +10947,7 @@
         <v>46259</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1398965317349774</v>
+        <v>0.1394801734129232</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10995,22 +10975,22 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>4.867931798680258</v>
+        <v>4.555825161156846</v>
       </c>
       <c r="L95" t="n">
         <v>11</v>
       </c>
       <c r="M95" t="n">
-        <v>63.63636363636363</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N95" t="n">
-        <v>19.44007145253257</v>
+        <v>17.79602740297683</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>1.079518001263757</v>
+        <v>1.381247612571745</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11037,16 +11017,16 @@
         <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>6.390267740350508</v>
+        <v>6.66886786408628</v>
       </c>
       <c r="Z95" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA95" t="n">
-        <v>44</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB95" t="n">
-        <v>11.55158951422049</v>
+        <v>11.37674008022595</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
@@ -11086,7 +11066,7 @@
         <v>46259</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1274057716643832</v>
+        <v>0.1284466724658236</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11114,22 +11094,22 @@
         <v>14.68867757321659</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6578942520775621</v>
+        <v>1.480265808950887</v>
       </c>
       <c r="L96" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M96" t="n">
-        <v>58.06451612903226</v>
+        <v>58.73015873015873</v>
       </c>
       <c r="N96" t="n">
-        <v>12.75896352486635</v>
+        <v>12.21880744965162</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>9.281046277927295</v>
+        <v>8.395459080771994</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11195,7 +11175,7 @@
         <v>46259</v>
       </c>
       <c r="C97" t="n">
-        <v>1.893391299438088</v>
+        <v>1.877777846747603</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11223,16 +11203,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>5.934906750754299</v>
+        <v>5.061336847208886</v>
       </c>
       <c r="L97" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M97" t="n">
-        <v>50</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="N97" t="n">
-        <v>14.76656774783397</v>
+        <v>15.70959200841163</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11265,16 +11245,16 @@
         <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>9.828463182660375</v>
+        <v>10.57204377508396</v>
       </c>
       <c r="Z97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA97" t="n">
-        <v>41.66666666666666</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="AB97" t="n">
-        <v>10.42692936952895</v>
+        <v>12.74324733068823</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11314,7 +11294,7 @@
         <v>46259</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6586795114703123</v>
+        <v>0.6553486446856995</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11342,22 +11322,22 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>9.987266026287323</v>
+        <v>9.43107302990953</v>
       </c>
       <c r="L98" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M98" t="n">
-        <v>61.90476190476191</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N98" t="n">
-        <v>13.17398737151013</v>
+        <v>12.6215357960826</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>0.01157768001038839</v>
+        <v>0.5198952677133883</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11384,22 +11364,22 @@
         <v>10.6825105654681</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.6281430874930605</v>
+        <v>1.130655176834228</v>
       </c>
       <c r="Z98" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA98" t="n">
-        <v>39.21568627450981</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="AB98" t="n">
-        <v>10.98217636308735</v>
+        <v>11.51563585545586</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>7.418455427473358</v>
+        <v>6.94790163265675</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11433,16 +11413,16 @@
         <v>46259</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4600764138571027</v>
+        <v>0.4559128106513414</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11461,22 +11441,22 @@
         <v>21.64053449738032</v>
       </c>
       <c r="K99" t="n">
-        <v>4.451083646926945</v>
+        <v>3.505821395659536</v>
       </c>
       <c r="L99" t="n">
         <v>29</v>
       </c>
       <c r="M99" t="n">
-        <v>55.17241379310344</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N99" t="n">
-        <v>12.84057962852784</v>
+        <v>12.59459241398103</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>0.4774403967593654</v>
       </c>
       <c r="Q99" t="n">
         <v>33</v>
@@ -11542,7 +11522,7 @@
         <v>46259</v>
       </c>
       <c r="C100" t="n">
-        <v>337.6046863421847</v>
+        <v>336.9701661966081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11570,16 +11550,16 @@
         <v>12.69669682287478</v>
       </c>
       <c r="K100" t="n">
-        <v>10.15348589785079</v>
+        <v>9.94645498644684</v>
       </c>
       <c r="L100" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M100" t="n">
-        <v>61.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="N100" t="n">
-        <v>10.18641432150756</v>
+        <v>11.73954280918841</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11612,22 +11592,22 @@
         <v>11.67288888132132</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.360583574662644</v>
+        <v>1.545974060641719</v>
       </c>
       <c r="Z100" t="n">
         <v>57</v>
       </c>
       <c r="AA100" t="n">
-        <v>35.08771929824562</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB100" t="n">
-        <v>11.42378967284656</v>
+        <v>13.91287882775731</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>6.730997268584704</v>
+        <v>6.555370263206473</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11661,7 +11641,7 @@
         <v>46259</v>
       </c>
       <c r="C101" t="n">
-        <v>348.2615996842437</v>
+        <v>347.6187239016155</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11721,22 +11701,22 @@
         <v>11.75561335839466</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.317111095668599</v>
+        <v>1.499275421261481</v>
       </c>
       <c r="Z101" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA101" t="n">
-        <v>43.90243902439025</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="AB101" t="n">
-        <v>12.38952217998343</v>
+        <v>12.70179743752792</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.745390975401276</v>
+        <v>4.569229919868034</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11770,7 +11750,7 @@
         <v>46259</v>
       </c>
       <c r="C102" t="n">
-        <v>416.1351488910934</v>
+        <v>414.2103435867317</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11830,22 +11810,22 @@
         <v>11.13903673030769</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.399524781263762</v>
+        <v>2.850969252873181</v>
       </c>
       <c r="Z102" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA102" t="n">
-        <v>32.35294117647059</v>
+        <v>24.13793103448276</v>
       </c>
       <c r="AB102" t="n">
-        <v>14.53902862438785</v>
+        <v>13.63192783310294</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.664408357549708</v>
+        <v>2.212096951044862</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11879,7 +11859,7 @@
         <v>46259</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7598546976035957</v>
+        <v>0.7636019327028725</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11939,22 +11919,22 @@
         <v>18.08106682362138</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.030371634964811</v>
+        <v>0.5423013942445154</v>
       </c>
       <c r="Z103" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA103" t="n">
-        <v>38.29787234042553</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB103" t="n">
-        <v>12.65910342047405</v>
+        <v>13.04527401977847</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.042189083835614</v>
+        <v>7.498362329212305</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11988,7 +11968,7 @@
         <v>46259</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04725671639350872</v>
+        <v>0.04767307471556291</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12016,22 +11996,22 @@
         <v>18.611805593619</v>
       </c>
       <c r="K104" t="n">
-        <v>1.527979459194229</v>
+        <v>2.422498215368085</v>
       </c>
       <c r="L104" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M104" t="n">
-        <v>46.15384615384615</v>
+        <v>38.77551020408163</v>
       </c>
       <c r="N104" t="n">
-        <v>15.49298906260249</v>
+        <v>13.16720578589455</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.434817036617298</v>
+        <v>1.540190692590637</v>
       </c>
       <c r="Q104" t="n">
         <v>35</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -437,7 +437,7 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -670,7 +670,7 @@
         <v>46259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3920017505503378</v>
+        <v>0.3924181188650018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>18.04725545643595</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4266662399999843</v>
+        <v>0.5333353599999979</v>
       </c>
       <c r="L2" t="n">
         <v>30</v>
@@ -713,7 +713,7 @@
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>9.532661113256147</v>
+        <v>9.416443417599552</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -779,7 +779,7 @@
         <v>46259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6424415460700912</v>
+        <v>0.6411924413342788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5064339197677015</v>
+        <v>0.3110183782966347</v>
       </c>
       <c r="L3" t="n">
         <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>60.37735849056604</v>
+        <v>58.49056603773585</v>
       </c>
       <c r="N3" t="n">
-        <v>12.66709532431191</v>
+        <v>12.992007981713</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>9.445729701056592</v>
+        <v>9.658940541470651</v>
       </c>
       <c r="Q3" t="n">
         <v>37</v>
@@ -888,7 +888,7 @@
         <v>46259</v>
       </c>
       <c r="C4" t="n">
-        <v>1.494727934397123</v>
+        <v>1.498891458286545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         <v>18.2305339009923</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.11314990092869</v>
+        <v>1.840488750047009</v>
       </c>
       <c r="Z4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA4" t="n">
         <v>44</v>
       </c>
-      <c r="AA4" t="n">
-        <v>47.72727272727273</v>
-      </c>
       <c r="AB4" t="n">
-        <v>14.05792332230468</v>
+        <v>13.23044335691964</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.057108887546205</v>
+        <v>8.312501912499993</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -997,7 +997,7 @@
         <v>46259</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2302463910858833</v>
+        <v>0.228997306127111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,7 +1014,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1022,25 +1026,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>17.80973219631822</v>
+        <v>18.40585323077206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2719917564313334</v>
+        <v>0.4566227476491713</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>74.35897435897436</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N5" t="n">
-        <v>13.33766417053529</v>
+        <v>11.30960585175055</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.720608412960646</v>
+        <v>2.53181640272726</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1106,7 +1110,7 @@
         <v>46259</v>
       </c>
       <c r="C6" t="n">
-        <v>1.697702819373426</v>
+        <v>1.692498335143265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,10 +1138,10 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>3.738776089463158</v>
+        <v>3.420754102309265</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1172,16 +1176,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.357304425536859</v>
+        <v>7.641310225995457</v>
       </c>
       <c r="Z6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
-        <v>48.57142857142857</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.15406463341447</v>
+        <v>11.70740932634858</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1221,7 +1225,7 @@
         <v>46259</v>
       </c>
       <c r="C7" t="n">
-        <v>2.187965138508499</v>
+        <v>2.204619551747903</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,22 +1253,22 @@
         <v>12.3532304777189</v>
       </c>
       <c r="K7" t="n">
-        <v>2.837574957481448</v>
+        <v>3.620356839942174</v>
       </c>
       <c r="L7" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M7" t="n">
-        <v>58.8235294117647</v>
+        <v>50.79365079365079</v>
       </c>
       <c r="N7" t="n">
-        <v>13.04964433203072</v>
+        <v>12.45312503184046</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>5.019979365181437</v>
+        <v>4.226624278878788</v>
       </c>
       <c r="Q7" t="n">
         <v>49</v>
@@ -1291,16 +1295,16 @@
         <v>17.31307710509156</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.866187694713169</v>
+        <v>9.180104662330645</v>
       </c>
       <c r="Z7" t="n">
         <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.36271703915551</v>
+        <v>12.33928912392035</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1340,7 +1344,7 @@
         <v>46259</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3870054504775082</v>
+        <v>0.3872136346348402</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1404,7 @@
         <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.77800008402839</v>
+        <v>5.727314679906992</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
@@ -1411,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.358260191837591</v>
+        <v>2.410756957199578</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1445,7 +1449,7 @@
         <v>46259</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5787386305723394</v>
+        <v>0.5770731970759433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,16 +1509,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.943000208412564</v>
+        <v>7.210789908875048</v>
       </c>
       <c r="Z9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA9" t="n">
-        <v>52.94117647058823</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.11294478239028</v>
+        <v>10.26435311358188</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1554,7 +1558,7 @@
         <v>46259</v>
       </c>
       <c r="C10" t="n">
-        <v>1.922536442770257</v>
+        <v>1.921495641270376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1586,7 @@
         <v>10.84633778363752</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1083994254742704</v>
+        <v>0.05420384823848767</v>
       </c>
       <c r="L10" t="n">
         <v>41</v>
@@ -1597,7 +1601,7 @@
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.885221028742693</v>
+        <v>5.942575047401366</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1663,11 +1667,11 @@
         <v>46259</v>
       </c>
       <c r="C11" t="n">
-        <v>8.478104810933269</v>
+        <v>8.405242031711007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1677,7 +1681,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1723,22 +1727,22 @@
         <v>23.11730782489165</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.332525741974566</v>
+        <v>2.18049666868565</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="AA11" t="n">
-        <v>52.63157894736842</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.53590431090026</v>
+        <v>11.4075321336774</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.6764886433394679</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1772,7 +1776,7 @@
         <v>46259</v>
       </c>
       <c r="C12" t="n">
-        <v>7.078098553019795</v>
+        <v>7.057280616099149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1795,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1804,16 +1808,16 @@
         <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>7.740239116529968</v>
+        <v>7.423356060304886</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N12" t="n">
-        <v>18.35196818008896</v>
+        <v>18.25138940387051</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1846,7 +1850,7 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.23914260911552</v>
+        <v>4.520792189676948</v>
       </c>
       <c r="Z12" t="n">
         <v>11</v>
@@ -1855,7 +1859,7 @@
         <v>27.27272727272727</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.40124120252835</v>
+        <v>10.19016848477012</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1895,7 +1899,7 @@
         <v>46259</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2223355727660646</v>
+        <v>0.2219192044514007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1927,7 @@
         <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>5.25809708397067</v>
+        <v>5.06098001474804</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1959,7 +1963,7 @@
         <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.738725342883326</v>
+        <v>9.907757829861652</v>
       </c>
       <c r="Z13" t="n">
         <v>6</v>
@@ -1968,13 +1972,13 @@
         <v>50</v>
       </c>
       <c r="AB13" t="n">
-        <v>13.48475647319801</v>
+        <v>13.3233336455564</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2894648431558289</v>
+        <v>0.1023863630390642</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1998,7 +2002,7 @@
         <v>46259</v>
       </c>
       <c r="C14" t="n">
-        <v>8.665466243219088</v>
+        <v>8.691488664369896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,22 +2062,22 @@
         <v>12.90895707120068</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.020865538081583</v>
+        <v>0.7236309000578034</v>
       </c>
       <c r="Z14" t="n">
         <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>48.93617021276596</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.08317190342756</v>
+        <v>12.11589101364306</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.9892332027768291</v>
+        <v>1.285672624325396</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2107,7 +2111,7 @@
         <v>46259</v>
       </c>
       <c r="C15" t="n">
-        <v>14.90564283518286</v>
+        <v>15.03055045670674</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,22 +2171,22 @@
         <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.727452271231071</v>
+        <v>4.937458854509547</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.567483531887934</v>
+        <v>10.20717534907267</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.532122905027935</v>
+        <v>5.325484764542932</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2216,7 +2220,7 @@
         <v>46259</v>
       </c>
       <c r="C16" t="n">
-        <v>35.93175912503578</v>
+        <v>35.8901232511945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,22 +2248,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>3.188751139689638</v>
+        <v>3.06918132376881</v>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>65.71428571428571</v>
+        <v>68.1159420289855</v>
       </c>
       <c r="N16" t="n">
-        <v>18.36942990324292</v>
+        <v>18.35529890911982</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.600766832704252</v>
+        <v>6.7244336155728</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2286,7 +2290,7 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.21038608698997</v>
+        <v>11.3132709235056</v>
       </c>
       <c r="Z16" t="n">
         <v>29</v>
@@ -2335,7 +2339,7 @@
         <v>46259</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6878246550106608</v>
+        <v>0.684493788226048</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,22 +2367,22 @@
         <v>16.87409721257028</v>
       </c>
       <c r="K17" t="n">
-        <v>1.53657033147987</v>
+        <v>1.044868286377421</v>
       </c>
       <c r="L17" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M17" t="n">
-        <v>67.24137931034483</v>
+        <v>69.09090909090909</v>
       </c>
       <c r="N17" t="n">
-        <v>16.30300633150743</v>
+        <v>16.02126973535134</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.365617478923502</v>
+        <v>6.883211222474572</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2444,7 +2448,7 @@
         <v>46259</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09659522460546775</v>
+        <v>0.09638705023256616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,7 +2476,7 @@
         <v>21.20940117548115</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4329000103071357</v>
+        <v>0.2164549835086627</v>
       </c>
       <c r="L18" t="n">
         <v>35</v>
@@ -2487,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>9.52586252981944</v>
+        <v>9.76241378534224</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2662,7 +2666,7 @@
         <v>46259</v>
       </c>
       <c r="C20" t="n">
-        <v>1.611308349509479</v>
+        <v>1.607144666779199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,25 +2691,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>18.71559577638767</v>
+        <v>18.92576555578012</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06464519843447647</v>
+        <v>0.06480287622621095</v>
       </c>
       <c r="L20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M20" t="n">
-        <v>67.85714285714286</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N20" t="n">
-        <v>11.80397784294498</v>
+        <v>11.73360702046221</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.934104495876232</v>
+        <v>1.933943872519794</v>
       </c>
       <c r="Q20" t="n">
         <v>49</v>
@@ -2771,7 +2775,7 @@
         <v>46259</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9622050698701623</v>
+        <v>0.955126968194452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,22 +2803,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>3.574126053867777</v>
+        <v>2.812221738313658</v>
       </c>
       <c r="L21" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>54.71698113207547</v>
+        <v>54.23728813559322</v>
       </c>
       <c r="N21" t="n">
-        <v>16.30703483238944</v>
+        <v>16.6825238929974</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.273146310527776</v>
+        <v>5.045877011480915</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2880,7 +2884,7 @@
         <v>46259</v>
       </c>
       <c r="C22" t="n">
-        <v>0.337666922488509</v>
+        <v>0.33475242401856</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2940,16 +2944,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.973456019369807</v>
+        <v>8.767763082820391</v>
       </c>
       <c r="Z22" t="n">
         <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>54.54545454545455</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.89827904879843</v>
+        <v>13.12020963534471</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
@@ -2981,7 +2985,7 @@
         <v>46259</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7486129925139446</v>
+        <v>0.7702636660639189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,22 +3013,22 @@
         <v>27.73484467032905</v>
       </c>
       <c r="K23" t="n">
-        <v>1.985254660670099</v>
+        <v>4.934775277663728</v>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N23" t="n">
-        <v>25.26583029055753</v>
+        <v>17.27153905628944</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>7.858729544772847</v>
+        <v>4.827022032432415</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -3051,7 +3055,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>26.30019730610627</v>
+        <v>24.16872165075517</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3096,7 +3100,7 @@
         <v>46259</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1792424298086674</v>
+        <v>0.1779933646269352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3128,7 @@
         <v>23.47035234733546</v>
       </c>
       <c r="K24" t="n">
-        <v>6.018792094316905</v>
+        <v>5.27999167772093</v>
       </c>
       <c r="L24" t="n">
         <v>9</v>
@@ -3133,13 +3137,13 @@
         <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>12.06452679688787</v>
+        <v>12.74546888007776</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>3.755190779896189</v>
+        <v>4.483290934072048</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3166,16 +3170,16 @@
         <v>12.66805408629466</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.9016391521992</v>
+        <v>6.557371092000086</v>
       </c>
       <c r="Z24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>51.85185185185185</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="AB24" t="n">
-        <v>15.2747307352476</v>
+        <v>12.83318425402356</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3215,7 +3219,7 @@
         <v>46259</v>
       </c>
       <c r="C25" t="n">
-        <v>3.464104576606155</v>
+        <v>3.455777528827312</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,25 +3244,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>16.74581894046563</v>
+        <v>16.84600295124913</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1203351105115491</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M25" t="n">
-        <v>61.53846153846154</v>
+        <v>62.26415094339622</v>
       </c>
       <c r="N25" t="n">
-        <v>17.5338212425245</v>
+        <v>17.02258354059398</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.870194282501131</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3324,7 +3328,7 @@
         <v>46259</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4396748452511202</v>
+        <v>0.4375930436482395</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3423,7 +3427,7 @@
         <v>46259</v>
       </c>
       <c r="C27" t="n">
-        <v>47.54816792675651</v>
+        <v>48.92215176351917</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,7 +3455,7 @@
         <v>50.20031327035493</v>
       </c>
       <c r="K27" t="n">
-        <v>44.24621949190546</v>
+        <v>48.41445525655774</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3476,10 +3480,10 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>47.34081877172307</v>
+        <v>48.41445525655774</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.100300042863279</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>5</v>
@@ -3488,13 +3492,13 @@
         <v>40</v>
       </c>
       <c r="AB27" t="n">
-        <v>12.91986477688082</v>
+        <v>19.54791007974723</v>
       </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.983362521891409</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3518,7 +3522,7 @@
         <v>46259</v>
       </c>
       <c r="C28" t="n">
-        <v>1.615471873190722</v>
+        <v>1.620676357420883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,22 +3582,22 @@
         <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.451294161201167</v>
+        <v>2.137026417122168</v>
       </c>
       <c r="Z28" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA28" t="n">
-        <v>51.28205128205128</v>
+        <v>46.34146341463415</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.1655074559226</v>
+        <v>11.75570991198495</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.637881003427301</v>
+        <v>3.947329047391324</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3627,7 +3631,7 @@
         <v>46259</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4015780223517721</v>
+        <v>0.4007452857224443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,7 +3659,7 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>11.08948257562987</v>
+        <v>10.85912066306292</v>
       </c>
       <c r="L29" t="n">
         <v>7</v>
@@ -3697,7 +3701,7 @@
         <v>48.55798797437896</v>
       </c>
       <c r="Y29" t="n">
-        <v>12.3377631321607</v>
+        <v>12.51954488212091</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3742,7 +3746,7 @@
         <v>46259</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4180241717011459</v>
+        <v>0.417191475042257</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,7 +3778,7 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>14.19286851767927</v>
+        <v>13.96539836996833</v>
       </c>
       <c r="L30" t="n">
         <v>3</v>
@@ -3816,22 +3820,22 @@
         <v>18.28742967351311</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.461535318786868</v>
+        <v>3.653838210428684</v>
       </c>
       <c r="Z30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA30" t="n">
-        <v>43.75</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.82654903909837</v>
+        <v>14.16975474939946</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.772911401485704</v>
+        <v>6.58683404890783</v>
       </c>
       <c r="AE30" t="n">
         <v>50</v>
@@ -3865,16 +3869,16 @@
         <v>46259</v>
       </c>
       <c r="C31" t="n">
-        <v>0.190900483227763</v>
+        <v>0.1917331998718714</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3884,7 +3888,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3897,22 +3901,22 @@
         <v>18.68860738081651</v>
       </c>
       <c r="K31" t="n">
-        <v>9.630853194553168</v>
+        <v>10.10906799327629</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>88.88888888888889</v>
+        <v>87.5</v>
       </c>
       <c r="N31" t="n">
-        <v>14.72026057876797</v>
+        <v>15.76876179144892</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3367179901370809</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3936,25 +3940,25 @@
         <v>87.5</v>
       </c>
       <c r="X31" t="n">
-        <v>10.34816965405449</v>
+        <v>10.82639592994425</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.6500483530901602</v>
+        <v>0.6472536895645309</v>
       </c>
       <c r="Z31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>30</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB31" t="n">
-        <v>8.15303860280935</v>
+        <v>9.186968181927581</v>
       </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.411128532945446</v>
+        <v>9.413676680070903</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3988,21 +3992,21 @@
         <v>46259</v>
       </c>
       <c r="C32" t="n">
-        <v>2.273318648239885</v>
+        <v>2.250418949270439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -4016,16 +4020,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>4.309793287416075</v>
+        <v>3.259055034027591</v>
       </c>
       <c r="L32" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M32" t="n">
-        <v>53.19148936170212</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N32" t="n">
-        <v>10.04046136466732</v>
+        <v>10.25829907235677</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4058,22 +4062,22 @@
         <v>16.72680602412306</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.589209075087067</v>
+        <v>8.520085745345085</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA32" t="n">
-        <v>47.05882352941177</v>
+        <v>50</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.40978584043263</v>
+        <v>12.57267934693818</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.4445270090229103</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>25</v>
@@ -4107,7 +4111,7 @@
         <v>46259</v>
       </c>
       <c r="C33" t="n">
-        <v>1.743502217104141</v>
+        <v>1.747665740993563</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4139,7 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>6.394282698786657</v>
+        <v>6.648354723111383</v>
       </c>
       <c r="L33" t="n">
         <v>28</v>
@@ -4144,7 +4148,7 @@
         <v>64.28571428571429</v>
       </c>
       <c r="N33" t="n">
-        <v>10.64617202775737</v>
+        <v>10.92805046826421</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4216,7 +4220,7 @@
         <v>46259</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7935797331398504</v>
+        <v>0.7960779428196545</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4244,7 +4248,7 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>4.562880560837002</v>
+        <v>4.892047233644714</v>
       </c>
       <c r="L34" t="n">
         <v>22</v>
@@ -4253,7 +4257,7 @@
         <v>72.72727272727273</v>
       </c>
       <c r="N34" t="n">
-        <v>10.11946514086019</v>
+        <v>9.616943003587124</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4325,7 +4329,7 @@
         <v>46259</v>
       </c>
       <c r="C35" t="n">
-        <v>1.980826729850954</v>
+        <v>1.983949452032315</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4357,7 +4361,7 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>11.66960355272302</v>
+        <v>11.84564779866479</v>
       </c>
       <c r="L35" t="n">
         <v>9</v>
@@ -4399,16 +4403,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>4.678513777939298</v>
+        <v>4.528241916751141</v>
       </c>
       <c r="Z35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA35" t="n">
-        <v>33.33333333333334</v>
+        <v>37.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>12.40592897629132</v>
+        <v>14.89562390716056</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4448,7 +4452,7 @@
         <v>46259</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08160631439436906</v>
+        <v>0.08139813523334197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4476,16 +4480,16 @@
         <v>14.21000360644873</v>
       </c>
       <c r="K36" t="n">
-        <v>4.53921373405386</v>
+        <v>4.272532338489099</v>
       </c>
       <c r="L36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M36" t="n">
-        <v>64</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N36" t="n">
-        <v>20.37787463574827</v>
+        <v>20.5096675101567</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4676,7 +4680,7 @@
         <v>46259</v>
       </c>
       <c r="C38" t="n">
-        <v>1.633167087930007</v>
+        <v>1.636289810111368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4704,7 +4708,7 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>3.081864627335795</v>
+        <v>3.278963887752462</v>
       </c>
       <c r="L38" t="n">
         <v>60</v>
@@ -4713,13 +4717,13 @@
         <v>51.66666666666666</v>
       </c>
       <c r="N38" t="n">
-        <v>11.73894987460513</v>
+        <v>11.3855037388882</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>6.711302126397145</v>
+        <v>6.507652535662767</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4785,7 +4789,7 @@
         <v>46259</v>
       </c>
       <c r="C39" t="n">
-        <v>2.756294721304176</v>
+        <v>2.760458562667135</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4845,22 +4849,22 @@
         <v>11.08431820998319</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.780422177816854</v>
+        <v>1.632045178206687</v>
       </c>
       <c r="Z39" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA39" t="n">
-        <v>38.70967741935484</v>
+        <v>39.34426229508197</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.08059302588321</v>
+        <v>12.18024030574959</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.296065932824799</v>
+        <v>4.440424556662226</v>
       </c>
       <c r="AE39" t="n">
         <v>44</v>
@@ -4894,7 +4898,7 @@
         <v>46259</v>
       </c>
       <c r="C40" t="n">
-        <v>0.247317092907253</v>
+        <v>0.2466925604204766</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4954,7 +4958,7 @@
         <v>43.91653617576685</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.147267046451721</v>
+        <v>6.384266762133405</v>
       </c>
       <c r="Z40" t="n">
         <v>5</v>
@@ -5003,7 +5007,7 @@
         <v>46259</v>
       </c>
       <c r="C41" t="n">
-        <v>1.854878147778156</v>
+        <v>1.856959909826956</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,10 +5035,10 @@
         <v>22.39878122993594</v>
       </c>
       <c r="K41" t="n">
-        <v>22.58080459128436</v>
+        <v>22.71837916307777</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5069,22 +5073,22 @@
         <v>26.020221165252</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.729257687508335</v>
+        <v>2.620089039396678</v>
       </c>
       <c r="Z41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA41" t="n">
-        <v>21.42857142857143</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AB41" t="n">
-        <v>16.89080470537415</v>
+        <v>18.18783163318335</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.2783388982700252</v>
+        <v>0.3901327869944571</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5118,7 +5122,7 @@
         <v>46259</v>
       </c>
       <c r="C42" t="n">
-        <v>3.676447787175579</v>
+        <v>3.684774834954423</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5176,18 +5180,22 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.937848301577031</v>
+        <v>4.72253528070028</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>6.491686943496477</v>
+      </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.325096905530014</v>
+        <v>5.539048225986953</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5219,7 +5227,7 @@
         <v>46259</v>
       </c>
       <c r="C43" t="n">
-        <v>6.656535330376705</v>
+        <v>6.60969497230525</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,22 +5255,22 @@
         <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>1.507936507936503</v>
+        <v>0.7936507936507908</v>
       </c>
       <c r="L43" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M43" t="n">
-        <v>71.875</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N43" t="n">
-        <v>18.368861113349</v>
+        <v>17.12829277832295</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.45504300234558</v>
+        <v>3.181102362204724</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5289,7 +5297,7 @@
         <v>20.83229097494805</v>
       </c>
       <c r="Y43" t="n">
-        <v>14.08192503228517</v>
+        <v>14.68650882799231</v>
       </c>
       <c r="Z43" t="n">
         <v>2</v>
@@ -5334,7 +5342,7 @@
         <v>46259</v>
       </c>
       <c r="C44" t="n">
-        <v>4.625745520272935</v>
+        <v>4.646563457193582</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5353,7 +5361,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5366,22 +5374,22 @@
         <v>20.15821391009879</v>
       </c>
       <c r="K44" t="n">
-        <v>3.127004306469261</v>
+        <v>3.591122244012146</v>
       </c>
       <c r="L44" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M44" t="n">
-        <v>78.57142857142857</v>
+        <v>75</v>
       </c>
       <c r="N44" t="n">
-        <v>17.88671937823317</v>
+        <v>18.72301468868908</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.664593565721955</v>
+        <v>6.186705595187547</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5439,7 +5447,7 @@
         <v>46259</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02373244788135759</v>
+        <v>0.02331608935112403</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5499,22 +5507,22 @@
         <v>19.58690552546656</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.724136251486297</v>
+        <v>3.448273365041554</v>
       </c>
       <c r="Z45" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AA45" t="n">
-        <v>53.19148936170212</v>
+        <v>41.46341463414634</v>
       </c>
       <c r="AB45" t="n">
-        <v>13.18215995678039</v>
+        <v>12.12027427869573</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.333334985380121</v>
+        <v>1.607145401785715</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5548,7 +5556,7 @@
         <v>46259</v>
       </c>
       <c r="C46" t="n">
-        <v>9.86770210038642</v>
+        <v>10.00301869037062</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5608,16 +5616,16 @@
         <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>6.138613861386144</v>
+        <v>4.851485148514856</v>
       </c>
       <c r="Z46" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA46" t="n">
-        <v>64.28571428571429</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB46" t="n">
-        <v>14.23125963062444</v>
+        <v>15.95252110668836</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5657,7 +5665,7 @@
         <v>46259</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7194679284981151</v>
+        <v>0.7215496905469156</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5685,7 +5693,7 @@
         <v>20.24791594168004</v>
       </c>
       <c r="K47" t="n">
-        <v>6.830694190623854</v>
+        <v>7.139806071784838</v>
       </c>
       <c r="L47" t="n">
         <v>15</v>
@@ -5694,13 +5702,13 @@
         <v>53.33333333333334</v>
       </c>
       <c r="N47" t="n">
-        <v>12.92127445020113</v>
+        <v>16.17334823117304</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>2.966662187667701</v>
+        <v>2.669590354026607</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5766,7 +5774,7 @@
         <v>46259</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05912293898102162</v>
+        <v>0.05933111814204871</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5794,22 +5802,22 @@
         <v>15.05707226133306</v>
       </c>
       <c r="K48" t="n">
-        <v>2.629922890883529</v>
+        <v>2.991295508888148</v>
       </c>
       <c r="L48" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M48" t="n">
-        <v>50.81967213114754</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N48" t="n">
-        <v>13.8759031246287</v>
+        <v>14.08651342994457</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>7.181216648630206</v>
+        <v>6.80514256712792</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5875,7 +5883,7 @@
         <v>46259</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2600160273507488</v>
+        <v>0.2598078431934168</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5903,7 +5911,7 @@
         <v>16.44500858212767</v>
       </c>
       <c r="K49" t="n">
-        <v>4.627516657811581</v>
+        <v>4.543745701032198</v>
       </c>
       <c r="L49" t="n">
         <v>33</v>
@@ -5912,13 +5920,13 @@
         <v>57.57575757575758</v>
       </c>
       <c r="N49" t="n">
-        <v>17.90458776653778</v>
+        <v>17.95169858271163</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.3560089678957379</v>
+        <v>0.4364242890938508</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5984,7 +5992,7 @@
         <v>46259</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6699212165599634</v>
+        <v>0.6720029784005845</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6012,22 +6020,22 @@
         <v>15.88388393069994</v>
       </c>
       <c r="K50" t="n">
-        <v>0.2492269277668768</v>
+        <v>0.5607486560107455</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>59.09090909090909</v>
+        <v>57.77777777777778</v>
       </c>
       <c r="N50" t="n">
-        <v>14.51295312933297</v>
+        <v>14.30484136865</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.741448375393142</v>
+        <v>3.42007332876364</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6093,7 +6101,7 @@
         <v>46259</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1740379455785058</v>
+        <v>0.1742461297358378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,10 +6126,10 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>21.55982902963817</v>
+        <v>21.84334516173415</v>
       </c>
       <c r="K51" t="n">
-        <v>0.7228851641749134</v>
+        <v>1.209182883165183</v>
       </c>
       <c r="L51" t="n">
         <v>16</v>
@@ -6130,13 +6138,13 @@
         <v>56.25</v>
       </c>
       <c r="N51" t="n">
-        <v>13.98141433611268</v>
+        <v>14.87406187598699</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>3.253595079691673</v>
+        <v>2.757474210671695</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6311,7 +6319,7 @@
         <v>46259</v>
       </c>
       <c r="C53" t="n">
-        <v>1.415619710603959</v>
+        <v>1.398965297572734</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6330,7 +6338,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6343,22 +6351,22 @@
         <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>4.907159967171038</v>
+        <v>3.67295337980964</v>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>16.25373172741129</v>
+        <v>15.20214662953156</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>2.948168679618068</v>
+        <v>4.173746844404125</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6416,7 +6424,7 @@
         <v>46259</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07910815925755969</v>
+        <v>0.0786918009355055</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6445,7 +6453,7 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>43.62153396198496</v>
+        <v>43.91826243778164</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -6457,7 +6465,7 @@
         <v>100</v>
       </c>
       <c r="N54" t="n">
-        <v>22.84645482583484</v>
+        <v>26.85664225430928</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
@@ -6529,7 +6537,7 @@
         <v>46259</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9309781644891926</v>
+        <v>0.9347253995884693</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6589,16 +6597,16 @@
         <v>21.18657262526651</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.787426504602788</v>
+        <v>4.404190988558021</v>
       </c>
       <c r="Z55" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AA55" t="n">
-        <v>42.85714285714285</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AB55" t="n">
-        <v>14.03605547884542</v>
+        <v>13.69780045256787</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6638,11 +6646,11 @@
         <v>46259</v>
       </c>
       <c r="C56" t="n">
-        <v>1.240749008619085</v>
+        <v>1.29071208908008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6652,12 +6660,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -6670,16 +6678,16 @@
         <v>19.65620512594927</v>
       </c>
       <c r="K56" t="n">
-        <v>10.88371808372093</v>
+        <v>15.34883720930231</v>
       </c>
       <c r="L56" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M56" t="n">
-        <v>85.71428571428571</v>
+        <v>100</v>
       </c>
       <c r="N56" t="n">
-        <v>25.91408746801734</v>
+        <v>20.11327023827909</v>
       </c>
       <c r="O56" t="n">
         <v>4</v>
@@ -6704,7 +6712,7 @@
         <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>10.91181299409456</v>
+        <v>7.324366842955444</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6715,7 +6723,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.8870945532258</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6741,7 +6749,7 @@
         <v>46259</v>
       </c>
       <c r="C57" t="n">
-        <v>1.327143478691212</v>
+        <v>1.305284660746165</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6769,22 +6777,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>5.121440018037737</v>
+        <v>3.390029318011933</v>
       </c>
       <c r="L57" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M57" t="n">
-        <v>73.33333333333333</v>
+        <v>70</v>
       </c>
       <c r="N57" t="n">
-        <v>19.34929690151939</v>
+        <v>18.19765533731722</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>4.640880091754029</v>
+        <v>6.393238038125326</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6811,10 +6819,10 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>18.18087109089797</v>
+        <v>19.52847929751788</v>
       </c>
       <c r="Z57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
@@ -6856,7 +6864,7 @@
         <v>46259</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6936536517423796</v>
+        <v>0.6869919183813331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6873,7 +6881,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %76.47: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6884,22 +6896,22 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>4.503185815044897</v>
+        <v>3.49955474133683</v>
       </c>
       <c r="L58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M58" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>15.3426468546036</v>
+        <v>15.02672648546539</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>3.346131658745755</v>
+        <v>4.348274994912349</v>
       </c>
       <c r="Q58" t="n">
         <v>23</v>
@@ -6926,16 +6938,16 @@
         <v>13.39281154402059</v>
       </c>
       <c r="Y58" t="n">
-        <v>7.839673086794074</v>
+        <v>8.724765413231751</v>
       </c>
       <c r="Z58" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA58" t="n">
-        <v>55.55555555555556</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AB58" t="n">
-        <v>16.53962485713378</v>
+        <v>14.91878235739157</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -6975,7 +6987,7 @@
         <v>46259</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8019069397595525</v>
+        <v>0.8039887016001737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,22 +7015,22 @@
         <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>2.526262520134148</v>
+        <v>2.792422158358399</v>
       </c>
       <c r="L59" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M59" t="n">
-        <v>61.81818181818182</v>
+        <v>59.61538461538461</v>
       </c>
       <c r="N59" t="n">
-        <v>13.59018791299919</v>
+        <v>13.64800690827687</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5.338863765555613</v>
+        <v>5.066110645412158</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7084,7 +7096,7 @@
         <v>46259</v>
       </c>
       <c r="C60" t="n">
-        <v>11.6059998332604</v>
+        <v>11.56436395941911</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7112,7 +7124,7 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>1.03487033651235</v>
+        <v>0.6724134025697159</v>
       </c>
       <c r="L60" t="n">
         <v>39</v>
@@ -7121,13 +7133,13 @@
         <v>58.97435897435897</v>
       </c>
       <c r="N60" t="n">
-        <v>13.55750584364111</v>
+        <v>13.51153072974794</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.893787897474613</v>
+        <v>7.278644019517722</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7193,7 +7205,7 @@
         <v>46259</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6207908725201169</v>
+        <v>0.6220399377018492</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7210,11 +7222,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7225,22 +7233,22 @@
         <v>21.86172241533349</v>
       </c>
       <c r="K61" t="n">
-        <v>1.023220784735668</v>
+        <v>1.226485029128344</v>
       </c>
       <c r="L61" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M61" t="n">
-        <v>78.57142857142857</v>
+        <v>72.41379310344827</v>
       </c>
       <c r="N61" t="n">
-        <v>19.13859326488512</v>
+        <v>19.80334666481033</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.885857276707121</v>
+        <v>8.667212902183707</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7259,16 +7267,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.68419436898967</v>
+        <v>11.50649813875594</v>
       </c>
       <c r="Z61" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="n">
-        <v>52.94117647058823</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB61" t="n">
-        <v>11.77948701260922</v>
+        <v>11.49661565783674</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7308,7 +7316,7 @@
         <v>46259</v>
       </c>
       <c r="C62" t="n">
-        <v>9.139074308163794</v>
+        <v>9.159892245084441</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7368,16 +7376,16 @@
         <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.227171492204916</v>
+        <v>2.004454342984419</v>
       </c>
       <c r="Z62" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA62" t="n">
-        <v>47.45762711864407</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="AB62" t="n">
-        <v>15.1354421363008</v>
+        <v>14.43978516274581</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
@@ -7417,7 +7425,7 @@
         <v>46259</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1163722705091042</v>
+        <v>0.1155395538649959</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7477,7 +7485,7 @@
         <v>21.38078415792315</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.443278700023466</v>
+        <v>3.141358278738715</v>
       </c>
       <c r="Z63" t="n">
         <v>7</v>
@@ -7486,13 +7494,13 @@
         <v>14.28571428571429</v>
       </c>
       <c r="AB63" t="n">
-        <v>7.899991244479065</v>
+        <v>8.46117073708481</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>7.745977108784152</v>
+        <v>7.081083937764687</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7526,7 +7534,7 @@
         <v>46259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1461419167665794</v>
+        <v>0.1457255584445252</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7551,25 +7559,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>25.32432448436694</v>
+        <v>25.85620453775692</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>0.4304190947472142</v>
       </c>
       <c r="L64" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M64" t="n">
-        <v>58.62068965517241</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N64" t="n">
-        <v>17.70355895708433</v>
+        <v>15.64561856976326</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>5.000000000000004</v>
+        <v>4.549996849999993</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7635,7 +7643,7 @@
         <v>46259</v>
       </c>
       <c r="C65" t="n">
-        <v>6.937577478805432</v>
+        <v>6.921964026114947</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7663,7 +7671,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>22.46057977480955</v>
+        <v>22.18497456901478</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7701,13 +7709,13 @@
         <v>23.83860580378341</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.112759643916916</v>
+        <v>1.335311572700304</v>
       </c>
       <c r="Z65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA65" t="n">
-        <v>40.74074074074074</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="AB65" t="n">
         <v>9.083640390388112</v>
@@ -7716,7 +7724,7 @@
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.919729932483117</v>
+        <v>2.700751879699248</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7750,7 +7758,7 @@
         <v>46259</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4775634839931363</v>
+        <v>0.4758980507049195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7810,22 +7818,22 @@
         <v>15.2543368949956</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.6926400318959858</v>
+        <v>1.038960026198932</v>
       </c>
       <c r="Z66" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA66" t="n">
-        <v>42.5531914893617</v>
+        <v>39.58333333333334</v>
       </c>
       <c r="AB66" t="n">
-        <v>9.98915149477493</v>
+        <v>9.89303723539031</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>5.344377264493449</v>
+        <v>5.013124331670782</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7956,7 +7964,7 @@
         <v>46259</v>
       </c>
       <c r="C68" t="n">
-        <v>4.667381394114228</v>
+        <v>4.829761365589978</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8013,10 +8021,10 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>145.7315546439382</v>
+        <v>148.6250323553743</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.224163119129097</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8027,7 +8035,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>5.907223159754816</v>
+        <v>7.999999999999996</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8061,7 +8069,7 @@
         <v>46259</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4671545155328131</v>
+        <v>0.4600764138571027</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,7 +8121,7 @@
         <v>25.43142265824418</v>
       </c>
       <c r="Y69" t="n">
-        <v>4.510636042553184</v>
+        <v>5.957445191489352</v>
       </c>
       <c r="Z69" t="n">
         <v>7</v>
@@ -8122,13 +8130,13 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AB69" t="n">
-        <v>18.25732355523538</v>
+        <v>11.41149887926803</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.559717120024517</v>
+        <v>0.04525058745724619</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8154,7 +8162,7 @@
         <v>46259</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4101133731583673</v>
+        <v>0.4107378858681037</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8182,22 +8190,22 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>7.538258820677912</v>
+        <v>7.702016000550449</v>
       </c>
       <c r="L70" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M70" t="n">
-        <v>55.55555555555556</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N70" t="n">
-        <v>9.232269942075462</v>
+        <v>9.073436373158859</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>0.4293738659950419</v>
+        <v>0.2766744862491954</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8224,22 +8232,22 @@
         <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>6.546485603591956</v>
+        <v>6.404176400015837</v>
       </c>
       <c r="Z70" t="n">
         <v>27</v>
       </c>
       <c r="AA70" t="n">
-        <v>22.22222222222222</v>
+        <v>29.62962962962963</v>
       </c>
       <c r="AB70" t="n">
-        <v>11.55268773488956</v>
+        <v>10.36799476306691</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.555334120707941</v>
+        <v>1.705015820796119</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8273,7 +8281,7 @@
         <v>46259</v>
       </c>
       <c r="C71" t="n">
-        <v>3.12893598266787</v>
+        <v>3.124772458778449</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8301,22 +8309,22 @@
         <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>1.220544641252386</v>
+        <v>1.085855354527276</v>
       </c>
       <c r="L71" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M71" t="n">
-        <v>57.74647887323944</v>
+        <v>60</v>
       </c>
       <c r="N71" t="n">
-        <v>17.18276451732391</v>
+        <v>16.91677531245995</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.7700564756988548</v>
+        <v>0.9043249842093593</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8497,7 +8505,7 @@
         <v>46259</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07119734593404584</v>
+        <v>0.07078098761199166</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8514,7 +8522,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8525,22 +8537,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>8.219283658787923</v>
+        <v>7.586422998506892</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>62.5</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N73" t="n">
-        <v>10.17048915836387</v>
+        <v>10.78728381292863</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>1.645470456842646</v>
+        <v>2.243384373441448</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8567,22 +8579,22 @@
         <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.221165560300923</v>
+        <v>6.769579235547751</v>
       </c>
       <c r="Z73" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA73" t="n">
-        <v>52.63157894736842</v>
+        <v>50</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.4822167630246</v>
+        <v>13.29567252782323</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>4.029517387666948</v>
+        <v>3.464985718142299</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8616,7 +8628,7 @@
         <v>46259</v>
       </c>
       <c r="C74" t="n">
-        <v>5.594820547423735</v>
+        <v>5.511548799741149</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8676,22 +8688,22 @@
         <v>33.81594625096176</v>
       </c>
       <c r="Y74" t="n">
-        <v>4.609108013469765</v>
+        <v>6.028879429083245</v>
       </c>
       <c r="Z74" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA74" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB74" t="n">
-        <v>19.63294624302093</v>
+        <v>15.53516040802443</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>5.651369721221878</v>
+        <v>4.225894665074136</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8838,7 +8850,7 @@
         <v>46259</v>
       </c>
       <c r="C76" t="n">
-        <v>1.942313578191022</v>
+        <v>1.946477102080444</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8898,22 +8910,22 @@
         <v>14.64967258969352</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.252481894919534</v>
+        <v>2.042951296291273</v>
       </c>
       <c r="Z76" t="n">
         <v>48</v>
       </c>
       <c r="AA76" t="n">
-        <v>41.66666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="AB76" t="n">
-        <v>11.293656019294</v>
+        <v>11.91303403409348</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.787787699327414</v>
+        <v>1.997864094117641</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -8947,7 +8959,7 @@
         <v>46259</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5329391930793653</v>
+        <v>0.5325228247647014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8975,7 +8987,7 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>9.762043705178524</v>
+        <v>9.676290137520027</v>
       </c>
       <c r="L77" t="n">
         <v>27</v>
@@ -8984,7 +8996,7 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N77" t="n">
-        <v>16.36595029257426</v>
+        <v>15.87760212255727</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
@@ -9017,7 +9029,7 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>5.606650013329295</v>
+        <v>5.680396513042229</v>
       </c>
       <c r="Z77" t="n">
         <v>41</v>
@@ -9026,13 +9038,13 @@
         <v>43.90243902439025</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.63900580344974</v>
+        <v>11.39919723595496</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.654300315955617</v>
+        <v>4.579751533365028</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9066,7 +9078,7 @@
         <v>46259</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0482976121986442</v>
+        <v>0.0480894330376171</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,22 +9106,22 @@
         <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>3.3760804195067</v>
+        <v>2.930494298116493</v>
       </c>
       <c r="L78" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M78" t="n">
-        <v>63.04347826086956</v>
+        <v>62.5</v>
       </c>
       <c r="N78" t="n">
-        <v>17.99693567127776</v>
+        <v>18.54425621787096</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.6035434676584739</v>
+        <v>1.039056218641976</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9175,7 +9187,7 @@
         <v>46259</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8218921400508712</v>
+        <v>0.8264721115712964</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9203,22 +9215,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>3.663368216157559</v>
+        <v>4.241029506496674</v>
       </c>
       <c r="L79" t="n">
         <v>31</v>
       </c>
       <c r="M79" t="n">
-        <v>54.83870967741935</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N79" t="n">
-        <v>11.1415732128032</v>
+        <v>11.54552016276697</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.289396444320934</v>
+        <v>0.7280919011415143</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9284,7 +9296,7 @@
         <v>46259</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1288630307878778</v>
+        <v>0.1286548466305458</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9312,7 +9324,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.503999590040975</v>
+        <v>5.333553022739945</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9323,7 +9335,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.261450207981898</v>
+        <v>4.430161941136324</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9350,7 +9362,7 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.043159470251524</v>
+        <v>6.194951070617161</v>
       </c>
       <c r="Z80" t="n">
         <v>34</v>
@@ -9359,13 +9371,13 @@
         <v>32.35294117647059</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.76250695783027</v>
+        <v>11.41568521312473</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.082701502855344</v>
+        <v>1.924255623747595</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9399,7 +9411,7 @@
         <v>46259</v>
       </c>
       <c r="C81" t="n">
-        <v>1.202235857167333</v>
+        <v>1.209522103238116</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9459,22 +9471,22 @@
         <v>26.61221483076936</v>
       </c>
       <c r="Y81" t="n">
-        <v>5.482812690486149</v>
+        <v>4.909983756338376</v>
       </c>
       <c r="Z81" t="n">
         <v>13</v>
       </c>
       <c r="AA81" t="n">
-        <v>53.84615384615385</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="AB81" t="n">
-        <v>13.83922218726296</v>
+        <v>12.94561142715581</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>4.77922316363636</v>
+        <v>5.3528398087753</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9508,7 +9520,7 @@
         <v>46259</v>
       </c>
       <c r="C82" t="n">
-        <v>5.251324588233069</v>
+        <v>5.209688714391776</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9568,16 +9580,16 @@
         <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>6.07012859960051</v>
+        <v>6.814864943706755</v>
       </c>
       <c r="Z82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA82" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="AB82" t="n">
-        <v>8.470858704440229</v>
+        <v>7.387031692989503</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9617,7 +9629,7 @@
         <v>46259</v>
       </c>
       <c r="C83" t="n">
-        <v>5.907089601233432</v>
+        <v>5.938316506614402</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9677,22 +9689,22 @@
         <v>11.1541503667157</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.810124098895194</v>
+        <v>1.291058675629431</v>
       </c>
       <c r="Z83" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AA83" t="n">
-        <v>57.14285714285715</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.44930613497256</v>
+        <v>11.88178336919071</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>4.267115996077619</v>
+        <v>4.770531687596947</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9835,7 +9847,7 @@
         <v>46259</v>
       </c>
       <c r="C85" t="n">
-        <v>6.292221434265391</v>
+        <v>6.297425918495553</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9863,22 +9875,22 @@
         <v>12.61214035274981</v>
       </c>
       <c r="K85" t="n">
-        <v>1.705529898609148</v>
+        <v>1.789653579253159</v>
       </c>
       <c r="L85" t="n">
         <v>70</v>
       </c>
       <c r="M85" t="n">
-        <v>58.57142857142857</v>
+        <v>55.71428571428572</v>
       </c>
       <c r="N85" t="n">
-        <v>14.54219798356717</v>
+        <v>14.5475432561853</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.188916283771251</v>
+        <v>6.101156848825995</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9944,21 +9956,21 @@
         <v>46259</v>
       </c>
       <c r="C86" t="n">
-        <v>4.509165264001438</v>
+        <v>4.538310248700927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -9972,7 +9984,7 @@
         <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>5.710108613136478</v>
+        <v>6.393365783306648</v>
       </c>
       <c r="L86" t="n">
         <v>33</v>
@@ -9981,13 +9993,13 @@
         <v>51.51515151515152</v>
       </c>
       <c r="N86" t="n">
-        <v>15.52741283158099</v>
+        <v>15.52188244512326</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
       </c>
       <c r="P86" t="n">
-        <v>0.2742324179463518</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>54</v>
@@ -10014,7 +10026,7 @@
         <v>71.56995669069586</v>
       </c>
       <c r="Y86" t="n">
-        <v>12.10256650495314</v>
+        <v>11.5344415407188</v>
       </c>
       <c r="Z86" t="n">
         <v>2</v>
@@ -10059,7 +10071,7 @@
         <v>46259</v>
       </c>
       <c r="C87" t="n">
-        <v>5.678092295106321</v>
+        <v>5.724932653177776</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10087,16 +10099,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>5.29834691435207</v>
+        <v>6.166985889814192</v>
       </c>
       <c r="L87" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M87" t="n">
-        <v>54.16666666666666</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N87" t="n">
-        <v>11.24467722556862</v>
+        <v>10.00840651275545</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10129,16 +10141,16 @@
         <v>10.60669620884278</v>
       </c>
       <c r="Y87" t="n">
-        <v>4.799301919720778</v>
+        <v>4.013961605584648</v>
       </c>
       <c r="Z87" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA87" t="n">
-        <v>40.625</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.6941012351613</v>
+        <v>10.6518545966149</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10178,7 +10190,7 @@
         <v>46259</v>
       </c>
       <c r="C88" t="n">
-        <v>1.103350656794262</v>
+        <v>1.113759625254585</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10195,7 +10207,11 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>5</v>
       </c>
@@ -10238,16 +10254,16 @@
         <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>7.745867190829269</v>
+        <v>6.875545183195586</v>
       </c>
       <c r="Z88" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA88" t="n">
-        <v>58.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.54845664667655</v>
+        <v>12.92170019958537</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
@@ -10396,7 +10412,7 @@
         <v>46259</v>
       </c>
       <c r="C90" t="n">
-        <v>2.881202342828054</v>
+        <v>2.891611311288377</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10456,7 +10472,7 @@
         <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>7.794811275494018</v>
+        <v>7.461700029870966</v>
       </c>
       <c r="Z90" t="n">
         <v>15</v>
@@ -10465,7 +10481,7 @@
         <v>66.66666666666667</v>
       </c>
       <c r="AB90" t="n">
-        <v>15.81985550752225</v>
+        <v>15.78663974645206</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10505,7 +10521,7 @@
         <v>46259</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2285809378124471</v>
+        <v>0.2281645894830027</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10533,22 +10549,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>2.102764739857665</v>
+        <v>1.916789846509492</v>
       </c>
       <c r="L91" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M91" t="n">
-        <v>64.17910447761194</v>
+        <v>63.01369863013699</v>
       </c>
       <c r="N91" t="n">
-        <v>15.1274368629663</v>
+        <v>13.76899662532191</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.8787570664010591</v>
+        <v>1.062837786709991</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10614,7 +10630,7 @@
         <v>46259</v>
       </c>
       <c r="C92" t="n">
-        <v>1.107514260000024</v>
+        <v>1.109596022048824</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10642,7 +10658,7 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>5.111845470010001</v>
+        <v>5.309421120890434</v>
       </c>
       <c r="L92" t="n">
         <v>33</v>
@@ -10651,13 +10667,13 @@
         <v>51.51515151515152</v>
       </c>
       <c r="N92" t="n">
-        <v>12.53228292565582</v>
+        <v>12.48247435301077</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.747696529421173</v>
+        <v>2.554927043061905</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10684,16 +10700,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>8.331603656771158</v>
+        <v>8.159297262646959</v>
       </c>
       <c r="Z92" t="n">
         <v>31</v>
       </c>
       <c r="AA92" t="n">
-        <v>45.16129032258065</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.50569588085053</v>
+        <v>11.49653287937128</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10733,7 +10749,7 @@
         <v>46259</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04184405300232</v>
+        <v>0.04163587384129291</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10761,22 +10777,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>3.468206491952897</v>
+        <v>2.953439807681701</v>
       </c>
       <c r="L93" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M93" t="n">
-        <v>56.89655172413793</v>
+        <v>57.8125</v>
       </c>
       <c r="N93" t="n">
-        <v>20.27323651027488</v>
+        <v>18.58434810914331</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.446928959036332</v>
+        <v>2.95916309159685</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10842,7 +10858,7 @@
         <v>46259</v>
       </c>
       <c r="C94" t="n">
-        <v>7.858771187544038</v>
+        <v>7.780703924091614</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10902,7 +10918,7 @@
         <v>48.9849654478532</v>
       </c>
       <c r="Y94" t="n">
-        <v>7.361963190184051</v>
+        <v>8.282208588957051</v>
       </c>
       <c r="Z94" t="n">
         <v>2</v>
@@ -10947,7 +10963,7 @@
         <v>46259</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1394801734129232</v>
+        <v>0.1384392826040926</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10975,22 +10991,22 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>4.555825161156846</v>
+        <v>3.775562312631697</v>
       </c>
       <c r="L95" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>72.72727272727273</v>
+        <v>60</v>
       </c>
       <c r="N95" t="n">
-        <v>17.79602740297683</v>
+        <v>17.65857382010481</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>1.381247612571745</v>
+        <v>2.143508199615463</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11017,16 +11033,16 @@
         <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>6.66886786408628</v>
+        <v>7.365364830220866</v>
       </c>
       <c r="Z95" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA95" t="n">
-        <v>41.66666666666666</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AB95" t="n">
-        <v>11.37674008022595</v>
+        <v>12.66316037663308</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
@@ -11066,7 +11082,7 @@
         <v>46259</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1284466724658236</v>
+        <v>0.1278221299864374</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11094,22 +11110,22 @@
         <v>14.68867757321659</v>
       </c>
       <c r="K96" t="n">
-        <v>1.480265808950887</v>
+        <v>0.9868412958794925</v>
       </c>
       <c r="L96" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M96" t="n">
-        <v>58.73015873015873</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N96" t="n">
-        <v>12.21880744965162</v>
+        <v>11.92115686351219</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>8.395459080771994</v>
+        <v>8.925082306231392</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11175,7 +11191,7 @@
         <v>46259</v>
       </c>
       <c r="C97" t="n">
-        <v>1.877777846747603</v>
+        <v>1.889227775548666</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11203,16 +11219,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>5.061336847208886</v>
+        <v>5.70195832899314</v>
       </c>
       <c r="L97" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M97" t="n">
-        <v>44.73684210526316</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="N97" t="n">
-        <v>15.70959200841163</v>
+        <v>15.00924480821145</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11245,16 +11261,16 @@
         <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>10.57204377508396</v>
+        <v>10.02674831674559</v>
       </c>
       <c r="Z97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA97" t="n">
-        <v>23.07692307692308</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB97" t="n">
-        <v>12.74324733068823</v>
+        <v>10.42692936952895</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11294,7 +11310,7 @@
         <v>46259</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6553486446856995</v>
+        <v>0.6557650130003634</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11322,7 +11338,7 @@
         <v>11.53029241070767</v>
       </c>
       <c r="K98" t="n">
-        <v>9.43107302990953</v>
+        <v>9.500598818692051</v>
       </c>
       <c r="L98" t="n">
         <v>23</v>
@@ -11331,13 +11347,13 @@
         <v>60.8695652173913</v>
       </c>
       <c r="N98" t="n">
-        <v>12.6215357960826</v>
+        <v>12.6113669921252</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>0.5198952677133883</v>
+        <v>0.4560716440782597</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11364,7 +11380,7 @@
         <v>10.6825105654681</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.130655176834228</v>
+        <v>1.067839662054793</v>
       </c>
       <c r="Z98" t="n">
         <v>52</v>
@@ -11379,7 +11395,7 @@
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>6.94790163265675</v>
+        <v>7.006983688888868</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11522,7 +11538,7 @@
         <v>46259</v>
       </c>
       <c r="C100" t="n">
-        <v>336.9701661966081</v>
+        <v>337.3276085470303</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11550,13 +11566,13 @@
         <v>12.69669682287478</v>
       </c>
       <c r="K100" t="n">
-        <v>9.94645498644684</v>
+        <v>10.06308109532321</v>
       </c>
       <c r="L100" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M100" t="n">
-        <v>60</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N100" t="n">
         <v>11.73954280918841</v>
@@ -11592,22 +11608,22 @@
         <v>11.67288888132132</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.545974060641719</v>
+        <v>1.441538588393565</v>
       </c>
       <c r="Z100" t="n">
         <v>57</v>
       </c>
       <c r="AA100" t="n">
-        <v>31.57894736842105</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB100" t="n">
-        <v>13.91287882775731</v>
+        <v>13.39108595075927</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>6.555370263206473</v>
+        <v>6.654386967564907</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11641,7 +11657,7 @@
         <v>46259</v>
       </c>
       <c r="C101" t="n">
-        <v>347.6187239016155</v>
+        <v>347.8094194566113</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11701,7 +11717,7 @@
         <v>11.75561335839466</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.499275421261481</v>
+        <v>1.445240212426335</v>
       </c>
       <c r="Z101" t="n">
         <v>42</v>
@@ -11710,13 +11726,13 @@
         <v>40.47619047619047</v>
       </c>
       <c r="AB101" t="n">
-        <v>12.70179743752792</v>
+        <v>12.71472642050253</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.569229919868034</v>
+        <v>4.621552320142697</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11750,7 +11766,7 @@
         <v>46259</v>
       </c>
       <c r="C102" t="n">
-        <v>414.2103435867317</v>
+        <v>414.4490993007903</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11810,22 +11826,22 @@
         <v>11.13903673030769</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.850969252873181</v>
+        <v>2.794971408866476</v>
       </c>
       <c r="Z102" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA102" t="n">
-        <v>24.13793103448276</v>
+        <v>30</v>
       </c>
       <c r="AB102" t="n">
-        <v>13.63192783310294</v>
+        <v>13.18934854622082</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.212096951044862</v>
+        <v>2.268430577196145</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11859,7 +11875,7 @@
         <v>46259</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7636019327028725</v>
+        <v>0.7631855643882085</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11919,7 +11935,7 @@
         <v>18.08106682362138</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.5423013942445154</v>
+        <v>0.5965325748836903</v>
       </c>
       <c r="Z103" t="n">
         <v>46</v>
@@ -11934,7 +11950,7 @@
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.498362329212305</v>
+        <v>7.44789655420578</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3924181188650018</v>
+        <v>0.3930426315747381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>18.04725545643595</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5333353599999979</v>
+        <v>0.6933288533333304</v>
       </c>
       <c r="L2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" t="n">
-        <v>60</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N2" t="n">
-        <v>11.16500173156578</v>
+        <v>11.84276532860607</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>9.416443417599552</v>
+        <v>9.242589606132178</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -754,10 +754,10 @@
         <v>55</v>
       </c>
       <c r="AG2" t="n">
-        <v>39.07109157388132</v>
+        <v>39.28629303908279</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.92890842611868</v>
+        <v>15.71370696091721</v>
       </c>
       <c r="AI2" t="n">
         <v>39.82909179893205</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6411924413342788</v>
+        <v>0.6432742429371595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +807,37 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3110183782966347</v>
+        <v>0.6367047485413835</v>
       </c>
       <c r="L3" t="n">
         <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>58.49056603773585</v>
+        <v>62.26415094339622</v>
       </c>
       <c r="N3" t="n">
-        <v>12.992007981713</v>
+        <v>12.24434457600038</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>9.658940541470651</v>
+        <v>9.304055885826635</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
-        <v>59.45945945945946</v>
+        <v>60</v>
       </c>
       <c r="S3" t="n">
-        <v>55.15049442537836</v>
+        <v>57.77439736053181</v>
       </c>
       <c r="T3" t="n">
-        <v>4.308965034081098</v>
+        <v>2.225602639468192</v>
       </c>
       <c r="U3" t="n">
-        <v>43.48596473022936</v>
+        <v>43.5727090128925</v>
       </c>
       <c r="V3" t="n">
         <v>72</v>
@@ -863,10 +863,10 @@
         <v>61.11111111111111</v>
       </c>
       <c r="AG3" t="n">
-        <v>38.43474324065539</v>
+        <v>37.27338044858602</v>
       </c>
       <c r="AH3" t="n">
-        <v>22.67636787045572</v>
+        <v>23.8377306625251</v>
       </c>
       <c r="AI3" t="n">
         <v>44.86445909660515</v>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C4" t="n">
-        <v>1.498891458286545</v>
+        <v>1.51554587131777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,37 +948,37 @@
         <v>18.2305339009923</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.840488750047009</v>
+        <v>0.7498233557904577</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
-        <v>44</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.23044335691964</v>
+        <v>13.33090648938263</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.312501912499993</v>
+        <v>9.320060635629323</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>59.09090909090909</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AG4" t="n">
-        <v>40.1861461049917</v>
+        <v>42.46687392838871</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.90476298591739</v>
+        <v>14.67598321446844</v>
       </c>
       <c r="AI4" t="n">
-        <v>44.4097537410319</v>
+        <v>42.20623987810458</v>
       </c>
       <c r="AJ4" t="n">
         <v>65</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C5" t="n">
-        <v>0.228997306127111</v>
+        <v>0.229413674441775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.08: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1029,22 +1029,22 @@
         <v>18.40585323077206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4566227476491713</v>
+        <v>0.6392753535582107</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>77.77777777777777</v>
+        <v>81.08108108108108</v>
       </c>
       <c r="N5" t="n">
-        <v>11.30960585175055</v>
+        <v>11.02444119157126</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.53181640272726</v>
+        <v>2.345728979216388</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1053,10 +1053,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S5" t="n">
-        <v>42.35647588418864</v>
+        <v>42.51608074608905</v>
       </c>
       <c r="T5" t="n">
-        <v>18.61913387190892</v>
+        <v>18.45952901000851</v>
       </c>
       <c r="U5" t="n">
         <v>45.72685693412379</v>
@@ -1079,25 +1079,25 @@
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF5" t="n">
-        <v>50</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="AG5" t="n">
-        <v>26.86857444890078</v>
+        <v>26.99371723892521</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.13142555109922</v>
+        <v>24.11739387218591</v>
       </c>
       <c r="AI5" t="n">
-        <v>35.8317605399894</v>
+        <v>37.00446464458318</v>
       </c>
       <c r="AJ5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>51.5625</v>
+        <v>52.30769230769231</v>
       </c>
     </row>
     <row r="6">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C6" t="n">
-        <v>1.692498335143265</v>
+        <v>1.700825382922108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>3.420754102309265</v>
+        <v>3.929581522018988</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1176,16 +1176,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.641310225995457</v>
+        <v>7.186907875003246</v>
       </c>
       <c r="Z6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA6" t="n">
-        <v>52.94117647058823</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.70740932634858</v>
+        <v>12.01867986203533</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1200,10 +1200,10 @@
         <v>46.15384615384615</v>
       </c>
       <c r="AG6" t="n">
-        <v>41.27416342503602</v>
+        <v>42.13145232010588</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.879682728810131</v>
+        <v>4.022393833740274</v>
       </c>
       <c r="AI6" t="n">
         <v>33.34047468175682</v>
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C7" t="n">
-        <v>2.204619551747903</v>
+        <v>2.215028520208226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,22 +1253,22 @@
         <v>12.3532304777189</v>
       </c>
       <c r="K7" t="n">
-        <v>3.620356839942174</v>
+        <v>4.109593645149334</v>
       </c>
       <c r="L7" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M7" t="n">
-        <v>50.79365079365079</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>12.45312503184046</v>
+        <v>13.2663916994881</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>4.226624278878788</v>
+        <v>3.736837517693958</v>
       </c>
       <c r="Q7" t="n">
         <v>49</v>
@@ -1277,10 +1277,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S7" t="n">
-        <v>51.82831483228989</v>
+        <v>52.34575381288056</v>
       </c>
       <c r="T7" t="n">
-        <v>9.396174963628475</v>
+        <v>8.878735983037807</v>
       </c>
       <c r="U7" t="n">
         <v>47.24599944352045</v>
@@ -1292,19 +1292,19 @@
         <v>69.11764705882354</v>
       </c>
       <c r="X7" t="n">
-        <v>17.31307710509156</v>
+        <v>16.68422911664862</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.180104662330645</v>
+        <v>8.751304407252558</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.33928912392035</v>
+        <v>11.44657201260894</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3872136346348402</v>
+        <v>0.3845072805599636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,16 +1395,16 @@
         <v>37.55346297625253</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>33.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="X8" t="n">
         <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.727314679906992</v>
+        <v>6.386215202111467</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.410756957199578</v>
+        <v>1.723875176473932</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5770731970759433</v>
+        <v>0.5799877353081518</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,16 +1509,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.210789908875048</v>
+        <v>6.742153171425914</v>
       </c>
       <c r="Z9" t="n">
         <v>33</v>
       </c>
       <c r="AA9" t="n">
-        <v>54.54545454545455</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.26435311358188</v>
+        <v>9.206521977994369</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C10" t="n">
-        <v>1.921495641270376</v>
+        <v>1.927740927000418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,22 +1586,22 @@
         <v>10.84633778363752</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05420384823848767</v>
+        <v>0.379402135501361</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>43.90243902439025</v>
+        <v>44.18604651162791</v>
       </c>
       <c r="N10" t="n">
-        <v>10.11695680133792</v>
+        <v>10.08682753294634</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.942575047401366</v>
+        <v>5.599353796619999</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1642,10 +1642,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="AG10" t="n">
-        <v>41.21864473497867</v>
+        <v>40.96456125040517</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.95376905812477</v>
+        <v>14.20785254269828</v>
       </c>
       <c r="AI10" t="n">
         <v>37.54796321097091</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C11" t="n">
-        <v>8.405242031711007</v>
+        <v>8.332379252488744</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.82524642737302</v>
+        <v>51.86885361383736</v>
       </c>
       <c r="T11" t="n">
-        <v>9.399243368545342</v>
+        <v>9.355636182081007</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1727,16 +1727,16 @@
         <v>23.11730782489165</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.18049666868565</v>
+        <v>3.028467595396733</v>
       </c>
       <c r="Z11" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.4075321336774</v>
+        <v>12.18178350379042</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C12" t="n">
-        <v>7.057280616099149</v>
+        <v>7.098916489940442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1808,16 +1808,16 @@
         <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>7.423356060304886</v>
+        <v>8.057122172755072</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>76.92307692307692</v>
+        <v>75</v>
       </c>
       <c r="N12" t="n">
-        <v>18.25138940387051</v>
+        <v>12.26931455628307</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1850,7 +1850,7 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.520792189676948</v>
+        <v>3.957493028554093</v>
       </c>
       <c r="Z12" t="n">
         <v>11</v>
@@ -1859,7 +1859,7 @@
         <v>27.27272727272727</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.19016848477012</v>
+        <v>9.759433103302454</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2219192044514007</v>
+        <v>0.2217110202940687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1927,7 +1927,7 @@
         <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>5.06098001474804</v>
+        <v>4.962421480136703</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1938,7 +1938,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.0358018796950299</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1963,22 +1963,22 @@
         <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.907757829861652</v>
+        <v>9.992274073350826</v>
       </c>
       <c r="Z13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>13.3233336455564</v>
+        <v>11.78314719884925</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1023863630390642</v>
+        <v>0.008583626093905394</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C14" t="n">
-        <v>8.691488664369896</v>
+        <v>8.623830369377796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,40 +2044,40 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S14" t="n">
-        <v>35.29072284515984</v>
+        <v>36.14774801015613</v>
       </c>
       <c r="T14" t="n">
-        <v>25.68488691093772</v>
+        <v>24.82786174594143</v>
       </c>
       <c r="U14" t="n">
         <v>45.72685693412379</v>
       </c>
       <c r="V14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W14" t="n">
-        <v>58.69565217391305</v>
+        <v>59.57446808510638</v>
       </c>
       <c r="X14" t="n">
         <v>12.90895707120068</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.7236309000578034</v>
+        <v>1.49644095891962</v>
       </c>
       <c r="Z14" t="n">
         <v>47</v>
       </c>
       <c r="AA14" t="n">
-        <v>46.80851063829788</v>
+        <v>51.06382978723404</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.11589101364306</v>
+        <v>11.9718247120839</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.285672624325396</v>
+        <v>0.5112089816677323</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C15" t="n">
-        <v>15.03055045670674</v>
+        <v>14.93686974056383</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,22 +2171,22 @@
         <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.937458854509547</v>
+        <v>5.52995391705069</v>
       </c>
       <c r="Z15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.20717534907267</v>
+        <v>9.567483531887934</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.325484764542932</v>
+        <v>4.731707317073175</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2195,10 +2195,10 @@
         <v>56.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>24.45117694948185</v>
+        <v>23.82980612292542</v>
       </c>
       <c r="AH15" t="n">
-        <v>31.79882305051815</v>
+        <v>32.42019387707458</v>
       </c>
       <c r="AI15" t="n">
         <v>39.32559113685198</v>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C16" t="n">
-        <v>35.8901232511945</v>
+        <v>35.93175912503578</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,22 +2248,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>3.06918132376881</v>
+        <v>3.188751139689638</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>68.1159420289855</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="N16" t="n">
-        <v>18.35529890911982</v>
+        <v>18.36942990324292</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.7244336155728</v>
+        <v>6.600766832704252</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2272,10 +2272,10 @@
         <v>67.85714285714286</v>
       </c>
       <c r="S16" t="n">
-        <v>53.28180661229836</v>
+        <v>53.30881741662009</v>
       </c>
       <c r="T16" t="n">
-        <v>14.5753362448445</v>
+        <v>14.54832544052277</v>
       </c>
       <c r="U16" t="n">
         <v>49.33884318085762</v>
@@ -2290,13 +2290,13 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.3132709235056</v>
+        <v>11.21038608698997</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA16" t="n">
-        <v>51.72413793103448</v>
+        <v>50</v>
       </c>
       <c r="AB16" t="n">
         <v>13.40563990076058</v>
@@ -2314,19 +2314,19 @@
         <v>50</v>
       </c>
       <c r="AG16" t="n">
-        <v>37.23247774461121</v>
+        <v>37.40251450931709</v>
       </c>
       <c r="AH16" t="n">
-        <v>12.76752225538879</v>
+        <v>12.59748549068291</v>
       </c>
       <c r="AI16" t="n">
         <v>33.63088286932749</v>
       </c>
       <c r="AJ16" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AK16" t="n">
-        <v>53.44827586206897</v>
+        <v>53.04347826086956</v>
       </c>
     </row>
     <row r="17">
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C17" t="n">
-        <v>0.684493788226048</v>
+        <v>0.6819955785462439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,25 +2364,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>16.87409721257028</v>
+        <v>14.97831059765675</v>
       </c>
       <c r="K17" t="n">
-        <v>1.044868286377421</v>
+        <v>0.6760829556854198</v>
       </c>
       <c r="L17" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
-        <v>69.09090909090909</v>
+        <v>71.875</v>
       </c>
       <c r="N17" t="n">
-        <v>16.02126973535134</v>
+        <v>15.37873378196714</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.883211222474572</v>
+        <v>7.274733808960709</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2391,10 +2391,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="S17" t="n">
-        <v>47.33511350157781</v>
+        <v>47.37341812108448</v>
       </c>
       <c r="T17" t="n">
-        <v>17.88227780277002</v>
+        <v>17.84397318326335</v>
       </c>
       <c r="U17" t="n">
         <v>50.77005884206276</v>
@@ -2423,10 +2423,10 @@
         <v>56.09756097560975</v>
       </c>
       <c r="AG17" t="n">
-        <v>39.33376648054293</v>
+        <v>39.33818500298902</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.76379449506683</v>
+        <v>16.75937597262073</v>
       </c>
       <c r="AI17" t="n">
         <v>41.04052722210609</v>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09638705023256616</v>
+        <v>0.09617886628341357</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,25 +2473,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>21.20940117548115</v>
+        <v>20.63286244800348</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2164549835086627</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M18" t="n">
-        <v>71.42857142857143</v>
+        <v>72.97297297297297</v>
       </c>
       <c r="N18" t="n">
-        <v>15.8391443743535</v>
+        <v>16.44537530168647</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>9.76241378534224</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2500,10 +2500,10 @@
         <v>77.19298245614036</v>
       </c>
       <c r="S18" t="n">
-        <v>41.50182979771316</v>
+        <v>41.53657511007783</v>
       </c>
       <c r="T18" t="n">
-        <v>35.6911526584272</v>
+        <v>35.65640734606252</v>
       </c>
       <c r="U18" t="n">
         <v>64.79398895432649</v>
@@ -2532,10 +2532,10 @@
         <v>58.53658536585366</v>
       </c>
       <c r="AG18" t="n">
-        <v>40.84872725724959</v>
+        <v>40.94488272190983</v>
       </c>
       <c r="AH18" t="n">
-        <v>17.68785810860407</v>
+        <v>17.59170264394383</v>
       </c>
       <c r="AI18" t="n">
         <v>43.36710313403013</v>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02518970450669969</v>
+        <v>0.02539788366772679</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,22 +2585,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>2.209791412653428</v>
+        <v>3.054499559959467</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M19" t="n">
-        <v>55</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N19" t="n">
-        <v>18.14575358321196</v>
+        <v>16.10894371912864</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.62178307936765</v>
+        <v>6.739638220259847</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C20" t="n">
-        <v>1.607144666779199</v>
+        <v>1.61443107169084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,22 +2694,22 @@
         <v>18.92576555578012</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06480287622621095</v>
+        <v>0.5184724718954925</v>
       </c>
       <c r="L20" t="n">
         <v>27</v>
       </c>
       <c r="M20" t="n">
-        <v>66.66666666666667</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N20" t="n">
-        <v>11.73360702046221</v>
+        <v>12.03046448096047</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.933943872519794</v>
+        <v>1.473885835778832</v>
       </c>
       <c r="Q20" t="n">
         <v>49</v>
@@ -2750,10 +2750,10 @@
         <v>50</v>
       </c>
       <c r="AG20" t="n">
-        <v>40.74517029741634</v>
+        <v>40.66099521324126</v>
       </c>
       <c r="AH20" t="n">
-        <v>9.254829702583663</v>
+        <v>9.339004786758743</v>
       </c>
       <c r="AI20" t="n">
         <v>35.19952693346539</v>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C21" t="n">
-        <v>0.955126968194452</v>
+        <v>0.9701158286506815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,22 +2803,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>2.812221738313658</v>
+        <v>4.42565963311381</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="M21" t="n">
-        <v>54.23728813559322</v>
+        <v>51.06382978723404</v>
       </c>
       <c r="N21" t="n">
-        <v>16.6825238929974</v>
+        <v>15.50139722513888</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.045877011480915</v>
+        <v>3.422856393193197</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2827,10 +2827,10 @@
         <v>72.5</v>
       </c>
       <c r="S21" t="n">
-        <v>46.68344220956758</v>
+        <v>46.744049789912</v>
       </c>
       <c r="T21" t="n">
-        <v>25.81655779043242</v>
+        <v>25.755950210088</v>
       </c>
       <c r="U21" t="n">
         <v>57.16504419378943</v>
@@ -2859,10 +2859,10 @@
         <v>62.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>36.47568474119743</v>
+        <v>36.59706155279163</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.02431525880257</v>
+        <v>25.90293844720837</v>
       </c>
       <c r="AI21" t="n">
         <v>47.0324391373011</v>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C22" t="n">
-        <v>0.33475242401856</v>
+        <v>0.3364178575149562</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.767763082820391</v>
+        <v>8.31387175176136</v>
       </c>
       <c r="Z22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA22" t="n">
-        <v>36.36363636363637</v>
+        <v>50</v>
       </c>
       <c r="AB22" t="n">
-        <v>13.12020963534471</v>
+        <v>10.32220118604125</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7702636660639189</v>
+        <v>0.7631855643882085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,22 +3013,22 @@
         <v>27.73484467032905</v>
       </c>
       <c r="K23" t="n">
-        <v>4.934775277663728</v>
+        <v>3.970509349700957</v>
       </c>
       <c r="L23" t="n">
         <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>66.66666666666667</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N23" t="n">
-        <v>17.27153905628944</v>
+        <v>18.77493995709025</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>4.827022032432415</v>
+        <v>5.799231616745359</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -3055,7 +3055,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>24.16872165075517</v>
+        <v>24.86554992138855</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>43.43546988238708</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>46.66666666666666</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1779933646269352</v>
+        <v>0.1786178971137116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>23.47035234733546</v>
       </c>
       <c r="K24" t="n">
-        <v>5.27999167772093</v>
+        <v>5.649391824451677</v>
       </c>
       <c r="L24" t="n">
         <v>9</v>
@@ -3137,13 +3137,13 @@
         <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>12.74546888007776</v>
+        <v>12.17683750688129</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.483290934072048</v>
+        <v>4.117968026524332</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3170,16 +3170,16 @@
         <v>12.66805408629466</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.557371092000086</v>
+        <v>6.229505176744466</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
-        <v>57.69230769230769</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.83318425402356</v>
+        <v>12.82753207681854</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C25" t="n">
-        <v>3.455777528827312</v>
+        <v>3.478677386429438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,22 +3247,22 @@
         <v>16.84600295124913</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.6626542771084321</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M25" t="n">
-        <v>62.26415094339622</v>
+        <v>60</v>
       </c>
       <c r="N25" t="n">
-        <v>17.02258354059398</v>
+        <v>16.94598916835746</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>8.000000000000007</v>
+        <v>7.289044557371804</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3271,10 +3271,10 @@
         <v>66.66666666666667</v>
       </c>
       <c r="S25" t="n">
-        <v>36.41827758267355</v>
+        <v>36.45417813734804</v>
       </c>
       <c r="T25" t="n">
-        <v>30.24838908399312</v>
+        <v>30.21248852931863</v>
       </c>
       <c r="U25" t="n">
         <v>52.07048830990042</v>
@@ -3303,10 +3303,10 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG25" t="n">
-        <v>54.90570193925618</v>
+        <v>55.11702404082218</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.247165353890324</v>
+        <v>-1.458487455456329</v>
       </c>
       <c r="AI25" t="n">
         <v>38.74647126766948</v>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4375930436482395</v>
+        <v>0.4396748452511202</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,10 +3379,10 @@
         <v>47.91396311978173</v>
       </c>
       <c r="V26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W26" t="n">
-        <v>65</v>
+        <v>66.10169491525424</v>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -3396,19 +3396,19 @@
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF26" t="n">
-        <v>51.35135135135135</v>
+        <v>50</v>
       </c>
       <c r="AG26" t="n">
-        <v>41.99260026050308</v>
+        <v>40.3031191255554</v>
       </c>
       <c r="AH26" t="n">
-        <v>9.358751090848273</v>
+        <v>9.696880874444602</v>
       </c>
       <c r="AI26" t="n">
-        <v>35.89489666561879</v>
+        <v>34.47432540962683</v>
       </c>
       <c r="AJ26" t="n">
         <v>57</v>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C27" t="n">
-        <v>48.92215176351917</v>
+        <v>49.56750780805921</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,10 +3452,10 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>50.20031327035493</v>
+        <v>44.6752281083318</v>
       </c>
       <c r="K27" t="n">
-        <v>48.41445525655774</v>
+        <v>50.37226296419741</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3480,25 +3480,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>48.41445525655774</v>
+        <v>51.25643418700248</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.5845511482254873</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA27" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AB27" t="n">
-        <v>19.54791007974723</v>
+        <v>28.79351225808222</v>
       </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>6.000000000000005</v>
+        <v>5.447291054178905</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C28" t="n">
-        <v>1.620676357420883</v>
+        <v>1.638371572160169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,22 +3582,22 @@
         <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.137026417122168</v>
+        <v>1.068517998001506</v>
       </c>
       <c r="Z28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>46.34146341463415</v>
+        <v>45</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.75570991198495</v>
+        <v>11.58423179027747</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.947329047391324</v>
+        <v>4.984744898392279</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4007452857224443</v>
+        <v>0.3967898666740149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,11 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3659,16 +3663,16 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>10.85912066306292</v>
+        <v>9.764923692604977</v>
       </c>
       <c r="L29" t="n">
         <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>71.42857142857143</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N29" t="n">
-        <v>21.19010258095587</v>
+        <v>20.44925728269125</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3698,13 +3702,13 @@
         <v>100</v>
       </c>
       <c r="X29" t="n">
-        <v>48.55798797437896</v>
+        <v>39.82687732422523</v>
       </c>
       <c r="Y29" t="n">
-        <v>12.51954488212091</v>
+        <v>13.38299074378522</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3743,10 +3747,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C30" t="n">
-        <v>0.417191475042257</v>
+        <v>0.4213550384857588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3763,11 +3767,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>5</v>
       </c>
@@ -3778,17 +3778,13 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>13.96539836996833</v>
+        <v>15.10277100307225</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>100</v>
-      </c>
-      <c r="N30" t="n">
-        <v>9.068551388840314</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>5</v>
       </c>
@@ -3811,31 +3807,31 @@
         <v>51.31119428697273</v>
       </c>
       <c r="V30" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W30" t="n">
-        <v>64.17910447761194</v>
+        <v>65.15151515151516</v>
       </c>
       <c r="X30" t="n">
         <v>18.28742967351311</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.653838210428684</v>
+        <v>2.692305242603443</v>
       </c>
       <c r="Z30" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AA30" t="n">
-        <v>48.38709677419355</v>
+        <v>40</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.16975474939946</v>
+        <v>13.24460465484955</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.58683404890783</v>
+        <v>7.509883751347513</v>
       </c>
       <c r="AE30" t="n">
         <v>50</v>
@@ -3844,10 +3840,10 @@
         <v>58</v>
       </c>
       <c r="AG30" t="n">
-        <v>41.47694845391194</v>
+        <v>41.73438354615648</v>
       </c>
       <c r="AH30" t="n">
-        <v>16.52305154608806</v>
+        <v>16.26561645384352</v>
       </c>
       <c r="AI30" t="n">
         <v>44.23344176857823</v>
@@ -3866,10 +3862,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1917331998718714</v>
+        <v>0.1931904490027562</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3884,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3898,19 +3894,19 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>18.68860738081651</v>
+        <v>17.76611681824961</v>
       </c>
       <c r="K31" t="n">
-        <v>10.10906799327629</v>
+        <v>10.94594102175006</v>
       </c>
       <c r="L31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>87.5</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N31" t="n">
-        <v>15.76876179144892</v>
+        <v>17.65989719586737</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
@@ -3940,10 +3936,10 @@
         <v>87.5</v>
       </c>
       <c r="X31" t="n">
-        <v>10.82639592994425</v>
+        <v>11.90237073875007</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.6472536895645309</v>
+        <v>0.854700137884401</v>
       </c>
       <c r="Z31" t="n">
         <v>21</v>
@@ -3952,13 +3948,13 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.186968181927581</v>
+        <v>9.068575574857265</v>
       </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.413676680070903</v>
+        <v>9.224138587340247</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3989,24 +3985,24 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C32" t="n">
-        <v>2.250418949270439</v>
+        <v>2.337854379683305</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -4020,16 +4016,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>3.259055034027591</v>
+        <v>7.270974647419126</v>
       </c>
       <c r="L32" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="M32" t="n">
-        <v>53.84615384615385</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="N32" t="n">
-        <v>10.25829907235677</v>
+        <v>11.28779196070053</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4059,46 +4055,46 @@
         <v>55.76923076923077</v>
       </c>
       <c r="X32" t="n">
-        <v>16.72680602412306</v>
+        <v>16.29216385551018</v>
       </c>
       <c r="Y32" t="n">
-        <v>8.520085745345085</v>
+        <v>4.965820580816094</v>
       </c>
       <c r="Z32" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="AA32" t="n">
-        <v>50</v>
+        <v>32.25806451612903</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.57267934693818</v>
+        <v>9.183723376607542</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.19272438371937</v>
       </c>
       <c r="AE32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF32" t="n">
-        <v>56</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AG32" t="n">
-        <v>25.2048399966047</v>
+        <v>25.19696153519683</v>
       </c>
       <c r="AH32" t="n">
-        <v>30.7951600033953</v>
+        <v>28.64919231095702</v>
       </c>
       <c r="AI32" t="n">
-        <v>37.06733186979878</v>
+        <v>35.45793874685879</v>
       </c>
       <c r="AJ32" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AK32" t="n">
-        <v>54</v>
+        <v>52.94117647058823</v>
       </c>
     </row>
     <row r="33">
@@ -4108,10 +4104,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C33" t="n">
-        <v>1.747665740993563</v>
+        <v>1.768483677914209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,16 +4135,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>6.648354723111383</v>
+        <v>7.918734218022272</v>
       </c>
       <c r="L33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M33" t="n">
-        <v>64.28571428571429</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N33" t="n">
-        <v>10.92805046826421</v>
+        <v>11.52570662946747</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4217,10 +4213,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7960779428196545</v>
+        <v>0.8010742031302247</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,16 +4244,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>4.892047233644714</v>
+        <v>5.550359622795598</v>
       </c>
       <c r="L34" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M34" t="n">
-        <v>72.72727272727273</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N34" t="n">
-        <v>9.616943003587124</v>
+        <v>10.28060980369725</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4298,19 +4294,19 @@
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF34" t="n">
-        <v>54.05405405405406</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AG34" t="n">
-        <v>30.47347742351565</v>
+        <v>28.99945239964566</v>
       </c>
       <c r="AH34" t="n">
-        <v>23.58057663053841</v>
+        <v>26.5561031559099</v>
       </c>
       <c r="AI34" t="n">
-        <v>38.38404689217949</v>
+        <v>39.5810617556973</v>
       </c>
       <c r="AJ34" t="n">
         <v>50</v>
@@ -4326,14 +4322,14 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C35" t="n">
-        <v>1.983949452032315</v>
+        <v>2.055771270913838</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4343,14 +4339,10 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>5</v>
       </c>
@@ -4361,17 +4353,13 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>11.84564779866479</v>
+        <v>15.89462084616531</v>
       </c>
       <c r="L35" t="n">
-        <v>9</v>
-      </c>
-      <c r="M35" t="n">
-        <v>77.77777777777777</v>
-      </c>
-      <c r="N35" t="n">
-        <v>10.30232128559899</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>6</v>
       </c>
@@ -4403,22 +4391,22 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>4.528241916751141</v>
+        <v>1.072027187927516</v>
       </c>
       <c r="Z35" t="n">
         <v>16</v>
       </c>
       <c r="AA35" t="n">
-        <v>37.5</v>
+        <v>31.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>14.89562390716056</v>
+        <v>15.72761980842392</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.9380287351438032</v>
       </c>
       <c r="AE35" t="n">
         <v>7</v>
@@ -4449,10 +4437,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08139813523334197</v>
+        <v>0.08181449355539616</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4480,16 +4468,16 @@
         <v>14.21000360644873</v>
       </c>
       <c r="K36" t="n">
-        <v>4.272532338489099</v>
+        <v>4.80589512961862</v>
       </c>
       <c r="L36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M36" t="n">
-        <v>61.53846153846154</v>
+        <v>68</v>
       </c>
       <c r="N36" t="n">
-        <v>20.5096675101567</v>
+        <v>19.18020771280047</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4558,10 +4546,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06557650338183003</v>
+        <v>0.06578468254285713</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4586,25 +4574,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>14.02780799500539</v>
+        <v>12.9660944973907</v>
       </c>
       <c r="K37" t="n">
-        <v>6.747475769240485</v>
+        <v>7.086356295059404</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>55.26315789473684</v>
+        <v>56.81818181818182</v>
       </c>
       <c r="N37" t="n">
-        <v>18.8141351286606</v>
+        <v>17.68169419547634</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>1.173352551649232</v>
+        <v>0.853184043748012</v>
       </c>
       <c r="Q37" t="n">
         <v>37</v>
@@ -4631,16 +4619,16 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.808150201163408</v>
+        <v>4.505954164385539</v>
       </c>
       <c r="Z37" t="n">
         <v>57</v>
       </c>
       <c r="AA37" t="n">
-        <v>54.3859649122807</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AB37" t="n">
-        <v>12.86768914035915</v>
+        <v>13.52202384034265</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
@@ -4677,10 +4665,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C38" t="n">
-        <v>1.636289810111368</v>
+        <v>1.64357605639033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4708,22 +4696,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>3.278963887752462</v>
+        <v>3.738855504550442</v>
       </c>
       <c r="L38" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M38" t="n">
-        <v>51.66666666666666</v>
+        <v>50.9433962264151</v>
       </c>
       <c r="N38" t="n">
-        <v>11.3855037388882</v>
+        <v>11.09903794367203</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>6.507652535662767</v>
+        <v>6.035486380679145</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4732,10 +4720,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S38" t="n">
-        <v>58.37035432382478</v>
+        <v>58.78328348480863</v>
       </c>
       <c r="T38" t="n">
-        <v>-7.207563626150367</v>
+        <v>-7.620492787134218</v>
       </c>
       <c r="U38" t="n">
         <v>36.75230846944931</v>
@@ -4764,10 +4752,10 @@
         <v>56.66666666666666</v>
       </c>
       <c r="AG38" t="n">
-        <v>18.53072784867085</v>
+        <v>17.24363659119424</v>
       </c>
       <c r="AH38" t="n">
-        <v>38.13593881799581</v>
+        <v>39.42303007547243</v>
       </c>
       <c r="AI38" t="n">
         <v>39.19730700081361</v>
@@ -4786,10 +4774,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C39" t="n">
-        <v>2.760458562667135</v>
+        <v>2.781276499587782</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4849,37 +4837,37 @@
         <v>11.08431820998319</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.632045178206687</v>
+        <v>0.8902054323803532</v>
       </c>
       <c r="Z39" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AA39" t="n">
-        <v>39.34426229508197</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.18024030574959</v>
+        <v>12.20006929924564</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.440424556662226</v>
+        <v>5.155690807262636</v>
       </c>
       <c r="AE39" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF39" t="n">
-        <v>59.09090909090909</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="AG39" t="n">
-        <v>39.5316764229192</v>
+        <v>40.85929539633004</v>
       </c>
       <c r="AH39" t="n">
-        <v>19.55923266798989</v>
+        <v>18.66451412747949</v>
       </c>
       <c r="AI39" t="n">
-        <v>44.4097537410319</v>
+        <v>44.49431275003934</v>
       </c>
       <c r="AJ39" t="n">
         <v>66</v>
@@ -4895,10 +4883,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2466925604204766</v>
+        <v>0.2479416256022088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4955,19 +4943,19 @@
         <v>76.47058823529412</v>
       </c>
       <c r="X40" t="n">
-        <v>43.91653617576685</v>
+        <v>38.77366535417291</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.384266762133405</v>
+        <v>5.910267251769397</v>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA40" t="n">
-        <v>60</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.63467188629951</v>
+        <v>16.87361600645715</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -5004,19 +4992,19 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C41" t="n">
-        <v>1.856959909826956</v>
+        <v>1.946477102080444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5031,23 +5019,17 @@
       <c r="I41" t="n">
         <v>10</v>
       </c>
-      <c r="J41" t="n">
-        <v>22.39878122993594</v>
-      </c>
-      <c r="K41" t="n">
-        <v>22.71837916307777</v>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>10</v>
       </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
         <v>11</v>
       </c>
@@ -5070,25 +5052,25 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X41" t="n">
-        <v>26.020221165252</v>
+        <v>29.32206318118389</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.620089039396678</v>
+        <v>0.5319148936170248</v>
       </c>
       <c r="Z41" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="n">
-        <v>26.66666666666667</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="AB41" t="n">
-        <v>18.18783163318335</v>
+        <v>15.95500881590366</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.3901327869944571</v>
+        <v>2.48128342245989</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5119,10 +5101,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C42" t="n">
-        <v>3.684774834954423</v>
+        <v>3.695183803414746</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5180,7 +5162,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.72253528070028</v>
+        <v>4.453389900137294</v>
       </c>
       <c r="Z42" t="n">
         <v>3</v>
@@ -5189,13 +5171,13 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB42" t="n">
-        <v>6.491686943496477</v>
+        <v>6.645432670715945</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.539048225986953</v>
+        <v>5.805135414082763</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5224,10 +5206,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C43" t="n">
-        <v>6.60969497230525</v>
+        <v>6.614899456535412</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5241,7 +5223,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -5255,22 +5237,22 @@
         <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7936507936507908</v>
+        <v>0.8730158730158699</v>
       </c>
       <c r="L43" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M43" t="n">
-        <v>73.33333333333333</v>
+        <v>70.96774193548387</v>
       </c>
       <c r="N43" t="n">
-        <v>17.12829277832295</v>
+        <v>17.71277605686696</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.181102362204724</v>
+        <v>3.099921321793864</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5293,23 +5275,17 @@
       <c r="W43" t="n">
         <v>65.21739130434783</v>
       </c>
-      <c r="X43" t="n">
-        <v>20.83229097494805</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>14.68650882799231</v>
-      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>2</v>
       </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
         <v>10</v>
       </c>
@@ -5339,10 +5315,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C44" t="n">
-        <v>4.646563457193582</v>
+        <v>4.64239993330416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5374,7 +5350,7 @@
         <v>20.15821391009879</v>
       </c>
       <c r="K44" t="n">
-        <v>3.591122244012146</v>
+        <v>3.498300072063287</v>
       </c>
       <c r="L44" t="n">
         <v>12</v>
@@ -5389,7 +5365,7 @@
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.186705595187547</v>
+        <v>6.28193885639643</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5431,10 +5407,10 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK44" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -5444,10 +5420,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02331608935112403</v>
+        <v>0.02352426872033049</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,22 +5483,22 @@
         <v>19.58690552546656</v>
       </c>
       <c r="Y45" t="n">
-        <v>3.448273365041554</v>
+        <v>2.586204377229451</v>
       </c>
       <c r="Z45" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA45" t="n">
-        <v>41.46341463414634</v>
+        <v>47.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.12027427869573</v>
+        <v>13.74474632864256</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.607145401785715</v>
+        <v>2.477878628318564</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5553,10 +5529,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C46" t="n">
-        <v>10.00301869037062</v>
+        <v>10.00822317460078</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5616,13 +5592,13 @@
         <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.851485148514856</v>
+        <v>4.801980198019806</v>
       </c>
       <c r="Z46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="n">
-        <v>42.10526315789474</v>
+        <v>40</v>
       </c>
       <c r="AB46" t="n">
         <v>15.95252110668836</v>
@@ -5662,24 +5638,24 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7215496905469156</v>
+        <v>0.7935797331398504</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5693,22 +5669,18 @@
         <v>20.24791594168004</v>
       </c>
       <c r="K47" t="n">
-        <v>7.139806071784838</v>
+        <v>17.8352368866743</v>
       </c>
       <c r="L47" t="n">
-        <v>15</v>
-      </c>
-      <c r="M47" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="N47" t="n">
-        <v>16.17334823117304</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>2.669590354026607</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>52</v>
@@ -5731,17 +5703,27 @@
       <c r="W47" t="n">
         <v>72.46376811594203</v>
       </c>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
+      <c r="X47" t="n">
+        <v>17.8352368866743</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
       <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>31.70731707317073</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>16.00005393557753</v>
+      </c>
       <c r="AC47" t="n">
         <v>8</v>
       </c>
-      <c r="AD47" t="inlineStr"/>
+      <c r="AD47" t="n">
+        <v>7.999999999999996</v>
+      </c>
       <c r="AE47" t="n">
         <v>42</v>
       </c>
@@ -5749,10 +5731,10 @@
         <v>54.76190476190476</v>
       </c>
       <c r="AG47" t="n">
-        <v>32.64690266031537</v>
+        <v>33.26947210508134</v>
       </c>
       <c r="AH47" t="n">
-        <v>22.11500210158939</v>
+        <v>21.49243265682342</v>
       </c>
       <c r="AI47" t="n">
         <v>39.94911903473349</v>
@@ -5771,10 +5753,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05933111814204871</v>
+        <v>0.05912293898102162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5802,22 +5784,22 @@
         <v>15.05707226133306</v>
       </c>
       <c r="K48" t="n">
-        <v>2.991295508888148</v>
+        <v>2.629922890883529</v>
       </c>
       <c r="L48" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M48" t="n">
-        <v>57.89473684210526</v>
+        <v>50.81967213114754</v>
       </c>
       <c r="N48" t="n">
-        <v>14.08651342994457</v>
+        <v>13.8759031246287</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.80514256712792</v>
+        <v>7.181216648630206</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5858,10 +5840,10 @@
         <v>60.37735849056604</v>
       </c>
       <c r="AG48" t="n">
-        <v>24.25553816779807</v>
+        <v>24.35437015342251</v>
       </c>
       <c r="AH48" t="n">
-        <v>36.12182032276797</v>
+        <v>36.02298833714353</v>
       </c>
       <c r="AI48" t="n">
         <v>46.94147867320552</v>
@@ -5880,19 +5862,19 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2598078431934168</v>
+        <v>0.2631387297550698</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5911,22 +5893,22 @@
         <v>16.44500858212767</v>
       </c>
       <c r="K49" t="n">
-        <v>4.543745701032198</v>
+        <v>5.884056884021382</v>
       </c>
       <c r="L49" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M49" t="n">
-        <v>57.57575757575758</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="N49" t="n">
-        <v>17.95169858271163</v>
+        <v>18.40315683214271</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.4364242890938508</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5967,10 +5949,10 @@
         <v>63.04347826086956</v>
       </c>
       <c r="AG49" t="n">
-        <v>38.13302762758735</v>
+        <v>38.50646871132034</v>
       </c>
       <c r="AH49" t="n">
-        <v>24.91045063328222</v>
+        <v>24.53700954954923</v>
       </c>
       <c r="AI49" t="n">
         <v>48.60009642338971</v>
@@ -5989,10 +5971,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6720029784005845</v>
+        <v>0.6757502132916821</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6020,22 +6002,22 @@
         <v>15.88388393069994</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5607486560107455</v>
+        <v>1.121497280868855</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M50" t="n">
-        <v>57.77777777777778</v>
+        <v>56.25</v>
       </c>
       <c r="N50" t="n">
-        <v>14.30484136865</v>
+        <v>14.29162948824343</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.42007332876364</v>
+        <v>2.846578419557999</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6098,10 +6080,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1742461297358378</v>
+        <v>0.173621597040882</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6129,22 +6111,22 @@
         <v>21.84334516173415</v>
       </c>
       <c r="K51" t="n">
-        <v>1.209182883165183</v>
+        <v>0.8464290943944963</v>
       </c>
       <c r="L51" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>56.25</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N51" t="n">
-        <v>14.87406187598699</v>
+        <v>14.93710970110722</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>2.757474210671695</v>
+        <v>3.127102202749987</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6207,10 +6189,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C52" t="n">
-        <v>4.527901280240605</v>
+        <v>4.521655835669703</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6267,16 +6249,16 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X52" t="n">
-        <v>17.40749557792611</v>
+        <v>17.40541420286308</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.100530390182444</v>
+        <v>4.232806865475903</v>
       </c>
       <c r="Z52" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA52" t="n">
-        <v>44.44444444444444</v>
+        <v>48</v>
       </c>
       <c r="AB52" t="n">
         <v>12.14437304511339</v>
@@ -6285,7 +6267,7 @@
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.066205606436791</v>
+        <v>3.933699016564385</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6294,10 +6276,10 @@
         <v>68.42105263157895</v>
       </c>
       <c r="AG52" t="n">
-        <v>41.22689725018098</v>
+        <v>41.83844763423829</v>
       </c>
       <c r="AH52" t="n">
-        <v>27.19415538139796</v>
+        <v>26.58260499734066</v>
       </c>
       <c r="AI52" t="n">
         <v>52.54424010939046</v>
@@ -6316,10 +6298,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C53" t="n">
-        <v>1.398965297572734</v>
+        <v>1.384392805222989</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6351,7 +6333,7 @@
         <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>3.67295337980964</v>
+        <v>2.59303143848344</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -6360,13 +6342,13 @@
         <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>15.20214662953156</v>
+        <v>17.51835792581486</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4.173746844404125</v>
+        <v>5.270307822767362</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6421,10 +6403,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0786918009355055</v>
+        <v>0.07806726345242422</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6453,7 +6435,7 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>43.91826243778164</v>
+        <v>44.36335515147667</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -6534,10 +6516,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9347253995884693</v>
+        <v>0.938056266164903</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6588,25 +6570,25 @@
         <v>56.63145942523844</v>
       </c>
       <c r="V55" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W55" t="n">
-        <v>73.41772151898734</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="X55" t="n">
-        <v>21.18657262526651</v>
+        <v>20.41662385315768</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.404190988558021</v>
+        <v>4.06353812385194</v>
       </c>
       <c r="Z55" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AA55" t="n">
-        <v>40.54054054054054</v>
+        <v>34.21052631578947</v>
       </c>
       <c r="AB55" t="n">
-        <v>13.69780045256787</v>
+        <v>15.27637512355802</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6621,10 +6603,10 @@
         <v>56.52173913043478</v>
       </c>
       <c r="AG55" t="n">
-        <v>42.59801633826019</v>
+        <v>42.91713562477078</v>
       </c>
       <c r="AH55" t="n">
-        <v>13.92372279217459</v>
+        <v>13.604603505664</v>
       </c>
       <c r="AI55" t="n">
         <v>42.24743369429499</v>
@@ -6643,10 +6625,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C56" t="n">
-        <v>1.29071208908008</v>
+        <v>1.280303120619757</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6678,16 +6660,16 @@
         <v>19.65620512594927</v>
       </c>
       <c r="K56" t="n">
-        <v>15.34883720930231</v>
+        <v>14.41860465116278</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M56" t="n">
         <v>100</v>
       </c>
       <c r="N56" t="n">
-        <v>20.11327023827909</v>
+        <v>22.83824298348641</v>
       </c>
       <c r="O56" t="n">
         <v>4</v>
@@ -6712,7 +6694,7 @@
         <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>7.324366842955444</v>
+        <v>8.071750981318704</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6723,7 +6705,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.8870945532258</v>
+        <v>2.097558736585359</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6746,10 +6728,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C57" t="n">
-        <v>1.305284660746165</v>
+        <v>1.310489144976327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6777,22 +6759,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>3.390029318011933</v>
+        <v>3.802270259259144</v>
       </c>
       <c r="L57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M57" t="n">
-        <v>70</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="N57" t="n">
-        <v>18.19765533731722</v>
+        <v>18.18775420284279</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>6.393238038125326</v>
+        <v>5.970707312336487</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6810,19 +6792,19 @@
         <v>69.44100627964798</v>
       </c>
       <c r="V57" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W57" t="n">
-        <v>79.1304347826087</v>
+        <v>78.44827586206897</v>
       </c>
       <c r="X57" t="n">
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>19.52847929751788</v>
+        <v>19.20761996846259</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
@@ -6861,10 +6843,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6869919183813331</v>
+        <v>0.684493788226048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6881,11 +6863,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %76.47: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6896,22 +6874,22 @@
         <v>25.13652524897909</v>
       </c>
       <c r="K58" t="n">
-        <v>3.49955474133683</v>
+        <v>3.123196079990254</v>
       </c>
       <c r="L58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M58" t="n">
         <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>15.02672648546539</v>
+        <v>7.542905425994191</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>4.348274994912349</v>
+        <v>4.729104707176579</v>
       </c>
       <c r="Q58" t="n">
         <v>23</v>
@@ -6938,16 +6916,16 @@
         <v>13.39281154402059</v>
       </c>
       <c r="Y58" t="n">
-        <v>8.724765413231751</v>
+        <v>9.056672397653308</v>
       </c>
       <c r="Z58" t="n">
         <v>17</v>
       </c>
       <c r="AA58" t="n">
-        <v>76.47058823529412</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="AB58" t="n">
-        <v>14.91878235739157</v>
+        <v>15.13397225932492</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -6984,10 +6962,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8039887016001737</v>
+        <v>0.8006578348155609</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7015,22 +6993,22 @@
         <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>2.792422158358399</v>
+        <v>2.36656062075753</v>
       </c>
       <c r="L59" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M59" t="n">
-        <v>59.61538461538461</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N59" t="n">
-        <v>13.64800690827687</v>
+        <v>13.28423488391166</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5.066110645412158</v>
+        <v>5.503202750078673</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7093,10 +7071,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C60" t="n">
-        <v>11.56436395941911</v>
+        <v>11.59559086480008</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7124,7 +7102,7 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>0.6724134025697159</v>
+        <v>0.9442561030266861</v>
       </c>
       <c r="L60" t="n">
         <v>39</v>
@@ -7133,13 +7111,13 @@
         <v>58.97435897435897</v>
       </c>
       <c r="N60" t="n">
-        <v>13.51153072974794</v>
+        <v>13.55750584364111</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>7.278644019517722</v>
+        <v>6.989742823773959</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7180,10 +7158,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="AG60" t="n">
-        <v>25.77078802032711</v>
+        <v>26.2177935778743</v>
       </c>
       <c r="AH60" t="n">
-        <v>35.99391786202583</v>
+        <v>35.54691230447864</v>
       </c>
       <c r="AI60" t="n">
         <v>45.0410173444307</v>
@@ -7202,10 +7180,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6220399377018492</v>
+        <v>0.6249544759340576</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7230,25 +7208,25 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>21.86172241533349</v>
+        <v>18.99064616744801</v>
       </c>
       <c r="K61" t="n">
-        <v>1.226485029128344</v>
+        <v>1.700776859680997</v>
       </c>
       <c r="L61" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M61" t="n">
-        <v>72.41379310344827</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N61" t="n">
-        <v>19.80334666481033</v>
+        <v>15.95116413753036</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.667212902183707</v>
+        <v>8.160432394503392</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7267,16 +7245,16 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.50649813875594</v>
+        <v>11.09186608887585</v>
       </c>
       <c r="Z61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="n">
-        <v>52.63157894736842</v>
+        <v>50</v>
       </c>
       <c r="AB61" t="n">
-        <v>11.49661565783674</v>
+        <v>11.83234893488008</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7313,10 +7291,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C62" t="n">
-        <v>9.159892245084441</v>
+        <v>9.139074308163794</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7376,16 +7354,16 @@
         <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.004454342984419</v>
+        <v>2.227171492204916</v>
       </c>
       <c r="Z62" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AA62" t="n">
-        <v>48.33333333333334</v>
+        <v>47.45762711864407</v>
       </c>
       <c r="AB62" t="n">
-        <v>14.43978516274581</v>
+        <v>15.1354421363008</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
@@ -7422,10 +7400,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1155395538649959</v>
+        <v>0.1159559121870501</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7485,7 +7463,7 @@
         <v>21.38078415792315</v>
       </c>
       <c r="Y63" t="n">
-        <v>3.141358278738715</v>
+        <v>2.792318489381085</v>
       </c>
       <c r="Z63" t="n">
         <v>7</v>
@@ -7500,7 +7478,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>7.081083937764687</v>
+        <v>7.414724226121527</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7531,10 +7509,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1457255584445252</v>
+        <v>0.1463501009239113</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7562,22 +7540,22 @@
         <v>25.85620453775692</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4304190947472142</v>
+        <v>0.8608381894944062</v>
       </c>
       <c r="L64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M64" t="n">
-        <v>66.66666666666667</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N64" t="n">
-        <v>15.64561856976326</v>
+        <v>15.93197460878021</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.549996849999993</v>
+        <v>4.103834436443066</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7618,10 +7596,10 @@
         <v>62</v>
       </c>
       <c r="AG64" t="n">
-        <v>40.09797484696545</v>
+        <v>40.94836139915057</v>
       </c>
       <c r="AH64" t="n">
-        <v>21.90202515303455</v>
+        <v>21.05163860084943</v>
       </c>
       <c r="AI64" t="n">
         <v>48.15044693099298</v>
@@ -7640,10 +7618,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C65" t="n">
-        <v>6.921964026114947</v>
+        <v>6.979213352646725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7671,7 +7649,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>22.18497456901478</v>
+        <v>23.19552699026226</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7685,46 +7663,46 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R65" t="n">
-        <v>67.34693877551021</v>
+        <v>66</v>
       </c>
       <c r="S65" t="n">
-        <v>46.38283798573413</v>
+        <v>46.48220825304647</v>
       </c>
       <c r="T65" t="n">
-        <v>20.96410078977608</v>
+        <v>19.51779174695353</v>
       </c>
       <c r="U65" t="n">
-        <v>53.37920531457014</v>
+        <v>52.1538260502326</v>
       </c>
       <c r="V65" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W65" t="n">
-        <v>63.63636363636363</v>
+        <v>62.6865671641791</v>
       </c>
       <c r="X65" t="n">
         <v>23.83860580378341</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.335311572700304</v>
+        <v>0.5192878338278972</v>
       </c>
       <c r="Z65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA65" t="n">
-        <v>39.28571428571428</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.083640390388112</v>
+        <v>8.779187168866397</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.700751879699248</v>
+        <v>3.498881431767342</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7733,10 +7711,10 @@
         <v>54.54545454545455</v>
       </c>
       <c r="AG65" t="n">
-        <v>20.78146283703997</v>
+        <v>20.852763410836</v>
       </c>
       <c r="AH65" t="n">
-        <v>33.76399170841458</v>
+        <v>33.69269113461854</v>
       </c>
       <c r="AI65" t="n">
         <v>40.06618319896197</v>
@@ -7755,10 +7733,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4758980507049195</v>
+        <v>0.4767307475719878</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7815,25 +7793,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X66" t="n">
-        <v>15.2543368949956</v>
+        <v>14.06774811016638</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.038960026198932</v>
+        <v>0.8658041416015005</v>
       </c>
       <c r="Z66" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AA66" t="n">
-        <v>39.58333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB66" t="n">
-        <v>9.89303723539031</v>
+        <v>10.69839407866415</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>5.013124331670782</v>
+        <v>5.179036168036399</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7864,7 +7842,7 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C67" t="n">
         <v>0.02747967777615017</v>
@@ -7961,10 +7939,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C68" t="n">
-        <v>4.829761365589978</v>
+        <v>4.846415778621203</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8021,10 +7999,10 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>148.6250323553743</v>
+        <v>149.6966919775957</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>0.08583560085837494</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
@@ -8035,7 +8013,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.999999999999996</v>
+        <v>7.920963405674653</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8066,14 +8044,14 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4600764138571027</v>
+        <v>0.4559128106513414</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8083,7 +8061,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -8121,22 +8099,22 @@
         <v>25.43142265824418</v>
       </c>
       <c r="Y69" t="n">
-        <v>5.957445191489352</v>
+        <v>6.808512255319144</v>
       </c>
       <c r="Z69" t="n">
         <v>7</v>
       </c>
       <c r="AA69" t="n">
-        <v>57.14285714285715</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB69" t="n">
-        <v>11.41149887926803</v>
+        <v>10.64993948064956</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.04525058745724619</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8159,10 +8137,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4107378858681037</v>
+        <v>0.4071988351343381</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8190,22 +8168,22 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>7.702016000550449</v>
+        <v>6.774020527356694</v>
       </c>
       <c r="L70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M70" t="n">
-        <v>58.8235294117647</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N70" t="n">
-        <v>9.073436373158859</v>
+        <v>9.21929919714815</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>0.2766744862491954</v>
+        <v>1.148200158229695</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8232,22 +8210,22 @@
         <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>6.404176400015837</v>
+        <v>7.210628348047921</v>
       </c>
       <c r="Z70" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA70" t="n">
-        <v>29.62962962962963</v>
+        <v>20</v>
       </c>
       <c r="AB70" t="n">
-        <v>10.36799476306691</v>
+        <v>14.33323018882474</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.705015820796119</v>
+        <v>0.8507134361389612</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8256,10 +8234,10 @@
         <v>50</v>
       </c>
       <c r="AG70" t="n">
-        <v>34.51648060260157</v>
+        <v>34.67756232778175</v>
       </c>
       <c r="AH70" t="n">
-        <v>15.48351939739843</v>
+        <v>15.32243767221825</v>
       </c>
       <c r="AI70" t="n">
         <v>35.8317605399894</v>
@@ -8278,19 +8256,19 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C71" t="n">
-        <v>3.124772458778449</v>
+        <v>3.162244491256782</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8309,22 +8287,22 @@
         <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>1.085855354527276</v>
+        <v>2.298069205268161</v>
       </c>
       <c r="L71" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M71" t="n">
-        <v>60</v>
+        <v>57.74647887323944</v>
       </c>
       <c r="N71" t="n">
-        <v>16.91677531245995</v>
+        <v>17.78569554032562</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.9043249842093593</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8387,10 +8365,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07078098761199166</v>
+        <v>0.07098916677301874</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8418,22 +8396,22 @@
         <v>21.68783215290538</v>
       </c>
       <c r="K72" t="n">
-        <v>0.6268319472177541</v>
+        <v>0.9227929129847157</v>
       </c>
       <c r="L72" t="n">
         <v>22</v>
       </c>
       <c r="M72" t="n">
-        <v>59.09090909090909</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N72" t="n">
-        <v>16.46682554870169</v>
+        <v>15.64985265414489</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>4.34592639771878</v>
+        <v>4.039926927637283</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8457,10 +8435,10 @@
         <v>74.07407407407408</v>
       </c>
       <c r="X72" t="n">
-        <v>36.68527402492516</v>
+        <v>36.2849179599344</v>
       </c>
       <c r="Y72" t="n">
-        <v>21.19694646628101</v>
+        <v>20.9651730180077</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8502,10 +8480,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07078098761199166</v>
+        <v>0.07119734593404584</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8522,11 +8500,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8537,22 +8511,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>7.586422998506892</v>
+        <v>8.219283658787923</v>
       </c>
       <c r="L73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M73" t="n">
-        <v>85.71428571428571</v>
+        <v>62.5</v>
       </c>
       <c r="N73" t="n">
-        <v>10.78728381292863</v>
+        <v>10.17048915836387</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>2.243384373441448</v>
+        <v>1.645470456842646</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8579,22 +8553,22 @@
         <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.769579235547751</v>
+        <v>6.221165560300923</v>
       </c>
       <c r="Z73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA73" t="n">
-        <v>50</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB73" t="n">
-        <v>13.29567252782323</v>
+        <v>12.4822167630246</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>3.464985718142299</v>
+        <v>4.029517387666948</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8625,10 +8599,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C74" t="n">
-        <v>5.511548799741149</v>
+        <v>5.532366736661796</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8670,10 +8644,10 @@
         <v>74.28571428571429</v>
       </c>
       <c r="S74" t="n">
-        <v>50.78778079812829</v>
+        <v>51.09148801384538</v>
       </c>
       <c r="T74" t="n">
-        <v>23.497933487586</v>
+        <v>23.19422627186891</v>
       </c>
       <c r="U74" t="n">
         <v>57.93069315616084</v>
@@ -8685,25 +8659,25 @@
         <v>77.39130434782609</v>
       </c>
       <c r="X74" t="n">
-        <v>33.81594625096176</v>
+        <v>25.512639367661</v>
       </c>
       <c r="Y74" t="n">
-        <v>6.028879429083245</v>
+        <v>5.67393657517986</v>
       </c>
       <c r="Z74" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AA74" t="n">
-        <v>50</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB74" t="n">
-        <v>15.53516040802443</v>
+        <v>16.4414883283841</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>4.225894665074136</v>
+        <v>4.586286406691931</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8712,10 +8686,10 @@
         <v>51.28205128205128</v>
       </c>
       <c r="AG74" t="n">
-        <v>30.72506574634853</v>
+        <v>30.80984655693579</v>
       </c>
       <c r="AH74" t="n">
-        <v>20.55698553570276</v>
+        <v>20.4722047251155</v>
       </c>
       <c r="AI74" t="n">
         <v>36.19936288445796</v>
@@ -8734,10 +8708,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1240749048797704</v>
+        <v>0.1244912632018246</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8754,11 +8728,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8769,22 +8739,22 @@
         <v>23.35547482758762</v>
       </c>
       <c r="K75" t="n">
-        <v>0.4128530337389247</v>
+        <v>0.7498085771851626</v>
       </c>
       <c r="L75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>80</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>21.88013391565777</v>
+        <v>18.24441559719496</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>5.56417510055589</v>
+        <v>5.211118012986238</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8847,10 +8817,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C76" t="n">
-        <v>1.946477102080444</v>
+        <v>1.969376800841711</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8910,22 +8880,22 @@
         <v>14.64967258969352</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.042951296291273</v>
+        <v>0.8905170321223288</v>
       </c>
       <c r="Z76" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA76" t="n">
-        <v>37.5</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB76" t="n">
-        <v>11.91303403409348</v>
+        <v>11.43604088548736</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.997864094117641</v>
+        <v>3.137422247360011</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -8934,10 +8904,10 @@
         <v>56.25</v>
       </c>
       <c r="AG76" t="n">
-        <v>29.36012542539082</v>
+        <v>29.52316890365169</v>
       </c>
       <c r="AH76" t="n">
-        <v>26.88987457460918</v>
+        <v>26.72683109634831</v>
       </c>
       <c r="AI76" t="n">
         <v>39.32559113685198</v>
@@ -8956,10 +8926,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5325228247647014</v>
+        <v>0.5350209946822461</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8987,16 +8957,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>9.676290137520027</v>
+        <v>10.19080331131783</v>
       </c>
       <c r="L77" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M77" t="n">
-        <v>66.66666666666667</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N77" t="n">
-        <v>15.87760212255727</v>
+        <v>16.90273640953321</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
@@ -9005,19 +8975,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R77" t="n">
-        <v>58.62068965517241</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="S77" t="n">
-        <v>41.28967845879612</v>
+        <v>39.32236800222482</v>
       </c>
       <c r="T77" t="n">
-        <v>17.33101119637629</v>
+        <v>21.39191771206089</v>
       </c>
       <c r="U77" t="n">
-        <v>40.73783598787858</v>
+        <v>42.40904429659717</v>
       </c>
       <c r="V77" t="n">
         <v>75</v>
@@ -9029,22 +8999,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>5.680396513042229</v>
+        <v>5.237924594265831</v>
       </c>
       <c r="Z77" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="AA77" t="n">
-        <v>43.90243902439025</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.39919723595496</v>
+        <v>11.13919768245498</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.579751533365028</v>
+        <v>5.025296655170141</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9075,10 +9045,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0480894330376171</v>
+        <v>0.04850579135967129</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9106,22 +9076,22 @@
         <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>2.930494298116493</v>
+        <v>3.821666540896906</v>
       </c>
       <c r="L78" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M78" t="n">
-        <v>62.5</v>
+        <v>58.13953488372093</v>
       </c>
       <c r="N78" t="n">
-        <v>18.54425621787096</v>
+        <v>18.54781313496884</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>1.039056218641976</v>
+        <v>0.1717690199404043</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9184,19 +9154,19 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8264721115712964</v>
+        <v>0.8327174768258583</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9215,22 +9185,22 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>4.241029506496674</v>
+        <v>5.028743084081166</v>
       </c>
       <c r="L79" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M79" t="n">
-        <v>61.29032258064516</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N79" t="n">
-        <v>11.54552016276697</v>
+        <v>12.07238133735722</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0.7280919011415143</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9271,10 +9241,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>28.28921100399428</v>
+        <v>28.54351673023607</v>
       </c>
       <c r="AH79" t="n">
-        <v>24.4885667737835</v>
+        <v>24.23426104754171</v>
       </c>
       <c r="AI79" t="n">
         <v>37.00593802298759</v>
@@ -9293,10 +9263,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1286548466305458</v>
+        <v>0.1294875632746542</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9324,7 +9294,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>5.333553022739945</v>
+        <v>6.01532292945004</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9335,7 +9305,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.430161941136324</v>
+        <v>3.758585985916074</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9362,22 +9332,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.194951070617161</v>
+        <v>5.587799240813085</v>
       </c>
       <c r="Z80" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA80" t="n">
-        <v>32.35294117647059</v>
+        <v>35</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.41568521312473</v>
+        <v>11.51348611190969</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.924255623747595</v>
+        <v>2.554967196813474</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9408,10 +9378,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C81" t="n">
-        <v>1.209522103238116</v>
+        <v>1.207440341397495</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9468,25 +9438,25 @@
         <v>64.58333333333333</v>
       </c>
       <c r="X81" t="n">
-        <v>26.61221483076936</v>
+        <v>23.65045506047392</v>
       </c>
       <c r="Y81" t="n">
-        <v>4.909983756338376</v>
+        <v>5.073647377457946</v>
       </c>
       <c r="Z81" t="n">
         <v>13</v>
       </c>
       <c r="AA81" t="n">
-        <v>61.53846153846154</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB81" t="n">
-        <v>12.94561142715581</v>
+        <v>10.44751179815941</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>5.3528398087753</v>
+        <v>5.189657546551718</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9517,10 +9487,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C82" t="n">
-        <v>5.209688714391776</v>
+        <v>5.240915619772745</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9580,16 +9550,16 @@
         <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>6.814864943706755</v>
+        <v>6.256312685627075</v>
       </c>
       <c r="Z82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA82" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB82" t="n">
-        <v>7.387031692989503</v>
+        <v>8.227271296602501</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9626,10 +9596,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C83" t="n">
-        <v>5.938316506614402</v>
+        <v>5.99556583314618</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9671,10 +9641,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S83" t="n">
-        <v>58.92640685071011</v>
+        <v>59.24989390507386</v>
       </c>
       <c r="T83" t="n">
-        <v>2.049202905387453</v>
+        <v>1.725715851023701</v>
       </c>
       <c r="U83" t="n">
         <v>45.72685693412379</v>
@@ -9686,25 +9656,25 @@
         <v>61.53846153846154</v>
       </c>
       <c r="X83" t="n">
-        <v>11.1541503667157</v>
+        <v>12.63070246967208</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.291058675629431</v>
+        <v>1.706484641638217</v>
       </c>
       <c r="Z83" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="AA83" t="n">
-        <v>57.37704918032787</v>
+        <v>49.29577464788732</v>
       </c>
       <c r="AB83" t="n">
-        <v>11.88178336919071</v>
+        <v>12.31522583772626</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>4.770531687596947</v>
+        <v>4.368055555555572</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9735,10 +9705,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C84" t="n">
-        <v>2.138002058255684</v>
+        <v>2.146329264667207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9766,22 +9736,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>2.351613772456873</v>
+        <v>2.750258390755822</v>
       </c>
       <c r="L84" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="M84" t="n">
-        <v>49.18032786885246</v>
+        <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>10.92194658681683</v>
+        <v>10.44668109268372</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>2.587537343017265</v>
+        <v>2.189524040599955</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9790,10 +9760,10 @@
         <v>56.09756097560975</v>
       </c>
       <c r="S84" t="n">
-        <v>27.43720037537145</v>
+        <v>27.46024109160858</v>
       </c>
       <c r="T84" t="n">
-        <v>28.66036060023831</v>
+        <v>28.63731988400117</v>
       </c>
       <c r="U84" t="n">
         <v>41.04052722210609</v>
@@ -9822,10 +9792,10 @@
         <v>41.02564102564103</v>
       </c>
       <c r="AG84" t="n">
-        <v>26.93108900276497</v>
+        <v>26.97849257958032</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.09455202287606</v>
+        <v>14.04714844606071</v>
       </c>
       <c r="AI84" t="n">
         <v>27.07931000072518</v>
@@ -9844,10 +9814,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C85" t="n">
-        <v>6.297425918495553</v>
+        <v>6.380697666178139</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9875,22 +9845,22 @@
         <v>12.61214035274981</v>
       </c>
       <c r="K85" t="n">
-        <v>1.789653579253159</v>
+        <v>3.135632469557326</v>
       </c>
       <c r="L85" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M85" t="n">
-        <v>55.71428571428572</v>
+        <v>53.44827586206897</v>
       </c>
       <c r="N85" t="n">
-        <v>14.5475432561853</v>
+        <v>12.81713741108489</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.101156848825995</v>
+        <v>4.716476172169215</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9899,10 +9869,10 @@
         <v>60.60606060606061</v>
       </c>
       <c r="S85" t="n">
-        <v>66.09293694520967</v>
+        <v>66.69675667977876</v>
       </c>
       <c r="T85" t="n">
-        <v>-5.486876339149063</v>
+        <v>-6.090696073718149</v>
       </c>
       <c r="U85" t="n">
         <v>43.68344081994023</v>
@@ -9953,10 +9923,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C86" t="n">
-        <v>4.538310248700927</v>
+        <v>4.550801137842731</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9984,16 +9954,16 @@
         <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>6.393365783306648</v>
+        <v>6.686194537753964</v>
       </c>
       <c r="L86" t="n">
         <v>33</v>
       </c>
       <c r="M86" t="n">
-        <v>51.51515151515152</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N86" t="n">
-        <v>15.52188244512326</v>
+        <v>15.49051857681899</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
@@ -10023,13 +9993,13 @@
         <v>69.23076923076923</v>
       </c>
       <c r="X86" t="n">
-        <v>71.56995669069586</v>
+        <v>70.65007079462626</v>
       </c>
       <c r="Y86" t="n">
-        <v>11.5344415407188</v>
+        <v>11.29095587688633</v>
       </c>
       <c r="Z86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
@@ -10068,10 +10038,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C87" t="n">
-        <v>5.724932653177776</v>
+        <v>5.745750590098422</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10085,7 +10055,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -10099,16 +10069,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>6.166985889814192</v>
+        <v>6.553047656686228</v>
       </c>
       <c r="L87" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M87" t="n">
-        <v>63.63636363636363</v>
+        <v>65</v>
       </c>
       <c r="N87" t="n">
-        <v>10.00840651275545</v>
+        <v>9.279963059448857</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10123,10 +10093,10 @@
         <v>55.31914893617022</v>
       </c>
       <c r="S87" t="n">
-        <v>35.62106096664097</v>
+        <v>35.83121400882089</v>
       </c>
       <c r="T87" t="n">
-        <v>19.69808796952925</v>
+        <v>19.48793492734933</v>
       </c>
       <c r="U87" t="n">
         <v>41.24545983821874</v>
@@ -10141,22 +10111,22 @@
         <v>10.60669620884278</v>
       </c>
       <c r="Y87" t="n">
-        <v>4.013961605584648</v>
+        <v>3.664921465968596</v>
       </c>
       <c r="Z87" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA87" t="n">
-        <v>44.44444444444444</v>
+        <v>45.94594594594594</v>
       </c>
       <c r="AB87" t="n">
-        <v>10.6518545966149</v>
+        <v>11.61928107281155</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>0.3478260869565153</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10165,10 +10135,10 @@
         <v>44.18604651162791</v>
       </c>
       <c r="AG87" t="n">
-        <v>47.19173853599511</v>
+        <v>47.79050654933229</v>
       </c>
       <c r="AH87" t="n">
-        <v>-3.005692024367207</v>
+        <v>-3.604460037704378</v>
       </c>
       <c r="AI87" t="n">
         <v>30.43330983917051</v>
@@ -10187,14 +10157,14 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C88" t="n">
-        <v>1.113759625254585</v>
+        <v>1.131454839785692</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10204,14 +10174,10 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>5</v>
       </c>
@@ -10230,19 +10196,19 @@
       </c>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R88" t="n">
-        <v>70.58823529411765</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="S88" t="n">
-        <v>45.45875949106314</v>
+        <v>46.88783015410829</v>
       </c>
       <c r="T88" t="n">
-        <v>25.12947580305451</v>
+        <v>25.83944257316445</v>
       </c>
       <c r="U88" t="n">
-        <v>53.83109020528557</v>
+        <v>55.78244099712737</v>
       </c>
       <c r="V88" t="n">
         <v>78</v>
@@ -10254,22 +10220,22 @@
         <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>6.875545183195586</v>
+        <v>5.396000433403636</v>
       </c>
       <c r="Z88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA88" t="n">
-        <v>80</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.92170019958537</v>
+        <v>13.81940724482401</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>0.638450350263664</v>
       </c>
       <c r="AE88" t="n">
         <v>32</v>
@@ -10300,10 +10266,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C89" t="n">
-        <v>2.175474408207555</v>
+        <v>2.206701313588524</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10363,43 +10329,43 @@
         <v>27.21456043612742</v>
       </c>
       <c r="Y89" t="n">
-        <v>7.111111111111123</v>
+        <v>5.777777777777793</v>
       </c>
       <c r="Z89" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA89" t="n">
-        <v>64.70588235294117</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.56081322869333</v>
+        <v>13.43823198402062</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>3.110047846889941</v>
+        <v>4.481132075471683</v>
       </c>
       <c r="AE89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF89" t="n">
-        <v>47.61904761904762</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AG89" t="n">
-        <v>63.65744521179305</v>
+        <v>62.58210679307518</v>
       </c>
       <c r="AH89" t="n">
-        <v>-16.03839759274543</v>
+        <v>-17.12756133852972</v>
       </c>
       <c r="AI89" t="n">
-        <v>28.34400610153417</v>
+        <v>26.92029418081331</v>
       </c>
       <c r="AJ89" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AK89" t="n">
-        <v>48.31460674157304</v>
+        <v>47.77777777777778</v>
       </c>
     </row>
     <row r="90">
@@ -10409,10 +10375,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C90" t="n">
-        <v>2.891611311288377</v>
+        <v>2.945738074271474</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10472,16 +10438,16 @@
         <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>7.461700029870966</v>
+        <v>5.72951748867384</v>
       </c>
       <c r="Z90" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA90" t="n">
-        <v>66.66666666666667</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="AB90" t="n">
-        <v>15.78663974645206</v>
+        <v>12.83088714997792</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10518,10 +10484,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2281645894830027</v>
+        <v>0.2300382069285514</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10549,22 +10515,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>1.916789846509492</v>
+        <v>2.753699184121516</v>
       </c>
       <c r="L91" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="M91" t="n">
-        <v>63.01369863013699</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N91" t="n">
-        <v>13.76899662532191</v>
+        <v>12.55561191083563</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>1.062837786709991</v>
+        <v>0.2397001936029097</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10605,10 +10571,10 @@
         <v>40</v>
       </c>
       <c r="AG91" t="n">
-        <v>34.01938528685042</v>
+        <v>34.44675418674255</v>
       </c>
       <c r="AH91" t="n">
-        <v>5.980614713149578</v>
+        <v>5.553245813257455</v>
       </c>
       <c r="AI91" t="n">
         <v>26.34832568429192</v>
@@ -10627,10 +10593,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C92" t="n">
-        <v>1.109596022048824</v>
+        <v>1.114800506278986</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10658,22 +10624,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>5.309421120890434</v>
+        <v>5.803367756080324</v>
       </c>
       <c r="L92" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M92" t="n">
-        <v>51.51515151515152</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N92" t="n">
-        <v>12.48247435301077</v>
+        <v>12.87468424176228</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.554927043061905</v>
+        <v>2.076145864263812</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10700,16 +10666,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>8.159297262646959</v>
+        <v>7.728524729593966</v>
       </c>
       <c r="Z92" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA92" t="n">
-        <v>48.38709677419355</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.49653287937128</v>
+        <v>11.49689035872951</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10724,10 +10690,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.44033871275418</v>
+        <v>40.4828223728849</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.50083775783405</v>
+        <v>12.45835409770333</v>
       </c>
       <c r="AI92" t="n">
         <v>39.52330421009647</v>
@@ -10746,10 +10712,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04163587384129291</v>
+        <v>0.04184405300232</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10777,22 +10743,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>2.953439807681701</v>
+        <v>3.468206491952897</v>
       </c>
       <c r="L93" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="M93" t="n">
-        <v>57.8125</v>
+        <v>56.89655172413793</v>
       </c>
       <c r="N93" t="n">
-        <v>18.58434810914331</v>
+        <v>20.27323651027488</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.95916309159685</v>
+        <v>2.446928959036332</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10855,10 +10821,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C94" t="n">
-        <v>7.780703924091614</v>
+        <v>7.791112892551936</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10867,7 +10833,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10882,17 +10848,27 @@
       <c r="I94" t="n">
         <v>10</v>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>10.06134969325154</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2.114597544338337</v>
+      </c>
       <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="M94" t="n">
+        <v>31.11111111111111</v>
+      </c>
+      <c r="N94" t="n">
+        <v>11.15745031423081</v>
+      </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
-      <c r="P94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>5.763527054108231</v>
+      </c>
       <c r="Q94" t="n">
         <v>41</v>
       </c>
@@ -10900,10 +10876,10 @@
         <v>60.97560975609756</v>
       </c>
       <c r="S94" t="n">
-        <v>38.59318609941483</v>
+        <v>38.21126585164092</v>
       </c>
       <c r="T94" t="n">
-        <v>22.38242365668273</v>
+        <v>22.76434390445664</v>
       </c>
       <c r="U94" t="n">
         <v>45.72685693412379</v>
@@ -10915,16 +10891,20 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>48.9849654478532</v>
+        <v>47.10636343143248</v>
       </c>
       <c r="Y94" t="n">
-        <v>8.282208588957051</v>
+        <v>8.159509202453997</v>
       </c>
       <c r="Z94" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA94" t="inlineStr"/>
-      <c r="AB94" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>7.526956283294056</v>
+      </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
@@ -10960,10 +10940,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1384392826040926</v>
+        <v>0.139271999248201</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10991,22 +10971,22 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>3.775562312631697</v>
+        <v>4.399775587678545</v>
       </c>
       <c r="L95" t="n">
         <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N95" t="n">
-        <v>17.65857382010481</v>
+        <v>17.15024519071062</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>2.143508199615463</v>
+        <v>1.532785298927708</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11033,16 +11013,16 @@
         <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>7.365364830220866</v>
+        <v>6.80816458274932</v>
       </c>
       <c r="Z95" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA95" t="n">
-        <v>40.90909090909091</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB95" t="n">
-        <v>12.66316037663308</v>
+        <v>11.16434066640982</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
@@ -11079,10 +11059,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1278221299864374</v>
+        <v>0.1290712049526</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11110,22 +11090,22 @@
         <v>14.68867757321659</v>
       </c>
       <c r="K96" t="n">
-        <v>0.9868412958794925</v>
+        <v>1.973682427285306</v>
       </c>
       <c r="L96" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M96" t="n">
-        <v>61.29032258064516</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N96" t="n">
-        <v>11.92115686351219</v>
+        <v>13.0999134380232</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>8.925082306231392</v>
+        <v>7.870969628303914</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11188,10 +11168,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C97" t="n">
-        <v>1.889227775548666</v>
+        <v>1.890268735889406</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11219,7 +11199,7 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>5.70195832899314</v>
+        <v>5.76019987508043</v>
       </c>
       <c r="L97" t="n">
         <v>37</v>
@@ -11243,10 +11223,10 @@
         <v>56</v>
       </c>
       <c r="S97" t="n">
-        <v>35.7305919960984</v>
+        <v>35.76568104498055</v>
       </c>
       <c r="T97" t="n">
-        <v>20.2694080039016</v>
+        <v>20.23431895501945</v>
       </c>
       <c r="U97" t="n">
         <v>42.30602802165686</v>
@@ -11261,7 +11241,7 @@
         <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>10.02674831674559</v>
+        <v>9.977173253356275</v>
       </c>
       <c r="Z97" t="n">
         <v>12</v>
@@ -11285,10 +11265,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG97" t="n">
-        <v>54.04129508084883</v>
+        <v>53.57500491159924</v>
       </c>
       <c r="AH97" t="n">
-        <v>-1.409716133480408</v>
+        <v>-0.9434259642308191</v>
       </c>
       <c r="AI97" t="n">
         <v>37.25897138449667</v>
@@ -11307,19 +11287,19 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6557650130003634</v>
+        <v>0.6828283151755717</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11334,68 +11314,58 @@
       <c r="I98" t="n">
         <v>10</v>
       </c>
-      <c r="J98" t="n">
-        <v>11.53029241070767</v>
-      </c>
-      <c r="K98" t="n">
-        <v>9.500598818692051</v>
-      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
-        <v>23</v>
-      </c>
-      <c r="M98" t="n">
-        <v>60.8695652173913</v>
-      </c>
-      <c r="N98" t="n">
-        <v>12.6113669921252</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="n">
-        <v>10</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0.4560716440782597</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
       <c r="Q98" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R98" t="n">
-        <v>67.34693877551021</v>
+        <v>68.75</v>
       </c>
       <c r="S98" t="n">
-        <v>39.42371717975381</v>
+        <v>40.73866450169395</v>
       </c>
       <c r="T98" t="n">
-        <v>27.9232215957564</v>
+        <v>28.01133549830605</v>
       </c>
       <c r="U98" t="n">
-        <v>53.37920531457014</v>
+        <v>54.66692858410841</v>
       </c>
       <c r="V98" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W98" t="n">
-        <v>72.05882352941177</v>
+        <v>72.46376811594203</v>
       </c>
       <c r="X98" t="n">
-        <v>10.6825105654681</v>
+        <v>14.8539646257186</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.067839662054793</v>
+        <v>0.72639731633517</v>
       </c>
       <c r="Z98" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AA98" t="n">
-        <v>42.30769230769231</v>
+        <v>34</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.51563585545586</v>
+        <v>13.49083939623806</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>7.006983688888868</v>
+        <v>7.326824540499599</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11426,10 +11396,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4559128106513414</v>
+        <v>0.4575782439395582</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11457,22 +11427,22 @@
         <v>21.64053449738032</v>
       </c>
       <c r="K99" t="n">
-        <v>3.505821395659536</v>
+        <v>3.883924481269885</v>
       </c>
       <c r="L99" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M99" t="n">
-        <v>58.62068965517241</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N99" t="n">
-        <v>12.59459241398103</v>
+        <v>12.35242564873235</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.4774403967593654</v>
+        <v>0.1117357852138623</v>
       </c>
       <c r="Q99" t="n">
         <v>33</v>
@@ -11513,10 +11483,10 @@
         <v>51.28205128205128</v>
       </c>
       <c r="AG99" t="n">
-        <v>37.9132228715562</v>
+        <v>38.30054388387721</v>
       </c>
       <c r="AH99" t="n">
-        <v>13.36882841049508</v>
+        <v>12.98150739817407</v>
       </c>
       <c r="AI99" t="n">
         <v>36.19936288445796</v>
@@ -11535,10 +11505,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C100" t="n">
-        <v>337.3276085470303</v>
+        <v>342.6394962545406</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11566,16 +11536,16 @@
         <v>12.69669682287478</v>
       </c>
       <c r="K100" t="n">
-        <v>10.06308109532321</v>
+        <v>11.7962411234608</v>
       </c>
       <c r="L100" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M100" t="n">
-        <v>63.1578947368421</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N100" t="n">
-        <v>11.73954280918841</v>
+        <v>10.39378664525568</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11605,25 +11575,25 @@
         <v>64.91228070175438</v>
       </c>
       <c r="X100" t="n">
-        <v>11.67288888132132</v>
+        <v>11.8472509503817</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.441538588393565</v>
+        <v>0.04560668812820801</v>
       </c>
       <c r="Z100" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AA100" t="n">
-        <v>33.33333333333334</v>
+        <v>43.63636363636363</v>
       </c>
       <c r="AB100" t="n">
-        <v>13.39108595075927</v>
+        <v>11.79785461578604</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>6.654386967564907</v>
+        <v>7.958022702466872</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11654,10 +11624,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C101" t="n">
-        <v>347.8094194566113</v>
+        <v>349.1809230312539</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11717,22 +11687,22 @@
         <v>11.75561335839466</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.445240212426335</v>
+        <v>1.056612999402951</v>
       </c>
       <c r="Z101" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA101" t="n">
-        <v>40.47619047619047</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="AB101" t="n">
-        <v>12.71472642050253</v>
+        <v>11.81175403647738</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.621552320142697</v>
+        <v>4.996177258988743</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11763,10 +11733,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C102" t="n">
-        <v>414.4490993007903</v>
+        <v>415.7202539138702</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11826,22 +11796,22 @@
         <v>11.13903673030769</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.794971408866476</v>
+        <v>2.496834386210034</v>
       </c>
       <c r="Z102" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA102" t="n">
-        <v>30</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="AB102" t="n">
-        <v>13.18934854622082</v>
+        <v>13.69804258496672</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.268430577196145</v>
+        <v>2.567265993911427</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11872,10 +11842,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7631855643882085</v>
+        <v>0.772761796219204</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11932,25 +11902,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>18.08106682362138</v>
+        <v>19.04159364785436</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.5965325748836903</v>
+        <v>0.1613807947813739</v>
       </c>
       <c r="Z103" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA103" t="n">
-        <v>39.1304347826087</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB103" t="n">
-        <v>13.04527401977847</v>
+        <v>11.99388688883607</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.44789655420578</v>
+        <v>7.851289678903028</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>
@@ -11959,10 +11929,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="AG103" t="n">
-        <v>38.26204122409825</v>
+        <v>38.6893046122883</v>
       </c>
       <c r="AH103" t="n">
-        <v>23.50266465825469</v>
+        <v>23.07540127006464</v>
       </c>
       <c r="AI103" t="n">
         <v>45.0410173444307</v>
@@ -11981,10 +11951,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04767307471556291</v>
+        <v>0.04746489555453581</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12012,37 +11982,37 @@
         <v>18.611805593619</v>
       </c>
       <c r="K104" t="n">
-        <v>2.422498215368085</v>
+        <v>1.975238837281168</v>
       </c>
       <c r="L104" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M104" t="n">
-        <v>38.77551020408163</v>
+        <v>45.28301886792453</v>
       </c>
       <c r="N104" t="n">
-        <v>13.16720578589455</v>
+        <v>15.97840695207225</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>1.540190692590637</v>
+        <v>1.985541966662785</v>
       </c>
       <c r="Q104" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R104" t="n">
-        <v>60</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="S104" t="n">
-        <v>50.23156808333601</v>
+        <v>50.91613101646293</v>
       </c>
       <c r="T104" t="n">
-        <v>9.768431916663992</v>
+        <v>10.84857486589001</v>
       </c>
       <c r="U104" t="n">
-        <v>43.5727090128925</v>
+        <v>45.0410173444307</v>
       </c>
       <c r="V104" t="n">
         <v>69</v>
@@ -12068,10 +12038,10 @@
         <v>64.28571428571429</v>
       </c>
       <c r="AG104" t="n">
-        <v>42.12299183139859</v>
+        <v>43.128261986993</v>
       </c>
       <c r="AH104" t="n">
-        <v>22.1627224543157</v>
+        <v>21.15745229872129</v>
       </c>
       <c r="AI104" t="n">
         <v>49.16636571945582</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46260</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3930426315747381</v>
+        <v>0.3959571698069466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>18.04725545643595</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6933288533333304</v>
+        <v>1.440002453333311</v>
       </c>
       <c r="L2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M2" t="n">
-        <v>58.06451612903226</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="N2" t="n">
-        <v>11.84276532860607</v>
+        <v>11.37775503601097</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>9.242589606132178</v>
+        <v>8.438483181824319</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -779,7 +779,7 @@
         <v>46260</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6432742429371595</v>
+        <v>0.6457724128547041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6367047485413835</v>
+        <v>1.027529643465996</v>
       </c>
       <c r="L3" t="n">
         <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>62.26415094339622</v>
+        <v>56.60377358490566</v>
       </c>
       <c r="N3" t="n">
-        <v>12.24434457600038</v>
+        <v>13.06613946922564</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>9.304055885826635</v>
+        <v>8.881213257612618</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -888,7 +888,7 @@
         <v>46260</v>
       </c>
       <c r="C4" t="n">
-        <v>1.51554587131777</v>
+        <v>1.54885453874754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,25 +945,25 @@
         <v>63.01369863013699</v>
       </c>
       <c r="X4" t="n">
-        <v>18.2305339009923</v>
+        <v>20.64833628068863</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7498233557904577</v>
+        <v>0.6011983289222922</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>41.66666666666666</v>
+        <v>36.11111111111111</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.33090648938263</v>
+        <v>15.50941848313939</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.320060635629323</v>
+        <v>9.455648874097545</v>
       </c>
       <c r="AE4" t="n">
         <v>42</v>
@@ -997,7 +997,7 @@
         <v>46260</v>
       </c>
       <c r="C5" t="n">
-        <v>0.229413674441775</v>
+        <v>0.2308709235726598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.08: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %79.49: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1029,22 +1029,22 @@
         <v>18.40585323077206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6392753535582107</v>
+        <v>1.278541939992972</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>81.08108108108108</v>
+        <v>79.48717948717949</v>
       </c>
       <c r="N5" t="n">
-        <v>11.02444119157126</v>
+        <v>11.50353668362903</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.345728979216388</v>
+        <v>1.699726345810726</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1110,7 +1110,7 @@
         <v>46260</v>
       </c>
       <c r="C6" t="n">
-        <v>1.700825382922108</v>
+        <v>1.725807002573035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>3.929581522018988</v>
+        <v>5.456092886520403</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1176,16 +1176,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.186907875003246</v>
+        <v>5.823674829815739</v>
       </c>
       <c r="Z6" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
-        <v>48.57142857142857</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.01867986203533</v>
+        <v>11.82269995469782</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1225,7 +1225,7 @@
         <v>46260</v>
       </c>
       <c r="C7" t="n">
-        <v>2.215028520208226</v>
+        <v>2.264991600461042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,22 +1253,22 @@
         <v>12.3532304777189</v>
       </c>
       <c r="K7" t="n">
-        <v>4.109593645149334</v>
+        <v>6.457931797423599</v>
       </c>
       <c r="L7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>53.33333333333334</v>
+        <v>57.5</v>
       </c>
       <c r="N7" t="n">
-        <v>13.2663916994881</v>
+        <v>13.89571591804074</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>3.736837517693958</v>
+        <v>1.448523540275781</v>
       </c>
       <c r="Q7" t="n">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>16.68422911664862</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.751304407252558</v>
+        <v>6.693061879324935</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AA7" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.44657201260894</v>
+        <v>11.52972966061313</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1344,11 +1344,11 @@
         <v>46260</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3845072805599636</v>
+        <v>0.3753474170436321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.386215202111467</v>
+        <v>8.616314696579064</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
@@ -1415,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.723875176473932</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1449,7 +1449,7 @@
         <v>46260</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5799877353081518</v>
+        <v>0.5841512989598331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,16 +1509,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.742153171425914</v>
+        <v>6.072682150485775</v>
       </c>
       <c r="Z9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>51.51515151515152</v>
+        <v>50</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.206521977994369</v>
+        <v>9.575550115304702</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1558,7 +1558,7 @@
         <v>46260</v>
       </c>
       <c r="C10" t="n">
-        <v>1.927740927000418</v>
+        <v>1.951681586310605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,22 +1586,22 @@
         <v>10.84633778363752</v>
       </c>
       <c r="K10" t="n">
-        <v>0.379402135501361</v>
+        <v>1.62601626016261</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>44.18604651162791</v>
+        <v>35.55555555555556</v>
       </c>
       <c r="N10" t="n">
-        <v>10.08682753294634</v>
+        <v>10.32123575410374</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.599353796619999</v>
+        <v>4.303999999999997</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1667,7 +1667,7 @@
         <v>46260</v>
       </c>
       <c r="C11" t="n">
-        <v>8.332379252488744</v>
+        <v>8.410446515941169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,16 +1727,16 @@
         <v>23.11730782489165</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.028467595396733</v>
+        <v>2.119927316777703</v>
       </c>
       <c r="Z11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AA11" t="n">
-        <v>61.29032258064516</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.18178350379042</v>
+        <v>11.4076836700006</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1776,7 +1776,7 @@
         <v>46260</v>
       </c>
       <c r="C12" t="n">
-        <v>7.098916489940442</v>
+        <v>7.182188237623028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,11 +1793,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1808,16 +1804,16 @@
         <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>8.057122172755072</v>
+        <v>9.324654397655419</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N12" t="n">
-        <v>12.26931455628307</v>
+        <v>13.49509280675115</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1850,7 +1846,7 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.957493028554093</v>
+        <v>2.830894706308396</v>
       </c>
       <c r="Z12" t="n">
         <v>11</v>
@@ -1859,7 +1855,7 @@
         <v>27.27272727272727</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.759433103302454</v>
+        <v>9.441911489688975</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1899,11 +1895,11 @@
         <v>46260</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2217110202940687</v>
+        <v>0.2212946717564449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1913,7 +1909,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1927,7 +1923,7 @@
         <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>4.962421480136703</v>
+        <v>4.765313773759505</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1938,7 +1934,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0358018796950299</v>
+        <v>0.2240113810447752</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1963,7 +1959,7 @@
         <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.992274073350826</v>
+        <v>10.1612985314707</v>
       </c>
       <c r="Z13" t="n">
         <v>8</v>
@@ -1978,7 +1974,7 @@
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.008583626093905394</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2002,7 +1998,7 @@
         <v>46260</v>
       </c>
       <c r="C14" t="n">
-        <v>8.623830369377796</v>
+        <v>8.748737990901674</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,22 +2058,22 @@
         <v>12.90895707120068</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49644095891962</v>
+        <v>0.06971469640548733</v>
       </c>
       <c r="Z14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>51.06382978723404</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.9718247120839</v>
+        <v>11.61195342651899</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.5112089816677323</v>
+        <v>1.93163193493362</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2111,7 +2107,7 @@
         <v>46260</v>
       </c>
       <c r="C15" t="n">
-        <v>14.93686974056383</v>
+        <v>14.91605180364319</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2167,7 @@
         <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.52995391705069</v>
+        <v>5.661619486504277</v>
       </c>
       <c r="Z15" t="n">
         <v>10</v>
@@ -2186,7 +2182,7 @@
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.731707317073175</v>
+        <v>4.598743893928825</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2220,7 +2216,7 @@
         <v>46260</v>
       </c>
       <c r="C16" t="n">
-        <v>35.93175912503578</v>
+        <v>35.97339499887708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,22 +2244,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>3.188751139689638</v>
+        <v>3.308320955610489</v>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>65.71428571428571</v>
+        <v>63.76811594202898</v>
       </c>
       <c r="N16" t="n">
-        <v>18.36942990324292</v>
+        <v>18.14434792096311</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.600766832704252</v>
+        <v>6.477386315536782</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2290,7 +2286,7 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.21038608698997</v>
+        <v>11.10750125047431</v>
       </c>
       <c r="Z16" t="n">
         <v>30</v>
@@ -2339,7 +2335,7 @@
         <v>46260</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6819955785462439</v>
+        <v>0.6824119468609078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,25 +2360,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>14.97831059765675</v>
+        <v>15.13508436993211</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6760829556854198</v>
+        <v>0.9236429933767054</v>
       </c>
       <c r="L17" t="n">
         <v>64</v>
       </c>
       <c r="M17" t="n">
-        <v>71.875</v>
+        <v>70.3125</v>
       </c>
       <c r="N17" t="n">
-        <v>15.37873378196714</v>
+        <v>15.59750544488855</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.274733808960709</v>
+        <v>7.011594901590801</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2448,7 +2444,7 @@
         <v>46260</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09617886628341357</v>
+        <v>0.09742794124957614</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,25 +2469,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>20.63286244800348</v>
+        <v>20.97644296643689</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.739128950850621</v>
       </c>
       <c r="L18" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>72.97297297297297</v>
+        <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>16.44537530168647</v>
+        <v>14.85774688515832</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>10.00000000000001</v>
+        <v>8.119659696654313</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2666,16 +2662,16 @@
         <v>46260</v>
       </c>
       <c r="C20" t="n">
-        <v>1.61443107169084</v>
+        <v>1.648780540620492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2694,22 +2690,22 @@
         <v>18.92576555578012</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5184724718954925</v>
+        <v>2.657155384764143</v>
       </c>
       <c r="L20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M20" t="n">
-        <v>62.96296296296296</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="N20" t="n">
-        <v>12.03046448096047</v>
+        <v>15.53051389831679</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.473885835778832</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>49</v>
@@ -2775,7 +2771,7 @@
         <v>46260</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9701158286506815</v>
+        <v>0.9817739020549964</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,22 +2799,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>4.42565963311381</v>
+        <v>5.680563397533489</v>
       </c>
       <c r="L21" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>51.06382978723404</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="N21" t="n">
-        <v>15.50139722513888</v>
+        <v>14.73325745630745</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>3.422856393193197</v>
+        <v>2.194761768766895</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2884,7 +2880,7 @@
         <v>46260</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3364178575149562</v>
+        <v>0.335168792333224</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,16 +2940,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.31387175176136</v>
+        <v>8.65428754088936</v>
       </c>
       <c r="Z22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>50</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.32220118604125</v>
+        <v>12.32494428928839</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
@@ -2985,7 +2981,7 @@
         <v>46260</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7631855643882085</v>
+        <v>0.7627691960735447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,7 +3009,7 @@
         <v>27.73484467032905</v>
       </c>
       <c r="K23" t="n">
-        <v>3.970509349700957</v>
+        <v>3.913786544956355</v>
       </c>
       <c r="L23" t="n">
         <v>9</v>
@@ -3028,7 +3024,7 @@
         <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>5.799231616745359</v>
+        <v>5.856983618252198</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -3055,7 +3051,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>24.86554992138855</v>
+        <v>24.90654074434457</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3100,7 +3096,7 @@
         <v>46260</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1786178971137116</v>
+        <v>0.1779933646269352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3124,7 @@
         <v>23.47035234733546</v>
       </c>
       <c r="K24" t="n">
-        <v>5.649391824451677</v>
+        <v>5.27999167772093</v>
       </c>
       <c r="L24" t="n">
         <v>9</v>
@@ -3137,13 +3133,13 @@
         <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>12.17683750688129</v>
+        <v>12.74546888007776</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.117968026524332</v>
+        <v>4.483290934072048</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3170,16 +3166,16 @@
         <v>12.66805408629466</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.229505176744466</v>
+        <v>6.557371092000086</v>
       </c>
       <c r="Z24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>55.55555555555556</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.82753207681854</v>
+        <v>12.83318425402356</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3219,7 +3215,7 @@
         <v>46260</v>
       </c>
       <c r="C25" t="n">
-        <v>3.478677386429438</v>
+        <v>3.495331481987125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,22 +3243,22 @@
         <v>16.84600295124913</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6626542771084321</v>
+        <v>1.144574638554219</v>
       </c>
       <c r="L25" t="n">
         <v>55</v>
       </c>
       <c r="M25" t="n">
-        <v>60</v>
+        <v>58.18181818181818</v>
       </c>
       <c r="N25" t="n">
-        <v>16.94598916835746</v>
+        <v>16.85239075330353</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.289044557371804</v>
+        <v>6.777847834096917</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3328,7 +3324,7 @@
         <v>46260</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4396748452511202</v>
+        <v>0.4480020121085627</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3423,7 @@
         <v>46260</v>
       </c>
       <c r="C27" t="n">
-        <v>49.56750780805921</v>
+        <v>50.25449972644055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3451,7 @@
         <v>44.6752281083318</v>
       </c>
       <c r="K27" t="n">
-        <v>50.37226296419741</v>
+        <v>52.45638084652357</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3480,25 +3476,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>51.25643418700248</v>
+        <v>54.9825843402522</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5845511482254873</v>
+        <v>1.629991850040746</v>
       </c>
       <c r="Z27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>25</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB27" t="n">
-        <v>28.79351225808222</v>
+        <v>29.81059277025319</v>
       </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.447291054178905</v>
+        <v>4.442419221209615</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3522,7 +3518,7 @@
         <v>46260</v>
       </c>
       <c r="C28" t="n">
-        <v>1.638371572160169</v>
+        <v>1.624840040151164</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,22 +3578,22 @@
         <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.068517998001506</v>
+        <v>1.885606464473921</v>
       </c>
       <c r="Z28" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA28" t="n">
-        <v>45</v>
+        <v>43.18181818181818</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.58423179027747</v>
+        <v>11.82371558975147</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.984744898392279</v>
+        <v>4.193465797692886</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3631,7 +3627,7 @@
         <v>46260</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3967898666740149</v>
+        <v>0.3849236488746275</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3646,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3663,16 +3659,16 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>9.764923692604977</v>
+        <v>6.482343665581092</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
-        <v>85.71428571428571</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
-        <v>20.44925728269125</v>
+        <v>15.4238136460709</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3705,10 +3701,10 @@
         <v>39.82687732422523</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.38299074378522</v>
+        <v>15.97331973978805</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3750,7 +3746,7 @@
         <v>46260</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4213550384857588</v>
+        <v>0.4325967435754099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,10 +3774,10 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>15.10277100307225</v>
+        <v>18.1737000022087</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3813,25 +3809,25 @@
         <v>65.15151515151516</v>
       </c>
       <c r="X30" t="n">
-        <v>18.28742967351311</v>
+        <v>19.87976438285015</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.692305242603443</v>
+        <v>1.423146257772834</v>
       </c>
       <c r="Z30" t="n">
         <v>40</v>
       </c>
       <c r="AA30" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>13.24460465484955</v>
+        <v>12.84109102484534</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>7.509883751347513</v>
+        <v>8.700677102816801</v>
       </c>
       <c r="AE30" t="n">
         <v>50</v>
@@ -3865,7 +3861,7 @@
         <v>46260</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1931904490027562</v>
+        <v>0.1946477181188604</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3884,7 +3880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3897,16 +3893,16 @@
         <v>17.76611681824961</v>
       </c>
       <c r="K31" t="n">
-        <v>10.94594102175006</v>
+        <v>11.78282552739045</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>83.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N31" t="n">
-        <v>17.65989719586737</v>
+        <v>16.66090557653058</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
@@ -3936,10 +3932,10 @@
         <v>87.5</v>
       </c>
       <c r="X31" t="n">
-        <v>11.90237073875007</v>
+        <v>12.26104032611355</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.854700137884401</v>
+        <v>0.4259846491123653</v>
       </c>
       <c r="Z31" t="n">
         <v>21</v>
@@ -3948,13 +3944,13 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.068575574857265</v>
+        <v>9.186968181927581</v>
       </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.224138587340247</v>
+        <v>9.61497366270696</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3988,7 +3984,7 @@
         <v>46260</v>
       </c>
       <c r="C32" t="n">
-        <v>2.337854379683305</v>
+        <v>2.389899221984921</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4016,16 +4012,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>7.270974647419126</v>
+        <v>9.659019432236683</v>
       </c>
       <c r="L32" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M32" t="n">
-        <v>48.14814814814815</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N32" t="n">
-        <v>11.28779196070053</v>
+        <v>10.4033552121596</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4058,22 +4054,22 @@
         <v>16.29216385551018</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.965820580816094</v>
+        <v>2.850188861356773</v>
       </c>
       <c r="Z32" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
-        <v>32.25806451612903</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.183723376607542</v>
+        <v>12.05042040260712</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.19272438371937</v>
+        <v>5.300896706112878</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4107,7 +4103,7 @@
         <v>46260</v>
       </c>
       <c r="C33" t="n">
-        <v>1.768483677914209</v>
+        <v>1.780974567056012</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,16 +4131,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>7.918734218022272</v>
+        <v>8.680969664283712</v>
       </c>
       <c r="L33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M33" t="n">
-        <v>55.55555555555556</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="N33" t="n">
-        <v>11.52570662946747</v>
+        <v>11.21304164856593</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4216,7 +4212,7 @@
         <v>46260</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8010742031302247</v>
+        <v>0.8135650129556882</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4244,16 +4240,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>5.550359622795598</v>
+        <v>7.196161552137337</v>
       </c>
       <c r="L34" t="n">
         <v>19</v>
       </c>
       <c r="M34" t="n">
-        <v>73.68421052631579</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N34" t="n">
-        <v>10.28060980369725</v>
+        <v>8.8967926345666</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4325,11 +4321,11 @@
         <v>46260</v>
       </c>
       <c r="C35" t="n">
-        <v>2.055771270913838</v>
+        <v>2.021421643143328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4339,10 +4335,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>BAZ_ORAN_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>5</v>
       </c>
@@ -4353,13 +4353,17 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>15.89462084616531</v>
+        <v>13.95815196803931</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>75</v>
+      </c>
+      <c r="N35" t="n">
+        <v>10.09458095312001</v>
+      </c>
       <c r="O35" t="n">
         <v>6</v>
       </c>
@@ -4391,22 +4395,22 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.072027187927516</v>
+        <v>2.725002443620861</v>
       </c>
       <c r="Z35" t="n">
         <v>16</v>
       </c>
       <c r="AA35" t="n">
-        <v>31.25</v>
+        <v>37.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>15.72761980842392</v>
+        <v>13.67575307230967</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.9380287351438032</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>7</v>
@@ -4549,21 +4553,21 @@
         <v>46260</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06578468254285713</v>
+        <v>0.0672419366700468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4577,22 +4581,22 @@
         <v>12.9660944973907</v>
       </c>
       <c r="K37" t="n">
-        <v>7.086356295059404</v>
+        <v>9.458519975791834</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M37" t="n">
-        <v>56.81818181818182</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N37" t="n">
-        <v>17.68169419547634</v>
+        <v>17.15751421834236</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.853184043748012</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>37</v>
@@ -4619,22 +4623,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.505954164385539</v>
+        <v>2.390581906940503</v>
       </c>
       <c r="Z37" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="AA37" t="n">
-        <v>57.89473684210526</v>
+        <v>49.29577464788732</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.52202384034265</v>
+        <v>13.52819482318692</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.648834840430158</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4668,7 +4672,7 @@
         <v>46260</v>
       </c>
       <c r="C38" t="n">
-        <v>1.64357605639033</v>
+        <v>1.668557676041257</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4696,22 +4700,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>3.738855504550442</v>
+        <v>5.315639627902069</v>
       </c>
       <c r="L38" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M38" t="n">
-        <v>50.9433962264151</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="N38" t="n">
-        <v>11.09903794367203</v>
+        <v>10.25753574761961</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>6.035486380679145</v>
+        <v>4.447924722907803</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4777,7 +4781,7 @@
         <v>46260</v>
       </c>
       <c r="C39" t="n">
-        <v>2.781276499587782</v>
+        <v>2.829157500526438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4834,25 +4838,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X39" t="n">
-        <v>11.08431820998319</v>
+        <v>13.14448726963784</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.8902054323803532</v>
+        <v>1.019671608812822</v>
       </c>
       <c r="Z39" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AA39" t="n">
-        <v>46.55172413793103</v>
+        <v>37.3134328358209</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.20006929924564</v>
+        <v>12.61575624381794</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.155690807262636</v>
+        <v>5.031634540051311</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4886,11 +4890,11 @@
         <v>46260</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2479416256022088</v>
+        <v>0.2539788264764787</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4900,7 +4904,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4946,22 +4950,22 @@
         <v>38.77366535417291</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.910267251769397</v>
+        <v>3.619249697021287</v>
       </c>
       <c r="Z40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="n">
-        <v>42.85714285714285</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB40" t="n">
-        <v>16.87361600645715</v>
+        <v>17.08312770763141</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.432599661901623</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4995,11 +4999,11 @@
         <v>46260</v>
       </c>
       <c r="C41" t="n">
-        <v>1.946477102080444</v>
+        <v>1.882982330977764</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5009,7 +5013,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -5052,25 +5056,25 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X41" t="n">
-        <v>29.32206318118389</v>
+        <v>29.59721231101309</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.5319148936170248</v>
+        <v>3.980891848638213</v>
       </c>
       <c r="Z41" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AA41" t="n">
-        <v>21.42857142857143</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB41" t="n">
-        <v>15.95500881590366</v>
+        <v>12.8276595140947</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.48128342245989</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5104,7 +5108,7 @@
         <v>46260</v>
       </c>
       <c r="C42" t="n">
-        <v>3.695183803414746</v>
+        <v>3.738901597937519</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5162,22 +5166,22 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.453389900137294</v>
+        <v>3.322976018199075</v>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>33.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="AB42" t="n">
-        <v>6.645432670715945</v>
+        <v>7.843680062354141</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.805135414082763</v>
+        <v>6.906526190812256</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5209,7 +5213,7 @@
         <v>46260</v>
       </c>
       <c r="C43" t="n">
-        <v>6.614899456535412</v>
+        <v>6.630512909225897</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5237,7 +5241,7 @@
         <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8730158730158699</v>
+        <v>1.111111111111107</v>
       </c>
       <c r="L43" t="n">
         <v>31</v>
@@ -5246,13 +5250,13 @@
         <v>70.96774193548387</v>
       </c>
       <c r="N43" t="n">
-        <v>17.71277605686696</v>
+        <v>17.76152976155454</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.099921321793864</v>
+        <v>2.857142857142869</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5318,7 +5322,7 @@
         <v>46260</v>
       </c>
       <c r="C44" t="n">
-        <v>4.64239993330416</v>
+        <v>4.702771823384619</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5335,11 +5339,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5350,22 +5350,22 @@
         <v>20.15821391009879</v>
       </c>
       <c r="K44" t="n">
-        <v>3.498300072063287</v>
+        <v>4.844239259818228</v>
       </c>
       <c r="L44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M44" t="n">
-        <v>75</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N44" t="n">
-        <v>18.72301468868908</v>
+        <v>19.82944032395692</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>6.28193885639643</v>
+        <v>4.917543182706585</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5532,7 +5532,7 @@
         <v>46260</v>
       </c>
       <c r="C46" t="n">
-        <v>10.00822317460078</v>
+        <v>10.08108595382305</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5592,16 +5592,16 @@
         <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.801980198019806</v>
+        <v>4.108910891089113</v>
       </c>
       <c r="Z46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA46" t="n">
-        <v>40</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB46" t="n">
-        <v>15.95252110668836</v>
+        <v>14.78260926109439</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5756,7 +5756,7 @@
         <v>46260</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05912293898102162</v>
+        <v>0.05933111814204871</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5784,22 +5784,22 @@
         <v>15.05707226133306</v>
       </c>
       <c r="K48" t="n">
-        <v>2.629922890883529</v>
+        <v>2.991295508888148</v>
       </c>
       <c r="L48" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M48" t="n">
-        <v>50.81967213114754</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N48" t="n">
-        <v>13.8759031246287</v>
+        <v>14.08651342994457</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>7.181216648630206</v>
+        <v>6.80514256712792</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5865,7 +5865,7 @@
         <v>46260</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2631387297550698</v>
+        <v>0.2741722309103488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5893,16 +5893,16 @@
         <v>16.44500858212767</v>
       </c>
       <c r="K49" t="n">
-        <v>5.884056884021382</v>
+        <v>10.32381330088523</v>
       </c>
       <c r="L49" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="M49" t="n">
-        <v>65.51724137931035</v>
+        <v>62.5</v>
       </c>
       <c r="N49" t="n">
-        <v>18.40315683214271</v>
+        <v>22.7101407218383</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5931,17 +5931,27 @@
       <c r="W49" t="n">
         <v>67.6056338028169</v>
       </c>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
+      <c r="X49" t="n">
+        <v>12.16673414089682</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.643019077025665</v>
+      </c>
       <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>40.32258064516129</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>10.52451268096039</v>
+      </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
-      <c r="AD49" t="inlineStr"/>
+      <c r="AD49" t="n">
+        <v>8.496581375874968</v>
+      </c>
       <c r="AE49" t="n">
         <v>46</v>
       </c>
@@ -5974,7 +5984,7 @@
         <v>46260</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6757502132916821</v>
+        <v>0.693237283635895</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6002,22 +6012,22 @@
         <v>15.88388393069994</v>
       </c>
       <c r="K50" t="n">
-        <v>1.121497280868855</v>
+        <v>3.738320333944856</v>
       </c>
       <c r="L50" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M50" t="n">
-        <v>56.25</v>
+        <v>54.34782608695652</v>
       </c>
       <c r="N50" t="n">
-        <v>14.29162948824343</v>
+        <v>16.35052689205138</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.846578419557999</v>
+        <v>0.2522497619132258</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6083,7 +6093,7 @@
         <v>46260</v>
       </c>
       <c r="C51" t="n">
-        <v>0.173621597040882</v>
+        <v>0.1750788463799462</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6111,22 +6121,22 @@
         <v>21.84334516173415</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8464290943944963</v>
+        <v>1.692858309708001</v>
       </c>
       <c r="L51" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M51" t="n">
-        <v>53.33333333333334</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N51" t="n">
-        <v>14.93710970110722</v>
+        <v>15.19944145636646</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>3.127102202749987</v>
+        <v>2.268735217634998</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6192,7 +6202,7 @@
         <v>46260</v>
       </c>
       <c r="C52" t="n">
-        <v>4.521655835669703</v>
+        <v>4.527901280240605</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6252,13 +6262,13 @@
         <v>17.40541420286308</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.232806865475903</v>
+        <v>4.100530390182444</v>
       </c>
       <c r="Z52" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA52" t="n">
-        <v>48</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB52" t="n">
         <v>12.14437304511339</v>
@@ -6267,7 +6277,7 @@
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.933699016564385</v>
+        <v>4.066205606436791</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6301,7 +6311,7 @@
         <v>46260</v>
       </c>
       <c r="C53" t="n">
-        <v>1.384392805222989</v>
+        <v>1.381270082833449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6333,7 +6343,7 @@
         <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>2.59303143848344</v>
+        <v>2.361616225203589</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -6342,13 +6352,13 @@
         <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>17.51835792581486</v>
+        <v>16.71756518363199</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>5.270307822767362</v>
+        <v>5.508298894374164</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6519,11 +6529,11 @@
         <v>46260</v>
       </c>
       <c r="C55" t="n">
-        <v>0.938056266164903</v>
+        <v>0.9563759936139247</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6533,7 +6543,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6579,22 +6589,22 @@
         <v>20.41662385315768</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.06353812385194</v>
+        <v>2.18995132806209</v>
       </c>
       <c r="Z55" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA55" t="n">
-        <v>34.21052631578947</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="AB55" t="n">
-        <v>15.27637512355802</v>
+        <v>13.34520534258593</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>0.8281855319946518</v>
       </c>
       <c r="AE55" t="n">
         <v>46</v>
@@ -6628,7 +6638,7 @@
         <v>46260</v>
       </c>
       <c r="C56" t="n">
-        <v>1.280303120619757</v>
+        <v>1.28967120805568</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6660,16 +6670,16 @@
         <v>19.65620512594927</v>
       </c>
       <c r="K56" t="n">
-        <v>14.41860465116278</v>
+        <v>15.25581536744185</v>
       </c>
       <c r="L56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M56" t="n">
         <v>100</v>
       </c>
       <c r="N56" t="n">
-        <v>22.83824298348641</v>
+        <v>20.11327023827909</v>
       </c>
       <c r="O56" t="n">
         <v>4</v>
@@ -6694,7 +6704,7 @@
         <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>8.071750981318704</v>
+        <v>7.399104120767874</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6705,7 +6715,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.097558736585359</v>
+        <v>2.808715676600093</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6731,7 +6741,7 @@
         <v>46260</v>
       </c>
       <c r="C57" t="n">
-        <v>1.310489144976327</v>
+        <v>1.315693629206488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6759,22 +6769,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>3.802270259259144</v>
+        <v>4.214511200506355</v>
       </c>
       <c r="L57" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M57" t="n">
-        <v>71.7948717948718</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N57" t="n">
-        <v>18.18775420284279</v>
+        <v>18.05290037670157</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>5.970707312336487</v>
+        <v>5.551519392882343</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6801,7 +6811,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>19.20761996846259</v>
+        <v>18.88676063940727</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6846,7 +6856,7 @@
         <v>46260</v>
       </c>
       <c r="C58" t="n">
-        <v>0.684493788226048</v>
+        <v>0.6753338451851975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6860,7 +6870,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6871,25 +6881,25 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>25.13652524897909</v>
+        <v>25.99164732164354</v>
       </c>
       <c r="K58" t="n">
-        <v>3.123196079990254</v>
+        <v>2.918775877454416</v>
       </c>
       <c r="L58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M58" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N58" t="n">
-        <v>7.542905425994191</v>
+        <v>6.7349914256295</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>4.729104707176579</v>
+        <v>4.937120636370396</v>
       </c>
       <c r="Q58" t="n">
         <v>23</v>
@@ -6912,27 +6922,17 @@
       <c r="W58" t="n">
         <v>82.5</v>
       </c>
-      <c r="X58" t="n">
-        <v>13.39281154402059</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>9.056672397653308</v>
-      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>70.58823529411765</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>15.13397225932492</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="n">
         <v>3</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>46260</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8006578348155609</v>
+        <v>0.8069032000701227</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6993,22 +6993,22 @@
         <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>2.36656062075753</v>
+        <v>3.165049729500424</v>
       </c>
       <c r="L59" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="M59" t="n">
-        <v>63.63636363636363</v>
+        <v>61.70212765957447</v>
       </c>
       <c r="N59" t="n">
-        <v>13.28423488391166</v>
+        <v>13.73289869303025</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5.503202750078673</v>
+        <v>4.686616526795517</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7074,7 +7074,7 @@
         <v>46260</v>
       </c>
       <c r="C60" t="n">
-        <v>11.59559086480008</v>
+        <v>11.68927158094299</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7102,22 +7102,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9442561030266861</v>
+        <v>1.759784204397641</v>
       </c>
       <c r="L60" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M60" t="n">
-        <v>58.97435897435897</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N60" t="n">
-        <v>13.55750584364111</v>
+        <v>14.18370317433011</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.989742823773959</v>
+        <v>6.132300539344793</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7183,7 +7183,7 @@
         <v>46260</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6249544759340576</v>
+        <v>0.6237053709900658</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>18.99064616744801</v>
       </c>
       <c r="K61" t="n">
-        <v>1.700776859680997</v>
+        <v>1.497506144652716</v>
       </c>
       <c r="L61" t="n">
         <v>33</v>
@@ -7220,13 +7220,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N61" t="n">
-        <v>15.95116413753036</v>
+        <v>15.99580046180742</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.160432394503392</v>
+        <v>8.377047060870302</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7245,13 +7245,13 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.09186608887585</v>
+        <v>11.26956797582287</v>
       </c>
       <c r="Z61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="n">
-        <v>50</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB61" t="n">
         <v>11.83234893488008</v>
@@ -7294,7 +7294,7 @@
         <v>46260</v>
       </c>
       <c r="C62" t="n">
-        <v>9.139074308163794</v>
+        <v>9.12346085547331</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7354,16 +7354,16 @@
         <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.227171492204916</v>
+        <v>2.394209354120269</v>
       </c>
       <c r="Z62" t="n">
         <v>59</v>
       </c>
       <c r="AA62" t="n">
-        <v>47.45762711864407</v>
+        <v>45.76271186440678</v>
       </c>
       <c r="AB62" t="n">
-        <v>15.1354421363008</v>
+        <v>15.03545359182985</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
@@ -7403,7 +7403,7 @@
         <v>46260</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1159559121870501</v>
+        <v>0.1167886288311584</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>21.38078415792315</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.792318489381085</v>
+        <v>2.094238910665824</v>
       </c>
       <c r="Z63" t="n">
         <v>7</v>
@@ -7472,13 +7472,13 @@
         <v>14.28571428571429</v>
       </c>
       <c r="AB63" t="n">
-        <v>8.46117073708481</v>
+        <v>7.899991244479065</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>7.414724226121527</v>
+        <v>8.07486811947722</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7512,7 +7512,7 @@
         <v>46260</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1463501009239113</v>
+        <v>0.1480155342121281</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7540,22 +7540,22 @@
         <v>25.85620453775692</v>
       </c>
       <c r="K64" t="n">
-        <v>0.8608381894944062</v>
+        <v>2.008613259943881</v>
       </c>
       <c r="L64" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M64" t="n">
-        <v>60.71428571428572</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N64" t="n">
-        <v>15.93197460878021</v>
+        <v>15.04299023450893</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.103834436443066</v>
+        <v>2.932484468182417</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7621,7 +7621,7 @@
         <v>46260</v>
       </c>
       <c r="C65" t="n">
-        <v>6.979213352646725</v>
+        <v>6.989622321107048</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>23.19552699026226</v>
+        <v>23.37926379412545</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7666,43 +7666,43 @@
         <v>50</v>
       </c>
       <c r="R65" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S65" t="n">
         <v>46.48220825304647</v>
       </c>
       <c r="T65" t="n">
-        <v>19.51779174695353</v>
+        <v>21.51779174695353</v>
       </c>
       <c r="U65" t="n">
-        <v>52.1538260502326</v>
+        <v>54.18970269185592</v>
       </c>
       <c r="V65" t="n">
         <v>67</v>
       </c>
       <c r="W65" t="n">
-        <v>62.6865671641791</v>
+        <v>64.17910447761194</v>
       </c>
       <c r="X65" t="n">
-        <v>23.83860580378341</v>
+        <v>24.57355301923612</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.5192878338278972</v>
+        <v>0.9587020648967548</v>
       </c>
       <c r="Z65" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA65" t="n">
-        <v>40.74074074074074</v>
+        <v>40</v>
       </c>
       <c r="AB65" t="n">
-        <v>8.779187168866397</v>
+        <v>9.010466124963772</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>3.498881431767342</v>
+        <v>3.07073715562175</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7736,7 +7736,7 @@
         <v>46260</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4767307475719878</v>
+        <v>0.4763143792573239</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7793,25 +7793,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X66" t="n">
-        <v>14.06774811016638</v>
+        <v>14.56154975385107</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.8658041416015005</v>
+        <v>1.379317196194785</v>
       </c>
       <c r="Z66" t="n">
         <v>54</v>
       </c>
       <c r="AA66" t="n">
-        <v>44.44444444444444</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB66" t="n">
-        <v>10.69839407866415</v>
+        <v>10.27632487453329</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>5.179036168036399</v>
+        <v>4.685308063621452</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7845,7 +7845,7 @@
         <v>46260</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02747967777615017</v>
+        <v>0.02789603609820436</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7873,22 +7873,22 @@
         <v>13.52521428537139</v>
       </c>
       <c r="K67" t="n">
-        <v>2.061245107645004</v>
+        <v>3.607626004318454</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N67" t="n">
-        <v>7.671407444036571</v>
+        <v>7.104188996989391</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.899599490786308</v>
+        <v>0.3787115010869924</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7905,7 +7905,7 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>7.94656182183715</v>
+        <v>6.551814206112083</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
@@ -7942,7 +7942,7 @@
         <v>46260</v>
       </c>
       <c r="C68" t="n">
-        <v>4.846415778621203</v>
+        <v>4.783961967859264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7999,13 +7999,13 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>149.6966919775957</v>
+        <v>151.8400112220386</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.08583560085837494</v>
+        <v>2.212764659574462</v>
       </c>
       <c r="Z68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
@@ -8013,7 +8013,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>7.920963405674653</v>
+        <v>5.91819097889259</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8047,11 +8047,11 @@
         <v>46260</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4559128106513414</v>
+        <v>0.4600764138571027</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -8099,22 +8099,22 @@
         <v>25.43142265824418</v>
       </c>
       <c r="Y69" t="n">
-        <v>6.808512255319144</v>
+        <v>5.957445191489352</v>
       </c>
       <c r="Z69" t="n">
         <v>7</v>
       </c>
       <c r="AA69" t="n">
-        <v>42.85714285714285</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB69" t="n">
-        <v>10.64993948064956</v>
+        <v>11.41149887926803</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>0.04525058745724619</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8140,16 +8140,16 @@
         <v>46260</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4071988351343381</v>
+        <v>0.4134442399429802</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8168,22 +8168,22 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>6.774020527356694</v>
+        <v>8.411665146402814</v>
       </c>
       <c r="L70" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>55.55555555555556</v>
+        <v>60</v>
       </c>
       <c r="N70" t="n">
-        <v>9.21929919714815</v>
+        <v>9.342326941007865</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>1.148200158229695</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8210,22 +8210,22 @@
         <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>7.210628348047921</v>
+        <v>5.787473029553968</v>
       </c>
       <c r="Z70" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA70" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AB70" t="n">
-        <v>14.33323018882474</v>
+        <v>11.19973885708153</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.8507134361389612</v>
+        <v>2.34844244347685</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8259,7 +8259,7 @@
         <v>46260</v>
       </c>
       <c r="C71" t="n">
-        <v>3.162244491256782</v>
+        <v>3.210125809668976</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8287,16 +8287,16 @@
         <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>2.298069205268161</v>
+        <v>3.847021678144014</v>
       </c>
       <c r="L71" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="M71" t="n">
-        <v>57.74647887323944</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="N71" t="n">
-        <v>17.78569554032562</v>
+        <v>18.09911134683085</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8483,7 +8483,7 @@
         <v>46260</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07119734593404584</v>
+        <v>0.07078098761199166</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8500,7 +8500,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8511,22 +8515,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>8.219283658787923</v>
+        <v>7.586422998506892</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>62.5</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N73" t="n">
-        <v>10.17048915836387</v>
+        <v>10.78728381292863</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>1.645470456842646</v>
+        <v>2.243384373441448</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8553,22 +8557,22 @@
         <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.221165560300923</v>
+        <v>6.769579235547751</v>
       </c>
       <c r="Z73" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA73" t="n">
-        <v>52.63157894736842</v>
+        <v>50</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.4822167630246</v>
+        <v>13.29567252782323</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>4.029517387666948</v>
+        <v>3.464985718142299</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8602,7 +8606,7 @@
         <v>46260</v>
       </c>
       <c r="C74" t="n">
-        <v>5.532366736661796</v>
+        <v>5.527162252431634</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8662,22 +8666,22 @@
         <v>25.512639367661</v>
       </c>
       <c r="Y74" t="n">
-        <v>5.67393657517986</v>
+        <v>5.762672288655713</v>
       </c>
       <c r="Z74" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA74" t="n">
-        <v>45.45454545454545</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB74" t="n">
-        <v>16.4414883283841</v>
+        <v>17.51252122941868</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>4.586286406691931</v>
+        <v>4.496442985229299</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8711,7 +8715,7 @@
         <v>46260</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1244912632018246</v>
+        <v>0.1249076215238787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8739,22 +8743,22 @@
         <v>23.35547482758762</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7498085771851626</v>
+        <v>1.086764120631378</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>72.72727272727273</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N75" t="n">
-        <v>18.24441559719496</v>
+        <v>19.66198819310451</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>5.211118012986238</v>
+        <v>4.860414636980015</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8820,7 +8824,7 @@
         <v>46260</v>
       </c>
       <c r="C76" t="n">
-        <v>1.969376800841711</v>
+        <v>1.989153936262477</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8877,25 +8881,25 @@
         <v>61.81818181818182</v>
       </c>
       <c r="X76" t="n">
-        <v>14.64967258969352</v>
+        <v>15.91088274943551</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.8905170321223288</v>
+        <v>0.9844527979274709</v>
       </c>
       <c r="Z76" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA76" t="n">
-        <v>42.85714285714285</v>
+        <v>51.06382978723404</v>
       </c>
       <c r="AB76" t="n">
-        <v>11.43604088548736</v>
+        <v>11.96434750500554</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.137422247360011</v>
+        <v>3.045528997500113</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -8929,7 +8933,7 @@
         <v>46260</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5350209946822461</v>
+        <v>0.5479280932978543</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8957,16 +8961,16 @@
         <v>14.90307427679485</v>
       </c>
       <c r="K77" t="n">
-        <v>10.19080331131783</v>
+        <v>12.84909818013313</v>
       </c>
       <c r="L77" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="M77" t="n">
-        <v>68.96551724137932</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N77" t="n">
-        <v>16.90273640953321</v>
+        <v>16.70695952106052</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
@@ -8999,22 +9003,22 @@
         <v>16.28154284245451</v>
       </c>
       <c r="Y77" t="n">
-        <v>5.237924594265831</v>
+        <v>2.951839628557285</v>
       </c>
       <c r="Z77" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AA77" t="n">
-        <v>45.65217391304348</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB77" t="n">
-        <v>11.13919768245498</v>
+        <v>12.10535285520056</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>5.025296655170141</v>
+        <v>7.262538871902924</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9048,16 +9052,16 @@
         <v>46260</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04850579135967129</v>
+        <v>0.04871397052069839</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9076,22 +9080,22 @@
         <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>3.821666540896906</v>
+        <v>4.267252662287135</v>
       </c>
       <c r="L78" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M78" t="n">
-        <v>58.13953488372093</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N78" t="n">
-        <v>18.54781313496884</v>
+        <v>17.21017009301777</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.1717690199404043</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9157,7 +9161,7 @@
         <v>46260</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8327174768258583</v>
+        <v>0.8481227851212707</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9174,7 +9178,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>5</v>
       </c>
@@ -9185,16 +9193,16 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>5.028743084081166</v>
+        <v>6.971779242343867</v>
       </c>
       <c r="L79" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M79" t="n">
-        <v>64.28571428571429</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="N79" t="n">
-        <v>12.07238133735722</v>
+        <v>11.22239942884223</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
@@ -9266,7 +9274,7 @@
         <v>46260</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1294875632746542</v>
+        <v>0.1317775390422571</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9294,7 +9302,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>6.01532292945004</v>
+        <v>7.890194263526307</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9305,7 +9313,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>3.758585985916074</v>
+        <v>1.955512037841367</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9332,22 +9340,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>5.587799240813085</v>
+        <v>3.918128065937276</v>
       </c>
       <c r="Z80" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="AA80" t="n">
-        <v>35</v>
+        <v>31.48148148148148</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.51348611190969</v>
+        <v>12.32755663990113</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.554967196813474</v>
+        <v>4.248326819510706</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9381,7 +9389,7 @@
         <v>46260</v>
       </c>
       <c r="C81" t="n">
-        <v>1.207440341397495</v>
+        <v>1.223053794087979</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9441,22 +9449,22 @@
         <v>23.65045506047392</v>
       </c>
       <c r="Y81" t="n">
-        <v>5.073647377457946</v>
+        <v>3.846151438373357</v>
       </c>
       <c r="Z81" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA81" t="n">
-        <v>38.46153846153846</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB81" t="n">
-        <v>10.44751179815941</v>
+        <v>10.98924405333862</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>5.189657546551718</v>
+        <v>6.40000234382978</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9490,7 +9498,7 @@
         <v>46260</v>
       </c>
       <c r="C82" t="n">
-        <v>5.240915619772745</v>
+        <v>5.261733556693392</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9550,7 +9558,7 @@
         <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>6.256312685627075</v>
+        <v>5.883944513573947</v>
       </c>
       <c r="Z82" t="n">
         <v>7</v>
@@ -9559,7 +9567,7 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AB82" t="n">
-        <v>8.227271296602501</v>
+        <v>8.315231402804265</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9599,7 +9607,7 @@
         <v>46260</v>
       </c>
       <c r="C83" t="n">
-        <v>5.99556583314618</v>
+        <v>5.953929959304887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9659,22 +9667,22 @@
         <v>12.63070246967208</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.706484641638217</v>
+        <v>2.389078498293506</v>
       </c>
       <c r="Z83" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA83" t="n">
-        <v>49.29577464788732</v>
+        <v>50</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.31522583772626</v>
+        <v>12.50841496688073</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>4.368055555555572</v>
+        <v>3.699300699300712</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9708,7 +9716,7 @@
         <v>46260</v>
       </c>
       <c r="C84" t="n">
-        <v>2.146329264667207</v>
+        <v>2.177556170048176</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9736,22 +9744,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>2.750258390755822</v>
+        <v>4.245170028712653</v>
       </c>
       <c r="L84" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="M84" t="n">
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>10.44668109268372</v>
+        <v>11.58160239314899</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>2.189524040599955</v>
+        <v>0.7240910740319739</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9817,7 +9825,7 @@
         <v>46260</v>
       </c>
       <c r="C85" t="n">
-        <v>6.380697666178139</v>
+        <v>6.448355961170241</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9845,22 +9853,22 @@
         <v>12.61214035274981</v>
       </c>
       <c r="K85" t="n">
-        <v>3.135632469557326</v>
+        <v>4.229240317929484</v>
       </c>
       <c r="L85" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M85" t="n">
-        <v>53.44827586206897</v>
+        <v>57.4074074074074</v>
       </c>
       <c r="N85" t="n">
-        <v>12.81713741108489</v>
+        <v>12.58313778139682</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>4.716476172169215</v>
+        <v>3.617756083195656</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9926,7 +9934,7 @@
         <v>46260</v>
       </c>
       <c r="C86" t="n">
-        <v>4.550801137842731</v>
+        <v>4.625745520272935</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9954,16 +9962,16 @@
         <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>6.686194537753964</v>
+        <v>8.443144736472341</v>
       </c>
       <c r="L86" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M86" t="n">
-        <v>54.54545454545455</v>
+        <v>72</v>
       </c>
       <c r="N86" t="n">
-        <v>15.49051857681899</v>
+        <v>12.24412062426394</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
@@ -9996,7 +10004,7 @@
         <v>70.65007079462626</v>
       </c>
       <c r="Y86" t="n">
-        <v>11.29095587688633</v>
+        <v>9.830060459484724</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
@@ -10041,7 +10049,7 @@
         <v>46260</v>
       </c>
       <c r="C87" t="n">
-        <v>5.745750590098422</v>
+        <v>5.813408885090523</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10069,16 +10077,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>6.553047656686228</v>
+        <v>7.807748399020409</v>
       </c>
       <c r="L87" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M87" t="n">
-        <v>65</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N87" t="n">
-        <v>9.279963059448857</v>
+        <v>10.05615854119981</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10111,22 +10119,22 @@
         <v>10.60669620884278</v>
       </c>
       <c r="Y87" t="n">
-        <v>3.664921465968596</v>
+        <v>2.530541012216403</v>
       </c>
       <c r="Z87" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AA87" t="n">
-        <v>45.94594594594594</v>
+        <v>38.77551020408163</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.61928107281155</v>
+        <v>11.99051425558094</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.3478260869565153</v>
+        <v>1.507609668755605</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10160,7 +10168,7 @@
         <v>46260</v>
       </c>
       <c r="C88" t="n">
-        <v>1.131454839785692</v>
+        <v>1.142904768794934</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10220,22 +10228,22 @@
         <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>5.396000433403636</v>
+        <v>4.438640898635926</v>
       </c>
       <c r="Z88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA88" t="n">
-        <v>63.63636363636363</v>
+        <v>70</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.81940724482401</v>
+        <v>14.14289847092548</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.638450350263664</v>
+        <v>1.633881221496558</v>
       </c>
       <c r="AE88" t="n">
         <v>32</v>
@@ -10269,7 +10277,7 @@
         <v>46260</v>
       </c>
       <c r="C89" t="n">
-        <v>2.206701313588524</v>
+        <v>2.215028520208226</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10329,22 +10337,22 @@
         <v>27.21456043612742</v>
       </c>
       <c r="Y89" t="n">
-        <v>5.777777777777793</v>
+        <v>5.422220862222238</v>
       </c>
       <c r="Z89" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="n">
-        <v>52.63157894736842</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.43823198402062</v>
+        <v>13.45429903085463</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>4.481132075471683</v>
+        <v>4.840226932278668</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10378,7 +10386,7 @@
         <v>46260</v>
       </c>
       <c r="C90" t="n">
-        <v>2.945738074271474</v>
+        <v>2.951983518842375</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10438,13 +10446,13 @@
         <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>5.72951748867384</v>
+        <v>5.529648709321422</v>
       </c>
       <c r="Z90" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA90" t="n">
-        <v>58.8235294117647</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB90" t="n">
         <v>12.83088714997792</v>
@@ -10487,16 +10495,16 @@
         <v>46260</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2300382069285514</v>
+        <v>0.2346181586719366</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10515,22 +10523,22 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>2.753699184121516</v>
+        <v>4.799476666049829</v>
       </c>
       <c r="L91" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="M91" t="n">
-        <v>61.53846153846154</v>
+        <v>66.0377358490566</v>
       </c>
       <c r="N91" t="n">
-        <v>12.55561191083563</v>
+        <v>14.93392473092584</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>0.2397001936029097</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>46</v>
@@ -10596,7 +10604,7 @@
         <v>46260</v>
       </c>
       <c r="C92" t="n">
-        <v>1.114800506278986</v>
+        <v>1.12937307794507</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10613,7 +10621,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H92" t="n">
         <v>5</v>
       </c>
@@ -10624,22 +10636,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>5.803367756080324</v>
+        <v>7.186419836209845</v>
       </c>
       <c r="L92" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M92" t="n">
-        <v>63.33333333333334</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="N92" t="n">
-        <v>12.87468424176228</v>
+        <v>11.47873103029748</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>2.076145864263812</v>
+        <v>0.7590328747180797</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10666,16 +10678,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.728524729593966</v>
+        <v>6.522360327497023</v>
       </c>
       <c r="Z92" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AA92" t="n">
-        <v>45.45454545454545</v>
+        <v>53.65853658536585</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.49689035872951</v>
+        <v>11.50202474682687</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10715,7 +10727,7 @@
         <v>46260</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04184405300232</v>
+        <v>0.0422604113243742</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10743,22 +10755,22 @@
         <v>13.53506152683441</v>
       </c>
       <c r="K93" t="n">
-        <v>3.468206491952897</v>
+        <v>4.497739860495331</v>
       </c>
       <c r="L93" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="M93" t="n">
-        <v>56.89655172413793</v>
+        <v>63.46153846153846</v>
       </c>
       <c r="N93" t="n">
-        <v>20.27323651027488</v>
+        <v>19.11345824251768</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.446928959036332</v>
+        <v>1.437600604099365</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10824,7 +10836,7 @@
         <v>46260</v>
       </c>
       <c r="C94" t="n">
-        <v>7.791112892551936</v>
+        <v>7.874384640234522</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10852,22 +10864,22 @@
         <v>10.06134969325154</v>
       </c>
       <c r="K94" t="n">
-        <v>2.114597544338337</v>
+        <v>3.206002728512969</v>
       </c>
       <c r="L94" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="M94" t="n">
-        <v>31.11111111111111</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="N94" t="n">
-        <v>11.15745031423081</v>
+        <v>14.60794312578426</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>5.763527054108231</v>
+        <v>4.64507600793127</v>
       </c>
       <c r="Q94" t="n">
         <v>41</v>
@@ -10894,7 +10906,7 @@
         <v>47.10636343143248</v>
       </c>
       <c r="Y94" t="n">
-        <v>8.159509202453997</v>
+        <v>7.177914110429451</v>
       </c>
       <c r="Z94" t="n">
         <v>3</v>
@@ -10903,7 +10915,7 @@
         <v>66.66666666666667</v>
       </c>
       <c r="AB94" t="n">
-        <v>7.526956283294056</v>
+        <v>7.826121987750933</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
@@ -10943,7 +10955,7 @@
         <v>46260</v>
       </c>
       <c r="C95" t="n">
-        <v>0.139271999248201</v>
+        <v>0.1394801734129232</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10971,22 +10983,22 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>4.399775587678545</v>
+        <v>4.555825161156846</v>
       </c>
       <c r="L95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M95" t="n">
-        <v>70</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N95" t="n">
-        <v>17.15024519071062</v>
+        <v>17.79602740297683</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>1.532785298927708</v>
+        <v>1.381247612571745</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11013,7 +11025,7 @@
         <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>6.80816458274932</v>
+        <v>6.66886786408628</v>
       </c>
       <c r="Z95" t="n">
         <v>24</v>
@@ -11022,7 +11034,7 @@
         <v>41.66666666666666</v>
       </c>
       <c r="AB95" t="n">
-        <v>11.16434066640982</v>
+        <v>11.37674008022595</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
@@ -11062,7 +11074,7 @@
         <v>46260</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1290712049526</v>
+        <v>0.1309448223981488</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11090,22 +11102,22 @@
         <v>14.68867757321659</v>
       </c>
       <c r="K96" t="n">
-        <v>1.973682427285306</v>
+        <v>3.453948071762492</v>
       </c>
       <c r="L96" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="M96" t="n">
-        <v>55.55555555555556</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="N96" t="n">
-        <v>13.0999134380232</v>
+        <v>14.89759144000573</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.870969628303914</v>
+        <v>6.327503251685229</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11171,7 +11183,7 @@
         <v>46260</v>
       </c>
       <c r="C97" t="n">
-        <v>1.890268735889406</v>
+        <v>1.909004752128572</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11199,16 +11211,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>5.76019987508043</v>
+        <v>6.808476654299689</v>
       </c>
       <c r="L97" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M97" t="n">
-        <v>48.64864864864865</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N97" t="n">
-        <v>15.00924480821145</v>
+        <v>15.33088048225494</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11241,16 +11253,16 @@
         <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>9.977173253356275</v>
+        <v>9.084882590236788</v>
       </c>
       <c r="Z97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA97" t="n">
-        <v>41.66666666666666</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="AB97" t="n">
-        <v>10.42692936952895</v>
+        <v>10.41431718008398</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11290,7 +11302,7 @@
         <v>46260</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6828283151755717</v>
+        <v>0.6811629214414351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11347,25 +11359,25 @@
         <v>72.46376811594203</v>
       </c>
       <c r="X98" t="n">
-        <v>14.8539646257186</v>
+        <v>15.47968337611683</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.72639731633517</v>
+        <v>1.505117343881901</v>
       </c>
       <c r="Z98" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AA98" t="n">
-        <v>34</v>
+        <v>32.69230769230769</v>
       </c>
       <c r="AB98" t="n">
-        <v>13.49083939623806</v>
+        <v>13.34973421825646</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>7.326824540499599</v>
+        <v>6.594132081759129</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11399,16 +11411,16 @@
         <v>46260</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4575782439395582</v>
+        <v>0.4617418473534989</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11427,22 +11439,22 @@
         <v>21.64053449738032</v>
       </c>
       <c r="K99" t="n">
-        <v>3.883924481269885</v>
+        <v>4.829186779800199</v>
       </c>
       <c r="L99" t="n">
         <v>28</v>
       </c>
       <c r="M99" t="n">
-        <v>64.28571428571429</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N99" t="n">
-        <v>12.35242564873235</v>
+        <v>12.14580322778225</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.1117357852138623</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>33</v>
@@ -11508,16 +11520,16 @@
         <v>46260</v>
       </c>
       <c r="C100" t="n">
-        <v>342.6394962545406</v>
+        <v>349.8166833079946</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -11532,27 +11544,17 @@
       <c r="I100" t="n">
         <v>10</v>
       </c>
-      <c r="J100" t="n">
-        <v>12.69669682287478</v>
-      </c>
-      <c r="K100" t="n">
-        <v>11.7962411234608</v>
-      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
-        <v>17</v>
-      </c>
-      <c r="M100" t="n">
-        <v>52.94117647058823</v>
-      </c>
-      <c r="N100" t="n">
-        <v>10.39378664525568</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="n">
         <v>5</v>
       </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="n">
         <v>48</v>
       </c>
@@ -11575,25 +11577,25 @@
         <v>64.91228070175438</v>
       </c>
       <c r="X100" t="n">
-        <v>11.8472509503817</v>
+        <v>15.09065341954294</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.04560668812820801</v>
+        <v>0.8277330215197276</v>
       </c>
       <c r="Z100" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AA100" t="n">
-        <v>43.63636363636363</v>
+        <v>38.77551020408163</v>
       </c>
       <c r="AB100" t="n">
-        <v>11.79785461578604</v>
+        <v>14.01566572437516</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>7.958022702466872</v>
+        <v>7.232129704201073</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11627,7 +11629,7 @@
         <v>46260</v>
       </c>
       <c r="C101" t="n">
-        <v>349.1809230312539</v>
+        <v>353.6030675656404</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11684,25 +11686,25 @@
         <v>53.84615384615385</v>
       </c>
       <c r="X101" t="n">
-        <v>11.75561335839466</v>
+        <v>12.28498792189239</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.056612999402951</v>
+        <v>0.2759430500513749</v>
       </c>
       <c r="Z101" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA101" t="n">
-        <v>43.90243902439025</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.81175403647738</v>
+        <v>11.00744684891971</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.996177258988743</v>
+        <v>5.739895793470906</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11736,7 +11738,7 @@
         <v>46260</v>
       </c>
       <c r="C102" t="n">
-        <v>415.7202539138702</v>
+        <v>419.3771359663617</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11796,22 +11798,22 @@
         <v>11.13903673030769</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.496834386210034</v>
+        <v>1.639148062204143</v>
       </c>
       <c r="Z102" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AA102" t="n">
-        <v>26.47058823529412</v>
+        <v>29.72972972972973</v>
       </c>
       <c r="AB102" t="n">
-        <v>13.69804258496672</v>
+        <v>14.69226624811142</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.567265993911427</v>
+        <v>3.416859321146681</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11845,7 +11847,7 @@
         <v>46260</v>
       </c>
       <c r="C103" t="n">
-        <v>0.772761796219204</v>
+        <v>0.7844198696235188</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11902,25 +11904,25 @@
         <v>68.18181818181819</v>
       </c>
       <c r="X103" t="n">
-        <v>19.04159364785436</v>
+        <v>21.73107604932552</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.1613807947813739</v>
+        <v>0.8942665594065757</v>
       </c>
       <c r="Z103" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA103" t="n">
-        <v>42.10526315789474</v>
+        <v>43.24324324324324</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.99388688883607</v>
+        <v>15.86336079108647</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.851289678903028</v>
+        <v>7.169851020630191</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46260</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3959571698069466</v>
+        <v>0.3963735381216105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>18.04725545643595</v>
       </c>
       <c r="K2" t="n">
-        <v>1.440002453333311</v>
+        <v>1.546671573333325</v>
       </c>
       <c r="L2" t="n">
         <v>33</v>
@@ -707,13 +707,13 @@
         <v>51.51515151515152</v>
       </c>
       <c r="N2" t="n">
-        <v>11.37775503601097</v>
+        <v>11.44853795737839</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>8.438483181824319</v>
+        <v>8.324574597762169</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -779,7 +779,7 @@
         <v>46260</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6457724128547041</v>
+        <v>0.6461887811693681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.027529643465996</v>
+        <v>1.092668168145861</v>
       </c>
       <c r="L3" t="n">
         <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>56.60377358490566</v>
+        <v>58.49056603773585</v>
       </c>
       <c r="N3" t="n">
-        <v>13.06613946922564</v>
+        <v>12.80061761725111</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>8.881213257612618</v>
+        <v>8.811056225203906</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -888,7 +888,7 @@
         <v>46260</v>
       </c>
       <c r="C4" t="n">
-        <v>1.54885453874754</v>
+        <v>1.525954839778093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         <v>20.64833628068863</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6011983289222922</v>
+        <v>2.070802206657685</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA4" t="n">
-        <v>36.11111111111111</v>
+        <v>37.14285714285715</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.50941848313939</v>
+        <v>16.08595786741356</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.455648874097545</v>
+        <v>8.096867912749694</v>
       </c>
       <c r="AE4" t="n">
         <v>42</v>
@@ -997,7 +997,7 @@
         <v>46260</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2308709235726598</v>
+        <v>0.2319118243741001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %79.49: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1029,22 +1029,22 @@
         <v>18.40585323077206</v>
       </c>
       <c r="K5" t="n">
-        <v>1.278541939992972</v>
+        <v>1.735164687642143</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>79.48717948717949</v>
+        <v>80</v>
       </c>
       <c r="N5" t="n">
-        <v>11.50353668362903</v>
+        <v>11.83017222636494</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.699726345810726</v>
+        <v>1.243262657746014</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1110,7 +1110,7 @@
         <v>46260</v>
       </c>
       <c r="C6" t="n">
-        <v>1.725807002573035</v>
+        <v>1.717479795953333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>5.456092886520403</v>
+        <v>4.947255760779656</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1176,16 +1176,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.823674829815739</v>
+        <v>6.278085848664983</v>
       </c>
       <c r="Z6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="n">
         <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.82269995469782</v>
+        <v>11.20462901185882</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1225,7 +1225,7 @@
         <v>46260</v>
       </c>
       <c r="C7" t="n">
-        <v>2.264991600461042</v>
+        <v>2.269155124350464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,22 +1253,22 @@
         <v>12.3532304777189</v>
       </c>
       <c r="K7" t="n">
-        <v>6.457931797423599</v>
+        <v>6.653623535161968</v>
       </c>
       <c r="L7" t="n">
         <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="N7" t="n">
-        <v>13.89571591804074</v>
+        <v>13.72160353748486</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.448523540275781</v>
+        <v>1.262382299082554</v>
       </c>
       <c r="Q7" t="n">
         <v>49</v>
@@ -1295,7 +1295,7 @@
         <v>16.68422911664862</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.693061879324935</v>
+        <v>6.521544392975242</v>
       </c>
       <c r="Z7" t="n">
         <v>30</v>
@@ -1304,7 +1304,7 @@
         <v>40</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.52972966061313</v>
+        <v>11.61592700380395</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1344,7 +1344,7 @@
         <v>46260</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3753474170436321</v>
+        <v>0.3747228645716362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.616314696579064</v>
+        <v>8.768370908943279</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>46260</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5841512989598331</v>
+        <v>0.5787386305723394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,16 +1509,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.072682150485775</v>
+        <v>6.943000208412564</v>
       </c>
       <c r="Z9" t="n">
         <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>50</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.575550115304702</v>
+        <v>10.11294478239028</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1558,7 +1558,7 @@
         <v>46260</v>
       </c>
       <c r="C10" t="n">
-        <v>1.951681586310605</v>
+        <v>1.950640625969865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,22 +1586,22 @@
         <v>10.84633778363752</v>
       </c>
       <c r="K10" t="n">
-        <v>1.62601626016261</v>
+        <v>1.571812411924123</v>
       </c>
       <c r="L10" t="n">
         <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>35.55555555555556</v>
+        <v>37.77777777777778</v>
       </c>
       <c r="N10" t="n">
-        <v>10.32123575410374</v>
+        <v>10.33045012050676</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>4.303999999999997</v>
+        <v>4.359661881504473</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1667,7 +1667,7 @@
         <v>46260</v>
       </c>
       <c r="C11" t="n">
-        <v>8.410446515941169</v>
+        <v>8.34799270517923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,16 +1727,16 @@
         <v>23.11730782489165</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.119927316777703</v>
+        <v>2.846759539672916</v>
       </c>
       <c r="Z11" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA11" t="n">
-        <v>62.85714285714285</v>
+        <v>60.60606060606061</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.4076836700006</v>
+        <v>11.98281951353008</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1776,7 +1776,7 @@
         <v>46260</v>
       </c>
       <c r="C12" t="n">
-        <v>7.182188237623028</v>
+        <v>7.145756848011897</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,16 +1804,16 @@
         <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>9.324654397655419</v>
+        <v>8.770109049261521</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>61.53846153846154</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>13.49509280675115</v>
+        <v>14.38160145879287</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1846,16 +1846,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.830894706308396</v>
+        <v>3.323781472290888</v>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>27.27272727272727</v>
+        <v>25</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.441911489688975</v>
+        <v>9.759433103302454</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1895,7 +1895,7 @@
         <v>46260</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2212946717564449</v>
+        <v>0.2200455867976726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>4.765313773759505</v>
+        <v>4.173972027493322</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2240113810447752</v>
+        <v>0.7929312441774528</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1959,7 +1959,7 @@
         <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>10.1612985314707</v>
+        <v>10.66838787903293</v>
       </c>
       <c r="Z13" t="n">
         <v>8</v>
@@ -1998,7 +1998,7 @@
         <v>46260</v>
       </c>
       <c r="C14" t="n">
-        <v>8.748737990901674</v>
+        <v>8.753942475131835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,25 +2055,25 @@
         <v>59.57446808510638</v>
       </c>
       <c r="X14" t="n">
-        <v>12.90895707120068</v>
+        <v>13.50145199425789</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.06971469640548733</v>
+        <v>0.5322294500295754</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.61195342651899</v>
+        <v>12.25836860253546</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.93163193493362</v>
+        <v>1.475624256837094</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2107,7 +2107,7 @@
         <v>46260</v>
       </c>
       <c r="C15" t="n">
-        <v>14.91605180364319</v>
+        <v>14.70787243443672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,22 +2167,22 @@
         <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.661619486504277</v>
+        <v>6.978275181040161</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.567483531887934</v>
+        <v>10.48751967571703</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.598743893928825</v>
+        <v>3.248407643312101</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2216,7 +2216,7 @@
         <v>46260</v>
       </c>
       <c r="C16" t="n">
-        <v>35.97339499887708</v>
+        <v>35.64030800814673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>3.308320955610489</v>
+        <v>2.351762428243709</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M16" t="n">
-        <v>63.76811594202898</v>
+        <v>65.85365853658537</v>
       </c>
       <c r="N16" t="n">
-        <v>18.14434792096311</v>
+        <v>17.8225095684651</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.477386315536782</v>
+        <v>7.47250207549508</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2286,16 +2286,16 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.10750125047431</v>
+        <v>11.93057994259955</v>
       </c>
       <c r="Z16" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.40563990076058</v>
+        <v>13.1674972814445</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
@@ -2335,7 +2335,7 @@
         <v>46260</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6824119468609078</v>
+        <v>0.667423086196499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,25 +2360,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>15.13508436993211</v>
+        <v>16.70278702842509</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9236429933767054</v>
+        <v>0.5646242620541031</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="M17" t="n">
-        <v>70.3125</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N17" t="n">
-        <v>15.59750544488855</v>
+        <v>15.4411099493113</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.011594901590801</v>
+        <v>7.393629511875455</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2444,7 +2444,7 @@
         <v>46260</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09742794124957614</v>
+        <v>0.09680340876279972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,22 +2472,22 @@
         <v>20.97644296643689</v>
       </c>
       <c r="K18" t="n">
-        <v>1.739128950850621</v>
+        <v>1.086960893194799</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>70</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N18" t="n">
-        <v>14.85774688515832</v>
+        <v>15.71182240184449</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>8.119659696654313</v>
+        <v>8.817199595329051</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2662,7 +2662,7 @@
         <v>46260</v>
       </c>
       <c r="C20" t="n">
-        <v>1.648780540620492</v>
+        <v>1.64149429434153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,16 +2690,16 @@
         <v>18.92576555578012</v>
       </c>
       <c r="K20" t="n">
-        <v>2.657155384764143</v>
+        <v>2.2034956659579</v>
       </c>
       <c r="L20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M20" t="n">
-        <v>44.82758620689656</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N20" t="n">
-        <v>15.53051389831679</v>
+        <v>16.59764475400589</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -2771,7 +2771,7 @@
         <v>46260</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9817739020549964</v>
+        <v>0.971781301909337</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,22 +2799,22 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>5.680563397533489</v>
+        <v>4.604935280928268</v>
       </c>
       <c r="L21" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M21" t="n">
-        <v>56.09756097560975</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N21" t="n">
-        <v>14.73325745630745</v>
+        <v>16.07122873295376</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.194761768766895</v>
+        <v>3.245606634098008</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2880,16 +2880,16 @@
         <v>46260</v>
       </c>
       <c r="C22" t="n">
-        <v>0.335168792333224</v>
+        <v>0.3301724724833542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2897,24 +2897,38 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>5</v>
       </c>
       <c r="I22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>10.07269919155901</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.06308693855059389</v>
+      </c>
       <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="M22" t="n">
+        <v>75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13.6274302469148</v>
+      </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>9.930648119572538</v>
+      </c>
       <c r="Q22" t="n">
         <v>2</v>
       </c>
@@ -2940,16 +2954,16 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.65428754088936</v>
+        <v>10.01596681055777</v>
       </c>
       <c r="Z22" t="n">
         <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>45.45454545454545</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.32494428928839</v>
+        <v>12.64143153315367</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
@@ -2981,7 +2995,7 @@
         <v>46260</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7627691960735447</v>
+        <v>0.7536093323490338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3023,7 @@
         <v>27.73484467032905</v>
       </c>
       <c r="K23" t="n">
-        <v>3.913786544956355</v>
+        <v>2.66591742707718</v>
       </c>
       <c r="L23" t="n">
         <v>9</v>
@@ -3018,13 +3032,13 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N23" t="n">
-        <v>18.77493995709025</v>
+        <v>25.2492217942063</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>5.856983618252198</v>
+        <v>7.143639054442952</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -3051,7 +3065,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>24.90654074434457</v>
+        <v>25.80831530069095</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3096,7 +3110,7 @@
         <v>46260</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1779933646269352</v>
+        <v>0.1782015487842672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3138,7 @@
         <v>23.47035234733546</v>
       </c>
       <c r="K24" t="n">
-        <v>5.27999167772093</v>
+        <v>5.403129000268203</v>
       </c>
       <c r="L24" t="n">
         <v>9</v>
@@ -3133,13 +3147,13 @@
         <v>44.44444444444444</v>
       </c>
       <c r="N24" t="n">
-        <v>12.74546888007776</v>
+        <v>12.66278934205094</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.483290934072048</v>
+        <v>4.361228213367463</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3166,16 +3180,16 @@
         <v>12.66805408629466</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.557371092000086</v>
+        <v>6.448078956313652</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
-        <v>57.69230769230769</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.83318425402356</v>
+        <v>12.86006130287472</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3215,7 +3229,7 @@
         <v>46260</v>
       </c>
       <c r="C25" t="n">
-        <v>3.495331481987125</v>
+        <v>3.48075898963738</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,22 +3257,22 @@
         <v>16.84600295124913</v>
       </c>
       <c r="K25" t="n">
-        <v>1.144574638554219</v>
+        <v>0.7228897289156766</v>
       </c>
       <c r="L25" t="n">
         <v>55</v>
       </c>
       <c r="M25" t="n">
-        <v>58.18181818181818</v>
+        <v>60</v>
       </c>
       <c r="N25" t="n">
-        <v>16.85239075330353</v>
+        <v>16.94598916835746</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>6.777847834096917</v>
+        <v>7.224882338731398</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3324,7 +3338,7 @@
         <v>46260</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4480020121085627</v>
+        <v>0.4554964423366775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3423,7 +3437,7 @@
         <v>46260</v>
       </c>
       <c r="C27" t="n">
-        <v>50.25449972644055</v>
+        <v>49.92141273571021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,7 +3465,7 @@
         <v>44.6752281083318</v>
       </c>
       <c r="K27" t="n">
-        <v>52.45638084652357</v>
+        <v>51.4458994490321</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3479,7 +3493,7 @@
         <v>54.9825843402522</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.629991850040746</v>
+        <v>2.281988590057049</v>
       </c>
       <c r="Z27" t="n">
         <v>6</v>
@@ -3494,7 +3508,7 @@
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.442419221209615</v>
+        <v>3.804837364470393</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3518,7 +3532,7 @@
         <v>46260</v>
       </c>
       <c r="C28" t="n">
-        <v>1.624840040151164</v>
+        <v>1.617553635239522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,22 +3592,22 @@
         <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.885606464473921</v>
+        <v>2.325588974317461</v>
       </c>
       <c r="Z28" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>43.18181818181818</v>
+        <v>50</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.82371558975147</v>
+        <v>11.09112479202844</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.193465797692886</v>
+        <v>3.76189729438593</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3627,7 +3641,7 @@
         <v>46260</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3849236488746275</v>
+        <v>0.3847154647172956</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3673,7 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>6.482343665581092</v>
+        <v>6.424753187439358</v>
       </c>
       <c r="L29" t="n">
         <v>8</v>
@@ -3701,7 +3715,7 @@
         <v>39.82687732422523</v>
       </c>
       <c r="Y29" t="n">
-        <v>15.97331973978805</v>
+        <v>16.01876517727811</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3746,7 +3760,7 @@
         <v>46260</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4325967435754099</v>
+        <v>0.4321803752607459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,7 +3788,7 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>18.1737000022087</v>
+        <v>18.05995946893317</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3812,7 +3826,7 @@
         <v>19.87976438285015</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.423146257772834</v>
+        <v>1.518025100637665</v>
       </c>
       <c r="Z30" t="n">
         <v>40</v>
@@ -3827,7 +3841,7 @@
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>8.700677102816801</v>
+        <v>8.612718122306106</v>
       </c>
       <c r="AE30" t="n">
         <v>50</v>
@@ -3861,7 +3875,7 @@
         <v>46260</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1946477181188604</v>
+        <v>0.1983949332329178</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,16 +3907,16 @@
         <v>17.76611681824961</v>
       </c>
       <c r="K31" t="n">
-        <v>11.78282552739045</v>
+        <v>13.93478650261488</v>
       </c>
       <c r="L31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
         <v>75</v>
       </c>
       <c r="N31" t="n">
-        <v>16.66090557653058</v>
+        <v>21.58764950302011</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
@@ -3932,25 +3946,25 @@
         <v>87.5</v>
       </c>
       <c r="X31" t="n">
-        <v>12.26104032611355</v>
+        <v>15.13032923800595</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4259846491123653</v>
+        <v>1.038425533309772</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA31" t="n">
-        <v>33.33333333333334</v>
+        <v>37.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.186968181927581</v>
+        <v>9.54991073289974</v>
       </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.61497366270696</v>
+        <v>9.055610235573431</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3984,7 +3998,7 @@
         <v>46260</v>
       </c>
       <c r="C32" t="n">
-        <v>2.389899221984921</v>
+        <v>2.373244808953696</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,16 +4026,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>9.659019432236683</v>
+        <v>8.894842187680418</v>
       </c>
       <c r="L32" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M32" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="N32" t="n">
-        <v>10.4033552121596</v>
+        <v>10.05140696430216</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4054,22 +4068,22 @@
         <v>16.29216385551018</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.850188861356773</v>
+        <v>3.527193592654454</v>
       </c>
       <c r="Z32" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA32" t="n">
-        <v>38.88888888888889</v>
+        <v>37.83783783783784</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.05042040260712</v>
+        <v>12.34865277684842</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.300896706112878</v>
+        <v>4.636339061662231</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4103,7 +4117,7 @@
         <v>46260</v>
       </c>
       <c r="C33" t="n">
-        <v>1.780974567056012</v>
+        <v>1.831978449016888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4117,7 +4131,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -4131,16 +4145,16 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>8.680969664283712</v>
+        <v>11.79339555215793</v>
       </c>
       <c r="L33" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M33" t="n">
-        <v>46.42857142857143</v>
+        <v>35</v>
       </c>
       <c r="N33" t="n">
-        <v>11.21304164856593</v>
+        <v>11.24432156054373</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4169,17 +4183,27 @@
       <c r="W33" t="n">
         <v>62.71186440677966</v>
       </c>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
+      <c r="X33" t="n">
+        <v>13.38136992079653</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.400560224089631</v>
+      </c>
       <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>40.38461538461539</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.624387755341449</v>
+      </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
-      <c r="AD33" t="inlineStr"/>
+      <c r="AD33" t="n">
+        <v>6.693181818181815</v>
+      </c>
       <c r="AE33" t="n">
         <v>29</v>
       </c>
@@ -4212,7 +4236,7 @@
         <v>46260</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8135650129556882</v>
+        <v>0.8131486446410242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4240,7 +4264,7 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>7.196161552137337</v>
+        <v>7.141300435431042</v>
       </c>
       <c r="L34" t="n">
         <v>19</v>
@@ -4321,7 +4345,7 @@
         <v>46260</v>
       </c>
       <c r="C35" t="n">
-        <v>2.021421643143328</v>
+        <v>2.03287157215257</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4338,11 +4362,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>5</v>
       </c>
@@ -4353,16 +4373,16 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>13.95815196803931</v>
+        <v>14.60364458680314</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N35" t="n">
-        <v>10.09458095312001</v>
+        <v>8.916991455449475</v>
       </c>
       <c r="O35" t="n">
         <v>6</v>
@@ -4395,16 +4415,16 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.725002443620861</v>
+        <v>2.174008137127337</v>
       </c>
       <c r="Z35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>37.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB35" t="n">
-        <v>13.67575307230967</v>
+        <v>15.35229831342463</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4553,7 +4573,7 @@
         <v>46260</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0672419366700468</v>
+        <v>0.06661739918696551</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,16 +4601,16 @@
         <v>12.9660944973907</v>
       </c>
       <c r="K37" t="n">
-        <v>9.458519975791834</v>
+        <v>8.441878398335056</v>
       </c>
       <c r="L37" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>59.45945945945946</v>
+        <v>55</v>
       </c>
       <c r="N37" t="n">
-        <v>17.15751421834236</v>
+        <v>13.24932532116409</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
@@ -4623,22 +4643,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.390581906940503</v>
+        <v>3.297170017274098</v>
       </c>
       <c r="Z37" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AA37" t="n">
-        <v>49.29577464788732</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.52819482318692</v>
+        <v>13.08245291089954</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.648834840430158</v>
+        <v>0.7267936035082467</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4672,7 +4692,7 @@
         <v>46260</v>
       </c>
       <c r="C38" t="n">
-        <v>1.668557676041257</v>
+        <v>1.661271429762295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4700,22 +4720,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>5.315639627902069</v>
+        <v>4.855748011104066</v>
       </c>
       <c r="L38" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>54.76190476190476</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N38" t="n">
-        <v>10.25753574761961</v>
+        <v>10.04512095799568</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>4.447924722907803</v>
+        <v>4.906027648909794</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4781,7 +4801,7 @@
         <v>46260</v>
       </c>
       <c r="C39" t="n">
-        <v>2.829157500526438</v>
+        <v>2.783358102795724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4841,22 +4861,22 @@
         <v>13.14448726963784</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.019671608812822</v>
+        <v>2.622000014587744</v>
       </c>
       <c r="Z39" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AA39" t="n">
-        <v>37.3134328358209</v>
+        <v>45.76271186440678</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.61575624381794</v>
+        <v>12.07677473510738</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.031634540051311</v>
+        <v>3.468956012567836</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4890,7 +4910,7 @@
         <v>46260</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2539788264764787</v>
+        <v>0.2533542939897023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4950,7 +4970,7 @@
         <v>38.77366535417291</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.619249697021287</v>
+        <v>3.856249412702983</v>
       </c>
       <c r="Z40" t="n">
         <v>9</v>
@@ -4965,7 +4985,7 @@
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.432599661901623</v>
+        <v>1.189625514201798</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -4999,11 +5019,11 @@
         <v>46260</v>
       </c>
       <c r="C41" t="n">
-        <v>1.882982330977764</v>
+        <v>1.913168434858853</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5013,7 +5033,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -5059,22 +5079,22 @@
         <v>29.59721231101309</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.980891848638213</v>
+        <v>2.44160880516886</v>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="n">
-        <v>44.44444444444444</v>
+        <v>30</v>
       </c>
       <c r="AB41" t="n">
-        <v>12.8276595140947</v>
+        <v>8.570955018008446</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.572366136825686</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5108,7 +5128,7 @@
         <v>46260</v>
       </c>
       <c r="C42" t="n">
-        <v>3.738901597937519</v>
+        <v>3.736819677256039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5166,7 +5186,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.322976018199075</v>
+        <v>3.37680837788531</v>
       </c>
       <c r="Z42" t="n">
         <v>4</v>
@@ -5181,7 +5201,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.906526190812256</v>
+        <v>6.854660367686305</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5213,7 +5233,7 @@
         <v>46260</v>
       </c>
       <c r="C43" t="n">
-        <v>6.630512909225897</v>
+        <v>6.60969497230525</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5241,22 +5261,22 @@
         <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>1.111111111111107</v>
+        <v>0.7936507936507908</v>
       </c>
       <c r="L43" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M43" t="n">
-        <v>70.96774193548387</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N43" t="n">
-        <v>17.76152976155454</v>
+        <v>17.12829277832295</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.857142857142869</v>
+        <v>3.181102362204724</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5322,7 +5342,7 @@
         <v>46260</v>
       </c>
       <c r="C44" t="n">
-        <v>4.702771823384619</v>
+        <v>4.746489617907392</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5350,22 +5370,22 @@
         <v>20.15821391009879</v>
       </c>
       <c r="K44" t="n">
-        <v>4.844239259818228</v>
+        <v>5.81888975977769</v>
       </c>
       <c r="L44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M44" t="n">
-        <v>63.63636363636363</v>
+        <v>60</v>
       </c>
       <c r="N44" t="n">
-        <v>19.82944032395692</v>
+        <v>21.1641194607964</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>4.917543182706585</v>
+        <v>3.951194583229856</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5423,7 +5443,7 @@
         <v>46260</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02352426872033049</v>
+        <v>0.02373244788135759</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5483,22 +5503,22 @@
         <v>19.58690552546656</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.586204377229451</v>
+        <v>1.724136251486297</v>
       </c>
       <c r="Z45" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="AA45" t="n">
-        <v>47.5</v>
+        <v>53.19148936170212</v>
       </c>
       <c r="AB45" t="n">
-        <v>13.74474632864256</v>
+        <v>13.18215995678039</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.477878628318564</v>
+        <v>3.333334985380121</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5532,7 +5552,7 @@
         <v>46260</v>
       </c>
       <c r="C46" t="n">
-        <v>10.08108595382305</v>
+        <v>10.07588146959288</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5592,7 +5612,7 @@
         <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.108910891089113</v>
+        <v>4.158415841584173</v>
       </c>
       <c r="Z46" t="n">
         <v>24</v>
@@ -5865,7 +5885,7 @@
         <v>46260</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2741722309103488</v>
+        <v>0.2698004633242956</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5882,7 +5902,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>5</v>
       </c>
@@ -5893,16 +5917,16 @@
         <v>16.44500858212767</v>
       </c>
       <c r="K49" t="n">
-        <v>10.32381330088523</v>
+        <v>8.564663333883992</v>
       </c>
       <c r="L49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M49" t="n">
-        <v>62.5</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N49" t="n">
-        <v>22.7101407218383</v>
+        <v>17.82085713801315</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5935,22 +5959,22 @@
         <v>12.16673414089682</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.643019077025665</v>
+        <v>3.211353913976067</v>
       </c>
       <c r="Z49" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AA49" t="n">
-        <v>40.32258064516129</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="AB49" t="n">
-        <v>10.52451268096039</v>
+        <v>12.0203276350777</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>8.496581375874968</v>
+        <v>7.013886814771963</v>
       </c>
       <c r="AE49" t="n">
         <v>46</v>
@@ -5984,7 +6008,7 @@
         <v>46260</v>
       </c>
       <c r="C50" t="n">
-        <v>0.693237283635895</v>
+        <v>0.6924045470065672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6012,22 +6036,22 @@
         <v>15.88388393069994</v>
       </c>
       <c r="K50" t="n">
-        <v>3.738320333944856</v>
+        <v>3.613706870061417</v>
       </c>
       <c r="L50" t="n">
         <v>46</v>
       </c>
       <c r="M50" t="n">
-        <v>54.34782608695652</v>
+        <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>16.35052689205138</v>
+        <v>16.78129669195023</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2522497619132258</v>
+        <v>0.3728204902687438</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6093,7 +6117,7 @@
         <v>46260</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1750788463799462</v>
+        <v>0.1761197471813865</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6121,22 +6145,22 @@
         <v>21.84334516173415</v>
       </c>
       <c r="K51" t="n">
-        <v>1.692858309708001</v>
+        <v>2.297455494942025</v>
       </c>
       <c r="L51" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M51" t="n">
-        <v>61.11111111111111</v>
+        <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>15.19944145636646</v>
+        <v>13.39073506465679</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>2.268735217634998</v>
+        <v>1.664307774636842</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6202,7 +6226,7 @@
         <v>46260</v>
       </c>
       <c r="C52" t="n">
-        <v>4.527901280240605</v>
+        <v>4.482101882509889</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6262,22 +6286,22 @@
         <v>17.40541420286308</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.100530390182444</v>
+        <v>5.070546669024834</v>
       </c>
       <c r="Z52" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AA52" t="n">
-        <v>44.44444444444444</v>
+        <v>50</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.14437304511339</v>
+        <v>11.83407973743981</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.066205606436791</v>
+        <v>3.085926683641071</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6311,7 +6335,7 @@
         <v>46260</v>
       </c>
       <c r="C53" t="n">
-        <v>1.381270082833449</v>
+        <v>1.396883535523934</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,7 +6367,7 @@
         <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>2.361616225203589</v>
+        <v>3.518680489547399</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -6352,13 +6376,13 @@
         <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>16.71756518363199</v>
+        <v>15.20214662953156</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>5.508298894374164</v>
+        <v>4.32899597373162</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6416,7 +6440,7 @@
         <v>46260</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07806726345242422</v>
+        <v>0.07785908429139712</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6445,7 +6469,7 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>44.36335515147667</v>
+        <v>44.51171938937502</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -6529,7 +6553,7 @@
         <v>46260</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9563759936139247</v>
+        <v>0.9517961014098391</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6589,22 +6613,22 @@
         <v>20.41662385315768</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.18995132806209</v>
+        <v>2.658343971107335</v>
       </c>
       <c r="Z55" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA55" t="n">
-        <v>45.83333333333334</v>
+        <v>50</v>
       </c>
       <c r="AB55" t="n">
-        <v>13.34520534258593</v>
+        <v>13.31878217121371</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.8281855319946518</v>
+        <v>0.3509864561902054</v>
       </c>
       <c r="AE55" t="n">
         <v>46</v>
@@ -6638,7 +6662,7 @@
         <v>46260</v>
       </c>
       <c r="C56" t="n">
-        <v>1.28967120805568</v>
+        <v>1.304243779929944</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6670,7 +6694,7 @@
         <v>19.65620512594927</v>
       </c>
       <c r="K56" t="n">
-        <v>15.25581536744185</v>
+        <v>16.55814238139535</v>
       </c>
       <c r="L56" t="n">
         <v>3</v>
@@ -6679,7 +6703,7 @@
         <v>100</v>
       </c>
       <c r="N56" t="n">
-        <v>20.11327023827909</v>
+        <v>28.61821100734219</v>
       </c>
       <c r="O56" t="n">
         <v>4</v>
@@ -6704,7 +6728,7 @@
         <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>7.399104120767874</v>
+        <v>6.352765176087738</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6715,7 +6739,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.808715676600093</v>
+        <v>3.894652982301361</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6741,7 +6765,7 @@
         <v>46260</v>
       </c>
       <c r="C57" t="n">
-        <v>1.315693629206488</v>
+        <v>1.32193899446105</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6769,22 +6793,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>4.214511200506355</v>
+        <v>4.709199076790527</v>
       </c>
       <c r="L57" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M57" t="n">
-        <v>72.22222222222223</v>
+        <v>71.875</v>
       </c>
       <c r="N57" t="n">
-        <v>18.05290037670157</v>
+        <v>20.69688533337153</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>5.551519392882343</v>
+        <v>5.052852060619206</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6811,7 +6835,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>18.88676063940727</v>
+        <v>18.50173041995328</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6856,7 +6880,7 @@
         <v>46260</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6753338451851975</v>
+        <v>0.6903227851659459</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6873,7 +6897,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6884,22 +6912,22 @@
         <v>25.99164732164354</v>
       </c>
       <c r="K58" t="n">
-        <v>2.918775877454416</v>
+        <v>5.203043674067254</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="N58" t="n">
-        <v>6.7349914256295</v>
+        <v>20.17267028505273</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>4.937120636370396</v>
+        <v>2.658626811785103</v>
       </c>
       <c r="Q58" t="n">
         <v>23</v>
@@ -6965,7 +6993,7 @@
         <v>46260</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8069032000701227</v>
+        <v>0.8035723332855098</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6993,22 +7021,22 @@
         <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>3.165049729500424</v>
+        <v>2.739188191899533</v>
       </c>
       <c r="L59" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M59" t="n">
-        <v>61.70212765957447</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N59" t="n">
-        <v>13.73289869303025</v>
+        <v>13.3915163865691</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>4.686616526795517</v>
+        <v>5.120550298951332</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7074,7 +7102,7 @@
         <v>46260</v>
       </c>
       <c r="C60" t="n">
-        <v>11.68927158094299</v>
+        <v>11.66845364402234</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7102,22 +7130,22 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>1.759784204397641</v>
+        <v>1.578555737426335</v>
       </c>
       <c r="L60" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M60" t="n">
-        <v>57.14285714285715</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="N60" t="n">
-        <v>14.18370317433011</v>
+        <v>14.47746955601596</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.132300539344793</v>
+        <v>6.321653439504171</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7183,7 +7211,7 @@
         <v>46260</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6237053709900658</v>
+        <v>0.6232890424376615</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7211,7 +7239,7 @@
         <v>18.99064616744801</v>
       </c>
       <c r="K61" t="n">
-        <v>1.497506144652716</v>
+        <v>1.429755710278902</v>
       </c>
       <c r="L61" t="n">
         <v>33</v>
@@ -7220,13 +7248,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N61" t="n">
-        <v>15.99580046180742</v>
+        <v>16.60922402508292</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.377047060870302</v>
+        <v>8.449437967888752</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7245,7 +7273,7 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.26956797582287</v>
+        <v>11.32879628142524</v>
       </c>
       <c r="Z61" t="n">
         <v>19</v>
@@ -7294,7 +7322,7 @@
         <v>46260</v>
       </c>
       <c r="C62" t="n">
-        <v>9.12346085547331</v>
+        <v>9.139074308163794</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7354,16 +7382,16 @@
         <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.394209354120269</v>
+        <v>2.227171492204916</v>
       </c>
       <c r="Z62" t="n">
         <v>59</v>
       </c>
       <c r="AA62" t="n">
-        <v>45.76271186440678</v>
+        <v>47.45762711864407</v>
       </c>
       <c r="AB62" t="n">
-        <v>15.03545359182985</v>
+        <v>15.1354421363008</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
@@ -7403,7 +7431,7 @@
         <v>46260</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1167886288311584</v>
+        <v>0.113041393940061</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7463,22 +7491,22 @@
         <v>21.38078415792315</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.094238910665824</v>
+        <v>5.235605391847809</v>
       </c>
       <c r="Z63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA63" t="n">
-        <v>14.28571428571429</v>
+        <v>20</v>
       </c>
       <c r="AB63" t="n">
-        <v>7.899991244479065</v>
+        <v>8.489419906398876</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>8.07486811947722</v>
+        <v>5.027621004547978</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7512,7 +7540,7 @@
         <v>46260</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1480155342121281</v>
+        <v>0.1482237085850297</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7540,7 +7568,7 @@
         <v>25.85620453775692</v>
       </c>
       <c r="K64" t="n">
-        <v>2.008613259943881</v>
+        <v>2.152081843893416</v>
       </c>
       <c r="L64" t="n">
         <v>27</v>
@@ -7549,13 +7577,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N64" t="n">
-        <v>15.04299023450893</v>
+        <v>14.8828864774671</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>2.932484468182417</v>
+        <v>2.787919839420128</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7621,7 +7649,7 @@
         <v>46260</v>
       </c>
       <c r="C65" t="n">
-        <v>6.989622321107048</v>
+        <v>6.99482680533721</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7677,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>23.37926379412545</v>
+        <v>23.47113219605706</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7684,25 +7712,25 @@
         <v>64.17910447761194</v>
       </c>
       <c r="X65" t="n">
-        <v>24.57355301923612</v>
+        <v>24.66542142116772</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.9587020648967548</v>
+        <v>0.9579955784819405</v>
       </c>
       <c r="Z65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA65" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.010466124963772</v>
+        <v>8.299560422847058</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>3.07073715562175</v>
+        <v>3.071428571428581</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7736,7 +7764,7 @@
         <v>46260</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4763143792573239</v>
+        <v>0.4758980507049195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7796,7 +7824,7 @@
         <v>14.56154975385107</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.379317196194785</v>
+        <v>1.465517839922703</v>
       </c>
       <c r="Z66" t="n">
         <v>54</v>
@@ -7811,7 +7839,7 @@
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.685308063621452</v>
+        <v>4.601924179913652</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7845,7 +7873,7 @@
         <v>46260</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02789603609820436</v>
+        <v>0.02768785693717727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7873,7 +7901,7 @@
         <v>13.52521428537139</v>
       </c>
       <c r="K67" t="n">
-        <v>3.607626004318454</v>
+        <v>2.834435555981729</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -7882,13 +7910,13 @@
         <v>25</v>
       </c>
       <c r="N67" t="n">
-        <v>7.104188996989391</v>
+        <v>6.573256403145478</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0.3787115010869924</v>
+        <v>1.133437877804799</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7905,7 +7933,7 @@
         <v>10.87173616493582</v>
       </c>
       <c r="Y67" t="n">
-        <v>6.551814206112083</v>
+        <v>7.249188013974606</v>
       </c>
       <c r="Z67" t="n">
         <v>3</v>
@@ -7942,7 +7970,7 @@
         <v>46260</v>
       </c>
       <c r="C68" t="n">
-        <v>4.783961967859264</v>
+        <v>4.8339248894794</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8002,7 +8030,7 @@
         <v>151.8400112220386</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.212764659574462</v>
+        <v>1.191490659574457</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8013,7 +8041,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>5.91819097889259</v>
+        <v>6.890610318761247</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8047,11 +8075,11 @@
         <v>46260</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4600764138571027</v>
+        <v>0.4509165105785117</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8061,7 +8089,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -8099,22 +8127,22 @@
         <v>25.43142265824418</v>
       </c>
       <c r="Y69" t="n">
-        <v>5.957445191489352</v>
+        <v>7.829787872340432</v>
       </c>
       <c r="Z69" t="n">
         <v>7</v>
       </c>
       <c r="AA69" t="n">
-        <v>57.14285714285715</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB69" t="n">
-        <v>11.41149887926803</v>
+        <v>12.38000738583723</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.04525058745724619</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8140,7 +8168,7 @@
         <v>46260</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4134442399429802</v>
+        <v>0.4205223416186905</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8168,16 +8196,16 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>8.411665146402814</v>
+        <v>10.26765614737826</v>
       </c>
       <c r="L70" t="n">
         <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>60</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N70" t="n">
-        <v>9.342326941007865</v>
+        <v>12.42488814076528</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
@@ -8210,22 +8238,22 @@
         <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>5.787473029553968</v>
+        <v>4.174569086051494</v>
       </c>
       <c r="Z70" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="AA70" t="n">
-        <v>30</v>
+        <v>32.43243243243244</v>
       </c>
       <c r="AB70" t="n">
-        <v>11.19973885708153</v>
+        <v>11.15205145045965</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>2.34844244347685</v>
+        <v>3.992083184456274</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8259,7 +8287,7 @@
         <v>46260</v>
       </c>
       <c r="C71" t="n">
-        <v>3.210125809668976</v>
+        <v>3.214289333558398</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8287,7 +8315,7 @@
         <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>3.847021678144014</v>
+        <v>3.981710964869123</v>
       </c>
       <c r="L71" t="n">
         <v>61</v>
@@ -8296,7 +8324,7 @@
         <v>57.37704918032787</v>
       </c>
       <c r="N71" t="n">
-        <v>18.09911134683085</v>
+        <v>17.92282119072383</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8393,25 +8421,25 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>21.68783215290538</v>
+        <v>23.28291329508295</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9227929129847157</v>
+        <v>3.02115262273992</v>
       </c>
       <c r="L72" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M72" t="n">
-        <v>63.63636363636363</v>
+        <v>50</v>
       </c>
       <c r="N72" t="n">
-        <v>15.64985265414489</v>
+        <v>16.54921427825406</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>4.039926927637283</v>
+        <v>1.920816576869955</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8483,7 +8511,7 @@
         <v>46260</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07078098761199166</v>
+        <v>0.07119734593404584</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8500,11 +8528,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8515,22 +8539,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>7.586422998506892</v>
+        <v>8.219283658787923</v>
       </c>
       <c r="L73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M73" t="n">
-        <v>85.71428571428571</v>
+        <v>62.5</v>
       </c>
       <c r="N73" t="n">
-        <v>10.78728381292863</v>
+        <v>10.17048915836387</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>2.243384373441448</v>
+        <v>1.645470456842646</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8557,22 +8581,22 @@
         <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.769579235547751</v>
+        <v>6.221165560300923</v>
       </c>
       <c r="Z73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA73" t="n">
-        <v>50</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB73" t="n">
-        <v>13.29567252782323</v>
+        <v>12.4822167630246</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>3.464985718142299</v>
+        <v>4.029517387666948</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8606,7 +8630,7 @@
         <v>46260</v>
       </c>
       <c r="C74" t="n">
-        <v>5.527162252431634</v>
+        <v>5.54277570512212</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8666,22 +8690,22 @@
         <v>25.512639367661</v>
       </c>
       <c r="Y74" t="n">
-        <v>5.762672288655713</v>
+        <v>5.496465148228181</v>
       </c>
       <c r="Z74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA74" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="AB74" t="n">
-        <v>17.51252122941868</v>
+        <v>15.53953837202927</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>4.496442985229299</v>
+        <v>4.765467089496267</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8715,7 +8739,7 @@
         <v>46260</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1249076215238787</v>
+        <v>0.1255321640032649</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8743,22 +8767,22 @@
         <v>23.35547482758762</v>
       </c>
       <c r="K75" t="n">
-        <v>1.086764120631378</v>
+        <v>1.592201479271282</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>63.63636363636363</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>19.66198819310451</v>
+        <v>14.19840838697934</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.860414636980015</v>
+        <v>4.338717398134229</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8824,7 +8848,7 @@
         <v>46260</v>
       </c>
       <c r="C76" t="n">
-        <v>1.989153936262477</v>
+        <v>1.965213277160469</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8884,22 +8908,22 @@
         <v>15.91088274943551</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.9844527979274709</v>
+        <v>2.176164217616594</v>
       </c>
       <c r="Z76" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA76" t="n">
-        <v>51.06382978723404</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB76" t="n">
-        <v>11.96434750500554</v>
+        <v>12.26340242104013</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.045528997500113</v>
+        <v>1.864408370206083</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -8933,16 +8957,16 @@
         <v>46260</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5479280932978543</v>
+        <v>0.5575043650992886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8957,27 +8981,17 @@
       <c r="I77" t="n">
         <v>10</v>
       </c>
-      <c r="J77" t="n">
-        <v>14.90307427679485</v>
-      </c>
-      <c r="K77" t="n">
-        <v>12.84909818013313</v>
-      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
-        <v>19</v>
-      </c>
-      <c r="M77" t="n">
-        <v>63.1578947368421</v>
-      </c>
-      <c r="N77" t="n">
-        <v>16.70695952106052</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
         <v>8</v>
       </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
         <v>28</v>
       </c>
@@ -9000,25 +9014,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X77" t="n">
-        <v>16.28154284245451</v>
+        <v>17.9084436362188</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.951839628557285</v>
+        <v>2.618179309090907</v>
       </c>
       <c r="Z77" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="AA77" t="n">
-        <v>44.44444444444444</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB77" t="n">
-        <v>12.10535285520056</v>
+        <v>10.52745124503913</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>7.262538871902924</v>
+        <v>7.580286175115858</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9052,7 +9066,7 @@
         <v>46260</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04871397052069839</v>
+        <v>0.04913032905093195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9080,16 +9094,16 @@
         <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>4.267252662287135</v>
+        <v>5.158425350654117</v>
       </c>
       <c r="L78" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M78" t="n">
-        <v>69.23076923076923</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N78" t="n">
-        <v>17.21017009301777</v>
+        <v>18.09519035765859</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9161,7 +9175,7 @@
         <v>46260</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8481227851212707</v>
+        <v>0.8427100769715177</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9178,11 +9192,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>5</v>
       </c>
@@ -9193,16 +9203,16 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>6.971779242343867</v>
+        <v>6.289086793259591</v>
       </c>
       <c r="L79" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M79" t="n">
-        <v>78.94736842105263</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N79" t="n">
-        <v>11.22239942884223</v>
+        <v>10.75498602908957</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
@@ -9274,7 +9284,7 @@
         <v>46260</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1317775390422571</v>
+        <v>0.1305284640760945</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9302,7 +9312,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>7.890194263526307</v>
+        <v>6.867539403461165</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9313,7 +9323,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>1.955512037841367</v>
+        <v>2.931161898200663</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9340,22 +9350,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>3.918128065937276</v>
+        <v>4.828855810643395</v>
       </c>
       <c r="Z80" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AA80" t="n">
-        <v>31.48148148148148</v>
+        <v>37.77777777777778</v>
       </c>
       <c r="AB80" t="n">
-        <v>12.32755663990113</v>
+        <v>12.09197351306652</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>4.248326819510706</v>
+        <v>3.332043778991622</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9389,7 +9399,7 @@
         <v>46260</v>
       </c>
       <c r="C81" t="n">
-        <v>1.223053794087979</v>
+        <v>1.205358579556873</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9449,22 +9459,22 @@
         <v>23.65045506047392</v>
       </c>
       <c r="Y81" t="n">
-        <v>3.846151438373357</v>
+        <v>5.237310998577516</v>
       </c>
       <c r="Z81" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA81" t="n">
-        <v>35.29411764705883</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB81" t="n">
-        <v>10.98924405333862</v>
+        <v>11.39481103130034</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>6.40000234382978</v>
+        <v>5.025911623667612</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9498,7 +9508,7 @@
         <v>46260</v>
       </c>
       <c r="C82" t="n">
-        <v>5.261733556693392</v>
+        <v>5.160766435638841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9558,16 +9568,16 @@
         <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>5.883944513573947</v>
+        <v>7.689932419477441</v>
       </c>
       <c r="Z82" t="n">
         <v>7</v>
       </c>
       <c r="AA82" t="n">
-        <v>57.14285714285715</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB82" t="n">
-        <v>8.315231402804265</v>
+        <v>7.707406747978768</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9607,7 +9617,7 @@
         <v>46260</v>
       </c>
       <c r="C83" t="n">
-        <v>5.953929959304887</v>
+        <v>5.922703053923917</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9667,22 +9677,22 @@
         <v>12.63070246967208</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.389078498293506</v>
+        <v>2.901023890784971</v>
       </c>
       <c r="Z83" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA83" t="n">
-        <v>50</v>
+        <v>41.79104477611941</v>
       </c>
       <c r="AB83" t="n">
-        <v>12.50841496688073</v>
+        <v>13.29647771314206</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.699300699300712</v>
+        <v>3.191564147627435</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9716,7 +9726,7 @@
         <v>46260</v>
       </c>
       <c r="C84" t="n">
-        <v>2.177556170048176</v>
+        <v>2.15881999517633</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9744,22 +9754,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>4.245170028712653</v>
+        <v>3.348221531094753</v>
       </c>
       <c r="L84" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M84" t="n">
-        <v>50</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="N84" t="n">
-        <v>11.58160239314899</v>
+        <v>11.36476701015985</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0.7240910740319739</v>
+        <v>1.598265015531286</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9825,7 +9835,7 @@
         <v>46260</v>
       </c>
       <c r="C85" t="n">
-        <v>6.448355961170241</v>
+        <v>6.437946992709917</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9853,22 +9863,22 @@
         <v>12.61214035274981</v>
       </c>
       <c r="K85" t="n">
-        <v>4.229240317929484</v>
+        <v>4.060992956641463</v>
       </c>
       <c r="L85" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M85" t="n">
-        <v>57.4074074074074</v>
+        <v>55.35714285714285</v>
       </c>
       <c r="N85" t="n">
-        <v>12.58313778139682</v>
+        <v>12.24931108700451</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>3.617756083195656</v>
+        <v>3.785286812513688</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9934,7 +9944,7 @@
         <v>46260</v>
       </c>
       <c r="C86" t="n">
-        <v>4.625745520272935</v>
+        <v>4.627827440954415</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9962,7 +9972,7 @@
         <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>8.443144736472341</v>
+        <v>8.491952009765292</v>
       </c>
       <c r="L86" t="n">
         <v>25</v>
@@ -9971,7 +9981,7 @@
         <v>72</v>
       </c>
       <c r="N86" t="n">
-        <v>12.24412062426394</v>
+        <v>12.27844673925762</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
@@ -10004,7 +10014,7 @@
         <v>70.65007079462626</v>
       </c>
       <c r="Y86" t="n">
-        <v>9.830060459484724</v>
+        <v>9.789477452668971</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
@@ -10049,7 +10059,7 @@
         <v>46260</v>
       </c>
       <c r="C87" t="n">
-        <v>5.813408885090523</v>
+        <v>5.740546105868261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10077,16 +10087,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>7.807748399020409</v>
+        <v>6.456532214968225</v>
       </c>
       <c r="L87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M87" t="n">
-        <v>68.42105263157895</v>
+        <v>65</v>
       </c>
       <c r="N87" t="n">
-        <v>10.05615854119981</v>
+        <v>9.279963059448857</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10119,22 +10129,22 @@
         <v>10.60669620884278</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.530541012216403</v>
+        <v>3.752181500872598</v>
       </c>
       <c r="Z87" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AA87" t="n">
-        <v>38.77551020408163</v>
+        <v>45.94594594594594</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.99051425558094</v>
+        <v>11.53063239809339</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.507609668755605</v>
+        <v>0.257479601087951</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10168,7 +10178,7 @@
         <v>46260</v>
       </c>
       <c r="C88" t="n">
-        <v>1.142904768794934</v>
+        <v>1.138741165380993</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10228,22 +10238,22 @@
         <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>4.438640898635926</v>
+        <v>4.786771041985272</v>
       </c>
       <c r="Z88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA88" t="n">
-        <v>70</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="AB88" t="n">
-        <v>14.14289847092548</v>
+        <v>13.38078431232302</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.633881221496558</v>
+        <v>1.274223100394711</v>
       </c>
       <c r="AE88" t="n">
         <v>32</v>
@@ -10277,7 +10287,7 @@
         <v>46260</v>
       </c>
       <c r="C89" t="n">
-        <v>2.215028520208226</v>
+        <v>2.258746155890141</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10337,22 +10347,22 @@
         <v>27.21456043612742</v>
       </c>
       <c r="Y89" t="n">
-        <v>5.422220862222238</v>
+        <v>3.555555555555556</v>
       </c>
       <c r="Z89" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA89" t="n">
-        <v>57.14285714285715</v>
+        <v>48</v>
       </c>
       <c r="AB89" t="n">
-        <v>13.45429903085463</v>
+        <v>12.88646361450231</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>4.840226932278668</v>
+        <v>6.682027649769584</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10386,7 +10396,7 @@
         <v>46260</v>
       </c>
       <c r="C90" t="n">
-        <v>2.951983518842375</v>
+        <v>2.956147042731797</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10446,7 +10456,7 @@
         <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>5.529648709321422</v>
+        <v>5.396406243050789</v>
       </c>
       <c r="Z90" t="n">
         <v>18</v>
@@ -10455,7 +10465,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB90" t="n">
-        <v>12.83088714997792</v>
+        <v>12.9602786450444</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10495,7 +10505,7 @@
         <v>46260</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2346181586719366</v>
+        <v>0.2333690737131643</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10523,16 +10533,16 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>4.799476666049829</v>
+        <v>4.241534131969127</v>
       </c>
       <c r="L91" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M91" t="n">
-        <v>66.0377358490566</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N91" t="n">
-        <v>14.93392473092584</v>
+        <v>13.70636854701426</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10604,7 +10614,7 @@
         <v>46260</v>
       </c>
       <c r="C92" t="n">
-        <v>1.12937307794507</v>
+        <v>1.123127712690508</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10623,7 +10633,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -10636,22 +10646,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>7.186419836209845</v>
+        <v>6.593685375579716</v>
       </c>
       <c r="L92" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M92" t="n">
-        <v>77.27272727272727</v>
+        <v>75</v>
       </c>
       <c r="N92" t="n">
-        <v>11.47873103029748</v>
+        <v>12.98401798456282</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.7590328747180797</v>
+        <v>1.319322640422071</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10678,16 +10688,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>6.522360327497023</v>
+        <v>7.039286057612138</v>
       </c>
       <c r="Z92" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AA92" t="n">
-        <v>53.65853658536585</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.50202474682687</v>
+        <v>11.51843604221565</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10836,7 +10846,7 @@
         <v>46260</v>
       </c>
       <c r="C94" t="n">
-        <v>7.874384640234522</v>
+        <v>7.942042935226623</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10853,7 +10863,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H94" t="n">
         <v>5</v>
       </c>
@@ -10864,22 +10878,22 @@
         <v>10.06134969325154</v>
       </c>
       <c r="K94" t="n">
-        <v>3.206002728512969</v>
+        <v>4.092769440654842</v>
       </c>
       <c r="L94" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M94" t="n">
-        <v>35.29411764705883</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="N94" t="n">
-        <v>14.60794312578426</v>
+        <v>13.36504840235806</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>4.64507600793127</v>
+        <v>3.753604193971172</v>
       </c>
       <c r="Q94" t="n">
         <v>41</v>
@@ -10906,16 +10920,16 @@
         <v>47.10636343143248</v>
       </c>
       <c r="Y94" t="n">
-        <v>7.177914110429451</v>
+        <v>6.380368098159517</v>
       </c>
       <c r="Z94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA94" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="AB94" t="n">
-        <v>7.826121987750933</v>
+        <v>8.912256662677548</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
@@ -10955,7 +10969,7 @@
         <v>46260</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1394801734129232</v>
+        <v>0.1384392826040926</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10983,22 +10997,22 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>4.555825161156846</v>
+        <v>3.775562312631697</v>
       </c>
       <c r="L95" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>72.72727272727273</v>
+        <v>60</v>
       </c>
       <c r="N95" t="n">
-        <v>17.79602740297683</v>
+        <v>17.65857382010481</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>1.381247612571745</v>
+        <v>2.143508199615463</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11025,16 +11039,16 @@
         <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>6.66886786408628</v>
+        <v>7.365364830220866</v>
       </c>
       <c r="Z95" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA95" t="n">
-        <v>41.66666666666666</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AB95" t="n">
-        <v>11.37674008022595</v>
+        <v>12.66316037663308</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
@@ -11074,7 +11088,7 @@
         <v>46260</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1309448223981488</v>
+        <v>0.1311530065554807</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11102,22 +11116,22 @@
         <v>14.68867757321659</v>
       </c>
       <c r="K96" t="n">
-        <v>3.453948071762492</v>
+        <v>3.618425541031933</v>
       </c>
       <c r="L96" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M96" t="n">
-        <v>50.98039215686274</v>
+        <v>52.83018867924528</v>
       </c>
       <c r="N96" t="n">
-        <v>14.89759144000573</v>
+        <v>15.3409343063313</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.327503251685229</v>
+        <v>6.1587255602924</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11183,7 +11197,7 @@
         <v>46260</v>
       </c>
       <c r="C97" t="n">
-        <v>1.909004752128572</v>
+        <v>1.925659165159797</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11211,16 +11225,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>6.808476654299689</v>
+        <v>7.740288103932391</v>
       </c>
       <c r="L97" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M97" t="n">
-        <v>47.05882352941177</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N97" t="n">
-        <v>15.33088048225494</v>
+        <v>15.36480226587528</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11253,16 +11267,16 @@
         <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>9.084882590236788</v>
+        <v>8.29172693442387</v>
       </c>
       <c r="Z97" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AA97" t="n">
-        <v>30.76923076923077</v>
+        <v>35</v>
       </c>
       <c r="AB97" t="n">
-        <v>10.41431718008398</v>
+        <v>10.12124489740237</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11302,7 +11316,7 @@
         <v>46260</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6811629214414351</v>
+        <v>0.6682557433013079</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11362,22 +11376,22 @@
         <v>15.47968337611683</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.505117343881901</v>
+        <v>3.371471128440839</v>
       </c>
       <c r="Z98" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="AA98" t="n">
-        <v>32.69230769230769</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="AB98" t="n">
-        <v>13.34973421825646</v>
+        <v>12.47197412499304</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>6.594132081759129</v>
+        <v>4.790023118029152</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11520,7 +11534,7 @@
         <v>46260</v>
       </c>
       <c r="C100" t="n">
-        <v>349.8166833079946</v>
+        <v>345.0296149773133</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11580,22 +11594,22 @@
         <v>15.09065341954294</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.8277330215197276</v>
+        <v>2.184856455557216</v>
       </c>
       <c r="Z100" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AA100" t="n">
-        <v>38.77551020408163</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB100" t="n">
-        <v>14.01566572437516</v>
+        <v>13.39507036278363</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>7.232129704201073</v>
+        <v>5.945034003656746</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11629,7 +11643,7 @@
         <v>46260</v>
       </c>
       <c r="C101" t="n">
-        <v>353.6030675656404</v>
+        <v>352.2977991847291</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11689,22 +11703,22 @@
         <v>12.28498792189239</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.2759430500513749</v>
+        <v>0.6440582342580492</v>
       </c>
       <c r="Z101" t="n">
         <v>42</v>
       </c>
       <c r="AA101" t="n">
-        <v>42.85714285714285</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.00744684891971</v>
+        <v>11.10456531072113</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>5.739895793470906</v>
+        <v>5.390660760249255</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11738,7 +11752,7 @@
         <v>46260</v>
       </c>
       <c r="C102" t="n">
-        <v>419.3771359663617</v>
+        <v>419.9750417522305</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11798,22 +11812,22 @@
         <v>11.13903673030769</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.639148062204143</v>
+        <v>1.498915041772375</v>
       </c>
       <c r="Z102" t="n">
         <v>37</v>
       </c>
       <c r="AA102" t="n">
-        <v>29.72972972972973</v>
+        <v>32.43243243243244</v>
       </c>
       <c r="AB102" t="n">
-        <v>14.69226624811142</v>
+        <v>14.36666630901875</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>3.416859321146681</v>
+        <v>3.554361822219898</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11847,7 +11861,7 @@
         <v>46260</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7844198696235188</v>
+        <v>0.7744272692696803</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11907,22 +11921,22 @@
         <v>21.73107604932552</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.8942665594065757</v>
+        <v>2.156758785057622</v>
       </c>
       <c r="Z103" t="n">
         <v>37</v>
       </c>
       <c r="AA103" t="n">
-        <v>43.24324324324324</v>
+        <v>45.94594594594594</v>
       </c>
       <c r="AB103" t="n">
-        <v>15.86336079108647</v>
+        <v>14.19651305872401</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.169851020630191</v>
+        <v>5.97204379411953</v>
       </c>
       <c r="AE103" t="n">
         <v>34</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46260</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3963735381216105</v>
+        <v>0.393458999889402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>18.04725545643595</v>
       </c>
       <c r="K2" t="n">
-        <v>1.546671573333325</v>
+        <v>0.7999979733333218</v>
       </c>
       <c r="L2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M2" t="n">
-        <v>51.51515151515152</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N2" t="n">
-        <v>11.44853795737839</v>
+        <v>11.84276532860607</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>8.324574597762169</v>
+        <v>9.126986321071694</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -779,7 +779,7 @@
         <v>46260</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6461887811693681</v>
+        <v>0.6436906112518235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>15.98490517159132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.092668168145861</v>
+        <v>0.7018432732212476</v>
       </c>
       <c r="L3" t="n">
         <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>58.49056603773585</v>
+        <v>60.37735849056604</v>
       </c>
       <c r="N3" t="n">
-        <v>12.80061761725111</v>
+        <v>12.41245197393265</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>8.811056225203906</v>
+        <v>9.233353059438333</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -888,7 +888,7 @@
         <v>46260</v>
       </c>
       <c r="C4" t="n">
-        <v>1.525954839778093</v>
+        <v>1.522832117596732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
         <v>20.64833628068863</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.070802206657685</v>
+        <v>2.271205043085422</v>
       </c>
       <c r="Z4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA4" t="n">
-        <v>37.14285714285715</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.08595786741356</v>
+        <v>16.0557060830229</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.096867912749694</v>
+        <v>7.908411190705822</v>
       </c>
       <c r="AE4" t="n">
         <v>42</v>
@@ -997,7 +997,7 @@
         <v>46260</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2319118243741001</v>
+        <v>0.2310791077299917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1029,22 +1029,22 @@
         <v>18.40585323077206</v>
       </c>
       <c r="K5" t="n">
-        <v>1.735164687642143</v>
+        <v>1.369868242947492</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>80</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N5" t="n">
-        <v>11.83017222636494</v>
+        <v>11.54609159961377</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.243262657746014</v>
+        <v>1.60810286656945</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1110,7 +1110,7 @@
         <v>46260</v>
       </c>
       <c r="C6" t="n">
-        <v>1.717479795953333</v>
+        <v>1.703948105103469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>34.26396223505859</v>
       </c>
       <c r="K6" t="n">
-        <v>4.947255760779656</v>
+        <v>4.120396647884994</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1176,16 +1176,16 @@
         <v>11.97728590062597</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.278085848664983</v>
+        <v>7.016502667972812</v>
       </c>
       <c r="Z6" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.20462901185882</v>
+        <v>11.96471300336523</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1225,7 +1225,7 @@
         <v>46260</v>
       </c>
       <c r="C7" t="n">
-        <v>2.269155124350464</v>
+        <v>2.258746155890141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,22 +1253,22 @@
         <v>12.3532304777189</v>
       </c>
       <c r="K7" t="n">
-        <v>6.653623535161968</v>
+        <v>6.164386729954807</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>60</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="N7" t="n">
-        <v>13.72160353748486</v>
+        <v>12.92951265381202</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.262382299082554</v>
+        <v>1.729029222119816</v>
       </c>
       <c r="Q7" t="n">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>16.68422911664862</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.521544392975242</v>
+        <v>6.95034464805333</v>
       </c>
       <c r="Z7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA7" t="n">
-        <v>40</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.61592700380395</v>
+        <v>11.30388131261403</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1344,7 +1344,7 @@
         <v>46260</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3747228645716362</v>
+        <v>0.3730574312834195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>30.59320720320773</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.768370908943279</v>
+        <v>9.17384441054072</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>46260</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5787386305723394</v>
+        <v>0.5749914352353221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,16 +1509,16 @@
         <v>11.90150170974167</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.943000208412564</v>
+        <v>7.545522205865895</v>
       </c>
       <c r="Z9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA9" t="n">
-        <v>52.94117647058823</v>
+        <v>50</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.11294478239028</v>
+        <v>9.83035885986545</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
@@ -1558,7 +1558,7 @@
         <v>46260</v>
       </c>
       <c r="C10" t="n">
-        <v>1.950640625969865</v>
+        <v>1.943354379690903</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,22 +1586,22 @@
         <v>10.84633778363752</v>
       </c>
       <c r="K10" t="n">
-        <v>1.571812411924123</v>
+        <v>1.192410265582655</v>
       </c>
       <c r="L10" t="n">
         <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>37.77777777777778</v>
+        <v>40</v>
       </c>
       <c r="N10" t="n">
-        <v>10.33045012050676</v>
+        <v>10.02801711176273</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>4.359661881504473</v>
+        <v>4.750939049479785</v>
       </c>
       <c r="Q10" t="n">
         <v>41</v>
@@ -1667,7 +1667,7 @@
         <v>46260</v>
       </c>
       <c r="C11" t="n">
-        <v>8.34799270517923</v>
+        <v>8.290743378647452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,16 +1727,16 @@
         <v>23.11730782489165</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.846759539672916</v>
+        <v>3.513022410660205</v>
       </c>
       <c r="Z11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>60.60606060606061</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.98281951353008</v>
+        <v>11.99720551097435</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1776,7 +1776,7 @@
         <v>46260</v>
       </c>
       <c r="C12" t="n">
-        <v>7.145756848011897</v>
+        <v>7.052076131868987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,7 +1793,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1804,16 +1808,16 @@
         <v>11.11876289107619</v>
       </c>
       <c r="K12" t="n">
-        <v>8.770109049261521</v>
+        <v>7.344135296248622</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M12" t="n">
-        <v>58.33333333333334</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N12" t="n">
-        <v>14.38160145879287</v>
+        <v>18.25138940387051</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1846,16 +1850,16 @@
         <v>28.6826569971012</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.323781472290888</v>
+        <v>4.591204584817299</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>25</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.759433103302454</v>
+        <v>10.19016848477012</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -1895,7 +1899,7 @@
         <v>46260</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2200455867976726</v>
+        <v>0.2187965218241197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1927,7 @@
         <v>45.31810005101507</v>
       </c>
       <c r="K13" t="n">
-        <v>4.173972027493322</v>
+        <v>3.582639742628801</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1934,7 +1938,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7929312441774528</v>
+        <v>1.368337648946683</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1959,7 +1963,7 @@
         <v>16.61490210926415</v>
       </c>
       <c r="Y13" t="n">
-        <v>10.66838787903293</v>
+        <v>11.1754691132224</v>
       </c>
       <c r="Z13" t="n">
         <v>8</v>
@@ -1998,7 +2002,7 @@
         <v>46260</v>
       </c>
       <c r="C14" t="n">
-        <v>8.753942475131835</v>
+        <v>8.70710211706038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,22 +2062,22 @@
         <v>13.50145199425789</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5322294500295754</v>
+        <v>1.06445890005914</v>
       </c>
       <c r="Z14" t="n">
         <v>48</v>
       </c>
       <c r="AA14" t="n">
-        <v>50</v>
+        <v>47.91666666666666</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.25836860253546</v>
+        <v>12.44466610182263</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.475624256837094</v>
+        <v>0.9456066945606634</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2107,7 +2111,7 @@
         <v>46260</v>
       </c>
       <c r="C15" t="n">
-        <v>14.70787243443672</v>
+        <v>14.6974634659764</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2171,7 @@
         <v>48.8712056268954</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.978275181040161</v>
+        <v>7.044107965766944</v>
       </c>
       <c r="Z15" t="n">
         <v>8</v>
@@ -2182,7 +2186,7 @@
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.248407643312101</v>
+        <v>3.179886685552413</v>
       </c>
       <c r="AE15" t="n">
         <v>32</v>
@@ -2216,7 +2220,7 @@
         <v>46260</v>
       </c>
       <c r="C16" t="n">
-        <v>35.64030800814673</v>
+        <v>35.61949007122609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,22 +2248,22 @@
         <v>13.95417336448531</v>
       </c>
       <c r="K16" t="n">
-        <v>2.351762428243709</v>
+        <v>2.291977520283295</v>
       </c>
       <c r="L16" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M16" t="n">
-        <v>65.85365853658537</v>
+        <v>66.26506024096386</v>
       </c>
       <c r="N16" t="n">
-        <v>17.8225095684651</v>
+        <v>17.74486329610112</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.47250207549508</v>
+        <v>7.535314759349832</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2286,7 +2290,7 @@
         <v>16.64483533193928</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.93057994259955</v>
+        <v>11.98202236085737</v>
       </c>
       <c r="Z16" t="n">
         <v>27</v>
@@ -2335,7 +2339,7 @@
         <v>46260</v>
       </c>
       <c r="C17" t="n">
-        <v>0.667423086196499</v>
+        <v>0.6453560445400401</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,25 +2364,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>16.70278702842509</v>
+        <v>19.00208060987847</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5646242620541031</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M17" t="n">
-        <v>72.72727272727273</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N17" t="n">
-        <v>15.4411099493113</v>
+        <v>13.85500148009473</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.393629511875455</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2444,7 +2448,7 @@
         <v>46260</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09680340876279972</v>
+        <v>0.09617886628341357</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,22 +2476,22 @@
         <v>20.97644296643689</v>
       </c>
       <c r="K18" t="n">
-        <v>1.086960893194799</v>
+        <v>0.4347824007561396</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M18" t="n">
-        <v>68.42105263157895</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="N18" t="n">
-        <v>15.71182240184449</v>
+        <v>16.18939240621242</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>8.817199595329051</v>
+        <v>9.523809750566903</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2553,7 +2557,7 @@
         <v>46260</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02539788366772679</v>
+        <v>0.02518970450669969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,22 +2585,22 @@
         <v>12.84048157776297</v>
       </c>
       <c r="K19" t="n">
-        <v>3.054499559959467</v>
+        <v>2.209791412653428</v>
       </c>
       <c r="L19" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>57.14285714285715</v>
+        <v>55</v>
       </c>
       <c r="N19" t="n">
-        <v>16.10894371912864</v>
+        <v>18.14575358321196</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>6.739638220259847</v>
+        <v>7.62178307936765</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -2662,7 +2666,7 @@
         <v>46260</v>
       </c>
       <c r="C20" t="n">
-        <v>1.64149429434153</v>
+        <v>1.64357605639033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2694,7 @@
         <v>18.92576555578012</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2034956659579</v>
+        <v>2.33311132119689</v>
       </c>
       <c r="L20" t="n">
         <v>30</v>
@@ -2771,7 +2775,7 @@
         <v>46260</v>
       </c>
       <c r="C21" t="n">
-        <v>0.971781301909337</v>
+        <v>0.9705321969653453</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,7 +2803,7 @@
         <v>14.36185804747686</v>
       </c>
       <c r="K21" t="n">
-        <v>4.604935280928268</v>
+        <v>4.470478545067436</v>
       </c>
       <c r="L21" t="n">
         <v>45</v>
@@ -2808,13 +2812,13 @@
         <v>53.33333333333334</v>
       </c>
       <c r="N21" t="n">
-        <v>16.07122873295376</v>
+        <v>15.48870140099583</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>3.245606634098008</v>
+        <v>3.378486921939361</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2880,7 +2884,7 @@
         <v>46260</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3301724724833542</v>
+        <v>0.3312133732847946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2903,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.86: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2912,22 +2916,22 @@
         <v>10.07269919155901</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06308693855059389</v>
+        <v>0.3785455429749396</v>
       </c>
       <c r="L22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M22" t="n">
-        <v>75</v>
+        <v>75.86206896551724</v>
       </c>
       <c r="N22" t="n">
-        <v>13.6274302469148</v>
+        <v>14.0617482332803</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.930648119572538</v>
+        <v>9.585170222361761</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2954,7 +2958,7 @@
         <v>23.69855403109109</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.01596681055777</v>
+        <v>9.732283402430985</v>
       </c>
       <c r="Z22" t="n">
         <v>11</v>
@@ -2995,7 +2999,7 @@
         <v>46260</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7536093323490338</v>
+        <v>0.7494457291432725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3023,22 +3027,22 @@
         <v>27.73484467032905</v>
       </c>
       <c r="K23" t="n">
-        <v>2.66591742707718</v>
+        <v>2.098700270159282</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>25.2492217942063</v>
+        <v>25.26583029055753</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>7.143639054442952</v>
+        <v>7.738883755555559</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -3065,7 +3069,7 @@
         <v>45.87078932576518</v>
       </c>
       <c r="Y23" t="n">
-        <v>25.80831530069095</v>
+        <v>26.21821566019422</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3110,7 +3114,7 @@
         <v>46260</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1782015487842672</v>
+        <v>0.1759115630240545</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3138,22 +3142,22 @@
         <v>23.47035234733546</v>
       </c>
       <c r="K24" t="n">
-        <v>5.403129000268203</v>
+        <v>4.048642094070343</v>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>44.44444444444444</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N24" t="n">
-        <v>12.66278934205094</v>
+        <v>12.01857428254015</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.361228213367463</v>
+        <v>5.719784310639109</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3180,16 +3184,16 @@
         <v>12.66805408629466</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.448078956313652</v>
+        <v>7.650271465257175</v>
       </c>
       <c r="Z24" t="n">
         <v>27</v>
       </c>
       <c r="AA24" t="n">
-        <v>55.55555555555556</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.86006130287472</v>
+        <v>11.84288578987343</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3229,7 +3233,7 @@
         <v>46260</v>
       </c>
       <c r="C25" t="n">
-        <v>3.48075898963738</v>
+        <v>3.472431941858536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,7 +3261,7 @@
         <v>16.84600295124913</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7228897289156766</v>
+        <v>0.4819295481927499</v>
       </c>
       <c r="L25" t="n">
         <v>55</v>
@@ -3266,13 +3270,13 @@
         <v>60</v>
       </c>
       <c r="N25" t="n">
-        <v>16.94598916835746</v>
+        <v>17.03187086590652</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.224882338731398</v>
+        <v>7.482012423140683</v>
       </c>
       <c r="Q25" t="n">
         <v>45</v>
@@ -3338,7 +3342,7 @@
         <v>46260</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4554964423366775</v>
+        <v>0.4550801137842731</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3437,7 +3441,7 @@
         <v>46260</v>
       </c>
       <c r="C27" t="n">
-        <v>49.92141273571021</v>
+        <v>50.48349703256766</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3469,7 @@
         <v>44.6752281083318</v>
       </c>
       <c r="K27" t="n">
-        <v>51.4458994490321</v>
+        <v>53.15108680729894</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3493,22 +3497,20 @@
         <v>54.9825843402522</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.281988590057049</v>
+        <v>1.181744091279535</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>29.81059277025319</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.804837364470393</v>
+        <v>4.875876288659809</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3532,7 +3534,7 @@
         <v>46260</v>
       </c>
       <c r="C28" t="n">
-        <v>1.617553635239522</v>
+        <v>1.618594595580262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,22 +3594,22 @@
         <v>18.7701780791061</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.325588974317461</v>
+        <v>2.262731591435174</v>
       </c>
       <c r="Z28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA28" t="n">
-        <v>50</v>
+        <v>48.78048780487805</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.09112479202844</v>
+        <v>11.09551382093546</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.76189729438593</v>
+        <v>3.823790524758852</v>
       </c>
       <c r="AE28" t="n">
         <v>45</v>
@@ -3641,7 +3643,7 @@
         <v>46260</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3847154647172956</v>
+        <v>0.3788864677773976</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3660,7 +3662,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3673,16 +3675,16 @@
         <v>21.08862618190814</v>
       </c>
       <c r="K29" t="n">
-        <v>6.424753187439358</v>
+        <v>4.812263912762438</v>
       </c>
       <c r="L29" t="n">
         <v>8</v>
       </c>
       <c r="M29" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="N29" t="n">
-        <v>15.4238136460709</v>
+        <v>16.5204194541522</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
@@ -3715,7 +3717,7 @@
         <v>39.82687732422523</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.01876517727811</v>
+        <v>17.29120261659504</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3760,7 +3762,7 @@
         <v>46260</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4321803752607459</v>
+        <v>0.4288495084761331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3788,10 +3790,10 @@
         <v>19.31293850160538</v>
       </c>
       <c r="K30" t="n">
-        <v>18.05995946893317</v>
+        <v>17.15005698354024</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3826,22 +3828,22 @@
         <v>19.87976438285015</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.518025100637665</v>
+        <v>2.277037674675653</v>
       </c>
       <c r="Z30" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA30" t="n">
-        <v>42.5</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.84109102484534</v>
+        <v>13.02314100627515</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>8.612718122306106</v>
+        <v>7.90291466975207</v>
       </c>
       <c r="AE30" t="n">
         <v>50</v>
@@ -3875,7 +3877,7 @@
         <v>46260</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1983949332329178</v>
+        <v>0.1979785849034733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,11 +3894,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>5</v>
       </c>
@@ -3907,16 +3905,16 @@
         <v>17.76611681824961</v>
       </c>
       <c r="K31" t="n">
-        <v>13.93478650261488</v>
+        <v>13.69568484183665</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N31" t="n">
-        <v>21.58764950302011</v>
+        <v>19.79952100570422</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
@@ -3949,22 +3947,22 @@
         <v>15.13032923800595</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.038425533309772</v>
+        <v>1.246104658663394</v>
       </c>
       <c r="Z31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>37.5</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.54991073289974</v>
+        <v>8.7117675738023</v>
       </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.055610235573431</v>
+        <v>8.864354475415192</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3998,7 +3996,7 @@
         <v>46260</v>
       </c>
       <c r="C32" t="n">
-        <v>2.373244808953696</v>
+        <v>2.394062745874343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4026,16 +4024,16 @@
         <v>11.40736836637816</v>
       </c>
       <c r="K32" t="n">
-        <v>8.894842187680418</v>
+        <v>9.85006010160745</v>
       </c>
       <c r="L32" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M32" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N32" t="n">
-        <v>10.05140696430216</v>
+        <v>10.4033552121596</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4068,22 +4066,22 @@
         <v>16.29216385551018</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.527193592654454</v>
+        <v>2.680940904870721</v>
       </c>
       <c r="Z32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
-        <v>37.83783783783784</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.34865277684842</v>
+        <v>11.66714271954782</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.636339061662231</v>
+        <v>5.465588287212986</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4117,7 +4115,7 @@
         <v>46260</v>
       </c>
       <c r="C33" t="n">
-        <v>1.831978449016888</v>
+        <v>1.826773964786727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4145,13 +4143,13 @@
         <v>16.35407824144015</v>
       </c>
       <c r="K33" t="n">
-        <v>11.79339555215793</v>
+        <v>11.47580067843021</v>
       </c>
       <c r="L33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M33" t="n">
-        <v>35</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="N33" t="n">
         <v>11.24432156054373</v>
@@ -4187,22 +4185,22 @@
         <v>13.38136992079653</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.400560224089631</v>
+        <v>1.680672268907557</v>
       </c>
       <c r="Z33" t="n">
         <v>52</v>
       </c>
       <c r="AA33" t="n">
-        <v>40.38461538461539</v>
+        <v>36.53846153846154</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.624387755341449</v>
+        <v>9.004967211098064</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>6.693181818181815</v>
+        <v>6.427350427350431</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4236,7 +4234,7 @@
         <v>46260</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8131486446410242</v>
+        <v>0.80565417465065</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4264,16 +4262,16 @@
         <v>20.55024425142384</v>
       </c>
       <c r="K34" t="n">
-        <v>7.141300435431042</v>
+        <v>6.153821373472468</v>
       </c>
       <c r="L34" t="n">
         <v>19</v>
       </c>
       <c r="M34" t="n">
-        <v>63.1578947368421</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N34" t="n">
-        <v>8.8967926345666</v>
+        <v>10.22963839593302</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4345,11 +4343,11 @@
         <v>46260</v>
       </c>
       <c r="C35" t="n">
-        <v>2.03287157215257</v>
+        <v>2.071384723604322</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4359,7 +4357,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4373,17 +4371,13 @@
         <v>22.90920320256731</v>
       </c>
       <c r="K35" t="n">
-        <v>14.60364458680314</v>
+        <v>16.77483315638935</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N35" t="n">
-        <v>8.916991455449475</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>6</v>
       </c>
@@ -4415,22 +4409,22 @@
         <v>17.15050612259421</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.174008137127337</v>
+        <v>0.3206754956839419</v>
       </c>
       <c r="Z35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
-        <v>33.33333333333334</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB35" t="n">
-        <v>15.35229831342463</v>
+        <v>10.1803673588835</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.684727011009535</v>
       </c>
       <c r="AE35" t="n">
         <v>7</v>
@@ -4464,7 +4458,7 @@
         <v>46260</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08181449355539616</v>
+        <v>0.08098177670310841</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4492,16 +4486,16 @@
         <v>14.21000360644873</v>
       </c>
       <c r="K36" t="n">
-        <v>4.80589512961862</v>
+        <v>3.739169280677901</v>
       </c>
       <c r="L36" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>68</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N36" t="n">
-        <v>19.18020771280047</v>
+        <v>20.88828552891385</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4573,7 +4567,7 @@
         <v>46260</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06661739918696551</v>
+        <v>0.0668255783479926</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4601,16 +4595,16 @@
         <v>12.9660944973907</v>
       </c>
       <c r="K37" t="n">
-        <v>8.441878398335056</v>
+        <v>8.780758924153975</v>
       </c>
       <c r="L37" t="n">
         <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="N37" t="n">
-        <v>13.24932532116409</v>
+        <v>15.13534679504481</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
@@ -4643,22 +4637,22 @@
         <v>12.13930183605394</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.297170017274098</v>
+        <v>2.994973980496241</v>
       </c>
       <c r="Z37" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA37" t="n">
-        <v>47.82608695652174</v>
+        <v>47.14285714285715</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.08245291089954</v>
+        <v>12.17603319232258</v>
       </c>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.7267936035082467</v>
+        <v>1.036055615614895</v>
       </c>
       <c r="AE37" t="n">
         <v>47</v>
@@ -4692,7 +4686,7 @@
         <v>46260</v>
       </c>
       <c r="C38" t="n">
-        <v>1.661271429762295</v>
+        <v>1.656066945532133</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4720,22 +4714,22 @@
         <v>12.1721159722968</v>
       </c>
       <c r="K38" t="n">
-        <v>4.855748011104066</v>
+        <v>4.527252572496754</v>
       </c>
       <c r="L38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M38" t="n">
-        <v>54.54545454545455</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N38" t="n">
-        <v>10.04512095799568</v>
+        <v>10.81984119742141</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>4.906027648909794</v>
+        <v>5.235713455404878</v>
       </c>
       <c r="Q38" t="n">
         <v>43</v>
@@ -4801,7 +4795,7 @@
         <v>46260</v>
       </c>
       <c r="C39" t="n">
-        <v>2.783358102795724</v>
+        <v>2.77503105501688</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4861,22 +4855,22 @@
         <v>13.14448726963784</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.622000014587744</v>
+        <v>2.913328413068816</v>
       </c>
       <c r="Z39" t="n">
         <v>59</v>
       </c>
       <c r="AA39" t="n">
-        <v>45.76271186440678</v>
+        <v>40.67796610169491</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.07677473510738</v>
+        <v>12.52088334591607</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.468956012567836</v>
+        <v>3.179294888245698</v>
       </c>
       <c r="AE39" t="n">
         <v>42</v>
@@ -4910,7 +4904,7 @@
         <v>46260</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2533542939897023</v>
+        <v>0.2537706423191468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4970,7 +4964,7 @@
         <v>38.77366535417291</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.856249412702983</v>
+        <v>3.698252130268231</v>
       </c>
       <c r="Z40" t="n">
         <v>9</v>
@@ -4985,7 +4979,7 @@
         <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.189625514201798</v>
+        <v>1.351738570199845</v>
       </c>
       <c r="AE40" t="n">
         <v>14</v>
@@ -5019,7 +5013,7 @@
         <v>46260</v>
       </c>
       <c r="C41" t="n">
-        <v>1.913168434858853</v>
+        <v>1.919413720588896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5079,22 +5073,22 @@
         <v>29.59721231101309</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.44160880516886</v>
+        <v>2.123142319273719</v>
       </c>
       <c r="Z41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA41" t="n">
-        <v>30</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB41" t="n">
-        <v>8.570955018008446</v>
+        <v>15.157130260983</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.572366136825686</v>
+        <v>0.8958784553408816</v>
       </c>
       <c r="AE41" t="n">
         <v>11</v>
@@ -5128,7 +5122,7 @@
         <v>46260</v>
       </c>
       <c r="C42" t="n">
-        <v>3.736819677256039</v>
+        <v>3.753474090287264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5186,7 +5180,7 @@
         <v>25.82713732855415</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.37680837788531</v>
+        <v>2.946174127197709</v>
       </c>
       <c r="Z42" t="n">
         <v>4</v>
@@ -5201,7 +5195,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.854660367686305</v>
+        <v>7.267952406169909</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5233,7 +5227,7 @@
         <v>46260</v>
       </c>
       <c r="C43" t="n">
-        <v>6.60969497230525</v>
+        <v>6.620103940765573</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5261,22 +5255,22 @@
         <v>15.35826860100024</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7936507936507908</v>
+        <v>0.952380952380949</v>
       </c>
       <c r="L43" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M43" t="n">
-        <v>73.33333333333333</v>
+        <v>70.96774193548387</v>
       </c>
       <c r="N43" t="n">
-        <v>17.12829277832295</v>
+        <v>17.74052745685094</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.181102362204724</v>
+        <v>3.018867924528301</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5342,7 +5336,7 @@
         <v>46260</v>
       </c>
       <c r="C44" t="n">
-        <v>4.746489617907392</v>
+        <v>4.709017267955521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5370,22 +5364,22 @@
         <v>20.15821391009879</v>
       </c>
       <c r="K44" t="n">
-        <v>5.81888975977769</v>
+        <v>4.983476056640801</v>
       </c>
       <c r="L44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M44" t="n">
-        <v>60</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N44" t="n">
-        <v>21.1641194607964</v>
+        <v>19.82944032395692</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>3.951194583229856</v>
+        <v>4.778393830904104</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5443,7 +5437,7 @@
         <v>46260</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02373244788135759</v>
+        <v>0.02394062704238469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,22 +5497,22 @@
         <v>19.58690552546656</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.724136251486297</v>
+        <v>0.8620681257431539</v>
       </c>
       <c r="Z45" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AA45" t="n">
-        <v>53.19148936170212</v>
+        <v>51.21951219512195</v>
       </c>
       <c r="AB45" t="n">
-        <v>13.18215995678039</v>
+        <v>12.3323041522808</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.333334985380121</v>
+        <v>4.173913855198497</v>
       </c>
       <c r="AE45" t="n">
         <v>18</v>
@@ -5552,7 +5546,7 @@
         <v>46260</v>
       </c>
       <c r="C46" t="n">
-        <v>10.07588146959288</v>
+        <v>10.08629043805321</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5612,7 +5606,7 @@
         <v>27.31942745255147</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.158415841584173</v>
+        <v>4.059405940594063</v>
       </c>
       <c r="Z46" t="n">
         <v>24</v>
@@ -5776,7 +5770,7 @@
         <v>46260</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05933111814204871</v>
+        <v>0.05912293898102162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,22 +5798,22 @@
         <v>15.05707226133306</v>
       </c>
       <c r="K48" t="n">
-        <v>2.991295508888148</v>
+        <v>2.629922890883529</v>
       </c>
       <c r="L48" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M48" t="n">
-        <v>57.89473684210526</v>
+        <v>50.81967213114754</v>
       </c>
       <c r="N48" t="n">
-        <v>14.08651342994457</v>
+        <v>13.8759031246287</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.80514256712792</v>
+        <v>7.181216648630206</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5885,7 +5879,7 @@
         <v>46260</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2698004633242956</v>
+        <v>0.2687595625228552</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5904,7 +5898,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -5917,16 +5911,16 @@
         <v>16.44500858212767</v>
       </c>
       <c r="K49" t="n">
-        <v>8.564663333883992</v>
+        <v>8.145816591814059</v>
       </c>
       <c r="L49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M49" t="n">
-        <v>76.47058823529412</v>
+        <v>81.25</v>
       </c>
       <c r="N49" t="n">
-        <v>17.82085713801315</v>
+        <v>18.23852758951411</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5959,22 +5953,22 @@
         <v>12.16673414089682</v>
       </c>
       <c r="Y49" t="n">
-        <v>3.211353913976067</v>
+        <v>3.584768318235909</v>
       </c>
       <c r="Z49" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA49" t="n">
-        <v>40.38461538461539</v>
+        <v>35.84905660377358</v>
       </c>
       <c r="AB49" t="n">
-        <v>12.0203276350777</v>
+        <v>10.64714131544404</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>7.013886814771963</v>
+        <v>6.653753322855382</v>
       </c>
       <c r="AE49" t="n">
         <v>46</v>
@@ -6008,7 +6002,7 @@
         <v>46260</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6924045470065672</v>
+        <v>0.6949027566863712</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6036,22 +6030,22 @@
         <v>15.88388393069994</v>
       </c>
       <c r="K50" t="n">
-        <v>3.613706870061417</v>
+        <v>3.987547230559096</v>
       </c>
       <c r="L50" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M50" t="n">
-        <v>50</v>
+        <v>57.4468085106383</v>
       </c>
       <c r="N50" t="n">
-        <v>16.78129669195023</v>
+        <v>16.47816984893857</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>0.3728204902687438</v>
+        <v>0.01197525066467531</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6117,7 +6111,7 @@
         <v>46260</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1761197471813865</v>
+        <v>0.1740379455785058</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,22 +6139,22 @@
         <v>21.84334516173415</v>
       </c>
       <c r="K51" t="n">
-        <v>2.297455494942025</v>
+        <v>1.088261124473977</v>
       </c>
       <c r="L51" t="n">
         <v>16</v>
       </c>
       <c r="M51" t="n">
-        <v>50</v>
+        <v>56.25</v>
       </c>
       <c r="N51" t="n">
-        <v>13.39073506465679</v>
+        <v>14.89742569756567</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.664307774636842</v>
+        <v>2.880392681738475</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6226,7 +6220,7 @@
         <v>46260</v>
       </c>
       <c r="C52" t="n">
-        <v>4.482101882509889</v>
+        <v>4.459202024907764</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6286,22 +6280,22 @@
         <v>17.40541420286308</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.070546669024834</v>
+        <v>5.555558170438902</v>
       </c>
       <c r="Z52" t="n">
         <v>22</v>
       </c>
       <c r="AA52" t="n">
-        <v>50</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.83407973743981</v>
+        <v>11.0585103907066</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.085926683641071</v>
+        <v>2.588232597078022</v>
       </c>
       <c r="AE52" t="n">
         <v>38</v>
@@ -6335,7 +6329,7 @@
         <v>46260</v>
       </c>
       <c r="C53" t="n">
-        <v>1.396883535523934</v>
+        <v>1.381270082833449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6367,7 +6361,7 @@
         <v>32.18878367052428</v>
       </c>
       <c r="K53" t="n">
-        <v>3.518680489547399</v>
+        <v>2.361616225203589</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -6376,13 +6370,13 @@
         <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>15.20214662953156</v>
+        <v>16.71756518363199</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4.32899597373162</v>
+        <v>5.508298894374164</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6553,7 +6547,7 @@
         <v>46260</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9517961014098391</v>
+        <v>0.949297891730035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6613,22 +6607,22 @@
         <v>20.41662385315768</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.658343971107335</v>
+        <v>2.913839730103751</v>
       </c>
       <c r="Z55" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AA55" t="n">
-        <v>50</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="AB55" t="n">
-        <v>13.31878217121371</v>
+        <v>13.09752514237847</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.3509864561902054</v>
+        <v>0.08874619168862674</v>
       </c>
       <c r="AE55" t="n">
         <v>46</v>
@@ -6662,7 +6656,7 @@
         <v>46260</v>
       </c>
       <c r="C56" t="n">
-        <v>1.304243779929944</v>
+        <v>1.332347962921373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6679,11 +6673,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>5</v>
       </c>
@@ -6694,17 +6684,13 @@
         <v>19.65620512594927</v>
       </c>
       <c r="K56" t="n">
-        <v>16.55814238139535</v>
+        <v>19.06976744186046</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
-      </c>
-      <c r="M56" t="n">
-        <v>100</v>
-      </c>
-      <c r="N56" t="n">
-        <v>28.61821100734219</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>4</v>
       </c>
@@ -6728,7 +6714,7 @@
         <v>77.60169745451894</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.352765176087738</v>
+        <v>4.334830289502389</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6739,7 +6725,7 @@
         <v>10</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.894652982301361</v>
+        <v>5.921872848437493</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6765,7 +6751,7 @@
         <v>46260</v>
       </c>
       <c r="C57" t="n">
-        <v>1.32193899446105</v>
+        <v>1.311530026000727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6793,22 +6779,22 @@
         <v>22.16703947828081</v>
       </c>
       <c r="K57" t="n">
-        <v>4.709199076790527</v>
+        <v>3.884717194296106</v>
       </c>
       <c r="L57" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="M57" t="n">
-        <v>71.875</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="N57" t="n">
-        <v>20.69688533337153</v>
+        <v>18.16158347653016</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>5.052852060619206</v>
+        <v>5.886604854751121</v>
       </c>
       <c r="Q57" t="n">
         <v>29</v>
@@ -6835,7 +6821,7 @@
         <v>38.8912515650709</v>
       </c>
       <c r="Y57" t="n">
-        <v>18.50173041995328</v>
+        <v>19.14344907806389</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
@@ -6880,7 +6866,7 @@
         <v>46260</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6903227851659459</v>
+        <v>0.693237283635895</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6912,7 +6898,7 @@
         <v>25.99164732164354</v>
       </c>
       <c r="K58" t="n">
-        <v>5.203043674067254</v>
+        <v>5.64720416885427</v>
       </c>
       <c r="L58" t="n">
         <v>5</v>
@@ -6921,13 +6907,13 @@
         <v>80</v>
       </c>
       <c r="N58" t="n">
-        <v>20.17267028505273</v>
+        <v>20.07597438544447</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>2.658626811785103</v>
+        <v>2.227030852028333</v>
       </c>
       <c r="Q58" t="n">
         <v>23</v>
@@ -6993,7 +6979,7 @@
         <v>46260</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8035723332855098</v>
+        <v>0.7998250983944123</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7021,22 +7007,22 @@
         <v>11.19029932893916</v>
       </c>
       <c r="K59" t="n">
-        <v>2.739188191899533</v>
+        <v>2.260092714456152</v>
       </c>
       <c r="L59" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M59" t="n">
-        <v>61.11111111111111</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N59" t="n">
-        <v>13.3915163865691</v>
+        <v>13.28423488391166</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5.120550298951332</v>
+        <v>5.613047214392397</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7102,7 +7088,7 @@
         <v>46260</v>
       </c>
       <c r="C60" t="n">
-        <v>11.66845364402234</v>
+        <v>11.62681777018105</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7130,7 +7116,7 @@
         <v>18.35497088063963</v>
       </c>
       <c r="K60" t="n">
-        <v>1.578555737426335</v>
+        <v>1.216098803483678</v>
       </c>
       <c r="L60" t="n">
         <v>41</v>
@@ -7139,13 +7125,13 @@
         <v>58.53658536585366</v>
       </c>
       <c r="N60" t="n">
-        <v>14.47746955601596</v>
+        <v>14.3286994718115</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.321653439504171</v>
+        <v>6.702393469726231</v>
       </c>
       <c r="Q60" t="n">
         <v>47</v>
@@ -7211,7 +7197,7 @@
         <v>46260</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6232890424376615</v>
+        <v>0.6220399377018492</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7239,22 +7225,22 @@
         <v>18.99064616744801</v>
       </c>
       <c r="K61" t="n">
-        <v>1.429755710278902</v>
+        <v>1.226485029128344</v>
       </c>
       <c r="L61" t="n">
         <v>33</v>
       </c>
       <c r="M61" t="n">
-        <v>66.66666666666667</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="N61" t="n">
-        <v>16.60922402508292</v>
+        <v>16.31282289321498</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>8.449437967888752</v>
+        <v>8.667212902183707</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7273,7 +7259,7 @@
         <v>14.38860808994691</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.32879628142524</v>
+        <v>11.50649813875594</v>
       </c>
       <c r="Z61" t="n">
         <v>19</v>
@@ -7282,7 +7268,7 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AB61" t="n">
-        <v>11.83234893488008</v>
+        <v>11.49661565783674</v>
       </c>
       <c r="AC61" t="n">
         <v>2</v>
@@ -7322,7 +7308,7 @@
         <v>46260</v>
       </c>
       <c r="C62" t="n">
-        <v>9.139074308163794</v>
+        <v>9.102642918552663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7382,16 +7368,16 @@
         <v>12.33548861456359</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.227171492204916</v>
+        <v>2.616926503340766</v>
       </c>
       <c r="Z62" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AA62" t="n">
-        <v>47.45762711864407</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB62" t="n">
-        <v>15.1354421363008</v>
+        <v>16.21263069528937</v>
       </c>
       <c r="AC62" t="n">
         <v>2</v>
@@ -7431,7 +7417,7 @@
         <v>46260</v>
       </c>
       <c r="C63" t="n">
-        <v>0.113041393940061</v>
+        <v>0.1124168614532846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7491,7 +7477,7 @@
         <v>21.38078415792315</v>
       </c>
       <c r="Y63" t="n">
-        <v>5.235605391847809</v>
+        <v>5.759160887402581</v>
       </c>
       <c r="Z63" t="n">
         <v>5</v>
@@ -7506,7 +7492,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>5.027621004547978</v>
+        <v>4.500001435185153</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7540,7 +7526,7 @@
         <v>46260</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1482237085850297</v>
+        <v>0.1480155342121281</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7568,7 +7554,7 @@
         <v>25.85620453775692</v>
       </c>
       <c r="K64" t="n">
-        <v>2.152081843893416</v>
+        <v>2.008613259943881</v>
       </c>
       <c r="L64" t="n">
         <v>27</v>
@@ -7577,13 +7563,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N64" t="n">
-        <v>14.8828864774671</v>
+        <v>15.04299023450893</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>2.787919839420128</v>
+        <v>2.932484468182417</v>
       </c>
       <c r="Q64" t="n">
         <v>54</v>
@@ -7649,7 +7635,7 @@
         <v>46260</v>
       </c>
       <c r="C65" t="n">
-        <v>6.99482680533721</v>
+        <v>6.974008868416563</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7677,7 +7663,7 @@
         <v>23.08687434430191</v>
       </c>
       <c r="K65" t="n">
-        <v>23.47113219605706</v>
+        <v>23.10365858833068</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7715,22 +7701,22 @@
         <v>24.66542142116772</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.9579955784819405</v>
+        <v>1.252763448784089</v>
       </c>
       <c r="Z65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA65" t="n">
-        <v>37.5</v>
+        <v>32</v>
       </c>
       <c r="AB65" t="n">
-        <v>8.299560422847058</v>
+        <v>8.694966192804298</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>3.071428571428581</v>
+        <v>2.782089552238798</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -7764,7 +7750,7 @@
         <v>46260</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4758980507049195</v>
+        <v>0.4813107190924131</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7824,22 +7810,22 @@
         <v>14.56154975385107</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.465517839922703</v>
+        <v>0.3448272300832556</v>
       </c>
       <c r="Z66" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AA66" t="n">
-        <v>38.88888888888889</v>
+        <v>40.81632653061224</v>
       </c>
       <c r="AB66" t="n">
-        <v>10.27632487453329</v>
+        <v>9.922037288572005</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.601924179913652</v>
+        <v>5.674740821505953</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7970,7 +7956,7 @@
         <v>46260</v>
       </c>
       <c r="C68" t="n">
-        <v>4.8339248894794</v>
+        <v>5.037940734796442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8027,10 +8013,10 @@
         <v>81.81818181818181</v>
       </c>
       <c r="X68" t="n">
-        <v>151.8400112220386</v>
+        <v>159.3416285775886</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.191490659574457</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -8041,7 +8027,7 @@
         <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>6.890610318761247</v>
+        <v>7.999999999999996</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -8075,16 +8061,16 @@
         <v>46260</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4509165105785117</v>
+        <v>0.4421729754064053</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8099,17 +8085,27 @@
       <c r="I69" t="n">
         <v>10</v>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>10.04255578723404</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.4730387080678078</v>
+      </c>
       <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="M69" t="n">
+        <v>57.69230769230769</v>
+      </c>
+      <c r="N69" t="n">
+        <v>18.21568942489576</v>
+      </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>7.491523486019336</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -8127,16 +8123,16 @@
         <v>25.43142265824418</v>
       </c>
       <c r="Y69" t="n">
-        <v>7.829787872340432</v>
+        <v>9.61702225531914</v>
       </c>
       <c r="Z69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA69" t="n">
-        <v>28.57142857142857</v>
+        <v>20</v>
       </c>
       <c r="AB69" t="n">
-        <v>12.38000738583723</v>
+        <v>9.653812840176823</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
@@ -8168,7 +8164,7 @@
         <v>46260</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4205223416186905</v>
+        <v>0.4209386701710949</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8196,13 +8192,13 @@
         <v>22.39155244612799</v>
       </c>
       <c r="K70" t="n">
-        <v>10.26765614737826</v>
+        <v>10.37682412519401</v>
       </c>
       <c r="L70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M70" t="n">
-        <v>33.33333333333334</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="N70" t="n">
         <v>12.42488814076528</v>
@@ -8238,22 +8234,22 @@
         <v>15.07139085698337</v>
       </c>
       <c r="Y70" t="n">
-        <v>4.174569086051494</v>
+        <v>4.07969930390778</v>
       </c>
       <c r="Z70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AA70" t="n">
-        <v>32.43243243243244</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB70" t="n">
-        <v>11.15205145045965</v>
+        <v>10.9495070901659</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>3.992083184456274</v>
+        <v>4.087039623148225</v>
       </c>
       <c r="AE70" t="n">
         <v>44</v>
@@ -8287,7 +8283,7 @@
         <v>46260</v>
       </c>
       <c r="C71" t="n">
-        <v>3.214289333558398</v>
+        <v>3.191389793429809</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8315,16 +8311,16 @@
         <v>14.16774499061678</v>
       </c>
       <c r="K71" t="n">
-        <v>3.981710964869123</v>
+        <v>3.240914752773549</v>
       </c>
       <c r="L71" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M71" t="n">
-        <v>57.37704918032787</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N71" t="n">
-        <v>17.92282119072383</v>
+        <v>18.59390630912633</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8396,7 +8392,7 @@
         <v>46260</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07098916677301874</v>
+        <v>0.06953190744134484</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8424,22 +8420,22 @@
         <v>23.28291329508295</v>
       </c>
       <c r="K72" t="n">
-        <v>3.02115262273992</v>
+        <v>0.9063435209609061</v>
       </c>
       <c r="L72" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M72" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N72" t="n">
-        <v>16.54921427825406</v>
+        <v>15.00645247730578</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>1.920816576869955</v>
+        <v>4.05688714524548</v>
       </c>
       <c r="Q72" t="n">
         <v>12</v>
@@ -8466,7 +8462,7 @@
         <v>36.2849179599344</v>
       </c>
       <c r="Y72" t="n">
-        <v>20.9651730180077</v>
+        <v>22.58759295026298</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -8511,7 +8507,7 @@
         <v>46260</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07119734593404584</v>
+        <v>0.07078098761199166</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8528,7 +8524,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8539,22 +8539,22 @@
         <v>25.51322853101174</v>
       </c>
       <c r="K73" t="n">
-        <v>8.219283658787923</v>
+        <v>7.586422998506892</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>62.5</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N73" t="n">
-        <v>10.17048915836387</v>
+        <v>10.78728381292863</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>1.645470456842646</v>
+        <v>2.243384373441448</v>
       </c>
       <c r="Q73" t="n">
         <v>13</v>
@@ -8581,22 +8581,22 @@
         <v>15.39840978549829</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.221165560300923</v>
+        <v>6.769579235547751</v>
       </c>
       <c r="Z73" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA73" t="n">
-        <v>52.63157894736842</v>
+        <v>50</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.4822167630246</v>
+        <v>13.29567252782323</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>4.029517387666948</v>
+        <v>3.464985718142299</v>
       </c>
       <c r="AE73" t="n">
         <v>14</v>
@@ -8630,7 +8630,7 @@
         <v>46260</v>
       </c>
       <c r="C74" t="n">
-        <v>5.54277570512212</v>
+        <v>5.485526378590341</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8690,22 +8690,22 @@
         <v>25.512639367661</v>
       </c>
       <c r="Y74" t="n">
-        <v>5.496465148228181</v>
+        <v>6.472557996462447</v>
       </c>
       <c r="Z74" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA74" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AB74" t="n">
-        <v>15.53953837202927</v>
+        <v>17.75675278568983</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>4.765467089496267</v>
+        <v>3.771558302005229</v>
       </c>
       <c r="AE74" t="n">
         <v>39</v>
@@ -8739,7 +8739,7 @@
         <v>46260</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1255321640032649</v>
+        <v>0.1249076215238787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8767,22 +8767,22 @@
         <v>23.35547482758762</v>
       </c>
       <c r="K75" t="n">
-        <v>1.592201479271282</v>
+        <v>1.086764120631378</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>72.72727272727273</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N75" t="n">
-        <v>14.19840838697934</v>
+        <v>19.66198819310451</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.338717398134229</v>
+        <v>4.860414636980015</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8848,7 +8848,7 @@
         <v>46260</v>
       </c>
       <c r="C76" t="n">
-        <v>1.965213277160469</v>
+        <v>1.955845110200027</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8908,22 +8908,22 @@
         <v>15.91088274943551</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.176164217616594</v>
+        <v>2.6424902072539</v>
       </c>
       <c r="Z76" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA76" t="n">
-        <v>39.1304347826087</v>
+        <v>37.77777777777778</v>
       </c>
       <c r="AB76" t="n">
-        <v>12.26340242104013</v>
+        <v>12.72855854612421</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.864408370206083</v>
+        <v>1.394355500295719</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -8957,7 +8957,7 @@
         <v>46260</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5575043650992886</v>
+        <v>0.555422563496408</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9017,22 +9017,22 @@
         <v>17.9084436362188</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.618179309090907</v>
+        <v>2.981817054545444</v>
       </c>
       <c r="Z77" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AA77" t="n">
-        <v>33.33333333333334</v>
+        <v>29.72972972972973</v>
       </c>
       <c r="AB77" t="n">
-        <v>10.52745124503913</v>
+        <v>10.69135818890833</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>7.580286175115858</v>
+        <v>7.233884136337931</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9066,7 +9066,7 @@
         <v>46260</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04913032905093195</v>
+        <v>0.04871397052069839</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,16 +9094,16 @@
         <v>19.55444062370759</v>
       </c>
       <c r="K78" t="n">
-        <v>5.158425350654117</v>
+        <v>4.267252662287135</v>
       </c>
       <c r="L78" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M78" t="n">
-        <v>57.14285714285715</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N78" t="n">
-        <v>18.09519035765859</v>
+        <v>17.21017009301777</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9175,7 +9175,7 @@
         <v>46260</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8427100769715177</v>
+        <v>0.8377138166609475</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9203,16 +9203,16 @@
         <v>17.82098817333901</v>
       </c>
       <c r="K79" t="n">
-        <v>6.289086793259591</v>
+        <v>5.658919953792863</v>
       </c>
       <c r="L79" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M79" t="n">
-        <v>68.18181818181819</v>
+        <v>68</v>
       </c>
       <c r="N79" t="n">
-        <v>10.75498602908957</v>
+        <v>11.6562330562585</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
@@ -9284,7 +9284,7 @@
         <v>46260</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1305284640760945</v>
+        <v>0.1303202899113723</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>71.23464781554135</v>
       </c>
       <c r="K80" t="n">
-        <v>6.867539403461165</v>
+        <v>6.697101017407192</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -9323,7 +9323,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>2.931161898200663</v>
+        <v>3.095584557685371</v>
       </c>
       <c r="Q80" t="n">
         <v>38</v>
@@ -9350,22 +9350,22 @@
         <v>12.28985457065945</v>
       </c>
       <c r="Y80" t="n">
-        <v>4.828855810643395</v>
+        <v>4.98064012517977</v>
       </c>
       <c r="Z80" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA80" t="n">
-        <v>37.77777777777778</v>
+        <v>38.63636363636363</v>
       </c>
       <c r="AB80" t="n">
-        <v>12.09197351306652</v>
+        <v>11.89118976789149</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>3.332043778991622</v>
+        <v>3.1776259899014</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9399,7 +9399,7 @@
         <v>46260</v>
       </c>
       <c r="C81" t="n">
-        <v>1.205358579556873</v>
+        <v>1.189745126866389</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9459,22 +9459,22 @@
         <v>23.65045506047392</v>
       </c>
       <c r="Y81" t="n">
-        <v>5.237310998577516</v>
+        <v>6.464806937662104</v>
       </c>
       <c r="Z81" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA81" t="n">
-        <v>38.46153846153846</v>
+        <v>60</v>
       </c>
       <c r="AB81" t="n">
-        <v>11.39481103130034</v>
+        <v>9.172334471552661</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>5.025911623667612</v>
+        <v>3.779532544484954</v>
       </c>
       <c r="AE81" t="n">
         <v>30</v>
@@ -9508,7 +9508,7 @@
         <v>46260</v>
       </c>
       <c r="C82" t="n">
-        <v>5.160766435638841</v>
+        <v>5.142030419399675</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>15.46633812458305</v>
       </c>
       <c r="Y82" t="n">
-        <v>7.689932419477441</v>
+        <v>8.025061502879394</v>
       </c>
       <c r="Z82" t="n">
         <v>7</v>
@@ -9577,7 +9577,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="AB82" t="n">
-        <v>7.707406747978768</v>
+        <v>6.869343211763873</v>
       </c>
       <c r="AC82" t="n">
         <v>4</v>
@@ -9617,7 +9617,7 @@
         <v>46260</v>
       </c>
       <c r="C83" t="n">
-        <v>5.922703053923917</v>
+        <v>5.917498569693755</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9677,22 +9677,22 @@
         <v>12.63070246967208</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.901023890784971</v>
+        <v>2.986348122866889</v>
       </c>
       <c r="Z83" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA83" t="n">
-        <v>41.79104477611941</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB83" t="n">
-        <v>13.29647771314206</v>
+        <v>13.15132689498084</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.191564147627435</v>
+        <v>3.106420404573451</v>
       </c>
       <c r="AE83" t="n">
         <v>35</v>
@@ -9726,7 +9726,7 @@
         <v>46260</v>
       </c>
       <c r="C84" t="n">
-        <v>2.15881999517633</v>
+        <v>2.154656471286908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9754,22 +9754,22 @@
         <v>12.58559368645602</v>
       </c>
       <c r="K84" t="n">
-        <v>3.348221531094753</v>
+        <v>3.148903019020843</v>
       </c>
       <c r="L84" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M84" t="n">
-        <v>48.14814814814815</v>
+        <v>47.27272727272727</v>
       </c>
       <c r="N84" t="n">
-        <v>11.36476701015985</v>
+        <v>11.35525530958798</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>1.598265015531286</v>
+        <v>1.794587171361206</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9835,7 +9835,7 @@
         <v>46260</v>
       </c>
       <c r="C85" t="n">
-        <v>6.437946992709917</v>
+        <v>6.422333540019432</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9863,22 +9863,22 @@
         <v>12.61214035274981</v>
       </c>
       <c r="K85" t="n">
-        <v>4.060992956641463</v>
+        <v>3.808621914709431</v>
       </c>
       <c r="L85" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M85" t="n">
-        <v>55.35714285714285</v>
+        <v>54.3859649122807</v>
       </c>
       <c r="N85" t="n">
-        <v>12.24931108700451</v>
+        <v>13.32407414826631</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>3.785286812513688</v>
+        <v>4.037601124051404</v>
       </c>
       <c r="Q85" t="n">
         <v>33</v>
@@ -9944,7 +9944,7 @@
         <v>46260</v>
       </c>
       <c r="C86" t="n">
-        <v>4.627827440954415</v>
+        <v>4.569537154081897</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9972,16 +9972,16 @@
         <v>16.85049362996875</v>
       </c>
       <c r="K86" t="n">
-        <v>8.491952009765292</v>
+        <v>7.125430226769769</v>
       </c>
       <c r="L86" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M86" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="N86" t="n">
-        <v>12.27844673925762</v>
+        <v>15.08322006173449</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
@@ -10014,7 +10014,7 @@
         <v>70.65007079462626</v>
       </c>
       <c r="Y86" t="n">
-        <v>9.789477452668971</v>
+        <v>10.9257335696687</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
@@ -10059,7 +10059,7 @@
         <v>46260</v>
       </c>
       <c r="C87" t="n">
-        <v>5.740546105868261</v>
+        <v>5.730137137407938</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10087,16 +10087,16 @@
         <v>18.00075516267509</v>
       </c>
       <c r="K87" t="n">
-        <v>6.456532214968225</v>
+        <v>6.263501331532195</v>
       </c>
       <c r="L87" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M87" t="n">
-        <v>65</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N87" t="n">
-        <v>9.279963059448857</v>
+        <v>9.744140336298139</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10129,22 +10129,22 @@
         <v>10.60669620884278</v>
       </c>
       <c r="Y87" t="n">
-        <v>3.752181500872598</v>
+        <v>3.926701570680624</v>
       </c>
       <c r="Z87" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA87" t="n">
-        <v>45.94594594594594</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.53063239809339</v>
+        <v>10.71726603719635</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.257479601087951</v>
+        <v>0.07629427792916754</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10178,7 +10178,7 @@
         <v>46260</v>
       </c>
       <c r="C88" t="n">
-        <v>1.138741165380993</v>
+        <v>1.133536681150832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10238,22 +10238,22 @@
         <v>33.98872804376856</v>
       </c>
       <c r="Y88" t="n">
-        <v>4.786771041985272</v>
+        <v>5.221932045802125</v>
       </c>
       <c r="Z88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA88" t="n">
-        <v>72.72727272727273</v>
+        <v>60</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.38078431232302</v>
+        <v>13.50943238616407</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.274223100394711</v>
+        <v>0.8209367114065724</v>
       </c>
       <c r="AE88" t="n">
         <v>32</v>
@@ -10287,7 +10287,7 @@
         <v>46260</v>
       </c>
       <c r="C89" t="n">
-        <v>2.258746155890141</v>
+        <v>2.300382029731434</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10347,22 +10347,22 @@
         <v>27.21456043612742</v>
       </c>
       <c r="Y89" t="n">
-        <v>3.555555555555556</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="Z89" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AA89" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB89" t="n">
-        <v>12.88646361450231</v>
+        <v>12.70823999064093</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>6.682027649769584</v>
+        <v>8.371040723981892</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10396,7 +10396,7 @@
         <v>46260</v>
       </c>
       <c r="C90" t="n">
-        <v>2.956147042731797</v>
+        <v>2.960310566621219</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>28.31474910394056</v>
       </c>
       <c r="Y90" t="n">
-        <v>5.396406243050789</v>
+        <v>5.263163776780145</v>
       </c>
       <c r="Z90" t="n">
         <v>18</v>
@@ -10465,7 +10465,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AB90" t="n">
-        <v>12.9602786450444</v>
+        <v>12.99858432942908</v>
       </c>
       <c r="AC90" t="n">
         <v>3</v>
@@ -10505,7 +10505,7 @@
         <v>46260</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2333690737131643</v>
+        <v>0.2329527053985004</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10533,16 +10533,16 @@
         <v>12.82910965979691</v>
       </c>
       <c r="K91" t="n">
-        <v>4.241534131969127</v>
+        <v>4.055550311602851</v>
       </c>
       <c r="L91" t="n">
         <v>56</v>
       </c>
       <c r="M91" t="n">
-        <v>64.28571428571429</v>
+        <v>66.07142857142857</v>
       </c>
       <c r="N91" t="n">
-        <v>13.70636854701426</v>
+        <v>13.9384196746034</v>
       </c>
       <c r="O91" t="n">
         <v>3</v>
@@ -10614,7 +10614,7 @@
         <v>46260</v>
       </c>
       <c r="C92" t="n">
-        <v>1.123127712690508</v>
+        <v>1.121045871325368</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10631,11 +10631,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>5</v>
       </c>
@@ -10646,22 +10642,22 @@
         <v>17.14668918177976</v>
       </c>
       <c r="K92" t="n">
-        <v>6.593685375579716</v>
+        <v>6.396102196952591</v>
       </c>
       <c r="L92" t="n">
         <v>28</v>
       </c>
       <c r="M92" t="n">
-        <v>75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N92" t="n">
-        <v>12.98401798456282</v>
+        <v>12.83279850063158</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>1.319322640422071</v>
+        <v>1.507477971400117</v>
       </c>
       <c r="Q92" t="n">
         <v>57</v>
@@ -10688,16 +10684,16 @@
         <v>14.66530414303924</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.039286057612138</v>
+        <v>7.211599016709735</v>
       </c>
       <c r="Z92" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA92" t="n">
-        <v>54.05405405405406</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.51843604221565</v>
+        <v>11.83582838031085</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10846,7 +10842,7 @@
         <v>46260</v>
       </c>
       <c r="C94" t="n">
-        <v>7.942042935226623</v>
+        <v>7.910816029845654</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10878,22 +10874,22 @@
         <v>10.06134969325154</v>
       </c>
       <c r="K94" t="n">
-        <v>4.092769440654842</v>
+        <v>3.683492496589369</v>
       </c>
       <c r="L94" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M94" t="n">
-        <v>43.33333333333334</v>
+        <v>40.625</v>
       </c>
       <c r="N94" t="n">
-        <v>13.36504840235806</v>
+        <v>14.0441082191919</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>3.753604193971172</v>
+        <v>4.163157894736846</v>
       </c>
       <c r="Q94" t="n">
         <v>41</v>
@@ -10920,7 +10916,7 @@
         <v>47.10636343143248</v>
       </c>
       <c r="Y94" t="n">
-        <v>6.380368098159517</v>
+        <v>6.748466257668717</v>
       </c>
       <c r="Z94" t="n">
         <v>4</v>
@@ -10929,7 +10925,7 @@
         <v>75</v>
       </c>
       <c r="AB94" t="n">
-        <v>8.912256662677548</v>
+        <v>8.205457218427318</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
@@ -10969,7 +10965,7 @@
         <v>46260</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1384392826040926</v>
+        <v>0.1382310984467607</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10997,22 +10993,22 @@
         <v>26.29234238613365</v>
       </c>
       <c r="K95" t="n">
-        <v>3.775562312631697</v>
+        <v>3.619505248586607</v>
       </c>
       <c r="L95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M95" t="n">
-        <v>60</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N95" t="n">
-        <v>17.65857382010481</v>
+        <v>17.87115840771863</v>
       </c>
       <c r="O95" t="n">
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>2.143508199615463</v>
+        <v>2.297342325368668</v>
       </c>
       <c r="Q95" t="n">
         <v>23</v>
@@ -11039,16 +11035,16 @@
         <v>12.02674045451106</v>
       </c>
       <c r="Y95" t="n">
-        <v>7.365364830220866</v>
+        <v>7.504668235293577</v>
       </c>
       <c r="Z95" t="n">
         <v>22</v>
       </c>
       <c r="AA95" t="n">
-        <v>40.90909090909091</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB95" t="n">
-        <v>12.66316037663308</v>
+        <v>12.49841075723962</v>
       </c>
       <c r="AC95" t="n">
         <v>6</v>
@@ -11088,7 +11084,7 @@
         <v>46260</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1311530065554807</v>
+        <v>0.1299039215967084</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11116,22 +11112,22 @@
         <v>14.68867757321659</v>
       </c>
       <c r="K96" t="n">
-        <v>3.618425541031933</v>
+        <v>2.631576514889189</v>
       </c>
       <c r="L96" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M96" t="n">
-        <v>52.83018867924528</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N96" t="n">
-        <v>15.3409343063313</v>
+        <v>14.09166643988666</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.1587255602924</v>
+        <v>7.179489719756815</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11197,7 +11193,7 @@
         <v>46260</v>
       </c>
       <c r="C97" t="n">
-        <v>1.925659165159797</v>
+        <v>1.919413720588896</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11225,16 +11221,16 @@
         <v>15.29546198849009</v>
       </c>
       <c r="K97" t="n">
-        <v>7.740288103932391</v>
+        <v>7.390856589996631</v>
       </c>
       <c r="L97" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M97" t="n">
-        <v>46.66666666666666</v>
+        <v>46.875</v>
       </c>
       <c r="N97" t="n">
-        <v>15.36480226587528</v>
+        <v>14.96272344862648</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11267,16 +11263,16 @@
         <v>17.48153629159777</v>
       </c>
       <c r="Y97" t="n">
-        <v>8.29172693442387</v>
+        <v>8.589162195287726</v>
       </c>
       <c r="Z97" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA97" t="n">
-        <v>35</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB97" t="n">
-        <v>10.12124489740237</v>
+        <v>10.37055685066437</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11425,7 +11421,7 @@
         <v>46260</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4617418473534989</v>
+        <v>0.4596600455424388</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11453,16 +11449,16 @@
         <v>21.64053449738032</v>
       </c>
       <c r="K99" t="n">
-        <v>4.829186779800199</v>
+        <v>4.356555606903556</v>
       </c>
       <c r="L99" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M99" t="n">
-        <v>57.14285714285715</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N99" t="n">
-        <v>12.14580322778225</v>
+        <v>12.84057962852784</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11534,7 +11530,7 @@
         <v>46260</v>
       </c>
       <c r="C100" t="n">
-        <v>345.0296149773133</v>
+        <v>344.0245396202923</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11594,22 +11590,22 @@
         <v>15.09065341954294</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.184856455557216</v>
+        <v>2.469793127809117</v>
       </c>
       <c r="Z100" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA100" t="n">
-        <v>33.33333333333334</v>
+        <v>32.60869565217391</v>
       </c>
       <c r="AB100" t="n">
-        <v>13.39507036278363</v>
+        <v>13.37159696626481</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>5.945034003656746</v>
+        <v>5.670250325048498</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11643,7 +11639,7 @@
         <v>46260</v>
       </c>
       <c r="C101" t="n">
-        <v>352.2977991847291</v>
+        <v>350.8757145289745</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11703,22 +11699,22 @@
         <v>12.28498792189239</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.6440582342580492</v>
+        <v>1.045118248172627</v>
       </c>
       <c r="Z101" t="n">
         <v>42</v>
       </c>
       <c r="AA101" t="n">
-        <v>45.23809523809524</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.10456531072113</v>
+        <v>12.2563651980264</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>5.390660760249255</v>
+        <v>5.0072130491287</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11752,7 +11748,7 @@
         <v>46260</v>
       </c>
       <c r="C102" t="n">
-        <v>419.9750417522305</v>
+        <v>418.4234548911136</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11812,22 +11808,22 @@
         <v>11.13903673030769</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.498915041772375</v>
+        <v>1.862824736475399</v>
       </c>
       <c r="Z102" t="n">
         <v>37</v>
       </c>
       <c r="AA102" t="n">
-        <v>32.43243243243244</v>
+        <v>29.72972972972973</v>
       </c>
       <c r="AB102" t="n">
-        <v>14.36666630901875</v>
+        <v>12.39601835146762</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>3.554361822219898</v>
+        <v>3.196724640892146</v>
       </c>
       <c r="AE102" t="n">
         <v>24</v>
@@ -11861,7 +11857,7 @@
         <v>46260</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7744272692696803</v>
+        <v>0.7719291391143952</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11921,22 +11917,22 @@
         <v>21.73107604932552</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.156758785057622</v>
+        <v>2.47237932305